--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22FDDCEC-7CC5-4758-9C7F-587FAB2A059D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66627658-B2C2-4097-8D64-509AF0967A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="PL_R1a" sheetId="3" r:id="rId2"/>
-    <sheet name="PL_R1b" sheetId="4" r:id="rId3"/>
+    <sheet name="IT_R1a" sheetId="3" r:id="rId2"/>
+    <sheet name="IT_R1b" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -114,21 +114,6 @@
     <t>Dlltsdsp_L1</t>
   </si>
   <si>
-    <t>PL4</t>
-  </si>
-  <si>
-    <t>PL5</t>
-  </si>
-  <si>
-    <t>PL6</t>
-  </si>
-  <si>
-    <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
-  </si>
-  <si>
-    <t>PL10</t>
-  </si>
-  <si>
     <t>Elig_pen</t>
   </si>
   <si>
@@ -140,35 +125,33 @@
   <si>
     <t>Elig_pen_L1_Sp</t>
   </si>
+  <si>
+    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
+  </si>
+  <si>
+    <t>ITF</t>
+  </si>
+  <si>
+    <t>ITG</t>
+  </si>
+  <si>
+    <t>ITH</t>
+  </si>
+  <si>
+    <t>ITI</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -181,21 +164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -214,12 +183,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,7 +521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -569,7 +535,7 @@
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -590,11 +556,11 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -627,10 +593,10 @@
         <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
         <v>13</v>
@@ -660,16 +626,16 @@
         <v>21</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="S1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="T1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="U1" t="s">
         <v>22</v>
@@ -688,1628 +654,1628 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4">
-        <v>2.6343611823775308E-2</v>
+      <c r="B2">
+        <v>0.22998112918573135</v>
       </c>
       <c r="C2">
-        <v>5.3668579583419406E-3</v>
+        <v>1.7020791590843191E-3</v>
       </c>
       <c r="D2">
-        <v>-2.7719915297806912E-4</v>
+        <v>-5.614398686302799E-5</v>
       </c>
       <c r="E2">
-        <v>1.8920096068991333E-6</v>
+        <v>4.4409870650847396E-7</v>
       </c>
       <c r="F2">
-        <v>-4.6433616180181422E-3</v>
+        <v>-1.0808630481981776E-4</v>
       </c>
       <c r="G2">
-        <v>-3.6776803093065925E-3</v>
+        <v>4.4904890822141234E-5</v>
       </c>
       <c r="H2">
-        <v>-2.7843486652685216E-4</v>
+        <v>-2.5856304136416953E-4</v>
       </c>
       <c r="I2">
-        <v>-1.7753917657219089E-4</v>
+        <v>-5.0634096087199426E-5</v>
       </c>
       <c r="J2">
-        <v>2.4639112621217506E-3</v>
+        <v>3.7224195143447454E-4</v>
       </c>
       <c r="K2">
-        <v>5.0829113200582469E-4</v>
+        <v>2.1027824044394472E-4</v>
       </c>
       <c r="L2">
-        <v>1.0635959103853375E-4</v>
+        <v>-1.2114777377603185E-4</v>
       </c>
       <c r="M2">
-        <v>-5.844408574935925E-4</v>
+        <v>-5.4049268603414383E-6</v>
       </c>
       <c r="N2">
-        <v>2.2991545278116914E-5</v>
+        <v>-3.112135246937004E-4</v>
       </c>
       <c r="O2">
-        <v>-2.4270331619106783E-4</v>
+        <v>-4.8831263666758136E-4</v>
       </c>
       <c r="P2">
-        <v>-6.8772113354153923E-4</v>
+        <v>-5.1058898359563547E-4</v>
       </c>
       <c r="Q2">
-        <v>-4.5090525248299256E-4</v>
+        <v>1.553474449606079E-4</v>
       </c>
       <c r="R2">
-        <v>-8.9018126526219793E-5</v>
+        <v>-1.8797879356674985E-4</v>
       </c>
       <c r="S2">
-        <v>-1.0229633540871381E-4</v>
+        <v>-2.0908544040013001E-5</v>
       </c>
       <c r="T2">
-        <v>-1.8970289536642709E-4</v>
+        <v>2.3529380347903371E-5</v>
       </c>
       <c r="U2">
-        <v>-1.1324460160590867E-5</v>
+        <v>1.2968942956576634E-5</v>
       </c>
       <c r="V2">
-        <v>-1.9936894281242699E-4</v>
+        <v>7.0167077762441703E-5</v>
       </c>
       <c r="W2">
-        <v>1.5645308944060334E-5</v>
+        <v>-1.7881476909892036E-4</v>
       </c>
       <c r="X2">
-        <v>7.6543356479846503E-3</v>
+        <v>9.828460085670827E-4</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
-        <v>0.3181959903630372</v>
+      <c r="B3">
+        <v>0.62322187179225863</v>
       </c>
       <c r="C3">
-        <v>-2.7719915297806912E-4</v>
+        <v>-5.614398686302799E-5</v>
       </c>
       <c r="D3">
-        <v>2.5668484214542431E-3</v>
+        <v>1.3422217047275092E-3</v>
       </c>
       <c r="E3">
-        <v>-1.8538210495775125E-5</v>
+        <v>-9.5313476064370976E-6</v>
       </c>
       <c r="F3">
-        <v>-3.8862744131162516E-4</v>
+        <v>-1.5637336153288741E-4</v>
       </c>
       <c r="G3">
-        <v>-1.3756356167799154E-3</v>
+        <v>-2.2612256997407102E-4</v>
       </c>
       <c r="H3">
-        <v>-1.2282647977942228E-4</v>
+        <v>3.2439744495514275E-5</v>
       </c>
       <c r="I3">
-        <v>3.5126047238841218E-5</v>
+        <v>3.5959808069365232E-5</v>
       </c>
       <c r="J3">
-        <v>-3.1305657485458244E-3</v>
+        <v>-7.3647252124877348E-4</v>
       </c>
       <c r="K3">
-        <v>-1.0048781554374518E-4</v>
+        <v>-8.6512334449860562E-5</v>
       </c>
       <c r="L3">
-        <v>-3.4144511261048963E-5</v>
+        <v>1.3365469505967727E-4</v>
       </c>
       <c r="M3">
-        <v>-1.3848462602997474E-4</v>
+        <v>1.0786887447586033E-4</v>
       </c>
       <c r="N3">
-        <v>-8.0963781757079079E-5</v>
+        <v>2.3830195897339874E-4</v>
       </c>
       <c r="O3">
-        <v>-2.7993113199366662E-4</v>
+        <v>1.2676641342715053E-4</v>
       </c>
       <c r="P3">
-        <v>-3.4546758669357254E-4</v>
+        <v>-3.2102528274203027E-5</v>
       </c>
       <c r="Q3">
-        <v>3.4574498054642036E-4</v>
+        <v>-2.4934892580094452E-4</v>
       </c>
       <c r="R3">
-        <v>1.8422387502360985E-4</v>
+        <v>-2.4310981119817464E-4</v>
       </c>
       <c r="S3">
-        <v>2.5685998969708981E-4</v>
+        <v>-6.3948372772215309E-5</v>
       </c>
       <c r="T3">
-        <v>4.5406255584136629E-4</v>
+        <v>-1.9561435392379499E-4</v>
       </c>
       <c r="U3">
-        <v>-1.3404151775062525E-5</v>
+        <v>-2.1657460727906143E-5</v>
       </c>
       <c r="V3">
-        <v>3.4788948626124708E-5</v>
+        <v>5.5424101516887009E-5</v>
       </c>
       <c r="W3">
-        <v>-1.8142000347178694E-4</v>
+        <v>-6.5897830156759832E-5</v>
       </c>
       <c r="X3">
-        <v>-8.4567787563106789E-2</v>
+        <v>-4.5569479181656131E-2</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
-        <v>-2.3715695251981966E-3</v>
+      <c r="B4">
+        <v>-4.3462167958222119E-3</v>
       </c>
       <c r="C4">
-        <v>1.8920096068991333E-6</v>
+        <v>4.4409870650847396E-7</v>
       </c>
       <c r="D4">
-        <v>-1.8538210495775125E-5</v>
+        <v>-9.5313476064370976E-6</v>
       </c>
       <c r="E4">
-        <v>1.3457292939635774E-7</v>
+        <v>6.8367008855067024E-8</v>
       </c>
       <c r="F4">
-        <v>3.2315641303405011E-6</v>
+        <v>1.7893946659305985E-6</v>
       </c>
       <c r="G4">
-        <v>9.9409808974975072E-6</v>
+        <v>2.2115500777097791E-6</v>
       </c>
       <c r="H4">
-        <v>9.8112878460748613E-7</v>
+        <v>-2.0593825206629331E-7</v>
       </c>
       <c r="I4">
-        <v>-4.1039134946190166E-7</v>
+        <v>-3.2353270977064023E-7</v>
       </c>
       <c r="J4">
-        <v>2.1610939456789656E-5</v>
+        <v>3.9262931312461467E-6</v>
       </c>
       <c r="K4">
-        <v>3.7724976782131382E-7</v>
+        <v>5.018275744685696E-7</v>
       </c>
       <c r="L4">
-        <v>1.5569365569310717E-7</v>
+        <v>-9.3746123465261359E-7</v>
       </c>
       <c r="M4">
-        <v>1.067762896292385E-6</v>
+        <v>-6.225705231806413E-7</v>
       </c>
       <c r="N4">
-        <v>7.6469728831407894E-7</v>
+        <v>-1.553823230643895E-6</v>
       </c>
       <c r="O4">
-        <v>2.1490370786274093E-6</v>
+        <v>-8.1288867895539397E-7</v>
       </c>
       <c r="P4">
-        <v>2.7146379352560677E-6</v>
+        <v>2.3206820198426247E-7</v>
       </c>
       <c r="Q4">
-        <v>-2.44371537367534E-6</v>
+        <v>1.8265184703276574E-6</v>
       </c>
       <c r="R4">
-        <v>-1.4785204240020582E-6</v>
+        <v>1.6928956128348815E-6</v>
       </c>
       <c r="S4">
-        <v>-1.9888802995509953E-6</v>
+        <v>4.2099051499104546E-7</v>
       </c>
       <c r="T4">
-        <v>-3.2683282910578023E-6</v>
+        <v>1.3033922271891339E-6</v>
       </c>
       <c r="U4">
-        <v>1.0014663766217625E-7</v>
+        <v>1.4223959351566777E-7</v>
       </c>
       <c r="V4">
-        <v>-2.2960131475809173E-7</v>
+        <v>-3.9682743802403028E-7</v>
       </c>
       <c r="W4">
-        <v>1.27896864324413E-6</v>
+        <v>3.2193975308948642E-7</v>
       </c>
       <c r="X4">
-        <v>6.0860329152661978E-4</v>
+        <v>3.2133579636969248E-4</v>
       </c>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="4">
-        <v>-5.4060965547403077E-2</v>
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>0.23479384788814828</v>
       </c>
       <c r="C5">
-        <v>-4.6433616180181422E-3</v>
+        <v>-1.0808630481981776E-4</v>
       </c>
       <c r="D5">
-        <v>-3.8862744131162516E-4</v>
+        <v>-1.5637336153288741E-4</v>
       </c>
       <c r="E5">
-        <v>3.2315641303405011E-6</v>
+        <v>1.7893946659305985E-6</v>
       </c>
       <c r="F5">
-        <v>1.5825368195614819E-2</v>
+        <v>8.6293143029709512E-3</v>
       </c>
       <c r="G5">
-        <v>4.1235215762363258E-3</v>
+        <v>-1.3880899169022138E-3</v>
       </c>
       <c r="H5">
-        <v>4.0281872018644183E-4</v>
+        <v>-1.834348454667848E-5</v>
       </c>
       <c r="I5">
-        <v>3.0705554862836505E-4</v>
+        <v>8.7045757070425452E-5</v>
       </c>
       <c r="J5">
-        <v>-2.5190367446812105E-3</v>
+        <v>-1.9619946988589342E-3</v>
       </c>
       <c r="K5">
-        <v>-4.468439400441617E-4</v>
+        <v>2.3466264384647121E-4</v>
       </c>
       <c r="L5">
-        <v>3.3787023733376342E-5</v>
+        <v>-7.8362714848679795E-5</v>
       </c>
       <c r="M5">
-        <v>3.1482580280244943E-4</v>
+        <v>-1.9254464959928962E-4</v>
       </c>
       <c r="N5">
-        <v>6.5726871856437892E-4</v>
+        <v>-1.7429388959566607E-5</v>
       </c>
       <c r="O5">
-        <v>3.8665594355202738E-4</v>
+        <v>-1.7495300318323736E-4</v>
       </c>
       <c r="P5">
-        <v>-2.823565070913703E-4</v>
+        <v>-7.9731745316214764E-5</v>
       </c>
       <c r="Q5">
-        <v>8.4795382028646444E-4</v>
+        <v>-9.3481757255879823E-5</v>
       </c>
       <c r="R5">
-        <v>-1.7891080780154008E-4</v>
+        <v>-1.077979316841469E-4</v>
       </c>
       <c r="S5">
-        <v>-2.1899761468195797E-4</v>
+        <v>-9.9366022642346369E-5</v>
       </c>
       <c r="T5">
-        <v>-4.8695436244397408E-4</v>
+        <v>-1.3411948146053944E-4</v>
       </c>
       <c r="U5">
-        <v>-5.7633243204244939E-5</v>
+        <v>-2.8667399687093604E-5</v>
       </c>
       <c r="V5">
-        <v>1.9417590047065102E-4</v>
+        <v>1.9712251969617237E-4</v>
       </c>
       <c r="W5">
-        <v>1.2809451426632184E-4</v>
+        <v>2.4895788473839079E-4</v>
       </c>
       <c r="X5">
-        <v>1.4397331009588232E-2</v>
+        <v>3.5444588136896646E-3</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.60522845759132438</v>
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.25826583193833513</v>
       </c>
       <c r="C6">
-        <v>-3.6776803093065925E-3</v>
+        <v>4.4904890822141234E-5</v>
       </c>
       <c r="D6">
-        <v>-1.3756356167799154E-3</v>
+        <v>-2.2612256997407102E-4</v>
       </c>
       <c r="E6">
-        <v>9.9409808974975072E-6</v>
+        <v>2.2115500777097791E-6</v>
       </c>
       <c r="F6">
-        <v>4.1235215762363258E-3</v>
+        <v>-1.3880899169022138E-3</v>
       </c>
       <c r="G6">
-        <v>1.1558658214574604E-2</v>
+        <v>8.3551970033034287E-3</v>
       </c>
       <c r="H6">
-        <v>6.0818387818930425E-5</v>
+        <v>-1.4084637520637554E-4</v>
       </c>
       <c r="I6">
-        <v>1.2064215171368048E-4</v>
+        <v>-4.5112218177005038E-5</v>
       </c>
       <c r="J6">
-        <v>5.3743779962185136E-4</v>
+        <v>-1.6704932942320106E-3</v>
       </c>
       <c r="K6">
-        <v>-1.558382003366901E-4</v>
+        <v>2.6720374651377553E-4</v>
       </c>
       <c r="L6">
-        <v>6.482752066134384E-5</v>
+        <v>-1.0673722520163661E-4</v>
       </c>
       <c r="M6">
-        <v>5.2159586973511522E-4</v>
+        <v>-6.3962884729208387E-5</v>
       </c>
       <c r="N6">
-        <v>1.893107110076224E-4</v>
+        <v>-1.43138160232259E-4</v>
       </c>
       <c r="O6">
-        <v>3.9618009994061773E-4</v>
+        <v>-8.8339540572557416E-5</v>
       </c>
       <c r="P6">
-        <v>3.7774064400202369E-4</v>
+        <v>-6.3195224674416706E-5</v>
       </c>
       <c r="Q6">
-        <v>1.6709534463342762E-4</v>
+        <v>-7.1385934498273016E-5</v>
       </c>
       <c r="R6">
-        <v>1.1168626672433506E-4</v>
+        <v>-2.7297467645640591E-4</v>
       </c>
       <c r="S6">
-        <v>-3.3655972360597305E-4</v>
+        <v>2.4193804931321294E-5</v>
       </c>
       <c r="T6">
-        <v>-4.4306370508044845E-4</v>
+        <v>-8.3345793615817888E-5</v>
       </c>
       <c r="U6">
-        <v>-1.4862197364529512E-5</v>
+        <v>-1.6924789068817206E-5</v>
       </c>
       <c r="V6">
-        <v>-3.1845428339174206E-5</v>
+        <v>1.5470403159916326E-5</v>
       </c>
       <c r="W6">
-        <v>4.3526462312966883E-4</v>
+        <v>-1.0271957056281859E-4</v>
       </c>
       <c r="X6">
-        <v>4.6632872781196821E-2</v>
+        <v>6.0106919686074498E-3</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4">
-        <v>-4.8836963145182724E-2</v>
+      <c r="B7">
+        <v>4.8163041551457779E-2</v>
       </c>
       <c r="C7">
-        <v>-2.7843486652685216E-4</v>
+        <v>-2.5856304136416953E-4</v>
       </c>
       <c r="D7">
-        <v>-1.2282647977942228E-4</v>
+        <v>3.2439744495514275E-5</v>
       </c>
       <c r="E7">
-        <v>9.8112878460748613E-7</v>
+        <v>-2.0593825206629331E-7</v>
       </c>
       <c r="F7">
-        <v>4.0281872018644183E-4</v>
+        <v>-1.834348454667848E-5</v>
       </c>
       <c r="G7">
-        <v>6.0818387818930425E-5</v>
+        <v>-1.4084637520637554E-4</v>
       </c>
       <c r="H7">
-        <v>6.2822670539382655E-3</v>
+        <v>2.7458838248491657E-3</v>
       </c>
       <c r="I7">
-        <v>5.9313841182509789E-3</v>
+        <v>2.0299845977886713E-3</v>
       </c>
       <c r="J7">
-        <v>1.2269301862180343E-4</v>
+        <v>-1.4867163228958892E-5</v>
       </c>
       <c r="K7">
-        <v>-3.8497761691685657E-4</v>
+        <v>-4.2581298883898435E-4</v>
       </c>
       <c r="L7">
-        <v>-2.8396117869529923E-5</v>
+        <v>-9.8879532510809441E-6</v>
       </c>
       <c r="M7">
-        <v>3.8416953814995338E-4</v>
+        <v>-7.3042663369066326E-5</v>
       </c>
       <c r="N7">
-        <v>8.4320619222859057E-4</v>
+        <v>-2.1416435374224749E-4</v>
       </c>
       <c r="O7">
-        <v>3.2419067167904479E-3</v>
+        <v>4.2995755551848626E-4</v>
       </c>
       <c r="P7">
-        <v>8.0595752355284121E-8</v>
+        <v>1.4254276448890258E-5</v>
       </c>
       <c r="Q7">
-        <v>1.61783154657442E-4</v>
+        <v>7.2052685367862798E-5</v>
       </c>
       <c r="R7">
-        <v>-1.6802371965335123E-4</v>
+        <v>2.3272290795791598E-4</v>
       </c>
       <c r="S7">
-        <v>2.760091848339136E-6</v>
+        <v>-1.1293050367463782E-5</v>
       </c>
       <c r="T7">
-        <v>1.9543567043054153E-5</v>
+        <v>-5.1098474064123749E-5</v>
       </c>
       <c r="U7">
-        <v>1.5342265415308932E-5</v>
+        <v>1.8961281724561984E-5</v>
       </c>
       <c r="V7">
-        <v>-4.7903373677727289E-6</v>
+        <v>-9.357905184582049E-5</v>
       </c>
       <c r="W7">
-        <v>1.140654028563377E-5</v>
+        <v>-2.8531020893252427E-4</v>
       </c>
       <c r="X7">
-        <v>-2.2998120395008731E-3</v>
+        <v>-3.2021165840525612E-3</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="4">
-        <v>-0.24874574281994752</v>
+      <c r="B8">
+        <v>1.4261546141064077E-2</v>
       </c>
       <c r="C8">
-        <v>-1.7753917657219089E-4</v>
+        <v>-5.0634096087199426E-5</v>
       </c>
       <c r="D8">
-        <v>3.5126047238841218E-5</v>
+        <v>3.5959808069365232E-5</v>
       </c>
       <c r="E8">
-        <v>-4.1039134946190166E-7</v>
+        <v>-3.2353270977064023E-7</v>
       </c>
       <c r="F8">
-        <v>3.0705554862836505E-4</v>
+        <v>8.7045757070425452E-5</v>
       </c>
       <c r="G8">
-        <v>1.2064215171368048E-4</v>
+        <v>-4.5112218177005038E-5</v>
       </c>
       <c r="H8">
-        <v>5.9313841182509789E-3</v>
+        <v>2.0299845977886713E-3</v>
       </c>
       <c r="I8">
-        <v>7.9839268103995345E-3</v>
+        <v>2.9027551204147718E-3</v>
       </c>
       <c r="J8">
-        <v>6.8876488419936707E-5</v>
+        <v>-1.0677293934852191E-4</v>
       </c>
       <c r="K8">
-        <v>-7.4932287084550049E-4</v>
+        <v>-5.5422431617530932E-4</v>
       </c>
       <c r="L8">
-        <v>-9.5063480626907679E-5</v>
+        <v>9.807976383711443E-5</v>
       </c>
       <c r="M8">
-        <v>4.2855158499598102E-4</v>
+        <v>2.8557926751862769E-4</v>
       </c>
       <c r="N8">
-        <v>1.0069029894225802E-3</v>
+        <v>3.0831952862965441E-5</v>
       </c>
       <c r="O8">
-        <v>3.3970657654480048E-3</v>
+        <v>8.3036959235938135E-4</v>
       </c>
       <c r="P8">
-        <v>2.5267622229004473E-6</v>
+        <v>-1.7861127686384344E-5</v>
       </c>
       <c r="Q8">
-        <v>1.5577456237941345E-4</v>
+        <v>6.3116284849172892E-5</v>
       </c>
       <c r="R8">
-        <v>-1.4406263831567021E-4</v>
+        <v>5.1320575761931936E-5</v>
       </c>
       <c r="S8">
-        <v>-4.8497600330886775E-5</v>
+        <v>-7.0650423620749817E-5</v>
       </c>
       <c r="T8">
-        <v>-8.0460027071795488E-5</v>
+        <v>-1.0799987451518564E-4</v>
       </c>
       <c r="U8">
-        <v>3.611673980905823E-5</v>
+        <v>2.6038174193982952E-5</v>
       </c>
       <c r="V8">
-        <v>7.561009290744285E-8</v>
+        <v>-1.507512047668792E-4</v>
       </c>
       <c r="W8">
-        <v>3.1649876239178351E-5</v>
+        <v>-3.5961257294858879E-4</v>
       </c>
       <c r="X8">
-        <v>-7.1321262605937019E-3</v>
+        <v>-3.4336828012955511E-3</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4">
-        <v>1.324675467255426</v>
+      <c r="B9">
+        <v>-6.6368314335145022E-3</v>
       </c>
       <c r="C9">
-        <v>2.4639112621217506E-3</v>
+        <v>3.7224195143447454E-4</v>
       </c>
       <c r="D9">
-        <v>-3.1305657485458244E-3</v>
+        <v>-7.3647252124877348E-4</v>
       </c>
       <c r="E9">
-        <v>2.1610939456789656E-5</v>
+        <v>3.9262931312461467E-6</v>
       </c>
       <c r="F9">
-        <v>-2.5190367446812105E-3</v>
+        <v>-1.9619946988589342E-3</v>
       </c>
       <c r="G9">
-        <v>5.3743779962185136E-4</v>
+        <v>-1.6704932942320106E-3</v>
       </c>
       <c r="H9">
-        <v>1.2269301862180343E-4</v>
+        <v>-1.4867163228958892E-5</v>
       </c>
       <c r="I9">
-        <v>6.8876488419936707E-5</v>
+        <v>-1.0677293934852191E-4</v>
       </c>
       <c r="J9">
-        <v>8.5162299550266586E-3</v>
+        <v>4.6971573946409141E-3</v>
       </c>
       <c r="K9">
-        <v>7.7245389523948344E-5</v>
+        <v>-2.0795282759234856E-4</v>
       </c>
       <c r="L9">
-        <v>2.282283555950556E-4</v>
+        <v>-2.2364463656005874E-5</v>
       </c>
       <c r="M9">
-        <v>2.2314591418818013E-4</v>
+        <v>7.5296355466448247E-5</v>
       </c>
       <c r="N9">
-        <v>1.8890408864855393E-4</v>
+        <v>2.0870254285064189E-4</v>
       </c>
       <c r="O9">
-        <v>3.123480933953475E-4</v>
+        <v>2.7035363338898154E-4</v>
       </c>
       <c r="P9">
-        <v>6.2237773173130437E-4</v>
+        <v>2.0042412272291456E-5</v>
       </c>
       <c r="Q9">
-        <v>-8.0867858516690469E-4</v>
+        <v>1.4696850123456636E-4</v>
       </c>
       <c r="R9">
-        <v>4.1322779688653805E-5</v>
+        <v>2.6652123611358965E-4</v>
       </c>
       <c r="S9">
-        <v>-1.8626505865663653E-4</v>
+        <v>1.6343181816298215E-4</v>
       </c>
       <c r="T9">
-        <v>-4.6946608921159122E-4</v>
+        <v>3.0376354830611131E-4</v>
       </c>
       <c r="U9">
-        <v>1.4323600843936784E-5</v>
+        <v>4.7273086918398714E-5</v>
       </c>
       <c r="V9">
-        <v>-8.2372482179821072E-6</v>
+        <v>-1.6696500194858695E-5</v>
       </c>
       <c r="W9">
-        <v>5.203610798507341E-4</v>
+        <v>2.8668575943555444E-4</v>
       </c>
       <c r="X9">
-        <v>0.10359730768003406</v>
+        <v>2.8127789996577932E-2</v>
       </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4">
-        <v>-3.8265035805041502E-2</v>
+      <c r="B10">
+        <v>0.39941543818973613</v>
       </c>
       <c r="C10">
-        <v>5.0829113200582469E-4</v>
+        <v>2.1027824044394472E-4</v>
       </c>
       <c r="D10">
-        <v>-1.0048781554374518E-4</v>
+        <v>-8.6512334449860562E-5</v>
       </c>
       <c r="E10">
-        <v>3.7724976782131382E-7</v>
+        <v>5.018275744685696E-7</v>
       </c>
       <c r="F10">
-        <v>-4.468439400441617E-4</v>
+        <v>2.3466264384647121E-4</v>
       </c>
       <c r="G10">
-        <v>-1.558382003366901E-4</v>
+        <v>2.6720374651377553E-4</v>
       </c>
       <c r="H10">
-        <v>-3.8497761691685657E-4</v>
+        <v>-4.2581298883898435E-4</v>
       </c>
       <c r="I10">
-        <v>-7.4932287084550049E-4</v>
+        <v>-5.5422431617530932E-4</v>
       </c>
       <c r="J10">
-        <v>7.7245389523948344E-5</v>
+        <v>-2.0795282759234856E-4</v>
       </c>
       <c r="K10">
-        <v>8.5645993713182756E-3</v>
+        <v>3.7011682585107817E-3</v>
       </c>
       <c r="L10">
-        <v>8.7724498626597005E-5</v>
+        <v>1.6294324064392166E-5</v>
       </c>
       <c r="M10">
-        <v>3.8187677034152074E-3</v>
+        <v>9.3940496506934455E-4</v>
       </c>
       <c r="N10">
-        <v>6.9601363851319875E-3</v>
+        <v>2.5616173714592613E-3</v>
       </c>
       <c r="O10">
-        <v>7.1697600417376696E-3</v>
+        <v>2.5730298487589526E-3</v>
       </c>
       <c r="P10">
-        <v>-1.4751297373827054E-3</v>
+        <v>-4.2346694574074375E-4</v>
       </c>
       <c r="Q10">
-        <v>2.6044992468864515E-4</v>
+        <v>-3.1348623754018048E-4</v>
       </c>
       <c r="R10">
-        <v>-3.8269899229402158E-5</v>
+        <v>-7.3143722303468462E-5</v>
       </c>
       <c r="S10">
-        <v>-1.4574904422939741E-4</v>
+        <v>5.1670636040525774E-5</v>
       </c>
       <c r="T10">
-        <v>3.2537705910654351E-4</v>
+        <v>4.455067477793619E-5</v>
       </c>
       <c r="U10">
-        <v>8.0141356386209596E-5</v>
+        <v>-1.8187881926069277E-5</v>
       </c>
       <c r="V10">
-        <v>-5.970480753483469E-4</v>
+        <v>2.9393006523171106E-4</v>
       </c>
       <c r="W10">
-        <v>-4.1935670615840981E-4</v>
+        <v>1.4936873688883834E-4</v>
       </c>
       <c r="X10">
-        <v>-3.886351712518131E-3</v>
+        <v>1.0442731807533932E-3</v>
       </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="4">
-        <v>-2.2379294471970582E-2</v>
+      <c r="B11">
+        <v>4.8557956790069565E-2</v>
       </c>
       <c r="C11">
-        <v>1.0635959103853375E-4</v>
+        <v>-1.2114777377603185E-4</v>
       </c>
       <c r="D11">
-        <v>-3.4144511261048963E-5</v>
+        <v>1.3365469505967727E-4</v>
       </c>
       <c r="E11">
-        <v>1.5569365569310717E-7</v>
+        <v>-9.3746123465261359E-7</v>
       </c>
       <c r="F11">
-        <v>3.3787023733376342E-5</v>
+        <v>-7.8362714848679795E-5</v>
       </c>
       <c r="G11">
-        <v>6.482752066134384E-5</v>
+        <v>-1.0673722520163661E-4</v>
       </c>
       <c r="H11">
-        <v>-2.8396117869529923E-5</v>
+        <v>-9.8879532510809441E-6</v>
       </c>
       <c r="I11">
-        <v>-9.5063480626907679E-5</v>
+        <v>9.807976383711443E-5</v>
       </c>
       <c r="J11">
-        <v>2.282283555950556E-4</v>
+        <v>-2.2364463656005874E-5</v>
       </c>
       <c r="K11">
-        <v>8.7724498626597005E-5</v>
+        <v>1.6294324064392166E-5</v>
       </c>
       <c r="L11">
-        <v>2.8384895375316182E-3</v>
+        <v>1.5361863222091198E-3</v>
       </c>
       <c r="M11">
-        <v>1.4206614753360764E-3</v>
+        <v>7.5947130712913913E-4</v>
       </c>
       <c r="N11">
-        <v>1.4013029320487115E-3</v>
+        <v>8.2800392410344774E-4</v>
       </c>
       <c r="O11">
-        <v>1.3876849597985194E-3</v>
+        <v>8.8931060775672476E-4</v>
       </c>
       <c r="P11">
-        <v>-2.5751056481954928E-4</v>
+        <v>2.4636038076436046E-4</v>
       </c>
       <c r="Q11">
-        <v>-6.1838779001913418E-5</v>
+        <v>1.511375291290164E-4</v>
       </c>
       <c r="R11">
-        <v>-1.7911782456869112E-4</v>
+        <v>1.3731456188678301E-4</v>
       </c>
       <c r="S11">
-        <v>3.9487288328093168E-5</v>
+        <v>1.5400546516053707E-5</v>
       </c>
       <c r="T11">
-        <v>-1.2996507442466351E-4</v>
+        <v>-4.6039777457916077E-6</v>
       </c>
       <c r="U11">
-        <v>-1.1191905305022853E-5</v>
+        <v>1.0648834815214715E-5</v>
       </c>
       <c r="V11">
-        <v>5.8595607596281926E-5</v>
+        <v>-2.2740963322433698E-4</v>
       </c>
       <c r="W11">
-        <v>5.8589092771857637E-5</v>
+        <v>-1.9755096550922975E-4</v>
       </c>
       <c r="X11">
-        <v>2.390619750444814E-4</v>
+        <v>-5.6209306917620484E-3</v>
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="4">
-        <v>0.16294886485561291</v>
+      <c r="B12">
+        <v>8.324986155760998E-2</v>
       </c>
       <c r="C12">
-        <v>-5.844408574935925E-4</v>
+        <v>-5.4049268603414383E-6</v>
       </c>
       <c r="D12">
-        <v>-1.3848462602997474E-4</v>
+        <v>1.0786887447586033E-4</v>
       </c>
       <c r="E12">
-        <v>1.067762896292385E-6</v>
+        <v>-6.225705231806413E-7</v>
       </c>
       <c r="F12">
-        <v>3.1482580280244943E-4</v>
+        <v>-1.9254464959928962E-4</v>
       </c>
       <c r="G12">
-        <v>5.2159586973511522E-4</v>
+        <v>-6.3962884729208387E-5</v>
       </c>
       <c r="H12">
-        <v>3.8416953814995338E-4</v>
+        <v>-7.3042663369066326E-5</v>
       </c>
       <c r="I12">
-        <v>4.2855158499598102E-4</v>
+        <v>2.8557926751862769E-4</v>
       </c>
       <c r="J12">
-        <v>2.2314591418818013E-4</v>
+        <v>7.5296355466448247E-5</v>
       </c>
       <c r="K12">
-        <v>3.8187677034152074E-3</v>
+        <v>9.3940496506934455E-4</v>
       </c>
       <c r="L12">
-        <v>1.4206614753360764E-3</v>
+        <v>7.5947130712913913E-4</v>
       </c>
       <c r="M12">
-        <v>6.1777682459215255E-3</v>
+        <v>3.145142660462659E-3</v>
       </c>
       <c r="N12">
-        <v>5.33546472340252E-3</v>
+        <v>2.0781272389979806E-3</v>
       </c>
       <c r="O12">
-        <v>5.6149275806504032E-3</v>
+        <v>2.2276453424161431E-3</v>
       </c>
       <c r="P12">
-        <v>1.5694294519553943E-5</v>
+        <v>8.3934901531948079E-5</v>
       </c>
       <c r="Q12">
-        <v>1.9145598516012935E-5</v>
+        <v>3.9374504148149899E-4</v>
       </c>
       <c r="R12">
-        <v>-4.0416158840703739E-4</v>
+        <v>5.1057785978522383E-4</v>
       </c>
       <c r="S12">
-        <v>-2.0584432238953169E-4</v>
+        <v>7.0866712507610037E-5</v>
       </c>
       <c r="T12">
-        <v>-1.8715223490815185E-4</v>
+        <v>8.8411283400370707E-5</v>
       </c>
       <c r="U12">
-        <v>6.2061495991615645E-6</v>
+        <v>9.2588776716026838E-6</v>
       </c>
       <c r="V12">
-        <v>1.0191725340045479E-4</v>
+        <v>-1.6291297573435196E-4</v>
       </c>
       <c r="W12">
-        <v>-1.8046623580512868E-4</v>
+        <v>-2.302174325195459E-4</v>
       </c>
       <c r="X12">
-        <v>-1.2520711603184742E-3</v>
+        <v>-6.7552407167642582E-3</v>
       </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="4">
-        <v>-5.8391607058840916E-2</v>
+      <c r="B13">
+        <v>0.19183090799829272</v>
       </c>
       <c r="C13">
-        <v>2.2991545278116914E-5</v>
+        <v>-3.112135246937004E-4</v>
       </c>
       <c r="D13">
-        <v>-8.0963781757079079E-5</v>
+        <v>2.3830195897339874E-4</v>
       </c>
       <c r="E13">
-        <v>7.6469728831407894E-7</v>
+        <v>-1.553823230643895E-6</v>
       </c>
       <c r="F13">
-        <v>6.5726871856437892E-4</v>
+        <v>-1.7429388959566607E-5</v>
       </c>
       <c r="G13">
-        <v>1.893107110076224E-4</v>
+        <v>-1.43138160232259E-4</v>
       </c>
       <c r="H13">
-        <v>8.4320619222859057E-4</v>
+        <v>-2.1416435374224749E-4</v>
       </c>
       <c r="I13">
-        <v>1.0069029894225802E-3</v>
+        <v>3.0831952862965441E-5</v>
       </c>
       <c r="J13">
-        <v>1.8890408864855393E-4</v>
+        <v>2.0870254285064189E-4</v>
       </c>
       <c r="K13">
-        <v>6.9601363851319875E-3</v>
+        <v>2.5616173714592613E-3</v>
       </c>
       <c r="L13">
-        <v>1.4013029320487115E-3</v>
+        <v>8.2800392410344774E-4</v>
       </c>
       <c r="M13">
-        <v>5.33546472340252E-3</v>
+        <v>2.0781272389979806E-3</v>
       </c>
       <c r="N13">
-        <v>1.1413306352600848E-2</v>
+        <v>4.9808954357441673E-3</v>
       </c>
       <c r="O13">
-        <v>9.1028119230782151E-3</v>
+        <v>3.9099269000366895E-3</v>
       </c>
       <c r="P13">
-        <v>-1.1887252957870176E-4</v>
+        <v>3.0194222816008233E-4</v>
       </c>
       <c r="Q13">
-        <v>3.4988652602544953E-4</v>
+        <v>1.0293514294964199E-4</v>
       </c>
       <c r="R13">
-        <v>-5.3082041293571556E-4</v>
+        <v>3.659308904274954E-4</v>
       </c>
       <c r="S13">
-        <v>-8.8401030889947822E-5</v>
+        <v>1.184986218552204E-4</v>
       </c>
       <c r="T13">
-        <v>-7.2297357444823282E-6</v>
+        <v>1.1614573506557222E-4</v>
       </c>
       <c r="U13">
-        <v>-2.6169309912909029E-5</v>
+        <v>-3.7995578682103217E-5</v>
       </c>
       <c r="V13">
-        <v>-3.6213513475169285E-4</v>
+        <v>1.0351564600148656E-4</v>
       </c>
       <c r="W13">
-        <v>-9.8067864292601323E-5</v>
+        <v>3.1126334246759334E-4</v>
       </c>
       <c r="X13">
-        <v>-6.9144881382541268E-3</v>
+        <v>-1.1909887307919777E-2</v>
       </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="4">
-        <v>-0.19881408388444202</v>
+      <c r="B14">
+        <v>0.12587912167647741</v>
       </c>
       <c r="C14">
-        <v>-2.4270331619106783E-4</v>
+        <v>-4.8831263666758136E-4</v>
       </c>
       <c r="D14">
-        <v>-2.7993113199366662E-4</v>
+        <v>1.2676641342715053E-4</v>
       </c>
       <c r="E14">
-        <v>2.1490370786274093E-6</v>
+        <v>-8.1288867895539397E-7</v>
       </c>
       <c r="F14">
-        <v>3.8665594355202738E-4</v>
+        <v>-1.7495300318323736E-4</v>
       </c>
       <c r="G14">
-        <v>3.9618009994061773E-4</v>
+        <v>-8.8339540572557416E-5</v>
       </c>
       <c r="H14">
-        <v>3.2419067167904479E-3</v>
+        <v>4.2995755551848626E-4</v>
       </c>
       <c r="I14">
-        <v>3.3970657654480048E-3</v>
+        <v>8.3036959235938135E-4</v>
       </c>
       <c r="J14">
-        <v>3.123480933953475E-4</v>
+        <v>2.7035363338898154E-4</v>
       </c>
       <c r="K14">
-        <v>7.1697600417376696E-3</v>
+        <v>2.5730298487589526E-3</v>
       </c>
       <c r="L14">
-        <v>1.3876849597985194E-3</v>
+        <v>8.8931060775672476E-4</v>
       </c>
       <c r="M14">
-        <v>5.6149275806504032E-3</v>
+        <v>2.2276453424161431E-3</v>
       </c>
       <c r="N14">
-        <v>9.1028119230782151E-3</v>
+        <v>3.9099269000366895E-3</v>
       </c>
       <c r="O14">
-        <v>1.4589443794681767E-2</v>
+        <v>5.5631085185884888E-3</v>
       </c>
       <c r="P14">
-        <v>-1.2800001179528032E-4</v>
+        <v>3.1621292489909195E-4</v>
       </c>
       <c r="Q14">
-        <v>1.5507703188406352E-4</v>
+        <v>2.4251065955846213E-4</v>
       </c>
       <c r="R14">
-        <v>-6.0784804703804818E-4</v>
+        <v>7.5057610610881659E-4</v>
       </c>
       <c r="S14">
-        <v>-2.7446783242094904E-4</v>
+        <v>1.8522446870024344E-4</v>
       </c>
       <c r="T14">
-        <v>-8.8823405686766691E-5</v>
+        <v>1.5369221576009315E-4</v>
       </c>
       <c r="U14">
-        <v>5.5301583834629979E-6</v>
+        <v>-9.9999081838189575E-6</v>
       </c>
       <c r="V14">
-        <v>-4.0919773094095059E-4</v>
+        <v>-9.347311524682397E-6</v>
       </c>
       <c r="W14">
-        <v>-2.1362939494865181E-4</v>
+        <v>-1.4167535976461866E-4</v>
       </c>
       <c r="X14">
-        <v>-2.9149407095898916E-3</v>
+        <v>-9.1577693838158919E-3</v>
       </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="4">
-        <v>9.7645772267365497E-2</v>
+      <c r="B15">
+        <v>0.13013159587915407</v>
       </c>
       <c r="C15">
-        <v>-6.8772113354153923E-4</v>
+        <v>-5.1058898359563547E-4</v>
       </c>
       <c r="D15">
-        <v>-3.4546758669357254E-4</v>
+        <v>-3.2102528274203027E-5</v>
       </c>
       <c r="E15">
-        <v>2.7146379352560677E-6</v>
+        <v>2.3206820198426247E-7</v>
       </c>
       <c r="F15">
-        <v>-2.823565070913703E-4</v>
+        <v>-7.9731745316214764E-5</v>
       </c>
       <c r="G15">
-        <v>3.7774064400202369E-4</v>
+        <v>-6.3195224674416706E-5</v>
       </c>
       <c r="H15">
-        <v>8.0595752355284121E-8</v>
+        <v>1.4254276448890258E-5</v>
       </c>
       <c r="I15">
-        <v>2.5267622229004473E-6</v>
+        <v>-1.7861127686384344E-5</v>
       </c>
       <c r="J15">
-        <v>6.2237773173130437E-4</v>
+        <v>2.0042412272291456E-5</v>
       </c>
       <c r="K15">
-        <v>-1.4751297373827054E-3</v>
+        <v>-4.2346694574074375E-4</v>
       </c>
       <c r="L15">
-        <v>-2.5751056481954928E-4</v>
+        <v>2.4636038076436046E-4</v>
       </c>
       <c r="M15">
-        <v>1.5694294519553943E-5</v>
+        <v>8.3934901531948079E-5</v>
       </c>
       <c r="N15">
-        <v>-1.1887252957870176E-4</v>
+        <v>3.0194222816008233E-4</v>
       </c>
       <c r="O15">
-        <v>-1.2800001179528032E-4</v>
+        <v>3.1621292489909195E-4</v>
       </c>
       <c r="P15">
-        <v>3.7832160466840939E-3</v>
+        <v>3.7227445475122726E-3</v>
       </c>
       <c r="Q15">
-        <v>4.8954179791904596E-5</v>
+        <v>3.308100951615817E-6</v>
       </c>
       <c r="R15">
-        <v>1.1109432132050946E-4</v>
+        <v>1.5187328114232498E-4</v>
       </c>
       <c r="S15">
-        <v>1.8850654133109233E-4</v>
+        <v>5.8234556663350396E-5</v>
       </c>
       <c r="T15">
-        <v>-1.0446876054194212E-4</v>
+        <v>7.7171209770333601E-5</v>
       </c>
       <c r="U15">
-        <v>-3.7643420158571284E-5</v>
+        <v>-2.2027093898393277E-6</v>
       </c>
       <c r="V15">
-        <v>2.2761659104754279E-4</v>
+        <v>-2.0201559451680612E-4</v>
       </c>
       <c r="W15">
-        <v>1.7597304070282062E-4</v>
+        <v>-4.0637434341484304E-4</v>
       </c>
       <c r="X15">
-        <v>1.1478086618962005E-2</v>
+        <v>1.1174667430248891E-3</v>
       </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="4">
-        <v>2.1936002951917274E-2</v>
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>-0.25052726994454366</v>
       </c>
       <c r="C16">
-        <v>-4.5090525248299256E-4</v>
+        <v>1.553474449606079E-4</v>
       </c>
       <c r="D16">
-        <v>3.4574498054642036E-4</v>
+        <v>-2.4934892580094452E-4</v>
       </c>
       <c r="E16">
-        <v>-2.44371537367534E-6</v>
+        <v>1.8265184703276574E-6</v>
       </c>
       <c r="F16">
-        <v>8.4795382028646444E-4</v>
+        <v>-9.3481757255879823E-5</v>
       </c>
       <c r="G16">
-        <v>1.6709534463342762E-4</v>
+        <v>-7.1385934498273016E-5</v>
       </c>
       <c r="H16">
-        <v>1.61783154657442E-4</v>
+        <v>7.2052685367862798E-5</v>
       </c>
       <c r="I16">
-        <v>1.5577456237941345E-4</v>
+        <v>6.3116284849172892E-5</v>
       </c>
       <c r="J16">
-        <v>-8.0867858516690469E-4</v>
+        <v>1.4696850123456636E-4</v>
       </c>
       <c r="K16">
-        <v>2.6044992468864515E-4</v>
+        <v>-3.1348623754018048E-4</v>
       </c>
       <c r="L16">
-        <v>-6.1838779001913418E-5</v>
+        <v>1.511375291290164E-4</v>
       </c>
       <c r="M16">
-        <v>1.9145598516012935E-5</v>
+        <v>3.9374504148149899E-4</v>
       </c>
       <c r="N16">
-        <v>3.4988652602544953E-4</v>
+        <v>1.0293514294964199E-4</v>
       </c>
       <c r="O16">
-        <v>1.5507703188406352E-4</v>
+        <v>2.4251065955846213E-4</v>
       </c>
       <c r="P16">
-        <v>4.8954179791904596E-5</v>
+        <v>3.308100951615817E-6</v>
       </c>
       <c r="Q16">
-        <v>4.4296692098591307E-3</v>
+        <v>2.1011725247917306E-3</v>
       </c>
       <c r="R16">
-        <v>2.1284993750123669E-3</v>
+        <v>1.030713574456993E-3</v>
       </c>
       <c r="S16">
-        <v>2.1396349772318224E-3</v>
+        <v>8.6521251908371066E-4</v>
       </c>
       <c r="T16">
-        <v>2.1660614940950573E-3</v>
+        <v>8.929108871038136E-4</v>
       </c>
       <c r="U16">
-        <v>3.4659792046539237E-6</v>
+        <v>1.9458219512307852E-5</v>
       </c>
       <c r="V16">
-        <v>-3.6522267289872914E-5</v>
+        <v>-1.399344671267247E-4</v>
       </c>
       <c r="W16">
-        <v>-1.181430754422948E-4</v>
+        <v>-2.2476016799124289E-4</v>
       </c>
       <c r="X16">
-        <v>-1.3909312122353095E-2</v>
+        <v>7.018659839133099E-3</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="4">
-        <v>0.12907336711082143</v>
+        <v>36</v>
+      </c>
+      <c r="B17">
+        <v>-0.3610938556438133</v>
       </c>
       <c r="C17">
-        <v>-8.9018126526219793E-5</v>
+        <v>-1.8797879356674985E-4</v>
       </c>
       <c r="D17">
-        <v>1.8422387502360985E-4</v>
+        <v>-2.4310981119817464E-4</v>
       </c>
       <c r="E17">
-        <v>-1.4785204240020582E-6</v>
+        <v>1.6928956128348815E-6</v>
       </c>
       <c r="F17">
-        <v>-1.7891080780154008E-4</v>
+        <v>-1.077979316841469E-4</v>
       </c>
       <c r="G17">
-        <v>1.1168626672433506E-4</v>
+        <v>-2.7297467645640591E-4</v>
       </c>
       <c r="H17">
-        <v>-1.6802371965335123E-4</v>
+        <v>2.3272290795791598E-4</v>
       </c>
       <c r="I17">
-        <v>-1.4406263831567021E-4</v>
+        <v>5.1320575761931936E-5</v>
       </c>
       <c r="J17">
-        <v>4.1322779688653805E-5</v>
+        <v>2.6652123611358965E-4</v>
       </c>
       <c r="K17">
-        <v>-3.8269899229402158E-5</v>
+        <v>-7.3143722303468462E-5</v>
       </c>
       <c r="L17">
-        <v>-1.7911782456869112E-4</v>
+        <v>1.3731456188678301E-4</v>
       </c>
       <c r="M17">
-        <v>-4.0416158840703739E-4</v>
+        <v>5.1057785978522383E-4</v>
       </c>
       <c r="N17">
-        <v>-5.3082041293571556E-4</v>
+        <v>3.659308904274954E-4</v>
       </c>
       <c r="O17">
-        <v>-6.0784804703804818E-4</v>
+        <v>7.5057610610881659E-4</v>
       </c>
       <c r="P17">
-        <v>1.1109432132050946E-4</v>
+        <v>1.5187328114232498E-4</v>
       </c>
       <c r="Q17">
-        <v>2.1284993750123669E-3</v>
+        <v>1.030713574456993E-3</v>
       </c>
       <c r="R17">
-        <v>5.537074872079566E-3</v>
+        <v>3.2315672807933663E-3</v>
       </c>
       <c r="S17">
-        <v>2.1775559583691517E-3</v>
+        <v>8.7393912375672222E-4</v>
       </c>
       <c r="T17">
-        <v>2.2172354318026775E-3</v>
+        <v>9.1349007929998486E-4</v>
       </c>
       <c r="U17">
-        <v>-1.4339978267825268E-5</v>
+        <v>6.7384101524742115E-6</v>
       </c>
       <c r="V17">
-        <v>1.5813262028249562E-4</v>
+        <v>-1.9422720710969378E-4</v>
       </c>
       <c r="W17">
-        <v>1.8421843565788568E-4</v>
+        <v>-2.7843696041894177E-4</v>
       </c>
       <c r="X17">
-        <v>-7.2042011024067241E-3</v>
+        <v>7.1344382078609879E-3</v>
       </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="4">
-        <v>4.2479455116697012E-2</v>
+        <v>37</v>
+      </c>
+      <c r="B18">
+        <v>-4.5873394593235646E-2</v>
       </c>
       <c r="C18">
-        <v>-1.0229633540871381E-4</v>
+        <v>-2.0908544040013001E-5</v>
       </c>
       <c r="D18">
-        <v>2.5685998969708981E-4</v>
+        <v>-6.3948372772215309E-5</v>
       </c>
       <c r="E18">
-        <v>-1.9888802995509953E-6</v>
+        <v>4.2099051499104546E-7</v>
       </c>
       <c r="F18">
-        <v>-2.1899761468195797E-4</v>
+        <v>-9.9366022642346369E-5</v>
       </c>
       <c r="G18">
-        <v>-3.3655972360597305E-4</v>
+        <v>2.4193804931321294E-5</v>
       </c>
       <c r="H18">
-        <v>2.760091848339136E-6</v>
+        <v>-1.1293050367463782E-5</v>
       </c>
       <c r="I18">
-        <v>-4.8497600330886775E-5</v>
+        <v>-7.0650423620749817E-5</v>
       </c>
       <c r="J18">
-        <v>-1.8626505865663653E-4</v>
+        <v>1.6343181816298215E-4</v>
       </c>
       <c r="K18">
-        <v>-1.4574904422939741E-4</v>
+        <v>5.1670636040525774E-5</v>
       </c>
       <c r="L18">
-        <v>3.9487288328093168E-5</v>
+        <v>1.5400546516053707E-5</v>
       </c>
       <c r="M18">
-        <v>-2.0584432238953169E-4</v>
+        <v>7.0866712507610037E-5</v>
       </c>
       <c r="N18">
-        <v>-8.8401030889947822E-5</v>
+        <v>1.184986218552204E-4</v>
       </c>
       <c r="O18">
-        <v>-2.7446783242094904E-4</v>
+        <v>1.8522446870024344E-4</v>
       </c>
       <c r="P18">
-        <v>1.8850654133109233E-4</v>
+        <v>5.8234556663350396E-5</v>
       </c>
       <c r="Q18">
-        <v>2.1396349772318224E-3</v>
+        <v>8.6521251908371066E-4</v>
       </c>
       <c r="R18">
-        <v>2.1775559583691517E-3</v>
+        <v>8.7393912375672222E-4</v>
       </c>
       <c r="S18">
-        <v>4.5899749068653442E-3</v>
+        <v>1.6577037796374709E-3</v>
       </c>
       <c r="T18">
-        <v>2.1844837139621052E-3</v>
+        <v>8.603254104734211E-4</v>
       </c>
       <c r="U18">
-        <v>4.5785646660027088E-6</v>
+        <v>-5.8407923815361145E-7</v>
       </c>
       <c r="V18">
-        <v>7.1384329701992778E-5</v>
+        <v>-7.6149259974676138E-5</v>
       </c>
       <c r="W18">
-        <v>-7.7877465371618479E-5</v>
+        <v>-6.6462540564192978E-5</v>
       </c>
       <c r="X18">
-        <v>-1.0070318168489634E-2</v>
+        <v>1.3963498683085356E-3</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="4">
-        <v>0.21426808195558211</v>
+        <v>38</v>
+      </c>
+      <c r="B19">
+        <v>-0.12220417564629157</v>
       </c>
       <c r="C19">
-        <v>-1.8970289536642709E-4</v>
+        <v>2.3529380347903371E-5</v>
       </c>
       <c r="D19">
-        <v>4.5406255584136629E-4</v>
+        <v>-1.9561435392379499E-4</v>
       </c>
       <c r="E19">
-        <v>-3.2683282910578023E-6</v>
+        <v>1.3033922271891339E-6</v>
       </c>
       <c r="F19">
-        <v>-4.8695436244397408E-4</v>
+        <v>-1.3411948146053944E-4</v>
       </c>
       <c r="G19">
-        <v>-4.4306370508044845E-4</v>
+        <v>-8.3345793615817888E-5</v>
       </c>
       <c r="H19">
-        <v>1.9543567043054153E-5</v>
+        <v>-5.1098474064123749E-5</v>
       </c>
       <c r="I19">
-        <v>-8.0460027071795488E-5</v>
+        <v>-1.0799987451518564E-4</v>
       </c>
       <c r="J19">
-        <v>-4.6946608921159122E-4</v>
+        <v>3.0376354830611131E-4</v>
       </c>
       <c r="K19">
-        <v>3.2537705910654351E-4</v>
+        <v>4.455067477793619E-5</v>
       </c>
       <c r="L19">
-        <v>-1.2996507442466351E-4</v>
+        <v>-4.6039777457916077E-6</v>
       </c>
       <c r="M19">
-        <v>-1.8715223490815185E-4</v>
+        <v>8.8411283400370707E-5</v>
       </c>
       <c r="N19">
-        <v>-7.2297357444823282E-6</v>
+        <v>1.1614573506557222E-4</v>
       </c>
       <c r="O19">
-        <v>-8.8823405686766691E-5</v>
+        <v>1.5369221576009315E-4</v>
       </c>
       <c r="P19">
-        <v>-1.0446876054194212E-4</v>
+        <v>7.7171209770333601E-5</v>
       </c>
       <c r="Q19">
-        <v>2.1660614940950573E-3</v>
+        <v>8.929108871038136E-4</v>
       </c>
       <c r="R19">
-        <v>2.2172354318026775E-3</v>
+        <v>9.1349007929998486E-4</v>
       </c>
       <c r="S19">
-        <v>2.1844837139621052E-3</v>
+        <v>8.603254104734211E-4</v>
       </c>
       <c r="T19">
-        <v>3.4712084335804267E-3</v>
+        <v>1.6273186714505223E-3</v>
       </c>
       <c r="U19">
-        <v>-8.4872143593259628E-6</v>
+        <v>1.5584606163557486E-6</v>
       </c>
       <c r="V19">
-        <v>1.7494661746656821E-4</v>
+        <v>-1.3891124440295076E-4</v>
       </c>
       <c r="W19">
-        <v>1.0339544800023939E-5</v>
+        <v>-1.4191275969462107E-4</v>
       </c>
       <c r="X19">
-        <v>-1.7266336102648678E-2</v>
+        <v>6.1133070258525268E-3</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="4">
-        <v>4.4306050873005043E-2</v>
+      <c r="B20">
+        <v>-2.3237860381584884E-2</v>
       </c>
       <c r="C20">
-        <v>-1.1324460160590867E-5</v>
+        <v>1.2968942956576634E-5</v>
       </c>
       <c r="D20">
-        <v>-1.3404151775062525E-5</v>
+        <v>-2.1657460727906143E-5</v>
       </c>
       <c r="E20">
-        <v>1.0014663766217625E-7</v>
+        <v>1.4223959351566777E-7</v>
       </c>
       <c r="F20">
-        <v>-5.7633243204244939E-5</v>
+        <v>-2.8667399687093604E-5</v>
       </c>
       <c r="G20">
-        <v>-1.4862197364529512E-5</v>
+        <v>-1.6924789068817206E-5</v>
       </c>
       <c r="H20">
-        <v>1.5342265415308932E-5</v>
+        <v>1.8961281724561984E-5</v>
       </c>
       <c r="I20">
-        <v>3.611673980905823E-5</v>
+        <v>2.6038174193982952E-5</v>
       </c>
       <c r="J20">
-        <v>1.4323600843936784E-5</v>
+        <v>4.7273086918398714E-5</v>
       </c>
       <c r="K20">
-        <v>8.0141356386209596E-5</v>
+        <v>-1.8187881926069277E-5</v>
       </c>
       <c r="L20">
-        <v>-1.1191905305022853E-5</v>
+        <v>1.0648834815214715E-5</v>
       </c>
       <c r="M20">
-        <v>6.2061495991615645E-6</v>
+        <v>9.2588776716026838E-6</v>
       </c>
       <c r="N20">
-        <v>-2.6169309912909029E-5</v>
+        <v>-3.7995578682103217E-5</v>
       </c>
       <c r="O20">
-        <v>5.5301583834629979E-6</v>
+        <v>-9.9999081838189575E-6</v>
       </c>
       <c r="P20">
-        <v>-3.7643420158571284E-5</v>
+        <v>-2.2027093898393277E-6</v>
       </c>
       <c r="Q20">
-        <v>3.4659792046539237E-6</v>
+        <v>1.9458219512307852E-5</v>
       </c>
       <c r="R20">
-        <v>-1.4339978267825268E-5</v>
+        <v>6.7384101524742115E-6</v>
       </c>
       <c r="S20">
-        <v>4.5785646660027088E-6</v>
+        <v>-5.8407923815361145E-7</v>
       </c>
       <c r="T20">
-        <v>-8.4872143593259628E-6</v>
+        <v>1.5584606163557486E-6</v>
       </c>
       <c r="U20">
-        <v>3.8802517082310338E-5</v>
+        <v>2.0339892214170915E-5</v>
       </c>
       <c r="V20">
-        <v>-1.0680661807577533E-4</v>
+        <v>-8.1505028307338407E-5</v>
       </c>
       <c r="W20">
-        <v>-1.4507903397191995E-4</v>
+        <v>-9.4299035647029721E-5</v>
       </c>
       <c r="X20">
-        <v>-2.817317713658795E-4</v>
+        <v>4.372412946563321E-4</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="4">
-        <v>8.8910569575186046E-2</v>
+      <c r="B21">
+        <v>6.2526475485622859E-2</v>
       </c>
       <c r="C21">
-        <v>-1.9936894281242699E-4</v>
+        <v>7.0167077762441703E-5</v>
       </c>
       <c r="D21">
-        <v>3.4788948626124708E-5</v>
+        <v>5.5424101516887009E-5</v>
       </c>
       <c r="E21">
-        <v>-2.2960131475809173E-7</v>
+        <v>-3.9682743802403028E-7</v>
       </c>
       <c r="F21">
-        <v>1.9417590047065102E-4</v>
+        <v>1.9712251969617237E-4</v>
       </c>
       <c r="G21">
-        <v>-3.1845428339174206E-5</v>
+        <v>1.5470403159916326E-5</v>
       </c>
       <c r="H21">
-        <v>-4.7903373677727289E-6</v>
+        <v>-9.357905184582049E-5</v>
       </c>
       <c r="I21">
-        <v>7.561009290744285E-8</v>
+        <v>-1.507512047668792E-4</v>
       </c>
       <c r="J21">
-        <v>-8.2372482179821072E-6</v>
+        <v>-1.6696500194858695E-5</v>
       </c>
       <c r="K21">
-        <v>-5.970480753483469E-4</v>
+        <v>2.9393006523171106E-4</v>
       </c>
       <c r="L21">
-        <v>5.8595607596281926E-5</v>
+        <v>-2.2740963322433698E-4</v>
       </c>
       <c r="M21">
-        <v>1.0191725340045479E-4</v>
+        <v>-1.6291297573435196E-4</v>
       </c>
       <c r="N21">
-        <v>-3.6213513475169285E-4</v>
+        <v>1.0351564600148656E-4</v>
       </c>
       <c r="O21">
-        <v>-4.0919773094095059E-4</v>
+        <v>-9.347311524682397E-6</v>
       </c>
       <c r="P21">
-        <v>2.2761659104754279E-4</v>
+        <v>-2.0201559451680612E-4</v>
       </c>
       <c r="Q21">
-        <v>-3.6522267289872914E-5</v>
+        <v>-1.399344671267247E-4</v>
       </c>
       <c r="R21">
-        <v>1.5813262028249562E-4</v>
+        <v>-1.9422720710969378E-4</v>
       </c>
       <c r="S21">
-        <v>7.1384329701992778E-5</v>
+        <v>-7.6149259974676138E-5</v>
       </c>
       <c r="T21">
-        <v>1.7494661746656821E-4</v>
+        <v>-1.3891124440295076E-4</v>
       </c>
       <c r="U21">
-        <v>-1.0680661807577533E-4</v>
+        <v>-8.1505028307338407E-5</v>
       </c>
       <c r="V21">
-        <v>4.7345590970943423E-3</v>
+        <v>3.1060681624128449E-3</v>
       </c>
       <c r="W21">
-        <v>9.6980310520711145E-4</v>
+        <v>6.570313553941029E-4</v>
       </c>
       <c r="X21">
-        <v>3.6275997376113839E-4</v>
+        <v>-7.4593714544866907E-4</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="4">
-        <v>0.28512783010365322</v>
+      <c r="B22">
+        <v>-0.55547867509646554</v>
       </c>
       <c r="C22">
-        <v>1.5645308944060334E-5</v>
+        <v>-1.7881476909892036E-4</v>
       </c>
       <c r="D22">
-        <v>-1.8142000347178694E-4</v>
+        <v>-6.5897830156759832E-5</v>
       </c>
       <c r="E22">
-        <v>1.27896864324413E-6</v>
+        <v>3.2193975308948642E-7</v>
       </c>
       <c r="F22">
-        <v>1.2809451426632184E-4</v>
+        <v>2.4895788473839079E-4</v>
       </c>
       <c r="G22">
-        <v>4.3526462312966883E-4</v>
+        <v>-1.0271957056281859E-4</v>
       </c>
       <c r="H22">
-        <v>1.140654028563377E-5</v>
+        <v>-2.8531020893252427E-4</v>
       </c>
       <c r="I22">
-        <v>3.1649876239178351E-5</v>
+        <v>-3.5961257294858879E-4</v>
       </c>
       <c r="J22">
-        <v>5.203610798507341E-4</v>
+        <v>2.8668575943555444E-4</v>
       </c>
       <c r="K22">
-        <v>-4.1935670615840981E-4</v>
+        <v>1.4936873688883834E-4</v>
       </c>
       <c r="L22">
-        <v>5.8589092771857637E-5</v>
+        <v>-1.9755096550922975E-4</v>
       </c>
       <c r="M22">
-        <v>-1.8046623580512868E-4</v>
+        <v>-2.302174325195459E-4</v>
       </c>
       <c r="N22">
-        <v>-9.8067864292601323E-5</v>
+        <v>3.1126334246759334E-4</v>
       </c>
       <c r="O22">
-        <v>-2.1362939494865181E-4</v>
+        <v>-1.4167535976461866E-4</v>
       </c>
       <c r="P22">
-        <v>1.7597304070282062E-4</v>
+        <v>-4.0637434341484304E-4</v>
       </c>
       <c r="Q22">
-        <v>-1.181430754422948E-4</v>
+        <v>-2.2476016799124289E-4</v>
       </c>
       <c r="R22">
-        <v>1.8421843565788568E-4</v>
+        <v>-2.7843696041894177E-4</v>
       </c>
       <c r="S22">
-        <v>-7.7877465371618479E-5</v>
+        <v>-6.6462540564192978E-5</v>
       </c>
       <c r="T22">
-        <v>1.0339544800023939E-5</v>
+        <v>-1.4191275969462107E-4</v>
       </c>
       <c r="U22">
-        <v>-1.4507903397191995E-4</v>
+        <v>-9.4299035647029721E-5</v>
       </c>
       <c r="V22">
-        <v>9.6980310520711145E-4</v>
+        <v>6.570313553941029E-4</v>
       </c>
       <c r="W22">
-        <v>4.1891007381508073E-3</v>
+        <v>6.5432972020286594E-3</v>
       </c>
       <c r="X22">
-        <v>8.0986841574922017E-3</v>
+        <v>4.5594033364915847E-3</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="4">
-        <v>-13.563324274697759</v>
+      <c r="B23">
+        <v>-22.98535177645309</v>
       </c>
       <c r="C23">
-        <v>7.6543356479846503E-3</v>
+        <v>9.828460085670827E-4</v>
       </c>
       <c r="D23">
-        <v>-8.4567787563106789E-2</v>
+        <v>-4.5569479181656131E-2</v>
       </c>
       <c r="E23">
-        <v>6.0860329152661978E-4</v>
+        <v>3.2133579636969248E-4</v>
       </c>
       <c r="F23">
-        <v>1.4397331009588232E-2</v>
+        <v>3.5444588136896646E-3</v>
       </c>
       <c r="G23">
-        <v>4.6632872781196821E-2</v>
+        <v>6.0106919686074498E-3</v>
       </c>
       <c r="H23">
-        <v>-2.2998120395008731E-3</v>
+        <v>-3.2021165840525612E-3</v>
       </c>
       <c r="I23">
-        <v>-7.1321262605937019E-3</v>
+        <v>-3.4336828012955511E-3</v>
       </c>
       <c r="J23">
-        <v>0.10359730768003406</v>
+        <v>2.8127789996577932E-2</v>
       </c>
       <c r="K23">
-        <v>-3.886351712518131E-3</v>
+        <v>1.0442731807533932E-3</v>
       </c>
       <c r="L23">
-        <v>2.390619750444814E-4</v>
+        <v>-5.6209306917620484E-3</v>
       </c>
       <c r="M23">
-        <v>-1.2520711603184742E-3</v>
+        <v>-6.7552407167642582E-3</v>
       </c>
       <c r="N23">
-        <v>-6.9144881382541268E-3</v>
+        <v>-1.1909887307919777E-2</v>
       </c>
       <c r="O23">
-        <v>-2.9149407095898916E-3</v>
+        <v>-9.1577693838158919E-3</v>
       </c>
       <c r="P23">
-        <v>1.1478086618962005E-2</v>
+        <v>1.1174667430248891E-3</v>
       </c>
       <c r="Q23">
-        <v>-1.3909312122353095E-2</v>
+        <v>7.018659839133099E-3</v>
       </c>
       <c r="R23">
-        <v>-7.2042011024067241E-3</v>
+        <v>7.1344382078609879E-3</v>
       </c>
       <c r="S23">
-        <v>-1.0070318168489634E-2</v>
+        <v>1.3963498683085356E-3</v>
       </c>
       <c r="T23">
-        <v>-1.7266336102648678E-2</v>
+        <v>6.1133070258525268E-3</v>
       </c>
       <c r="U23">
-        <v>-2.817317713658795E-4</v>
+        <v>4.372412946563321E-4</v>
       </c>
       <c r="V23">
-        <v>3.6275997376113839E-4</v>
+        <v>-7.4593714544866907E-4</v>
       </c>
       <c r="W23">
-        <v>8.0986841574922017E-3</v>
+        <v>4.5594033364915847E-3</v>
       </c>
       <c r="X23">
-        <v>2.824203176953624</v>
+        <v>1.5671857842644181</v>
       </c>
     </row>
   </sheetData>
@@ -2342,10 +2308,10 @@
         <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H1" t="s">
         <v>13</v>
@@ -2381,10 +2347,10 @@
         <v>27</v>
       </c>
       <c r="S1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="T1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="U1" t="s">
         <v>28</v>
@@ -2393,16 +2359,16 @@
         <v>29</v>
       </c>
       <c r="W1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="X1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="Y1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="Z1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA1" t="s">
         <v>22</v>
@@ -2421,2576 +2387,2576 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4">
-        <v>8.9348060650980304E-2</v>
+      <c r="B2">
+        <v>0.42950978758956926</v>
       </c>
       <c r="C2">
-        <v>2.1378949705125831E-3</v>
+        <v>1.1813828873128165E-3</v>
       </c>
       <c r="D2">
-        <v>-5.1281767340943026E-4</v>
+        <v>-2.3981732435172069E-5</v>
       </c>
       <c r="E2">
-        <v>3.5271491877640177E-6</v>
+        <v>1.0360145988679781E-7</v>
       </c>
       <c r="F2">
-        <v>-1.4841939752014087E-3</v>
+        <v>6.4098621197589768E-6</v>
       </c>
       <c r="G2">
-        <v>-7.2250499292950306E-4</v>
+        <v>9.5493238904099562E-5</v>
       </c>
       <c r="H2">
-        <v>-1.3462047170082533E-4</v>
+        <v>3.2829049298176734E-5</v>
       </c>
       <c r="I2">
-        <v>-5.8450276199566837E-5</v>
+        <v>1.1128859445666598E-5</v>
       </c>
       <c r="J2">
-        <v>1.4333344131114755E-3</v>
+        <v>1.6677379330217546E-5</v>
       </c>
       <c r="K2">
-        <v>5.8201769832119958E-4</v>
+        <v>7.2028680854050158E-4</v>
       </c>
       <c r="L2">
-        <v>-1.7472697626508277E-4</v>
+        <v>2.5773114144463221E-5</v>
       </c>
       <c r="M2">
-        <v>-1.0598238338953922E-4</v>
+        <v>1.1403913970563951E-5</v>
       </c>
       <c r="N2">
-        <v>-3.2421178064628056E-4</v>
+        <v>-6.0443326077459248E-5</v>
       </c>
       <c r="O2">
-        <v>-2.0983155588325908E-4</v>
+        <v>1.4833265365829447E-5</v>
       </c>
       <c r="P2">
-        <v>-1.1171967814567695E-4</v>
+        <v>2.5209115763472662E-5</v>
       </c>
       <c r="Q2">
-        <v>-5.3800566034262556E-4</v>
+        <v>-3.0788827845712973E-4</v>
       </c>
       <c r="R2">
-        <v>-2.478741427454379E-4</v>
+        <v>4.323123876386103E-4</v>
       </c>
       <c r="S2">
-        <v>6.1427279594138432E-4</v>
+        <v>4.4798522741220265E-5</v>
       </c>
       <c r="T2">
-        <v>5.5466772504872257E-4</v>
+        <v>-1.7668958970381063E-4</v>
       </c>
       <c r="U2">
-        <v>-1.5677121331265714E-4</v>
+        <v>-4.5645015236555101E-5</v>
       </c>
       <c r="V2">
-        <v>1.5920863486497524E-4</v>
+        <v>-3.0902924175937679E-5</v>
       </c>
       <c r="W2">
-        <v>-8.5817286168784275E-5</v>
+        <v>4.3576829731504916E-5</v>
       </c>
       <c r="X2">
-        <v>1.0156104627540754E-4</v>
+        <v>-3.8514277944535827E-5</v>
       </c>
       <c r="Y2">
-        <v>-3.3521403284949712E-5</v>
+        <v>1.3079467251342531E-5</v>
       </c>
       <c r="Z2">
-        <v>-1.5688205116323162E-4</v>
+        <v>4.3568309409761172E-5</v>
       </c>
       <c r="AA2">
-        <v>-1.9736096650505703E-6</v>
+        <v>4.1173285590256976E-6</v>
       </c>
       <c r="AB2">
-        <v>-4.7449604074645312E-5</v>
+        <v>6.2958981598370162E-5</v>
       </c>
       <c r="AC2">
-        <v>2.3455745983574309E-5</v>
+        <v>8.5749457677295702E-5</v>
       </c>
       <c r="AD2">
-        <v>1.6857530957748779E-2</v>
+        <v>-9.1001292384887411E-5</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
-        <v>0.60381314719608881</v>
+      <c r="B3">
+        <v>0.65476016845179141</v>
       </c>
       <c r="C3">
-        <v>-5.1281767340943026E-4</v>
+        <v>-2.3981732435172069E-5</v>
       </c>
       <c r="D3">
-        <v>2.3844739183201623E-3</v>
+        <v>9.9101177043926184E-4</v>
       </c>
       <c r="E3">
-        <v>-1.8378597695600023E-5</v>
+        <v>-7.3308593633552224E-6</v>
       </c>
       <c r="F3">
-        <v>-1.1083184260959195E-4</v>
+        <v>-1.2896712841854946E-4</v>
       </c>
       <c r="G3">
-        <v>-3.4181129244505518E-4</v>
+        <v>-1.9809603978624161E-4</v>
       </c>
       <c r="H3">
-        <v>8.1903585171010963E-5</v>
+        <v>8.0957263278851836E-5</v>
       </c>
       <c r="I3">
-        <v>2.387403542555358E-4</v>
+        <v>1.3875070082092789E-4</v>
       </c>
       <c r="J3">
-        <v>-7.6456502345577729E-4</v>
+        <v>-3.2671603472007611E-4</v>
       </c>
       <c r="K3">
-        <v>9.4585903253827097E-7</v>
+        <v>-1.5764843735922634E-4</v>
       </c>
       <c r="L3">
-        <v>9.9117664961559035E-5</v>
+        <v>3.2322771130592273E-4</v>
       </c>
       <c r="M3">
-        <v>-2.7440640576018548E-5</v>
+        <v>-6.174047871332659E-5</v>
       </c>
       <c r="N3">
-        <v>-1.5185173199025459E-4</v>
+        <v>-9.148874330031434E-5</v>
       </c>
       <c r="O3">
-        <v>-9.5596832627227349E-5</v>
+        <v>6.7512797467801471E-5</v>
       </c>
       <c r="P3">
-        <v>-1.3902028479349663E-4</v>
+        <v>7.5634715548172676E-5</v>
       </c>
       <c r="Q3">
-        <v>-2.234659537241924E-4</v>
+        <v>8.3802275798517279E-5</v>
       </c>
       <c r="R3">
-        <v>-1.5469338216407731E-4</v>
+        <v>-1.0087551247140673E-4</v>
       </c>
       <c r="S3">
-        <v>-3.3067803239834187E-4</v>
+        <v>-8.3307533787629895E-5</v>
       </c>
       <c r="T3">
-        <v>-3.3319941634982501E-4</v>
+        <v>-1.1574897419484257E-4</v>
       </c>
       <c r="U3">
-        <v>-2.3659332545406669E-5</v>
+        <v>-7.8362493866083668E-6</v>
       </c>
       <c r="V3">
-        <v>-2.3546741053537268E-5</v>
+        <v>1.5666039869506924E-4</v>
       </c>
       <c r="W3">
-        <v>7.7873862657812376E-5</v>
+        <v>-1.2298696125120662E-4</v>
       </c>
       <c r="X3">
-        <v>-7.1675353142093903E-6</v>
+        <v>-1.2836239432304809E-4</v>
       </c>
       <c r="Y3">
-        <v>1.1212773813667684E-4</v>
+        <v>-2.3560051062982562E-5</v>
       </c>
       <c r="Z3">
-        <v>-1.3917052107153671E-5</v>
+        <v>-7.3000092347791021E-5</v>
       </c>
       <c r="AA3">
-        <v>-2.828757844919056E-6</v>
+        <v>-8.3156851569843749E-6</v>
       </c>
       <c r="AB3">
-        <v>1.4090163746053111E-4</v>
+        <v>-3.5903404885761526E-5</v>
       </c>
       <c r="AC3">
-        <v>9.0805900671418749E-5</v>
+        <v>-1.7499159508445848E-4</v>
       </c>
       <c r="AD3">
-        <v>-7.5836301001550976E-2</v>
+        <v>-3.2778703372456267E-2</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
-        <v>-4.6111903694334381E-3</v>
+      <c r="B4">
+        <v>-4.4854699997804639E-3</v>
       </c>
       <c r="C4">
-        <v>3.5271491877640177E-6</v>
+        <v>1.0360145988679781E-7</v>
       </c>
       <c r="D4">
-        <v>-1.8378597695600023E-5</v>
+        <v>-7.3308593633552224E-6</v>
       </c>
       <c r="E4">
-        <v>1.430491867632303E-7</v>
+        <v>5.4826218598397927E-8</v>
       </c>
       <c r="F4">
-        <v>1.11656947320135E-6</v>
+        <v>1.3094592632862049E-6</v>
       </c>
       <c r="G4">
-        <v>2.6400456476396888E-6</v>
+        <v>1.8262022345777703E-6</v>
       </c>
       <c r="H4">
-        <v>-4.2568870459441522E-7</v>
+        <v>-5.1687635790890592E-7</v>
       </c>
       <c r="I4">
-        <v>-1.9118424677530191E-6</v>
+        <v>-9.9723166950410929E-7</v>
       </c>
       <c r="J4">
-        <v>4.9596405299146083E-6</v>
+        <v>1.616744807652249E-6</v>
       </c>
       <c r="K4">
-        <v>-2.1221418287030967E-8</v>
+        <v>1.0863008532843724E-6</v>
       </c>
       <c r="L4">
-        <v>-8.5209272892361801E-7</v>
+        <v>-2.3680664673693299E-6</v>
       </c>
       <c r="M4">
-        <v>1.6120274185067257E-7</v>
+        <v>5.0653723137447347E-7</v>
       </c>
       <c r="N4">
-        <v>1.2854223154350354E-6</v>
+        <v>6.9206558048013447E-7</v>
       </c>
       <c r="O4">
-        <v>9.3290036390889064E-7</v>
+        <v>-4.1974750809693905E-7</v>
       </c>
       <c r="P4">
-        <v>1.2791728390481435E-6</v>
+        <v>-4.7770817388431298E-7</v>
       </c>
       <c r="Q4">
-        <v>1.8454807501943858E-6</v>
+        <v>-6.7190330242530857E-7</v>
       </c>
       <c r="R4">
-        <v>6.0771688077465181E-7</v>
+        <v>5.0540706364847081E-7</v>
       </c>
       <c r="S4">
-        <v>2.8590179296312574E-6</v>
+        <v>7.9662784823796918E-7</v>
       </c>
       <c r="T4">
-        <v>2.8419259205187364E-6</v>
+        <v>9.7176323483467558E-7</v>
       </c>
       <c r="U4">
-        <v>2.3564734219994542E-7</v>
+        <v>4.4817086984422027E-8</v>
       </c>
       <c r="V4">
-        <v>2.7838880913184927E-7</v>
+        <v>-1.1866799563889454E-6</v>
       </c>
       <c r="W4">
-        <v>-4.7265588234288104E-7</v>
+        <v>8.8049174438544032E-7</v>
       </c>
       <c r="X4">
-        <v>4.5962854604265045E-8</v>
+        <v>9.7119313994013702E-7</v>
       </c>
       <c r="Y4">
-        <v>-7.5455006679457648E-7</v>
+        <v>1.6164427698259502E-7</v>
       </c>
       <c r="Z4">
-        <v>1.9600890451548775E-7</v>
+        <v>5.3963416203317821E-7</v>
       </c>
       <c r="AA4">
-        <v>2.003233718119105E-8</v>
+        <v>4.4960952120793899E-8</v>
       </c>
       <c r="AB4">
-        <v>-1.0294716363322767E-6</v>
+        <v>2.2423539939320507E-7</v>
       </c>
       <c r="AC4">
-        <v>-6.5860031041157542E-7</v>
+        <v>1.1546564149823158E-6</v>
       </c>
       <c r="AD4">
-        <v>5.7973829599509454E-4</v>
+        <v>2.406449329559597E-4</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="4">
-        <v>-7.1342935380500473E-4</v>
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>9.1050485262207506E-2</v>
       </c>
       <c r="C5">
-        <v>-1.4841939752014087E-3</v>
+        <v>6.4098621197589768E-6</v>
       </c>
       <c r="D5">
-        <v>-1.1083184260959195E-4</v>
+        <v>-1.2896712841854946E-4</v>
       </c>
       <c r="E5">
-        <v>1.11656947320135E-6</v>
+        <v>1.3094592632862049E-6</v>
       </c>
       <c r="F5">
-        <v>4.442203710841453E-3</v>
+        <v>3.5624086229247066E-3</v>
       </c>
       <c r="G5">
-        <v>9.0741131892469482E-4</v>
+        <v>-5.363624329670501E-4</v>
       </c>
       <c r="H5">
-        <v>1.1733856661157735E-4</v>
+        <v>4.3754261694985142E-5</v>
       </c>
       <c r="I5">
-        <v>-2.1412298981261357E-5</v>
+        <v>3.2134069318341473E-7</v>
       </c>
       <c r="J5">
-        <v>-1.7544367072647796E-3</v>
+        <v>-1.4296299555938631E-3</v>
       </c>
       <c r="K5">
-        <v>-7.0873077904449805E-4</v>
+        <v>-9.1252288887271635E-5</v>
       </c>
       <c r="L5">
-        <v>5.6605800597719544E-4</v>
+        <v>5.7093650099508805E-4</v>
       </c>
       <c r="M5">
-        <v>9.9240079141970435E-5</v>
+        <v>-1.2585510464085514E-4</v>
       </c>
       <c r="N5">
-        <v>3.5020524910467105E-4</v>
+        <v>-1.8364908175837918E-4</v>
       </c>
       <c r="O5">
-        <v>-1.0455658193429487E-4</v>
+        <v>-2.789649915213657E-4</v>
       </c>
       <c r="P5">
-        <v>-1.5422155624574685E-4</v>
+        <v>-1.9956218477922808E-4</v>
       </c>
       <c r="Q5">
-        <v>5.9349516997347979E-5</v>
+        <v>4.017072789060962E-5</v>
       </c>
       <c r="R5">
-        <v>3.1993894182171672E-4</v>
+        <v>8.9968575282365531E-5</v>
       </c>
       <c r="S5">
-        <v>8.9292672279733115E-5</v>
+        <v>-2.0451611298511309E-4</v>
       </c>
       <c r="T5">
-        <v>2.0840183636636764E-4</v>
+        <v>-1.5476135349585607E-4</v>
       </c>
       <c r="U5">
-        <v>1.6147596058271744E-4</v>
+        <v>4.1987299758546818E-6</v>
       </c>
       <c r="V5">
-        <v>-2.2830257504989106E-4</v>
+        <v>-2.3721053787927347E-4</v>
       </c>
       <c r="W5">
-        <v>4.5787869085019486E-5</v>
+        <v>-7.8424872763294395E-5</v>
       </c>
       <c r="X5">
-        <v>3.8135466088274868E-5</v>
+        <v>-9.1383671079326822E-5</v>
       </c>
       <c r="Y5">
-        <v>-1.8488770561471499E-5</v>
+        <v>-3.8689048464089684E-5</v>
       </c>
       <c r="Z5">
-        <v>3.997399335774948E-4</v>
+        <v>-1.7700660590338774E-5</v>
       </c>
       <c r="AA5">
-        <v>4.208968378236963E-5</v>
+        <v>-1.8881016109089429E-5</v>
       </c>
       <c r="AB5">
-        <v>-2.6422282860934232E-4</v>
+        <v>-3.2183353474086237E-7</v>
       </c>
       <c r="AC5">
-        <v>-4.4303037884616502E-4</v>
+        <v>-8.4855327018075813E-5</v>
       </c>
       <c r="AD5">
-        <v>2.7579245401921013E-3</v>
+        <v>3.5875425679274472E-3</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.5987239751423169</v>
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>0.32981297980516772</v>
       </c>
       <c r="C6">
-        <v>-7.2250499292950306E-4</v>
+        <v>9.5493238904099562E-5</v>
       </c>
       <c r="D6">
-        <v>-3.4181129244505518E-4</v>
+        <v>-1.9809603978624161E-4</v>
       </c>
       <c r="E6">
-        <v>2.6400456476396888E-6</v>
+        <v>1.8262022345777703E-6</v>
       </c>
       <c r="F6">
-        <v>9.0741131892469482E-4</v>
+        <v>-5.363624329670501E-4</v>
       </c>
       <c r="G6">
-        <v>2.2804130578253845E-3</v>
+        <v>3.5404491735365352E-3</v>
       </c>
       <c r="H6">
-        <v>3.1458421300258402E-5</v>
+        <v>-8.9062276712406239E-6</v>
       </c>
       <c r="I6">
-        <v>6.0236101421737298E-6</v>
+        <v>-2.6210867595016305E-5</v>
       </c>
       <c r="J6">
-        <v>-1.9179290433165696E-4</v>
+        <v>-8.176102183099197E-4</v>
       </c>
       <c r="K6">
-        <v>-1.7604567663596828E-4</v>
+        <v>5.9197284356773407E-5</v>
       </c>
       <c r="L6">
-        <v>8.8560979143958735E-5</v>
+        <v>-4.1614336434651553E-5</v>
       </c>
       <c r="M6">
-        <v>9.4440222765384044E-5</v>
+        <v>6.4021095996027902E-5</v>
       </c>
       <c r="N6">
-        <v>6.7559487316326636E-5</v>
+        <v>6.8621173421243558E-5</v>
       </c>
       <c r="O6">
-        <v>7.4737322727571148E-5</v>
+        <v>9.5614742672519995E-5</v>
       </c>
       <c r="P6">
-        <v>-7.534088914274502E-6</v>
+        <v>8.2477699225380846E-5</v>
       </c>
       <c r="Q6">
-        <v>2.9485245123905203E-5</v>
+        <v>-9.3982628226355319E-5</v>
       </c>
       <c r="R6">
-        <v>-1.2588479992685689E-5</v>
+        <v>1.1913882776938599E-4</v>
       </c>
       <c r="S6">
-        <v>7.9950505298631352E-5</v>
+        <v>-3.2744006691192221E-5</v>
       </c>
       <c r="T6">
-        <v>9.3875974443845159E-5</v>
+        <v>-2.0876399576951366E-4</v>
       </c>
       <c r="U6">
-        <v>5.9134027520987842E-6</v>
+        <v>-1.5611644632758858E-5</v>
       </c>
       <c r="V6">
-        <v>-4.4511162789488169E-5</v>
+        <v>-9.3776691258086529E-5</v>
       </c>
       <c r="W6">
-        <v>2.5114144440440203E-5</v>
+        <v>9.3725988055200254E-7</v>
       </c>
       <c r="X6">
-        <v>-1.0952295818186125E-4</v>
+        <v>4.9960686878304332E-5</v>
       </c>
       <c r="Y6">
-        <v>-5.1463143459226993E-6</v>
+        <v>4.0101324938063287E-6</v>
       </c>
       <c r="Z6">
-        <v>-1.3919000939627106E-5</v>
+        <v>-6.2429725571425121E-7</v>
       </c>
       <c r="AA6">
-        <v>-2.1925658110142883E-5</v>
+        <v>-1.1722711849127205E-5</v>
       </c>
       <c r="AB6">
-        <v>8.8874373863293693E-5</v>
+        <v>7.0087298320472961E-5</v>
       </c>
       <c r="AC6">
-        <v>1.6303727140673172E-4</v>
+        <v>1.3461443381087212E-4</v>
       </c>
       <c r="AD6">
-        <v>1.1411024659940046E-2</v>
+        <v>5.3350735952675046E-3</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4">
-        <v>5.2885363302323643E-2</v>
+      <c r="B7">
+        <v>2.194141116195546E-2</v>
       </c>
       <c r="C7">
-        <v>-1.3462047170082533E-4</v>
+        <v>3.2829049298176734E-5</v>
       </c>
       <c r="D7">
-        <v>8.1903585171010963E-5</v>
+        <v>8.0957263278851836E-5</v>
       </c>
       <c r="E7">
-        <v>-4.2568870459441522E-7</v>
+        <v>-5.1687635790890592E-7</v>
       </c>
       <c r="F7">
-        <v>1.1733856661157735E-4</v>
+        <v>4.3754261694985142E-5</v>
       </c>
       <c r="G7">
-        <v>3.1458421300258402E-5</v>
+        <v>-8.9062276712406239E-6</v>
       </c>
       <c r="H7">
-        <v>2.2243956012727123E-3</v>
+        <v>1.7466314860259053E-3</v>
       </c>
       <c r="I7">
-        <v>2.0200014007549245E-3</v>
+        <v>1.440025211366047E-3</v>
       </c>
       <c r="J7">
-        <v>1.019883290175036E-4</v>
+        <v>-7.9780439776055035E-6</v>
       </c>
       <c r="K7">
-        <v>-1.3637350589591659E-4</v>
+        <v>-1.6721586189561102E-4</v>
       </c>
       <c r="L7">
-        <v>-1.6130356547071659E-4</v>
+        <v>-3.9909465635914456E-5</v>
       </c>
       <c r="M7">
-        <v>8.8336708688888921E-5</v>
+        <v>-1.0058020292087554E-5</v>
       </c>
       <c r="N7">
-        <v>1.2361716804417107E-4</v>
+        <v>-1.0282727127745189E-4</v>
       </c>
       <c r="O7">
-        <v>3.0268690630423211E-4</v>
+        <v>-6.4679684563358604E-5</v>
       </c>
       <c r="P7">
-        <v>7.3390649258686961E-4</v>
+        <v>2.4483608863119831E-4</v>
       </c>
       <c r="Q7">
-        <v>7.5145726585203963E-5</v>
+        <v>6.951287894309846E-5</v>
       </c>
       <c r="R7">
-        <v>8.377904535069378E-5</v>
+        <v>-5.9402096654258881E-5</v>
       </c>
       <c r="S7">
-        <v>5.1155609454321436E-5</v>
+        <v>1.6672596359617936E-4</v>
       </c>
       <c r="T7">
-        <v>-2.0183261454045854E-7</v>
+        <v>5.4513010038388643E-5</v>
       </c>
       <c r="U7">
-        <v>7.2011266837547594E-5</v>
+        <v>7.877396459491173E-5</v>
       </c>
       <c r="V7">
-        <v>5.3218873450096299E-5</v>
+        <v>-1.4702682419550348E-5</v>
       </c>
       <c r="W7">
-        <v>-3.8827624145483763E-5</v>
+        <v>3.8820135270743711E-6</v>
       </c>
       <c r="X7">
-        <v>-4.4598908025281609E-5</v>
+        <v>9.6495393545886827E-5</v>
       </c>
       <c r="Y7">
-        <v>5.1535617502044751E-5</v>
+        <v>4.6540385602321095E-5</v>
       </c>
       <c r="Z7">
-        <v>1.0105872094033608E-4</v>
+        <v>5.038424332845081E-5</v>
       </c>
       <c r="AA7">
-        <v>1.7375076608549855E-5</v>
+        <v>-2.4663283213307208E-6</v>
       </c>
       <c r="AB7">
-        <v>1.2186040185418932E-6</v>
+        <v>2.043208115373393E-5</v>
       </c>
       <c r="AC7">
-        <v>-5.8010567303918369E-5</v>
+        <v>1.7919395327540806E-5</v>
       </c>
       <c r="AD7">
-        <v>-5.9445462667799464E-3</v>
+        <v>-4.3943825161759324E-3</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="4">
-        <v>-5.9035679980169987E-2</v>
+      <c r="B8">
+        <v>7.1733411640234959E-2</v>
       </c>
       <c r="C8">
-        <v>-5.8450276199566837E-5</v>
+        <v>1.1128859445666598E-5</v>
       </c>
       <c r="D8">
-        <v>2.387403542555358E-4</v>
+        <v>1.3875070082092789E-4</v>
       </c>
       <c r="E8">
-        <v>-1.9118424677530191E-6</v>
+        <v>-9.9723166950410929E-7</v>
       </c>
       <c r="F8">
-        <v>-2.1412298981261357E-5</v>
+        <v>3.2134069318341473E-7</v>
       </c>
       <c r="G8">
-        <v>6.0236101421737298E-6</v>
+        <v>-2.6210867595016305E-5</v>
       </c>
       <c r="H8">
-        <v>2.0200014007549245E-3</v>
+        <v>1.440025211366047E-3</v>
       </c>
       <c r="I8">
-        <v>3.6602226280522884E-3</v>
+        <v>1.9391514955351126E-3</v>
       </c>
       <c r="J8">
-        <v>2.8199374239040362E-4</v>
+        <v>-2.3796413414870263E-5</v>
       </c>
       <c r="K8">
-        <v>-1.1529726137831026E-4</v>
+        <v>-2.5940328093132894E-4</v>
       </c>
       <c r="L8">
-        <v>-3.9503265002578745E-4</v>
+        <v>2.0183338037808689E-5</v>
       </c>
       <c r="M8">
-        <v>9.4763674631219487E-5</v>
+        <v>5.0863873120004035E-5</v>
       </c>
       <c r="N8">
-        <v>1.8987062602167484E-4</v>
+        <v>-2.8455747229007441E-6</v>
       </c>
       <c r="O8">
-        <v>4.9463674912620216E-4</v>
+        <v>1.7259336452055531E-4</v>
       </c>
       <c r="P8">
-        <v>1.0542995877709854E-3</v>
+        <v>6.0517264307315187E-4</v>
       </c>
       <c r="Q8">
-        <v>2.3912161588622038E-4</v>
+        <v>1.3150589659768138E-5</v>
       </c>
       <c r="R8">
-        <v>8.1584044476632728E-5</v>
+        <v>-7.1223835878054848E-5</v>
       </c>
       <c r="S8">
-        <v>-1.5212372795215422E-5</v>
+        <v>9.6380415550510745E-5</v>
       </c>
       <c r="T8">
-        <v>-6.2221392322220134E-5</v>
+        <v>6.7858375722436466E-5</v>
       </c>
       <c r="U8">
-        <v>3.9574644989513578E-5</v>
+        <v>7.4509910596189436E-5</v>
       </c>
       <c r="V8">
-        <v>4.6968887024939274E-5</v>
+        <v>4.5416097483290727E-5</v>
       </c>
       <c r="W8">
-        <v>-1.6511008231171798E-4</v>
+        <v>1.5383205870277763E-5</v>
       </c>
       <c r="X8">
-        <v>-1.3891222622651602E-4</v>
+        <v>-6.0949923426508926E-5</v>
       </c>
       <c r="Y8">
-        <v>-7.8805103623854223E-5</v>
+        <v>4.4280955911512763E-5</v>
       </c>
       <c r="Z8">
-        <v>-8.8137421412312096E-5</v>
+        <v>1.879742920110985E-5</v>
       </c>
       <c r="AA8">
-        <v>3.0262697181533942E-5</v>
+        <v>6.4612010417570585E-6</v>
       </c>
       <c r="AB8">
-        <v>1.1344195733202446E-4</v>
+        <v>4.9048343757721069E-6</v>
       </c>
       <c r="AC8">
-        <v>5.3407069862678683E-6</v>
+        <v>-4.9403651879806158E-5</v>
       </c>
       <c r="AD8">
-        <v>-1.037822997273978E-2</v>
+        <v>-6.5312864947751209E-3</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4">
-        <v>1.2895086942826064</v>
+      <c r="B9">
+        <v>0.34789272050457709</v>
       </c>
       <c r="C9">
-        <v>1.4333344131114755E-3</v>
+        <v>1.6677379330217546E-5</v>
       </c>
       <c r="D9">
-        <v>-7.6456502345577729E-4</v>
+        <v>-3.2671603472007611E-4</v>
       </c>
       <c r="E9">
-        <v>4.9596405299146083E-6</v>
+        <v>1.616744807652249E-6</v>
       </c>
       <c r="F9">
-        <v>-1.7544367072647796E-3</v>
+        <v>-1.4296299555938631E-3</v>
       </c>
       <c r="G9">
-        <v>-1.9179290433165696E-4</v>
+        <v>-8.176102183099197E-4</v>
       </c>
       <c r="H9">
-        <v>1.019883290175036E-4</v>
+        <v>-7.9780439776055035E-6</v>
       </c>
       <c r="I9">
-        <v>2.8199374239040362E-4</v>
+        <v>-2.3796413414870263E-5</v>
       </c>
       <c r="J9">
-        <v>3.2526119197627467E-3</v>
+        <v>3.9578432175268645E-3</v>
       </c>
       <c r="K9">
-        <v>1.0854416163122863E-3</v>
+        <v>5.9704600289512094E-4</v>
       </c>
       <c r="L9">
-        <v>-1.6380337647256874E-3</v>
+        <v>-2.1141529838280505E-3</v>
       </c>
       <c r="M9">
-        <v>-9.6190690552108997E-5</v>
+        <v>-6.3294292918192937E-5</v>
       </c>
       <c r="N9">
-        <v>-3.6160612919309892E-4</v>
+        <v>-1.4787579674292598E-4</v>
       </c>
       <c r="O9">
-        <v>-6.5605413015894156E-5</v>
+        <v>-2.2370673279252539E-4</v>
       </c>
       <c r="P9">
-        <v>-1.509165369921831E-4</v>
+        <v>-2.0574058764962774E-4</v>
       </c>
       <c r="Q9">
-        <v>-1.9429136353927477E-4</v>
+        <v>-5.6203256731004677E-5</v>
       </c>
       <c r="R9">
-        <v>-1.7539058007589887E-4</v>
+        <v>-6.3013656706980398E-4</v>
       </c>
       <c r="S9">
-        <v>-1.323195016357478E-4</v>
+        <v>1.2249841507555462E-4</v>
       </c>
       <c r="T9">
-        <v>-2.4617182098494712E-4</v>
+        <v>2.2472173535308717E-4</v>
       </c>
       <c r="U9">
-        <v>-2.7241963645371989E-4</v>
+        <v>-4.5006814949378646E-5</v>
       </c>
       <c r="V9">
-        <v>2.4341988672408471E-4</v>
+        <v>8.529570117160029E-5</v>
       </c>
       <c r="W9">
-        <v>-9.9255582211676789E-5</v>
+        <v>1.3178235406130197E-4</v>
       </c>
       <c r="X9">
-        <v>5.7243262684678921E-7</v>
+        <v>-3.1841219088219824E-5</v>
       </c>
       <c r="Y9">
-        <v>-8.8470684447113784E-5</v>
+        <v>3.0783141663231432E-5</v>
       </c>
       <c r="Z9">
-        <v>-2.3701643682282818E-4</v>
+        <v>6.4842173534579352E-5</v>
       </c>
       <c r="AA9">
-        <v>-3.4354885130066467E-5</v>
+        <v>3.1385956297426025E-5</v>
       </c>
       <c r="AB9">
-        <v>3.2232468323598051E-4</v>
+        <v>2.0855462036519694E-4</v>
       </c>
       <c r="AC9">
-        <v>3.2174971918415111E-4</v>
+        <v>3.9602656651541428E-5</v>
       </c>
       <c r="AD9">
-        <v>2.6791919175330262E-2</v>
+        <v>1.2966391664548427E-2</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="4">
-        <v>7.9993958011896155E-2</v>
+      <c r="B10">
+        <v>0.42281856314506849</v>
       </c>
       <c r="C10">
-        <v>5.8201769832119958E-4</v>
+        <v>7.2028680854050158E-4</v>
       </c>
       <c r="D10">
-        <v>9.4585903253827097E-7</v>
+        <v>-1.5764843735922634E-4</v>
       </c>
       <c r="E10">
-        <v>-2.1221418287030967E-8</v>
+        <v>1.0863008532843724E-6</v>
       </c>
       <c r="F10">
-        <v>-7.0873077904449805E-4</v>
+        <v>-9.1252288887271635E-5</v>
       </c>
       <c r="G10">
-        <v>-1.7604567663596828E-4</v>
+        <v>5.9197284356773407E-5</v>
       </c>
       <c r="H10">
-        <v>-1.3637350589591659E-4</v>
+        <v>-1.6721586189561102E-4</v>
       </c>
       <c r="I10">
-        <v>-1.1529726137831026E-4</v>
+        <v>-2.5940328093132894E-4</v>
       </c>
       <c r="J10">
-        <v>1.0854416163122863E-3</v>
+        <v>5.9704600289512094E-4</v>
       </c>
       <c r="K10">
-        <v>2.995343295935887E-3</v>
+        <v>1.665698547901539E-3</v>
       </c>
       <c r="L10">
-        <v>-1.9182622919458692E-3</v>
+        <v>-7.6811733546807283E-4</v>
       </c>
       <c r="M10">
-        <v>-4.1915650671086327E-5</v>
+        <v>-1.1621131824486104E-5</v>
       </c>
       <c r="N10">
-        <v>4.7182690193440287E-4</v>
+        <v>2.4270926713893757E-4</v>
       </c>
       <c r="O10">
-        <v>9.4841418176039272E-4</v>
+        <v>3.7647039094852161E-4</v>
       </c>
       <c r="P10">
-        <v>1.0725749521502863E-3</v>
+        <v>6.3123972504564735E-4</v>
       </c>
       <c r="Q10">
-        <v>-1.0106434591382167E-3</v>
+        <v>-4.257129006434232E-4</v>
       </c>
       <c r="R10">
-        <v>-1.0679144080364582E-4</v>
+        <v>6.2036780529101462E-5</v>
       </c>
       <c r="S10">
-        <v>-5.4679450596076371E-5</v>
+        <v>-1.8910506694746619E-5</v>
       </c>
       <c r="T10">
-        <v>-2.6135042648314235E-5</v>
+        <v>-1.3822405959195921E-4</v>
       </c>
       <c r="U10">
-        <v>-1.1165839284151663E-5</v>
+        <v>1.2677846451092208E-4</v>
       </c>
       <c r="V10">
-        <v>2.4252039609296786E-4</v>
+        <v>3.3747335471180173E-5</v>
       </c>
       <c r="W10">
-        <v>-1.7158304461154829E-5</v>
+        <v>-1.872209523951523E-5</v>
       </c>
       <c r="X10">
-        <v>6.921207913606535E-6</v>
+        <v>-1.2070038645887165E-4</v>
       </c>
       <c r="Y10">
-        <v>-9.7114594806233271E-5</v>
+        <v>3.9985449702516495E-5</v>
       </c>
       <c r="Z10">
-        <v>-1.8405582293781238E-5</v>
+        <v>2.2418101799622728E-5</v>
       </c>
       <c r="AA10">
-        <v>-1.9006955766936448E-5</v>
+        <v>-6.25166751773641E-6</v>
       </c>
       <c r="AB10">
-        <v>1.6086110173334223E-4</v>
+        <v>2.1052615565188645E-4</v>
       </c>
       <c r="AC10">
-        <v>2.1000598181414526E-4</v>
+        <v>-2.1215426605875374E-5</v>
       </c>
       <c r="AD10">
-        <v>-1.4886325390575245E-3</v>
+        <v>4.2760243892310318E-3</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="4">
-        <v>0.13223978062491082</v>
+      <c r="B11">
+        <v>-0.51986759855910503</v>
       </c>
       <c r="C11">
-        <v>-1.7472697626508277E-4</v>
+        <v>2.5773114144463221E-5</v>
       </c>
       <c r="D11">
-        <v>9.9117664961559035E-5</v>
+        <v>3.2322771130592273E-4</v>
       </c>
       <c r="E11">
-        <v>-8.5209272892361801E-7</v>
+        <v>-2.3680664673693299E-6</v>
       </c>
       <c r="F11">
-        <v>5.6605800597719544E-4</v>
+        <v>5.7093650099508805E-4</v>
       </c>
       <c r="G11">
-        <v>8.8560979143958735E-5</v>
+        <v>-4.1614336434651553E-5</v>
       </c>
       <c r="H11">
-        <v>-1.6130356547071659E-4</v>
+        <v>-3.9909465635914456E-5</v>
       </c>
       <c r="I11">
-        <v>-3.9503265002578745E-4</v>
+        <v>2.0183338037808689E-5</v>
       </c>
       <c r="J11">
-        <v>-1.6380337647256874E-3</v>
+        <v>-2.1141529838280505E-3</v>
       </c>
       <c r="K11">
-        <v>-1.9182622919458692E-3</v>
+        <v>-7.6811733546807283E-4</v>
       </c>
       <c r="L11">
-        <v>3.7812162078111533E-3</v>
+        <v>3.1531862503220405E-3</v>
       </c>
       <c r="M11">
-        <v>1.5536206476802952E-4</v>
+        <v>1.4668942957838239E-5</v>
       </c>
       <c r="N11">
-        <v>6.5342764178740863E-4</v>
+        <v>3.2611779943426326E-4</v>
       </c>
       <c r="O11">
-        <v>3.6716989801827658E-4</v>
+        <v>4.1540083612640825E-4</v>
       </c>
       <c r="P11">
-        <v>4.8915918916433434E-4</v>
+        <v>3.4861428708961523E-4</v>
       </c>
       <c r="Q11">
-        <v>1.7933353220065243E-5</v>
+        <v>3.9805177609202698E-5</v>
       </c>
       <c r="R11">
-        <v>1.1439255813779054E-4</v>
+        <v>-1.8562341258781894E-4</v>
       </c>
       <c r="S11">
-        <v>2.7283814574093957E-5</v>
+        <v>3.1952547323941529E-4</v>
       </c>
       <c r="T11">
-        <v>8.9443821451347459E-5</v>
+        <v>3.6593037718058298E-4</v>
       </c>
       <c r="U11">
-        <v>2.0069615242873694E-4</v>
+        <v>8.856278085677446E-5</v>
       </c>
       <c r="V11">
-        <v>-2.5013552785383818E-4</v>
+        <v>1.8217096591236474E-4</v>
       </c>
       <c r="W11">
-        <v>3.3362421270361365E-5</v>
+        <v>-4.5872664248433273E-5</v>
       </c>
       <c r="X11">
-        <v>7.9866966008777579E-6</v>
+        <v>2.7888289334066039E-6</v>
       </c>
       <c r="Y11">
-        <v>2.3235590198675445E-5</v>
+        <v>-1.1066110228778476E-5</v>
       </c>
       <c r="Z11">
-        <v>1.4009585377950783E-4</v>
+        <v>-3.3797742482051009E-5</v>
       </c>
       <c r="AA11">
-        <v>2.351986218588519E-5</v>
+        <v>6.1434974962383906E-6</v>
       </c>
       <c r="AB11">
-        <v>-1.7450713973967118E-4</v>
+        <v>-1.4470526959323464E-4</v>
       </c>
       <c r="AC11">
-        <v>-2.5058153014061862E-4</v>
+        <v>1.8399041315952567E-4</v>
       </c>
       <c r="AD11">
-        <v>-2.9151590101669615E-3</v>
+        <v>-1.0969298898247083E-2</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="4">
-        <v>8.2979261003069266E-3</v>
+      <c r="B12">
+        <v>0.11417231029821581</v>
       </c>
       <c r="C12">
-        <v>-1.0598238338953922E-4</v>
+        <v>1.1403913970563951E-5</v>
       </c>
       <c r="D12">
-        <v>-2.7440640576018548E-5</v>
+        <v>-6.174047871332659E-5</v>
       </c>
       <c r="E12">
-        <v>1.6120274185067257E-7</v>
+        <v>5.0653723137447347E-7</v>
       </c>
       <c r="F12">
-        <v>9.9240079141970435E-5</v>
+        <v>-1.2585510464085514E-4</v>
       </c>
       <c r="G12">
-        <v>9.4440222765384044E-5</v>
+        <v>6.4021095996027902E-5</v>
       </c>
       <c r="H12">
-        <v>8.8336708688888921E-5</v>
+        <v>-1.0058020292087554E-5</v>
       </c>
       <c r="I12">
-        <v>9.4763674631219487E-5</v>
+        <v>5.0863873120004035E-5</v>
       </c>
       <c r="J12">
-        <v>-9.6190690552108997E-5</v>
+        <v>-6.3294292918192937E-5</v>
       </c>
       <c r="K12">
-        <v>-4.1915650671086327E-5</v>
+        <v>-1.1621131824486104E-5</v>
       </c>
       <c r="L12">
-        <v>1.5536206476802952E-4</v>
+        <v>1.4668942957838239E-5</v>
       </c>
       <c r="M12">
-        <v>3.6090238425499042E-3</v>
+        <v>1.4213539173641774E-3</v>
       </c>
       <c r="N12">
-        <v>1.8917471726779917E-3</v>
+        <v>7.3789629714998413E-4</v>
       </c>
       <c r="O12">
-        <v>1.9072554478237133E-3</v>
+        <v>7.7416010788985024E-4</v>
       </c>
       <c r="P12">
-        <v>1.9585514335853254E-3</v>
+        <v>7.9605144501014395E-4</v>
       </c>
       <c r="Q12">
-        <v>-7.3059785904031055E-5</v>
+        <v>4.1771596682051279E-5</v>
       </c>
       <c r="R12">
-        <v>1.0997341996359145E-4</v>
+        <v>6.0291652041174224E-5</v>
       </c>
       <c r="S12">
-        <v>1.5171397537326014E-5</v>
+        <v>7.5709480456004818E-5</v>
       </c>
       <c r="T12">
-        <v>7.0228643840069196E-5</v>
+        <v>-9.2492038032912196E-5</v>
       </c>
       <c r="U12">
-        <v>4.558927174047966E-5</v>
+        <v>-7.3720245042518278E-6</v>
       </c>
       <c r="V12">
-        <v>1.1882944242108997E-5</v>
+        <v>-7.2057653136608834E-6</v>
       </c>
       <c r="W12">
-        <v>5.8706372003354665E-5</v>
+        <v>6.5067158609018042E-5</v>
       </c>
       <c r="X12">
-        <v>-5.848259982244814E-5</v>
+        <v>1.3770282227285339E-4</v>
       </c>
       <c r="Y12">
-        <v>9.190594323640689E-5</v>
+        <v>-3.6913870727648638E-5</v>
       </c>
       <c r="Z12">
-        <v>8.2246656586812208E-5</v>
+        <v>4.7724499751832005E-5</v>
       </c>
       <c r="AA12">
-        <v>-1.8613485823371137E-6</v>
+        <v>6.8284507372023869E-6</v>
       </c>
       <c r="AB12">
-        <v>5.3051461264878416E-5</v>
+        <v>-3.4920607621271194E-5</v>
       </c>
       <c r="AC12">
-        <v>3.6524291445780403E-5</v>
+        <v>-7.0923082753068963E-5</v>
       </c>
       <c r="AD12">
-        <v>-9.3416955262896407E-4</v>
+        <v>9.4548228122112721E-4</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="4">
-        <v>5.5974546324766977E-2</v>
+      <c r="B13">
+        <v>0.19971630085493411</v>
       </c>
       <c r="C13">
-        <v>-3.2421178064628056E-4</v>
+        <v>-6.0443326077459248E-5</v>
       </c>
       <c r="D13">
-        <v>-1.5185173199025459E-4</v>
+        <v>-9.148874330031434E-5</v>
       </c>
       <c r="E13">
-        <v>1.2854223154350354E-6</v>
+        <v>6.9206558048013447E-7</v>
       </c>
       <c r="F13">
-        <v>3.5020524910467105E-4</v>
+        <v>-1.8364908175837918E-4</v>
       </c>
       <c r="G13">
-        <v>6.7559487316326636E-5</v>
+        <v>6.8621173421243558E-5</v>
       </c>
       <c r="H13">
-        <v>1.2361716804417107E-4</v>
+        <v>-1.0282727127745189E-4</v>
       </c>
       <c r="I13">
-        <v>1.8987062602167484E-4</v>
+        <v>-2.8455747229007441E-6</v>
       </c>
       <c r="J13">
-        <v>-3.6160612919309892E-4</v>
+        <v>-1.4787579674292598E-4</v>
       </c>
       <c r="K13">
-        <v>4.7182690193440287E-4</v>
+        <v>2.4270926713893757E-4</v>
       </c>
       <c r="L13">
-        <v>6.5342764178740863E-4</v>
+        <v>3.2611779943426326E-4</v>
       </c>
       <c r="M13">
-        <v>1.8917471726779917E-3</v>
+        <v>7.3789629714998413E-4</v>
       </c>
       <c r="N13">
-        <v>3.5293042739493667E-3</v>
+        <v>1.7511641182216E-3</v>
       </c>
       <c r="O13">
-        <v>2.9485803790894193E-3</v>
+        <v>1.2502079650126333E-3</v>
       </c>
       <c r="P13">
-        <v>3.2564690781601755E-3</v>
+        <v>1.4098845464972825E-3</v>
       </c>
       <c r="Q13">
-        <v>7.2353818321076107E-5</v>
+        <v>6.1356645282104023E-5</v>
       </c>
       <c r="R13">
-        <v>2.0693843517814562E-4</v>
+        <v>1.9580070893802974E-4</v>
       </c>
       <c r="S13">
-        <v>-1.8220764828616188E-4</v>
+        <v>-1.0875277460531407E-4</v>
       </c>
       <c r="T13">
-        <v>-4.9566238101488483E-5</v>
+        <v>-7.8931758385123019E-5</v>
       </c>
       <c r="U13">
-        <v>6.2801061833890018E-4</v>
+        <v>1.7406270982262627E-4</v>
       </c>
       <c r="V13">
-        <v>-2.6970514440185752E-4</v>
+        <v>2.9334828664448855E-4</v>
       </c>
       <c r="W13">
-        <v>-1.1406301577190095E-4</v>
+        <v>3.6697775670773683E-5</v>
       </c>
       <c r="X13">
-        <v>-3.4266100819235713E-4</v>
+        <v>1.4211459793614541E-4</v>
       </c>
       <c r="Y13">
-        <v>-1.6320484686426474E-4</v>
+        <v>-3.3834740673162615E-5</v>
       </c>
       <c r="Z13">
-        <v>7.30046122418212E-5</v>
+        <v>3.2820462139969983E-6</v>
       </c>
       <c r="AA13">
-        <v>1.2213572819311466E-5</v>
+        <v>8.3564551043839466E-6</v>
       </c>
       <c r="AB13">
-        <v>-5.0480222038985252E-5</v>
+        <v>-2.4033348125394877E-5</v>
       </c>
       <c r="AC13">
-        <v>-1.4669476305043992E-4</v>
+        <v>-9.7998225566881328E-6</v>
       </c>
       <c r="AD13">
-        <v>1.0271345560211747E-3</v>
+        <v>1.4462751017154333E-3</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="4">
-        <v>5.713665661729727E-2</v>
+      <c r="B14">
+        <v>0.29168404955317967</v>
       </c>
       <c r="C14">
-        <v>-2.0983155588325908E-4</v>
+        <v>1.4833265365829447E-5</v>
       </c>
       <c r="D14">
-        <v>-9.5596832627227349E-5</v>
+        <v>6.7512797467801471E-5</v>
       </c>
       <c r="E14">
-        <v>9.3290036390889064E-7</v>
+        <v>-4.1974750809693905E-7</v>
       </c>
       <c r="F14">
-        <v>-1.0455658193429487E-4</v>
+        <v>-2.789649915213657E-4</v>
       </c>
       <c r="G14">
-        <v>7.4737322727571148E-5</v>
+        <v>9.5614742672519995E-5</v>
       </c>
       <c r="H14">
-        <v>3.0268690630423211E-4</v>
+        <v>-6.4679684563358604E-5</v>
       </c>
       <c r="I14">
-        <v>4.9463674912620216E-4</v>
+        <v>1.7259336452055531E-4</v>
       </c>
       <c r="J14">
-        <v>-6.5605413015894156E-5</v>
+        <v>-2.2370673279252539E-4</v>
       </c>
       <c r="K14">
-        <v>9.4841418176039272E-4</v>
+        <v>3.7647039094852161E-4</v>
       </c>
       <c r="L14">
-        <v>3.6716989801827658E-4</v>
+        <v>4.1540083612640825E-4</v>
       </c>
       <c r="M14">
-        <v>1.9072554478237133E-3</v>
+        <v>7.7416010788985024E-4</v>
       </c>
       <c r="N14">
-        <v>2.9485803790894193E-3</v>
+        <v>1.2502079650126333E-3</v>
       </c>
       <c r="O14">
-        <v>4.1981566897571054E-3</v>
+        <v>2.232799390752313E-3</v>
       </c>
       <c r="P14">
-        <v>3.7075893818901778E-3</v>
+        <v>1.8483045249128519E-3</v>
       </c>
       <c r="Q14">
-        <v>1.5846772047639455E-4</v>
+        <v>8.8979624131823361E-5</v>
       </c>
       <c r="R14">
-        <v>6.0468036211832345E-5</v>
+        <v>2.2366172230404137E-4</v>
       </c>
       <c r="S14">
-        <v>-1.9320837066656824E-4</v>
+        <v>-2.5426314852149611E-5</v>
       </c>
       <c r="T14">
-        <v>-8.5893438060492868E-5</v>
+        <v>-1.3167895673096852E-5</v>
       </c>
       <c r="U14">
-        <v>6.559901005875967E-4</v>
+        <v>3.2389978195724141E-4</v>
       </c>
       <c r="V14">
-        <v>-1.1971320635747577E-4</v>
+        <v>2.512152397360008E-4</v>
       </c>
       <c r="W14">
-        <v>-4.1705962644330644E-5</v>
+        <v>9.8929173283288639E-5</v>
       </c>
       <c r="X14">
-        <v>-3.3572535816878905E-4</v>
+        <v>2.2465508670203258E-4</v>
       </c>
       <c r="Y14">
-        <v>-1.3064646822236504E-4</v>
+        <v>3.3656129223273322E-6</v>
       </c>
       <c r="Z14">
-        <v>6.103160377827963E-5</v>
+        <v>3.2727317686222787E-5</v>
       </c>
       <c r="AA14">
-        <v>-6.7215733700893941E-6</v>
+        <v>1.2350769156671299E-5</v>
       </c>
       <c r="AB14">
-        <v>4.664616439460115E-5</v>
+        <v>-2.2486544475838711E-5</v>
       </c>
       <c r="AC14">
-        <v>-5.1681169110135924E-5</v>
+        <v>-2.6309775435641013E-5</v>
       </c>
       <c r="AD14">
-        <v>-1.5030337911851382E-3</v>
+        <v>-4.7847068426994585E-3</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="4">
-        <v>-4.8783911622783151E-2</v>
+      <c r="B15">
+        <v>0.25090874773798066</v>
       </c>
       <c r="C15">
-        <v>-1.1171967814567695E-4</v>
+        <v>2.5209115763472662E-5</v>
       </c>
       <c r="D15">
-        <v>-1.3902028479349663E-4</v>
+        <v>7.5634715548172676E-5</v>
       </c>
       <c r="E15">
-        <v>1.2791728390481435E-6</v>
+        <v>-4.7770817388431298E-7</v>
       </c>
       <c r="F15">
-        <v>-1.5422155624574685E-4</v>
+        <v>-1.9956218477922808E-4</v>
       </c>
       <c r="G15">
-        <v>-7.534088914274502E-6</v>
+        <v>8.2477699225380846E-5</v>
       </c>
       <c r="H15">
-        <v>7.3390649258686961E-4</v>
+        <v>2.4483608863119831E-4</v>
       </c>
       <c r="I15">
-        <v>1.0542995877709854E-3</v>
+        <v>6.0517264307315187E-4</v>
       </c>
       <c r="J15">
-        <v>-1.509165369921831E-4</v>
+        <v>-2.0574058764962774E-4</v>
       </c>
       <c r="K15">
-        <v>1.0725749521502863E-3</v>
+        <v>6.3123972504564735E-4</v>
       </c>
       <c r="L15">
-        <v>4.8915918916433434E-4</v>
+        <v>3.4861428708961523E-4</v>
       </c>
       <c r="M15">
-        <v>1.9585514335853254E-3</v>
+        <v>7.9605144501014395E-4</v>
       </c>
       <c r="N15">
-        <v>3.2564690781601755E-3</v>
+        <v>1.4098845464972825E-3</v>
       </c>
       <c r="O15">
-        <v>3.7075893818901778E-3</v>
+        <v>1.8483045249128519E-3</v>
       </c>
       <c r="P15">
-        <v>5.1029986213978152E-3</v>
+        <v>2.8135734091937971E-3</v>
       </c>
       <c r="Q15">
-        <v>1.7654115088536662E-4</v>
+        <v>1.2345537630727128E-4</v>
       </c>
       <c r="R15">
-        <v>9.2818083717914387E-5</v>
+        <v>1.3827101726314613E-4</v>
       </c>
       <c r="S15">
-        <v>-1.7929022879356845E-4</v>
+        <v>-3.0119656923040814E-5</v>
       </c>
       <c r="T15">
-        <v>6.5427083993441297E-6</v>
+        <v>-4.5802527792361146E-5</v>
       </c>
       <c r="U15">
-        <v>9.4642507874961727E-4</v>
+        <v>6.1540032607335289E-4</v>
       </c>
       <c r="V15">
-        <v>-9.6309731293083166E-6</v>
+        <v>3.6677601638455905E-4</v>
       </c>
       <c r="W15">
-        <v>-1.1110473511152453E-4</v>
+        <v>1.7219597287869182E-4</v>
       </c>
       <c r="X15">
-        <v>-2.7546744608097879E-4</v>
+        <v>2.6827901500771269E-4</v>
       </c>
       <c r="Y15">
-        <v>-1.4443453478243015E-4</v>
+        <v>7.167162809348026E-5</v>
       </c>
       <c r="Z15">
-        <v>2.2957341918358983E-5</v>
+        <v>8.6216263244923218E-5</v>
       </c>
       <c r="AA15">
-        <v>3.4330402264518938E-6</v>
+        <v>4.5493221811450846E-6</v>
       </c>
       <c r="AB15">
-        <v>8.3259101799032945E-5</v>
+        <v>1.408505672128755E-5</v>
       </c>
       <c r="AC15">
-        <v>-4.8012866210581528E-5</v>
+        <v>-1.1224282453956892E-4</v>
       </c>
       <c r="AD15">
-        <v>-1.2930376256462804E-3</v>
+        <v>-5.8488023755043344E-3</v>
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="4">
-        <v>-8.0941970740667959E-2</v>
+      <c r="B16">
+        <v>0.57120376022285979</v>
       </c>
       <c r="C16">
-        <v>-5.3800566034262556E-4</v>
+        <v>-3.0788827845712973E-4</v>
       </c>
       <c r="D16">
-        <v>-2.234659537241924E-4</v>
+        <v>8.3802275798517279E-5</v>
       </c>
       <c r="E16">
-        <v>1.8454807501943858E-6</v>
+        <v>-6.7190330242530857E-7</v>
       </c>
       <c r="F16">
-        <v>5.9349516997347979E-5</v>
+        <v>4.017072789060962E-5</v>
       </c>
       <c r="G16">
-        <v>2.9485245123905203E-5</v>
+        <v>-9.3982628226355319E-5</v>
       </c>
       <c r="H16">
-        <v>7.5145726585203963E-5</v>
+        <v>6.951287894309846E-5</v>
       </c>
       <c r="I16">
-        <v>2.3912161588622038E-4</v>
+        <v>1.3150589659768138E-5</v>
       </c>
       <c r="J16">
-        <v>-1.9429136353927477E-4</v>
+        <v>-5.6203256731004677E-5</v>
       </c>
       <c r="K16">
-        <v>-1.0106434591382167E-3</v>
+        <v>-4.257129006434232E-4</v>
       </c>
       <c r="L16">
-        <v>1.7933353220065243E-5</v>
+        <v>3.9805177609202698E-5</v>
       </c>
       <c r="M16">
-        <v>-7.3059785904031055E-5</v>
+        <v>4.1771596682051279E-5</v>
       </c>
       <c r="N16">
-        <v>7.2353818321076107E-5</v>
+        <v>6.1356645282104023E-5</v>
       </c>
       <c r="O16">
-        <v>1.5846772047639455E-4</v>
+        <v>8.8979624131823361E-5</v>
       </c>
       <c r="P16">
-        <v>1.7654115088536662E-4</v>
+        <v>1.2345537630727128E-4</v>
       </c>
       <c r="Q16">
-        <v>2.3363076028689251E-3</v>
+        <v>3.5098467750619882E-3</v>
       </c>
       <c r="R16">
-        <v>-6.5462926223466432E-6</v>
+        <v>6.5270789530333043E-5</v>
       </c>
       <c r="S16">
-        <v>-8.3977818949783421E-5</v>
+        <v>-1.7893555910582204E-4</v>
       </c>
       <c r="T16">
-        <v>-1.3337655526353181E-4</v>
+        <v>1.0334058002351717E-4</v>
       </c>
       <c r="U16">
-        <v>1.104315907786309E-4</v>
+        <v>6.5715158586556691E-5</v>
       </c>
       <c r="V16">
-        <v>-1.020519664954822E-4</v>
+        <v>-3.8603200729467958E-4</v>
       </c>
       <c r="W16">
-        <v>-5.653202421927999E-5</v>
+        <v>-2.1876948828038662E-5</v>
       </c>
       <c r="X16">
-        <v>-3.7911758061467884E-5</v>
+        <v>6.7961101381772317E-5</v>
       </c>
       <c r="Y16">
-        <v>3.0437751538011097E-5</v>
+        <v>4.0371473711887408E-6</v>
       </c>
       <c r="Z16">
-        <v>-6.8374622187699616E-5</v>
+        <v>-4.6955772177119609E-5</v>
       </c>
       <c r="AA16">
-        <v>1.1067812563149952E-5</v>
+        <v>-4.5548181966953026E-6</v>
       </c>
       <c r="AB16">
-        <v>-2.5378545422404235E-5</v>
+        <v>1.4032805404520503E-4</v>
       </c>
       <c r="AC16">
-        <v>-3.3332294734626962E-5</v>
+        <v>-1.1006495881467885E-4</v>
       </c>
       <c r="AD16">
-        <v>6.7264183222607741E-3</v>
+        <v>-2.4236098168558735E-3</v>
       </c>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="4">
-        <v>-3.4997827709622349E-3</v>
+      <c r="B17">
+        <v>-6.4716894005230757E-2</v>
       </c>
       <c r="C17">
-        <v>-2.478741427454379E-4</v>
+        <v>4.323123876386103E-4</v>
       </c>
       <c r="D17">
-        <v>-1.5469338216407731E-4</v>
+        <v>-1.0087551247140673E-4</v>
       </c>
       <c r="E17">
-        <v>6.0771688077465181E-7</v>
+        <v>5.0540706364847081E-7</v>
       </c>
       <c r="F17">
-        <v>3.1993894182171672E-4</v>
+        <v>8.9968575282365531E-5</v>
       </c>
       <c r="G17">
-        <v>-1.2588479992685689E-5</v>
+        <v>1.1913882776938599E-4</v>
       </c>
       <c r="H17">
-        <v>8.377904535069378E-5</v>
+        <v>-5.9402096654258881E-5</v>
       </c>
       <c r="I17">
-        <v>8.1584044476632728E-5</v>
+        <v>-7.1223835878054848E-5</v>
       </c>
       <c r="J17">
-        <v>-1.7539058007589887E-4</v>
+        <v>-6.3013656706980398E-4</v>
       </c>
       <c r="K17">
-        <v>-1.0679144080364582E-4</v>
+        <v>6.2036780529101462E-5</v>
       </c>
       <c r="L17">
-        <v>1.1439255813779054E-4</v>
+        <v>-1.8562341258781894E-4</v>
       </c>
       <c r="M17">
-        <v>1.0997341996359145E-4</v>
+        <v>6.0291652041174224E-5</v>
       </c>
       <c r="N17">
-        <v>2.0693843517814562E-4</v>
+        <v>1.9580070893802974E-4</v>
       </c>
       <c r="O17">
-        <v>6.0468036211832345E-5</v>
+        <v>2.2366172230404137E-4</v>
       </c>
       <c r="P17">
-        <v>9.2818083717914387E-5</v>
+        <v>1.3827101726314613E-4</v>
       </c>
       <c r="Q17">
-        <v>-6.5462926223466432E-6</v>
+        <v>6.5270789530333043E-5</v>
       </c>
       <c r="R17">
-        <v>1.5762753051083414E-3</v>
+        <v>2.0107644702404264E-3</v>
       </c>
       <c r="S17">
-        <v>-3.300726887807354E-4</v>
+        <v>-9.350014621200514E-4</v>
       </c>
       <c r="T17">
-        <v>-1.4874567519345701E-4</v>
+        <v>-9.0606070013744345E-4</v>
       </c>
       <c r="U17">
-        <v>-3.7487864741313681E-4</v>
+        <v>-3.4357792987650709E-4</v>
       </c>
       <c r="V17">
-        <v>2.4100651304006658E-4</v>
+        <v>2.5283361495398129E-4</v>
       </c>
       <c r="W17">
-        <v>-1.3436179327516295E-5</v>
+        <v>4.372494467800698E-5</v>
       </c>
       <c r="X17">
-        <v>-1.7528105067789862E-5</v>
+        <v>1.4873086409861858E-4</v>
       </c>
       <c r="Y17">
-        <v>-5.7590483616071827E-6</v>
+        <v>1.4575078802275864E-5</v>
       </c>
       <c r="Z17">
-        <v>7.1078295700124135E-5</v>
+        <v>3.4878855291728622E-5</v>
       </c>
       <c r="AA17">
-        <v>6.7695233030124434E-6</v>
+        <v>3.6224620755998698E-6</v>
       </c>
       <c r="AB17">
-        <v>-1.4001522593270403E-4</v>
+        <v>-6.8702079427808752E-5</v>
       </c>
       <c r="AC17">
-        <v>-1.5266083285691602E-4</v>
+        <v>7.5335457031693899E-5</v>
       </c>
       <c r="AD17">
-        <v>6.6769879789826108E-3</v>
+        <v>3.6818938854404452E-3</v>
       </c>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="4">
-        <v>0.15366683427594111</v>
+        <v>32</v>
+      </c>
+      <c r="B18">
+        <v>0.16029042920422648</v>
       </c>
       <c r="C18">
-        <v>6.1427279594138432E-4</v>
+        <v>4.4798522741220265E-5</v>
       </c>
       <c r="D18">
-        <v>-3.3067803239834187E-4</v>
+        <v>-8.3307533787629895E-5</v>
       </c>
       <c r="E18">
-        <v>2.8590179296312574E-6</v>
+        <v>7.9662784823796918E-7</v>
       </c>
       <c r="F18">
-        <v>8.9292672279733115E-5</v>
+        <v>-2.0451611298511309E-4</v>
       </c>
       <c r="G18">
-        <v>7.9950505298631352E-5</v>
+        <v>-3.2744006691192221E-5</v>
       </c>
       <c r="H18">
-        <v>5.1155609454321436E-5</v>
+        <v>1.6672596359617936E-4</v>
       </c>
       <c r="I18">
-        <v>-1.5212372795215422E-5</v>
+        <v>9.6380415550510745E-5</v>
       </c>
       <c r="J18">
-        <v>-1.323195016357478E-4</v>
+        <v>1.2249841507555462E-4</v>
       </c>
       <c r="K18">
-        <v>-5.4679450596076371E-5</v>
+        <v>-1.8910506694746619E-5</v>
       </c>
       <c r="L18">
-        <v>2.7283814574093957E-5</v>
+        <v>3.1952547323941529E-4</v>
       </c>
       <c r="M18">
-        <v>1.5171397537326014E-5</v>
+        <v>7.5709480456004818E-5</v>
       </c>
       <c r="N18">
-        <v>-1.8220764828616188E-4</v>
+        <v>-1.0875277460531407E-4</v>
       </c>
       <c r="O18">
-        <v>-1.9320837066656824E-4</v>
+        <v>-2.5426314852149611E-5</v>
       </c>
       <c r="P18">
-        <v>-1.7929022879356845E-4</v>
+        <v>-3.0119656923040814E-5</v>
       </c>
       <c r="Q18">
-        <v>-8.3977818949783421E-5</v>
+        <v>-1.7893555910582204E-4</v>
       </c>
       <c r="R18">
-        <v>-3.300726887807354E-4</v>
+        <v>-9.350014621200514E-4</v>
       </c>
       <c r="S18">
-        <v>3.8173349384536003E-3</v>
+        <v>4.5440247539090296E-3</v>
       </c>
       <c r="T18">
-        <v>7.4371893374084082E-4</v>
+        <v>1.3591955274427935E-4</v>
       </c>
       <c r="U18">
-        <v>1.0923277628792426E-4</v>
+        <v>2.0939781282367669E-4</v>
       </c>
       <c r="V18">
-        <v>-9.1522287950639809E-5</v>
+        <v>-1.5827391573904295E-4</v>
       </c>
       <c r="W18">
-        <v>-7.0630198159846516E-6</v>
+        <v>-6.7217942808272835E-5</v>
       </c>
       <c r="X18">
-        <v>1.1910474475766686E-5</v>
+        <v>2.041428087776284E-4</v>
       </c>
       <c r="Y18">
-        <v>5.8663311544334198E-5</v>
+        <v>-6.9796853036685784E-5</v>
       </c>
       <c r="Z18">
-        <v>3.4770534328209656E-5</v>
+        <v>-5.6924903724590468E-5</v>
       </c>
       <c r="AA18">
-        <v>-5.8638096900432519E-6</v>
+        <v>2.7161807825584712E-5</v>
       </c>
       <c r="AB18">
-        <v>-3.8233516207175893E-5</v>
+        <v>-1.4083957655738834E-4</v>
       </c>
       <c r="AC18">
-        <v>-2.0782078275869732E-5</v>
+        <v>-1.893404132890618E-4</v>
       </c>
       <c r="AD18">
-        <v>9.1862895541709351E-3</v>
+        <v>1.5007304696578738E-3</v>
       </c>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="4">
-        <v>0.1246558894631655</v>
+        <v>33</v>
+      </c>
+      <c r="B19">
+        <v>2.0393789138828847E-2</v>
       </c>
       <c r="C19">
-        <v>5.5466772504872257E-4</v>
+        <v>-1.7668958970381063E-4</v>
       </c>
       <c r="D19">
-        <v>-3.3319941634982501E-4</v>
+        <v>-1.1574897419484257E-4</v>
       </c>
       <c r="E19">
-        <v>2.8419259205187364E-6</v>
+        <v>9.7176323483467558E-7</v>
       </c>
       <c r="F19">
-        <v>2.0840183636636764E-4</v>
+        <v>-1.5476135349585607E-4</v>
       </c>
       <c r="G19">
-        <v>9.3875974443845159E-5</v>
+        <v>-2.0876399576951366E-4</v>
       </c>
       <c r="H19">
-        <v>-2.0183261454045854E-7</v>
+        <v>5.4513010038388643E-5</v>
       </c>
       <c r="I19">
-        <v>-6.2221392322220134E-5</v>
+        <v>6.7858375722436466E-5</v>
       </c>
       <c r="J19">
-        <v>-2.4617182098494712E-4</v>
+        <v>2.2472173535308717E-4</v>
       </c>
       <c r="K19">
-        <v>-2.6135042648314235E-5</v>
+        <v>-1.3822405959195921E-4</v>
       </c>
       <c r="L19">
-        <v>8.9443821451347459E-5</v>
+        <v>3.6593037718058298E-4</v>
       </c>
       <c r="M19">
-        <v>7.0228643840069196E-5</v>
+        <v>-9.2492038032912196E-5</v>
       </c>
       <c r="N19">
-        <v>-4.9566238101488483E-5</v>
+        <v>-7.8931758385123019E-5</v>
       </c>
       <c r="O19">
-        <v>-8.5893438060492868E-5</v>
+        <v>-1.3167895673096852E-5</v>
       </c>
       <c r="P19">
-        <v>6.5427083993441297E-6</v>
+        <v>-4.5802527792361146E-5</v>
       </c>
       <c r="Q19">
-        <v>-1.3337655526353181E-4</v>
+        <v>1.0334058002351717E-4</v>
       </c>
       <c r="R19">
-        <v>-1.4874567519345701E-4</v>
+        <v>-9.0606070013744345E-4</v>
       </c>
       <c r="S19">
-        <v>7.4371893374084082E-4</v>
+        <v>1.3591955274427935E-4</v>
       </c>
       <c r="T19">
-        <v>3.4936607476696757E-3</v>
+        <v>4.3191848888843266E-3</v>
       </c>
       <c r="U19">
-        <v>4.8423944443180692E-5</v>
+        <v>6.5217623253893762E-5</v>
       </c>
       <c r="V19">
-        <v>-8.7184348245534973E-5</v>
+        <v>-2.8962661318062159E-4</v>
       </c>
       <c r="W19">
-        <v>-3.2975212339121738E-5</v>
+        <v>-9.7666847680694785E-6</v>
       </c>
       <c r="X19">
-        <v>-9.5141647576126921E-5</v>
+        <v>-1.3496034807452964E-4</v>
       </c>
       <c r="Y19">
-        <v>-6.7065280275297595E-5</v>
+        <v>-5.92182729886473E-5</v>
       </c>
       <c r="Z19">
-        <v>-4.8973262859037061E-5</v>
+        <v>-3.2785687742397773E-5</v>
       </c>
       <c r="AA19">
-        <v>-4.8937315467659898E-6</v>
+        <v>-2.3922446473303755E-6</v>
       </c>
       <c r="AB19">
-        <v>7.3534887910118359E-5</v>
+        <v>5.1634118493158754E-5</v>
       </c>
       <c r="AC19">
-        <v>1.0589810000322369E-4</v>
+        <v>4.1208944327527698E-4</v>
       </c>
       <c r="AD19">
-        <v>9.3784556867295976E-3</v>
+        <v>3.6039532159013871E-3</v>
       </c>
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="4">
-        <v>9.091129616241489E-2</v>
+      <c r="B20">
+        <v>0.13017798038052569</v>
       </c>
       <c r="C20">
-        <v>-1.5677121331265714E-4</v>
+        <v>-4.5645015236555101E-5</v>
       </c>
       <c r="D20">
-        <v>-2.3659332545406669E-5</v>
+        <v>-7.8362493866083668E-6</v>
       </c>
       <c r="E20">
-        <v>2.3564734219994542E-7</v>
+        <v>4.4817086984422027E-8</v>
       </c>
       <c r="F20">
-        <v>1.6147596058271744E-4</v>
+        <v>4.1987299758546818E-6</v>
       </c>
       <c r="G20">
-        <v>5.9134027520987842E-6</v>
+        <v>-1.5611644632758858E-5</v>
       </c>
       <c r="H20">
-        <v>7.2011266837547594E-5</v>
+        <v>7.877396459491173E-5</v>
       </c>
       <c r="I20">
-        <v>3.9574644989513578E-5</v>
+        <v>7.4509910596189436E-5</v>
       </c>
       <c r="J20">
-        <v>-2.7241963645371989E-4</v>
+        <v>-4.5006814949378646E-5</v>
       </c>
       <c r="K20">
-        <v>-1.1165839284151663E-5</v>
+        <v>1.2677846451092208E-4</v>
       </c>
       <c r="L20">
-        <v>2.0069615242873694E-4</v>
+        <v>8.856278085677446E-5</v>
       </c>
       <c r="M20">
-        <v>4.558927174047966E-5</v>
+        <v>-7.3720245042518278E-6</v>
       </c>
       <c r="N20">
-        <v>6.2801061833890018E-4</v>
+        <v>1.7406270982262627E-4</v>
       </c>
       <c r="O20">
-        <v>6.559901005875967E-4</v>
+        <v>3.2389978195724141E-4</v>
       </c>
       <c r="P20">
-        <v>9.4642507874961727E-4</v>
+        <v>6.1540032607335289E-4</v>
       </c>
       <c r="Q20">
-        <v>1.104315907786309E-4</v>
+        <v>6.5715158586556691E-5</v>
       </c>
       <c r="R20">
-        <v>-3.7487864741313681E-4</v>
+        <v>-3.4357792987650709E-4</v>
       </c>
       <c r="S20">
-        <v>1.0923277628792426E-4</v>
+        <v>2.0939781282367669E-4</v>
       </c>
       <c r="T20">
-        <v>4.8423944443180692E-5</v>
+        <v>6.5217623253893762E-5</v>
       </c>
       <c r="U20">
-        <v>1.4350014054332675E-3</v>
+        <v>1.008261484233452E-3</v>
       </c>
       <c r="V20">
-        <v>-6.8631139953777244E-4</v>
+        <v>-2.4978881273230661E-4</v>
       </c>
       <c r="W20">
-        <v>-1.1028045464205345E-4</v>
+        <v>-3.948317424458816E-5</v>
       </c>
       <c r="X20">
-        <v>-1.6557649409661791E-4</v>
+        <v>-4.5257520764793691E-6</v>
       </c>
       <c r="Y20">
-        <v>-1.0101514991632649E-4</v>
+        <v>2.0389241874314737E-5</v>
       </c>
       <c r="Z20">
-        <v>1.1873078140548151E-4</v>
+        <v>-7.6716696928476194E-6</v>
       </c>
       <c r="AA20">
-        <v>2.2494318755295086E-5</v>
+        <v>1.1777113110683288E-5</v>
       </c>
       <c r="AB20">
-        <v>-4.3729037356283378E-5</v>
+        <v>-3.7115820882262419E-5</v>
       </c>
       <c r="AC20">
-        <v>-1.0870711282057795E-4</v>
+        <v>-5.79482122171688E-5</v>
       </c>
       <c r="AD20">
-        <v>-8.6221236392767684E-4</v>
+        <v>-7.9911588958017817E-4</v>
       </c>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="4">
-        <v>4.7885198829616442E-2</v>
+      <c r="B21">
+        <v>0.37879530067661465</v>
       </c>
       <c r="C21">
-        <v>1.5920863486497524E-4</v>
+        <v>-3.0902924175937679E-5</v>
       </c>
       <c r="D21">
-        <v>-2.3546741053537268E-5</v>
+        <v>1.5666039869506924E-4</v>
       </c>
       <c r="E21">
-        <v>2.7838880913184927E-7</v>
+        <v>-1.1866799563889454E-6</v>
       </c>
       <c r="F21">
-        <v>-2.2830257504989106E-4</v>
+        <v>-2.3721053787927347E-4</v>
       </c>
       <c r="G21">
-        <v>-4.4511162789488169E-5</v>
+        <v>-9.3776691258086529E-5</v>
       </c>
       <c r="H21">
-        <v>5.3218873450096299E-5</v>
+        <v>-1.4702682419550348E-5</v>
       </c>
       <c r="I21">
-        <v>4.6968887024939274E-5</v>
+        <v>4.5416097483290727E-5</v>
       </c>
       <c r="J21">
-        <v>2.4341988672408471E-4</v>
+        <v>8.529570117160029E-5</v>
       </c>
       <c r="K21">
-        <v>2.4252039609296786E-4</v>
+        <v>3.3747335471180173E-5</v>
       </c>
       <c r="L21">
-        <v>-2.5013552785383818E-4</v>
+        <v>1.8217096591236474E-4</v>
       </c>
       <c r="M21">
-        <v>1.1882944242108997E-5</v>
+        <v>-7.2057653136608834E-6</v>
       </c>
       <c r="N21">
-        <v>-2.6970514440185752E-4</v>
+        <v>2.9334828664448855E-4</v>
       </c>
       <c r="O21">
-        <v>-1.1971320635747577E-4</v>
+        <v>2.512152397360008E-4</v>
       </c>
       <c r="P21">
-        <v>-9.6309731293083166E-6</v>
+        <v>3.6677601638455905E-4</v>
       </c>
       <c r="Q21">
-        <v>-1.020519664954822E-4</v>
+        <v>-3.8603200729467958E-4</v>
       </c>
       <c r="R21">
-        <v>2.4100651304006658E-4</v>
+        <v>2.5283361495398129E-4</v>
       </c>
       <c r="S21">
-        <v>-9.1522287950639809E-5</v>
+        <v>-1.5827391573904295E-4</v>
       </c>
       <c r="T21">
-        <v>-8.7184348245534973E-5</v>
+        <v>-2.8962661318062159E-4</v>
       </c>
       <c r="U21">
-        <v>-6.8631139953777244E-4</v>
+        <v>-2.4978881273230661E-4</v>
       </c>
       <c r="V21">
-        <v>2.7057287053403761E-3</v>
+        <v>1.020618716293366E-2</v>
       </c>
       <c r="W21">
-        <v>6.4534245765817788E-5</v>
+        <v>-1.086100255102908E-4</v>
       </c>
       <c r="X21">
-        <v>2.1969469202214807E-4</v>
+        <v>1.4887519083336406E-4</v>
       </c>
       <c r="Y21">
-        <v>2.6249194021832941E-5</v>
+        <v>-2.0355804551274077E-6</v>
       </c>
       <c r="Z21">
-        <v>-9.4380453457757469E-5</v>
+        <v>-2.7078447112403214E-5</v>
       </c>
       <c r="AA21">
-        <v>-1.2115890182293189E-5</v>
+        <v>8.2431394185044805E-6</v>
       </c>
       <c r="AB21">
-        <v>6.8799396829530041E-5</v>
+        <v>-8.2599655664781081E-6</v>
       </c>
       <c r="AC21">
-        <v>1.4958669920582524E-4</v>
+        <v>-5.2070342442906911E-5</v>
       </c>
       <c r="AD21">
-        <v>4.4626317628550889E-4</v>
+        <v>-5.5713626066278051E-3</v>
       </c>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="4">
-        <v>-0.10356934212609739</v>
+        <v>35</v>
+      </c>
+      <c r="B22">
+        <v>-0.27766488699825514</v>
       </c>
       <c r="C22">
-        <v>-8.5817286168784275E-5</v>
+        <v>4.3576829731504916E-5</v>
       </c>
       <c r="D22">
-        <v>7.7873862657812376E-5</v>
+        <v>-1.2298696125120662E-4</v>
       </c>
       <c r="E22">
-        <v>-4.7265588234288104E-7</v>
+        <v>8.8049174438544032E-7</v>
       </c>
       <c r="F22">
-        <v>4.5787869085019486E-5</v>
+        <v>-7.8424872763294395E-5</v>
       </c>
       <c r="G22">
-        <v>2.5114144440440203E-5</v>
+        <v>9.3725988055200254E-7</v>
       </c>
       <c r="H22">
-        <v>-3.8827624145483763E-5</v>
+        <v>3.8820135270743711E-6</v>
       </c>
       <c r="I22">
-        <v>-1.6511008231171798E-4</v>
+        <v>1.5383205870277763E-5</v>
       </c>
       <c r="J22">
-        <v>-9.9255582211676789E-5</v>
+        <v>1.3178235406130197E-4</v>
       </c>
       <c r="K22">
-        <v>-1.7158304461154829E-5</v>
+        <v>-1.872209523951523E-5</v>
       </c>
       <c r="L22">
-        <v>3.3362421270361365E-5</v>
+        <v>-4.5872664248433273E-5</v>
       </c>
       <c r="M22">
-        <v>5.8706372003354665E-5</v>
+        <v>6.5067158609018042E-5</v>
       </c>
       <c r="N22">
-        <v>-1.1406301577190095E-4</v>
+        <v>3.6697775670773683E-5</v>
       </c>
       <c r="O22">
-        <v>-4.1705962644330644E-5</v>
+        <v>9.8929173283288639E-5</v>
       </c>
       <c r="P22">
-        <v>-1.1110473511152453E-4</v>
+        <v>1.7219597287869182E-4</v>
       </c>
       <c r="Q22">
-        <v>-5.653202421927999E-5</v>
+        <v>-2.1876948828038662E-5</v>
       </c>
       <c r="R22">
-        <v>-1.3436179327516295E-5</v>
+        <v>4.372494467800698E-5</v>
       </c>
       <c r="S22">
-        <v>-7.0630198159846516E-6</v>
+        <v>-6.7217942808272835E-5</v>
       </c>
       <c r="T22">
-        <v>-3.2975212339121738E-5</v>
+        <v>-9.7666847680694785E-6</v>
       </c>
       <c r="U22">
-        <v>-1.1028045464205345E-4</v>
+        <v>-3.948317424458816E-5</v>
       </c>
       <c r="V22">
-        <v>6.4534245765817788E-5</v>
+        <v>-1.086100255102908E-4</v>
       </c>
       <c r="W22">
-        <v>2.1760800977880003E-3</v>
+        <v>1.1722214570811971E-3</v>
       </c>
       <c r="X22">
-        <v>1.1196525804420363E-3</v>
+        <v>5.9443298502252122E-4</v>
       </c>
       <c r="Y22">
-        <v>1.102309475884777E-3</v>
+        <v>5.3101566325762907E-4</v>
       </c>
       <c r="Z22">
-        <v>1.1028218747268545E-3</v>
+        <v>5.4423248259039035E-4</v>
       </c>
       <c r="AA22">
-        <v>-5.7090357573773861E-6</v>
+        <v>-2.0699234436439499E-6</v>
       </c>
       <c r="AB22">
-        <v>-4.8719394921323154E-5</v>
+        <v>4.4309904665515811E-5</v>
       </c>
       <c r="AC22">
-        <v>8.9707692788211903E-6</v>
+        <v>6.038989192358533E-5</v>
       </c>
       <c r="AD22">
-        <v>-3.7109114793377022E-3</v>
+        <v>3.586347692408634E-3</v>
       </c>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="4">
-        <v>2.8485467897695252E-2</v>
+        <v>36</v>
+      </c>
+      <c r="B23">
+        <v>-0.4402387216427821</v>
       </c>
       <c r="C23">
-        <v>1.0156104627540754E-4</v>
+        <v>-3.8514277944535827E-5</v>
       </c>
       <c r="D23">
-        <v>-7.1675353142093903E-6</v>
+        <v>-1.2836239432304809E-4</v>
       </c>
       <c r="E23">
-        <v>4.5962854604265045E-8</v>
+        <v>9.7119313994013702E-7</v>
       </c>
       <c r="F23">
-        <v>3.8135466088274868E-5</v>
+        <v>-9.1383671079326822E-5</v>
       </c>
       <c r="G23">
-        <v>-1.0952295818186125E-4</v>
+        <v>4.9960686878304332E-5</v>
       </c>
       <c r="H23">
-        <v>-4.4598908025281609E-5</v>
+        <v>9.6495393545886827E-5</v>
       </c>
       <c r="I23">
-        <v>-1.3891222622651602E-4</v>
+        <v>-6.0949923426508926E-5</v>
       </c>
       <c r="J23">
-        <v>5.7243262684678921E-7</v>
+        <v>-3.1841219088219824E-5</v>
       </c>
       <c r="K23">
-        <v>6.921207913606535E-6</v>
+        <v>-1.2070038645887165E-4</v>
       </c>
       <c r="L23">
-        <v>7.9866966008777579E-6</v>
+        <v>2.7888289334066039E-6</v>
       </c>
       <c r="M23">
-        <v>-5.848259982244814E-5</v>
+        <v>1.3770282227285339E-4</v>
       </c>
       <c r="N23">
-        <v>-3.4266100819235713E-4</v>
+        <v>1.4211459793614541E-4</v>
       </c>
       <c r="O23">
-        <v>-3.3572535816878905E-4</v>
+        <v>2.2465508670203258E-4</v>
       </c>
       <c r="P23">
-        <v>-2.7546744608097879E-4</v>
+        <v>2.6827901500771269E-4</v>
       </c>
       <c r="Q23">
-        <v>-3.7911758061467884E-5</v>
+        <v>6.7961101381772317E-5</v>
       </c>
       <c r="R23">
-        <v>-1.7528105067789862E-5</v>
+        <v>1.4873086409861858E-4</v>
       </c>
       <c r="S23">
-        <v>1.1910474475766686E-5</v>
+        <v>2.041428087776284E-4</v>
       </c>
       <c r="T23">
-        <v>-9.5141647576126921E-5</v>
+        <v>-1.3496034807452964E-4</v>
       </c>
       <c r="U23">
-        <v>-1.6557649409661791E-4</v>
+        <v>-4.5257520764793691E-6</v>
       </c>
       <c r="V23">
-        <v>2.1969469202214807E-4</v>
+        <v>1.4887519083336406E-4</v>
       </c>
       <c r="W23">
-        <v>1.1196525804420363E-3</v>
+        <v>5.9443298502252122E-4</v>
       </c>
       <c r="X23">
-        <v>3.3870022465209947E-3</v>
+        <v>2.1379719415412922E-3</v>
       </c>
       <c r="Y23">
-        <v>1.118894349564005E-3</v>
+        <v>5.2706159712855927E-4</v>
       </c>
       <c r="Z23">
-        <v>1.1150468027512257E-3</v>
+        <v>5.5102598180861273E-4</v>
       </c>
       <c r="AA23">
-        <v>4.8545870228533804E-6</v>
+        <v>-2.3914320144305206E-6</v>
       </c>
       <c r="AB23">
-        <v>-1.8629015663200498E-4</v>
+        <v>-3.2951175346861031E-5</v>
       </c>
       <c r="AC23">
-        <v>-1.2097161861534855E-4</v>
+        <v>-9.0502807889612747E-5</v>
       </c>
       <c r="AD23">
-        <v>-5.561380232454369E-4</v>
+        <v>3.5477088726258753E-3</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="4">
-        <v>-6.9692231796347676E-2</v>
+        <v>37</v>
+      </c>
+      <c r="B24">
+        <v>-1.7272663814893903E-2</v>
       </c>
       <c r="C24">
-        <v>-3.3521403284949712E-5</v>
+        <v>1.3079467251342531E-5</v>
       </c>
       <c r="D24">
-        <v>1.1212773813667684E-4</v>
+        <v>-2.3560051062982562E-5</v>
       </c>
       <c r="E24">
-        <v>-7.5455006679457648E-7</v>
+        <v>1.6164427698259502E-7</v>
       </c>
       <c r="F24">
-        <v>-1.8488770561471499E-5</v>
+        <v>-3.8689048464089684E-5</v>
       </c>
       <c r="G24">
-        <v>-5.1463143459226993E-6</v>
+        <v>4.0101324938063287E-6</v>
       </c>
       <c r="H24">
-        <v>5.1535617502044751E-5</v>
+        <v>4.6540385602321095E-5</v>
       </c>
       <c r="I24">
-        <v>-7.8805103623854223E-5</v>
+        <v>4.4280955911512763E-5</v>
       </c>
       <c r="J24">
-        <v>-8.8470684447113784E-5</v>
+        <v>3.0783141663231432E-5</v>
       </c>
       <c r="K24">
-        <v>-9.7114594806233271E-5</v>
+        <v>3.9985449702516495E-5</v>
       </c>
       <c r="L24">
-        <v>2.3235590198675445E-5</v>
+        <v>-1.1066110228778476E-5</v>
       </c>
       <c r="M24">
-        <v>9.190594323640689E-5</v>
+        <v>-3.6913870727648638E-5</v>
       </c>
       <c r="N24">
-        <v>-1.6320484686426474E-4</v>
+        <v>-3.3834740673162615E-5</v>
       </c>
       <c r="O24">
-        <v>-1.3064646822236504E-4</v>
+        <v>3.3656129223273322E-6</v>
       </c>
       <c r="P24">
-        <v>-1.4443453478243015E-4</v>
+        <v>7.167162809348026E-5</v>
       </c>
       <c r="Q24">
-        <v>3.0437751538011097E-5</v>
+        <v>4.0371473711887408E-6</v>
       </c>
       <c r="R24">
-        <v>-5.7590483616071827E-6</v>
+        <v>1.4575078802275864E-5</v>
       </c>
       <c r="S24">
-        <v>5.8663311544334198E-5</v>
+        <v>-6.9796853036685784E-5</v>
       </c>
       <c r="T24">
-        <v>-6.7065280275297595E-5</v>
+        <v>-5.92182729886473E-5</v>
       </c>
       <c r="U24">
-        <v>-1.0101514991632649E-4</v>
+        <v>2.0389241874314737E-5</v>
       </c>
       <c r="V24">
-        <v>2.6249194021832941E-5</v>
+        <v>-2.0355804551274077E-6</v>
       </c>
       <c r="W24">
-        <v>1.102309475884777E-3</v>
+        <v>5.3101566325762907E-4</v>
       </c>
       <c r="X24">
-        <v>1.118894349564005E-3</v>
+        <v>5.2706159712855927E-4</v>
       </c>
       <c r="Y24">
-        <v>2.2167282524817246E-3</v>
+        <v>1.0131294787028677E-3</v>
       </c>
       <c r="Z24">
-        <v>1.1116278749998684E-3</v>
+        <v>5.2300297726871946E-4</v>
       </c>
       <c r="AA24">
-        <v>-2.5018214780577292E-6</v>
+        <v>-8.7785579112093743E-6</v>
       </c>
       <c r="AB24">
-        <v>-6.8499929378805166E-5</v>
+        <v>5.5867781433451772E-5</v>
       </c>
       <c r="AC24">
-        <v>3.0694742162410413E-5</v>
+        <v>1.487109373341243E-6</v>
       </c>
       <c r="AD24">
-        <v>-4.8499570315652489E-3</v>
+        <v>3.6299477316696161E-4</v>
       </c>
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="4">
-        <v>-4.5130675473809737E-2</v>
+        <v>38</v>
+      </c>
+      <c r="B25">
+        <v>-0.20965427441247456</v>
       </c>
       <c r="C25">
-        <v>-1.5688205116323162E-4</v>
+        <v>4.3568309409761172E-5</v>
       </c>
       <c r="D25">
-        <v>-1.3917052107153671E-5</v>
+        <v>-7.3000092347791021E-5</v>
       </c>
       <c r="E25">
-        <v>1.9600890451548775E-7</v>
+        <v>5.3963416203317821E-7</v>
       </c>
       <c r="F25">
-        <v>3.997399335774948E-4</v>
+        <v>-1.7700660590338774E-5</v>
       </c>
       <c r="G25">
-        <v>-1.3919000939627106E-5</v>
+        <v>-6.2429725571425121E-7</v>
       </c>
       <c r="H25">
-        <v>1.0105872094033608E-4</v>
+        <v>5.038424332845081E-5</v>
       </c>
       <c r="I25">
-        <v>-8.8137421412312096E-5</v>
+        <v>1.879742920110985E-5</v>
       </c>
       <c r="J25">
-        <v>-2.3701643682282818E-4</v>
+        <v>6.4842173534579352E-5</v>
       </c>
       <c r="K25">
-        <v>-1.8405582293781238E-5</v>
+        <v>2.2418101799622728E-5</v>
       </c>
       <c r="L25">
-        <v>1.4009585377950783E-4</v>
+        <v>-3.3797742482051009E-5</v>
       </c>
       <c r="M25">
-        <v>8.2246656586812208E-5</v>
+        <v>4.7724499751832005E-5</v>
       </c>
       <c r="N25">
-        <v>7.30046122418212E-5</v>
+        <v>3.2820462139969983E-6</v>
       </c>
       <c r="O25">
-        <v>6.103160377827963E-5</v>
+        <v>3.2727317686222787E-5</v>
       </c>
       <c r="P25">
-        <v>2.2957341918358983E-5</v>
+        <v>8.6216263244923218E-5</v>
       </c>
       <c r="Q25">
-        <v>-6.8374622187699616E-5</v>
+        <v>-4.6955772177119609E-5</v>
       </c>
       <c r="R25">
-        <v>7.1078295700124135E-5</v>
+        <v>3.4878855291728622E-5</v>
       </c>
       <c r="S25">
-        <v>3.4770534328209656E-5</v>
+        <v>-5.6924903724590468E-5</v>
       </c>
       <c r="T25">
-        <v>-4.8973262859037061E-5</v>
+        <v>-3.2785687742397773E-5</v>
       </c>
       <c r="U25">
-        <v>1.1873078140548151E-4</v>
+        <v>-7.6716696928476194E-6</v>
       </c>
       <c r="V25">
-        <v>-9.4380453457757469E-5</v>
+        <v>-2.7078447112403214E-5</v>
       </c>
       <c r="W25">
-        <v>1.1028218747268545E-3</v>
+        <v>5.4423248259039035E-4</v>
       </c>
       <c r="X25">
-        <v>1.1150468027512257E-3</v>
+        <v>5.5102598180861273E-4</v>
       </c>
       <c r="Y25">
-        <v>1.1116278749998684E-3</v>
+        <v>5.2300297726871946E-4</v>
       </c>
       <c r="Z25">
-        <v>1.7519035202233145E-3</v>
+        <v>9.9638738944707902E-4</v>
       </c>
       <c r="AA25">
-        <v>1.4762133781142026E-5</v>
+        <v>-7.0352348341679649E-6</v>
       </c>
       <c r="AB25">
-        <v>-1.7972366124449938E-4</v>
+        <v>1.00645059274738E-5</v>
       </c>
       <c r="AC25">
-        <v>-1.765913351190519E-4</v>
+        <v>-2.6915311918489941E-5</v>
       </c>
       <c r="AD25">
-        <v>-1.272986976051561E-3</v>
+        <v>1.9152171973603129E-3</v>
       </c>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="4">
-        <v>2.7964587419416968E-3</v>
+      <c r="B26">
+        <v>-2.4903653230387596E-2</v>
       </c>
       <c r="C26">
-        <v>-1.9736096650505703E-6</v>
+        <v>4.1173285590256976E-6</v>
       </c>
       <c r="D26">
-        <v>-2.828757844919056E-6</v>
+        <v>-8.3156851569843749E-6</v>
       </c>
       <c r="E26">
-        <v>2.003233718119105E-8</v>
+        <v>4.4960952120793899E-8</v>
       </c>
       <c r="F26">
-        <v>4.208968378236963E-5</v>
+        <v>-1.8881016109089429E-5</v>
       </c>
       <c r="G26">
-        <v>-2.1925658110142883E-5</v>
+        <v>-1.1722711849127205E-5</v>
       </c>
       <c r="H26">
-        <v>1.7375076608549855E-5</v>
+        <v>-2.4663283213307208E-6</v>
       </c>
       <c r="I26">
-        <v>3.0262697181533942E-5</v>
+        <v>6.4612010417570585E-6</v>
       </c>
       <c r="J26">
-        <v>-3.4354885130066467E-5</v>
+        <v>3.1385956297426025E-5</v>
       </c>
       <c r="K26">
-        <v>-1.9006955766936448E-5</v>
+        <v>-6.25166751773641E-6</v>
       </c>
       <c r="L26">
-        <v>2.351986218588519E-5</v>
+        <v>6.1434974962383906E-6</v>
       </c>
       <c r="M26">
-        <v>-1.8613485823371137E-6</v>
+        <v>6.8284507372023869E-6</v>
       </c>
       <c r="N26">
-        <v>1.2213572819311466E-5</v>
+        <v>8.3564551043839466E-6</v>
       </c>
       <c r="O26">
-        <v>-6.7215733700893941E-6</v>
+        <v>1.2350769156671299E-5</v>
       </c>
       <c r="P26">
-        <v>3.4330402264518938E-6</v>
+        <v>4.5493221811450846E-6</v>
       </c>
       <c r="Q26">
-        <v>1.1067812563149952E-5</v>
+        <v>-4.5548181966953026E-6</v>
       </c>
       <c r="R26">
-        <v>6.7695233030124434E-6</v>
+        <v>3.6224620755998698E-6</v>
       </c>
       <c r="S26">
-        <v>-5.8638096900432519E-6</v>
+        <v>2.7161807825584712E-5</v>
       </c>
       <c r="T26">
-        <v>-4.8937315467659898E-6</v>
+        <v>-2.3922446473303755E-6</v>
       </c>
       <c r="U26">
-        <v>2.2494318755295086E-5</v>
+        <v>1.1777113110683288E-5</v>
       </c>
       <c r="V26">
-        <v>-1.2115890182293189E-5</v>
+        <v>8.2431394185044805E-6</v>
       </c>
       <c r="W26">
-        <v>-5.7090357573773861E-6</v>
+        <v>-2.0699234436439499E-6</v>
       </c>
       <c r="X26">
-        <v>4.8545870228533804E-6</v>
+        <v>-2.3914320144305206E-6</v>
       </c>
       <c r="Y26">
-        <v>-2.5018214780577292E-6</v>
+        <v>-8.7785579112093743E-6</v>
       </c>
       <c r="Z26">
-        <v>1.4762133781142026E-5</v>
+        <v>-7.0352348341679649E-6</v>
       </c>
       <c r="AA26">
-        <v>2.1130317308718572E-5</v>
+        <v>1.2819214310287792E-5</v>
       </c>
       <c r="AB26">
-        <v>-8.0033766838765567E-5</v>
+        <v>-4.9887427569553912E-5</v>
       </c>
       <c r="AC26">
-        <v>-1.0048548789039693E-4</v>
+        <v>-5.9489903332642547E-5</v>
       </c>
       <c r="AD26">
-        <v>-2.6607548019418905E-4</v>
+        <v>1.169123702854084E-4</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="4">
-        <v>0.18973731482379352</v>
+      <c r="B27">
+        <v>8.6058928368833471E-2</v>
       </c>
       <c r="C27">
-        <v>-4.7449604074645312E-5</v>
+        <v>6.2958981598370162E-5</v>
       </c>
       <c r="D27">
-        <v>1.4090163746053111E-4</v>
+        <v>-3.5903404885761526E-5</v>
       </c>
       <c r="E27">
-        <v>-1.0294716363322767E-6</v>
+        <v>2.2423539939320507E-7</v>
       </c>
       <c r="F27">
-        <v>-2.6422282860934232E-4</v>
+        <v>-3.2183353474086237E-7</v>
       </c>
       <c r="G27">
-        <v>8.8874373863293693E-5</v>
+        <v>7.0087298320472961E-5</v>
       </c>
       <c r="H27">
-        <v>1.2186040185418932E-6</v>
+        <v>2.043208115373393E-5</v>
       </c>
       <c r="I27">
-        <v>1.1344195733202446E-4</v>
+        <v>4.9048343757721069E-6</v>
       </c>
       <c r="J27">
-        <v>3.2232468323598051E-4</v>
+        <v>2.0855462036519694E-4</v>
       </c>
       <c r="K27">
-        <v>1.6086110173334223E-4</v>
+        <v>2.1052615565188645E-4</v>
       </c>
       <c r="L27">
-        <v>-1.7450713973967118E-4</v>
+        <v>-1.4470526959323464E-4</v>
       </c>
       <c r="M27">
-        <v>5.3051461264878416E-5</v>
+        <v>-3.4920607621271194E-5</v>
       </c>
       <c r="N27">
-        <v>-5.0480222038985252E-5</v>
+        <v>-2.4033348125394877E-5</v>
       </c>
       <c r="O27">
-        <v>4.664616439460115E-5</v>
+        <v>-2.2486544475838711E-5</v>
       </c>
       <c r="P27">
-        <v>8.3259101799032945E-5</v>
+        <v>1.408505672128755E-5</v>
       </c>
       <c r="Q27">
-        <v>-2.5378545422404235E-5</v>
+        <v>1.4032805404520503E-4</v>
       </c>
       <c r="R27">
-        <v>-1.4001522593270403E-4</v>
+        <v>-6.8702079427808752E-5</v>
       </c>
       <c r="S27">
-        <v>-3.8233516207175893E-5</v>
+        <v>-1.4083957655738834E-4</v>
       </c>
       <c r="T27">
-        <v>7.3534887910118359E-5</v>
+        <v>5.1634118493158754E-5</v>
       </c>
       <c r="U27">
-        <v>-4.3729037356283378E-5</v>
+        <v>-3.7115820882262419E-5</v>
       </c>
       <c r="V27">
-        <v>6.8799396829530041E-5</v>
+        <v>-8.2599655664781081E-6</v>
       </c>
       <c r="W27">
-        <v>-4.8719394921323154E-5</v>
+        <v>4.4309904665515811E-5</v>
       </c>
       <c r="X27">
-        <v>-1.8629015663200498E-4</v>
+        <v>-3.2951175346861031E-5</v>
       </c>
       <c r="Y27">
-        <v>-6.8499929378805166E-5</v>
+        <v>5.5867781433451772E-5</v>
       </c>
       <c r="Z27">
-        <v>-1.7972366124449938E-4</v>
+        <v>1.00645059274738E-5</v>
       </c>
       <c r="AA27">
-        <v>-8.0033766838765567E-5</v>
+        <v>-4.9887427569553912E-5</v>
       </c>
       <c r="AB27">
-        <v>2.057505110128869E-3</v>
+        <v>1.917771574130183E-3</v>
       </c>
       <c r="AC27">
-        <v>6.7602924030992287E-4</v>
+        <v>4.2236923479040925E-4</v>
       </c>
       <c r="AD27">
-        <v>-3.7313973756243173E-3</v>
+        <v>1.8686066019870623E-3</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="4">
-        <v>6.5977847346881391E-2</v>
+      <c r="B28">
+        <v>-0.67928216994032609</v>
       </c>
       <c r="C28">
-        <v>2.3455745983574309E-5</v>
+        <v>8.5749457677295702E-5</v>
       </c>
       <c r="D28">
-        <v>9.0805900671418749E-5</v>
+        <v>-1.7499159508445848E-4</v>
       </c>
       <c r="E28">
-        <v>-6.5860031041157542E-7</v>
+        <v>1.1546564149823158E-6</v>
       </c>
       <c r="F28">
-        <v>-4.4303037884616502E-4</v>
+        <v>-8.4855327018075813E-5</v>
       </c>
       <c r="G28">
-        <v>1.6303727140673172E-4</v>
+        <v>1.3461443381087212E-4</v>
       </c>
       <c r="H28">
-        <v>-5.8010567303918369E-5</v>
+        <v>1.7919395327540806E-5</v>
       </c>
       <c r="I28">
-        <v>5.3407069862678683E-6</v>
+        <v>-4.9403651879806158E-5</v>
       </c>
       <c r="J28">
-        <v>3.2174971918415111E-4</v>
+        <v>3.9602656651541428E-5</v>
       </c>
       <c r="K28">
-        <v>2.1000598181414526E-4</v>
+        <v>-2.1215426605875374E-5</v>
       </c>
       <c r="L28">
-        <v>-2.5058153014061862E-4</v>
+        <v>1.8399041315952567E-4</v>
       </c>
       <c r="M28">
-        <v>3.6524291445780403E-5</v>
+        <v>-7.0923082753068963E-5</v>
       </c>
       <c r="N28">
-        <v>-1.4669476305043992E-4</v>
+        <v>-9.7998225566881328E-6</v>
       </c>
       <c r="O28">
-        <v>-5.1681169110135924E-5</v>
+        <v>-2.6309775435641013E-5</v>
       </c>
       <c r="P28">
-        <v>-4.8012866210581528E-5</v>
+        <v>-1.1224282453956892E-4</v>
       </c>
       <c r="Q28">
-        <v>-3.3332294734626962E-5</v>
+        <v>-1.1006495881467885E-4</v>
       </c>
       <c r="R28">
-        <v>-1.5266083285691602E-4</v>
+        <v>7.5335457031693899E-5</v>
       </c>
       <c r="S28">
-        <v>-2.0782078275869732E-5</v>
+        <v>-1.893404132890618E-4</v>
       </c>
       <c r="T28">
-        <v>1.0589810000322369E-4</v>
+        <v>4.1208944327527698E-4</v>
       </c>
       <c r="U28">
-        <v>-1.0870711282057795E-4</v>
+        <v>-5.79482122171688E-5</v>
       </c>
       <c r="V28">
-        <v>1.4958669920582524E-4</v>
+        <v>-5.2070342442906911E-5</v>
       </c>
       <c r="W28">
-        <v>8.9707692788211903E-6</v>
+        <v>6.038989192358533E-5</v>
       </c>
       <c r="X28">
-        <v>-1.2097161861534855E-4</v>
+        <v>-9.0502807889612747E-5</v>
       </c>
       <c r="Y28">
-        <v>3.0694742162410413E-5</v>
+        <v>1.487109373341243E-6</v>
       </c>
       <c r="Z28">
-        <v>-1.765913351190519E-4</v>
+        <v>-2.6915311918489941E-5</v>
       </c>
       <c r="AA28">
-        <v>-1.0048548789039693E-4</v>
+        <v>-5.9489903332642547E-5</v>
       </c>
       <c r="AB28">
-        <v>6.7602924030992287E-4</v>
+        <v>4.2236923479040925E-4</v>
       </c>
       <c r="AC28">
-        <v>2.6721078677265399E-3</v>
+        <v>5.2682043366341575E-3</v>
       </c>
       <c r="AD28">
-        <v>-1.6168139900143591E-3</v>
+        <v>7.1947123740678303E-3</v>
       </c>
     </row>
     <row r="29" spans="1:30" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="4">
-        <v>-21.812429440667948</v>
+      <c r="B29">
+        <v>-24.763095017560172</v>
       </c>
       <c r="C29">
-        <v>1.6857530957748779E-2</v>
+        <v>-9.1001292384887411E-5</v>
       </c>
       <c r="D29">
-        <v>-7.5836301001550976E-2</v>
+        <v>-3.2778703372456267E-2</v>
       </c>
       <c r="E29">
-        <v>5.7973829599509454E-4</v>
+        <v>2.406449329559597E-4</v>
       </c>
       <c r="F29">
-        <v>2.7579245401921013E-3</v>
+        <v>3.5875425679274472E-3</v>
       </c>
       <c r="G29">
-        <v>1.1411024659940046E-2</v>
+        <v>5.3350735952675046E-3</v>
       </c>
       <c r="H29">
-        <v>-5.9445462667799464E-3</v>
+        <v>-4.3943825161759324E-3</v>
       </c>
       <c r="I29">
-        <v>-1.037822997273978E-2</v>
+        <v>-6.5312864947751209E-3</v>
       </c>
       <c r="J29">
-        <v>2.6791919175330262E-2</v>
+        <v>1.2966391664548427E-2</v>
       </c>
       <c r="K29">
-        <v>-1.4886325390575245E-3</v>
+        <v>4.2760243892310318E-3</v>
       </c>
       <c r="L29">
-        <v>-2.9151590101669615E-3</v>
+        <v>-1.0969298898247083E-2</v>
       </c>
       <c r="M29">
-        <v>-9.3416955262896407E-4</v>
+        <v>9.4548228122112721E-4</v>
       </c>
       <c r="N29">
-        <v>1.0271345560211747E-3</v>
+        <v>1.4462751017154333E-3</v>
       </c>
       <c r="O29">
-        <v>-1.5030337911851382E-3</v>
+        <v>-4.7847068426994585E-3</v>
       </c>
       <c r="P29">
-        <v>-1.2930376256462804E-3</v>
+        <v>-5.8488023755043344E-3</v>
       </c>
       <c r="Q29">
-        <v>6.7264183222607741E-3</v>
+        <v>-2.4236098168558735E-3</v>
       </c>
       <c r="R29">
-        <v>6.6769879789826108E-3</v>
+        <v>3.6818938854404452E-3</v>
       </c>
       <c r="S29">
-        <v>9.1862895541709351E-3</v>
+        <v>1.5007304696578738E-3</v>
       </c>
       <c r="T29">
-        <v>9.3784556867295976E-3</v>
+        <v>3.6039532159013871E-3</v>
       </c>
       <c r="U29">
-        <v>-8.6221236392767684E-4</v>
+        <v>-7.9911588958017817E-4</v>
       </c>
       <c r="V29">
-        <v>4.4626317628550889E-4</v>
+        <v>-5.5713626066278051E-3</v>
       </c>
       <c r="W29">
-        <v>-3.7109114793377022E-3</v>
+        <v>3.586347692408634E-3</v>
       </c>
       <c r="X29">
-        <v>-5.561380232454369E-4</v>
+        <v>3.5477088726258753E-3</v>
       </c>
       <c r="Y29">
-        <v>-4.8499570315652489E-3</v>
+        <v>3.6299477316696161E-4</v>
       </c>
       <c r="Z29">
-        <v>-1.272986976051561E-3</v>
+        <v>1.9152171973603129E-3</v>
       </c>
       <c r="AA29">
-        <v>-2.6607548019418905E-4</v>
+        <v>1.169123702854084E-4</v>
       </c>
       <c r="AB29">
-        <v>-3.7313973756243173E-3</v>
+        <v>1.8686066019870623E-3</v>
       </c>
       <c r="AC29">
-        <v>-1.6168139900143591E-3</v>
+        <v>7.1947123740678303E-3</v>
       </c>
       <c r="AD29">
-        <v>2.4434118645062464</v>
+        <v>1.0991495579570776</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66627658-B2C2-4097-8D64-509AF0967A59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{913F3487-274F-46E5-88D3-2A39AF35FFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="IT_R1a" sheetId="3" r:id="rId2"/>
-    <sheet name="IT_R1b" sheetId="4" r:id="rId3"/>
+    <sheet name="EL_R1a" sheetId="3" r:id="rId2"/>
+    <sheet name="EL_R1b" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="37">
   <si>
     <t>Description:</t>
   </si>
@@ -126,19 +126,13 @@
     <t>Elig_pen_L1_Sp</t>
   </si>
   <si>
-    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
+    <t>Regions: EL3 = Attika (omitted), EL4 = Aegean Islands, EL7 = Central and Northern Greece</t>
   </si>
   <si>
-    <t>ITF</t>
+    <t>EL4</t>
   </si>
   <si>
-    <t>ITG</t>
-  </si>
-  <si>
-    <t>ITH</t>
-  </si>
-  <si>
-    <t>ITI</t>
+    <t>EL7</t>
   </si>
 </sst>
 </file>
@@ -521,9 +515,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,7 +525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -539,7 +533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -547,7 +541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -555,7 +549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
@@ -570,13 +564,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X23"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:V21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.73046875" customWidth="1"/>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -632,1650 +626,1376 @@
         <v>36</v>
       </c>
       <c r="S1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="T1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="U1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V1" t="s">
-        <v>23</v>
-      </c>
-      <c r="W1" t="s">
-        <v>24</v>
-      </c>
-      <c r="X1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2">
-        <v>0.22998112918573135</v>
+        <v>1.3490792681466395E-2</v>
       </c>
       <c r="C2">
-        <v>1.7020791590843191E-3</v>
+        <v>3.6772928538931645E-3</v>
       </c>
       <c r="D2">
-        <v>-5.614398686302799E-5</v>
+        <v>1.4291666306625564E-4</v>
       </c>
       <c r="E2">
-        <v>4.4409870650847396E-7</v>
+        <v>-7.5679541917964013E-7</v>
       </c>
       <c r="F2">
-        <v>-1.0808630481981776E-4</v>
+        <v>4.632845655283312E-4</v>
       </c>
       <c r="G2">
-        <v>4.4904890822141234E-5</v>
+        <v>9.2694504139246669E-5</v>
       </c>
       <c r="H2">
-        <v>-2.5856304136416953E-4</v>
+        <v>-6.0168984741827008E-4</v>
       </c>
       <c r="I2">
-        <v>-5.0634096087199426E-5</v>
+        <v>-2.6946246288375134E-4</v>
       </c>
       <c r="J2">
-        <v>3.7224195143447454E-4</v>
+        <v>2.7203901518497802E-4</v>
       </c>
       <c r="K2">
-        <v>2.1027824044394472E-4</v>
+        <v>1.2000002113984241E-3</v>
       </c>
       <c r="L2">
-        <v>-1.2114777377603185E-4</v>
+        <v>5.5054485348267237E-5</v>
       </c>
       <c r="M2">
-        <v>-5.4049268603414383E-6</v>
+        <v>-1.4148358955888682E-5</v>
       </c>
       <c r="N2">
-        <v>-3.112135246937004E-4</v>
+        <v>3.863695026518042E-4</v>
       </c>
       <c r="O2">
-        <v>-4.8831263666758136E-4</v>
+        <v>2.3163888480428078E-4</v>
       </c>
       <c r="P2">
-        <v>-5.1058898359563547E-4</v>
+        <v>-3.0865009980015961E-4</v>
       </c>
       <c r="Q2">
-        <v>1.553474449606079E-4</v>
+        <v>4.0188813869035346E-4</v>
       </c>
       <c r="R2">
-        <v>-1.8797879356674985E-4</v>
+        <v>-2.9677535593191848E-5</v>
       </c>
       <c r="S2">
-        <v>-2.0908544040013001E-5</v>
+        <v>-2.4245275848219696E-7</v>
       </c>
       <c r="T2">
-        <v>2.3529380347903371E-5</v>
+        <v>-1.2705913473042105E-4</v>
       </c>
       <c r="U2">
-        <v>1.2968942956576634E-5</v>
+        <v>3.1551512185646051E-4</v>
       </c>
       <c r="V2">
-        <v>7.0167077762441703E-5</v>
-      </c>
-      <c r="W2">
-        <v>-1.7881476909892036E-4</v>
-      </c>
-      <c r="X2">
-        <v>9.828460085670827E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-7.8078685214055411E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3">
-        <v>0.62322187179225863</v>
+        <v>0.37764772700050597</v>
       </c>
       <c r="C3">
-        <v>-5.614398686302799E-5</v>
+        <v>1.4291666306625564E-4</v>
       </c>
       <c r="D3">
-        <v>1.3422217047275092E-3</v>
+        <v>1.7012386337136056E-3</v>
       </c>
       <c r="E3">
-        <v>-9.5313476064370976E-6</v>
+        <v>-1.2329620218144277E-5</v>
       </c>
       <c r="F3">
-        <v>-1.5637336153288741E-4</v>
+        <v>-1.0056606979545885E-3</v>
       </c>
       <c r="G3">
-        <v>-2.2612256997407102E-4</v>
+        <v>-1.0647870612544843E-3</v>
       </c>
       <c r="H3">
-        <v>3.2439744495514275E-5</v>
+        <v>8.3301418978750166E-5</v>
       </c>
       <c r="I3">
-        <v>3.5959808069365232E-5</v>
+        <v>-2.6407318859940701E-4</v>
       </c>
       <c r="J3">
-        <v>-7.3647252124877348E-4</v>
+        <v>-2.3187287045147928E-4</v>
       </c>
       <c r="K3">
-        <v>-8.6512334449860562E-5</v>
+        <v>-6.0636738312894569E-4</v>
       </c>
       <c r="L3">
-        <v>1.3365469505967727E-4</v>
+        <v>-7.5339111904165084E-5</v>
       </c>
       <c r="M3">
-        <v>1.0786887447586033E-4</v>
+        <v>-4.3367704074832175E-5</v>
       </c>
       <c r="N3">
-        <v>2.3830195897339874E-4</v>
+        <v>-1.5777150107386395E-5</v>
       </c>
       <c r="O3">
-        <v>1.2676641342715053E-4</v>
+        <v>-3.1894721641678378E-4</v>
       </c>
       <c r="P3">
-        <v>-3.2102528274203027E-5</v>
+        <v>-4.3497562584504483E-4</v>
       </c>
       <c r="Q3">
-        <v>-2.4934892580094452E-4</v>
+        <v>6.9684311828802775E-5</v>
       </c>
       <c r="R3">
-        <v>-2.4310981119817464E-4</v>
+        <v>-1.3380529762663587E-4</v>
       </c>
       <c r="S3">
-        <v>-6.3948372772215309E-5</v>
+        <v>-3.1248638249967847E-5</v>
       </c>
       <c r="T3">
-        <v>-1.9561435392379499E-4</v>
+        <v>9.4054051431696241E-5</v>
       </c>
       <c r="U3">
-        <v>-2.1657460727906143E-5</v>
+        <v>2.5985514102137668E-5</v>
       </c>
       <c r="V3">
-        <v>5.5424101516887009E-5</v>
-      </c>
-      <c r="W3">
-        <v>-6.5897830156759832E-5</v>
-      </c>
-      <c r="X3">
-        <v>-4.5569479181656131E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-5.6059553699710142E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-4.3462167958222119E-3</v>
+        <v>-2.4956498333991877E-3</v>
       </c>
       <c r="C4">
-        <v>4.4409870650847396E-7</v>
+        <v>-7.5679541917964013E-7</v>
       </c>
       <c r="D4">
-        <v>-9.5313476064370976E-6</v>
+        <v>-1.2329620218144277E-5</v>
       </c>
       <c r="E4">
-        <v>6.8367008855067024E-8</v>
+        <v>9.0878205287295342E-8</v>
       </c>
       <c r="F4">
-        <v>1.7893946659305985E-6</v>
+        <v>9.4300765893607448E-6</v>
       </c>
       <c r="G4">
-        <v>2.2115500777097791E-6</v>
+        <v>9.5869127135391665E-6</v>
       </c>
       <c r="H4">
-        <v>-2.0593825206629331E-7</v>
+        <v>-5.6323518914428404E-7</v>
       </c>
       <c r="I4">
-        <v>-3.2353270977064023E-7</v>
+        <v>1.6550285956247799E-6</v>
       </c>
       <c r="J4">
-        <v>3.9262931312461467E-6</v>
+        <v>-1.6526554600478413E-6</v>
       </c>
       <c r="K4">
-        <v>5.018275744685696E-7</v>
+        <v>4.0160140974765551E-6</v>
       </c>
       <c r="L4">
-        <v>-9.3746123465261359E-7</v>
+        <v>6.4834350842692754E-7</v>
       </c>
       <c r="M4">
-        <v>-6.225705231806413E-7</v>
+        <v>3.3908806814171558E-7</v>
       </c>
       <c r="N4">
-        <v>-1.553823230643895E-6</v>
+        <v>1.2973641503029949E-7</v>
       </c>
       <c r="O4">
-        <v>-8.1288867895539397E-7</v>
+        <v>2.2258201795190681E-6</v>
       </c>
       <c r="P4">
-        <v>2.3206820198426247E-7</v>
+        <v>3.0507737098397738E-6</v>
       </c>
       <c r="Q4">
-        <v>1.8265184703276574E-6</v>
+        <v>-4.0371914302733008E-7</v>
       </c>
       <c r="R4">
-        <v>1.6928956128348815E-6</v>
+        <v>1.1114608187976817E-6</v>
       </c>
       <c r="S4">
-        <v>4.2099051499104546E-7</v>
+        <v>1.8706645064358191E-7</v>
       </c>
       <c r="T4">
-        <v>1.3033922271891339E-6</v>
+        <v>-6.3192587150617352E-7</v>
       </c>
       <c r="U4">
-        <v>1.4223959351566777E-7</v>
+        <v>-9.8253635935962116E-8</v>
       </c>
       <c r="V4">
-        <v>-3.9682743802403028E-7</v>
-      </c>
-      <c r="W4">
-        <v>3.2193975308948642E-7</v>
-      </c>
-      <c r="X4">
-        <v>3.2133579636969248E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.45">
+        <v>4.0176823221627843E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5">
-        <v>0.23479384788814828</v>
+        <v>0.27094337489620568</v>
       </c>
       <c r="C5">
-        <v>-1.0808630481981776E-4</v>
+        <v>4.632845655283312E-4</v>
       </c>
       <c r="D5">
-        <v>-1.5637336153288741E-4</v>
+        <v>-1.0056606979545885E-3</v>
       </c>
       <c r="E5">
-        <v>1.7893946659305985E-6</v>
+        <v>9.4300765893607448E-6</v>
       </c>
       <c r="F5">
-        <v>8.6293143029709512E-3</v>
+        <v>1.7929529691702899E-2</v>
       </c>
       <c r="G5">
-        <v>-1.3880899169022138E-3</v>
+        <v>4.1838358526473662E-3</v>
       </c>
       <c r="H5">
-        <v>-1.834348454667848E-5</v>
+        <v>5.8700006394866999E-4</v>
       </c>
       <c r="I5">
-        <v>8.7045757070425452E-5</v>
+        <v>4.4672392325036982E-5</v>
       </c>
       <c r="J5">
-        <v>-1.9619946988589342E-3</v>
+        <v>-5.7718797263359807E-3</v>
       </c>
       <c r="K5">
-        <v>2.3466264384647121E-4</v>
+        <v>8.2302022079732979E-4</v>
       </c>
       <c r="L5">
-        <v>-7.8362714848679795E-5</v>
+        <v>-9.1003105845614211E-5</v>
       </c>
       <c r="M5">
-        <v>-1.9254464959928962E-4</v>
+        <v>-4.5827959763669948E-4</v>
       </c>
       <c r="N5">
-        <v>-1.7429388959566607E-5</v>
+        <v>2.3489009347382522E-4</v>
       </c>
       <c r="O5">
-        <v>-1.7495300318323736E-4</v>
+        <v>5.4241715017937231E-5</v>
       </c>
       <c r="P5">
-        <v>-7.9731745316214764E-5</v>
+        <v>-4.0410286430518638E-4</v>
       </c>
       <c r="Q5">
-        <v>-9.3481757255879823E-5</v>
+        <v>-4.6360536494031643E-4</v>
       </c>
       <c r="R5">
-        <v>-1.077979316841469E-4</v>
+        <v>1.5710035019374582E-4</v>
       </c>
       <c r="S5">
-        <v>-9.9366022642346369E-5</v>
+        <v>-2.0750874282920951E-5</v>
       </c>
       <c r="T5">
-        <v>-1.3411948146053944E-4</v>
+        <v>3.2094295080778651E-4</v>
       </c>
       <c r="U5">
-        <v>-2.8667399687093604E-5</v>
+        <v>-3.7555176685383738E-4</v>
       </c>
       <c r="V5">
-        <v>1.9712251969617237E-4</v>
-      </c>
-      <c r="W5">
-        <v>2.4895788473839079E-4</v>
-      </c>
-      <c r="X5">
-        <v>3.5444588136896646E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
+        <v>2.604102244494421E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
       <c r="B6">
-        <v>0.25826583193833513</v>
+        <v>0.20274088955237338</v>
       </c>
       <c r="C6">
-        <v>4.4904890822141234E-5</v>
+        <v>9.2694504139246669E-5</v>
       </c>
       <c r="D6">
-        <v>-2.2612256997407102E-4</v>
+        <v>-1.0647870612544843E-3</v>
       </c>
       <c r="E6">
-        <v>2.2115500777097791E-6</v>
+        <v>9.5869127135391665E-6</v>
       </c>
       <c r="F6">
-        <v>-1.3880899169022138E-3</v>
+        <v>4.1838358526473662E-3</v>
       </c>
       <c r="G6">
-        <v>8.3551970033034287E-3</v>
+        <v>1.3906049449183692E-2</v>
       </c>
       <c r="H6">
-        <v>-1.4084637520637554E-4</v>
+        <v>-1.8608152685966467E-4</v>
       </c>
       <c r="I6">
-        <v>-4.5112218177005038E-5</v>
+        <v>-1.910397477433599E-4</v>
       </c>
       <c r="J6">
-        <v>-1.6704932942320106E-3</v>
+        <v>-5.2432002708331206E-3</v>
       </c>
       <c r="K6">
-        <v>2.6720374651377553E-4</v>
+        <v>9.1620527741184102E-4</v>
       </c>
       <c r="L6">
-        <v>-1.0673722520163661E-4</v>
+        <v>9.6172200859986467E-5</v>
       </c>
       <c r="M6">
-        <v>-6.3962884729208387E-5</v>
+        <v>1.1156557570858355E-4</v>
       </c>
       <c r="N6">
-        <v>-1.43138160232259E-4</v>
+        <v>2.3307451789803891E-4</v>
       </c>
       <c r="O6">
-        <v>-8.8339540572557416E-5</v>
+        <v>2.6987177937048447E-4</v>
       </c>
       <c r="P6">
-        <v>-6.3195224674416706E-5</v>
+        <v>-1.4057490681554635E-4</v>
       </c>
       <c r="Q6">
-        <v>-7.1385934498273016E-5</v>
+        <v>-2.2235447507986707E-4</v>
       </c>
       <c r="R6">
-        <v>-2.7297467645640591E-4</v>
+        <v>2.341255522252117E-5</v>
       </c>
       <c r="S6">
-        <v>2.4193804931321294E-5</v>
+        <v>-4.8776868845542328E-5</v>
       </c>
       <c r="T6">
-        <v>-8.3345793615817888E-5</v>
+        <v>-2.6853801445190454E-5</v>
       </c>
       <c r="U6">
-        <v>-1.6924789068817206E-5</v>
+        <v>2.0590629579182252E-4</v>
       </c>
       <c r="V6">
-        <v>1.5470403159916326E-5</v>
-      </c>
-      <c r="W6">
-        <v>-1.0271957056281859E-4</v>
-      </c>
-      <c r="X6">
-        <v>6.0106919686074498E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
+        <v>2.9663034082336587E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>4.8163041551457779E-2</v>
+        <v>-4.6031584301655992E-2</v>
       </c>
       <c r="C7">
-        <v>-2.5856304136416953E-4</v>
+        <v>-6.0168984741827008E-4</v>
       </c>
       <c r="D7">
-        <v>3.2439744495514275E-5</v>
+        <v>8.3301418978750166E-5</v>
       </c>
       <c r="E7">
-        <v>-2.0593825206629331E-7</v>
+        <v>-5.6323518914428404E-7</v>
       </c>
       <c r="F7">
-        <v>-1.834348454667848E-5</v>
+        <v>5.8700006394866999E-4</v>
       </c>
       <c r="G7">
-        <v>-1.4084637520637554E-4</v>
+        <v>-1.8608152685966467E-4</v>
       </c>
       <c r="H7">
-        <v>2.7458838248491657E-3</v>
+        <v>6.4785771973461309E-3</v>
       </c>
       <c r="I7">
-        <v>2.0299845977886713E-3</v>
+        <v>4.8674759439060562E-3</v>
       </c>
       <c r="J7">
-        <v>-1.4867163228958892E-5</v>
+        <v>-3.7827271097686313E-4</v>
       </c>
       <c r="K7">
-        <v>-4.2581298883898435E-4</v>
+        <v>-1.3476466162176089E-3</v>
       </c>
       <c r="L7">
-        <v>-9.8879532510809441E-6</v>
+        <v>-1.1389917743357204E-4</v>
       </c>
       <c r="M7">
-        <v>-7.3042663369066326E-5</v>
+        <v>-1.2373144140070139E-4</v>
       </c>
       <c r="N7">
-        <v>-2.1416435374224749E-4</v>
+        <v>-7.1477555068654309E-4</v>
       </c>
       <c r="O7">
-        <v>4.2995755551848626E-4</v>
+        <v>7.5317366670324512E-4</v>
       </c>
       <c r="P7">
-        <v>1.4254276448890258E-5</v>
+        <v>2.0006572933541468E-5</v>
       </c>
       <c r="Q7">
-        <v>7.2052685367862798E-5</v>
+        <v>2.6238160382761259E-4</v>
       </c>
       <c r="R7">
-        <v>2.3272290795791598E-4</v>
+        <v>-1.022146839478647E-4</v>
       </c>
       <c r="S7">
-        <v>-1.1293050367463782E-5</v>
+        <v>3.1624568107508716E-5</v>
       </c>
       <c r="T7">
-        <v>-5.1098474064123749E-5</v>
+        <v>-4.2615491851163414E-4</v>
       </c>
       <c r="U7">
-        <v>1.8961281724561984E-5</v>
+        <v>-4.9195427531996763E-4</v>
       </c>
       <c r="V7">
-        <v>-9.357905184582049E-5</v>
-      </c>
-      <c r="W7">
-        <v>-2.8531020893252427E-4</v>
-      </c>
-      <c r="X7">
-        <v>-3.2021165840525612E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-6.7234317913109813E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8">
-        <v>1.4261546141064077E-2</v>
+        <v>-4.9015560342806165E-2</v>
       </c>
       <c r="C8">
-        <v>-5.0634096087199426E-5</v>
+        <v>-2.6946246288375134E-4</v>
       </c>
       <c r="D8">
-        <v>3.5959808069365232E-5</v>
+        <v>-2.6407318859940701E-4</v>
       </c>
       <c r="E8">
-        <v>-3.2353270977064023E-7</v>
+        <v>1.6550285956247799E-6</v>
       </c>
       <c r="F8">
-        <v>8.7045757070425452E-5</v>
+        <v>4.4672392325036982E-5</v>
       </c>
       <c r="G8">
-        <v>-4.5112218177005038E-5</v>
+        <v>-1.910397477433599E-4</v>
       </c>
       <c r="H8">
-        <v>2.0299845977886713E-3</v>
+        <v>4.8674759439060562E-3</v>
       </c>
       <c r="I8">
-        <v>2.9027551204147718E-3</v>
+        <v>6.4268561296958208E-3</v>
       </c>
       <c r="J8">
-        <v>-1.0677293934852191E-4</v>
+        <v>-2.6108860715481365E-5</v>
       </c>
       <c r="K8">
-        <v>-5.5422431617530932E-4</v>
+        <v>-4.968648699489838E-4</v>
       </c>
       <c r="L8">
-        <v>9.807976383711443E-5</v>
+        <v>-1.9926058087830924E-5</v>
       </c>
       <c r="M8">
-        <v>2.8557926751862769E-4</v>
+        <v>1.2386395123325662E-4</v>
       </c>
       <c r="N8">
-        <v>3.0831952862965441E-5</v>
+        <v>4.9296523200919955E-4</v>
       </c>
       <c r="O8">
-        <v>8.3036959235938135E-4</v>
+        <v>2.3416140773884681E-3</v>
       </c>
       <c r="P8">
-        <v>-1.7861127686384344E-5</v>
+        <v>-2.3708190477269447E-4</v>
       </c>
       <c r="Q8">
-        <v>6.3116284849172892E-5</v>
+        <v>-3.0336901084799931E-4</v>
       </c>
       <c r="R8">
-        <v>5.1320575761931936E-5</v>
+        <v>-4.8055333535884691E-4</v>
       </c>
       <c r="S8">
-        <v>-7.0650423620749817E-5</v>
+        <v>4.7637402600803218E-5</v>
       </c>
       <c r="T8">
-        <v>-1.0799987451518564E-4</v>
+        <v>-6.8815416857900889E-4</v>
       </c>
       <c r="U8">
-        <v>2.6038174193982952E-5</v>
+        <v>-5.128077676078873E-4</v>
       </c>
       <c r="V8">
-        <v>-1.507512047668792E-4</v>
-      </c>
-      <c r="W8">
-        <v>-3.5961257294858879E-4</v>
-      </c>
-      <c r="X8">
-        <v>-3.4336828012955511E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.45">
+        <v>4.4859298221089361E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9">
-        <v>-6.6368314335145022E-3</v>
+        <v>-0.12674912600636642</v>
       </c>
       <c r="C9">
-        <v>3.7224195143447454E-4</v>
+        <v>2.7203901518497802E-4</v>
       </c>
       <c r="D9">
-        <v>-7.3647252124877348E-4</v>
+        <v>-2.3187287045147928E-4</v>
       </c>
       <c r="E9">
-        <v>3.9262931312461467E-6</v>
+        <v>-1.6526554600478413E-6</v>
       </c>
       <c r="F9">
-        <v>-1.9619946988589342E-3</v>
+        <v>-5.7718797263359807E-3</v>
       </c>
       <c r="G9">
-        <v>-1.6704932942320106E-3</v>
+        <v>-5.2432002708331206E-3</v>
       </c>
       <c r="H9">
-        <v>-1.4867163228958892E-5</v>
+        <v>-3.7827271097686313E-4</v>
       </c>
       <c r="I9">
-        <v>-1.0677293934852191E-4</v>
+        <v>-2.6108860715481365E-5</v>
       </c>
       <c r="J9">
-        <v>4.6971573946409141E-3</v>
+        <v>1.0410378728583761E-2</v>
       </c>
       <c r="K9">
-        <v>-2.0795282759234856E-4</v>
+        <v>-8.3131497624027676E-4</v>
       </c>
       <c r="L9">
-        <v>-2.2364463656005874E-5</v>
+        <v>-2.8096279877653206E-4</v>
       </c>
       <c r="M9">
-        <v>7.5296355466448247E-5</v>
+        <v>-8.0220139626363627E-5</v>
       </c>
       <c r="N9">
-        <v>2.0870254285064189E-4</v>
+        <v>-2.1406202123865482E-4</v>
       </c>
       <c r="O9">
-        <v>2.7035363338898154E-4</v>
+        <v>-2.6018199393194972E-4</v>
       </c>
       <c r="P9">
-        <v>2.0042412272291456E-5</v>
+        <v>8.9908888338798357E-4</v>
       </c>
       <c r="Q9">
-        <v>1.4696850123456636E-4</v>
+        <v>1.0855700319735689E-4</v>
       </c>
       <c r="R9">
-        <v>2.6652123611358965E-4</v>
+        <v>-4.1772132453508914E-5</v>
       </c>
       <c r="S9">
-        <v>1.6343181816298215E-4</v>
+        <v>9.7059166693343299E-5</v>
       </c>
       <c r="T9">
-        <v>3.0376354830611131E-4</v>
+        <v>-2.624674085734786E-4</v>
       </c>
       <c r="U9">
-        <v>4.7273086918398714E-5</v>
+        <v>1.3205699944878174E-5</v>
       </c>
       <c r="V9">
-        <v>-1.6696500194858695E-5</v>
-      </c>
-      <c r="W9">
-        <v>2.8668575943555444E-4</v>
-      </c>
-      <c r="X9">
-        <v>2.8127789996577932E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
+        <v>1.719209606785831E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10">
-        <v>0.39941543818973613</v>
+        <v>-6.2210885453259028E-2</v>
       </c>
       <c r="C10">
-        <v>2.1027824044394472E-4</v>
+        <v>1.2000002113984241E-3</v>
       </c>
       <c r="D10">
-        <v>-8.6512334449860562E-5</v>
+        <v>-6.0636738312894569E-4</v>
       </c>
       <c r="E10">
-        <v>5.018275744685696E-7</v>
+        <v>4.0160140974765551E-6</v>
       </c>
       <c r="F10">
-        <v>2.3466264384647121E-4</v>
+        <v>8.2302022079732979E-4</v>
       </c>
       <c r="G10">
-        <v>2.6720374651377553E-4</v>
+        <v>9.1620527741184102E-4</v>
       </c>
       <c r="H10">
-        <v>-4.2581298883898435E-4</v>
+        <v>-1.3476466162176089E-3</v>
       </c>
       <c r="I10">
-        <v>-5.5422431617530932E-4</v>
+        <v>-4.968648699489838E-4</v>
       </c>
       <c r="J10">
-        <v>-2.0795282759234856E-4</v>
+        <v>-8.3131497624027676E-4</v>
       </c>
       <c r="K10">
-        <v>3.7011682585107817E-3</v>
+        <v>1.1703905010635158E-2</v>
       </c>
       <c r="L10">
-        <v>1.6294324064392166E-5</v>
+        <v>7.7269284806363614E-5</v>
       </c>
       <c r="M10">
-        <v>9.3940496506934455E-4</v>
+        <v>1.2327310698780837E-3</v>
       </c>
       <c r="N10">
-        <v>2.5616173714592613E-3</v>
+        <v>7.3856151859786829E-3</v>
       </c>
       <c r="O10">
-        <v>2.5730298487589526E-3</v>
+        <v>9.6678621922782759E-3</v>
       </c>
       <c r="P10">
-        <v>-4.2346694574074375E-4</v>
+        <v>-1.0159284509709454E-3</v>
       </c>
       <c r="Q10">
-        <v>-3.1348623754018048E-4</v>
+        <v>2.6842562864406983E-4</v>
       </c>
       <c r="R10">
-        <v>-7.3143722303468462E-5</v>
+        <v>5.476491213534377E-4</v>
       </c>
       <c r="S10">
-        <v>5.1670636040525774E-5</v>
+        <v>-3.3585996022231419E-6</v>
       </c>
       <c r="T10">
-        <v>4.455067477793619E-5</v>
+        <v>-7.3704970850664206E-4</v>
       </c>
       <c r="U10">
-        <v>-1.8187881926069277E-5</v>
+        <v>-3.1329852400413299E-4</v>
       </c>
       <c r="V10">
-        <v>2.9393006523171106E-4</v>
-      </c>
-      <c r="W10">
-        <v>1.4936873688883834E-4</v>
-      </c>
-      <c r="X10">
-        <v>1.0442731807533932E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
+        <v>1.1773538846874168E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11">
-        <v>4.8557956790069565E-2</v>
+        <v>2.7391635461686173E-2</v>
       </c>
       <c r="C11">
-        <v>-1.2114777377603185E-4</v>
+        <v>5.5054485348267237E-5</v>
       </c>
       <c r="D11">
-        <v>1.3365469505967727E-4</v>
+        <v>-7.5339111904165084E-5</v>
       </c>
       <c r="E11">
-        <v>-9.3746123465261359E-7</v>
+        <v>6.4834350842692754E-7</v>
       </c>
       <c r="F11">
-        <v>-7.8362714848679795E-5</v>
+        <v>-9.1003105845614211E-5</v>
       </c>
       <c r="G11">
-        <v>-1.0673722520163661E-4</v>
+        <v>9.6172200859986467E-5</v>
       </c>
       <c r="H11">
-        <v>-9.8879532510809441E-6</v>
+        <v>-1.1389917743357204E-4</v>
       </c>
       <c r="I11">
-        <v>9.807976383711443E-5</v>
+        <v>-1.9926058087830924E-5</v>
       </c>
       <c r="J11">
-        <v>-2.2364463656005874E-5</v>
+        <v>-2.8096279877653206E-4</v>
       </c>
       <c r="K11">
-        <v>1.6294324064392166E-5</v>
+        <v>7.7269284806363614E-5</v>
       </c>
       <c r="L11">
-        <v>1.5361863222091198E-3</v>
+        <v>2.8468051165424402E-3</v>
       </c>
       <c r="M11">
-        <v>7.5947130712913913E-4</v>
+        <v>1.4259813595720655E-3</v>
       </c>
       <c r="N11">
-        <v>8.2800392410344774E-4</v>
+        <v>1.4831118052207972E-3</v>
       </c>
       <c r="O11">
-        <v>8.8931060775672476E-4</v>
+        <v>1.4464908331406697E-3</v>
       </c>
       <c r="P11">
-        <v>2.4636038076436046E-4</v>
+        <v>2.1013049816061605E-5</v>
       </c>
       <c r="Q11">
-        <v>1.511375291290164E-4</v>
+        <v>-9.579160590653178E-5</v>
       </c>
       <c r="R11">
-        <v>1.3731456188678301E-4</v>
+        <v>8.4774299747307838E-5</v>
       </c>
       <c r="S11">
-        <v>1.5400546516053707E-5</v>
+        <v>-1.2067355488589132E-5</v>
       </c>
       <c r="T11">
-        <v>-4.6039777457916077E-6</v>
+        <v>2.7901110677162888E-4</v>
       </c>
       <c r="U11">
-        <v>1.0648834815214715E-5</v>
+        <v>1.1238028491274068E-4</v>
       </c>
       <c r="V11">
-        <v>-2.2740963322433698E-4</v>
-      </c>
-      <c r="W11">
-        <v>-1.9755096550922975E-4</v>
-      </c>
-      <c r="X11">
-        <v>-5.6209306917620484E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
+        <v>9.0607179546344039E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
       <c r="B12">
-        <v>8.324986155760998E-2</v>
+        <v>-6.7002245296373872E-3</v>
       </c>
       <c r="C12">
-        <v>-5.4049268603414383E-6</v>
+        <v>-1.4148358955888682E-5</v>
       </c>
       <c r="D12">
-        <v>1.0786887447586033E-4</v>
+        <v>-4.3367704074832175E-5</v>
       </c>
       <c r="E12">
-        <v>-6.225705231806413E-7</v>
+        <v>3.3908806814171558E-7</v>
       </c>
       <c r="F12">
-        <v>-1.9254464959928962E-4</v>
+        <v>-4.5827959763669948E-4</v>
       </c>
       <c r="G12">
-        <v>-6.3962884729208387E-5</v>
+        <v>1.1156557570858355E-4</v>
       </c>
       <c r="H12">
-        <v>-7.3042663369066326E-5</v>
+        <v>-1.2373144140070139E-4</v>
       </c>
       <c r="I12">
-        <v>2.8557926751862769E-4</v>
+        <v>1.2386395123325662E-4</v>
       </c>
       <c r="J12">
-        <v>7.5296355466448247E-5</v>
+        <v>-8.0220139626363627E-5</v>
       </c>
       <c r="K12">
-        <v>9.3940496506934455E-4</v>
+        <v>1.2327310698780837E-3</v>
       </c>
       <c r="L12">
-        <v>7.5947130712913913E-4</v>
+        <v>1.4259813595720655E-3</v>
       </c>
       <c r="M12">
-        <v>3.145142660462659E-3</v>
+        <v>3.7186417196930399E-3</v>
       </c>
       <c r="N12">
-        <v>2.0781272389979806E-3</v>
+        <v>2.4501558708115967E-3</v>
       </c>
       <c r="O12">
-        <v>2.2276453424161431E-3</v>
+        <v>2.7831608806869277E-3</v>
       </c>
       <c r="P12">
-        <v>8.3934901531948079E-5</v>
+        <v>9.018579545903144E-5</v>
       </c>
       <c r="Q12">
-        <v>3.9374504148149899E-4</v>
+        <v>1.8086009059728935E-4</v>
       </c>
       <c r="R12">
-        <v>5.1057785978522383E-4</v>
+        <v>2.488303329208658E-4</v>
       </c>
       <c r="S12">
-        <v>7.0866712507610037E-5</v>
+        <v>-4.0774626567181859E-5</v>
       </c>
       <c r="T12">
-        <v>8.8411283400370707E-5</v>
+        <v>-1.3337813168979017E-4</v>
       </c>
       <c r="U12">
-        <v>9.2588776716026838E-6</v>
+        <v>8.293340180954805E-5</v>
       </c>
       <c r="V12">
-        <v>-1.6291297573435196E-4</v>
-      </c>
-      <c r="W12">
-        <v>-2.302174325195459E-4</v>
-      </c>
-      <c r="X12">
-        <v>-6.7552407167642582E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-7.978925730574289E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.19183090799829272</v>
+        <v>2.9234955166247672E-2</v>
       </c>
       <c r="C13">
-        <v>-3.112135246937004E-4</v>
+        <v>3.863695026518042E-4</v>
       </c>
       <c r="D13">
-        <v>2.3830195897339874E-4</v>
+        <v>-1.5777150107386395E-5</v>
       </c>
       <c r="E13">
-        <v>-1.553823230643895E-6</v>
+        <v>1.2973641503029949E-7</v>
       </c>
       <c r="F13">
-        <v>-1.7429388959566607E-5</v>
+        <v>2.3489009347382522E-4</v>
       </c>
       <c r="G13">
-        <v>-1.43138160232259E-4</v>
+        <v>2.3307451789803891E-4</v>
       </c>
       <c r="H13">
-        <v>-2.1416435374224749E-4</v>
+        <v>-7.1477555068654309E-4</v>
       </c>
       <c r="I13">
-        <v>3.0831952862965441E-5</v>
+        <v>4.9296523200919955E-4</v>
       </c>
       <c r="J13">
-        <v>2.0870254285064189E-4</v>
+        <v>-2.1406202123865482E-4</v>
       </c>
       <c r="K13">
-        <v>2.5616173714592613E-3</v>
+        <v>7.3856151859786829E-3</v>
       </c>
       <c r="L13">
-        <v>8.2800392410344774E-4</v>
+        <v>1.4831118052207972E-3</v>
       </c>
       <c r="M13">
-        <v>2.0781272389979806E-3</v>
+        <v>2.4501558708115967E-3</v>
       </c>
       <c r="N13">
-        <v>4.9808954357441673E-3</v>
+        <v>1.1326810704899257E-2</v>
       </c>
       <c r="O13">
-        <v>3.9099269000366895E-3</v>
+        <v>9.0740351142622709E-3</v>
       </c>
       <c r="P13">
-        <v>3.0194222816008233E-4</v>
+        <v>3.8110307757495973E-4</v>
       </c>
       <c r="Q13">
-        <v>1.0293514294964199E-4</v>
+        <v>2.2937991967032518E-4</v>
       </c>
       <c r="R13">
-        <v>3.659308904274954E-4</v>
+        <v>4.5087183031538918E-4</v>
       </c>
       <c r="S13">
-        <v>1.184986218552204E-4</v>
+        <v>-1.7467715395743418E-5</v>
       </c>
       <c r="T13">
-        <v>1.1614573506557222E-4</v>
+        <v>-4.0344896305024853E-4</v>
       </c>
       <c r="U13">
-        <v>-3.7995578682103217E-5</v>
+        <v>-1.2545223890460906E-4</v>
       </c>
       <c r="V13">
-        <v>1.0351564600148656E-4</v>
-      </c>
-      <c r="W13">
-        <v>3.1126334246759334E-4</v>
-      </c>
-      <c r="X13">
-        <v>-1.1909887307919777E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-8.551033110670252E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
       <c r="B14">
-        <v>0.12587912167647741</v>
+        <v>9.057466543445776E-2</v>
       </c>
       <c r="C14">
-        <v>-4.8831263666758136E-4</v>
+        <v>2.3163888480428078E-4</v>
       </c>
       <c r="D14">
-        <v>1.2676641342715053E-4</v>
+        <v>-3.1894721641678378E-4</v>
       </c>
       <c r="E14">
-        <v>-8.1288867895539397E-7</v>
+        <v>2.2258201795190681E-6</v>
       </c>
       <c r="F14">
-        <v>-1.7495300318323736E-4</v>
+        <v>5.4241715017937231E-5</v>
       </c>
       <c r="G14">
-        <v>-8.8339540572557416E-5</v>
+        <v>2.6987177937048447E-4</v>
       </c>
       <c r="H14">
-        <v>4.2995755551848626E-4</v>
+        <v>7.5317366670324512E-4</v>
       </c>
       <c r="I14">
-        <v>8.3036959235938135E-4</v>
+        <v>2.3416140773884681E-3</v>
       </c>
       <c r="J14">
-        <v>2.7035363338898154E-4</v>
+        <v>-2.6018199393194972E-4</v>
       </c>
       <c r="K14">
-        <v>2.5730298487589526E-3</v>
+        <v>9.6678621922782759E-3</v>
       </c>
       <c r="L14">
-        <v>8.8931060775672476E-4</v>
+        <v>1.4464908331406697E-3</v>
       </c>
       <c r="M14">
-        <v>2.2276453424161431E-3</v>
+        <v>2.7831608806869277E-3</v>
       </c>
       <c r="N14">
-        <v>3.9099269000366895E-3</v>
+        <v>9.0740351142622709E-3</v>
       </c>
       <c r="O14">
-        <v>5.5631085185884888E-3</v>
+        <v>1.5094037081146722E-2</v>
       </c>
       <c r="P14">
-        <v>3.1621292489909195E-4</v>
+        <v>-2.1269368284091133E-4</v>
       </c>
       <c r="Q14">
-        <v>2.4251065955846213E-4</v>
+        <v>5.644558484557494E-4</v>
       </c>
       <c r="R14">
-        <v>7.5057610610881659E-4</v>
+        <v>5.7497919218089336E-4</v>
       </c>
       <c r="S14">
-        <v>1.8522446870024344E-4</v>
+        <v>-3.0028542240709776E-5</v>
       </c>
       <c r="T14">
-        <v>1.5369221576009315E-4</v>
+        <v>-6.3689632433542795E-4</v>
       </c>
       <c r="U14">
-        <v>-9.9999081838189575E-6</v>
+        <v>-4.1032489785244311E-4</v>
       </c>
       <c r="V14">
-        <v>-9.347311524682397E-6</v>
-      </c>
-      <c r="W14">
-        <v>-1.4167535976461866E-4</v>
-      </c>
-      <c r="X14">
-        <v>-9.1577693838158919E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-1.4916441664816413E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
       <c r="B15">
-        <v>0.13013159587915407</v>
+        <v>0.43710827147578224</v>
       </c>
       <c r="C15">
-        <v>-5.1058898359563547E-4</v>
+        <v>-3.0865009980015961E-4</v>
       </c>
       <c r="D15">
-        <v>-3.2102528274203027E-5</v>
+        <v>-4.3497562584504483E-4</v>
       </c>
       <c r="E15">
-        <v>2.3206820198426247E-7</v>
+        <v>3.0507737098397738E-6</v>
       </c>
       <c r="F15">
-        <v>-7.9731745316214764E-5</v>
+        <v>-4.0410286430518638E-4</v>
       </c>
       <c r="G15">
-        <v>-6.3195224674416706E-5</v>
+        <v>-1.4057490681554635E-4</v>
       </c>
       <c r="H15">
-        <v>1.4254276448890258E-5</v>
+        <v>2.0006572933541468E-5</v>
       </c>
       <c r="I15">
-        <v>-1.7861127686384344E-5</v>
+        <v>-2.3708190477269447E-4</v>
       </c>
       <c r="J15">
-        <v>2.0042412272291456E-5</v>
+        <v>8.9908888338798357E-4</v>
       </c>
       <c r="K15">
-        <v>-4.2346694574074375E-4</v>
+        <v>-1.0159284509709454E-3</v>
       </c>
       <c r="L15">
-        <v>2.4636038076436046E-4</v>
+        <v>2.1013049816061605E-5</v>
       </c>
       <c r="M15">
-        <v>8.3934901531948079E-5</v>
+        <v>9.018579545903144E-5</v>
       </c>
       <c r="N15">
-        <v>3.0194222816008233E-4</v>
+        <v>3.8110307757495973E-4</v>
       </c>
       <c r="O15">
-        <v>3.1621292489909195E-4</v>
+        <v>-2.1269368284091133E-4</v>
       </c>
       <c r="P15">
-        <v>3.7227445475122726E-3</v>
+        <v>7.9163757808122376E-3</v>
       </c>
       <c r="Q15">
-        <v>3.308100951615817E-6</v>
+        <v>-3.1518789372380956E-4</v>
       </c>
       <c r="R15">
-        <v>1.5187328114232498E-4</v>
+        <v>-4.25936965378188E-5</v>
       </c>
       <c r="S15">
-        <v>5.8234556663350396E-5</v>
+        <v>-3.6613654418591566E-5</v>
       </c>
       <c r="T15">
-        <v>7.7171209770333601E-5</v>
+        <v>4.5195223573795882E-4</v>
       </c>
       <c r="U15">
-        <v>-2.2027093898393277E-6</v>
+        <v>-1.4336752763554467E-4</v>
       </c>
       <c r="V15">
-        <v>-2.0201559451680612E-4</v>
-      </c>
-      <c r="W15">
-        <v>-4.0637434341484304E-4</v>
-      </c>
-      <c r="X15">
-        <v>1.1174667430248891E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.45">
+        <v>1.5908035348794852E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16">
-        <v>-0.25052726994454366</v>
+        <v>-0.16989640255357782</v>
       </c>
       <c r="C16">
-        <v>1.553474449606079E-4</v>
+        <v>4.0188813869035346E-4</v>
       </c>
       <c r="D16">
-        <v>-2.4934892580094452E-4</v>
+        <v>6.9684311828802775E-5</v>
       </c>
       <c r="E16">
-        <v>1.8265184703276574E-6</v>
+        <v>-4.0371914302733008E-7</v>
       </c>
       <c r="F16">
-        <v>-9.3481757255879823E-5</v>
+        <v>-4.6360536494031643E-4</v>
       </c>
       <c r="G16">
-        <v>-7.1385934498273016E-5</v>
+        <v>-2.2235447507986707E-4</v>
       </c>
       <c r="H16">
-        <v>7.2052685367862798E-5</v>
+        <v>2.6238160382761259E-4</v>
       </c>
       <c r="I16">
-        <v>6.3116284849172892E-5</v>
+        <v>-3.0336901084799931E-4</v>
       </c>
       <c r="J16">
-        <v>1.4696850123456636E-4</v>
+        <v>1.0855700319735689E-4</v>
       </c>
       <c r="K16">
-        <v>-3.1348623754018048E-4</v>
+        <v>2.6842562864406983E-4</v>
       </c>
       <c r="L16">
-        <v>1.511375291290164E-4</v>
+        <v>-9.579160590653178E-5</v>
       </c>
       <c r="M16">
-        <v>3.9374504148149899E-4</v>
+        <v>1.8086009059728935E-4</v>
       </c>
       <c r="N16">
-        <v>1.0293514294964199E-4</v>
+        <v>2.2937991967032518E-4</v>
       </c>
       <c r="O16">
-        <v>2.4251065955846213E-4</v>
+        <v>5.644558484557494E-4</v>
       </c>
       <c r="P16">
-        <v>3.308100951615817E-6</v>
+        <v>-3.1518789372380956E-4</v>
       </c>
       <c r="Q16">
-        <v>2.1011725247917306E-3</v>
+        <v>5.8928014061728788E-3</v>
       </c>
       <c r="R16">
-        <v>1.030713574456993E-3</v>
+        <v>1.5682229226062613E-3</v>
       </c>
       <c r="S16">
-        <v>8.6521251908371066E-4</v>
+        <v>2.940216742451967E-5</v>
       </c>
       <c r="T16">
-        <v>8.929108871038136E-4</v>
+        <v>2.962614176114589E-4</v>
       </c>
       <c r="U16">
-        <v>1.9458219512307852E-5</v>
+        <v>-1.8807341008975358E-4</v>
       </c>
       <c r="V16">
-        <v>-1.399344671267247E-4</v>
-      </c>
-      <c r="W16">
-        <v>-2.2476016799124289E-4</v>
-      </c>
-      <c r="X16">
-        <v>7.018659839133099E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-5.1589569802391504E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>36</v>
       </c>
       <c r="B17">
-        <v>-0.3610938556438133</v>
+        <v>3.0771700814635813E-2</v>
       </c>
       <c r="C17">
-        <v>-1.8797879356674985E-4</v>
+        <v>-2.9677535593191848E-5</v>
       </c>
       <c r="D17">
-        <v>-2.4310981119817464E-4</v>
+        <v>-1.3380529762663587E-4</v>
       </c>
       <c r="E17">
-        <v>1.6928956128348815E-6</v>
+        <v>1.1114608187976817E-6</v>
       </c>
       <c r="F17">
-        <v>-1.077979316841469E-4</v>
+        <v>1.5710035019374582E-4</v>
       </c>
       <c r="G17">
-        <v>-2.7297467645640591E-4</v>
+        <v>2.341255522252117E-5</v>
       </c>
       <c r="H17">
-        <v>2.3272290795791598E-4</v>
+        <v>-1.022146839478647E-4</v>
       </c>
       <c r="I17">
-        <v>5.1320575761931936E-5</v>
+        <v>-4.8055333535884691E-4</v>
       </c>
       <c r="J17">
-        <v>2.6652123611358965E-4</v>
+        <v>-4.1772132453508914E-5</v>
       </c>
       <c r="K17">
-        <v>-7.3143722303468462E-5</v>
+        <v>5.476491213534377E-4</v>
       </c>
       <c r="L17">
-        <v>1.3731456188678301E-4</v>
+        <v>8.4774299747307838E-5</v>
       </c>
       <c r="M17">
-        <v>5.1057785978522383E-4</v>
+        <v>2.488303329208658E-4</v>
       </c>
       <c r="N17">
-        <v>3.659308904274954E-4</v>
+        <v>4.5087183031538918E-4</v>
       </c>
       <c r="O17">
-        <v>7.5057610610881659E-4</v>
+        <v>5.7497919218089336E-4</v>
       </c>
       <c r="P17">
-        <v>1.5187328114232498E-4</v>
+        <v>-4.25936965378188E-5</v>
       </c>
       <c r="Q17">
-        <v>1.030713574456993E-3</v>
+        <v>1.5682229226062613E-3</v>
       </c>
       <c r="R17">
-        <v>3.2315672807933663E-3</v>
+        <v>2.2256143332354912E-3</v>
       </c>
       <c r="S17">
-        <v>8.7393912375672222E-4</v>
+        <v>3.2231722892413251E-5</v>
       </c>
       <c r="T17">
-        <v>9.1349007929998486E-4</v>
+        <v>2.3805112849134888E-4</v>
       </c>
       <c r="U17">
-        <v>6.7384101524742115E-6</v>
+        <v>-8.8839496349793183E-5</v>
       </c>
       <c r="V17">
-        <v>-1.9422720710969378E-4</v>
-      </c>
-      <c r="W17">
-        <v>-2.7843696041894177E-4</v>
-      </c>
-      <c r="X17">
-        <v>7.1344382078609879E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.45">
+        <v>1.5181282276677667E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B18">
-        <v>-4.5873394593235646E-2</v>
+        <v>-6.4873071409165595E-2</v>
       </c>
       <c r="C18">
-        <v>-2.0908544040013001E-5</v>
+        <v>-2.4245275848219696E-7</v>
       </c>
       <c r="D18">
-        <v>-6.3948372772215309E-5</v>
+        <v>-3.1248638249967847E-5</v>
       </c>
       <c r="E18">
-        <v>4.2099051499104546E-7</v>
+        <v>1.8706645064358191E-7</v>
       </c>
       <c r="F18">
-        <v>-9.9366022642346369E-5</v>
+        <v>-2.0750874282920951E-5</v>
       </c>
       <c r="G18">
-        <v>2.4193804931321294E-5</v>
+        <v>-4.8776868845542328E-5</v>
       </c>
       <c r="H18">
-        <v>-1.1293050367463782E-5</v>
+        <v>3.1624568107508716E-5</v>
       </c>
       <c r="I18">
-        <v>-7.0650423620749817E-5</v>
+        <v>4.7637402600803218E-5</v>
       </c>
       <c r="J18">
-        <v>1.6343181816298215E-4</v>
+        <v>9.7059166693343299E-5</v>
       </c>
       <c r="K18">
-        <v>5.1670636040525774E-5</v>
+        <v>-3.3585996022231419E-6</v>
       </c>
       <c r="L18">
-        <v>1.5400546516053707E-5</v>
+        <v>-1.2067355488589132E-5</v>
       </c>
       <c r="M18">
-        <v>7.0866712507610037E-5</v>
+        <v>-4.0774626567181859E-5</v>
       </c>
       <c r="N18">
-        <v>1.184986218552204E-4</v>
+        <v>-1.7467715395743418E-5</v>
       </c>
       <c r="O18">
-        <v>1.8522446870024344E-4</v>
+        <v>-3.0028542240709776E-5</v>
       </c>
       <c r="P18">
-        <v>5.8234556663350396E-5</v>
+        <v>-3.6613654418591566E-5</v>
       </c>
       <c r="Q18">
-        <v>8.6521251908371066E-4</v>
+        <v>2.940216742451967E-5</v>
       </c>
       <c r="R18">
-        <v>8.7393912375672222E-4</v>
+        <v>3.2231722892413251E-5</v>
       </c>
       <c r="S18">
-        <v>1.6577037796374709E-3</v>
+        <v>4.5272498354550738E-5</v>
       </c>
       <c r="T18">
-        <v>8.603254104734211E-4</v>
+        <v>-1.2364970942538688E-4</v>
       </c>
       <c r="U18">
-        <v>-5.8407923815361145E-7</v>
+        <v>-1.7392997990391728E-4</v>
       </c>
       <c r="V18">
-        <v>-7.6149259974676138E-5</v>
-      </c>
-      <c r="W18">
-        <v>-6.6462540564192978E-5</v>
-      </c>
-      <c r="X18">
-        <v>1.3963498683085356E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.45">
+        <v>3.8153373019651153E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B19">
-        <v>-0.12220417564629157</v>
+        <v>-0.42590003100660639</v>
       </c>
       <c r="C19">
-        <v>2.3529380347903371E-5</v>
+        <v>-1.2705913473042105E-4</v>
       </c>
       <c r="D19">
-        <v>-1.9561435392379499E-4</v>
+        <v>9.4054051431696241E-5</v>
       </c>
       <c r="E19">
-        <v>1.3033922271891339E-6</v>
+        <v>-6.3192587150617352E-7</v>
       </c>
       <c r="F19">
-        <v>-1.3411948146053944E-4</v>
+        <v>3.2094295080778651E-4</v>
       </c>
       <c r="G19">
-        <v>-8.3345793615817888E-5</v>
+        <v>-2.6853801445190454E-5</v>
       </c>
       <c r="H19">
-        <v>-5.1098474064123749E-5</v>
+        <v>-4.2615491851163414E-4</v>
       </c>
       <c r="I19">
-        <v>-1.0799987451518564E-4</v>
+        <v>-6.8815416857900889E-4</v>
       </c>
       <c r="J19">
-        <v>3.0376354830611131E-4</v>
+        <v>-2.624674085734786E-4</v>
       </c>
       <c r="K19">
-        <v>4.455067477793619E-5</v>
+        <v>-7.3704970850664206E-4</v>
       </c>
       <c r="L19">
-        <v>-4.6039777457916077E-6</v>
+        <v>2.7901110677162888E-4</v>
       </c>
       <c r="M19">
-        <v>8.8411283400370707E-5</v>
+        <v>-1.3337813168979017E-4</v>
       </c>
       <c r="N19">
-        <v>1.1614573506557222E-4</v>
+        <v>-4.0344896305024853E-4</v>
       </c>
       <c r="O19">
-        <v>1.5369221576009315E-4</v>
+        <v>-6.3689632433542795E-4</v>
       </c>
       <c r="P19">
-        <v>7.7171209770333601E-5</v>
+        <v>4.5195223573795882E-4</v>
       </c>
       <c r="Q19">
-        <v>8.929108871038136E-4</v>
+        <v>2.962614176114589E-4</v>
       </c>
       <c r="R19">
-        <v>9.1349007929998486E-4</v>
+        <v>2.3805112849134888E-4</v>
       </c>
       <c r="S19">
-        <v>8.603254104734211E-4</v>
+        <v>-1.2364970942538688E-4</v>
       </c>
       <c r="T19">
-        <v>1.6273186714505223E-3</v>
+        <v>7.7864939498331724E-3</v>
       </c>
       <c r="U19">
-        <v>1.5584606163557486E-6</v>
+        <v>9.4674790505991032E-4</v>
       </c>
       <c r="V19">
-        <v>-1.3891124440295076E-4</v>
-      </c>
-      <c r="W19">
-        <v>-1.4191275969462107E-4</v>
-      </c>
-      <c r="X19">
-        <v>6.1133070258525268E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.45">
+        <v>-6.0919356178901034E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B20">
-        <v>-2.3237860381584884E-2</v>
+        <v>0.21482549845695692</v>
       </c>
       <c r="C20">
-        <v>1.2968942956576634E-5</v>
+        <v>3.1551512185646051E-4</v>
       </c>
       <c r="D20">
-        <v>-2.1657460727906143E-5</v>
+        <v>2.5985514102137668E-5</v>
       </c>
       <c r="E20">
-        <v>1.4223959351566777E-7</v>
+        <v>-9.8253635935962116E-8</v>
       </c>
       <c r="F20">
-        <v>-2.8667399687093604E-5</v>
+        <v>-3.7555176685383738E-4</v>
       </c>
       <c r="G20">
-        <v>-1.6924789068817206E-5</v>
+        <v>2.0590629579182252E-4</v>
       </c>
       <c r="H20">
-        <v>1.8961281724561984E-5</v>
+        <v>-4.9195427531996763E-4</v>
       </c>
       <c r="I20">
-        <v>2.6038174193982952E-5</v>
+        <v>-5.128077676078873E-4</v>
       </c>
       <c r="J20">
-        <v>4.7273086918398714E-5</v>
+        <v>1.3205699944878174E-5</v>
       </c>
       <c r="K20">
-        <v>-1.8187881926069277E-5</v>
+        <v>-3.1329852400413299E-4</v>
       </c>
       <c r="L20">
-        <v>1.0648834815214715E-5</v>
+        <v>1.1238028491274068E-4</v>
       </c>
       <c r="M20">
-        <v>9.2588776716026838E-6</v>
+        <v>8.293340180954805E-5</v>
       </c>
       <c r="N20">
-        <v>-3.7995578682103217E-5</v>
+        <v>-1.2545223890460906E-4</v>
       </c>
       <c r="O20">
-        <v>-9.9999081838189575E-6</v>
+        <v>-4.1032489785244311E-4</v>
       </c>
       <c r="P20">
-        <v>-2.2027093898393277E-6</v>
+        <v>-1.4336752763554467E-4</v>
       </c>
       <c r="Q20">
-        <v>1.9458219512307852E-5</v>
+        <v>-1.8807341008975358E-4</v>
       </c>
       <c r="R20">
-        <v>6.7384101524742115E-6</v>
+        <v>-8.8839496349793183E-5</v>
       </c>
       <c r="S20">
-        <v>-5.8407923815361145E-7</v>
+        <v>-1.7392997990391728E-4</v>
       </c>
       <c r="T20">
-        <v>1.5584606163557486E-6</v>
+        <v>9.4674790505991032E-4</v>
       </c>
       <c r="U20">
-        <v>2.0339892214170915E-5</v>
+        <v>5.7801893254681418E-3</v>
       </c>
       <c r="V20">
-        <v>-8.1505028307338407E-5</v>
-      </c>
-      <c r="W20">
-        <v>-9.4299035647029721E-5</v>
-      </c>
-      <c r="X20">
-        <v>4.372412946563321E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.45">
+        <v>1.9073189964824381E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B21">
-        <v>6.2526475485622859E-2</v>
+        <v>-14.054901345257093</v>
       </c>
       <c r="C21">
-        <v>7.0167077762441703E-5</v>
+        <v>-7.8078685214055411E-3</v>
       </c>
       <c r="D21">
-        <v>5.5424101516887009E-5</v>
+        <v>-5.6059553699710142E-2</v>
       </c>
       <c r="E21">
-        <v>-3.9682743802403028E-7</v>
+        <v>4.0176823221627843E-4</v>
       </c>
       <c r="F21">
-        <v>1.9712251969617237E-4</v>
+        <v>2.604102244494421E-2</v>
       </c>
       <c r="G21">
-        <v>1.5470403159916326E-5</v>
+        <v>2.9663034082336587E-2</v>
       </c>
       <c r="H21">
-        <v>-9.357905184582049E-5</v>
+        <v>-6.7234317913109813E-3</v>
       </c>
       <c r="I21">
-        <v>-1.507512047668792E-4</v>
+        <v>4.4859298221089361E-3</v>
       </c>
       <c r="J21">
-        <v>-1.6696500194858695E-5</v>
+        <v>1.719209606785831E-2</v>
       </c>
       <c r="K21">
-        <v>2.9393006523171106E-4</v>
+        <v>1.1773538846874168E-2</v>
       </c>
       <c r="L21">
-        <v>-2.2740963322433698E-4</v>
+        <v>9.0607179546344039E-4</v>
       </c>
       <c r="M21">
-        <v>-1.6291297573435196E-4</v>
+        <v>-7.978925730574289E-4</v>
       </c>
       <c r="N21">
-        <v>1.0351564600148656E-4</v>
+        <v>-8.551033110670252E-3</v>
       </c>
       <c r="O21">
-        <v>-9.347311524682397E-6</v>
+        <v>-1.4916441664816413E-3</v>
       </c>
       <c r="P21">
-        <v>-2.0201559451680612E-4</v>
+        <v>1.5908035348794852E-2</v>
       </c>
       <c r="Q21">
-        <v>-1.399344671267247E-4</v>
+        <v>-5.1589569802391504E-3</v>
       </c>
       <c r="R21">
-        <v>-1.9422720710969378E-4</v>
+        <v>1.5181282276677667E-3</v>
       </c>
       <c r="S21">
-        <v>-7.6149259974676138E-5</v>
+        <v>3.8153373019651153E-4</v>
       </c>
       <c r="T21">
-        <v>-1.3891124440295076E-4</v>
+        <v>-6.0919356178901034E-4</v>
       </c>
       <c r="U21">
-        <v>-8.1505028307338407E-5</v>
+        <v>1.9073189964824381E-3</v>
       </c>
       <c r="V21">
-        <v>3.1060681624128449E-3</v>
-      </c>
-      <c r="W21">
-        <v>6.570313553941029E-4</v>
-      </c>
-      <c r="X21">
-        <v>-7.4593714544866907E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22">
-        <v>-0.55547867509646554</v>
-      </c>
-      <c r="C22">
-        <v>-1.7881476909892036E-4</v>
-      </c>
-      <c r="D22">
-        <v>-6.5897830156759832E-5</v>
-      </c>
-      <c r="E22">
-        <v>3.2193975308948642E-7</v>
-      </c>
-      <c r="F22">
-        <v>2.4895788473839079E-4</v>
-      </c>
-      <c r="G22">
-        <v>-1.0271957056281859E-4</v>
-      </c>
-      <c r="H22">
-        <v>-2.8531020893252427E-4</v>
-      </c>
-      <c r="I22">
-        <v>-3.5961257294858879E-4</v>
-      </c>
-      <c r="J22">
-        <v>2.8668575943555444E-4</v>
-      </c>
-      <c r="K22">
-        <v>1.4936873688883834E-4</v>
-      </c>
-      <c r="L22">
-        <v>-1.9755096550922975E-4</v>
-      </c>
-      <c r="M22">
-        <v>-2.302174325195459E-4</v>
-      </c>
-      <c r="N22">
-        <v>3.1126334246759334E-4</v>
-      </c>
-      <c r="O22">
-        <v>-1.4167535976461866E-4</v>
-      </c>
-      <c r="P22">
-        <v>-4.0637434341484304E-4</v>
-      </c>
-      <c r="Q22">
-        <v>-2.2476016799124289E-4</v>
-      </c>
-      <c r="R22">
-        <v>-2.7843696041894177E-4</v>
-      </c>
-      <c r="S22">
-        <v>-6.6462540564192978E-5</v>
-      </c>
-      <c r="T22">
-        <v>-1.4191275969462107E-4</v>
-      </c>
-      <c r="U22">
-        <v>-9.4299035647029721E-5</v>
-      </c>
-      <c r="V22">
-        <v>6.570313553941029E-4</v>
-      </c>
-      <c r="W22">
-        <v>6.5432972020286594E-3</v>
-      </c>
-      <c r="X22">
-        <v>4.5594033364915847E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23">
-        <v>-22.98535177645309</v>
-      </c>
-      <c r="C23">
-        <v>9.828460085670827E-4</v>
-      </c>
-      <c r="D23">
-        <v>-4.5569479181656131E-2</v>
-      </c>
-      <c r="E23">
-        <v>3.2133579636969248E-4</v>
-      </c>
-      <c r="F23">
-        <v>3.5444588136896646E-3</v>
-      </c>
-      <c r="G23">
-        <v>6.0106919686074498E-3</v>
-      </c>
-      <c r="H23">
-        <v>-3.2021165840525612E-3</v>
-      </c>
-      <c r="I23">
-        <v>-3.4336828012955511E-3</v>
-      </c>
-      <c r="J23">
-        <v>2.8127789996577932E-2</v>
-      </c>
-      <c r="K23">
-        <v>1.0442731807533932E-3</v>
-      </c>
-      <c r="L23">
-        <v>-5.6209306917620484E-3</v>
-      </c>
-      <c r="M23">
-        <v>-6.7552407167642582E-3</v>
-      </c>
-      <c r="N23">
-        <v>-1.1909887307919777E-2</v>
-      </c>
-      <c r="O23">
-        <v>-9.1577693838158919E-3</v>
-      </c>
-      <c r="P23">
-        <v>1.1174667430248891E-3</v>
-      </c>
-      <c r="Q23">
-        <v>7.018659839133099E-3</v>
-      </c>
-      <c r="R23">
-        <v>7.1344382078609879E-3</v>
-      </c>
-      <c r="S23">
-        <v>1.3963498683085356E-3</v>
-      </c>
-      <c r="T23">
-        <v>6.1133070258525268E-3</v>
-      </c>
-      <c r="U23">
-        <v>4.372412946563321E-4</v>
-      </c>
-      <c r="V23">
-        <v>-7.4593714544866907E-4</v>
-      </c>
-      <c r="W23">
-        <v>4.5594033364915847E-3</v>
-      </c>
-      <c r="X23">
-        <v>1.5671857842644181</v>
+        <v>1.8911078671385251</v>
       </c>
     </row>
   </sheetData>
@@ -2285,13 +2005,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AD29"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AB27"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.46484375" customWidth="1"/>
+    <col min="1" max="1" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2365,2598 +2085,2252 @@
         <v>36</v>
       </c>
       <c r="Y1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="Z1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AA1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AB1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2">
-        <v>0.42950978758956926</v>
+        <v>0.19382961442167493</v>
       </c>
       <c r="C2">
-        <v>1.1813828873128165E-3</v>
+        <v>2.1307480000482869E-3</v>
       </c>
       <c r="D2">
-        <v>-2.3981732435172069E-5</v>
+        <v>1.2449775637758025E-4</v>
       </c>
       <c r="E2">
-        <v>1.0360145988679781E-7</v>
+        <v>-9.3145593237359163E-7</v>
       </c>
       <c r="F2">
-        <v>6.4098621197589768E-6</v>
+        <v>-1.1000568840222237E-4</v>
       </c>
       <c r="G2">
-        <v>9.5493238904099562E-5</v>
+        <v>-6.3394788041116435E-5</v>
       </c>
       <c r="H2">
-        <v>3.2829049298176734E-5</v>
+        <v>1.0667417238786555E-4</v>
       </c>
       <c r="I2">
-        <v>1.1128859445666598E-5</v>
+        <v>1.8863873649586753E-4</v>
       </c>
       <c r="J2">
-        <v>1.6677379330217546E-5</v>
+        <v>-2.4168753180869482E-4</v>
       </c>
       <c r="K2">
-        <v>7.2028680854050158E-4</v>
+        <v>9.5723827273676081E-4</v>
       </c>
       <c r="L2">
-        <v>2.5773114144463221E-5</v>
+        <v>-1.2956632547041211E-4</v>
       </c>
       <c r="M2">
-        <v>1.1403913970563951E-5</v>
+        <v>-8.5931739941312338E-5</v>
       </c>
       <c r="N2">
-        <v>-6.0443326077459248E-5</v>
+        <v>8.1240253852584896E-6</v>
       </c>
       <c r="O2">
-        <v>1.4833265365829447E-5</v>
+        <v>-3.0312456408524131E-5</v>
       </c>
       <c r="P2">
-        <v>2.5209115763472662E-5</v>
+        <v>-9.5059991684951156E-5</v>
       </c>
       <c r="Q2">
-        <v>-3.0788827845712973E-4</v>
+        <v>-7.4305946482570995E-4</v>
       </c>
       <c r="R2">
-        <v>4.323123876386103E-4</v>
+        <v>1.3494772241353481E-3</v>
       </c>
       <c r="S2">
-        <v>4.4798522741220265E-5</v>
+        <v>-4.7353575574801698E-4</v>
       </c>
       <c r="T2">
-        <v>-1.7668958970381063E-4</v>
+        <v>-2.4754747100904403E-4</v>
       </c>
       <c r="U2">
-        <v>-4.5645015236555101E-5</v>
+        <v>-3.2704499653844071E-4</v>
       </c>
       <c r="V2">
-        <v>-3.0902924175937679E-5</v>
+        <v>1.949414229772033E-4</v>
       </c>
       <c r="W2">
-        <v>4.3576829731504916E-5</v>
+        <v>1.7648531445258169E-4</v>
       </c>
       <c r="X2">
-        <v>-3.8514277944535827E-5</v>
+        <v>1.014071498706456E-4</v>
       </c>
       <c r="Y2">
-        <v>1.3079467251342531E-5</v>
+        <v>2.4205835851886067E-5</v>
       </c>
       <c r="Z2">
-        <v>4.3568309409761172E-5</v>
+        <v>-6.3709721385612279E-6</v>
       </c>
       <c r="AA2">
-        <v>4.1173285590256976E-6</v>
+        <v>6.0460818548896308E-5</v>
       </c>
       <c r="AB2">
-        <v>6.2958981598370162E-5</v>
-      </c>
-      <c r="AC2">
-        <v>8.5749457677295702E-5</v>
-      </c>
-      <c r="AD2">
-        <v>-9.1001292384887411E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-6.2625976485931358E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3">
-        <v>0.65476016845179141</v>
+        <v>0.38304187176063542</v>
       </c>
       <c r="C3">
-        <v>-2.3981732435172069E-5</v>
+        <v>1.2449775637758025E-4</v>
       </c>
       <c r="D3">
-        <v>9.9101177043926184E-4</v>
+        <v>1.5865543139412215E-3</v>
       </c>
       <c r="E3">
-        <v>-7.3308593633552224E-6</v>
+        <v>-1.253900235415456E-5</v>
       </c>
       <c r="F3">
-        <v>-1.2896712841854946E-4</v>
+        <v>-1.155349408917468E-3</v>
       </c>
       <c r="G3">
-        <v>-1.9809603978624161E-4</v>
+        <v>-1.1243371226831037E-3</v>
       </c>
       <c r="H3">
-        <v>8.0957263278851836E-5</v>
+        <v>-4.9884730432355265E-5</v>
       </c>
       <c r="I3">
-        <v>1.3875070082092789E-4</v>
+        <v>-1.8044212205466266E-4</v>
       </c>
       <c r="J3">
-        <v>-3.2671603472007611E-4</v>
+        <v>8.1805083562426495E-4</v>
       </c>
       <c r="K3">
-        <v>-1.5764843735922634E-4</v>
+        <v>2.9597203125346534E-5</v>
       </c>
       <c r="L3">
-        <v>3.2322771130592273E-4</v>
+        <v>4.1114319053123108E-4</v>
       </c>
       <c r="M3">
-        <v>-6.174047871332659E-5</v>
+        <v>6.5529619565728083E-5</v>
       </c>
       <c r="N3">
-        <v>-9.148874330031434E-5</v>
+        <v>4.3235420805170198E-5</v>
       </c>
       <c r="O3">
-        <v>6.7512797467801471E-5</v>
+        <v>-7.4750392459894607E-5</v>
       </c>
       <c r="P3">
-        <v>7.5634715548172676E-5</v>
+        <v>4.6498908706144038E-5</v>
       </c>
       <c r="Q3">
-        <v>8.3802275798517279E-5</v>
+        <v>-1.7568137279429935E-5</v>
       </c>
       <c r="R3">
-        <v>-1.0087551247140673E-4</v>
+        <v>-9.8305006343306876E-5</v>
       </c>
       <c r="S3">
-        <v>-8.3307533787629895E-5</v>
+        <v>-1.5642817740418131E-4</v>
       </c>
       <c r="T3">
-        <v>-1.1574897419484257E-4</v>
+        <v>-1.3764682901875117E-4</v>
       </c>
       <c r="U3">
-        <v>-7.8362493866083668E-6</v>
+        <v>-1.0075155160613712E-4</v>
       </c>
       <c r="V3">
-        <v>1.5666039869506924E-4</v>
+        <v>1.2533302175822948E-4</v>
       </c>
       <c r="W3">
-        <v>-1.2298696125120662E-4</v>
+        <v>1.3098656831334043E-4</v>
       </c>
       <c r="X3">
-        <v>-1.2836239432304809E-4</v>
+        <v>9.2599972771115896E-5</v>
       </c>
       <c r="Y3">
-        <v>-2.3560051062982562E-5</v>
+        <v>4.5745101166119566E-6</v>
       </c>
       <c r="Z3">
-        <v>-7.3000092347791021E-5</v>
+        <v>8.7681235197830439E-5</v>
       </c>
       <c r="AA3">
-        <v>-8.3156851569843749E-6</v>
+        <v>-3.861313075860821E-5</v>
       </c>
       <c r="AB3">
-        <v>-3.5903404885761526E-5</v>
-      </c>
-      <c r="AC3">
-        <v>-1.7499159508445848E-4</v>
-      </c>
-      <c r="AD3">
-        <v>-3.2778703372456267E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-4.9825583150525488E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4">
-        <v>-4.4854699997804639E-3</v>
+        <v>-2.6251505385235193E-3</v>
       </c>
       <c r="C4">
-        <v>1.0360145988679781E-7</v>
+        <v>-9.3145593237359163E-7</v>
       </c>
       <c r="D4">
-        <v>-7.3308593633552224E-6</v>
+        <v>-1.253900235415456E-5</v>
       </c>
       <c r="E4">
-        <v>5.4826218598397927E-8</v>
+        <v>1.0020652755961193E-7</v>
       </c>
       <c r="F4">
-        <v>1.3094592632862049E-6</v>
+        <v>1.0042098525425728E-5</v>
       </c>
       <c r="G4">
-        <v>1.8262022345777703E-6</v>
+        <v>9.73132403181893E-6</v>
       </c>
       <c r="H4">
-        <v>-5.1687635790890592E-7</v>
+        <v>4.8671301303356921E-7</v>
       </c>
       <c r="I4">
-        <v>-9.9723166950410929E-7</v>
+        <v>1.414299837116663E-6</v>
       </c>
       <c r="J4">
-        <v>1.616744807652249E-6</v>
+        <v>-8.2979512057389769E-6</v>
       </c>
       <c r="K4">
-        <v>1.0863008532843724E-6</v>
+        <v>-3.0231184027954905E-7</v>
       </c>
       <c r="L4">
-        <v>-2.3680664673693299E-6</v>
+        <v>-3.1139193051414435E-6</v>
       </c>
       <c r="M4">
-        <v>5.0653723137447347E-7</v>
+        <v>-5.2229565619198889E-7</v>
       </c>
       <c r="N4">
-        <v>6.9206558048013447E-7</v>
+        <v>-3.7353299648349461E-7</v>
       </c>
       <c r="O4">
-        <v>-4.1974750809693905E-7</v>
+        <v>4.6087485950709625E-7</v>
       </c>
       <c r="P4">
-        <v>-4.7770817388431298E-7</v>
+        <v>-3.4979389630883362E-7</v>
       </c>
       <c r="Q4">
-        <v>-6.7190330242530857E-7</v>
+        <v>4.6666631239744723E-8</v>
       </c>
       <c r="R4">
-        <v>5.0540706364847081E-7</v>
+        <v>3.28391158437022E-7</v>
       </c>
       <c r="S4">
-        <v>7.9662784823796918E-7</v>
+        <v>1.4839184184338562E-6</v>
       </c>
       <c r="T4">
-        <v>9.7176323483467558E-7</v>
+        <v>1.329150523484204E-6</v>
       </c>
       <c r="U4">
-        <v>4.4817086984422027E-8</v>
+        <v>6.7875171532627332E-7</v>
       </c>
       <c r="V4">
-        <v>-1.1866799563889454E-6</v>
+        <v>-9.6477969927690927E-7</v>
       </c>
       <c r="W4">
-        <v>8.8049174438544032E-7</v>
+        <v>-1.0179916760706139E-6</v>
       </c>
       <c r="X4">
-        <v>9.7119313994013702E-7</v>
+        <v>-7.1077695336537166E-7</v>
       </c>
       <c r="Y4">
-        <v>1.6164427698259502E-7</v>
+        <v>-4.0087643653158127E-8</v>
       </c>
       <c r="Z4">
-        <v>5.3963416203317821E-7</v>
+        <v>-7.6501219286060628E-7</v>
       </c>
       <c r="AA4">
-        <v>4.4960952120793899E-8</v>
+        <v>2.1338260029720769E-7</v>
       </c>
       <c r="AB4">
-        <v>2.2423539939320507E-7</v>
-      </c>
-      <c r="AC4">
-        <v>1.1546564149823158E-6</v>
-      </c>
-      <c r="AD4">
-        <v>2.406449329559597E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.45">
+        <v>3.9013265461511869E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5">
-        <v>9.1050485262207506E-2</v>
+        <v>-5.4402869521446517E-2</v>
       </c>
       <c r="C5">
-        <v>6.4098621197589768E-6</v>
+        <v>-1.1000568840222237E-4</v>
       </c>
       <c r="D5">
-        <v>-1.2896712841854946E-4</v>
+        <v>-1.155349408917468E-3</v>
       </c>
       <c r="E5">
-        <v>1.3094592632862049E-6</v>
+        <v>1.0042098525425728E-5</v>
       </c>
       <c r="F5">
-        <v>3.5624086229247066E-3</v>
+        <v>7.9467475822240681E-3</v>
       </c>
       <c r="G5">
-        <v>-5.363624329670501E-4</v>
+        <v>3.1912361902890892E-3</v>
       </c>
       <c r="H5">
-        <v>4.3754261694985142E-5</v>
+        <v>2.5985490636442341E-4</v>
       </c>
       <c r="I5">
-        <v>3.2134069318341473E-7</v>
+        <v>7.5062408366701003E-5</v>
       </c>
       <c r="J5">
-        <v>-1.4296299555938631E-3</v>
+        <v>-4.896261876893712E-3</v>
       </c>
       <c r="K5">
-        <v>-9.1252288887271635E-5</v>
+        <v>-9.5125597866427963E-5</v>
       </c>
       <c r="L5">
-        <v>5.7093650099508805E-4</v>
+        <v>1.3261655618437905E-3</v>
       </c>
       <c r="M5">
-        <v>-1.2585510464085514E-4</v>
+        <v>2.1776166745541854E-4</v>
       </c>
       <c r="N5">
-        <v>-1.8364908175837918E-4</v>
+        <v>-1.8314070013310431E-5</v>
       </c>
       <c r="O5">
-        <v>-2.789649915213657E-4</v>
+        <v>1.77667154917294E-4</v>
       </c>
       <c r="P5">
-        <v>-1.9956218477922808E-4</v>
+        <v>2.0587922257547233E-4</v>
       </c>
       <c r="Q5">
-        <v>4.017072789060962E-5</v>
+        <v>-2.2041431157727737E-4</v>
       </c>
       <c r="R5">
-        <v>8.9968575282365531E-5</v>
+        <v>3.3676687195317596E-4</v>
       </c>
       <c r="S5">
-        <v>-2.0451611298511309E-4</v>
+        <v>-4.5879463790758244E-4</v>
       </c>
       <c r="T5">
-        <v>-1.5476135349585607E-4</v>
+        <v>4.8710978056520091E-5</v>
       </c>
       <c r="U5">
-        <v>4.1987299758546818E-6</v>
+        <v>7.8020306661964745E-6</v>
       </c>
       <c r="V5">
-        <v>-2.3721053787927347E-4</v>
+        <v>-1.9494130794484805E-4</v>
       </c>
       <c r="W5">
-        <v>-7.8424872763294395E-5</v>
+        <v>-1.6367215783590593E-4</v>
       </c>
       <c r="X5">
-        <v>-9.1383671079326822E-5</v>
+        <v>-1.3422032601599111E-4</v>
       </c>
       <c r="Y5">
-        <v>-3.8689048464089684E-5</v>
+        <v>-1.668696514003031E-5</v>
       </c>
       <c r="Z5">
-        <v>-1.7700660590338774E-5</v>
+        <v>-1.384835918040448E-4</v>
       </c>
       <c r="AA5">
-        <v>-1.8881016109089429E-5</v>
+        <v>1.0506119119934676E-4</v>
       </c>
       <c r="AB5">
-        <v>-3.2183353474086237E-7</v>
-      </c>
-      <c r="AC5">
-        <v>-8.4855327018075813E-5</v>
-      </c>
-      <c r="AD5">
-        <v>3.5875425679274472E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.45">
+        <v>3.3245400537621983E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
       <c r="B6">
-        <v>0.32981297980516772</v>
+        <v>0.20804384197959896</v>
       </c>
       <c r="C6">
-        <v>9.5493238904099562E-5</v>
+        <v>-6.3394788041116435E-5</v>
       </c>
       <c r="D6">
-        <v>-1.9809603978624161E-4</v>
+        <v>-1.1243371226831037E-3</v>
       </c>
       <c r="E6">
-        <v>1.8262022345777703E-6</v>
+        <v>9.73132403181893E-6</v>
       </c>
       <c r="F6">
-        <v>-5.363624329670501E-4</v>
+        <v>3.1912361902890892E-3</v>
       </c>
       <c r="G6">
-        <v>3.5404491735365352E-3</v>
+        <v>6.6360680595561709E-3</v>
       </c>
       <c r="H6">
-        <v>-8.9062276712406239E-6</v>
+        <v>2.1069407051378121E-4</v>
       </c>
       <c r="I6">
-        <v>-2.6210867595016305E-5</v>
+        <v>1.486334994332322E-4</v>
       </c>
       <c r="J6">
-        <v>-8.176102183099197E-4</v>
+        <v>-4.125582565134951E-3</v>
       </c>
       <c r="K6">
-        <v>5.9197284356773407E-5</v>
+        <v>-9.3103984096623398E-5</v>
       </c>
       <c r="L6">
-        <v>-4.1614336434651553E-5</v>
+        <v>7.5107444263542399E-4</v>
       </c>
       <c r="M6">
-        <v>6.4021095996027902E-5</v>
+        <v>1.2483094877309268E-4</v>
       </c>
       <c r="N6">
-        <v>6.8621173421243558E-5</v>
+        <v>-7.2307011981283774E-5</v>
       </c>
       <c r="O6">
-        <v>9.5614742672519995E-5</v>
+        <v>6.1324393560588278E-5</v>
       </c>
       <c r="P6">
-        <v>8.2477699225380846E-5</v>
+        <v>8.5460270258782677E-5</v>
       </c>
       <c r="Q6">
-        <v>-9.3982628226355319E-5</v>
+        <v>-6.5990851223640332E-5</v>
       </c>
       <c r="R6">
-        <v>1.1913882776938599E-4</v>
+        <v>3.7750958698950544E-5</v>
       </c>
       <c r="S6">
-        <v>-3.2744006691192221E-5</v>
+        <v>-3.8443835193863489E-5</v>
       </c>
       <c r="T6">
-        <v>-2.0876399576951366E-4</v>
+        <v>-8.2644302262337111E-5</v>
       </c>
       <c r="U6">
-        <v>-1.5611644632758858E-5</v>
+        <v>2.9612488441949254E-6</v>
       </c>
       <c r="V6">
-        <v>-9.3776691258086529E-5</v>
+        <v>-3.2806154509847232E-4</v>
       </c>
       <c r="W6">
-        <v>9.3725988055200254E-7</v>
+        <v>-1.3412177158276389E-4</v>
       </c>
       <c r="X6">
-        <v>4.9960686878304332E-5</v>
+        <v>-1.6762702870388307E-4</v>
       </c>
       <c r="Y6">
-        <v>4.0101324938063287E-6</v>
+        <v>-2.2247134559976421E-5</v>
       </c>
       <c r="Z6">
-        <v>-6.2429725571425121E-7</v>
+        <v>-2.3514171009015325E-4</v>
       </c>
       <c r="AA6">
-        <v>-1.1722711849127205E-5</v>
+        <v>1.5979938600405963E-4</v>
       </c>
       <c r="AB6">
-        <v>7.0087298320472961E-5</v>
-      </c>
-      <c r="AC6">
-        <v>1.3461443381087212E-4</v>
-      </c>
-      <c r="AD6">
-        <v>5.3350735952675046E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.45">
+        <v>3.2721969509083626E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
       <c r="B7">
-        <v>2.194141116195546E-2</v>
+        <v>-6.5113974863413554E-2</v>
       </c>
       <c r="C7">
-        <v>3.2829049298176734E-5</v>
+        <v>1.0667417238786555E-4</v>
       </c>
       <c r="D7">
-        <v>8.0957263278851836E-5</v>
+        <v>-4.9884730432355265E-5</v>
       </c>
       <c r="E7">
-        <v>-5.1687635790890592E-7</v>
+        <v>4.8671301303356921E-7</v>
       </c>
       <c r="F7">
-        <v>4.3754261694985142E-5</v>
+        <v>2.5985490636442341E-4</v>
       </c>
       <c r="G7">
-        <v>-8.9062276712406239E-6</v>
+        <v>2.1069407051378121E-4</v>
       </c>
       <c r="H7">
-        <v>1.7466314860259053E-3</v>
+        <v>2.6854211336278296E-3</v>
       </c>
       <c r="I7">
-        <v>1.440025211366047E-3</v>
+        <v>2.0239547160266209E-3</v>
       </c>
       <c r="J7">
-        <v>-7.9780439776055035E-6</v>
+        <v>-2.4813193444136539E-4</v>
       </c>
       <c r="K7">
-        <v>-1.6721586189561102E-4</v>
+        <v>-2.573767665938133E-4</v>
       </c>
       <c r="L7">
-        <v>-3.9909465635914456E-5</v>
+        <v>5.9884140826031498E-5</v>
       </c>
       <c r="M7">
-        <v>-1.0058020292087554E-5</v>
+        <v>1.2501560988990729E-4</v>
       </c>
       <c r="N7">
-        <v>-1.0282727127745189E-4</v>
+        <v>-6.3277831151997851E-6</v>
       </c>
       <c r="O7">
-        <v>-6.4679684563358604E-5</v>
+        <v>-8.6483407450686884E-5</v>
       </c>
       <c r="P7">
-        <v>2.4483608863119831E-4</v>
+        <v>5.1250481257126656E-4</v>
       </c>
       <c r="Q7">
-        <v>6.951287894309846E-5</v>
+        <v>-3.0081075776384027E-6</v>
       </c>
       <c r="R7">
-        <v>-5.9402096654258881E-5</v>
+        <v>-3.1894093915342276E-5</v>
       </c>
       <c r="S7">
-        <v>1.6672596359617936E-4</v>
+        <v>1.4578170998571838E-4</v>
       </c>
       <c r="T7">
-        <v>5.4513010038388643E-5</v>
+        <v>9.6381864466779882E-5</v>
       </c>
       <c r="U7">
-        <v>7.877396459491173E-5</v>
+        <v>-2.7489470462136958E-4</v>
       </c>
       <c r="V7">
-        <v>-1.4702682419550348E-5</v>
+        <v>2.1808093315828448E-4</v>
       </c>
       <c r="W7">
-        <v>3.8820135270743711E-6</v>
+        <v>-2.3694978586048386E-4</v>
       </c>
       <c r="X7">
-        <v>9.6495393545886827E-5</v>
+        <v>-2.9635629880345616E-4</v>
       </c>
       <c r="Y7">
-        <v>4.6540385602321095E-5</v>
+        <v>-8.2879699778506683E-6</v>
       </c>
       <c r="Z7">
-        <v>5.038424332845081E-5</v>
+        <v>-1.8617858197068443E-4</v>
       </c>
       <c r="AA7">
-        <v>-2.4663283213307208E-6</v>
+        <v>2.0255178506772638E-5</v>
       </c>
       <c r="AB7">
-        <v>2.043208115373393E-5</v>
-      </c>
-      <c r="AC7">
-        <v>1.7919395327540806E-5</v>
-      </c>
-      <c r="AD7">
-        <v>-4.3943825161759324E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-1.5038346443663544E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
       <c r="B8">
-        <v>7.1733411640234959E-2</v>
+        <v>-0.1028429419831247</v>
       </c>
       <c r="C8">
-        <v>1.1128859445666598E-5</v>
+        <v>1.8863873649586753E-4</v>
       </c>
       <c r="D8">
-        <v>1.3875070082092789E-4</v>
+        <v>-1.8044212205466266E-4</v>
       </c>
       <c r="E8">
-        <v>-9.9723166950410929E-7</v>
+        <v>1.414299837116663E-6</v>
       </c>
       <c r="F8">
-        <v>3.2134069318341473E-7</v>
+        <v>7.5062408366701003E-5</v>
       </c>
       <c r="G8">
-        <v>-2.6210867595016305E-5</v>
+        <v>1.486334994332322E-4</v>
       </c>
       <c r="H8">
-        <v>1.440025211366047E-3</v>
+        <v>2.0239547160266209E-3</v>
       </c>
       <c r="I8">
-        <v>1.9391514955351126E-3</v>
+        <v>2.8035286784350833E-3</v>
       </c>
       <c r="J8">
-        <v>-2.3796413414870263E-5</v>
+        <v>-2.4502379256481947E-4</v>
       </c>
       <c r="K8">
-        <v>-2.5940328093132894E-4</v>
+        <v>-2.2859423290779639E-4</v>
       </c>
       <c r="L8">
-        <v>2.0183338037808689E-5</v>
+        <v>1.1256412262102271E-4</v>
       </c>
       <c r="M8">
-        <v>5.0863873120004035E-5</v>
+        <v>2.4503151523789781E-5</v>
       </c>
       <c r="N8">
-        <v>-2.8455747229007441E-6</v>
+        <v>-8.1358085624984217E-6</v>
       </c>
       <c r="O8">
-        <v>1.7259336452055531E-4</v>
+        <v>-6.8340105248003305E-5</v>
       </c>
       <c r="P8">
-        <v>6.0517264307315187E-4</v>
+        <v>7.6221005159245463E-4</v>
       </c>
       <c r="Q8">
-        <v>1.3150589659768138E-5</v>
+        <v>-1.2681633923612151E-4</v>
       </c>
       <c r="R8">
-        <v>-7.1223835878054848E-5</v>
+        <v>-1.2888456360103087E-4</v>
       </c>
       <c r="S8">
-        <v>9.6380415550510745E-5</v>
+        <v>1.622013668759116E-4</v>
       </c>
       <c r="T8">
-        <v>6.7858375722436466E-5</v>
+        <v>9.1443400557779828E-5</v>
       </c>
       <c r="U8">
-        <v>7.4509910596189436E-5</v>
+        <v>-1.6576871115611216E-4</v>
       </c>
       <c r="V8">
-        <v>4.5416097483290727E-5</v>
+        <v>-1.8873334196598936E-4</v>
       </c>
       <c r="W8">
-        <v>1.5383205870277763E-5</v>
+        <v>-5.8152093776901422E-4</v>
       </c>
       <c r="X8">
-        <v>-6.0949923426508926E-5</v>
+        <v>-5.6581064273221265E-4</v>
       </c>
       <c r="Y8">
-        <v>4.4280955911512763E-5</v>
+        <v>1.6563416971135568E-5</v>
       </c>
       <c r="Z8">
-        <v>1.879742920110985E-5</v>
+        <v>-1.7909501388125982E-4</v>
       </c>
       <c r="AA8">
-        <v>6.4612010417570585E-6</v>
+        <v>2.9216892939803868E-6</v>
       </c>
       <c r="AB8">
-        <v>4.9048343757721069E-6</v>
-      </c>
-      <c r="AC8">
-        <v>-4.9403651879806158E-5</v>
-      </c>
-      <c r="AD8">
-        <v>-6.5312864947751209E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.45">
+        <v>3.7513511035775684E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
       <c r="B9">
-        <v>0.34789272050457709</v>
+        <v>0.74915048668511852</v>
       </c>
       <c r="C9">
-        <v>1.6677379330217546E-5</v>
+        <v>-2.4168753180869482E-4</v>
       </c>
       <c r="D9">
-        <v>-3.2671603472007611E-4</v>
+        <v>8.1805083562426495E-4</v>
       </c>
       <c r="E9">
-        <v>1.616744807652249E-6</v>
+        <v>-8.2979512057389769E-6</v>
       </c>
       <c r="F9">
-        <v>-1.4296299555938631E-3</v>
+        <v>-4.896261876893712E-3</v>
       </c>
       <c r="G9">
-        <v>-8.176102183099197E-4</v>
+        <v>-4.125582565134951E-3</v>
       </c>
       <c r="H9">
-        <v>-7.9780439776055035E-6</v>
+        <v>-2.4813193444136539E-4</v>
       </c>
       <c r="I9">
-        <v>-2.3796413414870263E-5</v>
+        <v>-2.4502379256481947E-4</v>
       </c>
       <c r="J9">
-        <v>3.9578432175268645E-3</v>
+        <v>8.3978733755604943E-3</v>
       </c>
       <c r="K9">
-        <v>5.9704600289512094E-4</v>
+        <v>5.9886023769073959E-4</v>
       </c>
       <c r="L9">
-        <v>-2.1141529838280505E-3</v>
+        <v>-3.6565307999010506E-3</v>
       </c>
       <c r="M9">
-        <v>-6.3294292918192937E-5</v>
+        <v>9.0518955404603023E-6</v>
       </c>
       <c r="N9">
-        <v>-1.4787579674292598E-4</v>
+        <v>6.2635329561125906E-5</v>
       </c>
       <c r="O9">
-        <v>-2.2370673279252539E-4</v>
+        <v>8.6369471395305588E-6</v>
       </c>
       <c r="P9">
-        <v>-2.0574058764962774E-4</v>
+        <v>-1.6475461214403926E-4</v>
       </c>
       <c r="Q9">
-        <v>-5.6203256731004677E-5</v>
+        <v>2.5040212735620527E-4</v>
       </c>
       <c r="R9">
-        <v>-6.3013656706980398E-4</v>
+        <v>-4.2945772627142826E-4</v>
       </c>
       <c r="S9">
-        <v>1.2249841507555462E-4</v>
+        <v>1.0701705326355703E-4</v>
       </c>
       <c r="T9">
-        <v>2.2472173535308717E-4</v>
+        <v>6.6056414414733967E-5</v>
       </c>
       <c r="U9">
-        <v>-4.5006814949378646E-5</v>
+        <v>1.6689810786631588E-4</v>
       </c>
       <c r="V9">
-        <v>8.529570117160029E-5</v>
+        <v>-1.0831938223931223E-4</v>
       </c>
       <c r="W9">
-        <v>1.3178235406130197E-4</v>
+        <v>1.1576206327555336E-4</v>
       </c>
       <c r="X9">
-        <v>-3.1841219088219824E-5</v>
+        <v>1.4927116694363196E-4</v>
       </c>
       <c r="Y9">
-        <v>3.0783141663231432E-5</v>
+        <v>1.3277265771253002E-5</v>
       </c>
       <c r="Z9">
-        <v>6.4842173534579352E-5</v>
+        <v>1.6299710846095822E-4</v>
       </c>
       <c r="AA9">
-        <v>3.1385956297426025E-5</v>
+        <v>1.1641476624096295E-4</v>
       </c>
       <c r="AB9">
-        <v>2.0855462036519694E-4</v>
-      </c>
-      <c r="AC9">
-        <v>3.9602656651541428E-5</v>
-      </c>
-      <c r="AD9">
-        <v>1.2966391664548427E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-1.9799660230549215E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10">
-        <v>0.42281856314506849</v>
+        <v>-4.0916718964506625E-2</v>
       </c>
       <c r="C10">
-        <v>7.2028680854050158E-4</v>
+        <v>9.5723827273676081E-4</v>
       </c>
       <c r="D10">
-        <v>-1.5764843735922634E-4</v>
+        <v>2.9597203125346534E-5</v>
       </c>
       <c r="E10">
-        <v>1.0863008532843724E-6</v>
+        <v>-3.0231184027954905E-7</v>
       </c>
       <c r="F10">
-        <v>-9.1252288887271635E-5</v>
+        <v>-9.5125597866427963E-5</v>
       </c>
       <c r="G10">
-        <v>5.9197284356773407E-5</v>
+        <v>-9.3103984096623398E-5</v>
       </c>
       <c r="H10">
-        <v>-1.6721586189561102E-4</v>
+        <v>-2.573767665938133E-4</v>
       </c>
       <c r="I10">
-        <v>-2.5940328093132894E-4</v>
+        <v>-2.2859423290779639E-4</v>
       </c>
       <c r="J10">
-        <v>5.9704600289512094E-4</v>
+        <v>5.9886023769073959E-4</v>
       </c>
       <c r="K10">
-        <v>1.665698547901539E-3</v>
+        <v>2.8204067249765542E-3</v>
       </c>
       <c r="L10">
-        <v>-7.6811733546807283E-4</v>
+        <v>-1.2581648483755803E-3</v>
       </c>
       <c r="M10">
-        <v>-1.1621131824486104E-5</v>
+        <v>7.6569465355908937E-5</v>
       </c>
       <c r="N10">
-        <v>2.4270926713893757E-4</v>
+        <v>8.1331451819916163E-4</v>
       </c>
       <c r="O10">
-        <v>3.7647039094852161E-4</v>
+        <v>1.6483688127662238E-3</v>
       </c>
       <c r="P10">
-        <v>6.3123972504564735E-4</v>
+        <v>1.801235086427833E-3</v>
       </c>
       <c r="Q10">
-        <v>-4.257129006434232E-4</v>
+        <v>-1.0077216251422312E-3</v>
       </c>
       <c r="R10">
-        <v>6.2036780529101462E-5</v>
+        <v>6.2731150092097936E-4</v>
       </c>
       <c r="S10">
-        <v>-1.8910506694746619E-5</v>
+        <v>-6.2141630306236694E-4</v>
       </c>
       <c r="T10">
-        <v>-1.3822405959195921E-4</v>
+        <v>-3.0419301366085735E-4</v>
       </c>
       <c r="U10">
-        <v>1.2677846451092208E-4</v>
+        <v>3.0279826874187517E-4</v>
       </c>
       <c r="V10">
-        <v>3.3747335471180173E-5</v>
+        <v>1.7359609021109099E-4</v>
       </c>
       <c r="W10">
-        <v>-1.872209523951523E-5</v>
+        <v>6.1976889765541021E-4</v>
       </c>
       <c r="X10">
-        <v>-1.2070038645887165E-4</v>
+        <v>3.775465807769918E-4</v>
       </c>
       <c r="Y10">
-        <v>3.9985449702516495E-5</v>
+        <v>2.173227926256464E-5</v>
       </c>
       <c r="Z10">
-        <v>2.2418101799622728E-5</v>
+        <v>-3.5299881018857317E-5</v>
       </c>
       <c r="AA10">
-        <v>-6.25166751773641E-6</v>
+        <v>1.4826016861596775E-4</v>
       </c>
       <c r="AB10">
-        <v>2.1052615565188645E-4</v>
-      </c>
-      <c r="AC10">
-        <v>-2.1215426605875374E-5</v>
-      </c>
-      <c r="AD10">
-        <v>4.2760243892310318E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-4.2673207761173195E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
       <c r="B11">
-        <v>-0.51986759855910503</v>
+        <v>-0.58755092580254797</v>
       </c>
       <c r="C11">
-        <v>2.5773114144463221E-5</v>
+        <v>-1.2956632547041211E-4</v>
       </c>
       <c r="D11">
-        <v>3.2322771130592273E-4</v>
+        <v>4.1114319053123108E-4</v>
       </c>
       <c r="E11">
-        <v>-2.3680664673693299E-6</v>
+        <v>-3.1139193051414435E-6</v>
       </c>
       <c r="F11">
-        <v>5.7093650099508805E-4</v>
+        <v>1.3261655618437905E-3</v>
       </c>
       <c r="G11">
-        <v>-4.1614336434651553E-5</v>
+        <v>7.5107444263542399E-4</v>
       </c>
       <c r="H11">
-        <v>-3.9909465635914456E-5</v>
+        <v>5.9884140826031498E-5</v>
       </c>
       <c r="I11">
-        <v>2.0183338037808689E-5</v>
+        <v>1.1256412262102271E-4</v>
       </c>
       <c r="J11">
-        <v>-2.1141529838280505E-3</v>
+        <v>-3.6565307999010506E-3</v>
       </c>
       <c r="K11">
-        <v>-7.6811733546807283E-4</v>
+        <v>-1.2581648483755803E-3</v>
       </c>
       <c r="L11">
-        <v>3.1531862503220405E-3</v>
+        <v>6.0273620578461711E-3</v>
       </c>
       <c r="M11">
-        <v>1.4668942957838239E-5</v>
+        <v>1.7927672632638383E-4</v>
       </c>
       <c r="N11">
-        <v>3.2611779943426326E-4</v>
+        <v>2.752194887939909E-4</v>
       </c>
       <c r="O11">
-        <v>4.1540083612640825E-4</v>
+        <v>2.6027900196254344E-4</v>
       </c>
       <c r="P11">
-        <v>3.4861428708961523E-4</v>
+        <v>3.216188590860437E-4</v>
       </c>
       <c r="Q11">
-        <v>3.9805177609202698E-5</v>
+        <v>1.5171623426569331E-4</v>
       </c>
       <c r="R11">
-        <v>-1.8562341258781894E-4</v>
+        <v>-1.0433687915534819E-3</v>
       </c>
       <c r="S11">
-        <v>3.1952547323941529E-4</v>
+        <v>1.0013971528056147E-3</v>
       </c>
       <c r="T11">
-        <v>3.6593037718058298E-4</v>
+        <v>9.3018861694540284E-4</v>
       </c>
       <c r="U11">
-        <v>8.856278085677446E-5</v>
+        <v>-2.566096561118004E-5</v>
       </c>
       <c r="V11">
-        <v>1.8217096591236474E-4</v>
+        <v>1.2464002399635213E-5</v>
       </c>
       <c r="W11">
-        <v>-4.5872664248433273E-5</v>
+        <v>-2.9475886149186309E-5</v>
       </c>
       <c r="X11">
-        <v>2.7888289334066039E-6</v>
+        <v>9.1736617252843704E-5</v>
       </c>
       <c r="Y11">
-        <v>-1.1066110228778476E-5</v>
+        <v>-1.7007761436753583E-6</v>
       </c>
       <c r="Z11">
-        <v>-3.3797742482051009E-5</v>
+        <v>1.1689959669137606E-4</v>
       </c>
       <c r="AA11">
-        <v>6.1434974962383906E-6</v>
+        <v>-7.5025123757002741E-5</v>
       </c>
       <c r="AB11">
-        <v>-1.4470526959323464E-4</v>
-      </c>
-      <c r="AC11">
-        <v>1.8399041315952567E-4</v>
-      </c>
-      <c r="AD11">
-        <v>-1.0969298898247083E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-1.3057191873625834E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
       <c r="B12">
-        <v>0.11417231029821581</v>
+        <v>-2.3404513180308125E-3</v>
       </c>
       <c r="C12">
-        <v>1.1403913970563951E-5</v>
+        <v>-8.5931739941312338E-5</v>
       </c>
       <c r="D12">
-        <v>-6.174047871332659E-5</v>
+        <v>6.5529619565728083E-5</v>
       </c>
       <c r="E12">
-        <v>5.0653723137447347E-7</v>
+        <v>-5.2229565619198889E-7</v>
       </c>
       <c r="F12">
-        <v>-1.2585510464085514E-4</v>
+        <v>2.1776166745541854E-4</v>
       </c>
       <c r="G12">
-        <v>6.4021095996027902E-5</v>
+        <v>1.2483094877309268E-4</v>
       </c>
       <c r="H12">
-        <v>-1.0058020292087554E-5</v>
+        <v>1.2501560988990729E-4</v>
       </c>
       <c r="I12">
-        <v>5.0863873120004035E-5</v>
+        <v>2.4503151523789781E-5</v>
       </c>
       <c r="J12">
-        <v>-6.3294292918192937E-5</v>
+        <v>9.0518955404603023E-6</v>
       </c>
       <c r="K12">
-        <v>-1.1621131824486104E-5</v>
+        <v>7.6569465355908937E-5</v>
       </c>
       <c r="L12">
-        <v>1.4668942957838239E-5</v>
+        <v>1.7927672632638383E-4</v>
       </c>
       <c r="M12">
-        <v>1.4213539173641774E-3</v>
+        <v>3.1563728050734677E-3</v>
       </c>
       <c r="N12">
-        <v>7.3789629714998413E-4</v>
+        <v>1.7062651880303467E-3</v>
       </c>
       <c r="O12">
-        <v>7.7416010788985024E-4</v>
+        <v>1.7508562396835849E-3</v>
       </c>
       <c r="P12">
-        <v>7.9605144501014395E-4</v>
+        <v>1.7678909364794609E-3</v>
       </c>
       <c r="Q12">
-        <v>4.1771596682051279E-5</v>
+        <v>-1.0160636845071234E-4</v>
       </c>
       <c r="R12">
-        <v>6.0291652041174224E-5</v>
+        <v>-1.5641391682033552E-4</v>
       </c>
       <c r="S12">
-        <v>7.5709480456004818E-5</v>
+        <v>-4.3144205742130017E-4</v>
       </c>
       <c r="T12">
-        <v>-9.2492038032912196E-5</v>
+        <v>-3.1407362788607945E-5</v>
       </c>
       <c r="U12">
-        <v>-7.3720245042518278E-6</v>
+        <v>2.2226553138962043E-5</v>
       </c>
       <c r="V12">
-        <v>-7.2057653136608834E-6</v>
+        <v>1.4741133059672682E-4</v>
       </c>
       <c r="W12">
-        <v>6.5067158609018042E-5</v>
+        <v>-1.1472829739784293E-4</v>
       </c>
       <c r="X12">
-        <v>1.3770282227285339E-4</v>
+        <v>-1.1940146652703542E-5</v>
       </c>
       <c r="Y12">
-        <v>-3.6913870727648638E-5</v>
+        <v>-7.0717934358781028E-7</v>
       </c>
       <c r="Z12">
-        <v>4.7724499751832005E-5</v>
+        <v>-7.1097737409407734E-5</v>
       </c>
       <c r="AA12">
-        <v>6.8284507372023869E-6</v>
+        <v>1.9403402809785102E-4</v>
       </c>
       <c r="AB12">
-        <v>-3.4920607621271194E-5</v>
-      </c>
-      <c r="AC12">
-        <v>-7.0923082753068963E-5</v>
-      </c>
-      <c r="AD12">
-        <v>9.4548228122112721E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-3.7739459844945249E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
       <c r="B13">
-        <v>0.19971630085493411</v>
+        <v>-1.4708268829953736E-2</v>
       </c>
       <c r="C13">
-        <v>-6.0443326077459248E-5</v>
+        <v>8.1240253852584896E-6</v>
       </c>
       <c r="D13">
-        <v>-9.148874330031434E-5</v>
+        <v>4.3235420805170198E-5</v>
       </c>
       <c r="E13">
-        <v>6.9206558048013447E-7</v>
+        <v>-3.7353299648349461E-7</v>
       </c>
       <c r="F13">
-        <v>-1.8364908175837918E-4</v>
+        <v>-1.8314070013310431E-5</v>
       </c>
       <c r="G13">
-        <v>6.8621173421243558E-5</v>
+        <v>-7.2307011981283774E-5</v>
       </c>
       <c r="H13">
-        <v>-1.0282727127745189E-4</v>
+        <v>-6.3277831151997851E-6</v>
       </c>
       <c r="I13">
-        <v>-2.8455747229007441E-6</v>
+        <v>-8.1358085624984217E-6</v>
       </c>
       <c r="J13">
-        <v>-1.4787579674292598E-4</v>
+        <v>6.2635329561125906E-5</v>
       </c>
       <c r="K13">
-        <v>2.4270926713893757E-4</v>
+        <v>8.1331451819916163E-4</v>
       </c>
       <c r="L13">
-        <v>3.2611779943426326E-4</v>
+        <v>2.752194887939909E-4</v>
       </c>
       <c r="M13">
-        <v>7.3789629714998413E-4</v>
+        <v>1.7062651880303467E-3</v>
       </c>
       <c r="N13">
-        <v>1.7511641182216E-3</v>
+        <v>3.2592615684365746E-3</v>
       </c>
       <c r="O13">
-        <v>1.2502079650126333E-3</v>
+        <v>2.7307777895813046E-3</v>
       </c>
       <c r="P13">
-        <v>1.4098845464972825E-3</v>
+        <v>2.895894533881923E-3</v>
       </c>
       <c r="Q13">
-        <v>6.1356645282104023E-5</v>
+        <v>-8.3000501170189291E-5</v>
       </c>
       <c r="R13">
-        <v>1.9580070893802974E-4</v>
+        <v>2.3492579321381229E-4</v>
       </c>
       <c r="S13">
-        <v>-1.0875277460531407E-4</v>
+        <v>-4.9753150872791229E-4</v>
       </c>
       <c r="T13">
-        <v>-7.8931758385123019E-5</v>
+        <v>-4.9426998582451792E-4</v>
       </c>
       <c r="U13">
-        <v>1.7406270982262627E-4</v>
+        <v>3.5870855265314613E-4</v>
       </c>
       <c r="V13">
-        <v>2.9334828664448855E-4</v>
+        <v>-1.5575592414441246E-4</v>
       </c>
       <c r="W13">
-        <v>3.6697775670773683E-5</v>
+        <v>2.9420596425458229E-5</v>
       </c>
       <c r="X13">
-        <v>1.4211459793614541E-4</v>
+        <v>2.4672131667175857E-5</v>
       </c>
       <c r="Y13">
-        <v>-3.3834740673162615E-5</v>
+        <v>-2.7700495730804519E-6</v>
       </c>
       <c r="Z13">
-        <v>3.2820462139969983E-6</v>
+        <v>-1.1229312177606783E-4</v>
       </c>
       <c r="AA13">
-        <v>8.3564551043839466E-6</v>
+        <v>8.0863472799159688E-5</v>
       </c>
       <c r="AB13">
-        <v>-2.4033348125394877E-5</v>
-      </c>
-      <c r="AC13">
-        <v>-9.7998225566881328E-6</v>
-      </c>
-      <c r="AD13">
-        <v>1.4462751017154333E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-4.3291335557746665E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
       <c r="B14">
-        <v>0.29168404955317967</v>
+        <v>6.9898828335477184E-2</v>
       </c>
       <c r="C14">
-        <v>1.4833265365829447E-5</v>
+        <v>-3.0312456408524131E-5</v>
       </c>
       <c r="D14">
-        <v>6.7512797467801471E-5</v>
+        <v>-7.4750392459894607E-5</v>
       </c>
       <c r="E14">
-        <v>-4.1974750809693905E-7</v>
+        <v>4.6087485950709625E-7</v>
       </c>
       <c r="F14">
-        <v>-2.789649915213657E-4</v>
+        <v>1.77667154917294E-4</v>
       </c>
       <c r="G14">
-        <v>9.5614742672519995E-5</v>
+        <v>6.1324393560588278E-5</v>
       </c>
       <c r="H14">
-        <v>-6.4679684563358604E-5</v>
+        <v>-8.6483407450686884E-5</v>
       </c>
       <c r="I14">
-        <v>1.7259336452055531E-4</v>
+        <v>-6.8340105248003305E-5</v>
       </c>
       <c r="J14">
-        <v>-2.2370673279252539E-4</v>
+        <v>8.6369471395305588E-6</v>
       </c>
       <c r="K14">
-        <v>3.7647039094852161E-4</v>
+        <v>1.6483688127662238E-3</v>
       </c>
       <c r="L14">
-        <v>4.1540083612640825E-4</v>
+        <v>2.6027900196254344E-4</v>
       </c>
       <c r="M14">
-        <v>7.7416010788985024E-4</v>
+        <v>1.7508562396835849E-3</v>
       </c>
       <c r="N14">
-        <v>1.2502079650126333E-3</v>
+        <v>2.7307777895813046E-3</v>
       </c>
       <c r="O14">
-        <v>2.232799390752313E-3</v>
+        <v>4.7426719138698907E-3</v>
       </c>
       <c r="P14">
-        <v>1.8483045249128519E-3</v>
+        <v>4.1081345135720038E-3</v>
       </c>
       <c r="Q14">
-        <v>8.8979624131823361E-5</v>
+        <v>-2.7527809149645354E-5</v>
       </c>
       <c r="R14">
-        <v>2.2366172230404137E-4</v>
+        <v>5.7902372988285003E-4</v>
       </c>
       <c r="S14">
-        <v>-2.5426314852149611E-5</v>
+        <v>-8.0986208969290811E-4</v>
       </c>
       <c r="T14">
-        <v>-1.3167895673096852E-5</v>
+        <v>-5.7832535686846076E-4</v>
       </c>
       <c r="U14">
-        <v>3.2389978195724141E-4</v>
+        <v>8.4085658459097281E-4</v>
       </c>
       <c r="V14">
-        <v>2.512152397360008E-4</v>
+        <v>2.22872828440068E-4</v>
       </c>
       <c r="W14">
-        <v>9.8929173283288639E-5</v>
+        <v>2.5457971783146441E-4</v>
       </c>
       <c r="X14">
-        <v>2.2465508670203258E-4</v>
+        <v>2.4911801611292306E-4</v>
       </c>
       <c r="Y14">
-        <v>3.3656129223273322E-6</v>
+        <v>-1.2776954762038677E-5</v>
       </c>
       <c r="Z14">
-        <v>3.2727317686222787E-5</v>
+        <v>-7.7393034202703043E-5</v>
       </c>
       <c r="AA14">
-        <v>1.2350769156671299E-5</v>
+        <v>1.5485075705517142E-4</v>
       </c>
       <c r="AB14">
-        <v>-2.2486544475838711E-5</v>
-      </c>
-      <c r="AC14">
-        <v>-2.6309775435641013E-5</v>
-      </c>
-      <c r="AD14">
-        <v>-4.7847068426994585E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-1.713715752095897E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15">
-        <v>0.25090874773798066</v>
+        <v>0.16978121965856105</v>
       </c>
       <c r="C15">
-        <v>2.5209115763472662E-5</v>
+        <v>-9.5059991684951156E-5</v>
       </c>
       <c r="D15">
-        <v>7.5634715548172676E-5</v>
+        <v>4.6498908706144038E-5</v>
       </c>
       <c r="E15">
-        <v>-4.7770817388431298E-7</v>
+        <v>-3.4979389630883362E-7</v>
       </c>
       <c r="F15">
-        <v>-1.9956218477922808E-4</v>
+        <v>2.0587922257547233E-4</v>
       </c>
       <c r="G15">
-        <v>8.2477699225380846E-5</v>
+        <v>8.5460270258782677E-5</v>
       </c>
       <c r="H15">
-        <v>2.4483608863119831E-4</v>
+        <v>5.1250481257126656E-4</v>
       </c>
       <c r="I15">
-        <v>6.0517264307315187E-4</v>
+        <v>7.6221005159245463E-4</v>
       </c>
       <c r="J15">
-        <v>-2.0574058764962774E-4</v>
+        <v>-1.6475461214403926E-4</v>
       </c>
       <c r="K15">
-        <v>6.3123972504564735E-4</v>
+        <v>1.801235086427833E-3</v>
       </c>
       <c r="L15">
-        <v>3.4861428708961523E-4</v>
+        <v>3.216188590860437E-4</v>
       </c>
       <c r="M15">
-        <v>7.9605144501014395E-4</v>
+        <v>1.7678909364794609E-3</v>
       </c>
       <c r="N15">
-        <v>1.4098845464972825E-3</v>
+        <v>2.895894533881923E-3</v>
       </c>
       <c r="O15">
-        <v>1.8483045249128519E-3</v>
+        <v>4.1081345135720038E-3</v>
       </c>
       <c r="P15">
-        <v>2.8135734091937971E-3</v>
+        <v>5.7353118938614951E-3</v>
       </c>
       <c r="Q15">
-        <v>1.2345537630727128E-4</v>
+        <v>7.6372258124442725E-6</v>
       </c>
       <c r="R15">
-        <v>1.3827101726314613E-4</v>
+        <v>4.3451797205239923E-4</v>
       </c>
       <c r="S15">
-        <v>-3.0119656923040814E-5</v>
+        <v>-8.3158543155765021E-4</v>
       </c>
       <c r="T15">
-        <v>-4.5802527792361146E-5</v>
+        <v>-5.6977196696413003E-4</v>
       </c>
       <c r="U15">
-        <v>6.1540032607335289E-4</v>
+        <v>1.1226795311006376E-3</v>
       </c>
       <c r="V15">
-        <v>3.6677601638455905E-4</v>
+        <v>4.9239170257848628E-4</v>
       </c>
       <c r="W15">
-        <v>1.7219597287869182E-4</v>
+        <v>1.4218309761342227E-4</v>
       </c>
       <c r="X15">
-        <v>2.6827901500771269E-4</v>
+        <v>2.1920451306449863E-4</v>
       </c>
       <c r="Y15">
-        <v>7.167162809348026E-5</v>
+        <v>-1.5714883976621888E-5</v>
       </c>
       <c r="Z15">
-        <v>8.6216263244923218E-5</v>
+        <v>-2.8049707976259306E-4</v>
       </c>
       <c r="AA15">
-        <v>4.5493221811450846E-6</v>
+        <v>1.3201352587498635E-4</v>
       </c>
       <c r="AB15">
-        <v>1.408505672128755E-5</v>
-      </c>
-      <c r="AC15">
-        <v>-1.1224282453956892E-4</v>
-      </c>
-      <c r="AD15">
-        <v>-5.8488023755043344E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-7.1155846511253215E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16">
-        <v>0.57120376022285979</v>
+        <v>0.85205976212809986</v>
       </c>
       <c r="C16">
-        <v>-3.0788827845712973E-4</v>
+        <v>-7.4305946482570995E-4</v>
       </c>
       <c r="D16">
-        <v>8.3802275798517279E-5</v>
+        <v>-1.7568137279429935E-5</v>
       </c>
       <c r="E16">
-        <v>-6.7190330242530857E-7</v>
+        <v>4.6666631239744723E-8</v>
       </c>
       <c r="F16">
-        <v>4.017072789060962E-5</v>
+        <v>-2.2041431157727737E-4</v>
       </c>
       <c r="G16">
-        <v>-9.3982628226355319E-5</v>
+        <v>-6.5990851223640332E-5</v>
       </c>
       <c r="H16">
-        <v>6.951287894309846E-5</v>
+        <v>-3.0081075776384027E-6</v>
       </c>
       <c r="I16">
-        <v>1.3150589659768138E-5</v>
+        <v>-1.2681633923612151E-4</v>
       </c>
       <c r="J16">
-        <v>-5.6203256731004677E-5</v>
+        <v>2.5040212735620527E-4</v>
       </c>
       <c r="K16">
-        <v>-4.257129006434232E-4</v>
+        <v>-1.0077216251422312E-3</v>
       </c>
       <c r="L16">
-        <v>3.9805177609202698E-5</v>
+        <v>1.5171623426569331E-4</v>
       </c>
       <c r="M16">
-        <v>4.1771596682051279E-5</v>
+        <v>-1.0160636845071234E-4</v>
       </c>
       <c r="N16">
-        <v>6.1356645282104023E-5</v>
+        <v>-8.3000501170189291E-5</v>
       </c>
       <c r="O16">
-        <v>8.8979624131823361E-5</v>
+        <v>-2.7527809149645354E-5</v>
       </c>
       <c r="P16">
-        <v>1.2345537630727128E-4</v>
+        <v>7.6372258124442725E-6</v>
       </c>
       <c r="Q16">
-        <v>3.5098467750619882E-3</v>
+        <v>5.9054765621035857E-3</v>
       </c>
       <c r="R16">
-        <v>6.5270789530333043E-5</v>
+        <v>-1.3894756382616972E-4</v>
       </c>
       <c r="S16">
-        <v>-1.7893555910582204E-4</v>
+        <v>-9.3692310790764391E-5</v>
       </c>
       <c r="T16">
-        <v>1.0334058002351717E-4</v>
+        <v>-9.1994997244362637E-5</v>
       </c>
       <c r="U16">
-        <v>6.5715158586556691E-5</v>
+        <v>1.2194756336567666E-4</v>
       </c>
       <c r="V16">
-        <v>-3.8603200729467958E-4</v>
+        <v>-1.2593300728661941E-3</v>
       </c>
       <c r="W16">
-        <v>-2.1876948828038662E-5</v>
+        <v>-1.6390343491275421E-4</v>
       </c>
       <c r="X16">
-        <v>6.7961101381772317E-5</v>
+        <v>-1.1830518258243699E-4</v>
       </c>
       <c r="Y16">
-        <v>4.0371473711887408E-6</v>
+        <v>-3.0559053035554183E-5</v>
       </c>
       <c r="Z16">
-        <v>-4.6955772177119609E-5</v>
+        <v>-1.0325782387641695E-4</v>
       </c>
       <c r="AA16">
-        <v>-4.5548181966953026E-6</v>
+        <v>-1.6049956065878571E-4</v>
       </c>
       <c r="AB16">
-        <v>1.4032805404520503E-4</v>
-      </c>
-      <c r="AC16">
-        <v>-1.1006495881467885E-4</v>
-      </c>
-      <c r="AD16">
-        <v>-2.4236098168558735E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.45">
+        <v>2.1205497448888062E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>27</v>
       </c>
       <c r="B17">
-        <v>-6.4716894005230757E-2</v>
+        <v>-0.11693068350562144</v>
       </c>
       <c r="C17">
-        <v>4.323123876386103E-4</v>
+        <v>1.3494772241353481E-3</v>
       </c>
       <c r="D17">
-        <v>-1.0087551247140673E-4</v>
+        <v>-9.8305006343306876E-5</v>
       </c>
       <c r="E17">
-        <v>5.0540706364847081E-7</v>
+        <v>3.28391158437022E-7</v>
       </c>
       <c r="F17">
-        <v>8.9968575282365531E-5</v>
+        <v>3.3676687195317596E-4</v>
       </c>
       <c r="G17">
-        <v>1.1913882776938599E-4</v>
+        <v>3.7750958698950544E-5</v>
       </c>
       <c r="H17">
-        <v>-5.9402096654258881E-5</v>
+        <v>-3.1894093915342276E-5</v>
       </c>
       <c r="I17">
-        <v>-7.1223835878054848E-5</v>
+        <v>-1.2888456360103087E-4</v>
       </c>
       <c r="J17">
-        <v>-6.3013656706980398E-4</v>
+        <v>-4.2945772627142826E-4</v>
       </c>
       <c r="K17">
-        <v>6.2036780529101462E-5</v>
+        <v>6.2731150092097936E-4</v>
       </c>
       <c r="L17">
-        <v>-1.8562341258781894E-4</v>
+        <v>-1.0433687915534819E-3</v>
       </c>
       <c r="M17">
-        <v>6.0291652041174224E-5</v>
+        <v>-1.5641391682033552E-4</v>
       </c>
       <c r="N17">
-        <v>1.9580070893802974E-4</v>
+        <v>2.3492579321381229E-4</v>
       </c>
       <c r="O17">
-        <v>2.2366172230404137E-4</v>
+        <v>5.7902372988285003E-4</v>
       </c>
       <c r="P17">
-        <v>1.3827101726314613E-4</v>
+        <v>4.3451797205239923E-4</v>
       </c>
       <c r="Q17">
-        <v>6.5270789530333043E-5</v>
+        <v>-1.3894756382616972E-4</v>
       </c>
       <c r="R17">
-        <v>2.0107644702404264E-3</v>
+        <v>3.8489495352485559E-3</v>
       </c>
       <c r="S17">
-        <v>-9.350014621200514E-4</v>
+        <v>-2.284488590629922E-3</v>
       </c>
       <c r="T17">
-        <v>-9.0606070013744345E-4</v>
+        <v>-2.1048439830188945E-3</v>
       </c>
       <c r="U17">
-        <v>-3.4357792987650709E-4</v>
+        <v>-5.1527905561085977E-4</v>
       </c>
       <c r="V17">
-        <v>2.5283361495398129E-4</v>
+        <v>9.8282148729175213E-4</v>
       </c>
       <c r="W17">
-        <v>4.372494467800698E-5</v>
+        <v>1.3552041757478603E-4</v>
       </c>
       <c r="X17">
-        <v>1.4873086409861858E-4</v>
+        <v>5.4604269176165062E-5</v>
       </c>
       <c r="Y17">
-        <v>1.4575078802275864E-5</v>
+        <v>1.5841338765741885E-5</v>
       </c>
       <c r="Z17">
-        <v>3.4878855291728622E-5</v>
+        <v>7.3679516502650325E-7</v>
       </c>
       <c r="AA17">
-        <v>3.6224620755998698E-6</v>
+        <v>6.1502456345174331E-6</v>
       </c>
       <c r="AB17">
-        <v>-6.8702079427808752E-5</v>
-      </c>
-      <c r="AC17">
-        <v>7.5335457031693899E-5</v>
-      </c>
-      <c r="AD17">
-        <v>3.6818938854404452E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.45">
+        <v>2.8002401822964755E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
       <c r="B18">
-        <v>0.16029042920422648</v>
+        <v>-3.0063878511793204E-2</v>
       </c>
       <c r="C18">
-        <v>4.4798522741220265E-5</v>
+        <v>-4.7353575574801698E-4</v>
       </c>
       <c r="D18">
-        <v>-8.3307533787629895E-5</v>
+        <v>-1.5642817740418131E-4</v>
       </c>
       <c r="E18">
-        <v>7.9662784823796918E-7</v>
+        <v>1.4839184184338562E-6</v>
       </c>
       <c r="F18">
-        <v>-2.0451611298511309E-4</v>
+        <v>-4.5879463790758244E-4</v>
       </c>
       <c r="G18">
-        <v>-3.2744006691192221E-5</v>
+        <v>-3.8443835193863489E-5</v>
       </c>
       <c r="H18">
-        <v>1.6672596359617936E-4</v>
+        <v>1.4578170998571838E-4</v>
       </c>
       <c r="I18">
-        <v>9.6380415550510745E-5</v>
+        <v>1.622013668759116E-4</v>
       </c>
       <c r="J18">
-        <v>1.2249841507555462E-4</v>
+        <v>1.0701705326355703E-4</v>
       </c>
       <c r="K18">
-        <v>-1.8910506694746619E-5</v>
+        <v>-6.2141630306236694E-4</v>
       </c>
       <c r="L18">
-        <v>3.1952547323941529E-4</v>
+        <v>1.0013971528056147E-3</v>
       </c>
       <c r="M18">
-        <v>7.5709480456004818E-5</v>
+        <v>-4.3144205742130017E-4</v>
       </c>
       <c r="N18">
-        <v>-1.0875277460531407E-4</v>
+        <v>-4.9753150872791229E-4</v>
       </c>
       <c r="O18">
-        <v>-2.5426314852149611E-5</v>
+        <v>-8.0986208969290811E-4</v>
       </c>
       <c r="P18">
-        <v>-3.0119656923040814E-5</v>
+        <v>-8.3158543155765021E-4</v>
       </c>
       <c r="Q18">
-        <v>-1.7893555910582204E-4</v>
+        <v>-9.3692310790764391E-5</v>
       </c>
       <c r="R18">
-        <v>-9.350014621200514E-4</v>
+        <v>-2.284488590629922E-3</v>
       </c>
       <c r="S18">
-        <v>4.5440247539090296E-3</v>
+        <v>1.0259461517258669E-2</v>
       </c>
       <c r="T18">
-        <v>1.3591955274427935E-4</v>
+        <v>1.6705898961527626E-3</v>
       </c>
       <c r="U18">
-        <v>2.0939781282367669E-4</v>
+        <v>2.3883013571119721E-4</v>
       </c>
       <c r="V18">
-        <v>-1.5827391573904295E-4</v>
+        <v>-5.6938576349986581E-4</v>
       </c>
       <c r="W18">
-        <v>-6.7217942808272835E-5</v>
+        <v>-1.31244453111308E-4</v>
       </c>
       <c r="X18">
-        <v>2.041428087776284E-4</v>
+        <v>2.8000377992140439E-5</v>
       </c>
       <c r="Y18">
-        <v>-6.9796853036685784E-5</v>
+        <v>7.0159991111635122E-6</v>
       </c>
       <c r="Z18">
-        <v>-5.6924903724590468E-5</v>
+        <v>-7.3396142416442883E-5</v>
       </c>
       <c r="AA18">
-        <v>2.7161807825584712E-5</v>
+        <v>-1.7132698518577337E-4</v>
       </c>
       <c r="AB18">
-        <v>-1.4083957655738834E-4</v>
-      </c>
-      <c r="AC18">
-        <v>-1.893404132890618E-4</v>
-      </c>
-      <c r="AD18">
-        <v>1.5007304696578738E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.45">
+        <v>4.9111838682717596E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>33</v>
       </c>
       <c r="B19">
-        <v>2.0393789138828847E-2</v>
+        <v>0.15980262174939289</v>
       </c>
       <c r="C19">
-        <v>-1.7668958970381063E-4</v>
+        <v>-2.4754747100904403E-4</v>
       </c>
       <c r="D19">
-        <v>-1.1574897419484257E-4</v>
+        <v>-1.3764682901875117E-4</v>
       </c>
       <c r="E19">
-        <v>9.7176323483467558E-7</v>
+        <v>1.329150523484204E-6</v>
       </c>
       <c r="F19">
-        <v>-1.5476135349585607E-4</v>
+        <v>4.8710978056520091E-5</v>
       </c>
       <c r="G19">
-        <v>-2.0876399576951366E-4</v>
+        <v>-8.2644302262337111E-5</v>
       </c>
       <c r="H19">
-        <v>5.4513010038388643E-5</v>
+        <v>9.6381864466779882E-5</v>
       </c>
       <c r="I19">
-        <v>6.7858375722436466E-5</v>
+        <v>9.1443400557779828E-5</v>
       </c>
       <c r="J19">
-        <v>2.2472173535308717E-4</v>
+        <v>6.6056414414733967E-5</v>
       </c>
       <c r="K19">
-        <v>-1.3822405959195921E-4</v>
+        <v>-3.0419301366085735E-4</v>
       </c>
       <c r="L19">
-        <v>3.6593037718058298E-4</v>
+        <v>9.3018861694540284E-4</v>
       </c>
       <c r="M19">
-        <v>-9.2492038032912196E-5</v>
+        <v>-3.1407362788607945E-5</v>
       </c>
       <c r="N19">
-        <v>-7.8931758385123019E-5</v>
+        <v>-4.9426998582451792E-4</v>
       </c>
       <c r="O19">
-        <v>-1.3167895673096852E-5</v>
+        <v>-5.7832535686846076E-4</v>
       </c>
       <c r="P19">
-        <v>-4.5802527792361146E-5</v>
+        <v>-5.6977196696413003E-4</v>
       </c>
       <c r="Q19">
-        <v>1.0334058002351717E-4</v>
+        <v>-9.1994997244362637E-5</v>
       </c>
       <c r="R19">
-        <v>-9.0606070013744345E-4</v>
+        <v>-2.1048439830188945E-3</v>
       </c>
       <c r="S19">
-        <v>1.3591955274427935E-4</v>
+        <v>1.6705898961527626E-3</v>
       </c>
       <c r="T19">
-        <v>4.3191848888843266E-3</v>
+        <v>8.5474049984493473E-3</v>
       </c>
       <c r="U19">
-        <v>6.5217623253893762E-5</v>
+        <v>4.7508566574407107E-5</v>
       </c>
       <c r="V19">
-        <v>-2.8962661318062159E-4</v>
+        <v>-6.1949134619481913E-4</v>
       </c>
       <c r="W19">
-        <v>-9.7666847680694785E-6</v>
+        <v>1.6980393854504599E-4</v>
       </c>
       <c r="X19">
-        <v>-1.3496034807452964E-4</v>
+        <v>-2.1324809269281011E-5</v>
       </c>
       <c r="Y19">
-        <v>-5.92182729886473E-5</v>
+        <v>-1.4750903966183543E-5</v>
       </c>
       <c r="Z19">
-        <v>-3.2785687742397773E-5</v>
+        <v>-9.0501108482288087E-5</v>
       </c>
       <c r="AA19">
-        <v>-2.3922446473303755E-6</v>
+        <v>-3.8667498509784546E-5</v>
       </c>
       <c r="AB19">
-        <v>5.1634118493158754E-5</v>
-      </c>
-      <c r="AC19">
-        <v>4.1208944327527698E-4</v>
-      </c>
-      <c r="AD19">
-        <v>3.6039532159013871E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.45">
+        <v>4.3812493951153678E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0.13017798038052569</v>
+        <v>0.13963653873003565</v>
       </c>
       <c r="C20">
-        <v>-4.5645015236555101E-5</v>
+        <v>-3.2704499653844071E-4</v>
       </c>
       <c r="D20">
-        <v>-7.8362493866083668E-6</v>
+        <v>-1.0075155160613712E-4</v>
       </c>
       <c r="E20">
-        <v>4.4817086984422027E-8</v>
+        <v>6.7875171532627332E-7</v>
       </c>
       <c r="F20">
-        <v>4.1987299758546818E-6</v>
+        <v>7.8020306661964745E-6</v>
       </c>
       <c r="G20">
-        <v>-1.5611644632758858E-5</v>
+        <v>2.9612488441949254E-6</v>
       </c>
       <c r="H20">
-        <v>7.877396459491173E-5</v>
+        <v>-2.7489470462136958E-4</v>
       </c>
       <c r="I20">
-        <v>7.4509910596189436E-5</v>
+        <v>-1.6576871115611216E-4</v>
       </c>
       <c r="J20">
-        <v>-4.5006814949378646E-5</v>
+        <v>1.6689810786631588E-4</v>
       </c>
       <c r="K20">
-        <v>1.2677846451092208E-4</v>
+        <v>3.0279826874187517E-4</v>
       </c>
       <c r="L20">
-        <v>8.856278085677446E-5</v>
+        <v>-2.566096561118004E-5</v>
       </c>
       <c r="M20">
-        <v>-7.3720245042518278E-6</v>
+        <v>2.2226553138962043E-5</v>
       </c>
       <c r="N20">
-        <v>1.7406270982262627E-4</v>
+        <v>3.5870855265314613E-4</v>
       </c>
       <c r="O20">
-        <v>3.2389978195724141E-4</v>
+        <v>8.4085658459097281E-4</v>
       </c>
       <c r="P20">
-        <v>6.1540032607335289E-4</v>
+        <v>1.1226795311006376E-3</v>
       </c>
       <c r="Q20">
-        <v>6.5715158586556691E-5</v>
+        <v>1.2194756336567666E-4</v>
       </c>
       <c r="R20">
-        <v>-3.4357792987650709E-4</v>
+        <v>-5.1527905561085977E-4</v>
       </c>
       <c r="S20">
-        <v>2.0939781282367669E-4</v>
+        <v>2.3883013571119721E-4</v>
       </c>
       <c r="T20">
-        <v>6.5217623253893762E-5</v>
+        <v>4.7508566574407107E-5</v>
       </c>
       <c r="U20">
-        <v>1.008261484233452E-3</v>
+        <v>1.7145606913885358E-3</v>
       </c>
       <c r="V20">
-        <v>-2.4978881273230661E-4</v>
+        <v>-4.5949758867092479E-4</v>
       </c>
       <c r="W20">
-        <v>-3.948317424458816E-5</v>
+        <v>3.2986702022424986E-5</v>
       </c>
       <c r="X20">
-        <v>-4.5257520764793691E-6</v>
+        <v>5.0099491580307069E-5</v>
       </c>
       <c r="Y20">
-        <v>2.0389241874314737E-5</v>
+        <v>3.6440751267415326E-6</v>
       </c>
       <c r="Z20">
-        <v>-7.6716696928476194E-6</v>
+        <v>-5.9089978300843841E-5</v>
       </c>
       <c r="AA20">
-        <v>1.1777113110683288E-5</v>
+        <v>5.4190325870851362E-5</v>
       </c>
       <c r="AB20">
-        <v>-3.7115820882262419E-5</v>
-      </c>
-      <c r="AC20">
-        <v>-5.79482122171688E-5</v>
-      </c>
-      <c r="AD20">
-        <v>-7.9911588958017817E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.45">
+        <v>2.0761882388528443E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0.37879530067661465</v>
+        <v>0.13370476145222798</v>
       </c>
       <c r="C21">
-        <v>-3.0902924175937679E-5</v>
+        <v>1.949414229772033E-4</v>
       </c>
       <c r="D21">
-        <v>1.5666039869506924E-4</v>
+        <v>1.2533302175822948E-4</v>
       </c>
       <c r="E21">
-        <v>-1.1866799563889454E-6</v>
+        <v>-9.6477969927690927E-7</v>
       </c>
       <c r="F21">
-        <v>-2.3721053787927347E-4</v>
+        <v>-1.9494130794484805E-4</v>
       </c>
       <c r="G21">
-        <v>-9.3776691258086529E-5</v>
+        <v>-3.2806154509847232E-4</v>
       </c>
       <c r="H21">
-        <v>-1.4702682419550348E-5</v>
+        <v>2.1808093315828448E-4</v>
       </c>
       <c r="I21">
-        <v>4.5416097483290727E-5</v>
+        <v>-1.8873334196598936E-4</v>
       </c>
       <c r="J21">
-        <v>8.529570117160029E-5</v>
+        <v>-1.0831938223931223E-4</v>
       </c>
       <c r="K21">
-        <v>3.3747335471180173E-5</v>
+        <v>1.7359609021109099E-4</v>
       </c>
       <c r="L21">
-        <v>1.8217096591236474E-4</v>
+        <v>1.2464002399635213E-5</v>
       </c>
       <c r="M21">
-        <v>-7.2057653136608834E-6</v>
+        <v>1.4741133059672682E-4</v>
       </c>
       <c r="N21">
-        <v>2.9334828664448855E-4</v>
+        <v>-1.5575592414441246E-4</v>
       </c>
       <c r="O21">
-        <v>2.512152397360008E-4</v>
+        <v>2.22872828440068E-4</v>
       </c>
       <c r="P21">
-        <v>3.6677601638455905E-4</v>
+        <v>4.9239170257848628E-4</v>
       </c>
       <c r="Q21">
-        <v>-3.8603200729467958E-4</v>
+        <v>-1.2593300728661941E-3</v>
       </c>
       <c r="R21">
-        <v>2.5283361495398129E-4</v>
+        <v>9.8282148729175213E-4</v>
       </c>
       <c r="S21">
-        <v>-1.5827391573904295E-4</v>
+        <v>-5.6938576349986581E-4</v>
       </c>
       <c r="T21">
-        <v>-2.8962661318062159E-4</v>
+        <v>-6.1949134619481913E-4</v>
       </c>
       <c r="U21">
-        <v>-2.4978881273230661E-4</v>
+        <v>-4.5949758867092479E-4</v>
       </c>
       <c r="V21">
-        <v>1.020618716293366E-2</v>
+        <v>1.6807694196372087E-2</v>
       </c>
       <c r="W21">
-        <v>-1.086100255102908E-4</v>
+        <v>1.181718966471165E-4</v>
       </c>
       <c r="X21">
-        <v>1.4887519083336406E-4</v>
+        <v>1.8961340339684462E-4</v>
       </c>
       <c r="Y21">
-        <v>-2.0355804551274077E-6</v>
+        <v>-8.0600574156816798E-6</v>
       </c>
       <c r="Z21">
-        <v>-2.7078447112403214E-5</v>
+        <v>-2.430777826994806E-4</v>
       </c>
       <c r="AA21">
-        <v>8.2431394185044805E-6</v>
+        <v>-2.3251623034242682E-4</v>
       </c>
       <c r="AB21">
-        <v>-8.2599655664781081E-6</v>
-      </c>
-      <c r="AC21">
-        <v>-5.2070342442906911E-5</v>
-      </c>
-      <c r="AD21">
-        <v>-5.5713626066278051E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-4.4194947556180798E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
       <c r="B22">
-        <v>-0.27766488699825514</v>
+        <v>-5.7117740445388178E-2</v>
       </c>
       <c r="C22">
-        <v>4.3576829731504916E-5</v>
+        <v>1.7648531445258169E-4</v>
       </c>
       <c r="D22">
-        <v>-1.2298696125120662E-4</v>
+        <v>1.3098656831334043E-4</v>
       </c>
       <c r="E22">
-        <v>8.8049174438544032E-7</v>
+        <v>-1.0179916760706139E-6</v>
       </c>
       <c r="F22">
-        <v>-7.8424872763294395E-5</v>
+        <v>-1.6367215783590593E-4</v>
       </c>
       <c r="G22">
-        <v>9.3725988055200254E-7</v>
+        <v>-1.3412177158276389E-4</v>
       </c>
       <c r="H22">
-        <v>3.8820135270743711E-6</v>
+        <v>-2.3694978586048386E-4</v>
       </c>
       <c r="I22">
-        <v>1.5383205870277763E-5</v>
+        <v>-5.8152093776901422E-4</v>
       </c>
       <c r="J22">
-        <v>1.3178235406130197E-4</v>
+        <v>1.1576206327555336E-4</v>
       </c>
       <c r="K22">
-        <v>-1.872209523951523E-5</v>
+        <v>6.1976889765541021E-4</v>
       </c>
       <c r="L22">
-        <v>-4.5872664248433273E-5</v>
+        <v>-2.9475886149186309E-5</v>
       </c>
       <c r="M22">
-        <v>6.5067158609018042E-5</v>
+        <v>-1.1472829739784293E-4</v>
       </c>
       <c r="N22">
-        <v>3.6697775670773683E-5</v>
+        <v>2.9420596425458229E-5</v>
       </c>
       <c r="O22">
-        <v>9.8929173283288639E-5</v>
+        <v>2.5457971783146441E-4</v>
       </c>
       <c r="P22">
-        <v>1.7219597287869182E-4</v>
+        <v>1.4218309761342227E-4</v>
       </c>
       <c r="Q22">
-        <v>-2.1876948828038662E-5</v>
+        <v>-1.6390343491275421E-4</v>
       </c>
       <c r="R22">
-        <v>4.372494467800698E-5</v>
+        <v>1.3552041757478603E-4</v>
       </c>
       <c r="S22">
-        <v>-6.7217942808272835E-5</v>
+        <v>-1.31244453111308E-4</v>
       </c>
       <c r="T22">
-        <v>-9.7666847680694785E-6</v>
+        <v>1.6980393854504599E-4</v>
       </c>
       <c r="U22">
-        <v>-3.948317424458816E-5</v>
+        <v>3.2986702022424986E-5</v>
       </c>
       <c r="V22">
-        <v>-1.086100255102908E-4</v>
+        <v>1.181718966471165E-4</v>
       </c>
       <c r="W22">
-        <v>1.1722214570811971E-3</v>
+        <v>3.2974016513025511E-3</v>
       </c>
       <c r="X22">
-        <v>5.9443298502252122E-4</v>
+        <v>1.1496972877706713E-3</v>
       </c>
       <c r="Y22">
-        <v>5.3101566325762907E-4</v>
+        <v>-1.20549039466686E-6</v>
       </c>
       <c r="Z22">
-        <v>5.4423248259039035E-4</v>
+        <v>-1.4411766086040175E-4</v>
       </c>
       <c r="AA22">
-        <v>-2.0699234436439499E-6</v>
+        <v>-5.8108053631757841E-5</v>
       </c>
       <c r="AB22">
-        <v>4.4309904665515811E-5</v>
-      </c>
-      <c r="AC22">
-        <v>6.038989192358533E-5</v>
-      </c>
-      <c r="AD22">
-        <v>3.586347692408634E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-5.3873878962625724E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
       <c r="B23">
-        <v>-0.4402387216427821</v>
+        <v>-1.8588043261644888E-2</v>
       </c>
       <c r="C23">
-        <v>-3.8514277944535827E-5</v>
+        <v>1.014071498706456E-4</v>
       </c>
       <c r="D23">
-        <v>-1.2836239432304809E-4</v>
+        <v>9.2599972771115896E-5</v>
       </c>
       <c r="E23">
-        <v>9.7119313994013702E-7</v>
+        <v>-7.1077695336537166E-7</v>
       </c>
       <c r="F23">
-        <v>-9.1383671079326822E-5</v>
+        <v>-1.3422032601599111E-4</v>
       </c>
       <c r="G23">
-        <v>4.9960686878304332E-5</v>
+        <v>-1.6762702870388307E-4</v>
       </c>
       <c r="H23">
-        <v>9.6495393545886827E-5</v>
+        <v>-2.9635629880345616E-4</v>
       </c>
       <c r="I23">
-        <v>-6.0949923426508926E-5</v>
+        <v>-5.6581064273221265E-4</v>
       </c>
       <c r="J23">
-        <v>-3.1841219088219824E-5</v>
+        <v>1.4927116694363196E-4</v>
       </c>
       <c r="K23">
-        <v>-1.2070038645887165E-4</v>
+        <v>3.775465807769918E-4</v>
       </c>
       <c r="L23">
-        <v>2.7888289334066039E-6</v>
+        <v>9.1736617252843704E-5</v>
       </c>
       <c r="M23">
-        <v>1.3770282227285339E-4</v>
+        <v>-1.1940146652703542E-5</v>
       </c>
       <c r="N23">
-        <v>1.4211459793614541E-4</v>
+        <v>2.4672131667175857E-5</v>
       </c>
       <c r="O23">
-        <v>2.2465508670203258E-4</v>
+        <v>2.4911801611292306E-4</v>
       </c>
       <c r="P23">
-        <v>2.6827901500771269E-4</v>
+        <v>2.1920451306449863E-4</v>
       </c>
       <c r="Q23">
-        <v>6.7961101381772317E-5</v>
+        <v>-1.1830518258243699E-4</v>
       </c>
       <c r="R23">
-        <v>1.4873086409861858E-4</v>
+        <v>5.4604269176165062E-5</v>
       </c>
       <c r="S23">
-        <v>2.041428087776284E-4</v>
+        <v>2.8000377992140439E-5</v>
       </c>
       <c r="T23">
-        <v>-1.3496034807452964E-4</v>
+        <v>-2.1324809269281011E-5</v>
       </c>
       <c r="U23">
-        <v>-4.5257520764793691E-6</v>
+        <v>5.0099491580307069E-5</v>
       </c>
       <c r="V23">
-        <v>1.4887519083336406E-4</v>
+        <v>1.8961340339684462E-4</v>
       </c>
       <c r="W23">
-        <v>5.9443298502252122E-4</v>
+        <v>1.1496972877706713E-3</v>
       </c>
       <c r="X23">
-        <v>2.1379719415412922E-3</v>
+        <v>1.4883137917735538E-3</v>
       </c>
       <c r="Y23">
-        <v>5.2706159712855927E-4</v>
+        <v>2.1831796261984196E-5</v>
       </c>
       <c r="Z23">
-        <v>5.5102598180861273E-4</v>
+        <v>-1.0353493583790386E-4</v>
       </c>
       <c r="AA23">
-        <v>-2.3914320144305206E-6</v>
+        <v>-3.8240621488985614E-5</v>
       </c>
       <c r="AB23">
-        <v>-3.2951175346861031E-5</v>
-      </c>
-      <c r="AC23">
-        <v>-9.0502807889612747E-5</v>
-      </c>
-      <c r="AD23">
-        <v>3.5477088726258753E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-4.4876645369462094E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="B24">
-        <v>-1.7272663814893903E-2</v>
+        <v>-5.1114889715703445E-2</v>
       </c>
       <c r="C24">
-        <v>1.3079467251342531E-5</v>
+        <v>2.4205835851886067E-5</v>
       </c>
       <c r="D24">
-        <v>-2.3560051062982562E-5</v>
+        <v>4.5745101166119566E-6</v>
       </c>
       <c r="E24">
-        <v>1.6164427698259502E-7</v>
+        <v>-4.0087643653158127E-8</v>
       </c>
       <c r="F24">
-        <v>-3.8689048464089684E-5</v>
+        <v>-1.668696514003031E-5</v>
       </c>
       <c r="G24">
-        <v>4.0101324938063287E-6</v>
+        <v>-2.2247134559976421E-5</v>
       </c>
       <c r="H24">
-        <v>4.6540385602321095E-5</v>
+        <v>-8.2879699778506683E-6</v>
       </c>
       <c r="I24">
-        <v>4.4280955911512763E-5</v>
+        <v>1.6563416971135568E-5</v>
       </c>
       <c r="J24">
-        <v>3.0783141663231432E-5</v>
+        <v>1.3277265771253002E-5</v>
       </c>
       <c r="K24">
-        <v>3.9985449702516495E-5</v>
+        <v>2.173227926256464E-5</v>
       </c>
       <c r="L24">
-        <v>-1.1066110228778476E-5</v>
+        <v>-1.7007761436753583E-6</v>
       </c>
       <c r="M24">
-        <v>-3.6913870727648638E-5</v>
+        <v>-7.0717934358781028E-7</v>
       </c>
       <c r="N24">
-        <v>-3.3834740673162615E-5</v>
+        <v>-2.7700495730804519E-6</v>
       </c>
       <c r="O24">
-        <v>3.3656129223273322E-6</v>
+        <v>-1.2776954762038677E-5</v>
       </c>
       <c r="P24">
-        <v>7.167162809348026E-5</v>
+        <v>-1.5714883976621888E-5</v>
       </c>
       <c r="Q24">
-        <v>4.0371473711887408E-6</v>
+        <v>-3.0559053035554183E-5</v>
       </c>
       <c r="R24">
-        <v>1.4575078802275864E-5</v>
+        <v>1.5841338765741885E-5</v>
       </c>
       <c r="S24">
-        <v>-6.9796853036685784E-5</v>
+        <v>7.0159991111635122E-6</v>
       </c>
       <c r="T24">
-        <v>-5.92182729886473E-5</v>
+        <v>-1.4750903966183543E-5</v>
       </c>
       <c r="U24">
-        <v>2.0389241874314737E-5</v>
+        <v>3.6440751267415326E-6</v>
       </c>
       <c r="V24">
-        <v>-2.0355804551274077E-6</v>
+        <v>-8.0600574156816798E-6</v>
       </c>
       <c r="W24">
-        <v>5.3101566325762907E-4</v>
+        <v>-1.20549039466686E-6</v>
       </c>
       <c r="X24">
-        <v>5.2706159712855927E-4</v>
+        <v>2.1831796261984196E-5</v>
       </c>
       <c r="Y24">
-        <v>1.0131294787028677E-3</v>
+        <v>2.1768095277518191E-5</v>
       </c>
       <c r="Z24">
-        <v>5.2300297726871946E-4</v>
+        <v>-6.590099275599639E-5</v>
       </c>
       <c r="AA24">
-        <v>-8.7785579112093743E-6</v>
+        <v>-8.8596778412359124E-5</v>
       </c>
       <c r="AB24">
-        <v>5.5867781433451772E-5</v>
-      </c>
-      <c r="AC24">
-        <v>1.487109373341243E-6</v>
-      </c>
-      <c r="AD24">
-        <v>3.6299477316696161E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-5.3517830583046011E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B25">
-        <v>-0.20965427441247456</v>
+        <v>3.8077141386045996E-2</v>
       </c>
       <c r="C25">
-        <v>4.3568309409761172E-5</v>
+        <v>-6.3709721385612279E-6</v>
       </c>
       <c r="D25">
-        <v>-7.3000092347791021E-5</v>
+        <v>8.7681235197830439E-5</v>
       </c>
       <c r="E25">
-        <v>5.3963416203317821E-7</v>
+        <v>-7.6501219286060628E-7</v>
       </c>
       <c r="F25">
-        <v>-1.7700660590338774E-5</v>
+        <v>-1.384835918040448E-4</v>
       </c>
       <c r="G25">
-        <v>-6.2429725571425121E-7</v>
+        <v>-2.3514171009015325E-4</v>
       </c>
       <c r="H25">
-        <v>5.038424332845081E-5</v>
+        <v>-1.8617858197068443E-4</v>
       </c>
       <c r="I25">
-        <v>1.879742920110985E-5</v>
+        <v>-1.7909501388125982E-4</v>
       </c>
       <c r="J25">
-        <v>6.4842173534579352E-5</v>
+        <v>1.6299710846095822E-4</v>
       </c>
       <c r="K25">
-        <v>2.2418101799622728E-5</v>
+        <v>-3.5299881018857317E-5</v>
       </c>
       <c r="L25">
-        <v>-3.3797742482051009E-5</v>
+        <v>1.1689959669137606E-4</v>
       </c>
       <c r="M25">
-        <v>4.7724499751832005E-5</v>
+        <v>-7.1097737409407734E-5</v>
       </c>
       <c r="N25">
-        <v>3.2820462139969983E-6</v>
+        <v>-1.1229312177606783E-4</v>
       </c>
       <c r="O25">
-        <v>3.2727317686222787E-5</v>
+        <v>-7.7393034202703043E-5</v>
       </c>
       <c r="P25">
-        <v>8.6216263244923218E-5</v>
+        <v>-2.8049707976259306E-4</v>
       </c>
       <c r="Q25">
-        <v>-4.6955772177119609E-5</v>
+        <v>-1.0325782387641695E-4</v>
       </c>
       <c r="R25">
-        <v>3.4878855291728622E-5</v>
+        <v>7.3679516502650325E-7</v>
       </c>
       <c r="S25">
-        <v>-5.6924903724590468E-5</v>
+        <v>-7.3396142416442883E-5</v>
       </c>
       <c r="T25">
-        <v>-3.2785687742397773E-5</v>
+        <v>-9.0501108482288087E-5</v>
       </c>
       <c r="U25">
-        <v>-7.6716696928476194E-6</v>
+        <v>-5.9089978300843841E-5</v>
       </c>
       <c r="V25">
-        <v>-2.7078447112403214E-5</v>
+        <v>-2.430777826994806E-4</v>
       </c>
       <c r="W25">
-        <v>5.4423248259039035E-4</v>
+        <v>-1.4411766086040175E-4</v>
       </c>
       <c r="X25">
-        <v>5.5102598180861273E-4</v>
+        <v>-1.0353493583790386E-4</v>
       </c>
       <c r="Y25">
-        <v>5.2300297726871946E-4</v>
+        <v>-6.590099275599639E-5</v>
       </c>
       <c r="Z25">
-        <v>9.9638738944707902E-4</v>
+        <v>2.7952681900059737E-3</v>
       </c>
       <c r="AA25">
-        <v>-7.0352348341679649E-6</v>
+        <v>5.4109303342380678E-4</v>
       </c>
       <c r="AB25">
-        <v>1.00645059274738E-5</v>
-      </c>
-      <c r="AC25">
-        <v>-2.6915311918489941E-5</v>
-      </c>
-      <c r="AD25">
-        <v>1.9152171973603129E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.45">
+        <v>-1.2207348636756911E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B26">
-        <v>-2.4903653230387596E-2</v>
+        <v>-5.1972614615125333E-2</v>
       </c>
       <c r="C26">
-        <v>4.1173285590256976E-6</v>
+        <v>6.0460818548896308E-5</v>
       </c>
       <c r="D26">
-        <v>-8.3156851569843749E-6</v>
+        <v>-3.861313075860821E-5</v>
       </c>
       <c r="E26">
-        <v>4.4960952120793899E-8</v>
+        <v>2.1338260029720769E-7</v>
       </c>
       <c r="F26">
-        <v>-1.8881016109089429E-5</v>
+        <v>1.0506119119934676E-4</v>
       </c>
       <c r="G26">
-        <v>-1.1722711849127205E-5</v>
+        <v>1.5979938600405963E-4</v>
       </c>
       <c r="H26">
-        <v>-2.4663283213307208E-6</v>
+        <v>2.0255178506772638E-5</v>
       </c>
       <c r="I26">
-        <v>6.4612010417570585E-6</v>
+        <v>2.9216892939803868E-6</v>
       </c>
       <c r="J26">
-        <v>3.1385956297426025E-5</v>
+        <v>1.1641476624096295E-4</v>
       </c>
       <c r="K26">
-        <v>-6.25166751773641E-6</v>
+        <v>1.4826016861596775E-4</v>
       </c>
       <c r="L26">
-        <v>6.1434974962383906E-6</v>
+        <v>-7.5025123757002741E-5</v>
       </c>
       <c r="M26">
-        <v>6.8284507372023869E-6</v>
+        <v>1.9403402809785102E-4</v>
       </c>
       <c r="N26">
-        <v>8.3564551043839466E-6</v>
+        <v>8.0863472799159688E-5</v>
       </c>
       <c r="O26">
-        <v>1.2350769156671299E-5</v>
+        <v>1.5485075705517142E-4</v>
       </c>
       <c r="P26">
-        <v>4.5493221811450846E-6</v>
+        <v>1.3201352587498635E-4</v>
       </c>
       <c r="Q26">
-        <v>-4.5548181966953026E-6</v>
+        <v>-1.6049956065878571E-4</v>
       </c>
       <c r="R26">
-        <v>3.6224620755998698E-6</v>
+        <v>6.1502456345174331E-6</v>
       </c>
       <c r="S26">
-        <v>2.7161807825584712E-5</v>
+        <v>-1.7132698518577337E-4</v>
       </c>
       <c r="T26">
-        <v>-2.3922446473303755E-6</v>
+        <v>-3.8667498509784546E-5</v>
       </c>
       <c r="U26">
-        <v>1.1777113110683288E-5</v>
+        <v>5.4190325870851362E-5</v>
       </c>
       <c r="V26">
-        <v>8.2431394185044805E-6</v>
+        <v>-2.3251623034242682E-4</v>
       </c>
       <c r="W26">
-        <v>-2.0699234436439499E-6</v>
+        <v>-5.8108053631757841E-5</v>
       </c>
       <c r="X26">
-        <v>-2.3914320144305206E-6</v>
+        <v>-3.8240621488985614E-5</v>
       </c>
       <c r="Y26">
-        <v>-8.7785579112093743E-6</v>
+        <v>-8.8596778412359124E-5</v>
       </c>
       <c r="Z26">
-        <v>-7.0352348341679649E-6</v>
+        <v>5.4109303342380678E-4</v>
       </c>
       <c r="AA26">
-        <v>1.2819214310287792E-5</v>
+        <v>4.4954777677000818E-3</v>
       </c>
       <c r="AB26">
-        <v>-4.9887427569553912E-5</v>
-      </c>
-      <c r="AC26">
-        <v>-5.9489903332642547E-5</v>
-      </c>
-      <c r="AD26">
-        <v>1.169123702854084E-4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.45">
+        <v>2.5558828420983934E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B27">
-        <v>8.6058928368833471E-2</v>
+        <v>-14.488176498697358</v>
       </c>
       <c r="C27">
-        <v>6.2958981598370162E-5</v>
+        <v>-6.2625976485931358E-3</v>
       </c>
       <c r="D27">
-        <v>-3.5903404885761526E-5</v>
+        <v>-4.9825583150525488E-2</v>
       </c>
       <c r="E27">
-        <v>2.2423539939320507E-7</v>
+        <v>3.9013265461511869E-4</v>
       </c>
       <c r="F27">
-        <v>-3.2183353474086237E-7</v>
+        <v>3.3245400537621983E-2</v>
       </c>
       <c r="G27">
-        <v>7.0087298320472961E-5</v>
+        <v>3.2721969509083626E-2</v>
       </c>
       <c r="H27">
-        <v>2.043208115373393E-5</v>
+        <v>-1.5038346443663544E-4</v>
       </c>
       <c r="I27">
-        <v>4.9048343757721069E-6</v>
+        <v>3.7513511035775684E-3</v>
       </c>
       <c r="J27">
-        <v>2.0855462036519694E-4</v>
+        <v>-1.9799660230549215E-2</v>
       </c>
       <c r="K27">
-        <v>2.1052615565188645E-4</v>
+        <v>-4.2673207761173195E-3</v>
       </c>
       <c r="L27">
-        <v>-1.4470526959323464E-4</v>
+        <v>-1.3057191873625834E-2</v>
       </c>
       <c r="M27">
-        <v>-3.4920607621271194E-5</v>
+        <v>-3.7739459844945249E-3</v>
       </c>
       <c r="N27">
-        <v>-2.4033348125394877E-5</v>
+        <v>-4.3291335557746665E-3</v>
       </c>
       <c r="O27">
-        <v>-2.2486544475838711E-5</v>
+        <v>-1.713715752095897E-3</v>
       </c>
       <c r="P27">
-        <v>1.408505672128755E-5</v>
+        <v>-7.1155846511253215E-3</v>
       </c>
       <c r="Q27">
-        <v>1.4032805404520503E-4</v>
+        <v>2.1205497448888062E-3</v>
       </c>
       <c r="R27">
-        <v>-6.8702079427808752E-5</v>
+        <v>2.8002401822964755E-3</v>
       </c>
       <c r="S27">
-        <v>-1.4083957655738834E-4</v>
+        <v>4.9111838682717596E-3</v>
       </c>
       <c r="T27">
-        <v>5.1634118493158754E-5</v>
+        <v>4.3812493951153678E-3</v>
       </c>
       <c r="U27">
-        <v>-3.7115820882262419E-5</v>
+        <v>2.0761882388528443E-3</v>
       </c>
       <c r="V27">
-        <v>-8.2599655664781081E-6</v>
+        <v>-4.4194947556180798E-3</v>
       </c>
       <c r="W27">
-        <v>4.4309904665515811E-5</v>
+        <v>-5.3873878962625724E-3</v>
       </c>
       <c r="X27">
-        <v>-3.2951175346861031E-5</v>
+        <v>-4.4876645369462094E-3</v>
       </c>
       <c r="Y27">
-        <v>5.5867781433451772E-5</v>
+        <v>-5.3517830583046011E-4</v>
       </c>
       <c r="Z27">
-        <v>1.00645059274738E-5</v>
+        <v>-1.2207348636756911E-3</v>
       </c>
       <c r="AA27">
-        <v>-4.9887427569553912E-5</v>
+        <v>2.5558828420983934E-3</v>
       </c>
       <c r="AB27">
-        <v>1.917771574130183E-3</v>
-      </c>
-      <c r="AC27">
-        <v>4.2236923479040925E-4</v>
-      </c>
-      <c r="AD27">
-        <v>1.8686066019870623E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28">
-        <v>-0.67928216994032609</v>
-      </c>
-      <c r="C28">
-        <v>8.5749457677295702E-5</v>
-      </c>
-      <c r="D28">
-        <v>-1.7499159508445848E-4</v>
-      </c>
-      <c r="E28">
-        <v>1.1546564149823158E-6</v>
-      </c>
-      <c r="F28">
-        <v>-8.4855327018075813E-5</v>
-      </c>
-      <c r="G28">
-        <v>1.3461443381087212E-4</v>
-      </c>
-      <c r="H28">
-        <v>1.7919395327540806E-5</v>
-      </c>
-      <c r="I28">
-        <v>-4.9403651879806158E-5</v>
-      </c>
-      <c r="J28">
-        <v>3.9602656651541428E-5</v>
-      </c>
-      <c r="K28">
-        <v>-2.1215426605875374E-5</v>
-      </c>
-      <c r="L28">
-        <v>1.8399041315952567E-4</v>
-      </c>
-      <c r="M28">
-        <v>-7.0923082753068963E-5</v>
-      </c>
-      <c r="N28">
-        <v>-9.7998225566881328E-6</v>
-      </c>
-      <c r="O28">
-        <v>-2.6309775435641013E-5</v>
-      </c>
-      <c r="P28">
-        <v>-1.1224282453956892E-4</v>
-      </c>
-      <c r="Q28">
-        <v>-1.1006495881467885E-4</v>
-      </c>
-      <c r="R28">
-        <v>7.5335457031693899E-5</v>
-      </c>
-      <c r="S28">
-        <v>-1.893404132890618E-4</v>
-      </c>
-      <c r="T28">
-        <v>4.1208944327527698E-4</v>
-      </c>
-      <c r="U28">
-        <v>-5.79482122171688E-5</v>
-      </c>
-      <c r="V28">
-        <v>-5.2070342442906911E-5</v>
-      </c>
-      <c r="W28">
-        <v>6.038989192358533E-5</v>
-      </c>
-      <c r="X28">
-        <v>-9.0502807889612747E-5</v>
-      </c>
-      <c r="Y28">
-        <v>1.487109373341243E-6</v>
-      </c>
-      <c r="Z28">
-        <v>-2.6915311918489941E-5</v>
-      </c>
-      <c r="AA28">
-        <v>-5.9489903332642547E-5</v>
-      </c>
-      <c r="AB28">
-        <v>4.2236923479040925E-4</v>
-      </c>
-      <c r="AC28">
-        <v>5.2682043366341575E-3</v>
-      </c>
-      <c r="AD28">
-        <v>7.1947123740678303E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29">
-        <v>-24.763095017560172</v>
-      </c>
-      <c r="C29">
-        <v>-9.1001292384887411E-5</v>
-      </c>
-      <c r="D29">
-        <v>-3.2778703372456267E-2</v>
-      </c>
-      <c r="E29">
-        <v>2.406449329559597E-4</v>
-      </c>
-      <c r="F29">
-        <v>3.5875425679274472E-3</v>
-      </c>
-      <c r="G29">
-        <v>5.3350735952675046E-3</v>
-      </c>
-      <c r="H29">
-        <v>-4.3943825161759324E-3</v>
-      </c>
-      <c r="I29">
-        <v>-6.5312864947751209E-3</v>
-      </c>
-      <c r="J29">
-        <v>1.2966391664548427E-2</v>
-      </c>
-      <c r="K29">
-        <v>4.2760243892310318E-3</v>
-      </c>
-      <c r="L29">
-        <v>-1.0969298898247083E-2</v>
-      </c>
-      <c r="M29">
-        <v>9.4548228122112721E-4</v>
-      </c>
-      <c r="N29">
-        <v>1.4462751017154333E-3</v>
-      </c>
-      <c r="O29">
-        <v>-4.7847068426994585E-3</v>
-      </c>
-      <c r="P29">
-        <v>-5.8488023755043344E-3</v>
-      </c>
-      <c r="Q29">
-        <v>-2.4236098168558735E-3</v>
-      </c>
-      <c r="R29">
-        <v>3.6818938854404452E-3</v>
-      </c>
-      <c r="S29">
-        <v>1.5007304696578738E-3</v>
-      </c>
-      <c r="T29">
-        <v>3.6039532159013871E-3</v>
-      </c>
-      <c r="U29">
-        <v>-7.9911588958017817E-4</v>
-      </c>
-      <c r="V29">
-        <v>-5.5713626066278051E-3</v>
-      </c>
-      <c r="W29">
-        <v>3.586347692408634E-3</v>
-      </c>
-      <c r="X29">
-        <v>3.5477088726258753E-3</v>
-      </c>
-      <c r="Y29">
-        <v>3.6299477316696161E-4</v>
-      </c>
-      <c r="Z29">
-        <v>1.9152171973603129E-3</v>
-      </c>
-      <c r="AA29">
-        <v>1.169123702854084E-4</v>
-      </c>
-      <c r="AB29">
-        <v>1.8686066019870623E-3</v>
-      </c>
-      <c r="AC29">
-        <v>7.1947123740678303E-3</v>
-      </c>
-      <c r="AD29">
-        <v>1.0991495579570776</v>
+        <v>1.5941835609793777</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -8,8 +8,8 @@
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId2"/>
     <sheet name="Gof" sheetId="2" r:id="rId4"/>
-    <sheet name="R1a" sheetId="3" r:id="rId5"/>
-    <sheet name="R1b" sheetId="4" r:id="rId6"/>
+    <sheet name="UK_R1a" sheetId="3" r:id="rId5"/>
+    <sheet name="UK_R1b" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -2638,13 +2638,13 @@
         <v>80</v>
       </c>
       <c r="B5">
-        <v>0.23459876105008604</v>
+        <v>0.23457460709323752</v>
       </c>
       <c r="E5" t="s">
         <v>82</v>
       </c>
       <c r="F5">
-        <v>1627.0515559217042</v>
+        <v>1614.7716623691488</v>
       </c>
     </row>
     <row r="6">
@@ -2658,7 +2658,7 @@
         <v>83</v>
       </c>
       <c r="F6">
-        <v>-4435.0765464564156</v>
+        <v>-4435.2165052676528</v>
       </c>
     </row>
     <row r="9">
@@ -2671,13 +2671,13 @@
         <v>80</v>
       </c>
       <c r="B11">
-        <v>0.21544608431877854</v>
+        <v>0.21563075368666973</v>
       </c>
       <c r="E11" t="s">
         <v>82</v>
       </c>
       <c r="F11">
-        <v>4264.3364690622348</v>
+        <v>4274.13155279683</v>
       </c>
     </row>
     <row r="12">
@@ -2691,7 +2691,7 @@
         <v>83</v>
       </c>
       <c r="F12">
-        <v>-11484.865223256511</v>
+        <v>-11482.161900057554</v>
       </c>
     </row>
   </sheetData>
@@ -2812,103 +2812,103 @@
         <v>46</v>
       </c>
       <c r="B2" s="8">
-        <v>0.11398816262879816</v>
+        <v>0.11359133627106904</v>
       </c>
       <c r="C2">
-        <v>0.0013995941713900095</v>
+        <v>0.0013980971141358094</v>
       </c>
       <c r="D2">
-        <v>-0.00011841289748896116</v>
+        <v>-0.00011708985487617418</v>
       </c>
       <c r="E2">
-        <v>6.8085915090000327e-007</v>
+        <v>6.7227634231508149e-007</v>
       </c>
       <c r="F2">
-        <v>2.7939138722166476e-005</v>
+        <v>2.7520646571683896e-005</v>
       </c>
       <c r="G2">
-        <v>7.9436756533139143e-005</v>
+        <v>7.7652541774067931e-005</v>
       </c>
       <c r="H2">
-        <v>0.00058705975453535175</v>
+        <v>0.00058600628975402234</v>
       </c>
       <c r="I2">
-        <v>-0.0002313147972482199</v>
+        <v>-0.00023471322159609385</v>
       </c>
       <c r="J2">
-        <v>0.00015657981829582434</v>
+        <v>0.00015026841835324138</v>
       </c>
       <c r="K2">
-        <v>0.00024600259587507627</v>
+        <v>0.00024102666807401555</v>
       </c>
       <c r="L2">
-        <v>0.00014692807410498319</v>
+        <v>0.00014262183434820061</v>
       </c>
       <c r="M2">
-        <v>-0.00013129308599185984</v>
+        <v>-0.00013756333479140385</v>
       </c>
       <c r="N2">
-        <v>3.4078423331471977e-005</v>
+        <v>3.5043388232730045e-005</v>
       </c>
       <c r="O2">
-        <v>-7.2932807052994167e-006</v>
+        <v>-7.2658787175733938e-006</v>
       </c>
       <c r="P2">
-        <v>-1.0321650756574509e-005</v>
+        <v>-1.0313279095804779e-005</v>
       </c>
       <c r="Q2">
-        <v>-0.00033667236564179906</v>
+        <v>-0.00033837676189228064</v>
       </c>
       <c r="R2">
-        <v>-0.00013815147830413261</v>
+        <v>-0.00013864681664043526</v>
       </c>
       <c r="S2">
-        <v>-0.00019682073514282021</v>
+        <v>-0.00019891467061213149</v>
       </c>
       <c r="T2">
-        <v>-0.00028972702773992737</v>
+        <v>-0.00029029294062134659</v>
       </c>
       <c r="U2">
-        <v>-0.00013987655129243807</v>
+        <v>-0.000141661372201108</v>
       </c>
       <c r="V2">
-        <v>-0.00012975427562058098</v>
+        <v>-0.00013025375480035252</v>
       </c>
       <c r="W2">
-        <v>-0.00015085010404312037</v>
+        <v>-0.00015183116243841976</v>
       </c>
       <c r="X2">
-        <v>-0.00025463906167638782</v>
+        <v>-0.00025254984860159234</v>
       </c>
       <c r="Y2">
-        <v>7.5404030701307218e-005</v>
+        <v>7.3280843683331751e-005</v>
       </c>
       <c r="Z2">
-        <v>-0.00021796422342892853</v>
+        <v>-0.00021934855431962391</v>
       </c>
       <c r="AA2">
-        <v>-0.00019987672487490823</v>
+        <v>-0.00020098287771494732</v>
       </c>
       <c r="AB2">
-        <v>9.8041021552147103e-008</v>
+        <v>-5.8056569501719452e-008</v>
       </c>
       <c r="AC2">
-        <v>0.00024189102194164917</v>
+        <v>0.00024285737306896146</v>
       </c>
       <c r="AD2">
-        <v>0.00027084656310150411</v>
+        <v>0.00027299706461664664</v>
       </c>
       <c r="AE2">
-        <v>0.0001074943376380773</v>
+        <v>0.00010591189563416469</v>
       </c>
       <c r="AF2">
-        <v>-5.5779166842884718e-005</v>
+        <v>-5.7078248827969417e-005</v>
       </c>
       <c r="AG2">
-        <v>-3.1344449251640436e-005</v>
+        <v>-7.4029581693176244e-005</v>
       </c>
       <c r="AH2">
-        <v>0.0048086176920118413</v>
+        <v>0.0047689368203999048</v>
       </c>
     </row>
     <row r="3">
@@ -2916,103 +2916,103 @@
         <v>47</v>
       </c>
       <c r="B3" s="10">
-        <v>0.47733029081061273</v>
+        <v>0.47685450485681508</v>
       </c>
       <c r="C3">
-        <v>-0.00011841289748896116</v>
+        <v>-0.00011708985487617418</v>
       </c>
       <c r="D3">
-        <v>0.0015456985225087874</v>
+        <v>0.0015454974237025024</v>
       </c>
       <c r="E3">
-        <v>-1.173795303808575e-005</v>
+        <v>-1.1733981640349462e-005</v>
       </c>
       <c r="F3">
-        <v>-6.8939065299958107e-005</v>
+        <v>-6.9080064366133093e-005</v>
       </c>
       <c r="G3">
-        <v>-7.940275696823474e-005</v>
+        <v>-8.2408804197306798e-005</v>
       </c>
       <c r="H3">
-        <v>-0.00051088751500594567</v>
+        <v>-0.0005120221892076721</v>
       </c>
       <c r="I3">
-        <v>0.00012083204544951522</v>
+        <v>0.00011434738022537711</v>
       </c>
       <c r="J3">
-        <v>-9.0718268179490599e-005</v>
+        <v>-9.6031873718242181e-005</v>
       </c>
       <c r="K3">
-        <v>-6.6132634393574669e-005</v>
+        <v>-6.8453571502818326e-005</v>
       </c>
       <c r="L3">
-        <v>-0.00016163054537035739</v>
+        <v>-0.00016461808802113904</v>
       </c>
       <c r="M3">
-        <v>-7.4171144290684915e-005</v>
+        <v>-7.8838099770434447e-005</v>
       </c>
       <c r="N3">
-        <v>-0.00017713074277513584</v>
+        <v>-0.00017257373798703832</v>
       </c>
       <c r="O3">
-        <v>-8.9225907011246044e-007</v>
+        <v>-9.2692886320017311e-007</v>
       </c>
       <c r="P3">
-        <v>-4.5521562984527974e-007</v>
+        <v>-5.0761966319832248e-007</v>
       </c>
       <c r="Q3">
-        <v>8.0626244750043458e-005</v>
+        <v>8.2514034779570394e-005</v>
       </c>
       <c r="R3">
-        <v>5.3253814607887723e-005</v>
+        <v>5.6177203023033417e-005</v>
       </c>
       <c r="S3">
-        <v>-2.6939271765310038e-005</v>
+        <v>-2.4337907789519914e-005</v>
       </c>
       <c r="T3">
-        <v>5.0347652073151616e-006</v>
+        <v>6.8722039547261526e-006</v>
       </c>
       <c r="U3">
-        <v>6.1977822883550748e-005</v>
+        <v>6.2797708712373362e-005</v>
       </c>
       <c r="V3">
-        <v>6.1138501412604657e-005</v>
+        <v>6.3398944354010889e-005</v>
       </c>
       <c r="W3">
-        <v>3.3819013203876397e-005</v>
+        <v>3.6069679854242032e-005</v>
       </c>
       <c r="X3">
-        <v>2.1633846836399684e-005</v>
+        <v>2.3417570060156601e-005</v>
       </c>
       <c r="Y3">
-        <v>0.0001114796166682315</v>
+        <v>0.00011172316253667269</v>
       </c>
       <c r="Z3">
-        <v>4.2591480572090612e-005</v>
+        <v>4.4085336384846324e-005</v>
       </c>
       <c r="AA3">
-        <v>0.00017563297027386321</v>
+        <v>0.00017616197016771806</v>
       </c>
       <c r="AB3">
-        <v>-2.4787148813200225e-005</v>
+        <v>-2.5078399585291497e-005</v>
       </c>
       <c r="AC3">
-        <v>-7.1568605463563119e-005</v>
+        <v>-7.0956729907799623e-005</v>
       </c>
       <c r="AD3">
-        <v>4.9093640712729019e-006</v>
+        <v>6.8849653725101996e-006</v>
       </c>
       <c r="AE3">
-        <v>5.7976202840374219e-005</v>
+        <v>5.9172976478023137e-005</v>
       </c>
       <c r="AF3">
-        <v>0.00014072943821787781</v>
+        <v>0.00014136081967768693</v>
       </c>
       <c r="AG3">
-        <v>-0.00020998648002043367</v>
+        <v>-0.00012849749576103117</v>
       </c>
       <c r="AH3">
-        <v>-0.049491925000990214</v>
+        <v>-0.04948307015474266</v>
       </c>
     </row>
     <row r="4">
@@ -3020,103 +3020,103 @@
         <v>48</v>
       </c>
       <c r="B4" s="12">
-        <v>-0.0032139331039226196</v>
+        <v>-0.0032098437168196032</v>
       </c>
       <c r="C4">
-        <v>6.8085915090000327e-007</v>
+        <v>6.7227634231508149e-007</v>
       </c>
       <c r="D4">
-        <v>-1.173795303808575e-005</v>
+        <v>-1.1733981640349462e-005</v>
       </c>
       <c r="E4">
-        <v>9.0274799669534127e-008</v>
+        <v>9.0222396874744007e-008</v>
       </c>
       <c r="F4">
-        <v>4.646950401773888e-007</v>
+        <v>4.6636234174614282e-007</v>
       </c>
       <c r="G4">
-        <v>3.8160559334895824e-007</v>
+        <v>4.0547621789136092e-007</v>
       </c>
       <c r="H4">
-        <v>2.5673054120193959e-006</v>
+        <v>2.5784924967561606e-006</v>
       </c>
       <c r="I4">
-        <v>-8.480228523649277e-007</v>
+        <v>-8.0300923741739595e-007</v>
       </c>
       <c r="J4">
-        <v>3.7562880077246157e-007</v>
+        <v>4.1757203369746865e-007</v>
       </c>
       <c r="K4">
-        <v>4.1068181257465524e-007</v>
+        <v>4.2759812718041698e-007</v>
       </c>
       <c r="L4">
-        <v>1.1903757779224466e-006</v>
+        <v>1.2147503127165043e-006</v>
       </c>
       <c r="M4">
-        <v>5.4232890134215853e-007</v>
+        <v>5.7766673217541503e-007</v>
       </c>
       <c r="N4">
-        <v>1.4545375773057463e-006</v>
+        <v>1.4165566679502691e-006</v>
       </c>
       <c r="O4">
-        <v>9.5085277026373754e-009</v>
+        <v>9.6852229397344118e-009</v>
       </c>
       <c r="P4">
-        <v>-1.4515694310234655e-009</v>
+        <v>-1.2020460589674638e-009</v>
       </c>
       <c r="Q4">
-        <v>-4.7266436101894849e-007</v>
+        <v>-4.7948963595342538e-007</v>
       </c>
       <c r="R4">
-        <v>-3.5964707519903379e-007</v>
+        <v>-3.7455239923793113e-007</v>
       </c>
       <c r="S4">
-        <v>2.5932142245787572e-007</v>
+        <v>2.4517226698711502e-007</v>
       </c>
       <c r="T4">
-        <v>-3.8479150679286223e-008</v>
+        <v>-4.6240659276272373e-008</v>
       </c>
       <c r="U4">
-        <v>-4.3843596146809604e-007</v>
+        <v>-4.3868277338019054e-007</v>
       </c>
       <c r="V4">
-        <v>-3.4078693235601622e-007</v>
+        <v>-3.5541964169076004e-007</v>
       </c>
       <c r="W4">
-        <v>-2.1733689781517512e-007</v>
+        <v>-2.2754702857447962e-007</v>
       </c>
       <c r="X4">
-        <v>-2.6021175711219867e-007</v>
+        <v>-2.7358592908319505e-007</v>
       </c>
       <c r="Y4">
-        <v>-9.0396311968051293e-007</v>
+        <v>-9.051234141669532e-007</v>
       </c>
       <c r="Z4">
-        <v>-2.6456053478561645e-007</v>
+        <v>-2.7087084724034395e-007</v>
       </c>
       <c r="AA4">
-        <v>-1.4933504080459842e-006</v>
+        <v>-1.4911994023196376e-006</v>
       </c>
       <c r="AB4">
-        <v>1.5422978519739519e-007</v>
+        <v>1.5673365123438239e-007</v>
       </c>
       <c r="AC4">
-        <v>4.6362348524869867e-007</v>
+        <v>4.582745965067079e-007</v>
       </c>
       <c r="AD4">
-        <v>-1.0890154332727756e-007</v>
+        <v>-1.2202591966686603e-007</v>
       </c>
       <c r="AE4">
-        <v>-3.8182573147390111e-007</v>
+        <v>-3.8744391651259337e-007</v>
       </c>
       <c r="AF4">
-        <v>-9.9428078608149e-007</v>
+        <v>-9.9650222027005244e-007</v>
       </c>
       <c r="AG4">
-        <v>1.0475677959670686e-006</v>
+        <v>7.1453513400016207e-007</v>
       </c>
       <c r="AH4">
-        <v>0.00037280735200578998</v>
+        <v>0.00037267539835023793</v>
       </c>
     </row>
     <row r="5">
@@ -3124,103 +3124,103 @@
         <v>49</v>
       </c>
       <c r="B5" s="14">
-        <v>-0.071033340883348908</v>
+        <v>-0.07110354557523127</v>
       </c>
       <c r="C5">
-        <v>2.7939138722166476e-005</v>
+        <v>2.7520646571683896e-005</v>
       </c>
       <c r="D5">
-        <v>-6.8939065299958107e-005</v>
+        <v>-6.9080064366133093e-005</v>
       </c>
       <c r="E5">
-        <v>4.646950401773888e-007</v>
+        <v>4.6636234174614282e-007</v>
       </c>
       <c r="F5">
-        <v>0.0020645313104742124</v>
+        <v>0.00206506079692946</v>
       </c>
       <c r="G5">
-        <v>0.0015655300658148246</v>
+        <v>0.0015646099856003882</v>
       </c>
       <c r="H5">
-        <v>0.00014213459185177186</v>
+        <v>0.00014033092564500507</v>
       </c>
       <c r="I5">
-        <v>9.1629673528290933e-005</v>
+        <v>9.2671100855754813e-005</v>
       </c>
       <c r="J5">
-        <v>0.00012444404743517946</v>
+        <v>0.00012232060071717547</v>
       </c>
       <c r="K5">
-        <v>9.7123431816085979e-005</v>
+        <v>9.7198279153979853e-005</v>
       </c>
       <c r="L5">
-        <v>2.8563090011940051e-005</v>
+        <v>2.9035056073694396e-005</v>
       </c>
       <c r="M5">
-        <v>0.0004495253762899457</v>
+        <v>0.00044829410164114289</v>
       </c>
       <c r="N5">
-        <v>-0.00014565881974005576</v>
+        <v>-0.00014605157064270856</v>
       </c>
       <c r="O5">
-        <v>1.6867214052650899e-006</v>
+        <v>1.7112346973505279e-006</v>
       </c>
       <c r="P5">
-        <v>6.450281924140358e-007</v>
+        <v>6.7814932941932633e-007</v>
       </c>
       <c r="Q5">
-        <v>-0.00056132383378123944</v>
+        <v>-0.00056411637463037482</v>
       </c>
       <c r="R5">
-        <v>-0.00039147292005795432</v>
+        <v>-0.00039449510301402989</v>
       </c>
       <c r="S5">
-        <v>-0.00010730017587097989</v>
+        <v>-0.00011075681161146409</v>
       </c>
       <c r="T5">
-        <v>-0.00039814813205239064</v>
+        <v>-0.00040163735043565108</v>
       </c>
       <c r="U5">
-        <v>-0.00044539496547781174</v>
+        <v>-0.00044478516267592623</v>
       </c>
       <c r="V5">
-        <v>-0.00048067833742883813</v>
+        <v>-0.00048211654364706502</v>
       </c>
       <c r="W5">
-        <v>-0.00043532786456060768</v>
+        <v>-0.00043693200062624126</v>
       </c>
       <c r="X5">
-        <v>-0.00042957545151653604</v>
+        <v>-0.00043451709471479237</v>
       </c>
       <c r="Y5">
-        <v>-0.00032466075462096874</v>
+        <v>-0.00032673469439285281</v>
       </c>
       <c r="Z5">
-        <v>-0.00028788580349837568</v>
+        <v>-0.00029089887584337785</v>
       </c>
       <c r="AA5">
-        <v>-0.00032890940680191426</v>
+        <v>-0.00033179732867242976</v>
       </c>
       <c r="AB5">
-        <v>7.9975613732996471e-006</v>
+        <v>7.9745841928764217e-006</v>
       </c>
       <c r="AC5">
-        <v>4.2897866707225431e-005</v>
+        <v>4.4072456063990468e-005</v>
       </c>
       <c r="AD5">
-        <v>0.00013206656487358076</v>
+        <v>0.00013061181470744079</v>
       </c>
       <c r="AE5">
-        <v>-1.2124895440969658e-005</v>
+        <v>-1.4706941598042718e-005</v>
       </c>
       <c r="AF5">
-        <v>-0.00015196470410332782</v>
+        <v>-0.00015468192018798011</v>
       </c>
       <c r="AG5">
-        <v>-7.9596089003693984e-007</v>
+        <v>-4.2782723654834865e-005</v>
       </c>
       <c r="AH5">
-        <v>0.00091564648663443749</v>
+        <v>0.00092041665261907908</v>
       </c>
     </row>
     <row r="6">
@@ -3228,103 +3228,103 @@
         <v>50</v>
       </c>
       <c r="B6" s="16">
-        <v>-0.080696092392633006</v>
+        <v>-0.080912583748274591</v>
       </c>
       <c r="C6">
-        <v>7.9436756533139143e-005</v>
+        <v>7.7652541774067931e-005</v>
       </c>
       <c r="D6">
-        <v>-7.940275696823474e-005</v>
+        <v>-8.2408804197306798e-005</v>
       </c>
       <c r="E6">
-        <v>3.8160559334895824e-007</v>
+        <v>4.0547621789136092e-007</v>
       </c>
       <c r="F6">
-        <v>0.0015655300658148246</v>
+        <v>0.0015646099856003882</v>
       </c>
       <c r="G6">
-        <v>0.0027831918467699627</v>
+        <v>0.0027856205691699758</v>
       </c>
       <c r="H6">
-        <v>0.00042007557609929707</v>
+        <v>0.00042239431152880317</v>
       </c>
       <c r="I6">
-        <v>0.00015086425026770089</v>
+        <v>0.00016025694265519471</v>
       </c>
       <c r="J6">
-        <v>0.00048902505301028358</v>
+        <v>0.00049363966413035708</v>
       </c>
       <c r="K6">
-        <v>0.00045390302797035419</v>
+        <v>0.00046096984160473695</v>
       </c>
       <c r="L6">
-        <v>0.00059380136124633908</v>
+        <v>0.0005967131010088016</v>
       </c>
       <c r="M6">
-        <v>0.001043175776625194</v>
+        <v>0.0010511983857857084</v>
       </c>
       <c r="N6">
-        <v>-0.00021019617977505059</v>
+        <v>-0.00020929294131189407</v>
       </c>
       <c r="O6">
-        <v>-1.3441884041312004e-006</v>
+        <v>-1.278184171283687e-006</v>
       </c>
       <c r="P6">
-        <v>-1.0545664454212786e-006</v>
+        <v>-8.985522751580887e-007</v>
       </c>
       <c r="Q6">
-        <v>-0.00082101692628192057</v>
+        <v>-0.0008215556922441463</v>
       </c>
       <c r="R6">
-        <v>-0.00064362907747527549</v>
+        <v>-0.00064442408079817685</v>
       </c>
       <c r="S6">
-        <v>-0.00039829912652690057</v>
+        <v>-0.00039601170193055701</v>
       </c>
       <c r="T6">
-        <v>-0.00066667201812700965</v>
+        <v>-0.00066267907006707487</v>
       </c>
       <c r="U6">
-        <v>-0.00082074609173736295</v>
+        <v>-0.00081857691810634258</v>
       </c>
       <c r="V6">
-        <v>-0.0007231846081631471</v>
+        <v>-0.00071504885827797357</v>
       </c>
       <c r="W6">
-        <v>-0.00071067604861538693</v>
+        <v>-0.00071006264526796159</v>
       </c>
       <c r="X6">
-        <v>-0.00054462181463674653</v>
+        <v>-0.00053820320806017479</v>
       </c>
       <c r="Y6">
-        <v>-0.00068516740149460241</v>
+        <v>-0.00067557297336468696</v>
       </c>
       <c r="Z6">
-        <v>-0.00050655732563677767</v>
+        <v>-0.00050042910530610774</v>
       </c>
       <c r="AA6">
-        <v>-0.00083735958328595337</v>
+        <v>-0.00083055903265061228</v>
       </c>
       <c r="AB6">
-        <v>3.7553873130868101e-005</v>
+        <v>3.7642719560101116e-005</v>
       </c>
       <c r="AC6">
-        <v>0.00019126606738275066</v>
+        <v>0.00018890675867596103</v>
       </c>
       <c r="AD6">
-        <v>0.00013199117929681522</v>
+        <v>0.00012871115886852369</v>
       </c>
       <c r="AE6">
-        <v>-0.00023644010026557805</v>
+        <v>-0.00023683818894313236</v>
       </c>
       <c r="AF6">
-        <v>-0.00017348664564065881</v>
+        <v>-0.00016619995782553298</v>
       </c>
       <c r="AG6">
-        <v>0.00068130442701288922</v>
+        <v>0.00046921443000293205</v>
       </c>
       <c r="AH6">
-        <v>0.0012549964776884474</v>
+        <v>0.0013234439236597081</v>
       </c>
     </row>
     <row r="7">
@@ -3332,103 +3332,103 @@
         <v>51</v>
       </c>
       <c r="B7" s="18">
-        <v>0.67652518971931142</v>
+        <v>0.67660080479683671</v>
       </c>
       <c r="C7">
-        <v>0.00058705975453535175</v>
+        <v>0.00058600628975402234</v>
       </c>
       <c r="D7">
-        <v>-0.00051088751500594567</v>
+        <v>-0.0005120221892076721</v>
       </c>
       <c r="E7">
-        <v>2.5673054120193959e-006</v>
+        <v>2.5784924967561606e-006</v>
       </c>
       <c r="F7">
-        <v>0.00014213459185177186</v>
+        <v>0.00014033092564500507</v>
       </c>
       <c r="G7">
-        <v>0.00042007557609929707</v>
+        <v>0.00042239431152880317</v>
       </c>
       <c r="H7">
-        <v>0.0032716666587344597</v>
+        <v>0.0032704404917310932</v>
       </c>
       <c r="I7">
-        <v>0.00040316708415595549</v>
+        <v>0.00041508081218223766</v>
       </c>
       <c r="J7">
-        <v>0.00035447854394970708</v>
+        <v>0.00036419790291953007</v>
       </c>
       <c r="K7">
-        <v>8.5601834920474076e-005</v>
+        <v>9.518550761599758e-005</v>
       </c>
       <c r="L7">
-        <v>0.000239734432762618</v>
+        <v>0.0002480274280046609</v>
       </c>
       <c r="M7">
-        <v>0.00027273432255682604</v>
+        <v>0.00028419916515599365</v>
       </c>
       <c r="N7">
-        <v>-8.1446573631028737e-005</v>
+        <v>-8.0477117798164691e-005</v>
       </c>
       <c r="O7">
-        <v>-3.535584175017146e-006</v>
+        <v>-3.4218534843710983e-006</v>
       </c>
       <c r="P7">
-        <v>-5.5945102044640154e-006</v>
+        <v>-5.4648659865589639e-006</v>
       </c>
       <c r="Q7">
-        <v>-0.00015646992576572732</v>
+        <v>-0.00015477071053507374</v>
       </c>
       <c r="R7">
-        <v>-7.6198062304463215e-005</v>
+        <v>-7.6032979348026469e-005</v>
       </c>
       <c r="S7">
-        <v>-6.2104842858892381e-005</v>
+        <v>-5.9203399892025603e-005</v>
       </c>
       <c r="T7">
-        <v>2.1552420097017272e-005</v>
+        <v>2.5500080729325483e-005</v>
       </c>
       <c r="U7">
-        <v>6.1568832592699338e-005</v>
+        <v>6.2007720975197286e-005</v>
       </c>
       <c r="V7">
-        <v>-0.00010587455719134574</v>
+        <v>-9.9769081016158612e-005</v>
       </c>
       <c r="W7">
-        <v>-0.00025393836667947107</v>
+        <v>-0.00025362866905109371</v>
       </c>
       <c r="X7">
-        <v>-7.0309365027538748e-005</v>
+        <v>-6.2085647725066209e-005</v>
       </c>
       <c r="Y7">
-        <v>-0.0001233331028386974</v>
+        <v>-0.00011462089497807533</v>
       </c>
       <c r="Z7">
-        <v>-0.00012523228519289824</v>
+        <v>-0.00011952802026654087</v>
       </c>
       <c r="AA7">
-        <v>-8.5001769719806469e-005</v>
+        <v>-7.93694873565641e-005</v>
       </c>
       <c r="AB7">
-        <v>8.2228923339043136e-005</v>
+        <v>8.1943351384202562e-005</v>
       </c>
       <c r="AC7">
-        <v>0.0001219768268978863</v>
+        <v>0.0001221501864607003</v>
       </c>
       <c r="AD7">
-        <v>0.00013516010768858792</v>
+        <v>0.00013351884714512348</v>
       </c>
       <c r="AE7">
-        <v>-6.21703619920113e-005</v>
+        <v>-6.0357323272133487e-005</v>
       </c>
       <c r="AF7">
-        <v>-3.1305723117071999e-005</v>
+        <v>-2.4282177742245004e-005</v>
       </c>
       <c r="AG7">
-        <v>0.00062078379609775778</v>
+        <v>0.00044695214019631595</v>
       </c>
       <c r="AH7">
-        <v>0.018877120490660964</v>
+        <v>0.018881135012059978</v>
       </c>
     </row>
     <row r="8">
@@ -3436,103 +3436,103 @@
         <v>52</v>
       </c>
       <c r="B8" s="20">
-        <v>0.85673470135291319</v>
+        <v>0.85922786332623824</v>
       </c>
       <c r="C8">
-        <v>-0.0002313147972482199</v>
+        <v>-0.00023471322159609385</v>
       </c>
       <c r="D8">
-        <v>0.00012083204544951522</v>
+        <v>0.00011434738022537711</v>
       </c>
       <c r="E8">
-        <v>-8.480228523649277e-007</v>
+        <v>-8.0300923741739595e-007</v>
       </c>
       <c r="F8">
-        <v>9.1629673528290933e-005</v>
+        <v>9.2671100855754813e-005</v>
       </c>
       <c r="G8">
-        <v>0.00015086425026770089</v>
+        <v>0.00016025694265519471</v>
       </c>
       <c r="H8">
-        <v>0.00040316708415595549</v>
+        <v>0.00041508081218223766</v>
       </c>
       <c r="I8">
-        <v>0.0061187134268875926</v>
+        <v>0.0061188906741410009</v>
       </c>
       <c r="J8">
-        <v>0.0022466113337964414</v>
+        <v>0.0022474769629746969</v>
       </c>
       <c r="K8">
-        <v>0.0041344658701636837</v>
+        <v>0.0041244694778371635</v>
       </c>
       <c r="L8">
-        <v>0.0044008169817645049</v>
+        <v>0.0043939700493557362</v>
       </c>
       <c r="M8">
-        <v>0.0045164382834483978</v>
+        <v>0.0045133861793306557</v>
       </c>
       <c r="N8">
-        <v>-0.0014206363818308619</v>
+        <v>-0.0014257472969100128</v>
       </c>
       <c r="O8">
-        <v>1.8944434166787717e-005</v>
+        <v>1.9067385065363942e-005</v>
       </c>
       <c r="P8">
-        <v>1.4113373114515936e-005</v>
+        <v>1.4351202841288422e-005</v>
       </c>
       <c r="Q8">
-        <v>1.4483608160642536e-005</v>
+        <v>1.3852358689376773e-005</v>
       </c>
       <c r="R8">
-        <v>6.7056454873400031e-005</v>
+        <v>6.8955123347457133e-005</v>
       </c>
       <c r="S8">
-        <v>-1.2778129921261865e-005</v>
+        <v>-1.3979574404297899e-005</v>
       </c>
       <c r="T8">
-        <v>-8.2525619311895997e-005</v>
+        <v>-8.2800891487084735e-005</v>
       </c>
       <c r="U8">
-        <v>-0.0001624020976564132</v>
+        <v>-0.00015355436294518365</v>
       </c>
       <c r="V8">
-        <v>0.00013308551702902877</v>
+        <v>0.00014193966325015683</v>
       </c>
       <c r="W8">
-        <v>-2.0693796932810989e-006</v>
+        <v>1.3179819911249453e-006</v>
       </c>
       <c r="X8">
-        <v>-7.44891622407335e-006</v>
+        <v>-1.5912717474432167e-005</v>
       </c>
       <c r="Y8">
-        <v>-0.00031747070866658227</v>
+        <v>-0.00031639997418167476</v>
       </c>
       <c r="Z8">
-        <v>-1.4711588365243396e-005</v>
+        <v>-1.4007995097123534e-005</v>
       </c>
       <c r="AA8">
-        <v>-0.00012965240996178247</v>
+        <v>-0.00011363132741138045</v>
       </c>
       <c r="AB8">
-        <v>5.5224874918293561e-005</v>
+        <v>5.5522296960544603e-005</v>
       </c>
       <c r="AC8">
-        <v>-0.0005200261446622669</v>
+        <v>-0.00051970201999667915</v>
       </c>
       <c r="AD8">
-        <v>-0.00036028104304878774</v>
+        <v>-0.00036058967749348858</v>
       </c>
       <c r="AE8">
-        <v>-0.00035394575412383417</v>
+        <v>-0.00035877906580602213</v>
       </c>
       <c r="AF8">
-        <v>-0.00018755997337610748</v>
+        <v>-0.00017491402943353891</v>
       </c>
       <c r="AG8">
-        <v>7.6109867914079567e-005</v>
+        <v>0.00016006464235047892</v>
       </c>
       <c r="AH8">
-        <v>-0.011430772984092463</v>
+        <v>-0.011232066092847175</v>
       </c>
     </row>
     <row r="9">
@@ -3540,103 +3540,103 @@
         <v>53</v>
       </c>
       <c r="B9" s="22">
-        <v>0.25126465255839547</v>
+        <v>0.25360695828076513</v>
       </c>
       <c r="C9">
-        <v>0.00015657981829582434</v>
+        <v>0.00015026841835324138</v>
       </c>
       <c r="D9">
-        <v>-9.0718268179490599e-005</v>
+        <v>-9.6031873718242181e-005</v>
       </c>
       <c r="E9">
-        <v>3.7562880077246157e-007</v>
+        <v>4.1757203369746865e-007</v>
       </c>
       <c r="F9">
-        <v>0.00012444404743517946</v>
+        <v>0.00012232060071717547</v>
       </c>
       <c r="G9">
-        <v>0.00048902505301028358</v>
+        <v>0.00049363966413035708</v>
       </c>
       <c r="H9">
-        <v>0.00035447854394970708</v>
+        <v>0.00036419790291953007</v>
       </c>
       <c r="I9">
-        <v>0.0022466113337964414</v>
+        <v>0.0022474769629746969</v>
       </c>
       <c r="J9">
-        <v>0.0041968362756370815</v>
+        <v>0.0041872268207617412</v>
       </c>
       <c r="K9">
-        <v>0.003537709648125061</v>
+        <v>0.0035248170331339188</v>
       </c>
       <c r="L9">
-        <v>0.0036070371873968489</v>
+        <v>0.0035942949987693928</v>
       </c>
       <c r="M9">
-        <v>0.0036365844801449173</v>
+        <v>0.0036280502934296381</v>
       </c>
       <c r="N9">
-        <v>0.00028861295004688789</v>
+        <v>0.00029602044604634025</v>
       </c>
       <c r="O9">
-        <v>3.9160127678004289e-006</v>
+        <v>4.3416106806812574e-006</v>
       </c>
       <c r="P9">
-        <v>-8.4983725723963731e-007</v>
+        <v>-2.9899808424102921e-007</v>
       </c>
       <c r="Q9">
-        <v>-0.0002514795370388911</v>
+        <v>-0.00026631892315310125</v>
       </c>
       <c r="R9">
-        <v>-0.00022164717664375621</v>
+        <v>-0.00022818917779190452</v>
       </c>
       <c r="S9">
-        <v>-0.00014663070684256107</v>
+        <v>-0.00015884508767581476</v>
       </c>
       <c r="T9">
-        <v>-0.00015202392624410327</v>
+        <v>-0.00016409149728204085</v>
       </c>
       <c r="U9">
-        <v>-0.00024987601836300665</v>
+        <v>-0.00024183381064393392</v>
       </c>
       <c r="V9">
-        <v>-0.00019255884077203284</v>
+        <v>-0.00018418315726145807</v>
       </c>
       <c r="W9">
-        <v>-0.00027631505202345354</v>
+        <v>-0.00028044836944169206</v>
       </c>
       <c r="X9">
-        <v>2.8054524930847392e-005</v>
+        <v>4.4482454219400358e-006</v>
       </c>
       <c r="Y9">
-        <v>-0.0001245852545716979</v>
+        <v>-0.00012842965534823358</v>
       </c>
       <c r="Z9">
-        <v>-2.3589680206153197e-005</v>
+        <v>-3.1930394449418116e-005</v>
       </c>
       <c r="AA9">
-        <v>-1.803320425775674e-005</v>
+        <v>-3.9585097758878217e-006</v>
       </c>
       <c r="AB9">
-        <v>4.2409859864229088e-005</v>
+        <v>4.0758003315093919e-005</v>
       </c>
       <c r="AC9">
-        <v>-0.0002919541515715404</v>
+        <v>-0.00028368883087819663</v>
       </c>
       <c r="AD9">
-        <v>-3.3614499220319387e-005</v>
+        <v>-2.3910110003504156e-005</v>
       </c>
       <c r="AE9">
-        <v>0.00026899140026040327</v>
+        <v>0.00024885137786572527</v>
       </c>
       <c r="AF9">
-        <v>-1.6928540464836769e-005</v>
+        <v>-1.6513062395338146e-006</v>
       </c>
       <c r="AG9">
-        <v>0.00057241653331254502</v>
+        <v>0.00042103162078545764</v>
       </c>
       <c r="AH9">
-        <v>-0.00054365585265792548</v>
+        <v>-0.00038985163851377579</v>
       </c>
     </row>
     <row r="10">
@@ -3644,103 +3644,103 @@
         <v>54</v>
       </c>
       <c r="B10" s="24">
-        <v>0.25725152916594229</v>
+        <v>0.25933682789177659</v>
       </c>
       <c r="C10">
-        <v>0.00024600259587507627</v>
+        <v>0.00024102666807401555</v>
       </c>
       <c r="D10">
-        <v>-6.6132634393574669e-005</v>
+        <v>-6.8453571502818326e-005</v>
       </c>
       <c r="E10">
-        <v>4.1068181257465524e-007</v>
+        <v>4.2759812718041698e-007</v>
       </c>
       <c r="F10">
-        <v>9.7123431816085979e-005</v>
+        <v>9.7198279153979853e-005</v>
       </c>
       <c r="G10">
-        <v>0.00045390302797035419</v>
+        <v>0.00046096984160473695</v>
       </c>
       <c r="H10">
-        <v>8.5601834920474076e-005</v>
+        <v>9.518550761599758e-005</v>
       </c>
       <c r="I10">
-        <v>0.0041344658701636837</v>
+        <v>0.0041244694778371635</v>
       </c>
       <c r="J10">
-        <v>0.003537709648125061</v>
+        <v>0.0035248170331339188</v>
       </c>
       <c r="K10">
-        <v>0.0073188117363681797</v>
+        <v>0.0072973578615963342</v>
       </c>
       <c r="L10">
-        <v>0.0058132379230553047</v>
+        <v>0.0057956560349480112</v>
       </c>
       <c r="M10">
-        <v>0.0057923029449808887</v>
+        <v>0.0057774999933628366</v>
       </c>
       <c r="N10">
-        <v>0.00080107072848364057</v>
+        <v>0.00080213848942298628</v>
       </c>
       <c r="O10">
-        <v>4.6576888942279705e-006</v>
+        <v>4.961215945070755e-006</v>
       </c>
       <c r="P10">
-        <v>-4.0359688674558289e-006</v>
+        <v>-3.71386576004091e-006</v>
       </c>
       <c r="Q10">
-        <v>-0.00069703085980754142</v>
+        <v>-0.00069766694092154413</v>
       </c>
       <c r="R10">
-        <v>-0.00053530016660927548</v>
+        <v>-0.00052922548150550217</v>
       </c>
       <c r="S10">
-        <v>-0.00045765400232939204</v>
+        <v>-0.00045772158974038187</v>
       </c>
       <c r="T10">
-        <v>-0.00048976227999481241</v>
+        <v>-0.00048897081139790939</v>
       </c>
       <c r="U10">
-        <v>-0.00046954554131387982</v>
+        <v>-0.00045284673996856344</v>
       </c>
       <c r="V10">
-        <v>-0.00033688736490201747</v>
+        <v>-0.00032259302998460457</v>
       </c>
       <c r="W10">
-        <v>-0.0004413096422865515</v>
+        <v>-0.00043397716409476577</v>
       </c>
       <c r="X10">
-        <v>-0.00040198739122799393</v>
+        <v>-0.0004197649277422309</v>
       </c>
       <c r="Y10">
-        <v>3.8409589001284043e-005</v>
+        <v>3.7874952347481282e-005</v>
       </c>
       <c r="Z10">
-        <v>-0.00043423806303172544</v>
+        <v>-0.00043004364255322348</v>
       </c>
       <c r="AA10">
-        <v>-0.00027571195765492985</v>
+        <v>-0.00025166599501439974</v>
       </c>
       <c r="AB10">
-        <v>5.3716926110596392e-005</v>
+        <v>5.2598959074161194e-005</v>
       </c>
       <c r="AC10">
-        <v>-0.00020216445427437244</v>
+        <v>-0.00019475414661159133</v>
       </c>
       <c r="AD10">
-        <v>0.00010160611257649843</v>
+        <v>0.00010780576194735336</v>
       </c>
       <c r="AE10">
-        <v>0.00030052083731404132</v>
+        <v>0.00028884806339839306</v>
       </c>
       <c r="AF10">
-        <v>-0.00025202629325109596</v>
+        <v>-0.00023207430019676054</v>
       </c>
       <c r="AG10">
-        <v>-5.5478406149225335e-005</v>
+        <v>0.00017494730059802667</v>
       </c>
       <c r="AH10">
-        <v>-0.0041882289970275807</v>
+        <v>-0.0041181309685079104</v>
       </c>
     </row>
     <row r="11">
@@ -3748,103 +3748,103 @@
         <v>55</v>
       </c>
       <c r="B11" s="26">
-        <v>0.31976140717956114</v>
+        <v>0.32106784977555297</v>
       </c>
       <c r="C11">
-        <v>0.00014692807410498319</v>
+        <v>0.00014262183434820061</v>
       </c>
       <c r="D11">
-        <v>-0.00016163054537035739</v>
+        <v>-0.00016461808802113904</v>
       </c>
       <c r="E11">
-        <v>1.1903757779224466e-006</v>
+        <v>1.2147503127165043e-006</v>
       </c>
       <c r="F11">
-        <v>2.8563090011940051e-005</v>
+        <v>2.9035056073694396e-005</v>
       </c>
       <c r="G11">
-        <v>0.00059380136124633908</v>
+        <v>0.0005967131010088016</v>
       </c>
       <c r="H11">
-        <v>0.000239734432762618</v>
+        <v>0.0002480274280046609</v>
       </c>
       <c r="I11">
-        <v>0.0044008169817645049</v>
+        <v>0.0043939700493557362</v>
       </c>
       <c r="J11">
-        <v>0.0036070371873968489</v>
+        <v>0.0035942949987693928</v>
       </c>
       <c r="K11">
-        <v>0.0058132379230553047</v>
+        <v>0.0057956560349480112</v>
       </c>
       <c r="L11">
-        <v>0.0075311893618352724</v>
+        <v>0.0075153393941294316</v>
       </c>
       <c r="M11">
-        <v>0.0060402657169344159</v>
+        <v>0.0060259125902255399</v>
       </c>
       <c r="N11">
-        <v>0.0007118093802102772</v>
+        <v>0.00071847931517813235</v>
       </c>
       <c r="O11">
-        <v>3.9373928810888348e-006</v>
+        <v>4.2298826562230091e-006</v>
       </c>
       <c r="P11">
-        <v>-4.2900373983068876e-006</v>
+        <v>-3.8646342852340733e-006</v>
       </c>
       <c r="Q11">
-        <v>-0.00037305986983865837</v>
+        <v>-0.00038707347593605569</v>
       </c>
       <c r="R11">
-        <v>-0.00051416498036434537</v>
+        <v>-0.00051995248552363406</v>
       </c>
       <c r="S11">
-        <v>-0.00033038069968357509</v>
+        <v>-0.00034161533642113984</v>
       </c>
       <c r="T11">
-        <v>-0.00043571983349076316</v>
+        <v>-0.00044703190805250328</v>
       </c>
       <c r="U11">
-        <v>-0.00054820626421405371</v>
+        <v>-0.00054161931480620445</v>
       </c>
       <c r="V11">
-        <v>-0.00032614701593641424</v>
+        <v>-0.00032143011198852559</v>
       </c>
       <c r="W11">
-        <v>-0.00040308000617852004</v>
+        <v>-0.0004069918113282201</v>
       </c>
       <c r="X11">
-        <v>-0.00037290920588131551</v>
+        <v>-0.00039548996051627953</v>
       </c>
       <c r="Y11">
-        <v>-0.00040333258149122253</v>
+        <v>-0.00040824797919790032</v>
       </c>
       <c r="Z11">
-        <v>-0.00048595991328097016</v>
+        <v>-0.00049720377297905348</v>
       </c>
       <c r="AA11">
-        <v>-0.00025767891848559391</v>
+        <v>-0.00024747012169366346</v>
       </c>
       <c r="AB11">
-        <v>5.350073064821882e-005</v>
+        <v>5.2071056516731572e-005</v>
       </c>
       <c r="AC11">
-        <v>-0.00013208860999716615</v>
+        <v>-0.00012350492459081838</v>
       </c>
       <c r="AD11">
-        <v>-0.00012329542433654392</v>
+        <v>-0.00011351503032112651</v>
       </c>
       <c r="AE11">
-        <v>0.00032305703269878429</v>
+        <v>0.00030433484428222992</v>
       </c>
       <c r="AF11">
-        <v>-0.00024068436912990212</v>
+        <v>-0.00023084441795196602</v>
       </c>
       <c r="AG11">
-        <v>0.00018481443389585083</v>
+        <v>9.3763179742039141e-005</v>
       </c>
       <c r="AH11">
-        <v>-0.0014754839421946475</v>
+        <v>-0.0013814950383732511</v>
       </c>
     </row>
     <row r="12">
@@ -3852,103 +3852,103 @@
         <v>56</v>
       </c>
       <c r="B12" s="28">
-        <v>0.47574780058168054</v>
+        <v>0.47775971899717706</v>
       </c>
       <c r="C12">
-        <v>-0.00013129308599185984</v>
+        <v>-0.00013756333479140385</v>
       </c>
       <c r="D12">
-        <v>-7.4171144290684915e-005</v>
+        <v>-7.8838099770434447e-005</v>
       </c>
       <c r="E12">
-        <v>5.4232890134215853e-007</v>
+        <v>5.7766673217541503e-007</v>
       </c>
       <c r="F12">
-        <v>0.0004495253762899457</v>
+        <v>0.00044829410164114289</v>
       </c>
       <c r="G12">
-        <v>0.001043175776625194</v>
+        <v>0.0010511983857857084</v>
       </c>
       <c r="H12">
-        <v>0.00027273432255682604</v>
+        <v>0.00028419916515599365</v>
       </c>
       <c r="I12">
-        <v>0.0045164382834483978</v>
+        <v>0.0045133861793306557</v>
       </c>
       <c r="J12">
-        <v>0.0036365844801449173</v>
+        <v>0.0036280502934296381</v>
       </c>
       <c r="K12">
-        <v>0.0057923029449808887</v>
+        <v>0.0057774999933628366</v>
       </c>
       <c r="L12">
-        <v>0.0060402657169344159</v>
+        <v>0.0060259125902255399</v>
       </c>
       <c r="M12">
-        <v>0.0077115190021368992</v>
+        <v>0.0077064831144666029</v>
       </c>
       <c r="N12">
-        <v>0.00048809642884970156</v>
+        <v>0.00049201445242904609</v>
       </c>
       <c r="O12">
-        <v>-1.4027964585980434e-006</v>
+        <v>-1.1067651399144178e-006</v>
       </c>
       <c r="P12">
-        <v>-5.0249566190802026e-006</v>
+        <v>-4.5823041440376133e-006</v>
       </c>
       <c r="Q12">
-        <v>-3.8538516513184941e-005</v>
+        <v>-3.7776323812257172e-005</v>
       </c>
       <c r="R12">
-        <v>0.00015268892715170805</v>
+        <v>0.00015971788639749986</v>
       </c>
       <c r="S12">
-        <v>9.4930633120171755e-005</v>
+        <v>9.7566005558092066e-005</v>
       </c>
       <c r="T12">
-        <v>9.1523947926031978e-005</v>
+        <v>9.6489034177757796e-005</v>
       </c>
       <c r="U12">
-        <v>-0.00020890049935722932</v>
+        <v>-0.000188986987902472</v>
       </c>
       <c r="V12">
-        <v>-6.8847114739387615e-006</v>
+        <v>1.4358102278788209e-005</v>
       </c>
       <c r="W12">
-        <v>-8.8312276122099256e-005</v>
+        <v>-7.9815087748710649e-005</v>
       </c>
       <c r="X12">
-        <v>0.00012809697518807077</v>
+        <v>0.00011952289207832869</v>
       </c>
       <c r="Y12">
-        <v>0.00020252561573825406</v>
+        <v>0.00020985713066806614</v>
       </c>
       <c r="Z12">
-        <v>8.4960223050752591e-005</v>
+        <v>9.2799313031397858e-005</v>
       </c>
       <c r="AA12">
-        <v>0.00015200126383950376</v>
+        <v>0.00018008311292053592</v>
       </c>
       <c r="AB12">
-        <v>4.7193339386871017e-005</v>
+        <v>4.6065579995174311e-005</v>
       </c>
       <c r="AC12">
-        <v>-0.00026729841128667091</v>
+        <v>-0.00026226505850798743</v>
       </c>
       <c r="AD12">
-        <v>-5.5506595811832468e-005</v>
+        <v>-5.018473570997129e-005</v>
       </c>
       <c r="AE12">
-        <v>0.00035579202565603129</v>
+        <v>0.00034515252592353524</v>
       </c>
       <c r="AF12">
-        <v>0.00019750289991326674</v>
+        <v>0.00022279463100959105</v>
       </c>
       <c r="AG12">
-        <v>0.00044584606809503066</v>
+        <v>0.00049067050124961095</v>
       </c>
       <c r="AH12">
-        <v>-0.0046957001947725147</v>
+        <v>-0.004569063846149338</v>
       </c>
     </row>
     <row r="13">
@@ -3956,103 +3956,103 @@
         <v>57</v>
       </c>
       <c r="B13" s="30">
-        <v>-0.13174731939998388</v>
+        <v>-0.13066862089239675</v>
       </c>
       <c r="C13">
-        <v>3.4078423331471977e-005</v>
+        <v>3.5043388232730045e-005</v>
       </c>
       <c r="D13">
-        <v>-0.00017713074277513584</v>
+        <v>-0.00017257373798703832</v>
       </c>
       <c r="E13">
-        <v>1.4545375773057463e-006</v>
+        <v>1.4165566679502691e-006</v>
       </c>
       <c r="F13">
-        <v>-0.00014565881974005576</v>
+        <v>-0.00014605157064270856</v>
       </c>
       <c r="G13">
-        <v>-0.00021019617977505059</v>
+        <v>-0.00020929294131189407</v>
       </c>
       <c r="H13">
-        <v>-8.1446573631028737e-005</v>
+        <v>-8.0477117798164691e-005</v>
       </c>
       <c r="I13">
-        <v>-0.0014206363818308619</v>
+        <v>-0.0014257472969100128</v>
       </c>
       <c r="J13">
-        <v>0.00028861295004688789</v>
+        <v>0.00029602044604634025</v>
       </c>
       <c r="K13">
-        <v>0.00080107072848364057</v>
+        <v>0.00080213848942298628</v>
       </c>
       <c r="L13">
-        <v>0.0007118093802102772</v>
+        <v>0.00071847931517813235</v>
       </c>
       <c r="M13">
-        <v>0.00048809642884970156</v>
+        <v>0.00049201445242904609</v>
       </c>
       <c r="N13">
-        <v>0.004094252580168373</v>
+        <v>0.0040910579638959886</v>
       </c>
       <c r="O13">
-        <v>4.0818746748357006e-005</v>
+        <v>4.0812383343240115e-005</v>
       </c>
       <c r="P13">
-        <v>1.8973103170561286e-005</v>
+        <v>1.885137551298281e-005</v>
       </c>
       <c r="Q13">
-        <v>-0.0005246849932078663</v>
+        <v>-0.0005121126631316762</v>
       </c>
       <c r="R13">
-        <v>-0.00068760052753589248</v>
+        <v>-0.00067175411533876457</v>
       </c>
       <c r="S13">
-        <v>-0.00053656045712385228</v>
+        <v>-0.00052669154411597832</v>
       </c>
       <c r="T13">
-        <v>-0.00072871185539753064</v>
+        <v>-0.00071912123676505296</v>
       </c>
       <c r="U13">
-        <v>-0.00060861480083156789</v>
+        <v>-0.00059042356600135036</v>
       </c>
       <c r="V13">
-        <v>-0.00066572462976003592</v>
+        <v>-0.00066061582533483078</v>
       </c>
       <c r="W13">
-        <v>-0.0005919315770861025</v>
+        <v>-0.00057955817890526992</v>
       </c>
       <c r="X13">
-        <v>-0.00069134970251294068</v>
+        <v>-0.00069703045298511476</v>
       </c>
       <c r="Y13">
-        <v>-0.00023261891205772329</v>
+        <v>-0.00023404876873953179</v>
       </c>
       <c r="Z13">
-        <v>-0.0007785090143433152</v>
+        <v>-0.00076869596204488279</v>
       </c>
       <c r="AA13">
-        <v>-0.00086375479376982862</v>
+        <v>-0.00084984763262245739</v>
       </c>
       <c r="AB13">
-        <v>9.2010256900431719e-006</v>
+        <v>8.6458215088697105e-006</v>
       </c>
       <c r="AC13">
-        <v>1.4247399345001104e-005</v>
+        <v>1.5154491979107226e-005</v>
       </c>
       <c r="AD13">
-        <v>0.00027256776610522329</v>
+        <v>0.0002784889799418137</v>
       </c>
       <c r="AE13">
-        <v>0.00011325031857949285</v>
+        <v>0.00011393711548309037</v>
       </c>
       <c r="AF13">
-        <v>-0.00027352599018089869</v>
+        <v>-0.00026364471485490677</v>
       </c>
       <c r="AG13">
-        <v>-0.00084024514577010865</v>
+        <v>-0.00032225494974379355</v>
       </c>
       <c r="AH13">
-        <v>0.002212650853788333</v>
+        <v>0.0020793638939352347</v>
       </c>
     </row>
     <row r="14">
@@ -4060,103 +4060,103 @@
         <v>58</v>
       </c>
       <c r="B14" s="32">
-        <v>-0.0021595728993808899</v>
+        <v>-0.002138526041040663</v>
       </c>
       <c r="C14">
-        <v>-7.2932807052994167e-006</v>
+        <v>-7.2658787175733938e-006</v>
       </c>
       <c r="D14">
-        <v>-8.9225907011246044e-007</v>
+        <v>-9.2692886320017311e-007</v>
       </c>
       <c r="E14">
-        <v>9.5085277026373754e-009</v>
+        <v>9.6852229397344118e-009</v>
       </c>
       <c r="F14">
-        <v>1.6867214052650899e-006</v>
+        <v>1.7112346973505279e-006</v>
       </c>
       <c r="G14">
-        <v>-1.3441884041312004e-006</v>
+        <v>-1.278184171283687e-006</v>
       </c>
       <c r="H14">
-        <v>-3.535584175017146e-006</v>
+        <v>-3.4218534843710983e-006</v>
       </c>
       <c r="I14">
-        <v>1.8944434166787717e-005</v>
+        <v>1.9067385065363942e-005</v>
       </c>
       <c r="J14">
-        <v>3.9160127678004289e-006</v>
+        <v>4.3416106806812574e-006</v>
       </c>
       <c r="K14">
-        <v>4.6576888942279705e-006</v>
+        <v>4.961215945070755e-006</v>
       </c>
       <c r="L14">
-        <v>3.9373928810888348e-006</v>
+        <v>4.2298826562230091e-006</v>
       </c>
       <c r="M14">
-        <v>-1.4027964585980434e-006</v>
+        <v>-1.1067651399144178e-006</v>
       </c>
       <c r="N14">
-        <v>4.0818746748357006e-005</v>
+        <v>4.0812383343240115e-005</v>
       </c>
       <c r="O14">
-        <v>2.8408538387203361e-006</v>
+        <v>2.8399122266231839e-006</v>
       </c>
       <c r="P14">
-        <v>2.9014787761208582e-007</v>
+        <v>2.8986575734165905e-007</v>
       </c>
       <c r="Q14">
-        <v>-3.3695906090859578e-006</v>
+        <v>-3.3997527739620064e-006</v>
       </c>
       <c r="R14">
-        <v>-7.275864662143318e-006</v>
+        <v>-7.2701646569758692e-006</v>
       </c>
       <c r="S14">
-        <v>1.891599582272218e-006</v>
+        <v>1.8673892174073825e-006</v>
       </c>
       <c r="T14">
-        <v>-1.2974835566679962e-005</v>
+        <v>-1.3027165803206501e-005</v>
       </c>
       <c r="U14">
-        <v>-8.3535429938972749e-006</v>
+        <v>-8.3028669062405757e-006</v>
       </c>
       <c r="V14">
-        <v>-7.3312503525005998e-006</v>
+        <v>-7.3627490944076941e-006</v>
       </c>
       <c r="W14">
-        <v>-4.0501799875164717e-006</v>
+        <v>-4.0893353043444918e-006</v>
       </c>
       <c r="X14">
-        <v>-3.1603939579357625e-006</v>
+        <v>-3.1850705403547438e-006</v>
       </c>
       <c r="Y14">
-        <v>-1.0828958254950838e-005</v>
+        <v>-1.0869014037597765e-005</v>
       </c>
       <c r="Z14">
-        <v>-9.4188463124245971e-006</v>
+        <v>-9.4166379230923268e-006</v>
       </c>
       <c r="AA14">
-        <v>-1.1090096878962864e-005</v>
+        <v>-1.1050233474489576e-005</v>
       </c>
       <c r="AB14">
-        <v>4.6944373475961972e-007</v>
+        <v>4.7690028282287007e-007</v>
       </c>
       <c r="AC14">
-        <v>-3.0645800434848281e-006</v>
+        <v>-3.1184752206328778e-006</v>
       </c>
       <c r="AD14">
-        <v>-4.3642271318599857e-006</v>
+        <v>-4.2661558382127933e-006</v>
       </c>
       <c r="AE14">
-        <v>-2.5323665983099182e-006</v>
+        <v>-2.5242242813121687e-006</v>
       </c>
       <c r="AF14">
-        <v>-6.2780760006232988e-006</v>
+        <v>-6.2728560110516846e-006</v>
       </c>
       <c r="AG14">
-        <v>-4.9426247473076737e-006</v>
+        <v>-2.791041384473235e-006</v>
       </c>
       <c r="AH14">
-        <v>-0.00014012776881665252</v>
+        <v>-0.00013909885257408199</v>
       </c>
     </row>
     <row r="15">
@@ -4164,103 +4164,103 @@
         <v>59</v>
       </c>
       <c r="B15" s="34">
-        <v>0.00045143422872850756</v>
+        <v>0.00049010636444643053</v>
       </c>
       <c r="C15">
-        <v>-1.0321650756574509e-005</v>
+        <v>-1.0313279095804779e-005</v>
       </c>
       <c r="D15">
-        <v>-4.5521562984527974e-007</v>
+        <v>-5.0761966319832248e-007</v>
       </c>
       <c r="E15">
-        <v>-1.4515694310234655e-009</v>
+        <v>-1.2020460589674638e-009</v>
       </c>
       <c r="F15">
-        <v>6.450281924140358e-007</v>
+        <v>6.7814932941932633e-007</v>
       </c>
       <c r="G15">
-        <v>-1.0545664454212786e-006</v>
+        <v>-8.985522751580887e-007</v>
       </c>
       <c r="H15">
-        <v>-5.5945102044640154e-006</v>
+        <v>-5.4648659865589639e-006</v>
       </c>
       <c r="I15">
-        <v>1.4113373114515936e-005</v>
+        <v>1.4351202841288422e-005</v>
       </c>
       <c r="J15">
-        <v>-8.4983725723963731e-007</v>
+        <v>-2.9899808424102921e-007</v>
       </c>
       <c r="K15">
-        <v>-4.0359688674558289e-006</v>
+        <v>-3.71386576004091e-006</v>
       </c>
       <c r="L15">
-        <v>-4.2900373983068876e-006</v>
+        <v>-3.8646342852340733e-006</v>
       </c>
       <c r="M15">
-        <v>-5.0249566190802026e-006</v>
+        <v>-4.5823041440376133e-006</v>
       </c>
       <c r="N15">
-        <v>1.8973103170561286e-005</v>
+        <v>1.885137551298281e-005</v>
       </c>
       <c r="O15">
-        <v>2.9014787761208582e-007</v>
+        <v>2.8986575734165905e-007</v>
       </c>
       <c r="P15">
-        <v>3.2083180171917215e-006</v>
+        <v>3.2073417661311561e-006</v>
       </c>
       <c r="Q15">
-        <v>-1.0356663463528007e-005</v>
+        <v>-9.9734262464451707e-006</v>
       </c>
       <c r="R15">
-        <v>-1.0181453941933687e-005</v>
+        <v>-9.8170636641457777e-006</v>
       </c>
       <c r="S15">
-        <v>-2.5536265413952908e-006</v>
+        <v>-2.2368476667961545e-006</v>
       </c>
       <c r="T15">
-        <v>-2.2836291401328072e-005</v>
+        <v>-2.2529635188588143e-005</v>
       </c>
       <c r="U15">
-        <v>-9.2831767309734623e-006</v>
+        <v>-8.9271753366609594e-006</v>
       </c>
       <c r="V15">
-        <v>-1.7336730712185487e-005</v>
+        <v>-1.7086301633954229e-005</v>
       </c>
       <c r="W15">
-        <v>-1.027832495488416e-005</v>
+        <v>-9.9334594320396344e-006</v>
       </c>
       <c r="X15">
-        <v>-1.2054102181863628e-005</v>
+        <v>-1.1842412389255976e-005</v>
       </c>
       <c r="Y15">
-        <v>-1.4444735615151623e-005</v>
+        <v>-1.4280757574520347e-005</v>
       </c>
       <c r="Z15">
-        <v>-8.168941921261915e-006</v>
+        <v>-7.836280142973351e-006</v>
       </c>
       <c r="AA15">
-        <v>-1.6367049456531821e-005</v>
+        <v>-1.596663815510015e-005</v>
       </c>
       <c r="AB15">
-        <v>1.1399215541703141e-006</v>
+        <v>1.161740058585554e-006</v>
       </c>
       <c r="AC15">
-        <v>-9.1380285999287027e-006</v>
+        <v>-9.2712599328622994e-006</v>
       </c>
       <c r="AD15">
-        <v>-7.9742205118265739e-007</v>
+        <v>-9.1133321784729613e-007</v>
       </c>
       <c r="AE15">
-        <v>-1.118041368553518e-005</v>
+        <v>-1.0879904245285747e-005</v>
       </c>
       <c r="AF15">
-        <v>-1.4768927175091225e-005</v>
+        <v>-1.4488505380382428e-005</v>
       </c>
       <c r="AG15">
-        <v>-7.1234386532692521e-006</v>
+        <v>-1.4097114503809345e-007</v>
       </c>
       <c r="AH15">
-        <v>-0.0001400155663921891</v>
+        <v>-0.00013886736225618673</v>
       </c>
     </row>
     <row r="16">
@@ -4268,103 +4268,103 @@
         <v>60</v>
       </c>
       <c r="B16" s="36">
-        <v>0.15804386863378311</v>
+        <v>0.15506142277566445</v>
       </c>
       <c r="C16">
-        <v>-0.00033667236564179906</v>
+        <v>-0.00033837676189228064</v>
       </c>
       <c r="D16">
-        <v>8.0626244750043458e-005</v>
+        <v>8.2514034779570394e-005</v>
       </c>
       <c r="E16">
-        <v>-4.7266436101894849e-007</v>
+        <v>-4.7948963595342538e-007</v>
       </c>
       <c r="F16">
-        <v>-0.00056132383378123944</v>
+        <v>-0.00056411637463037482</v>
       </c>
       <c r="G16">
-        <v>-0.00082101692628192057</v>
+        <v>-0.0008215556922441463</v>
       </c>
       <c r="H16">
-        <v>-0.00015646992576572732</v>
+        <v>-0.00015477071053507374</v>
       </c>
       <c r="I16">
-        <v>1.4483608160642536e-005</v>
+        <v>1.3852358689376773e-005</v>
       </c>
       <c r="J16">
-        <v>-0.0002514795370388911</v>
+        <v>-0.00026631892315310125</v>
       </c>
       <c r="K16">
-        <v>-0.00069703085980754142</v>
+        <v>-0.00069766694092154413</v>
       </c>
       <c r="L16">
-        <v>-0.00037305986983865837</v>
+        <v>-0.00038707347593605569</v>
       </c>
       <c r="M16">
-        <v>-3.8538516513184941e-005</v>
+        <v>-3.7776323812257172e-005</v>
       </c>
       <c r="N16">
-        <v>-0.0005246849932078663</v>
+        <v>-0.0005121126631316762</v>
       </c>
       <c r="O16">
-        <v>-3.3695906090859578e-006</v>
+        <v>-3.3997527739620064e-006</v>
       </c>
       <c r="P16">
-        <v>-1.0356663463528007e-005</v>
+        <v>-9.9734262464451707e-006</v>
       </c>
       <c r="Q16">
-        <v>0.010069285242990124</v>
+        <v>0.010071493558697528</v>
       </c>
       <c r="R16">
-        <v>0.0044410866607642145</v>
+        <v>0.0044419285855789494</v>
       </c>
       <c r="S16">
-        <v>0.004327415929280611</v>
+        <v>0.0043351180198793323</v>
       </c>
       <c r="T16">
-        <v>0.0044706922006931844</v>
+        <v>0.0044804978858441306</v>
       </c>
       <c r="U16">
-        <v>0.0043003078286062545</v>
+        <v>0.0042938362724882608</v>
       </c>
       <c r="V16">
-        <v>0.0043731396082448961</v>
+        <v>0.0043876634106138155</v>
       </c>
       <c r="W16">
-        <v>0.0043554336067966621</v>
+        <v>0.0043531800293321564</v>
       </c>
       <c r="X16">
-        <v>0.0044132169677950526</v>
+        <v>0.0044440824316866138</v>
       </c>
       <c r="Y16">
-        <v>0.0043234142216752036</v>
+        <v>0.00433974655918371</v>
       </c>
       <c r="Z16">
-        <v>0.0044168457939362735</v>
+        <v>0.004431040204520802</v>
       </c>
       <c r="AA16">
-        <v>0.0045180258877900855</v>
+        <v>0.0045250173365123155</v>
       </c>
       <c r="AB16">
-        <v>-2.9016190706503183e-005</v>
+        <v>-3.0017280472275498e-005</v>
       </c>
       <c r="AC16">
-        <v>-0.00047262122166437593</v>
+        <v>-0.00047886181699185445</v>
       </c>
       <c r="AD16">
-        <v>0.00018394209430102238</v>
+        <v>0.00018886171291712016</v>
       </c>
       <c r="AE16">
-        <v>0.0017481211648762746</v>
+        <v>0.0017580860196611211</v>
       </c>
       <c r="AF16">
-        <v>0.0031817038263297222</v>
+        <v>0.0031983623043224207</v>
       </c>
       <c r="AG16">
-        <v>0.0012059012449505226</v>
+        <v>0.00083947930311241274</v>
       </c>
       <c r="AH16">
-        <v>-0.0053555860190492525</v>
+        <v>-0.0054567612245047855</v>
       </c>
     </row>
     <row r="17">
@@ -4372,103 +4372,103 @@
         <v>61</v>
       </c>
       <c r="B17" s="38">
-        <v>0.10522577121410281</v>
+        <v>0.10236924537949678</v>
       </c>
       <c r="C17">
-        <v>-0.00013815147830413261</v>
+        <v>-0.00013864681664043526</v>
       </c>
       <c r="D17">
-        <v>5.3253814607887723e-005</v>
+        <v>5.6177203023033417e-005</v>
       </c>
       <c r="E17">
-        <v>-3.5964707519903379e-007</v>
+        <v>-3.7455239923793113e-007</v>
       </c>
       <c r="F17">
-        <v>-0.00039147292005795432</v>
+        <v>-0.00039449510301402989</v>
       </c>
       <c r="G17">
-        <v>-0.00064362907747527549</v>
+        <v>-0.00064442408079817685</v>
       </c>
       <c r="H17">
-        <v>-7.6198062304463215e-005</v>
+        <v>-7.6032979348026469e-005</v>
       </c>
       <c r="I17">
-        <v>6.7056454873400031e-005</v>
+        <v>6.8955123347457133e-005</v>
       </c>
       <c r="J17">
-        <v>-0.00022164717664375621</v>
+        <v>-0.00022818917779190452</v>
       </c>
       <c r="K17">
-        <v>-0.00053530016660927548</v>
+        <v>-0.00052922548150550217</v>
       </c>
       <c r="L17">
-        <v>-0.00051416498036434537</v>
+        <v>-0.00051995248552363406</v>
       </c>
       <c r="M17">
-        <v>0.00015268892715170805</v>
+        <v>0.00015971788639749986</v>
       </c>
       <c r="N17">
-        <v>-0.00068760052753589248</v>
+        <v>-0.00067175411533876457</v>
       </c>
       <c r="O17">
-        <v>-7.275864662143318e-006</v>
+        <v>-7.2701646569758692e-006</v>
       </c>
       <c r="P17">
-        <v>-1.0181453941933687e-005</v>
+        <v>-9.8170636641457777e-006</v>
       </c>
       <c r="Q17">
-        <v>0.0044410866607642145</v>
+        <v>0.0044419285855789494</v>
       </c>
       <c r="R17">
-        <v>0.0066782435061568547</v>
+        <v>0.0066799344567449416</v>
       </c>
       <c r="S17">
-        <v>0.0042690845448231582</v>
+        <v>0.0042763429848778137</v>
       </c>
       <c r="T17">
-        <v>0.0044011669960470519</v>
+        <v>0.0044097288428386009</v>
       </c>
       <c r="U17">
-        <v>0.004265008239065126</v>
+        <v>0.0042581837776289426</v>
       </c>
       <c r="V17">
-        <v>0.0043219366877449358</v>
+        <v>0.0043353016823892664</v>
       </c>
       <c r="W17">
-        <v>0.0043227874743948218</v>
+        <v>0.0043206924494751968</v>
       </c>
       <c r="X17">
-        <v>0.0043878446353140402</v>
+        <v>0.0044164425374033341</v>
       </c>
       <c r="Y17">
-        <v>0.0043145360654691066</v>
+        <v>0.004329422033769733</v>
       </c>
       <c r="Z17">
-        <v>0.0043764528655819224</v>
+        <v>0.0043895897239976268</v>
       </c>
       <c r="AA17">
-        <v>0.0045049756999555463</v>
+        <v>0.0045111234723951869</v>
       </c>
       <c r="AB17">
-        <v>-1.5378794077151487e-005</v>
+        <v>-1.6622386995935939e-005</v>
       </c>
       <c r="AC17">
-        <v>-0.00041610900961192281</v>
+        <v>-0.00041751678414729174</v>
       </c>
       <c r="AD17">
-        <v>2.7747281600076486e-005</v>
+        <v>3.2292080787612801e-005</v>
       </c>
       <c r="AE17">
-        <v>0.0016605573957851421</v>
+        <v>0.0016652690023666859</v>
       </c>
       <c r="AF17">
-        <v>0.0030733863421157533</v>
+        <v>0.003089011713988097</v>
       </c>
       <c r="AG17">
-        <v>0.0011205039065298105</v>
+        <v>0.0008018143446887234</v>
       </c>
       <c r="AH17">
-        <v>-0.0043730982503792466</v>
+        <v>-0.0045096747070545182</v>
       </c>
     </row>
     <row r="18">
@@ -4476,103 +4476,103 @@
         <v>62</v>
       </c>
       <c r="B18" s="40">
-        <v>0.070625707562584017</v>
+        <v>0.068012711346531515</v>
       </c>
       <c r="C18">
-        <v>-0.00019682073514282021</v>
+        <v>-0.00019891467061213149</v>
       </c>
       <c r="D18">
-        <v>-2.6939271765310038e-005</v>
+        <v>-2.4337907789519914e-005</v>
       </c>
       <c r="E18">
-        <v>2.5932142245787572e-007</v>
+        <v>2.4517226698711502e-007</v>
       </c>
       <c r="F18">
-        <v>-0.00010730017587097989</v>
+        <v>-0.00011075681161146409</v>
       </c>
       <c r="G18">
-        <v>-0.00039829912652690057</v>
+        <v>-0.00039601170193055701</v>
       </c>
       <c r="H18">
-        <v>-6.2104842858892381e-005</v>
+        <v>-5.9203399892025603e-005</v>
       </c>
       <c r="I18">
-        <v>-1.2778129921261865e-005</v>
+        <v>-1.3979574404297899e-005</v>
       </c>
       <c r="J18">
-        <v>-0.00014663070684256107</v>
+        <v>-0.00015884508767581476</v>
       </c>
       <c r="K18">
-        <v>-0.00045765400232939204</v>
+        <v>-0.00045772158974038187</v>
       </c>
       <c r="L18">
-        <v>-0.00033038069968357509</v>
+        <v>-0.00034161533642113984</v>
       </c>
       <c r="M18">
-        <v>9.4930633120171755e-005</v>
+        <v>9.7566005558092066e-005</v>
       </c>
       <c r="N18">
-        <v>-0.00053656045712385228</v>
+        <v>-0.00052669154411597832</v>
       </c>
       <c r="O18">
-        <v>1.891599582272218e-006</v>
+        <v>1.8673892174073825e-006</v>
       </c>
       <c r="P18">
-        <v>-2.5536265413952908e-006</v>
+        <v>-2.2368476667961545e-006</v>
       </c>
       <c r="Q18">
-        <v>0.004327415929280611</v>
+        <v>0.0043351180198793323</v>
       </c>
       <c r="R18">
-        <v>0.0042690845448231582</v>
+        <v>0.0042763429848778137</v>
       </c>
       <c r="S18">
-        <v>0.0079961635222216571</v>
+        <v>0.0080117004643261765</v>
       </c>
       <c r="T18">
-        <v>0.0042943456825295318</v>
+        <v>0.0043103742711729526</v>
       </c>
       <c r="U18">
-        <v>0.0041665783537436669</v>
+        <v>0.0041661816160144327</v>
       </c>
       <c r="V18">
-        <v>0.0041870577023204909</v>
+        <v>0.004206306846294243</v>
       </c>
       <c r="W18">
-        <v>0.0041816398346145606</v>
+        <v>0.0041855769652265513</v>
       </c>
       <c r="X18">
-        <v>0.0042349397411615124</v>
+        <v>0.0042668289652239609</v>
       </c>
       <c r="Y18">
-        <v>0.0041917151923023914</v>
+        <v>0.0042098352684509762</v>
       </c>
       <c r="Z18">
-        <v>0.0042653493197065536</v>
+        <v>0.0042858444405529019</v>
       </c>
       <c r="AA18">
-        <v>0.004379235174620218</v>
+        <v>0.0043937614313859343</v>
       </c>
       <c r="AB18">
-        <v>-2.5018717378174825e-005</v>
+        <v>-2.5839820439571635e-005</v>
       </c>
       <c r="AC18">
-        <v>-0.00024658862539125279</v>
+        <v>-0.00025098057037031081</v>
       </c>
       <c r="AD18">
-        <v>0.00031449837564417323</v>
+        <v>0.00031896914087022526</v>
       </c>
       <c r="AE18">
-        <v>0.0016365071053053065</v>
+        <v>0.0016505758498428255</v>
       </c>
       <c r="AF18">
-        <v>0.0028708237296867956</v>
+        <v>0.0028929747397056244</v>
       </c>
       <c r="AG18">
-        <v>0.0010047526480274848</v>
+        <v>0.00080877730753728307</v>
       </c>
       <c r="AH18">
-        <v>-0.0025909203964719278</v>
+        <v>-0.0027156715441482761</v>
       </c>
     </row>
     <row r="19">
@@ -4580,103 +4580,103 @@
         <v>63</v>
       </c>
       <c r="B19" s="42">
-        <v>0.065430671944703547</v>
+        <v>0.062956599356593368</v>
       </c>
       <c r="C19">
-        <v>-0.00028972702773992737</v>
+        <v>-0.00029029294062134659</v>
       </c>
       <c r="D19">
-        <v>5.0347652073151616e-006</v>
+        <v>6.8722039547261526e-006</v>
       </c>
       <c r="E19">
-        <v>-3.8479150679286223e-008</v>
+        <v>-4.6240659276272373e-008</v>
       </c>
       <c r="F19">
-        <v>-0.00039814813205239064</v>
+        <v>-0.00040163735043565108</v>
       </c>
       <c r="G19">
-        <v>-0.00066667201812700965</v>
+        <v>-0.00066267907006707487</v>
       </c>
       <c r="H19">
-        <v>2.1552420097017272e-005</v>
+        <v>2.5500080729325483e-005</v>
       </c>
       <c r="I19">
-        <v>-8.2525619311895997e-005</v>
+        <v>-8.2800891487084735e-005</v>
       </c>
       <c r="J19">
-        <v>-0.00015202392624410327</v>
+        <v>-0.00016409149728204085</v>
       </c>
       <c r="K19">
-        <v>-0.00048976227999481241</v>
+        <v>-0.00048897081139790939</v>
       </c>
       <c r="L19">
-        <v>-0.00043571983349076316</v>
+        <v>-0.00044703190805250328</v>
       </c>
       <c r="M19">
-        <v>9.1523947926031978e-005</v>
+        <v>9.6489034177757796e-005</v>
       </c>
       <c r="N19">
-        <v>-0.00072871185539753064</v>
+        <v>-0.00071912123676505296</v>
       </c>
       <c r="O19">
-        <v>-1.2974835566679962e-005</v>
+        <v>-1.3027165803206501e-005</v>
       </c>
       <c r="P19">
-        <v>-2.2836291401328072e-005</v>
+        <v>-2.2529635188588143e-005</v>
       </c>
       <c r="Q19">
-        <v>0.0044706922006931844</v>
+        <v>0.0044804978858441306</v>
       </c>
       <c r="R19">
-        <v>0.0044011669960470519</v>
+        <v>0.0044097288428386009</v>
       </c>
       <c r="S19">
-        <v>0.0042943456825295318</v>
+        <v>0.0043103742711729526</v>
       </c>
       <c r="T19">
-        <v>0.0092835988686965701</v>
+        <v>0.0093044560527870222</v>
       </c>
       <c r="U19">
-        <v>0.004281041988312112</v>
+        <v>0.0042816507132088953</v>
       </c>
       <c r="V19">
-        <v>0.0043430818690055719</v>
+        <v>0.0043658056214556373</v>
       </c>
       <c r="W19">
-        <v>0.0043387784931490803</v>
+        <v>0.0043442588786653637</v>
       </c>
       <c r="X19">
-        <v>0.0044055836148852966</v>
+        <v>0.004440213402404523</v>
       </c>
       <c r="Y19">
-        <v>0.0043527444899560397</v>
+        <v>0.0043745342317952239</v>
       </c>
       <c r="Z19">
-        <v>0.0044207123744119383</v>
+        <v>0.0044453070537960205</v>
       </c>
       <c r="AA19">
-        <v>0.0045785681688785777</v>
+        <v>0.0045960476426064722</v>
       </c>
       <c r="AB19">
-        <v>-3.5125877717720797e-007</v>
+        <v>-1.282341499608308e-006</v>
       </c>
       <c r="AC19">
-        <v>1.7133551549641747e-005</v>
+        <v>1.3629212373405565e-005</v>
       </c>
       <c r="AD19">
-        <v>-0.00017302912446730284</v>
+        <v>-0.00017023947513039904</v>
       </c>
       <c r="AE19">
-        <v>0.0015359932535348156</v>
+        <v>0.0015513746894397732</v>
       </c>
       <c r="AF19">
-        <v>0.0031448871209165731</v>
+        <v>0.0031706616403304757</v>
       </c>
       <c r="AG19">
-        <v>0.0012060806748531955</v>
+        <v>0.00099766873034227424</v>
       </c>
       <c r="AH19">
-        <v>-0.0019732405212521168</v>
+        <v>-0.0020782339861934594</v>
       </c>
     </row>
     <row r="20">
@@ -4684,103 +4684,103 @@
         <v>64</v>
       </c>
       <c r="B20" s="44">
-        <v>0.032049985862881936</v>
+        <v>0.030338783212579268</v>
       </c>
       <c r="C20">
-        <v>-0.00013987655129243807</v>
+        <v>-0.000141661372201108</v>
       </c>
       <c r="D20">
-        <v>6.1977822883550748e-005</v>
+        <v>6.2797708712373362e-005</v>
       </c>
       <c r="E20">
-        <v>-4.3843596146809604e-007</v>
+        <v>-4.3868277338019054e-007</v>
       </c>
       <c r="F20">
-        <v>-0.00044539496547781174</v>
+        <v>-0.00044478516267592623</v>
       </c>
       <c r="G20">
-        <v>-0.00082074609173736295</v>
+        <v>-0.00081857691810634258</v>
       </c>
       <c r="H20">
-        <v>6.1568832592699338e-005</v>
+        <v>6.2007720975197286e-005</v>
       </c>
       <c r="I20">
-        <v>-0.0001624020976564132</v>
+        <v>-0.00015355436294518365</v>
       </c>
       <c r="J20">
-        <v>-0.00024987601836300665</v>
+        <v>-0.00024183381064393392</v>
       </c>
       <c r="K20">
-        <v>-0.00046954554131387982</v>
+        <v>-0.00045284673996856344</v>
       </c>
       <c r="L20">
-        <v>-0.00054820626421405371</v>
+        <v>-0.00054161931480620445</v>
       </c>
       <c r="M20">
-        <v>-0.00020890049935722932</v>
+        <v>-0.000188986987902472</v>
       </c>
       <c r="N20">
-        <v>-0.00060861480083156789</v>
+        <v>-0.00059042356600135036</v>
       </c>
       <c r="O20">
-        <v>-8.3535429938972749e-006</v>
+        <v>-8.3028669062405757e-006</v>
       </c>
       <c r="P20">
-        <v>-9.2831767309734623e-006</v>
+        <v>-8.9271753366609594e-006</v>
       </c>
       <c r="Q20">
-        <v>0.0043003078286062545</v>
+        <v>0.0042938362724882608</v>
       </c>
       <c r="R20">
-        <v>0.004265008239065126</v>
+        <v>0.0042581837776289426</v>
       </c>
       <c r="S20">
-        <v>0.0041665783537436669</v>
+        <v>0.0041661816160144327</v>
       </c>
       <c r="T20">
-        <v>0.004281041988312112</v>
+        <v>0.0042816507132088953</v>
       </c>
       <c r="U20">
-        <v>0.0082847249603434196</v>
+        <v>0.0082767712314703468</v>
       </c>
       <c r="V20">
-        <v>0.0041918115441036598</v>
+        <v>0.0041964661457340952</v>
       </c>
       <c r="W20">
-        <v>0.0041742799068859877</v>
+        <v>0.0041653563345809656</v>
       </c>
       <c r="X20">
-        <v>0.00421591787222351</v>
+        <v>0.0042371708420220443</v>
       </c>
       <c r="Y20">
-        <v>0.0041726902841755916</v>
+        <v>0.0041810169990916819</v>
       </c>
       <c r="Z20">
-        <v>0.0042349104063062722</v>
+        <v>0.0042389066211754069</v>
       </c>
       <c r="AA20">
-        <v>0.0043815688927323591</v>
+        <v>0.0043792376732927161</v>
       </c>
       <c r="AB20">
-        <v>-1.1709328923217208e-005</v>
+        <v>-1.2453839990589283e-005</v>
       </c>
       <c r="AC20">
-        <v>-0.00045947447657942314</v>
+        <v>-0.00046342542455989131</v>
       </c>
       <c r="AD20">
-        <v>-3.7281631257952226e-006</v>
+        <v>-9.1441644578781891e-007</v>
       </c>
       <c r="AE20">
-        <v>0.0011776755149863127</v>
+        <v>0.0011828160980148041</v>
       </c>
       <c r="AF20">
-        <v>0.0027456761097331985</v>
+        <v>0.0027547298535770528</v>
       </c>
       <c r="AG20">
-        <v>0.0010602267703547831</v>
+        <v>0.00061772670646473326</v>
       </c>
       <c r="AH20">
-        <v>-0.0043539141744750182</v>
+        <v>-0.0044316990434977339</v>
       </c>
     </row>
     <row r="21">
@@ -4788,103 +4788,103 @@
         <v>65</v>
       </c>
       <c r="B21" s="46">
-        <v>0.13491039781666883</v>
+        <v>0.13401280142697566</v>
       </c>
       <c r="C21">
-        <v>-0.00012975427562058098</v>
+        <v>-0.00013025375480035252</v>
       </c>
       <c r="D21">
-        <v>6.1138501412604657e-005</v>
+        <v>6.3398944354010889e-005</v>
       </c>
       <c r="E21">
-        <v>-3.4078693235601622e-007</v>
+        <v>-3.5541964169076004e-007</v>
       </c>
       <c r="F21">
-        <v>-0.00048067833742883813</v>
+        <v>-0.00048211654364706502</v>
       </c>
       <c r="G21">
-        <v>-0.0007231846081631471</v>
+        <v>-0.00071504885827797357</v>
       </c>
       <c r="H21">
-        <v>-0.00010587455719134574</v>
+        <v>-9.9769081016158612e-005</v>
       </c>
       <c r="I21">
-        <v>0.00013308551702902877</v>
+        <v>0.00014193966325015683</v>
       </c>
       <c r="J21">
-        <v>-0.00019255884077203284</v>
+        <v>-0.00018418315726145807</v>
       </c>
       <c r="K21">
-        <v>-0.00033688736490201747</v>
+        <v>-0.00032259302998460457</v>
       </c>
       <c r="L21">
-        <v>-0.00032614701593641424</v>
+        <v>-0.00032143011198852559</v>
       </c>
       <c r="M21">
-        <v>-6.8847114739387615e-006</v>
+        <v>1.4358102278788209e-005</v>
       </c>
       <c r="N21">
-        <v>-0.00066572462976003592</v>
+        <v>-0.00066061582533483078</v>
       </c>
       <c r="O21">
-        <v>-7.3312503525005998e-006</v>
+        <v>-7.3627490944076941e-006</v>
       </c>
       <c r="P21">
-        <v>-1.7336730712185487e-005</v>
+        <v>-1.7086301633954229e-005</v>
       </c>
       <c r="Q21">
-        <v>0.0043731396082448961</v>
+        <v>0.0043876634106138155</v>
       </c>
       <c r="R21">
-        <v>0.0043219366877449358</v>
+        <v>0.0043353016823892664</v>
       </c>
       <c r="S21">
-        <v>0.0041870577023204909</v>
+        <v>0.004206306846294243</v>
       </c>
       <c r="T21">
-        <v>0.0043430818690055719</v>
+        <v>0.0043658056214556373</v>
       </c>
       <c r="U21">
-        <v>0.0041918115441036598</v>
+        <v>0.0041964661457340952</v>
       </c>
       <c r="V21">
-        <v>0.0072615789734711165</v>
+        <v>0.0072775950404669366</v>
       </c>
       <c r="W21">
-        <v>0.0042518765692867548</v>
+        <v>0.0042611656586671459</v>
       </c>
       <c r="X21">
-        <v>0.0042849955358896996</v>
+        <v>0.0043175183687625632</v>
       </c>
       <c r="Y21">
-        <v>0.0042666919701503736</v>
+        <v>0.0042863136723823667</v>
       </c>
       <c r="Z21">
-        <v>0.0043061891759196237</v>
+        <v>0.0043339351432629984</v>
       </c>
       <c r="AA21">
-        <v>0.0044143215263017389</v>
+        <v>0.0044365655580845993</v>
       </c>
       <c r="AB21">
-        <v>-5.3893069807236225e-006</v>
+        <v>-5.8760228070261204e-006</v>
       </c>
       <c r="AC21">
-        <v>-0.00034266503006918252</v>
+        <v>-0.00035018724074283985</v>
       </c>
       <c r="AD21">
-        <v>8.4918994787493634e-005</v>
+        <v>8.8727838504066588e-005</v>
       </c>
       <c r="AE21">
-        <v>0.001582770996282249</v>
+        <v>0.0016020519241820594</v>
       </c>
       <c r="AF21">
-        <v>0.0030752642553974995</v>
+        <v>0.0031031974837165328</v>
       </c>
       <c r="AG21">
-        <v>0.00080262942849036625</v>
+        <v>0.00080997150630304998</v>
       </c>
       <c r="AH21">
-        <v>-0.0046888986886717554</v>
+        <v>-0.0048189745475510923</v>
       </c>
     </row>
     <row r="22">
@@ -4892,103 +4892,103 @@
         <v>66</v>
       </c>
       <c r="B22" s="48">
-        <v>0.021892108206781641</v>
+        <v>0.019452974880805218</v>
       </c>
       <c r="C22">
-        <v>-0.00015085010404312037</v>
+        <v>-0.00015183116243841976</v>
       </c>
       <c r="D22">
-        <v>3.3819013203876397e-005</v>
+        <v>3.6069679854242032e-005</v>
       </c>
       <c r="E22">
-        <v>-2.1733689781517512e-007</v>
+        <v>-2.2754702857447962e-007</v>
       </c>
       <c r="F22">
-        <v>-0.00043532786456060768</v>
+        <v>-0.00043693200062624126</v>
       </c>
       <c r="G22">
-        <v>-0.00071067604861538693</v>
+        <v>-0.00071006264526796159</v>
       </c>
       <c r="H22">
-        <v>-0.00025393836667947107</v>
+        <v>-0.00025362866905109371</v>
       </c>
       <c r="I22">
-        <v>-2.0693796932810989e-006</v>
+        <v>1.3179819911249453e-006</v>
       </c>
       <c r="J22">
-        <v>-0.00027631505202345354</v>
+        <v>-0.00028044836944169206</v>
       </c>
       <c r="K22">
-        <v>-0.0004413096422865515</v>
+        <v>-0.00043397716409476577</v>
       </c>
       <c r="L22">
-        <v>-0.00040308000617852004</v>
+        <v>-0.0004069918113282201</v>
       </c>
       <c r="M22">
-        <v>-8.8312276122099256e-005</v>
+        <v>-7.9815087748710649e-005</v>
       </c>
       <c r="N22">
-        <v>-0.0005919315770861025</v>
+        <v>-0.00057955817890526992</v>
       </c>
       <c r="O22">
-        <v>-4.0501799875164717e-006</v>
+        <v>-4.0893353043444918e-006</v>
       </c>
       <c r="P22">
-        <v>-1.027832495488416e-005</v>
+        <v>-9.9334594320396344e-006</v>
       </c>
       <c r="Q22">
-        <v>0.0043554336067966621</v>
+        <v>0.0043531800293321564</v>
       </c>
       <c r="R22">
-        <v>0.0043227874743948218</v>
+        <v>0.0043206924494751968</v>
       </c>
       <c r="S22">
-        <v>0.0041816398346145606</v>
+        <v>0.0041855769652265513</v>
       </c>
       <c r="T22">
-        <v>0.0043387784931490803</v>
+        <v>0.0043442588786653637</v>
       </c>
       <c r="U22">
-        <v>0.0041742799068859877</v>
+        <v>0.0041653563345809656</v>
       </c>
       <c r="V22">
-        <v>0.0042518765692867548</v>
+        <v>0.0042611656586671459</v>
       </c>
       <c r="W22">
-        <v>0.0064539183131388216</v>
+        <v>0.0064497782192131821</v>
       </c>
       <c r="X22">
-        <v>0.0042889442784570355</v>
+        <v>0.0043146729244704692</v>
       </c>
       <c r="Y22">
-        <v>0.0042880810991608644</v>
+        <v>0.0042993228951927519</v>
       </c>
       <c r="Z22">
-        <v>0.0042873274333284708</v>
+        <v>0.0042968643654653716</v>
       </c>
       <c r="AA22">
-        <v>0.0044377691764211765</v>
+        <v>0.0044403509285291104</v>
       </c>
       <c r="AB22">
-        <v>-1.5952207275908052e-005</v>
+        <v>-1.6897550593139865e-005</v>
       </c>
       <c r="AC22">
-        <v>-0.00025050362407433394</v>
+        <v>-0.00025400151325079669</v>
       </c>
       <c r="AD22">
-        <v>-1.3829772365725365e-005</v>
+        <v>-8.9780183348540964e-006</v>
       </c>
       <c r="AE22">
-        <v>0.0016740267262388931</v>
+        <v>0.0016847676746109496</v>
       </c>
       <c r="AF22">
-        <v>0.0029716097648097512</v>
+        <v>0.0029839414203983354</v>
       </c>
       <c r="AG22">
-        <v>0.0010347403588517228</v>
+        <v>0.00067550998153724788</v>
       </c>
       <c r="AH22">
-        <v>-0.0036578899468770105</v>
+        <v>-0.003770931809172361</v>
       </c>
     </row>
     <row r="23">
@@ -4996,103 +4996,103 @@
         <v>67</v>
       </c>
       <c r="B23" s="50">
-        <v>0.065336820200590714</v>
+        <v>0.064386739466251425</v>
       </c>
       <c r="C23">
-        <v>-0.00025463906167638782</v>
+        <v>-0.00025254984860159234</v>
       </c>
       <c r="D23">
-        <v>2.1633846836399684e-005</v>
+        <v>2.3417570060156601e-005</v>
       </c>
       <c r="E23">
-        <v>-2.6021175711219867e-007</v>
+        <v>-2.7358592908319505e-007</v>
       </c>
       <c r="F23">
-        <v>-0.00042957545151653604</v>
+        <v>-0.00043451709471479237</v>
       </c>
       <c r="G23">
-        <v>-0.00054462181463674653</v>
+        <v>-0.00053820320806017479</v>
       </c>
       <c r="H23">
-        <v>-7.0309365027538748e-005</v>
+        <v>-6.2085647725066209e-005</v>
       </c>
       <c r="I23">
-        <v>-7.44891622407335e-006</v>
+        <v>-1.5912717474432167e-005</v>
       </c>
       <c r="J23">
-        <v>2.8054524930847392e-005</v>
+        <v>4.4482454219400358e-006</v>
       </c>
       <c r="K23">
-        <v>-0.00040198739122799393</v>
+        <v>-0.0004197649277422309</v>
       </c>
       <c r="L23">
-        <v>-0.00037290920588131551</v>
+        <v>-0.00039548996051627953</v>
       </c>
       <c r="M23">
-        <v>0.00012809697518807077</v>
+        <v>0.00011952289207832869</v>
       </c>
       <c r="N23">
-        <v>-0.00069134970251294068</v>
+        <v>-0.00069703045298511476</v>
       </c>
       <c r="O23">
-        <v>-3.1603939579357625e-006</v>
+        <v>-3.1850705403547438e-006</v>
       </c>
       <c r="P23">
-        <v>-1.2054102181863628e-005</v>
+        <v>-1.1842412389255976e-005</v>
       </c>
       <c r="Q23">
-        <v>0.0044132169677950526</v>
+        <v>0.0044440824316866138</v>
       </c>
       <c r="R23">
-        <v>0.0043878446353140402</v>
+        <v>0.0044164425374033341</v>
       </c>
       <c r="S23">
-        <v>0.0042349397411615124</v>
+        <v>0.0042668289652239609</v>
       </c>
       <c r="T23">
-        <v>0.0044055836148852966</v>
+        <v>0.004440213402404523</v>
       </c>
       <c r="U23">
-        <v>0.00421591787222351</v>
+        <v>0.0042371708420220443</v>
       </c>
       <c r="V23">
-        <v>0.0042849955358896996</v>
+        <v>0.0043175183687625632</v>
       </c>
       <c r="W23">
-        <v>0.0042889442784570355</v>
+        <v>0.0043146729244704692</v>
       </c>
       <c r="X23">
-        <v>0.0077953634929515498</v>
+        <v>0.0078205216872762832</v>
       </c>
       <c r="Y23">
-        <v>0.0043513273300937131</v>
+        <v>0.0043745490483033545</v>
       </c>
       <c r="Z23">
-        <v>0.0043679637168793188</v>
+        <v>0.0044068840243035156</v>
       </c>
       <c r="AA23">
-        <v>0.0045084551409850168</v>
+        <v>0.0045440937360955265</v>
       </c>
       <c r="AB23">
-        <v>1.0608494910703623e-009</v>
+        <v>-5.1779918875337859e-007</v>
       </c>
       <c r="AC23">
-        <v>-0.00048686766689544109</v>
+        <v>-0.0004881801286019075</v>
       </c>
       <c r="AD23">
-        <v>-0.00011013681099597206</v>
+        <v>-0.00010656350159576319</v>
       </c>
       <c r="AE23">
-        <v>0.0017490971485472802</v>
+        <v>0.0017684976130275239</v>
       </c>
       <c r="AF23">
-        <v>0.0030471301384141988</v>
+        <v>0.0030833213827379784</v>
       </c>
       <c r="AG23">
-        <v>0.00026534736088187037</v>
+        <v>0.00067444117084719231</v>
       </c>
       <c r="AH23">
-        <v>-0.003127679824341755</v>
+        <v>-0.0032123679077894788</v>
       </c>
     </row>
     <row r="24">
@@ -5100,103 +5100,103 @@
         <v>68</v>
       </c>
       <c r="B24" s="52">
-        <v>0.1680739143303929</v>
+        <v>0.16764772850992243</v>
       </c>
       <c r="C24">
-        <v>7.5404030701307218e-005</v>
+        <v>7.3280843683331751e-005</v>
       </c>
       <c r="D24">
-        <v>0.0001114796166682315</v>
+        <v>0.00011172316253667269</v>
       </c>
       <c r="E24">
-        <v>-9.0396311968051293e-007</v>
+        <v>-9.051234141669532e-007</v>
       </c>
       <c r="F24">
-        <v>-0.00032466075462096874</v>
+        <v>-0.00032673469439285281</v>
       </c>
       <c r="G24">
-        <v>-0.00068516740149460241</v>
+        <v>-0.00067557297336468696</v>
       </c>
       <c r="H24">
-        <v>-0.0001233331028386974</v>
+        <v>-0.00011462089497807533</v>
       </c>
       <c r="I24">
-        <v>-0.00031747070866658227</v>
+        <v>-0.00031639997418167476</v>
       </c>
       <c r="J24">
-        <v>-0.0001245852545716979</v>
+        <v>-0.00012842965534823358</v>
       </c>
       <c r="K24">
-        <v>3.8409589001284043e-005</v>
+        <v>3.7874952347481282e-005</v>
       </c>
       <c r="L24">
-        <v>-0.00040333258149122253</v>
+        <v>-0.00040824797919790032</v>
       </c>
       <c r="M24">
-        <v>0.00020252561573825406</v>
+        <v>0.00020985713066806614</v>
       </c>
       <c r="N24">
-        <v>-0.00023261891205772329</v>
+        <v>-0.00023404876873953179</v>
       </c>
       <c r="O24">
-        <v>-1.0828958254950838e-005</v>
+        <v>-1.0869014037597765e-005</v>
       </c>
       <c r="P24">
-        <v>-1.4444735615151623e-005</v>
+        <v>-1.4280757574520347e-005</v>
       </c>
       <c r="Q24">
-        <v>0.0043234142216752036</v>
+        <v>0.00433974655918371</v>
       </c>
       <c r="R24">
-        <v>0.0043145360654691066</v>
+        <v>0.004329422033769733</v>
       </c>
       <c r="S24">
-        <v>0.0041917151923023914</v>
+        <v>0.0042098352684509762</v>
       </c>
       <c r="T24">
-        <v>0.0043527444899560397</v>
+        <v>0.0043745342317952239</v>
       </c>
       <c r="U24">
-        <v>0.0041726902841755916</v>
+        <v>0.0041810169990916819</v>
       </c>
       <c r="V24">
-        <v>0.0042666919701503736</v>
+        <v>0.0042863136723823667</v>
       </c>
       <c r="W24">
-        <v>0.0042880810991608644</v>
+        <v>0.0042993228951927519</v>
       </c>
       <c r="X24">
-        <v>0.0043513273300937131</v>
+        <v>0.0043745490483033545</v>
       </c>
       <c r="Y24">
-        <v>0.0085094465840428891</v>
+        <v>0.0085131627376036044</v>
       </c>
       <c r="Z24">
-        <v>0.0042712169235481004</v>
+        <v>0.0042961828779521007</v>
       </c>
       <c r="AA24">
-        <v>0.0044798296690595086</v>
+        <v>0.0045005115654512921</v>
       </c>
       <c r="AB24">
-        <v>-5.9599377844296076e-006</v>
+        <v>-5.8220095182255356e-006</v>
       </c>
       <c r="AC24">
-        <v>-0.00038921007535020212</v>
+        <v>-0.00039712586549750506</v>
       </c>
       <c r="AD24">
-        <v>0.0008629334652918133</v>
+        <v>0.00086351559759223853</v>
       </c>
       <c r="AE24">
-        <v>0.0018678280985273527</v>
+        <v>0.0018826994132921629</v>
       </c>
       <c r="AF24">
-        <v>0.003129184585592418</v>
+        <v>0.0031535758672299168</v>
       </c>
       <c r="AG24">
-        <v>0.00038995281757131669</v>
+        <v>0.00052346539664983481</v>
       </c>
       <c r="AH24">
-        <v>-0.0058778451857606296</v>
+        <v>-0.0059245720874912628</v>
       </c>
     </row>
     <row r="25">
@@ -5204,103 +5204,103 @@
         <v>69</v>
       </c>
       <c r="B25" s="54">
-        <v>0.096857858296614335</v>
+        <v>0.094354906985366263</v>
       </c>
       <c r="C25">
-        <v>-0.00021796422342892853</v>
+        <v>-0.00021934855431962391</v>
       </c>
       <c r="D25">
-        <v>4.2591480572090612e-005</v>
+        <v>4.4085336384846324e-005</v>
       </c>
       <c r="E25">
-        <v>-2.6456053478561645e-007</v>
+        <v>-2.7087084724034395e-007</v>
       </c>
       <c r="F25">
-        <v>-0.00028788580349837568</v>
+        <v>-0.00029089887584337785</v>
       </c>
       <c r="G25">
-        <v>-0.00050655732563677767</v>
+        <v>-0.00050042910530610774</v>
       </c>
       <c r="H25">
-        <v>-0.00012523228519289824</v>
+        <v>-0.00011952802026654087</v>
       </c>
       <c r="I25">
-        <v>-1.4711588365243396e-005</v>
+        <v>-1.4007995097123534e-005</v>
       </c>
       <c r="J25">
-        <v>-2.3589680206153197e-005</v>
+        <v>-3.1930394449418116e-005</v>
       </c>
       <c r="K25">
-        <v>-0.00043423806303172544</v>
+        <v>-0.00043004364255322348</v>
       </c>
       <c r="L25">
-        <v>-0.00048595991328097016</v>
+        <v>-0.00049720377297905348</v>
       </c>
       <c r="M25">
-        <v>8.4960223050752591e-005</v>
+        <v>9.2799313031397858e-005</v>
       </c>
       <c r="N25">
-        <v>-0.0007785090143433152</v>
+        <v>-0.00076869596204488279</v>
       </c>
       <c r="O25">
-        <v>-9.4188463124245971e-006</v>
+        <v>-9.4166379230923268e-006</v>
       </c>
       <c r="P25">
-        <v>-8.168941921261915e-006</v>
+        <v>-7.836280142973351e-006</v>
       </c>
       <c r="Q25">
-        <v>0.0044168457939362735</v>
+        <v>0.004431040204520802</v>
       </c>
       <c r="R25">
-        <v>0.0043764528655819224</v>
+        <v>0.0043895897239976268</v>
       </c>
       <c r="S25">
-        <v>0.0042653493197065536</v>
+        <v>0.0042858444405529019</v>
       </c>
       <c r="T25">
-        <v>0.0044207123744119383</v>
+        <v>0.0044453070537960205</v>
       </c>
       <c r="U25">
-        <v>0.0042349104063062722</v>
+        <v>0.0042389066211754069</v>
       </c>
       <c r="V25">
-        <v>0.0043061891759196237</v>
+        <v>0.0043339351432629984</v>
       </c>
       <c r="W25">
-        <v>0.0042873274333284708</v>
+        <v>0.0042968643654653716</v>
       </c>
       <c r="X25">
-        <v>0.0043679637168793188</v>
+        <v>0.0044068840243035156</v>
       </c>
       <c r="Y25">
-        <v>0.0042712169235481004</v>
+        <v>0.0042961828779521007</v>
       </c>
       <c r="Z25">
-        <v>0.007036925634116285</v>
+        <v>0.0070688189723414384</v>
       </c>
       <c r="AA25">
-        <v>0.0044910822637637352</v>
+        <v>0.0045153170508096243</v>
       </c>
       <c r="AB25">
-        <v>-1.2081414757277021e-005</v>
+        <v>-1.2818559623989413e-005</v>
       </c>
       <c r="AC25">
-        <v>-0.00024530378162208356</v>
+        <v>-0.00025119587401667708</v>
       </c>
       <c r="AD25">
-        <v>0.0001010009993970551</v>
+        <v>0.00010456921588847175</v>
       </c>
       <c r="AE25">
-        <v>0.0017644715469949269</v>
+        <v>0.0017832486769061081</v>
       </c>
       <c r="AF25">
-        <v>0.0031563807356067937</v>
+        <v>0.0031874655129236263</v>
       </c>
       <c r="AG25">
-        <v>0.0011806550761511219</v>
+        <v>0.0010635818670413776</v>
       </c>
       <c r="AH25">
-        <v>-0.0041652756734506663</v>
+        <v>-0.0042706723905415571</v>
       </c>
     </row>
     <row r="26">
@@ -5308,103 +5308,103 @@
         <v>70</v>
       </c>
       <c r="B26" s="56">
-        <v>-0.040113070015876259</v>
+        <v>-0.041484056304950549</v>
       </c>
       <c r="C26">
-        <v>-0.00019987672487490823</v>
+        <v>-0.00020098287771494732</v>
       </c>
       <c r="D26">
-        <v>0.00017563297027386321</v>
+        <v>0.00017616197016771806</v>
       </c>
       <c r="E26">
-        <v>-1.4933504080459842e-006</v>
+        <v>-1.4911994023196376e-006</v>
       </c>
       <c r="F26">
-        <v>-0.00032890940680191426</v>
+        <v>-0.00033179732867242976</v>
       </c>
       <c r="G26">
-        <v>-0.00083735958328595337</v>
+        <v>-0.00083055903265061228</v>
       </c>
       <c r="H26">
-        <v>-8.5001769719806469e-005</v>
+        <v>-7.93694873565641e-005</v>
       </c>
       <c r="I26">
-        <v>-0.00012965240996178247</v>
+        <v>-0.00011363132741138045</v>
       </c>
       <c r="J26">
-        <v>-1.803320425775674e-005</v>
+        <v>-3.9585097758878217e-006</v>
       </c>
       <c r="K26">
-        <v>-0.00027571195765492985</v>
+        <v>-0.00025166599501439974</v>
       </c>
       <c r="L26">
-        <v>-0.00025767891848559391</v>
+        <v>-0.00024747012169366346</v>
       </c>
       <c r="M26">
-        <v>0.00015200126383950376</v>
+        <v>0.00018008311292053592</v>
       </c>
       <c r="N26">
-        <v>-0.00086375479376982862</v>
+        <v>-0.00084984763262245739</v>
       </c>
       <c r="O26">
-        <v>-1.1090096878962864e-005</v>
+        <v>-1.1050233474489576e-005</v>
       </c>
       <c r="P26">
-        <v>-1.6367049456531821e-005</v>
+        <v>-1.596663815510015e-005</v>
       </c>
       <c r="Q26">
-        <v>0.0045180258877900855</v>
+        <v>0.0045250173365123155</v>
       </c>
       <c r="R26">
-        <v>0.0045049756999555463</v>
+        <v>0.0045111234723951869</v>
       </c>
       <c r="S26">
-        <v>0.004379235174620218</v>
+        <v>0.0043937614313859343</v>
       </c>
       <c r="T26">
-        <v>0.0045785681688785777</v>
+        <v>0.0045960476426064722</v>
       </c>
       <c r="U26">
-        <v>0.0043815688927323591</v>
+        <v>0.0043792376732927161</v>
       </c>
       <c r="V26">
-        <v>0.0044143215263017389</v>
+        <v>0.0044365655580845993</v>
       </c>
       <c r="W26">
-        <v>0.0044377691764211765</v>
+        <v>0.0044403509285291104</v>
       </c>
       <c r="X26">
-        <v>0.0045084551409850168</v>
+        <v>0.0045440937360955265</v>
       </c>
       <c r="Y26">
-        <v>0.0044798296690595086</v>
+        <v>0.0045005115654512921</v>
       </c>
       <c r="Z26">
-        <v>0.0044910822637637352</v>
+        <v>0.0045153170508096243</v>
       </c>
       <c r="AA26">
-        <v>0.0079913612321275522</v>
+        <v>0.0080001832550602621</v>
       </c>
       <c r="AB26">
-        <v>-9.6701332050080934e-006</v>
+        <v>-1.0544069994451776e-005</v>
       </c>
       <c r="AC26">
-        <v>-0.00046778980578362963</v>
+        <v>-0.0004726170569539949</v>
       </c>
       <c r="AD26">
-        <v>2.1537604811967267e-005</v>
+        <v>2.6544025858930484e-005</v>
       </c>
       <c r="AE26">
-        <v>0.0019858209277731093</v>
+        <v>0.0020019510590734303</v>
       </c>
       <c r="AF26">
-        <v>0.0032164466256521464</v>
+        <v>0.003242294489358883</v>
       </c>
       <c r="AG26">
-        <v>0.0012956974282763215</v>
+        <v>0.0010469865772954699</v>
       </c>
       <c r="AH26">
-        <v>-0.0072614458353719505</v>
+        <v>-0.0073577663560149189</v>
       </c>
     </row>
     <row r="27">
@@ -5412,103 +5412,103 @@
         <v>71</v>
       </c>
       <c r="B27" s="58">
-        <v>-0.022270732406206795</v>
+        <v>-0.022325442621004828</v>
       </c>
       <c r="C27">
-        <v>9.8041021552147103e-008</v>
+        <v>-5.8056569501719452e-008</v>
       </c>
       <c r="D27">
-        <v>-2.4787148813200225e-005</v>
+        <v>-2.5078399585291497e-005</v>
       </c>
       <c r="E27">
-        <v>1.5422978519739519e-007</v>
+        <v>1.5673365123438239e-007</v>
       </c>
       <c r="F27">
-        <v>7.9975613732996471e-006</v>
+        <v>7.9745841928764217e-006</v>
       </c>
       <c r="G27">
-        <v>3.7553873130868101e-005</v>
+        <v>3.7642719560101116e-005</v>
       </c>
       <c r="H27">
-        <v>8.2228923339043136e-005</v>
+        <v>8.1943351384202562e-005</v>
       </c>
       <c r="I27">
-        <v>5.5224874918293561e-005</v>
+        <v>5.5522296960544603e-005</v>
       </c>
       <c r="J27">
-        <v>4.2409859864229088e-005</v>
+        <v>4.0758003315093919e-005</v>
       </c>
       <c r="K27">
-        <v>5.3716926110596392e-005</v>
+        <v>5.2598959074161194e-005</v>
       </c>
       <c r="L27">
-        <v>5.350073064821882e-005</v>
+        <v>5.2071056516731572e-005</v>
       </c>
       <c r="M27">
-        <v>4.7193339386871017e-005</v>
+        <v>4.6065579995174311e-005</v>
       </c>
       <c r="N27">
-        <v>9.2010256900431719e-006</v>
+        <v>8.6458215088697105e-006</v>
       </c>
       <c r="O27">
-        <v>4.6944373475961972e-007</v>
+        <v>4.7690028282287007e-007</v>
       </c>
       <c r="P27">
-        <v>1.1399215541703141e-006</v>
+        <v>1.161740058585554e-006</v>
       </c>
       <c r="Q27">
-        <v>-2.9016190706503183e-005</v>
+        <v>-3.0017280472275498e-005</v>
       </c>
       <c r="R27">
-        <v>-1.5378794077151487e-005</v>
+        <v>-1.6622386995935939e-005</v>
       </c>
       <c r="S27">
-        <v>-2.5018717378174825e-005</v>
+        <v>-2.5839820439571635e-005</v>
       </c>
       <c r="T27">
-        <v>-3.5125877717720797e-007</v>
+        <v>-1.282341499608308e-006</v>
       </c>
       <c r="U27">
-        <v>-1.1709328923217208e-005</v>
+        <v>-1.2453839990589283e-005</v>
       </c>
       <c r="V27">
-        <v>-5.3893069807236225e-006</v>
+        <v>-5.8760228070261204e-006</v>
       </c>
       <c r="W27">
-        <v>-1.5952207275908052e-005</v>
+        <v>-1.6897550593139865e-005</v>
       </c>
       <c r="X27">
-        <v>1.0608494910703623e-009</v>
+        <v>-5.1779918875337859e-007</v>
       </c>
       <c r="Y27">
-        <v>-5.9599377844296076e-006</v>
+        <v>-5.8220095182255356e-006</v>
       </c>
       <c r="Z27">
-        <v>-1.2081414757277021e-005</v>
+        <v>-1.2818559623989413e-005</v>
       </c>
       <c r="AA27">
-        <v>-9.6701332050080934e-006</v>
+        <v>-1.0544069994451776e-005</v>
       </c>
       <c r="AB27">
-        <v>3.5480266552381437e-005</v>
+        <v>3.5447063535979491e-005</v>
       </c>
       <c r="AC27">
-        <v>-0.00015154091520933017</v>
+        <v>-0.00015118407474546127</v>
       </c>
       <c r="AD27">
-        <v>-0.00018023618716100275</v>
+        <v>-0.0001804888654457294</v>
       </c>
       <c r="AE27">
-        <v>-1.3640136812304742e-005</v>
+        <v>-1.4997555876432875e-005</v>
       </c>
       <c r="AF27">
-        <v>-3.6362874558384115e-005</v>
+        <v>-3.685547852687966e-005</v>
       </c>
       <c r="AG27">
-        <v>8.1272265389412232e-005</v>
+        <v>4.294321706028431e-005</v>
       </c>
       <c r="AH27">
-        <v>0.00022268895337598246</v>
+        <v>0.00023213381033761914</v>
       </c>
     </row>
     <row r="28">
@@ -5516,103 +5516,103 @@
         <v>72</v>
       </c>
       <c r="B28" s="60">
-        <v>-0.095687132454293958</v>
+        <v>-0.095091661064429775</v>
       </c>
       <c r="C28">
-        <v>0.00024189102194164917</v>
+        <v>0.00024285737306896146</v>
       </c>
       <c r="D28">
-        <v>-7.1568605463563119e-005</v>
+        <v>-7.0956729907799623e-005</v>
       </c>
       <c r="E28">
-        <v>4.6362348524869867e-007</v>
+        <v>4.582745965067079e-007</v>
       </c>
       <c r="F28">
-        <v>4.2897866707225431e-005</v>
+        <v>4.4072456063990468e-005</v>
       </c>
       <c r="G28">
-        <v>0.00019126606738275066</v>
+        <v>0.00018890675867596103</v>
       </c>
       <c r="H28">
-        <v>0.0001219768268978863</v>
+        <v>0.0001221501864607003</v>
       </c>
       <c r="I28">
-        <v>-0.0005200261446622669</v>
+        <v>-0.00051970201999667915</v>
       </c>
       <c r="J28">
-        <v>-0.0002919541515715404</v>
+        <v>-0.00028368883087819663</v>
       </c>
       <c r="K28">
-        <v>-0.00020216445427437244</v>
+        <v>-0.00019475414661159133</v>
       </c>
       <c r="L28">
-        <v>-0.00013208860999716615</v>
+        <v>-0.00012350492459081838</v>
       </c>
       <c r="M28">
-        <v>-0.00026729841128667091</v>
+        <v>-0.00026226505850798743</v>
       </c>
       <c r="N28">
-        <v>1.4247399345001104e-005</v>
+        <v>1.5154491979107226e-005</v>
       </c>
       <c r="O28">
-        <v>-3.0645800434848281e-006</v>
+        <v>-3.1184752206328778e-006</v>
       </c>
       <c r="P28">
-        <v>-9.1380285999287027e-006</v>
+        <v>-9.2712599328622994e-006</v>
       </c>
       <c r="Q28">
-        <v>-0.00047262122166437593</v>
+        <v>-0.00047886181699185445</v>
       </c>
       <c r="R28">
-        <v>-0.00041610900961192281</v>
+        <v>-0.00041751678414729174</v>
       </c>
       <c r="S28">
-        <v>-0.00024658862539125279</v>
+        <v>-0.00025098057037031081</v>
       </c>
       <c r="T28">
-        <v>1.7133551549641747e-005</v>
+        <v>1.3629212373405565e-005</v>
       </c>
       <c r="U28">
-        <v>-0.00045947447657942314</v>
+        <v>-0.00046342542455989131</v>
       </c>
       <c r="V28">
-        <v>-0.00034266503006918252</v>
+        <v>-0.00035018724074283985</v>
       </c>
       <c r="W28">
-        <v>-0.00025050362407433394</v>
+        <v>-0.00025400151325079669</v>
       </c>
       <c r="X28">
-        <v>-0.00048686766689544109</v>
+        <v>-0.0004881801286019075</v>
       </c>
       <c r="Y28">
-        <v>-0.00038921007535020212</v>
+        <v>-0.00039712586549750506</v>
       </c>
       <c r="Z28">
-        <v>-0.00024530378162208356</v>
+        <v>-0.00025119587401667708</v>
       </c>
       <c r="AA28">
-        <v>-0.00046778980578362963</v>
+        <v>-0.0004726170569539949</v>
       </c>
       <c r="AB28">
-        <v>-0.00015154091520933017</v>
+        <v>-0.00015118407474546127</v>
       </c>
       <c r="AC28">
-        <v>0.0063641960974797447</v>
+        <v>0.0063450000159098957</v>
       </c>
       <c r="AD28">
-        <v>0.0012276999518193213</v>
+        <v>0.0012283185379452243</v>
       </c>
       <c r="AE28">
-        <v>-8.0884329944847736e-005</v>
+        <v>-7.8348400127564981e-005</v>
       </c>
       <c r="AF28">
-        <v>-8.9394304962520099e-005</v>
+        <v>-9.4782249834445519e-005</v>
       </c>
       <c r="AG28">
-        <v>-0.0003560371088807509</v>
+        <v>-0.00032216493576712774</v>
       </c>
       <c r="AH28">
-        <v>0.005624265028120589</v>
+        <v>0.0056099886505088098</v>
       </c>
     </row>
     <row r="29">
@@ -5620,103 +5620,103 @@
         <v>73</v>
       </c>
       <c r="B29" s="62">
-        <v>0.033220764153930944</v>
+        <v>0.033268061759504697</v>
       </c>
       <c r="C29">
-        <v>0.00027084656310150411</v>
+        <v>0.00027299706461664664</v>
       </c>
       <c r="D29">
-        <v>4.9093640712729019e-006</v>
+        <v>6.8849653725101996e-006</v>
       </c>
       <c r="E29">
-        <v>-1.0890154332727756e-007</v>
+        <v>-1.2202591966686603e-007</v>
       </c>
       <c r="F29">
-        <v>0.00013206656487358076</v>
+        <v>0.00013061181470744079</v>
       </c>
       <c r="G29">
-        <v>0.00013199117929681522</v>
+        <v>0.00012871115886852369</v>
       </c>
       <c r="H29">
-        <v>0.00013516010768858792</v>
+        <v>0.00013351884714512348</v>
       </c>
       <c r="I29">
-        <v>-0.00036028104304878774</v>
+        <v>-0.00036058967749348858</v>
       </c>
       <c r="J29">
-        <v>-3.3614499220319387e-005</v>
+        <v>-2.3910110003504156e-005</v>
       </c>
       <c r="K29">
-        <v>0.00010160611257649843</v>
+        <v>0.00010780576194735336</v>
       </c>
       <c r="L29">
-        <v>-0.00012329542433654392</v>
+        <v>-0.00011351503032112651</v>
       </c>
       <c r="M29">
-        <v>-5.5506595811832468e-005</v>
+        <v>-5.018473570997129e-005</v>
       </c>
       <c r="N29">
-        <v>0.00027256776610522329</v>
+        <v>0.0002784889799418137</v>
       </c>
       <c r="O29">
-        <v>-4.3642271318599857e-006</v>
+        <v>-4.2661558382127933e-006</v>
       </c>
       <c r="P29">
-        <v>-7.9742205118265739e-007</v>
+        <v>-9.1133321784729613e-007</v>
       </c>
       <c r="Q29">
-        <v>0.00018394209430102238</v>
+        <v>0.00018886171291712016</v>
       </c>
       <c r="R29">
-        <v>2.7747281600076486e-005</v>
+        <v>3.2292080787612801e-005</v>
       </c>
       <c r="S29">
-        <v>0.00031449837564417323</v>
+        <v>0.00031896914087022526</v>
       </c>
       <c r="T29">
-        <v>-0.00017302912446730284</v>
+        <v>-0.00017023947513039904</v>
       </c>
       <c r="U29">
-        <v>-3.7281631257952226e-006</v>
+        <v>-9.1441644578781891e-007</v>
       </c>
       <c r="V29">
-        <v>8.4918994787493634e-005</v>
+        <v>8.8727838504066588e-005</v>
       </c>
       <c r="W29">
-        <v>-1.3829772365725365e-005</v>
+        <v>-8.9780183348540964e-006</v>
       </c>
       <c r="X29">
-        <v>-0.00011013681099597206</v>
+        <v>-0.00010656350159576319</v>
       </c>
       <c r="Y29">
-        <v>0.0008629334652918133</v>
+        <v>0.00086351559759223853</v>
       </c>
       <c r="Z29">
-        <v>0.0001010009993970551</v>
+        <v>0.00010456921588847175</v>
       </c>
       <c r="AA29">
-        <v>2.1537604811967267e-005</v>
+        <v>2.6544025858930484e-005</v>
       </c>
       <c r="AB29">
-        <v>-0.00018023618716100275</v>
+        <v>-0.0001804888654457294</v>
       </c>
       <c r="AC29">
-        <v>0.0012276999518193213</v>
+        <v>0.0012283185379452243</v>
       </c>
       <c r="AD29">
-        <v>0.0057900448523417903</v>
+        <v>0.0057873711135761731</v>
       </c>
       <c r="AE29">
-        <v>9.5890684405899526e-006</v>
+        <v>1.8020304025665856e-005</v>
       </c>
       <c r="AF29">
-        <v>7.3146297145975855e-005</v>
+        <v>7.7347014132476185e-005</v>
       </c>
       <c r="AG29">
-        <v>-0.00027487472792723253</v>
+        <v>-0.00012995715468037527</v>
       </c>
       <c r="AH29">
-        <v>0.0025170042559447851</v>
+        <v>0.0024411545717711062</v>
       </c>
     </row>
     <row r="30">
@@ -5724,103 +5724,103 @@
         <v>74</v>
       </c>
       <c r="B30" s="64">
-        <v>-0.060756540245491861</v>
+        <v>-0.062455264419143286</v>
       </c>
       <c r="C30">
-        <v>0.0001074943376380773</v>
+        <v>0.00010591189563416469</v>
       </c>
       <c r="D30">
-        <v>5.7976202840374219e-005</v>
+        <v>5.9172976478023137e-005</v>
       </c>
       <c r="E30">
-        <v>-3.8182573147390111e-007</v>
+        <v>-3.8744391651259337e-007</v>
       </c>
       <c r="F30">
-        <v>-1.2124895440969658e-005</v>
+        <v>-1.4706941598042718e-005</v>
       </c>
       <c r="G30">
-        <v>-0.00023644010026557805</v>
+        <v>-0.00023683818894313236</v>
       </c>
       <c r="H30">
-        <v>-6.21703619920113e-005</v>
+        <v>-6.0357323272133487e-005</v>
       </c>
       <c r="I30">
-        <v>-0.00035394575412383417</v>
+        <v>-0.00035877906580602213</v>
       </c>
       <c r="J30">
-        <v>0.00026899140026040327</v>
+        <v>0.00024885137786572527</v>
       </c>
       <c r="K30">
-        <v>0.00030052083731404132</v>
+        <v>0.00028884806339839306</v>
       </c>
       <c r="L30">
-        <v>0.00032305703269878429</v>
+        <v>0.00030433484428222992</v>
       </c>
       <c r="M30">
-        <v>0.00035579202565603129</v>
+        <v>0.00034515252592353524</v>
       </c>
       <c r="N30">
-        <v>0.00011325031857949285</v>
+        <v>0.00011393711548309037</v>
       </c>
       <c r="O30">
-        <v>-2.5323665983099182e-006</v>
+        <v>-2.5242242813121687e-006</v>
       </c>
       <c r="P30">
-        <v>-1.118041368553518e-005</v>
+        <v>-1.0879904245285747e-005</v>
       </c>
       <c r="Q30">
-        <v>0.0017481211648762746</v>
+        <v>0.0017580860196611211</v>
       </c>
       <c r="R30">
-        <v>0.0016605573957851421</v>
+        <v>0.0016652690023666859</v>
       </c>
       <c r="S30">
-        <v>0.0016365071053053065</v>
+        <v>0.0016505758498428255</v>
       </c>
       <c r="T30">
-        <v>0.0015359932535348156</v>
+        <v>0.0015513746894397732</v>
       </c>
       <c r="U30">
-        <v>0.0011776755149863127</v>
+        <v>0.0011828160980148041</v>
       </c>
       <c r="V30">
-        <v>0.001582770996282249</v>
+        <v>0.0016020519241820594</v>
       </c>
       <c r="W30">
-        <v>0.0016740267262388931</v>
+        <v>0.0016847676746109496</v>
       </c>
       <c r="X30">
-        <v>0.0017490971485472802</v>
+        <v>0.0017684976130275239</v>
       </c>
       <c r="Y30">
-        <v>0.0018678280985273527</v>
+        <v>0.0018826994132921629</v>
       </c>
       <c r="Z30">
-        <v>0.0017644715469949269</v>
+        <v>0.0017832486769061081</v>
       </c>
       <c r="AA30">
-        <v>0.0019858209277731093</v>
+        <v>0.0020019510590734303</v>
       </c>
       <c r="AB30">
-        <v>-1.3640136812304742e-005</v>
+        <v>-1.4997555876432875e-005</v>
       </c>
       <c r="AC30">
-        <v>-8.0884329944847736e-005</v>
+        <v>-7.8348400127564981e-005</v>
       </c>
       <c r="AD30">
-        <v>9.5890684405899526e-006</v>
+        <v>1.8020304025665856e-005</v>
       </c>
       <c r="AE30">
-        <v>0.0094665319745229105</v>
+        <v>0.009460594899688932</v>
       </c>
       <c r="AF30">
-        <v>0.0014641755331504015</v>
+        <v>0.0014819704497695831</v>
       </c>
       <c r="AG30">
-        <v>0.00060235951905336204</v>
+        <v>0.00058189440058690708</v>
       </c>
       <c r="AH30">
-        <v>-0.0031631723352119967</v>
+        <v>-0.0032132298677780614</v>
       </c>
     </row>
     <row r="31">
@@ -5828,103 +5828,103 @@
         <v>75</v>
       </c>
       <c r="B31" s="66">
-        <v>-0.16422303035578376</v>
+        <v>-0.16543716210415219</v>
       </c>
       <c r="C31">
-        <v>-5.5779166842884718e-005</v>
+        <v>-5.7078248827969417e-005</v>
       </c>
       <c r="D31">
-        <v>0.00014072943821787781</v>
+        <v>0.00014136081967768693</v>
       </c>
       <c r="E31">
-        <v>-9.9428078608149e-007</v>
+        <v>-9.9650222027005244e-007</v>
       </c>
       <c r="F31">
-        <v>-0.00015196470410332782</v>
+        <v>-0.00015468192018798011</v>
       </c>
       <c r="G31">
-        <v>-0.00017348664564065881</v>
+        <v>-0.00016619995782553298</v>
       </c>
       <c r="H31">
-        <v>-3.1305723117071999e-005</v>
+        <v>-2.4282177742245004e-005</v>
       </c>
       <c r="I31">
-        <v>-0.00018755997337610748</v>
+        <v>-0.00017491402943353891</v>
       </c>
       <c r="J31">
-        <v>-1.6928540464836769e-005</v>
+        <v>-1.6513062395338146e-006</v>
       </c>
       <c r="K31">
-        <v>-0.00025202629325109596</v>
+        <v>-0.00023207430019676054</v>
       </c>
       <c r="L31">
-        <v>-0.00024068436912990212</v>
+        <v>-0.00023084441795196602</v>
       </c>
       <c r="M31">
-        <v>0.00019750289991326674</v>
+        <v>0.00022279463100959105</v>
       </c>
       <c r="N31">
-        <v>-0.00027352599018089869</v>
+        <v>-0.00026364471485490677</v>
       </c>
       <c r="O31">
-        <v>-6.2780760006232988e-006</v>
+        <v>-6.2728560110516846e-006</v>
       </c>
       <c r="P31">
-        <v>-1.4768927175091225e-005</v>
+        <v>-1.4488505380382428e-005</v>
       </c>
       <c r="Q31">
-        <v>0.0031817038263297222</v>
+        <v>0.0031983623043224207</v>
       </c>
       <c r="R31">
-        <v>0.0030733863421157533</v>
+        <v>0.003089011713988097</v>
       </c>
       <c r="S31">
-        <v>0.0028708237296867956</v>
+        <v>0.0028929747397056244</v>
       </c>
       <c r="T31">
-        <v>0.0031448871209165731</v>
+        <v>0.0031706616403304757</v>
       </c>
       <c r="U31">
-        <v>0.0027456761097331985</v>
+        <v>0.0027547298535770528</v>
       </c>
       <c r="V31">
-        <v>0.0030752642553974995</v>
+        <v>0.0031031974837165328</v>
       </c>
       <c r="W31">
-        <v>0.0029716097648097512</v>
+        <v>0.0029839414203983354</v>
       </c>
       <c r="X31">
-        <v>0.0030471301384141988</v>
+        <v>0.0030833213827379784</v>
       </c>
       <c r="Y31">
-        <v>0.003129184585592418</v>
+        <v>0.0031535758672299168</v>
       </c>
       <c r="Z31">
-        <v>0.0031563807356067937</v>
+        <v>0.0031874655129236263</v>
       </c>
       <c r="AA31">
-        <v>0.0032164466256521464</v>
+        <v>0.003242294489358883</v>
       </c>
       <c r="AB31">
-        <v>-3.6362874558384115e-005</v>
+        <v>-3.685547852687966e-005</v>
       </c>
       <c r="AC31">
-        <v>-8.9394304962520099e-005</v>
+        <v>-9.4782249834445519e-005</v>
       </c>
       <c r="AD31">
-        <v>7.3146297145975855e-005</v>
+        <v>7.7347014132476185e-005</v>
       </c>
       <c r="AE31">
-        <v>0.0014641755331504015</v>
+        <v>0.0014819704497695831</v>
       </c>
       <c r="AF31">
-        <v>0.008866790776314094</v>
+        <v>0.0088990944098087908</v>
       </c>
       <c r="AG31">
-        <v>0.00095070916251311667</v>
+        <v>0.00091691908134480153</v>
       </c>
       <c r="AH31">
-        <v>-0.0060977869766199299</v>
+        <v>-0.006187198302084038</v>
       </c>
     </row>
     <row r="32">
@@ -5932,103 +5932,103 @@
         <v>76</v>
       </c>
       <c r="B32" s="68">
-        <v>0.13620924197685982</v>
+        <v>0.039852664637545041</v>
       </c>
       <c r="C32">
-        <v>-3.1344449251640436e-005</v>
+        <v>-7.4029581693176244e-005</v>
       </c>
       <c r="D32">
-        <v>-0.00020998648002043367</v>
+        <v>-0.00012849749576103117</v>
       </c>
       <c r="E32">
-        <v>1.0475677959670686e-006</v>
+        <v>7.1453513400016207e-007</v>
       </c>
       <c r="F32">
-        <v>-7.9596089003693984e-007</v>
+        <v>-4.2782723654834865e-005</v>
       </c>
       <c r="G32">
-        <v>0.00068130442701288922</v>
+        <v>0.00046921443000293205</v>
       </c>
       <c r="H32">
-        <v>0.00062078379609775778</v>
+        <v>0.00044695214019631595</v>
       </c>
       <c r="I32">
-        <v>7.6109867914079567e-005</v>
+        <v>0.00016006464235047892</v>
       </c>
       <c r="J32">
-        <v>0.00057241653331254502</v>
+        <v>0.00042103162078545764</v>
       </c>
       <c r="K32">
-        <v>-5.5478406149225335e-005</v>
+        <v>0.00017494730059802667</v>
       </c>
       <c r="L32">
-        <v>0.00018481443389585083</v>
+        <v>9.3763179742039141e-005</v>
       </c>
       <c r="M32">
-        <v>0.00044584606809503066</v>
+        <v>0.00049067050124961095</v>
       </c>
       <c r="N32">
-        <v>-0.00084024514577010865</v>
+        <v>-0.00032225494974379355</v>
       </c>
       <c r="O32">
-        <v>-4.9426247473076737e-006</v>
+        <v>-2.791041384473235e-006</v>
       </c>
       <c r="P32">
-        <v>-7.1234386532692521e-006</v>
+        <v>-1.4097114503809345e-007</v>
       </c>
       <c r="Q32">
-        <v>0.0012059012449505226</v>
+        <v>0.00083947930311241274</v>
       </c>
       <c r="R32">
-        <v>0.0011205039065298105</v>
+        <v>0.0008018143446887234</v>
       </c>
       <c r="S32">
-        <v>0.0010047526480274848</v>
+        <v>0.00080877730753728307</v>
       </c>
       <c r="T32">
-        <v>0.0012060806748531955</v>
+        <v>0.00099766873034227424</v>
       </c>
       <c r="U32">
-        <v>0.0010602267703547831</v>
+        <v>0.00061772670646473326</v>
       </c>
       <c r="V32">
-        <v>0.00080262942849036625</v>
+        <v>0.00080997150630304998</v>
       </c>
       <c r="W32">
-        <v>0.0010347403588517228</v>
+        <v>0.00067550998153724788</v>
       </c>
       <c r="X32">
-        <v>0.00026534736088187037</v>
+        <v>0.00067444117084719231</v>
       </c>
       <c r="Y32">
-        <v>0.00038995281757131669</v>
+        <v>0.00052346539664983481</v>
       </c>
       <c r="Z32">
-        <v>0.0011806550761511219</v>
+        <v>0.0010635818670413776</v>
       </c>
       <c r="AA32">
-        <v>0.0012956974282763215</v>
+        <v>0.0010469865772954699</v>
       </c>
       <c r="AB32">
-        <v>8.1272265389412232e-005</v>
+        <v>4.294321706028431e-005</v>
       </c>
       <c r="AC32">
-        <v>-0.0003560371088807509</v>
+        <v>-0.00032216493576712774</v>
       </c>
       <c r="AD32">
-        <v>-0.00027487472792723253</v>
+        <v>-0.00012995715468037527</v>
       </c>
       <c r="AE32">
-        <v>0.00060235951905336204</v>
+        <v>0.00058189440058690708</v>
       </c>
       <c r="AF32">
-        <v>0.00095070916251311667</v>
+        <v>0.00091691908134480153</v>
       </c>
       <c r="AG32">
-        <v>0.02649474115235638</v>
+        <v>0.013664545583987019</v>
       </c>
       <c r="AH32">
-        <v>0.0065812261217162472</v>
+        <v>0.0031383550768593156</v>
       </c>
     </row>
     <row r="33">
@@ -6036,103 +6036,103 @@
         <v>77</v>
       </c>
       <c r="B33" s="70">
-        <v>-18.833846177726048</v>
+        <v>-18.822070783824319</v>
       </c>
       <c r="C33">
-        <v>0.0048086176920118413</v>
+        <v>0.0047689368203999048</v>
       </c>
       <c r="D33">
-        <v>-0.049491925000990214</v>
+        <v>-0.04948307015474266</v>
       </c>
       <c r="E33">
-        <v>0.00037280735200578998</v>
+        <v>0.00037267539835023793</v>
       </c>
       <c r="F33">
-        <v>0.00091564648663443749</v>
+        <v>0.00092041665261907908</v>
       </c>
       <c r="G33">
-        <v>0.0012549964776884474</v>
+        <v>0.0013234439236597081</v>
       </c>
       <c r="H33">
-        <v>0.018877120490660964</v>
+        <v>0.018881135012059978</v>
       </c>
       <c r="I33">
-        <v>-0.011430772984092463</v>
+        <v>-0.011232066092847175</v>
       </c>
       <c r="J33">
-        <v>-0.00054365585265792548</v>
+        <v>-0.00038985163851377579</v>
       </c>
       <c r="K33">
-        <v>-0.0041882289970275807</v>
+        <v>-0.0041181309685079104</v>
       </c>
       <c r="L33">
-        <v>-0.0014754839421946475</v>
+        <v>-0.0013814950383732511</v>
       </c>
       <c r="M33">
-        <v>-0.0046957001947725147</v>
+        <v>-0.004569063846149338</v>
       </c>
       <c r="N33">
-        <v>0.002212650853788333</v>
+        <v>0.0020793638939352347</v>
       </c>
       <c r="O33">
-        <v>-0.00014012776881665252</v>
+        <v>-0.00013909885257408199</v>
       </c>
       <c r="P33">
-        <v>-0.0001400155663921891</v>
+        <v>-0.00013886736225618673</v>
       </c>
       <c r="Q33">
-        <v>-0.0053555860190492525</v>
+        <v>-0.0054567612245047855</v>
       </c>
       <c r="R33">
-        <v>-0.0043730982503792466</v>
+        <v>-0.0045096747070545182</v>
       </c>
       <c r="S33">
-        <v>-0.0025909203964719278</v>
+        <v>-0.0027156715441482761</v>
       </c>
       <c r="T33">
-        <v>-0.0019732405212521168</v>
+        <v>-0.0020782339861934594</v>
       </c>
       <c r="U33">
-        <v>-0.0043539141744750182</v>
+        <v>-0.0044316990434977339</v>
       </c>
       <c r="V33">
-        <v>-0.0046888986886717554</v>
+        <v>-0.0048189745475510923</v>
       </c>
       <c r="W33">
-        <v>-0.0036578899468770105</v>
+        <v>-0.003770931809172361</v>
       </c>
       <c r="X33">
-        <v>-0.003127679824341755</v>
+        <v>-0.0032123679077894788</v>
       </c>
       <c r="Y33">
-        <v>-0.0058778451857606296</v>
+        <v>-0.0059245720874912628</v>
       </c>
       <c r="Z33">
-        <v>-0.0041652756734506663</v>
+        <v>-0.0042706723905415571</v>
       </c>
       <c r="AA33">
-        <v>-0.0072614458353719505</v>
+        <v>-0.0073577663560149189</v>
       </c>
       <c r="AB33">
-        <v>0.00022268895337598246</v>
+        <v>0.00023213381033761914</v>
       </c>
       <c r="AC33">
-        <v>0.005624265028120589</v>
+        <v>0.0056099886505088098</v>
       </c>
       <c r="AD33">
-        <v>0.0025170042559447851</v>
+        <v>0.0024411545717711062</v>
       </c>
       <c r="AE33">
-        <v>-0.0031631723352119967</v>
+        <v>-0.0032132298677780614</v>
       </c>
       <c r="AF33">
-        <v>-0.0060977869766199299</v>
+        <v>-0.006187198302084038</v>
       </c>
       <c r="AG33">
-        <v>0.0065812261217162472</v>
+        <v>0.0031383550768593156</v>
       </c>
       <c r="AH33">
-        <v>1.6304988860956942</v>
+        <v>1.6302036939636992</v>
       </c>
     </row>
   </sheetData>
@@ -6265,115 +6265,115 @@
         <v>46</v>
       </c>
       <c r="B2" s="75">
-        <v>-0.034161121964383999</v>
+        <v>-0.03447310786181193</v>
       </c>
       <c r="C2">
-        <v>0.0004806493644211548</v>
+        <v>0.00048054566313035453</v>
       </c>
       <c r="D2">
-        <v>6.8282281744452876e-005</v>
+        <v>6.8169874321088094e-005</v>
       </c>
       <c r="E2">
-        <v>-6.9303614956544206e-007</v>
+        <v>-6.9209656383056889e-007</v>
       </c>
       <c r="F2">
-        <v>1.315523763110285e-005</v>
+        <v>1.3391970779690512e-005</v>
       </c>
       <c r="G2">
-        <v>1.9594426935733331e-005</v>
+        <v>2.0308155448938514e-005</v>
       </c>
       <c r="H2">
-        <v>0.00020140555045630542</v>
+        <v>0.00020151017086252724</v>
       </c>
       <c r="I2">
-        <v>0.00015264981821094155</v>
+        <v>0.00015276505175979683</v>
       </c>
       <c r="J2">
-        <v>-5.0914324036196768e-005</v>
+        <v>-5.1408264038339519e-005</v>
       </c>
       <c r="K2">
-        <v>0.00010126360180286576</v>
+        <v>0.00010140399935176278</v>
       </c>
       <c r="L2">
-        <v>0.00012245249611382439</v>
+        <v>0.00012185472924296953</v>
       </c>
       <c r="M2">
-        <v>9.6694742619722937e-005</v>
+        <v>9.6521384278589587e-005</v>
       </c>
       <c r="N2">
-        <v>0.00010467926566299976</v>
+        <v>0.00010444558569330413</v>
       </c>
       <c r="O2">
-        <v>-6.9526272724531758e-005</v>
+        <v>-6.9607966719087078e-005</v>
       </c>
       <c r="P2">
-        <v>4.6321500715517949e-007</v>
+        <v>4.7895691363334313e-007</v>
       </c>
       <c r="Q2">
-        <v>-2.5066602346869103e-006</v>
+        <v>-2.5040279840891912e-006</v>
       </c>
       <c r="R2">
-        <v>4.2133390487461083e-005</v>
+        <v>4.1875944996539152e-005</v>
       </c>
       <c r="S2">
-        <v>-3.1168353987290242e-005</v>
+        <v>-3.1098711971204675e-005</v>
       </c>
       <c r="T2">
-        <v>-5.1446202449047057e-006</v>
+        <v>-5.4613813978297603e-006</v>
       </c>
       <c r="U2">
-        <v>-3.700345368141268e-005</v>
+        <v>-3.7480288703548542e-005</v>
       </c>
       <c r="V2">
-        <v>-4.9591308710746426e-005</v>
+        <v>-4.9980629689385994e-005</v>
       </c>
       <c r="W2">
-        <v>-6.2267434250050691e-005</v>
+        <v>-6.2602483746615852e-005</v>
       </c>
       <c r="X2">
-        <v>-5.826686717243177e-005</v>
+        <v>-5.8408117287658447e-005</v>
       </c>
       <c r="Y2">
-        <v>-5.0174190819130785e-005</v>
+        <v>-5.042314594800197e-005</v>
       </c>
       <c r="Z2">
-        <v>-4.2629870900569591e-005</v>
+        <v>-4.3082702626064534e-005</v>
       </c>
       <c r="AA2">
-        <v>-2.4561806571481832e-005</v>
+        <v>-2.5142560580283122e-005</v>
       </c>
       <c r="AB2">
-        <v>-2.7528087196425463e-005</v>
+        <v>-2.8019454047388755e-005</v>
       </c>
       <c r="AC2">
-        <v>-3.8584073993231703e-005</v>
+        <v>-3.8873262195926312e-005</v>
       </c>
       <c r="AD2">
-        <v>-4.0237992835788979e-005</v>
+        <v>-4.0781699915135067e-005</v>
       </c>
       <c r="AE2">
-        <v>-5.2713845064020817e-005</v>
+        <v>-5.3070412191997546e-005</v>
       </c>
       <c r="AF2">
-        <v>4.3997728352519513e-006</v>
+        <v>4.4081203476355868e-006</v>
       </c>
       <c r="AG2">
-        <v>2.825831297490757e-005</v>
+        <v>2.80317234043927e-005</v>
       </c>
       <c r="AH2">
-        <v>-1.6696286098243872e-005</v>
+        <v>-1.6797083993527142e-005</v>
       </c>
       <c r="AI2">
-        <v>-2.8283079227622628e-005</v>
+        <v>-2.8608954356871651e-005</v>
       </c>
       <c r="AJ2">
-        <v>-5.1206342478769679e-005</v>
+        <v>-5.1467791083552262e-005</v>
       </c>
       <c r="AK2">
-        <v>-1.9136798726858858e-005</v>
+        <v>-3.9035868766022969e-005</v>
       </c>
       <c r="AL2">
-        <v>-0.0019417559221799605</v>
+        <v>-0.0019388168715905106</v>
       </c>
     </row>
     <row r="3">
@@ -6381,115 +6381,115 @@
         <v>47</v>
       </c>
       <c r="B3" s="77">
-        <v>0.59122563143335727</v>
+        <v>0.5913074091800915</v>
       </c>
       <c r="C3">
-        <v>6.8282281744452876e-005</v>
+        <v>6.8169874321088094e-005</v>
       </c>
       <c r="D3">
-        <v>0.0013329631168077171</v>
+        <v>0.0013327943223072731</v>
       </c>
       <c r="E3">
-        <v>-1.0900429532265198e-005</v>
+        <v>-1.0899180329491088e-005</v>
       </c>
       <c r="F3">
-        <v>-8.6163718358647464e-005</v>
+        <v>-8.5991569613007705e-005</v>
       </c>
       <c r="G3">
-        <v>-0.00011573745334654269</v>
+        <v>-0.00011533239622853036</v>
       </c>
       <c r="H3">
-        <v>0.00029608704029219037</v>
+        <v>0.00029618887632656358</v>
       </c>
       <c r="I3">
-        <v>3.078598349173919e-005</v>
+        <v>3.0730948456256322e-005</v>
       </c>
       <c r="J3">
-        <v>-0.0001395469818511652</v>
+        <v>-0.00013962934166484155</v>
       </c>
       <c r="K3">
-        <v>-5.0342990750022916e-005</v>
+        <v>-4.9005020462896971e-005</v>
       </c>
       <c r="L3">
-        <v>-8.5926973353193893e-005</v>
+        <v>-8.5155543468328453e-005</v>
       </c>
       <c r="M3">
-        <v>-0.00012230094868889599</v>
+        <v>-0.00012157483164564314</v>
       </c>
       <c r="N3">
-        <v>-0.00014081176321063382</v>
+        <v>-0.00013980302881216032</v>
       </c>
       <c r="O3">
-        <v>-1.5991790664160368e-005</v>
+        <v>-1.5874402039881561e-005</v>
       </c>
       <c r="P3">
-        <v>1.5557924069219642e-006</v>
+        <v>1.5646142807599532e-006</v>
       </c>
       <c r="Q3">
-        <v>-1.4252508182781621e-006</v>
+        <v>-1.4236952524422704e-006</v>
       </c>
       <c r="R3">
-        <v>3.8752501768856687e-005</v>
+        <v>3.8714182876630528e-005</v>
       </c>
       <c r="S3">
-        <v>-2.4060211098254122e-005</v>
+        <v>-2.4219661080674597e-005</v>
       </c>
       <c r="T3">
-        <v>-5.990519389073275e-005</v>
+        <v>-5.9952122240905384e-005</v>
       </c>
       <c r="U3">
-        <v>4.795299316556062e-005</v>
+        <v>4.8130757723908318e-005</v>
       </c>
       <c r="V3">
-        <v>4.2991731641617986e-005</v>
+        <v>4.3202380057743087e-005</v>
       </c>
       <c r="W3">
-        <v>2.6073869286871373e-005</v>
+        <v>2.5909104870195168e-005</v>
       </c>
       <c r="X3">
-        <v>2.1326741956019524e-005</v>
+        <v>2.1228324798706899e-005</v>
       </c>
       <c r="Y3">
-        <v>6.5248669655279534e-006</v>
+        <v>6.8829809831329886e-006</v>
       </c>
       <c r="Z3">
-        <v>6.5657177947819889e-005</v>
+        <v>6.5535942142662743e-005</v>
       </c>
       <c r="AA3">
-        <v>4.2284153889774259e-005</v>
+        <v>4.2639364669928501e-005</v>
       </c>
       <c r="AB3">
-        <v>1.264920486046886e-005</v>
+        <v>1.2736551211482011e-005</v>
       </c>
       <c r="AC3">
-        <v>2.6957194944391555e-005</v>
+        <v>2.7164932519162244e-005</v>
       </c>
       <c r="AD3">
-        <v>2.2741333583514711e-005</v>
+        <v>2.2956164990747818e-005</v>
       </c>
       <c r="AE3">
-        <v>9.9940663438703031e-005</v>
+        <v>0.00010006604332136668</v>
       </c>
       <c r="AF3">
-        <v>9.4987469364925118e-006</v>
+        <v>9.582056843246531e-006</v>
       </c>
       <c r="AG3">
-        <v>-2.3403354315185501e-005</v>
+        <v>-2.3431608989230924e-005</v>
       </c>
       <c r="AH3">
-        <v>1.0742117965037749e-005</v>
+        <v>1.0495556920705367e-005</v>
       </c>
       <c r="AI3">
-        <v>-8.057292928381754e-006</v>
+        <v>-7.9362880805802782e-006</v>
       </c>
       <c r="AJ3">
-        <v>-0.00011342191296093151</v>
+        <v>-0.00011341801768253654</v>
       </c>
       <c r="AK3">
-        <v>1.3987053647662728e-005</v>
+        <v>3.5163098304277426e-005</v>
       </c>
       <c r="AL3">
-        <v>-0.040570056449759265</v>
+        <v>-0.040567455750415794</v>
       </c>
     </row>
     <row r="4">
@@ -6497,115 +6497,115 @@
         <v>48</v>
       </c>
       <c r="B4" s="79">
-        <v>-0.0042516864646499133</v>
+        <v>-0.0042524479493871821</v>
       </c>
       <c r="C4">
-        <v>-6.9303614956544206e-007</v>
+        <v>-6.9209656383056889e-007</v>
       </c>
       <c r="D4">
-        <v>-1.0900429532265198e-005</v>
+        <v>-1.0899180329491088e-005</v>
       </c>
       <c r="E4">
-        <v>8.9826390903513195e-008</v>
+        <v>8.9816994799382785e-008</v>
       </c>
       <c r="F4">
-        <v>6.7451507721619639e-007</v>
+        <v>6.7328806385624695e-007</v>
       </c>
       <c r="G4">
-        <v>8.7094158130583899e-007</v>
+        <v>8.6812980943284699e-007</v>
       </c>
       <c r="H4">
-        <v>-3.0614504003743554e-006</v>
+        <v>-3.061957620653273e-006</v>
       </c>
       <c r="I4">
-        <v>-2.6483490169331919e-007</v>
+        <v>-2.6455315093286075e-007</v>
       </c>
       <c r="J4">
-        <v>1.2413135751965185e-006</v>
+        <v>1.2421253466078569e-006</v>
       </c>
       <c r="K4">
-        <v>3.3086973453711141e-007</v>
+        <v>3.2039377567481623e-007</v>
       </c>
       <c r="L4">
-        <v>6.1213133691199168e-007</v>
+        <v>6.0642634654903012e-007</v>
       </c>
       <c r="M4">
-        <v>8.9593879367845706e-007</v>
+        <v>8.907091412946021e-007</v>
       </c>
       <c r="N4">
-        <v>1.0558107761729728e-006</v>
+        <v>1.0485392673048434e-006</v>
       </c>
       <c r="O4">
-        <v>8.869398411431883e-008</v>
+        <v>8.781820504187064e-008</v>
       </c>
       <c r="P4">
-        <v>-1.1148471551623142e-008</v>
+        <v>-1.1221662106904966e-008</v>
       </c>
       <c r="Q4">
-        <v>8.9102230330252389e-009</v>
+        <v>8.8948240721396237e-009</v>
       </c>
       <c r="R4">
-        <v>-5.4863004550240887e-007</v>
+        <v>-5.4835431088383163e-007</v>
       </c>
       <c r="S4">
-        <v>1.4830784317378119e-007</v>
+        <v>1.4969418434769993e-007</v>
       </c>
       <c r="T4">
-        <v>5.6935243250235008e-007</v>
+        <v>5.6974350465891802e-007</v>
       </c>
       <c r="U4">
-        <v>-3.5145538122851824e-007</v>
+        <v>-3.532575194766782e-007</v>
       </c>
       <c r="V4">
-        <v>-3.7216991367534957e-007</v>
+        <v>-3.7417060888370339e-007</v>
       </c>
       <c r="W4">
-        <v>-2.3580908268989737e-007</v>
+        <v>-2.3501041342042465e-007</v>
       </c>
       <c r="X4">
-        <v>-1.6672695676636109e-007</v>
+        <v>-1.6678487566103056e-007</v>
       </c>
       <c r="Y4">
-        <v>-3.7500265445943861e-008</v>
+        <v>-4.0623993365705821e-008</v>
       </c>
       <c r="Z4">
-        <v>-5.6019454807650939e-007</v>
+        <v>-5.5983144051850427e-007</v>
       </c>
       <c r="AA4">
-        <v>-3.9623613642080207e-007</v>
+        <v>-3.992153775717283e-007</v>
       </c>
       <c r="AB4">
-        <v>-1.6106916197582968e-007</v>
+        <v>-1.6210919784383107e-007</v>
       </c>
       <c r="AC4">
-        <v>-2.3525181102311034e-007</v>
+        <v>-2.3724628733144898e-007</v>
       </c>
       <c r="AD4">
-        <v>-2.0962513312875841e-007</v>
+        <v>-2.1177052323927679e-007</v>
       </c>
       <c r="AE4">
-        <v>-8.5127797982569075e-007</v>
+        <v>-8.5242632732147948e-007</v>
       </c>
       <c r="AF4">
-        <v>-9.4888899428429478e-008</v>
+        <v>-9.5530001529084797e-008</v>
       </c>
       <c r="AG4">
-        <v>1.5527146780202242e-007</v>
+        <v>1.5571807342978988e-007</v>
       </c>
       <c r="AH4">
-        <v>-7.8172404035512918e-008</v>
+        <v>-7.6115863414235584e-008</v>
       </c>
       <c r="AI4">
-        <v>1.0182430891224358e-007</v>
+        <v>1.0087321904517026e-007</v>
       </c>
       <c r="AJ4">
-        <v>9.0416399825733349e-007</v>
+        <v>9.0394600337078703e-007</v>
       </c>
       <c r="AK4">
-        <v>-9.2118835686501744e-008</v>
+        <v>-2.6414144115373438e-007</v>
       </c>
       <c r="AL4">
-        <v>0.00033003390444120398</v>
+        <v>0.00033001634025847518</v>
       </c>
     </row>
     <row r="5">
@@ -6613,115 +6613,115 @@
         <v>49</v>
       </c>
       <c r="B5" s="81">
-        <v>-0.078694745217343251</v>
+        <v>-0.078329498047196924</v>
       </c>
       <c r="C5">
-        <v>1.315523763110285e-005</v>
+        <v>1.3391970779690512e-005</v>
       </c>
       <c r="D5">
-        <v>-8.6163718358647464e-005</v>
+        <v>-8.5991569613007705e-005</v>
       </c>
       <c r="E5">
-        <v>6.7451507721619639e-007</v>
+        <v>6.7328806385624695e-007</v>
       </c>
       <c r="F5">
-        <v>0.00067015315378009439</v>
+        <v>0.00067013778251117067</v>
       </c>
       <c r="G5">
-        <v>0.00050310515568090892</v>
+        <v>0.00050317903055342554</v>
       </c>
       <c r="H5">
-        <v>1.7503132630498501e-005</v>
+        <v>1.8088712703125392e-005</v>
       </c>
       <c r="I5">
-        <v>1.2156385401286423e-005</v>
+        <v>1.3588380087457621e-005</v>
       </c>
       <c r="J5">
-        <v>-1.0418748862538797e-005</v>
+        <v>-1.0357245425133056e-005</v>
       </c>
       <c r="K5">
-        <v>4.2246545742092917e-005</v>
+        <v>4.1507904336539052e-005</v>
       </c>
       <c r="L5">
-        <v>3.7524187253459485e-005</v>
+        <v>3.7420557942554778e-005</v>
       </c>
       <c r="M5">
-        <v>7.788874763855264e-005</v>
+        <v>7.7622541999522638e-005</v>
       </c>
       <c r="N5">
-        <v>0.00018862247776443644</v>
+        <v>0.00018899509347567885</v>
       </c>
       <c r="O5">
-        <v>1.1868818560886662e-005</v>
+        <v>1.2038766213433952e-005</v>
       </c>
       <c r="P5">
-        <v>1.8223919841767059e-006</v>
+        <v>1.8542121040226296e-006</v>
       </c>
       <c r="Q5">
-        <v>7.316377118896582e-008</v>
+        <v>7.4447727517481539e-008</v>
       </c>
       <c r="R5">
-        <v>8.413565634335535e-006</v>
+        <v>7.5227331911805372e-006</v>
       </c>
       <c r="S5">
-        <v>5.2977449790130669e-005</v>
+        <v>5.3709170208596563e-005</v>
       </c>
       <c r="T5">
-        <v>-1.8471393522964249e-005</v>
+        <v>-1.9019670863845164e-005</v>
       </c>
       <c r="U5">
-        <v>-0.00012281038905223406</v>
+        <v>-0.0001244164895879972</v>
       </c>
       <c r="V5">
-        <v>-8.1509598987286469e-005</v>
+        <v>-8.295507258406084e-005</v>
       </c>
       <c r="W5">
-        <v>-6.6888872018463447e-005</v>
+        <v>-6.7848612160217487e-005</v>
       </c>
       <c r="X5">
-        <v>-0.00010006611722477488</v>
+        <v>-0.00010109399779700163</v>
       </c>
       <c r="Y5">
-        <v>-0.0001263081914369294</v>
+        <v>-0.00012758147285488116</v>
       </c>
       <c r="Z5">
-        <v>-7.3997063512828938e-005</v>
+        <v>-7.5031401256444013e-005</v>
       </c>
       <c r="AA5">
-        <v>-4.6984366519952107e-005</v>
+        <v>-4.9325851238072333e-005</v>
       </c>
       <c r="AB5">
-        <v>-6.2434253876294952e-005</v>
+        <v>-6.3567293799264441e-005</v>
       </c>
       <c r="AC5">
-        <v>-0.00010534650333036697</v>
+        <v>-0.00010685115880732464</v>
       </c>
       <c r="AD5">
-        <v>-8.2780177273795975e-005</v>
+        <v>-8.4898031006578597e-005</v>
       </c>
       <c r="AE5">
-        <v>-0.000107509415348735</v>
+        <v>-0.00010865126415228991</v>
       </c>
       <c r="AF5">
-        <v>2.26961010598509e-006</v>
+        <v>2.1926453265303319e-006</v>
       </c>
       <c r="AG5">
-        <v>4.3649532064458574e-005</v>
+        <v>4.3873513722139039e-005</v>
       </c>
       <c r="AH5">
-        <v>4.745500655885128e-005</v>
+        <v>4.7993985968779263e-005</v>
       </c>
       <c r="AI5">
-        <v>4.0027981105601913e-005</v>
+        <v>3.852625327185831e-005</v>
       </c>
       <c r="AJ5">
-        <v>0.00014135953502622298</v>
+        <v>0.00014028980676457248</v>
       </c>
       <c r="AK5">
-        <v>0.00011625960718143543</v>
+        <v>-1.3335710271335162e-005</v>
       </c>
       <c r="AL5">
-        <v>0.0020655870931514386</v>
+        <v>0.0020606261019060507</v>
       </c>
     </row>
     <row r="6">
@@ -6729,115 +6729,115 @@
         <v>50</v>
       </c>
       <c r="B6" s="83">
-        <v>-0.19805267570713697</v>
+        <v>-0.19731452847972059</v>
       </c>
       <c r="C6">
-        <v>1.9594426935733331e-005</v>
+        <v>2.0308155448938514e-005</v>
       </c>
       <c r="D6">
-        <v>-0.00011573745334654269</v>
+        <v>-0.00011533239622853036</v>
       </c>
       <c r="E6">
-        <v>8.7094158130583899e-007</v>
+        <v>8.6812980943284699e-007</v>
       </c>
       <c r="F6">
-        <v>0.00050310515568090892</v>
+        <v>0.00050317903055342554</v>
       </c>
       <c r="G6">
-        <v>0.0010493370847588091</v>
+        <v>0.0010496913799295203</v>
       </c>
       <c r="H6">
-        <v>2.271164376232339e-005</v>
+        <v>2.3362488395145792e-005</v>
       </c>
       <c r="I6">
-        <v>-2.2486774206184542e-005</v>
+        <v>-2.0699846188767459e-005</v>
       </c>
       <c r="J6">
-        <v>-5.1920261644556557e-005</v>
+        <v>-5.2359184309498617e-005</v>
       </c>
       <c r="K6">
-        <v>9.4226964586113961e-005</v>
+        <v>9.4419134819472974e-005</v>
       </c>
       <c r="L6">
-        <v>0.00013488688358873692</v>
+        <v>0.00013545259268104857</v>
       </c>
       <c r="M6">
-        <v>0.00025007228937114375</v>
+        <v>0.0002503618727350838</v>
       </c>
       <c r="N6">
-        <v>0.00038554258444723876</v>
+        <v>0.00038699469378761437</v>
       </c>
       <c r="O6">
-        <v>-4.7602663543132653e-005</v>
+        <v>-4.7771901374165514e-005</v>
       </c>
       <c r="P6">
-        <v>2.4147228458122361e-006</v>
+        <v>2.4603687820911774e-006</v>
       </c>
       <c r="Q6">
-        <v>-8.8879568932071685e-007</v>
+        <v>-9.1225848976522461e-007</v>
       </c>
       <c r="R6">
-        <v>2.3456245420827382e-005</v>
+        <v>2.2431108813099372e-005</v>
       </c>
       <c r="S6">
-        <v>7.9627039021634667e-005</v>
+        <v>8.0204199527032056e-005</v>
       </c>
       <c r="T6">
-        <v>-3.7597417642994813e-005</v>
+        <v>-3.8372963454868469e-005</v>
       </c>
       <c r="U6">
-        <v>-0.00020850957064266095</v>
+        <v>-0.00021017813004035684</v>
       </c>
       <c r="V6">
-        <v>-0.00018188013625273464</v>
+        <v>-0.00018315885554813263</v>
       </c>
       <c r="W6">
-        <v>-0.00015823164391327434</v>
+        <v>-0.00015993530085241196</v>
       </c>
       <c r="X6">
-        <v>-0.00018221139465057336</v>
+        <v>-0.00018376457093564021</v>
       </c>
       <c r="Y6">
-        <v>-0.00020486134641343659</v>
+        <v>-0.00020606458585733571</v>
       </c>
       <c r="Z6">
-        <v>-0.00017474324192125716</v>
+        <v>-0.00017607238781062125</v>
       </c>
       <c r="AA6">
-        <v>-0.0001537601650462794</v>
+        <v>-0.0001554995325619835</v>
       </c>
       <c r="AB6">
-        <v>-0.00011696518752404421</v>
+        <v>-0.00011836384065181665</v>
       </c>
       <c r="AC6">
-        <v>-0.00018680862273720705</v>
+        <v>-0.00018844209870912096</v>
       </c>
       <c r="AD6">
-        <v>-0.00014673836609690419</v>
+        <v>-0.00014890060259505923</v>
       </c>
       <c r="AE6">
-        <v>-0.00022483419386846182</v>
+        <v>-0.00022597583648494143</v>
       </c>
       <c r="AF6">
-        <v>1.0892052774323267e-005</v>
+        <v>1.0797784405801636e-005</v>
       </c>
       <c r="AG6">
-        <v>5.8382577604353925e-005</v>
+        <v>5.855993087358473e-005</v>
       </c>
       <c r="AH6">
-        <v>-5.2216381271316628e-006</v>
+        <v>-5.0866145270530687e-006</v>
       </c>
       <c r="AI6">
-        <v>-6.0909667544953514e-005</v>
+        <v>-6.2332865699330159e-005</v>
       </c>
       <c r="AJ6">
-        <v>0.00015064902639828304</v>
+        <v>0.00014941008529652499</v>
       </c>
       <c r="AK6">
-        <v>0.00016877164215886424</v>
+        <v>2.9324926140685565e-005</v>
       </c>
       <c r="AL6">
-        <v>0.0029087277165818866</v>
+        <v>0.0028953746541147758</v>
       </c>
     </row>
     <row r="7">
@@ -6845,115 +6845,115 @@
         <v>51</v>
       </c>
       <c r="B7" s="85">
-        <v>0.45981033564064389</v>
+        <v>0.45925840192469874</v>
       </c>
       <c r="C7">
-        <v>0.00020140555045630542</v>
+        <v>0.00020151017086252724</v>
       </c>
       <c r="D7">
-        <v>0.00029608704029219037</v>
+        <v>0.00029618887632656358</v>
       </c>
       <c r="E7">
-        <v>-3.0614504003743554e-006</v>
+        <v>-3.061957620653273e-006</v>
       </c>
       <c r="F7">
-        <v>1.7503132630498501e-005</v>
+        <v>1.8088712703125392e-005</v>
       </c>
       <c r="G7">
-        <v>2.271164376232339e-005</v>
+        <v>2.3362488395145792e-005</v>
       </c>
       <c r="H7">
-        <v>0.0014115961519814092</v>
+        <v>0.0014118796618147818</v>
       </c>
       <c r="I7">
-        <v>0.00023182779523424503</v>
+        <v>0.00023186163281308382</v>
       </c>
       <c r="J7">
-        <v>-0.00071773641951895935</v>
+        <v>-0.00071856107838172856</v>
       </c>
       <c r="K7">
-        <v>0.00010187339337686029</v>
+        <v>0.00010111341259337375</v>
       </c>
       <c r="L7">
-        <v>9.4273337228479757e-005</v>
+        <v>9.3920935097236915e-005</v>
       </c>
       <c r="M7">
-        <v>0.0001069608805226497</v>
+        <v>0.00010665018783989879</v>
       </c>
       <c r="N7">
-        <v>0.00011415406871843499</v>
+        <v>0.00011388194348462254</v>
       </c>
       <c r="O7">
-        <v>2.4614560946271568e-005</v>
+        <v>2.5581652350260648e-005</v>
       </c>
       <c r="P7">
-        <v>-8.7172419634736985e-007</v>
+        <v>-8.2743835376433544e-007</v>
       </c>
       <c r="Q7">
-        <v>-1.972731014376247e-007</v>
+        <v>-1.961409966477304e-007</v>
       </c>
       <c r="R7">
-        <v>-8.996831243689152e-005</v>
+        <v>-9.0479183760732771e-005</v>
       </c>
       <c r="S7">
-        <v>2.3834775054689525e-005</v>
+        <v>2.4279578865299352e-005</v>
       </c>
       <c r="T7">
-        <v>-4.7107157310353188e-005</v>
+        <v>-4.7341094300730988e-005</v>
       </c>
       <c r="U7">
-        <v>9.0790645976573993e-005</v>
+        <v>9.1738259786628497e-005</v>
       </c>
       <c r="V7">
-        <v>9.5399644249249732e-005</v>
+        <v>9.6022349192697188e-005</v>
       </c>
       <c r="W7">
-        <v>9.1153278991749583e-005</v>
+        <v>9.2158404481895915e-005</v>
       </c>
       <c r="X7">
-        <v>8.9940267334252116e-005</v>
+        <v>9.0750299793510177e-005</v>
       </c>
       <c r="Y7">
-        <v>8.7445766701685281e-005</v>
+        <v>8.8126120935317102e-005</v>
       </c>
       <c r="Z7">
-        <v>0.0001001418964368541</v>
+        <v>0.0001010545858191576</v>
       </c>
       <c r="AA7">
-        <v>0.00010417043239365525</v>
+        <v>0.000104557831198107</v>
       </c>
       <c r="AB7">
-        <v>0.00010841865699134592</v>
+        <v>0.00010942995137356306</v>
       </c>
       <c r="AC7">
-        <v>8.9263433807360736e-005</v>
+        <v>9.0088088657474559e-005</v>
       </c>
       <c r="AD7">
-        <v>0.00011945629031378408</v>
+        <v>0.00012003343515775517</v>
       </c>
       <c r="AE7">
-        <v>0.0001131692016542721</v>
+        <v>0.0001138566623554453</v>
       </c>
       <c r="AF7">
-        <v>2.1153358266019548e-005</v>
+        <v>2.1113641894424745e-005</v>
       </c>
       <c r="AG7">
-        <v>6.5994015202632751e-005</v>
+        <v>6.5883162392173309e-005</v>
       </c>
       <c r="AH7">
-        <v>1.2387980138129553e-005</v>
+        <v>1.2138919900348181e-005</v>
       </c>
       <c r="AI7">
-        <v>-6.9332494336163224e-006</v>
+        <v>-6.3145695417952301e-006</v>
       </c>
       <c r="AJ7">
-        <v>5.7454150482989536e-005</v>
+        <v>5.8326591941274165e-005</v>
       </c>
       <c r="AK7">
-        <v>3.8548698070346059e-006</v>
+        <v>8.4700878838509994e-006</v>
       </c>
       <c r="AL7">
-        <v>-0.0076260202491087335</v>
+        <v>-0.0076330832499604548</v>
       </c>
     </row>
     <row r="8">
@@ -6961,115 +6961,115 @@
         <v>52</v>
       </c>
       <c r="B8" s="87">
-        <v>0.61806405384931185</v>
+        <v>0.6194382171279651</v>
       </c>
       <c r="C8">
-        <v>0.00015264981821094155</v>
+        <v>0.00015276505175979683</v>
       </c>
       <c r="D8">
-        <v>3.078598349173919e-005</v>
+        <v>3.0730948456256322e-005</v>
       </c>
       <c r="E8">
-        <v>-2.6483490169331919e-007</v>
+        <v>-2.6455315093286075e-007</v>
       </c>
       <c r="F8">
-        <v>1.2156385401286423e-005</v>
+        <v>1.3588380087457621e-005</v>
       </c>
       <c r="G8">
-        <v>-2.2486774206184542e-005</v>
+        <v>-2.0699846188767459e-005</v>
       </c>
       <c r="H8">
-        <v>0.00023182779523424503</v>
+        <v>0.00023186163281308382</v>
       </c>
       <c r="I8">
-        <v>0.0015689637653649511</v>
+        <v>0.0015684339999900852</v>
       </c>
       <c r="J8">
-        <v>-0.00093833680945874635</v>
+        <v>-0.00093679660480244136</v>
       </c>
       <c r="K8">
-        <v>0.00042605488506415059</v>
+        <v>0.00042519635717223089</v>
       </c>
       <c r="L8">
-        <v>0.00066368288869130714</v>
+        <v>0.00066318486198702336</v>
       </c>
       <c r="M8">
-        <v>0.00077930366799754797</v>
+        <v>0.00077873341703125457</v>
       </c>
       <c r="N8">
-        <v>0.00082605573261083269</v>
+        <v>0.00082615454713661223</v>
       </c>
       <c r="O8">
-        <v>-0.00059831497654204934</v>
+        <v>-0.00059658531133743409</v>
       </c>
       <c r="P8">
-        <v>4.9376960102334337e-006</v>
+        <v>4.9741180255006058e-006</v>
       </c>
       <c r="Q8">
-        <v>5.7704554824204859e-006</v>
+        <v>5.7938027852148624e-006</v>
       </c>
       <c r="R8">
-        <v>1.0242437068365293e-005</v>
+        <v>9.9884118408625876e-006</v>
       </c>
       <c r="S8">
-        <v>7.9918464931132808e-005</v>
+        <v>8.0509499691144187e-005</v>
       </c>
       <c r="T8">
-        <v>8.4364328717023769e-005</v>
+        <v>8.3498477974469634e-005</v>
       </c>
       <c r="U8">
-        <v>-3.0148578391721477e-005</v>
+        <v>-3.2466394013554081e-005</v>
       </c>
       <c r="V8">
-        <v>6.2187938429037392e-005</v>
+        <v>6.043100965120432e-005</v>
       </c>
       <c r="W8">
-        <v>-2.031882791498317e-006</v>
+        <v>-2.797375905598011e-006</v>
       </c>
       <c r="X8">
-        <v>4.0314357295996453e-005</v>
+        <v>4.0772776902932078e-005</v>
       </c>
       <c r="Y8">
-        <v>7.1114917507132495e-005</v>
+        <v>6.9254676939382734e-005</v>
       </c>
       <c r="Z8">
-        <v>1.2249078888976065e-005</v>
+        <v>1.0881209227988579e-005</v>
       </c>
       <c r="AA8">
-        <v>-1.4777864761639789e-005</v>
+        <v>-1.6760029603749785e-005</v>
       </c>
       <c r="AB8">
-        <v>5.7955561356669207e-005</v>
+        <v>5.5895091879126519e-005</v>
       </c>
       <c r="AC8">
-        <v>1.0375518309037584e-005</v>
+        <v>8.3497468397965464e-006</v>
       </c>
       <c r="AD8">
-        <v>-1.4658656117199059e-005</v>
+        <v>-1.7352770741063412e-005</v>
       </c>
       <c r="AE8">
-        <v>-1.6305131689403618e-006</v>
+        <v>-4.1950062328066119e-006</v>
       </c>
       <c r="AF8">
-        <v>7.4366907960093245e-006</v>
+        <v>7.4493111913573535e-006</v>
       </c>
       <c r="AG8">
-        <v>-2.0668615887442024e-005</v>
+        <v>-2.0326980570782559e-005</v>
       </c>
       <c r="AH8">
-        <v>-4.1948125660702634e-005</v>
+        <v>-4.0852301364071821e-005</v>
       </c>
       <c r="AI8">
-        <v>-0.00018489816420867982</v>
+        <v>-0.0001868719591569441</v>
       </c>
       <c r="AJ8">
-        <v>-3.8897854302263456e-005</v>
+        <v>-4.0137772070962703e-005</v>
       </c>
       <c r="AK8">
-        <v>-0.00011664284849520088</v>
+        <v>-0.00016535255547567719</v>
       </c>
       <c r="AL8">
-        <v>-0.0026415304948867423</v>
+        <v>-0.0026414587171512977</v>
       </c>
     </row>
     <row r="9">
@@ -7077,115 +7077,115 @@
         <v>88</v>
       </c>
       <c r="B9" s="89">
-        <v>0.57726028394270135</v>
+        <v>0.57825216887249675</v>
       </c>
       <c r="C9">
-        <v>-5.0914324036196768e-005</v>
+        <v>-5.1408264038339519e-005</v>
       </c>
       <c r="D9">
-        <v>-0.0001395469818511652</v>
+        <v>-0.00013962934166484155</v>
       </c>
       <c r="E9">
-        <v>1.2413135751965185e-006</v>
+        <v>1.2421253466078569e-006</v>
       </c>
       <c r="F9">
-        <v>-1.0418748862538797e-005</v>
+        <v>-1.0357245425133056e-005</v>
       </c>
       <c r="G9">
-        <v>-5.1920261644556557e-005</v>
+        <v>-5.2359184309498617e-005</v>
       </c>
       <c r="H9">
-        <v>-0.00071773641951895935</v>
+        <v>-0.00071856107838172856</v>
       </c>
       <c r="I9">
-        <v>-0.00093833680945874635</v>
+        <v>-0.00093679660480244136</v>
       </c>
       <c r="J9">
-        <v>0.0041402010919710719</v>
+        <v>0.0041395828355883461</v>
       </c>
       <c r="K9">
-        <v>-0.00020129193228542579</v>
+        <v>-0.00020152975388033659</v>
       </c>
       <c r="L9">
-        <v>-0.00014579020107707464</v>
+        <v>-0.00014598305028989486</v>
       </c>
       <c r="M9">
-        <v>-0.00016024241721804064</v>
+        <v>-0.00016022242602747812</v>
       </c>
       <c r="N9">
-        <v>-0.00019004836325501031</v>
+        <v>-0.00019027304124279653</v>
       </c>
       <c r="O9">
-        <v>-8.3714172330733049e-006</v>
+        <v>-8.8568261878870229e-006</v>
       </c>
       <c r="P9">
-        <v>-1.9253595790204248e-006</v>
+        <v>-1.9343904436306569e-006</v>
       </c>
       <c r="Q9">
-        <v>-2.5988882449922651e-006</v>
+        <v>-2.5649715897764787e-006</v>
       </c>
       <c r="R9">
-        <v>7.8169527626491383e-006</v>
+        <v>8.1717879430469233e-006</v>
       </c>
       <c r="S9">
-        <v>5.2816953392497128e-005</v>
+        <v>5.1890452740170718e-005</v>
       </c>
       <c r="T9">
-        <v>-7.739982226542675e-005</v>
+        <v>-7.6774783677483957e-005</v>
       </c>
       <c r="U9">
-        <v>2.3614299999299634e-005</v>
+        <v>2.1288568403162594e-005</v>
       </c>
       <c r="V9">
-        <v>-4.8513008977520795e-005</v>
+        <v>-5.021440527871188e-005</v>
       </c>
       <c r="W9">
-        <v>-2.0325985220728208e-005</v>
+        <v>-2.1437966321094992e-005</v>
       </c>
       <c r="X9">
-        <v>-3.8860004471957463e-005</v>
+        <v>-4.1486655542825619e-005</v>
       </c>
       <c r="Y9">
-        <v>-8.2410979926316082e-005</v>
+        <v>-8.4047184660404877e-005</v>
       </c>
       <c r="Z9">
-        <v>-2.2537636369674829e-005</v>
+        <v>-2.444286270466417e-005</v>
       </c>
       <c r="AA9">
-        <v>-7.2646382838468821e-006</v>
+        <v>-8.923909431237222e-006</v>
       </c>
       <c r="AB9">
-        <v>-4.4187601372885736e-005</v>
+        <v>-4.6377116563901116e-005</v>
       </c>
       <c r="AC9">
-        <v>-4.4753739520121162e-005</v>
+        <v>-4.6762092608255805e-005</v>
       </c>
       <c r="AD9">
-        <v>-3.1358436202584897e-005</v>
+        <v>-3.3452044187214005e-005</v>
       </c>
       <c r="AE9">
-        <v>-0.00019373703807179683</v>
+        <v>-0.0001957494149204507</v>
       </c>
       <c r="AF9">
-        <v>5.8634893408772074e-006</v>
+        <v>5.8770159925179499e-006</v>
       </c>
       <c r="AG9">
-        <v>-3.9672550754283334e-005</v>
+        <v>-3.9339478770001804e-005</v>
       </c>
       <c r="AH9">
-        <v>-3.7024937143857595e-005</v>
+        <v>-3.7445754457609943e-005</v>
       </c>
       <c r="AI9">
-        <v>3.9445661745304318e-005</v>
+        <v>3.8439506832055412e-005</v>
       </c>
       <c r="AJ9">
-        <v>-3.3230507639348504e-005</v>
+        <v>-3.4489947497507063e-005</v>
       </c>
       <c r="AK9">
-        <v>-0.00015034144203871142</v>
+        <v>-0.00011700011030614109</v>
       </c>
       <c r="AL9">
-        <v>0.0044770649131338431</v>
+        <v>0.0044804252880234919</v>
       </c>
     </row>
     <row r="10">
@@ -7193,115 +7193,115 @@
         <v>53</v>
       </c>
       <c r="B10" s="91">
-        <v>0.10078573897016904</v>
+        <v>0.099599284440068853</v>
       </c>
       <c r="C10">
-        <v>0.00010126360180286576</v>
+        <v>0.00010140399935176278</v>
       </c>
       <c r="D10">
-        <v>-5.0342990750022916e-005</v>
+        <v>-4.9005020462896971e-005</v>
       </c>
       <c r="E10">
-        <v>3.3086973453711141e-007</v>
+        <v>3.2039377567481623e-007</v>
       </c>
       <c r="F10">
-        <v>4.2246545742092917e-005</v>
+        <v>4.1507904336539052e-005</v>
       </c>
       <c r="G10">
-        <v>9.4226964586113961e-005</v>
+        <v>9.4419134819472974e-005</v>
       </c>
       <c r="H10">
-        <v>0.00010187339337686029</v>
+        <v>0.00010111341259337375</v>
       </c>
       <c r="I10">
-        <v>0.00042605488506415059</v>
+        <v>0.00042519635717223089</v>
       </c>
       <c r="J10">
-        <v>-0.00020129193228542579</v>
+        <v>-0.00020152975388033659</v>
       </c>
       <c r="K10">
-        <v>0.00332017185760392</v>
+        <v>0.0033167691277669049</v>
       </c>
       <c r="L10">
-        <v>0.0025047304341245043</v>
+        <v>0.0025014182025286328</v>
       </c>
       <c r="M10">
-        <v>0.0026156356107153505</v>
+        <v>0.0026120700176086187</v>
       </c>
       <c r="N10">
-        <v>0.0026659331906459202</v>
+        <v>0.0026622539202936779</v>
       </c>
       <c r="O10">
-        <v>0.00015074703077544308</v>
+        <v>0.00014995144868784903</v>
       </c>
       <c r="P10">
-        <v>-4.3020793683149192e-007</v>
+        <v>-4.1810153137825782e-007</v>
       </c>
       <c r="Q10">
-        <v>-1.604786450080104e-006</v>
+        <v>-1.6396018190962436e-006</v>
       </c>
       <c r="R10">
-        <v>-0.00014272809283416826</v>
+        <v>-0.00014176807557125868</v>
       </c>
       <c r="S10">
-        <v>0.00020325377109321594</v>
+        <v>0.00020263518891586399</v>
       </c>
       <c r="T10">
-        <v>0.00026315474052200676</v>
+        <v>0.00026207752813952858</v>
       </c>
       <c r="U10">
-        <v>-6.173081192299419e-005</v>
+        <v>-6.2299073328940394e-005</v>
       </c>
       <c r="V10">
-        <v>-0.00011896613488462276</v>
+        <v>-0.00011999222804868473</v>
       </c>
       <c r="W10">
-        <v>-5.5013635954640318e-005</v>
+        <v>-5.6698988704880328e-005</v>
       </c>
       <c r="X10">
-        <v>-5.7781675802826699e-005</v>
+        <v>-5.8865349146027587e-005</v>
       </c>
       <c r="Y10">
-        <v>-5.3697833389746222e-005</v>
+        <v>-5.4663939063665954e-005</v>
       </c>
       <c r="Z10">
-        <v>-9.860095398986162e-005</v>
+        <v>-9.8923831817166906e-005</v>
       </c>
       <c r="AA10">
-        <v>-6.026386910939715e-005</v>
+        <v>-6.1317867246222938e-005</v>
       </c>
       <c r="AB10">
-        <v>-3.9508774239970044e-005</v>
+        <v>-4.055750456241256e-005</v>
       </c>
       <c r="AC10">
-        <v>-7.7634912757440413e-005</v>
+        <v>-7.8643550191122465e-005</v>
       </c>
       <c r="AD10">
-        <v>-5.775452858847196e-005</v>
+        <v>-5.9062672938782089e-005</v>
       </c>
       <c r="AE10">
-        <v>-7.7758099457827645e-005</v>
+        <v>-7.9195655479165957e-005</v>
       </c>
       <c r="AF10">
-        <v>-2.2349779833868188e-006</v>
+        <v>-2.2534624426036198e-006</v>
       </c>
       <c r="AG10">
-        <v>-0.000166526442953639</v>
+        <v>-0.00016685463883088486</v>
       </c>
       <c r="AH10">
-        <v>-0.00013625504446151878</v>
+        <v>-0.0001367763667771299</v>
       </c>
       <c r="AI10">
-        <v>0.00010896257343324272</v>
+        <v>0.00010879291063045139</v>
       </c>
       <c r="AJ10">
-        <v>-4.6855981270844688e-005</v>
+        <v>-4.7453801521580262e-005</v>
       </c>
       <c r="AK10">
-        <v>0.00011501634060341896</v>
+        <v>3.8584340426474047e-005</v>
       </c>
       <c r="AL10">
-        <v>-0.00077408575993136684</v>
+        <v>-0.0008096289184060879</v>
       </c>
     </row>
     <row r="11">
@@ -7309,115 +7309,115 @@
         <v>54</v>
       </c>
       <c r="B11" s="93">
-        <v>0.11346463482745719</v>
+        <v>0.11281437525646949</v>
       </c>
       <c r="C11">
-        <v>0.00012245249611382439</v>
+        <v>0.00012185472924296953</v>
       </c>
       <c r="D11">
-        <v>-8.5926973353193893e-005</v>
+        <v>-8.5155543468328453e-005</v>
       </c>
       <c r="E11">
-        <v>6.1213133691199168e-007</v>
+        <v>6.0642634654903012e-007</v>
       </c>
       <c r="F11">
-        <v>3.7524187253459485e-005</v>
+        <v>3.7420557942554778e-005</v>
       </c>
       <c r="G11">
-        <v>0.00013488688358873692</v>
+        <v>0.00013545259268104857</v>
       </c>
       <c r="H11">
-        <v>9.4273337228479757e-005</v>
+        <v>9.3920935097236915e-005</v>
       </c>
       <c r="I11">
-        <v>0.00066368288869130714</v>
+        <v>0.00066318486198702336</v>
       </c>
       <c r="J11">
-        <v>-0.00014579020107707464</v>
+        <v>-0.00014598305028989486</v>
       </c>
       <c r="K11">
-        <v>0.0025047304341245043</v>
+        <v>0.0025014182025286328</v>
       </c>
       <c r="L11">
-        <v>0.0033852948362955511</v>
+        <v>0.0033829806946265935</v>
       </c>
       <c r="M11">
-        <v>0.003019684745954375</v>
+        <v>0.0030172999050713388</v>
       </c>
       <c r="N11">
-        <v>0.0030942313673050386</v>
+        <v>0.0030920681750480224</v>
       </c>
       <c r="O11">
-        <v>0.00029260456573791942</v>
+        <v>0.00029262052406351188</v>
       </c>
       <c r="P11">
-        <v>2.5887883004721387e-007</v>
+        <v>2.8794063844976778e-007</v>
       </c>
       <c r="Q11">
-        <v>-1.4646101603837558e-006</v>
+        <v>-1.4902028766873007e-006</v>
       </c>
       <c r="R11">
-        <v>-0.00015305689183741603</v>
+        <v>-0.00015199710269923872</v>
       </c>
       <c r="S11">
-        <v>0.00030993585201296193</v>
+        <v>0.00031034463706070437</v>
       </c>
       <c r="T11">
-        <v>0.000328528900930197</v>
+        <v>0.0003278457226088882</v>
       </c>
       <c r="U11">
-        <v>-1.5008380561770413e-005</v>
+        <v>-1.2742373175474511e-005</v>
       </c>
       <c r="V11">
-        <v>-8.8316072749160821e-005</v>
+        <v>-8.6813063785103756e-005</v>
       </c>
       <c r="W11">
-        <v>-4.6571471171513615e-005</v>
+        <v>-4.536775278098917e-005</v>
       </c>
       <c r="X11">
-        <v>-1.510709320142866e-005</v>
+        <v>-1.249148580986033e-005</v>
       </c>
       <c r="Y11">
-        <v>-4.9613902536066717e-005</v>
+        <v>-4.7960117308113088e-005</v>
       </c>
       <c r="Z11">
-        <v>-0.00010023035834984067</v>
+        <v>-9.8252908133621098e-005</v>
       </c>
       <c r="AA11">
-        <v>-4.2191261575575886e-005</v>
+        <v>-4.0656052550373258e-005</v>
       </c>
       <c r="AB11">
-        <v>1.7171750966217883e-005</v>
+        <v>2.0040460459102736e-005</v>
       </c>
       <c r="AC11">
-        <v>-4.9602434788195617e-005</v>
+        <v>-4.8002937312104348e-005</v>
       </c>
       <c r="AD11">
-        <v>-4.6372473683291846e-005</v>
+        <v>-4.4900241118335212e-005</v>
       </c>
       <c r="AE11">
-        <v>-4.9423767368642416e-005</v>
+        <v>-4.7765452124212161e-005</v>
       </c>
       <c r="AF11">
-        <v>-1.6254755521929196e-006</v>
+        <v>-1.6164222772267148e-006</v>
       </c>
       <c r="AG11">
-        <v>-0.00012914241574695824</v>
+        <v>-0.00012937079571624161</v>
       </c>
       <c r="AH11">
-        <v>-0.00012407580988533178</v>
+        <v>-0.00012512201768268775</v>
       </c>
       <c r="AI11">
-        <v>0.00030177305051170872</v>
+        <v>0.00030247311081404288</v>
       </c>
       <c r="AJ11">
-        <v>-2.4526401316439257e-005</v>
+        <v>-2.3627662492500335e-005</v>
       </c>
       <c r="AK11">
-        <v>0.00011910151776988397</v>
+        <v>5.1935758466562258e-005</v>
       </c>
       <c r="AL11">
-        <v>-0.00021970565402399354</v>
+        <v>-0.00024501891217756575</v>
       </c>
     </row>
     <row r="12">
@@ -7425,115 +7425,115 @@
         <v>55</v>
       </c>
       <c r="B12" s="95">
-        <v>0.1606708188392573</v>
+        <v>0.16000668222577039</v>
       </c>
       <c r="C12">
-        <v>9.6694742619722937e-005</v>
+        <v>9.6521384278589587e-005</v>
       </c>
       <c r="D12">
-        <v>-0.00012230094868889599</v>
+        <v>-0.00012157483164564314</v>
       </c>
       <c r="E12">
-        <v>8.9593879367845706e-007</v>
+        <v>8.907091412946021e-007</v>
       </c>
       <c r="F12">
-        <v>7.788874763855264e-005</v>
+        <v>7.7622541999522638e-005</v>
       </c>
       <c r="G12">
-        <v>0.00025007228937114375</v>
+        <v>0.0002503618727350838</v>
       </c>
       <c r="H12">
-        <v>0.0001069608805226497</v>
+        <v>0.00010665018783989879</v>
       </c>
       <c r="I12">
-        <v>0.00077930366799754797</v>
+        <v>0.00077873341703125457</v>
       </c>
       <c r="J12">
-        <v>-0.00016024241721804064</v>
+        <v>-0.00016022242602747812</v>
       </c>
       <c r="K12">
-        <v>0.0026156356107153505</v>
+        <v>0.0026120700176086187</v>
       </c>
       <c r="L12">
-        <v>0.003019684745954375</v>
+        <v>0.0030172999050713388</v>
       </c>
       <c r="M12">
-        <v>0.0036671435951301339</v>
+        <v>0.0036647887962689314</v>
       </c>
       <c r="N12">
-        <v>0.0033886941059434552</v>
+        <v>0.0033863803831321298</v>
       </c>
       <c r="O12">
-        <v>0.0002815228176409746</v>
+        <v>0.00028199643100195501</v>
       </c>
       <c r="P12">
-        <v>-1.3237693888395607e-006</v>
+        <v>-1.2956201845799085e-006</v>
       </c>
       <c r="Q12">
-        <v>-2.2864167503310169e-006</v>
+        <v>-2.3140646003710579e-006</v>
       </c>
       <c r="R12">
-        <v>-0.00013007331211444299</v>
+        <v>-0.0001292964478375597</v>
       </c>
       <c r="S12">
-        <v>0.00047078340345231584</v>
+        <v>0.00047092426954434036</v>
       </c>
       <c r="T12">
-        <v>0.00035424537403122385</v>
+        <v>0.00035319160136341554</v>
       </c>
       <c r="U12">
-        <v>-4.4801905352126622e-005</v>
+        <v>-4.1956448975510147e-005</v>
       </c>
       <c r="V12">
-        <v>-7.2154150656683039e-005</v>
+        <v>-7.0013929492082649e-005</v>
       </c>
       <c r="W12">
-        <v>-2.3870612708282385e-005</v>
+        <v>-2.1667358744415096e-005</v>
       </c>
       <c r="X12">
-        <v>-1.7739174661277426e-005</v>
+        <v>-1.5005553595656793e-005</v>
       </c>
       <c r="Y12">
-        <v>-1.4184649306315242e-005</v>
+        <v>-1.1828058482091426e-005</v>
       </c>
       <c r="Z12">
-        <v>-8.2612701275149849e-005</v>
+        <v>-8.0085500054187758e-005</v>
       </c>
       <c r="AA12">
-        <v>-4.7674315698546397e-005</v>
+        <v>-4.5597508974621758e-005</v>
       </c>
       <c r="AB12">
-        <v>5.8199118585528376e-005</v>
+        <v>6.0942412835395454e-005</v>
       </c>
       <c r="AC12">
-        <v>-5.3292285921018446e-005</v>
+        <v>-5.0953442497791946e-005</v>
       </c>
       <c r="AD12">
-        <v>-2.2180289135376348e-005</v>
+        <v>-1.9910351460070618e-005</v>
       </c>
       <c r="AE12">
-        <v>-3.6065863327354648e-005</v>
+        <v>-3.3746619638637789e-005</v>
       </c>
       <c r="AF12">
-        <v>-1.3809502020798206e-006</v>
+        <v>-1.42028363743978e-006</v>
       </c>
       <c r="AG12">
-        <v>-0.00011971708488613497</v>
+        <v>-0.00011987060802612407</v>
       </c>
       <c r="AH12">
-        <v>-0.00011987175225658488</v>
+        <v>-0.00012082046165643907</v>
       </c>
       <c r="AI12">
-        <v>0.00029247909836977609</v>
+        <v>0.00029348128661141077</v>
       </c>
       <c r="AJ12">
-        <v>3.3756692757188494e-005</v>
+        <v>3.4956935548667882e-005</v>
       </c>
       <c r="AK12">
-        <v>0.00014975296588664666</v>
+        <v>6.7486794861570319e-005</v>
       </c>
       <c r="AL12">
-        <v>0.00067582778195102557</v>
+        <v>0.00065205509805747654</v>
       </c>
     </row>
     <row r="13">
@@ -7541,115 +7541,115 @@
         <v>56</v>
       </c>
       <c r="B13" s="97">
-        <v>0.33966092037175177</v>
+        <v>0.3398255602710733</v>
       </c>
       <c r="C13">
-        <v>0.00010467926566299976</v>
+        <v>0.00010444558569330413</v>
       </c>
       <c r="D13">
-        <v>-0.00014081176321063382</v>
+        <v>-0.00013980302881216032</v>
       </c>
       <c r="E13">
-        <v>1.0558107761729728e-006</v>
+        <v>1.0485392673048434e-006</v>
       </c>
       <c r="F13">
-        <v>0.00018862247776443644</v>
+        <v>0.00018899509347567885</v>
       </c>
       <c r="G13">
-        <v>0.00038554258444723876</v>
+        <v>0.00038699469378761437</v>
       </c>
       <c r="H13">
-        <v>0.00011415406871843499</v>
+        <v>0.00011388194348462254</v>
       </c>
       <c r="I13">
-        <v>0.00082605573261083269</v>
+        <v>0.00082615454713661223</v>
       </c>
       <c r="J13">
-        <v>-0.00019004836325501031</v>
+        <v>-0.00019027304124279653</v>
       </c>
       <c r="K13">
-        <v>0.0026659331906459202</v>
+        <v>0.0026622539202936779</v>
       </c>
       <c r="L13">
-        <v>0.0030942313673050386</v>
+        <v>0.0030920681750480224</v>
       </c>
       <c r="M13">
-        <v>0.0033886941059434552</v>
+        <v>0.0033863803831321298</v>
       </c>
       <c r="N13">
-        <v>0.0038125318592739199</v>
+        <v>0.0038109370230396634</v>
       </c>
       <c r="O13">
-        <v>0.00026240003908121009</v>
+        <v>0.000262741077795686</v>
       </c>
       <c r="P13">
-        <v>-2.5341310257364543e-006</v>
+        <v>-2.5086827681518277e-006</v>
       </c>
       <c r="Q13">
-        <v>-3.7342859332660599e-006</v>
+        <v>-3.7581713590983594e-006</v>
       </c>
       <c r="R13">
-        <v>-0.00011226093151104403</v>
+        <v>-0.00011194201525773433</v>
       </c>
       <c r="S13">
-        <v>0.00053196108262082865</v>
+        <v>0.00053231966780324387</v>
       </c>
       <c r="T13">
-        <v>0.00036282616991804211</v>
+        <v>0.00036151255689164448</v>
       </c>
       <c r="U13">
-        <v>8.1408286837688628e-006</v>
+        <v>1.0016710099518202e-005</v>
       </c>
       <c r="V13">
-        <v>-4.9110043948302458e-005</v>
+        <v>-4.7510673227908057e-005</v>
       </c>
       <c r="W13">
-        <v>1.0633765871446142e-005</v>
+        <v>1.2305872353615341e-005</v>
       </c>
       <c r="X13">
-        <v>3.8119284756727182e-005</v>
+        <v>4.0658308357769931e-005</v>
       </c>
       <c r="Y13">
-        <v>2.8785063358073592e-005</v>
+        <v>3.0766009301888466e-005</v>
       </c>
       <c r="Z13">
-        <v>-9.0152015527852577e-005</v>
+        <v>-8.7941985322004344e-005</v>
       </c>
       <c r="AA13">
-        <v>-6.5709038139884755e-005</v>
+        <v>-6.3425491695266191e-005</v>
       </c>
       <c r="AB13">
-        <v>7.5695247923771329e-005</v>
+        <v>7.7510162386103623e-005</v>
       </c>
       <c r="AC13">
-        <v>-3.2810424652359805e-005</v>
+        <v>-3.1481235333647838e-005</v>
       </c>
       <c r="AD13">
-        <v>-2.0705570141084069e-005</v>
+        <v>-1.9936280294470705e-005</v>
       </c>
       <c r="AE13">
-        <v>-2.4391223401627402e-005</v>
+        <v>-2.3056856903303988e-005</v>
       </c>
       <c r="AF13">
-        <v>4.5535772324228527e-009</v>
+        <v>8.5718265796757686e-009</v>
       </c>
       <c r="AG13">
-        <v>-0.00013260663443049819</v>
+        <v>-0.00013277373316869544</v>
       </c>
       <c r="AH13">
-        <v>-0.0001376952113692458</v>
+        <v>-0.00013823067708078151</v>
       </c>
       <c r="AI13">
-        <v>0.00029389269658248833</v>
+        <v>0.00029411966285414507</v>
       </c>
       <c r="AJ13">
-        <v>0.00014647667481562296</v>
+        <v>0.00014694678852401834</v>
       </c>
       <c r="AK13">
-        <v>9.5208833662448265e-005</v>
+        <v>8.8557315503200998e-006</v>
       </c>
       <c r="AL13">
-        <v>0.0010585732786154468</v>
+        <v>0.001024277844601771</v>
       </c>
     </row>
     <row r="14">
@@ -7657,115 +7657,115 @@
         <v>57</v>
       </c>
       <c r="B14" s="99">
-        <v>-0.11577409757346709</v>
+        <v>-0.1166532382697136</v>
       </c>
       <c r="C14">
-        <v>-6.9526272724531758e-005</v>
+        <v>-6.9607966719087078e-005</v>
       </c>
       <c r="D14">
-        <v>-1.5991790664160368e-005</v>
+        <v>-1.5874402039881561e-005</v>
       </c>
       <c r="E14">
-        <v>8.869398411431883e-008</v>
+        <v>8.781820504187064e-008</v>
       </c>
       <c r="F14">
-        <v>1.1868818560886662e-005</v>
+        <v>1.2038766213433952e-005</v>
       </c>
       <c r="G14">
-        <v>-4.7602663543132653e-005</v>
+        <v>-4.7771901374165514e-005</v>
       </c>
       <c r="H14">
-        <v>2.4614560946271568e-005</v>
+        <v>2.5581652350260648e-005</v>
       </c>
       <c r="I14">
-        <v>-0.00059831497654204934</v>
+        <v>-0.00059658531133743409</v>
       </c>
       <c r="J14">
-        <v>-8.3714172330733049e-006</v>
+        <v>-8.8568261878870229e-006</v>
       </c>
       <c r="K14">
-        <v>0.00015074703077544308</v>
+        <v>0.00014995144868784903</v>
       </c>
       <c r="L14">
-        <v>0.00029260456573791942</v>
+        <v>0.00029262052406351188</v>
       </c>
       <c r="M14">
-        <v>0.0002815228176409746</v>
+        <v>0.00028199643100195501</v>
       </c>
       <c r="N14">
-        <v>0.00026240003908121009</v>
+        <v>0.000262741077795686</v>
       </c>
       <c r="O14">
-        <v>0.0021395972816364399</v>
+        <v>0.0021387709333727713</v>
       </c>
       <c r="P14">
-        <v>2.0027276781459541e-005</v>
+        <v>2.0015390694431587e-005</v>
       </c>
       <c r="Q14">
-        <v>9.9344986200104744e-006</v>
+        <v>9.9465809936613936e-006</v>
       </c>
       <c r="R14">
-        <v>6.9303612407478079e-006</v>
+        <v>6.0946395307074979e-006</v>
       </c>
       <c r="S14">
-        <v>-1.4186866042606081e-005</v>
+        <v>-1.3602843247704623e-005</v>
       </c>
       <c r="T14">
-        <v>-0.00020612950605417477</v>
+        <v>-0.00020700212506315644</v>
       </c>
       <c r="U14">
-        <v>1.253240485890963e-005</v>
+        <v>1.3413799586145005e-005</v>
       </c>
       <c r="V14">
-        <v>8.0493806280849869e-005</v>
+        <v>8.0660431203442612e-005</v>
       </c>
       <c r="W14">
-        <v>6.7918691504911745e-005</v>
+        <v>6.8495742001418113e-005</v>
       </c>
       <c r="X14">
-        <v>3.8211467289232066e-005</v>
+        <v>3.7920105360446594e-005</v>
       </c>
       <c r="Y14">
-        <v>1.8447568700749465e-005</v>
+        <v>1.9168559081904975e-005</v>
       </c>
       <c r="Z14">
-        <v>4.6568427712206451e-005</v>
+        <v>4.6999791038128381e-005</v>
       </c>
       <c r="AA14">
-        <v>2.7524613694881279e-005</v>
+        <v>2.8439756251447644e-005</v>
       </c>
       <c r="AB14">
-        <v>-6.1662800310140512e-006</v>
+        <v>-4.5204783373577239e-006</v>
       </c>
       <c r="AC14">
-        <v>-1.7576534025369548e-006</v>
+        <v>-1.1521190901402339e-006</v>
       </c>
       <c r="AD14">
-        <v>-3.3005065108149896e-005</v>
+        <v>-3.2139252947988007e-005</v>
       </c>
       <c r="AE14">
-        <v>-5.1818521380137331e-005</v>
+        <v>-5.0382519611860774e-005</v>
       </c>
       <c r="AF14">
-        <v>-2.7920312407014961e-006</v>
+        <v>-2.848590791806363e-006</v>
       </c>
       <c r="AG14">
-        <v>3.629048726057578e-005</v>
+        <v>3.6722687593711425e-005</v>
       </c>
       <c r="AH14">
-        <v>5.9681510107050635e-005</v>
+        <v>5.9884059190793127e-005</v>
       </c>
       <c r="AI14">
-        <v>0.00017946722395634739</v>
+        <v>0.00017977755866068824</v>
       </c>
       <c r="AJ14">
-        <v>4.5639660451942147e-006</v>
+        <v>4.8471868691038391e-006</v>
       </c>
       <c r="AK14">
-        <v>0.00019556529616013572</v>
+        <v>6.8655129968933713e-005</v>
       </c>
       <c r="AL14">
-        <v>-0.001124203656662306</v>
+        <v>-0.0011282370603845414</v>
       </c>
     </row>
     <row r="15">
@@ -7773,115 +7773,115 @@
         <v>58</v>
       </c>
       <c r="B15" s="101">
-        <v>-0.0018226419594614301</v>
+        <v>-0.0018481800119203773</v>
       </c>
       <c r="C15">
-        <v>4.6321500715517949e-007</v>
+        <v>4.7895691363334313e-007</v>
       </c>
       <c r="D15">
-        <v>1.5557924069219642e-006</v>
+        <v>1.5646142807599532e-006</v>
       </c>
       <c r="E15">
-        <v>-1.1148471551623142e-008</v>
+        <v>-1.1221662106904966e-008</v>
       </c>
       <c r="F15">
-        <v>1.8223919841767059e-006</v>
+        <v>1.8542121040226296e-006</v>
       </c>
       <c r="G15">
-        <v>2.4147228458122361e-006</v>
+        <v>2.4603687820911774e-006</v>
       </c>
       <c r="H15">
-        <v>-8.7172419634736985e-007</v>
+        <v>-8.2743835376433544e-007</v>
       </c>
       <c r="I15">
-        <v>4.9376960102334337e-006</v>
+        <v>4.9741180255006058e-006</v>
       </c>
       <c r="J15">
-        <v>-1.9253595790204248e-006</v>
+        <v>-1.9343904436306569e-006</v>
       </c>
       <c r="K15">
-        <v>-4.3020793683149192e-007</v>
+        <v>-4.1810153137825782e-007</v>
       </c>
       <c r="L15">
-        <v>2.5887883004721387e-007</v>
+        <v>2.8794063844976778e-007</v>
       </c>
       <c r="M15">
-        <v>-1.3237693888395607e-006</v>
+        <v>-1.2956201845799085e-006</v>
       </c>
       <c r="N15">
-        <v>-2.5341310257364543e-006</v>
+        <v>-2.5086827681518277e-006</v>
       </c>
       <c r="O15">
-        <v>2.0027276781459541e-005</v>
+        <v>2.0015390694431587e-005</v>
       </c>
       <c r="P15">
-        <v>1.3672189242598954e-006</v>
+        <v>1.368431351525146e-006</v>
       </c>
       <c r="Q15">
-        <v>8.4980884258777474e-008</v>
+        <v>8.4308699898198539e-008</v>
       </c>
       <c r="R15">
-        <v>2.6206547751870479e-007</v>
+        <v>2.1317402930758948e-007</v>
       </c>
       <c r="S15">
-        <v>-1.1854521649471154e-006</v>
+        <v>-1.1610384834266072e-006</v>
       </c>
       <c r="T15">
-        <v>1.5667981527159521e-006</v>
+        <v>1.5478332726930494e-006</v>
       </c>
       <c r="U15">
-        <v>-9.0804183238525827e-007</v>
+        <v>-9.6480725090007023e-007</v>
       </c>
       <c r="V15">
-        <v>1.267479724149314e-006</v>
+        <v>1.2232728494078606e-006</v>
       </c>
       <c r="W15">
-        <v>5.2827120676362946e-007</v>
+        <v>4.7341485122719644e-007</v>
       </c>
       <c r="X15">
-        <v>-1.3361758790843563e-006</v>
+        <v>-1.3794930473454928e-006</v>
       </c>
       <c r="Y15">
-        <v>-2.8306574873551401e-007</v>
+        <v>-3.4264232788703728e-007</v>
       </c>
       <c r="Z15">
-        <v>-9.6023156145441641e-007</v>
+        <v>-1.0098648268590349e-006</v>
       </c>
       <c r="AA15">
-        <v>-2.0599243549192285e-006</v>
+        <v>-2.1617005555535043e-006</v>
       </c>
       <c r="AB15">
-        <v>-1.2772291081765237e-006</v>
+        <v>-1.3025294112941431e-006</v>
       </c>
       <c r="AC15">
-        <v>-1.7200012153929567e-006</v>
+        <v>-1.7751102441287834e-006</v>
       </c>
       <c r="AD15">
-        <v>-1.2932730688513741e-006</v>
+        <v>-1.345773635430696e-006</v>
       </c>
       <c r="AE15">
-        <v>-2.6735682533017335e-006</v>
+        <v>-2.714266797101977e-006</v>
       </c>
       <c r="AF15">
-        <v>1.4374136639538981e-007</v>
+        <v>1.3966777373314725e-007</v>
       </c>
       <c r="AG15">
-        <v>2.1149954691117529e-006</v>
+        <v>2.1300944425176423e-006</v>
       </c>
       <c r="AH15">
-        <v>9.070752444544634e-007</v>
+        <v>9.3222441562626164e-007</v>
       </c>
       <c r="AI15">
-        <v>-4.5588783468617617e-007</v>
+        <v>-4.8971313256314852e-007</v>
       </c>
       <c r="AJ15">
-        <v>-2.0082259928800612e-006</v>
+        <v>-2.0319329748109412e-006</v>
       </c>
       <c r="AK15">
-        <v>2.1183388434044346e-006</v>
+        <v>-2.3772438135726513e-006</v>
       </c>
       <c r="AL15">
-        <v>-0.00012819660185451955</v>
+        <v>-0.00012841902460906143</v>
       </c>
     </row>
     <row r="16">
@@ -7889,115 +7889,115 @@
         <v>59</v>
       </c>
       <c r="B16" s="103">
-        <v>-0.00092473271276788155</v>
+        <v>-0.00088897543593672765</v>
       </c>
       <c r="C16">
-        <v>-2.5066602346869103e-006</v>
+        <v>-2.5040279840891912e-006</v>
       </c>
       <c r="D16">
-        <v>-1.4252508182781621e-006</v>
+        <v>-1.4236952524422704e-006</v>
       </c>
       <c r="E16">
-        <v>8.9102230330252389e-009</v>
+        <v>8.8948240721396237e-009</v>
       </c>
       <c r="F16">
-        <v>7.316377118896582e-008</v>
+        <v>7.4447727517481539e-008</v>
       </c>
       <c r="G16">
-        <v>-8.8879568932071685e-007</v>
+        <v>-9.1225848976522461e-007</v>
       </c>
       <c r="H16">
-        <v>-1.972731014376247e-007</v>
+        <v>-1.961409966477304e-007</v>
       </c>
       <c r="I16">
-        <v>5.7704554824204859e-006</v>
+        <v>5.7938027852148624e-006</v>
       </c>
       <c r="J16">
-        <v>-2.5988882449922651e-006</v>
+        <v>-2.5649715897764787e-006</v>
       </c>
       <c r="K16">
-        <v>-1.604786450080104e-006</v>
+        <v>-1.6396018190962436e-006</v>
       </c>
       <c r="L16">
-        <v>-1.4646101603837558e-006</v>
+        <v>-1.4902028766873007e-006</v>
       </c>
       <c r="M16">
-        <v>-2.2864167503310169e-006</v>
+        <v>-2.3140646003710579e-006</v>
       </c>
       <c r="N16">
-        <v>-3.7342859332660599e-006</v>
+        <v>-3.7581713590983594e-006</v>
       </c>
       <c r="O16">
-        <v>9.9344986200104744e-006</v>
+        <v>9.9465809936613936e-006</v>
       </c>
       <c r="P16">
-        <v>8.4980884258777474e-008</v>
+        <v>8.4308699898198539e-008</v>
       </c>
       <c r="Q16">
-        <v>1.6390166577954421e-006</v>
+        <v>1.6394696861428477e-006</v>
       </c>
       <c r="R16">
-        <v>-4.8279875107263909e-007</v>
+        <v>-4.8617231923466303e-007</v>
       </c>
       <c r="S16">
-        <v>-3.6503714157166492e-007</v>
+        <v>-3.6399385316071547e-007</v>
       </c>
       <c r="T16">
-        <v>1.2979724115604848e-006</v>
+        <v>1.2908032289600537e-006</v>
       </c>
       <c r="U16">
-        <v>1.8491670222805805e-006</v>
+        <v>1.781243005085752e-006</v>
       </c>
       <c r="V16">
-        <v>3.7620430098976341e-006</v>
+        <v>3.7015030745122381e-006</v>
       </c>
       <c r="W16">
-        <v>3.496302200014177e-006</v>
+        <v>3.4522138909796893e-006</v>
       </c>
       <c r="X16">
-        <v>2.9406742007107683e-006</v>
+        <v>2.9097383727674577e-006</v>
       </c>
       <c r="Y16">
-        <v>2.5684994098722313e-006</v>
+        <v>2.5143723418842807e-006</v>
       </c>
       <c r="Z16">
-        <v>2.4098941002141644e-006</v>
+        <v>2.3467233009478266e-006</v>
       </c>
       <c r="AA16">
-        <v>7.2670580250843814e-007</v>
+        <v>6.7963536811460842e-007</v>
       </c>
       <c r="AB16">
-        <v>6.128589158802805e-007</v>
+        <v>5.6149116629888317e-007</v>
       </c>
       <c r="AC16">
-        <v>3.2550493293675512e-006</v>
+        <v>3.1936538727755874e-006</v>
       </c>
       <c r="AD16">
-        <v>2.002944046406463e-006</v>
+        <v>1.9353818957403739e-006</v>
       </c>
       <c r="AE16">
-        <v>3.9631622441759688e-007</v>
+        <v>3.2972286052512984e-007</v>
       </c>
       <c r="AF16">
-        <v>4.1684926637691798e-007</v>
+        <v>4.1701073012715971e-007</v>
       </c>
       <c r="AG16">
-        <v>1.7450416840743005e-006</v>
+        <v>1.76075753321727e-006</v>
       </c>
       <c r="AH16">
-        <v>8.7934981246885767e-007</v>
+        <v>9.1702834080550278e-007</v>
       </c>
       <c r="AI16">
-        <v>-9.894558717211301e-007</v>
+        <v>-1.0414154927419024e-006</v>
       </c>
       <c r="AJ16">
-        <v>-1.1391537963898322e-006</v>
+        <v>-1.1884810149342194e-006</v>
       </c>
       <c r="AK16">
-        <v>8.2258635342248427e-007</v>
+        <v>-1.316007239660337e-006</v>
       </c>
       <c r="AL16">
-        <v>-4.0559767138226413e-005</v>
+        <v>-4.0504988340076681e-005</v>
       </c>
     </row>
     <row r="17">
@@ -8005,115 +8005,115 @@
         <v>89</v>
       </c>
       <c r="B17" s="105">
-        <v>0.082613623320623594</v>
+        <v>0.082833009670325988</v>
       </c>
       <c r="C17">
-        <v>4.2133390487461083e-005</v>
+        <v>4.1875944996539152e-005</v>
       </c>
       <c r="D17">
-        <v>3.8752501768856687e-005</v>
+        <v>3.8714182876630528e-005</v>
       </c>
       <c r="E17">
-        <v>-5.4863004550240887e-007</v>
+        <v>-5.4835431088383163e-007</v>
       </c>
       <c r="F17">
-        <v>8.413565634335535e-006</v>
+        <v>7.5227331911805372e-006</v>
       </c>
       <c r="G17">
-        <v>2.3456245420827382e-005</v>
+        <v>2.2431108813099372e-005</v>
       </c>
       <c r="H17">
-        <v>-8.996831243689152e-005</v>
+        <v>-9.0479183760732771e-005</v>
       </c>
       <c r="I17">
-        <v>1.0242437068365293e-005</v>
+        <v>9.9884118408625876e-006</v>
       </c>
       <c r="J17">
-        <v>7.8169527626491383e-006</v>
+        <v>8.1717879430469233e-006</v>
       </c>
       <c r="K17">
-        <v>-0.00014272809283416826</v>
+        <v>-0.00014176807557125868</v>
       </c>
       <c r="L17">
-        <v>-0.00015305689183741603</v>
+        <v>-0.00015199710269923872</v>
       </c>
       <c r="M17">
-        <v>-0.00013007331211444299</v>
+        <v>-0.0001292964478375597</v>
       </c>
       <c r="N17">
-        <v>-0.00011226093151104403</v>
+        <v>-0.00011194201525773433</v>
       </c>
       <c r="O17">
-        <v>6.9303612407478079e-006</v>
+        <v>6.0946395307074979e-006</v>
       </c>
       <c r="P17">
-        <v>2.6206547751870479e-007</v>
+        <v>2.1317402930758948e-007</v>
       </c>
       <c r="Q17">
-        <v>-4.8279875107263909e-007</v>
+        <v>-4.8617231923466303e-007</v>
       </c>
       <c r="R17">
-        <v>0.0008226006550602537</v>
+        <v>0.000823051690556491</v>
       </c>
       <c r="S17">
-        <v>-0.00023452765918568068</v>
+        <v>-0.0002346596565357907</v>
       </c>
       <c r="T17">
-        <v>7.9307027502110864e-005</v>
+        <v>7.9484871073317277e-005</v>
       </c>
       <c r="U17">
-        <v>-3.2416326597533315e-005</v>
+        <v>-3.05560379899552e-005</v>
       </c>
       <c r="V17">
-        <v>-5.8900756535987145e-005</v>
+        <v>-5.7295345112959382e-005</v>
       </c>
       <c r="W17">
-        <v>-4.0318313042413784e-005</v>
+        <v>-3.9057336877795627e-005</v>
       </c>
       <c r="X17">
-        <v>-2.7876233397252943e-005</v>
+        <v>-2.5827297826288664e-005</v>
       </c>
       <c r="Y17">
-        <v>-6.6530850359639558e-005</v>
+        <v>-6.4993340785407712e-005</v>
       </c>
       <c r="Z17">
-        <v>-6.5134884432676134e-005</v>
+        <v>-6.3434906773530194e-005</v>
       </c>
       <c r="AA17">
-        <v>-4.4408562723469071e-005</v>
+        <v>-4.2839034886375013e-005</v>
       </c>
       <c r="AB17">
-        <v>-6.4107242135798758e-005</v>
+        <v>-6.2496620788231143e-005</v>
       </c>
       <c r="AC17">
-        <v>-6.7517939387905148e-005</v>
+        <v>-6.5810035346780863e-005</v>
       </c>
       <c r="AD17">
-        <v>-2.7822035924801375e-005</v>
+        <v>-2.5440354069383242e-005</v>
       </c>
       <c r="AE17">
-        <v>-5.0380687409740284e-006</v>
+        <v>-3.2351092831639852e-006</v>
       </c>
       <c r="AF17">
-        <v>1.2761182121049299e-005</v>
+        <v>1.2773958360794778e-005</v>
       </c>
       <c r="AG17">
-        <v>-2.0564637155311837e-005</v>
+        <v>-2.0820177502445129e-005</v>
       </c>
       <c r="AH17">
-        <v>-1.5312110465500915e-006</v>
+        <v>-2.0996843085187855e-006</v>
       </c>
       <c r="AI17">
-        <v>1.6724647947093736e-005</v>
+        <v>1.7436231184573344e-005</v>
       </c>
       <c r="AJ17">
-        <v>-9.3650434656049569e-005</v>
+        <v>-9.279611695516552e-005</v>
       </c>
       <c r="AK17">
-        <v>7.0774106531142479e-005</v>
+        <v>0.00011058907162805344</v>
       </c>
       <c r="AL17">
-        <v>-0.0005232816548235205</v>
+        <v>-0.00052119386060870895</v>
       </c>
     </row>
     <row r="18">
@@ -8121,115 +8121,115 @@
         <v>90</v>
       </c>
       <c r="B18" s="107">
-        <v>0.32743190286805257</v>
+        <v>0.32701735346798622</v>
       </c>
       <c r="C18">
-        <v>-3.1168353987290242e-005</v>
+        <v>-3.1098711971204675e-005</v>
       </c>
       <c r="D18">
-        <v>-2.4060211098254122e-005</v>
+        <v>-2.4219661080674597e-005</v>
       </c>
       <c r="E18">
-        <v>1.4830784317378119e-007</v>
+        <v>1.4969418434769993e-007</v>
       </c>
       <c r="F18">
-        <v>5.2977449790130669e-005</v>
+        <v>5.3709170208596563e-005</v>
       </c>
       <c r="G18">
-        <v>7.9627039021634667e-005</v>
+        <v>8.0204199527032056e-005</v>
       </c>
       <c r="H18">
-        <v>2.3834775054689525e-005</v>
+        <v>2.4279578865299352e-005</v>
       </c>
       <c r="I18">
-        <v>7.9918464931132808e-005</v>
+        <v>8.0509499691144187e-005</v>
       </c>
       <c r="J18">
-        <v>5.2816953392497128e-005</v>
+        <v>5.1890452740170718e-005</v>
       </c>
       <c r="K18">
-        <v>0.00020325377109321594</v>
+        <v>0.00020263518891586399</v>
       </c>
       <c r="L18">
-        <v>0.00030993585201296193</v>
+        <v>0.00031034463706070437</v>
       </c>
       <c r="M18">
-        <v>0.00047078340345231584</v>
+        <v>0.00047092426954434036</v>
       </c>
       <c r="N18">
-        <v>0.00053196108262082865</v>
+        <v>0.00053231966780324387</v>
       </c>
       <c r="O18">
-        <v>-1.4186866042606081e-005</v>
+        <v>-1.3602843247704623e-005</v>
       </c>
       <c r="P18">
-        <v>-1.1854521649471154e-006</v>
+        <v>-1.1610384834266072e-006</v>
       </c>
       <c r="Q18">
-        <v>-3.6503714157166492e-007</v>
+        <v>-3.6399385316071547e-007</v>
       </c>
       <c r="R18">
-        <v>-0.00023452765918568068</v>
+        <v>-0.0002346596565357907</v>
       </c>
       <c r="S18">
-        <v>0.00070711014826681923</v>
+        <v>0.0007070197553689766</v>
       </c>
       <c r="T18">
-        <v>-0.00026076097233246949</v>
+        <v>-0.00026060151393509224</v>
       </c>
       <c r="U18">
-        <v>1.0529223552709273e-006</v>
+        <v>1.9492879247043485e-006</v>
       </c>
       <c r="V18">
-        <v>3.44160149904022e-005</v>
+        <v>3.5299601814821991e-005</v>
       </c>
       <c r="W18">
-        <v>3.8598906396723816e-005</v>
+        <v>3.9605215567342681e-005</v>
       </c>
       <c r="X18">
-        <v>4.3090790189222665e-005</v>
+        <v>4.3938961459226008e-005</v>
       </c>
       <c r="Y18">
-        <v>4.3399096498467226e-005</v>
+        <v>4.4359774896589122e-005</v>
       </c>
       <c r="Z18">
-        <v>3.6045999538909565e-005</v>
+        <v>3.6847810103707113e-005</v>
       </c>
       <c r="AA18">
-        <v>1.7921482915827864e-005</v>
+        <v>1.8586404540738522e-005</v>
       </c>
       <c r="AB18">
-        <v>7.769849208689261e-005</v>
+        <v>7.8527011996696106e-005</v>
       </c>
       <c r="AC18">
-        <v>2.5439297223988492e-005</v>
+        <v>2.6205955447055749e-005</v>
       </c>
       <c r="AD18">
-        <v>1.6898383782980733e-005</v>
+        <v>1.7406167113051325e-005</v>
       </c>
       <c r="AE18">
-        <v>1.9111631464182095e-005</v>
+        <v>1.9730830909869114e-005</v>
       </c>
       <c r="AF18">
-        <v>1.1638624454183509e-006</v>
+        <v>1.1211713232037788e-006</v>
       </c>
       <c r="AG18">
-        <v>6.8241317070275162e-006</v>
+        <v>6.9356755297149915e-006</v>
       </c>
       <c r="AH18">
-        <v>-4.6817119002805801e-005</v>
+        <v>-4.6469561175763666e-005</v>
       </c>
       <c r="AI18">
-        <v>-5.9382548501546993e-005</v>
+        <v>-5.8843734126049053e-005</v>
       </c>
       <c r="AJ18">
-        <v>6.1766429369361955e-005</v>
+        <v>6.237727405889792e-005</v>
       </c>
       <c r="AK18">
-        <v>-6.8797838839408361e-005</v>
+        <v>-6.4909895676663667e-005</v>
       </c>
       <c r="AL18">
-        <v>0.00029625832523900547</v>
+        <v>0.00029847927832251145</v>
       </c>
     </row>
     <row r="19">
@@ -8237,115 +8237,115 @@
         <v>91</v>
       </c>
       <c r="B19" s="109">
-        <v>-0.11759103311761213</v>
+        <v>-0.11804884825137288</v>
       </c>
       <c r="C19">
-        <v>-5.1446202449047057e-006</v>
+        <v>-5.4613813978297603e-006</v>
       </c>
       <c r="D19">
-        <v>-5.990519389073275e-005</v>
+        <v>-5.9952122240905384e-005</v>
       </c>
       <c r="E19">
-        <v>5.6935243250235008e-007</v>
+        <v>5.6974350465891802e-007</v>
       </c>
       <c r="F19">
-        <v>-1.8471393522964249e-005</v>
+        <v>-1.9019670863845164e-005</v>
       </c>
       <c r="G19">
-        <v>-3.7597417642994813e-005</v>
+        <v>-3.8372963454868469e-005</v>
       </c>
       <c r="H19">
-        <v>-4.7107157310353188e-005</v>
+        <v>-4.7341094300730988e-005</v>
       </c>
       <c r="I19">
-        <v>8.4364328717023769e-005</v>
+        <v>8.3498477974469634e-005</v>
       </c>
       <c r="J19">
-        <v>-7.739982226542675e-005</v>
+        <v>-7.6774783677483957e-005</v>
       </c>
       <c r="K19">
-        <v>0.00026315474052200676</v>
+        <v>0.00026207752813952858</v>
       </c>
       <c r="L19">
-        <v>0.000328528900930197</v>
+        <v>0.0003278457226088882</v>
       </c>
       <c r="M19">
-        <v>0.00035424537403122385</v>
+        <v>0.00035319160136341554</v>
       </c>
       <c r="N19">
-        <v>0.00036282616991804211</v>
+        <v>0.00036151255689164448</v>
       </c>
       <c r="O19">
-        <v>-0.00020612950605417477</v>
+        <v>-0.00020700212506315644</v>
       </c>
       <c r="P19">
-        <v>1.5667981527159521e-006</v>
+        <v>1.5478332726930494e-006</v>
       </c>
       <c r="Q19">
-        <v>1.2979724115604848e-006</v>
+        <v>1.2908032289600537e-006</v>
       </c>
       <c r="R19">
-        <v>7.9307027502110864e-005</v>
+        <v>7.9484871073317277e-005</v>
       </c>
       <c r="S19">
-        <v>-0.00026076097233246949</v>
+        <v>-0.00026060151393509224</v>
       </c>
       <c r="T19">
-        <v>0.0015176428227226448</v>
+        <v>0.0015177469819688285</v>
       </c>
       <c r="U19">
-        <v>-1.954756016601963e-005</v>
+        <v>-1.7907910230836128e-005</v>
       </c>
       <c r="V19">
-        <v>-0.00011733645250164716</v>
+        <v>-0.00011560387211441058</v>
       </c>
       <c r="W19">
-        <v>-9.9510944604367152e-005</v>
+        <v>-9.8273371861923564e-005</v>
       </c>
       <c r="X19">
-        <v>-3.837199490623242e-005</v>
+        <v>-3.7188242003786351e-005</v>
       </c>
       <c r="Y19">
-        <v>-6.4207556363445227e-005</v>
+        <v>-6.3030542521512264e-005</v>
       </c>
       <c r="Z19">
-        <v>-0.00011013977608649166</v>
+        <v>-0.00010900764366247546</v>
       </c>
       <c r="AA19">
-        <v>-3.6389777971275895e-005</v>
+        <v>-3.5431759040794025e-005</v>
       </c>
       <c r="AB19">
-        <v>-5.6836811984211174e-005</v>
+        <v>-5.5197557785431199e-005</v>
       </c>
       <c r="AC19">
-        <v>-9.5246400392910778e-005</v>
+        <v>-9.3847256416138388e-005</v>
       </c>
       <c r="AD19">
-        <v>-8.0487868817060468e-005</v>
+        <v>-7.8948896856809511e-005</v>
       </c>
       <c r="AE19">
-        <v>-0.00018168594190748452</v>
+        <v>-0.00018019357803006236</v>
       </c>
       <c r="AF19">
-        <v>-2.61080459476704e-006</v>
+        <v>-2.6359361889454048e-006</v>
       </c>
       <c r="AG19">
-        <v>1.40148763937476e-005</v>
+        <v>1.3748799963182637e-005</v>
       </c>
       <c r="AH19">
-        <v>1.3887436966015879e-005</v>
+        <v>1.3227164634994559e-005</v>
       </c>
       <c r="AI19">
-        <v>9.2868482712168867e-005</v>
+        <v>9.3637202463065259e-005</v>
       </c>
       <c r="AJ19">
-        <v>-1.1257623005125737e-005</v>
+        <v>-1.068163140729555e-005</v>
       </c>
       <c r="AK19">
-        <v>5.9300857922093262e-005</v>
+        <v>6.6450605024529841e-005</v>
       </c>
       <c r="AL19">
-        <v>0.0011382239793279675</v>
+        <v>0.0011417656754611624</v>
       </c>
     </row>
     <row r="20">
@@ -8353,115 +8353,115 @@
         <v>60</v>
       </c>
       <c r="B20" s="111">
-        <v>0.25063635283909563</v>
+        <v>0.24735505712957839</v>
       </c>
       <c r="C20">
-        <v>-3.700345368141268e-005</v>
+        <v>-3.7480288703548542e-005</v>
       </c>
       <c r="D20">
-        <v>4.795299316556062e-005</v>
+        <v>4.8130757723908318e-005</v>
       </c>
       <c r="E20">
-        <v>-3.5145538122851824e-007</v>
+        <v>-3.532575194766782e-007</v>
       </c>
       <c r="F20">
-        <v>-0.00012281038905223406</v>
+        <v>-0.0001244164895879972</v>
       </c>
       <c r="G20">
-        <v>-0.00020850957064266095</v>
+        <v>-0.00021017813004035684</v>
       </c>
       <c r="H20">
-        <v>9.0790645976573993e-005</v>
+        <v>9.1738259786628497e-005</v>
       </c>
       <c r="I20">
-        <v>-3.0148578391721477e-005</v>
+        <v>-3.2466394013554081e-005</v>
       </c>
       <c r="J20">
-        <v>2.3614299999299634e-005</v>
+        <v>2.1288568403162594e-005</v>
       </c>
       <c r="K20">
-        <v>-6.173081192299419e-005</v>
+        <v>-6.2299073328940394e-005</v>
       </c>
       <c r="L20">
-        <v>-1.5008380561770413e-005</v>
+        <v>-1.2742373175474511e-005</v>
       </c>
       <c r="M20">
-        <v>-4.4801905352126622e-005</v>
+        <v>-4.1956448975510147e-005</v>
       </c>
       <c r="N20">
-        <v>8.1408286837688628e-006</v>
+        <v>1.0016710099518202e-005</v>
       </c>
       <c r="O20">
-        <v>1.253240485890963e-005</v>
+        <v>1.3413799586145005e-005</v>
       </c>
       <c r="P20">
-        <v>-9.0804183238525827e-007</v>
+        <v>-9.6480725090007023e-007</v>
       </c>
       <c r="Q20">
-        <v>1.8491670222805805e-006</v>
+        <v>1.781243005085752e-006</v>
       </c>
       <c r="R20">
-        <v>-3.2416326597533315e-005</v>
+        <v>-3.05560379899552e-005</v>
       </c>
       <c r="S20">
-        <v>1.0529223552709273e-006</v>
+        <v>1.9492879247043485e-006</v>
       </c>
       <c r="T20">
-        <v>-1.954756016601963e-005</v>
+        <v>-1.7907910230836128e-005</v>
       </c>
       <c r="U20">
-        <v>0.0043607111347327568</v>
+        <v>0.0043688390600520773</v>
       </c>
       <c r="V20">
-        <v>0.0020870943170429087</v>
+        <v>0.0020935666657551518</v>
       </c>
       <c r="W20">
-        <v>0.002091877925856309</v>
+        <v>0.0020964399708307381</v>
       </c>
       <c r="X20">
-        <v>0.002102578255041745</v>
+        <v>0.0021066723809085547</v>
       </c>
       <c r="Y20">
-        <v>0.0020836224031251386</v>
+        <v>0.0020902758621374968</v>
       </c>
       <c r="Z20">
-        <v>0.0020894370026277027</v>
+        <v>0.0020958183074087653</v>
       </c>
       <c r="AA20">
-        <v>0.0020693967441865464</v>
+        <v>0.0020750595852434559</v>
       </c>
       <c r="AB20">
-        <v>0.0020876091508544841</v>
+        <v>0.002095174415683044</v>
       </c>
       <c r="AC20">
-        <v>0.0021115995066239074</v>
+        <v>0.0021189496498780322</v>
       </c>
       <c r="AD20">
-        <v>0.0021127435328369198</v>
+        <v>0.0021208935932498889</v>
       </c>
       <c r="AE20">
-        <v>0.0021316509186119072</v>
+        <v>0.0021399683870519572</v>
       </c>
       <c r="AF20">
-        <v>-9.0230866150821363e-006</v>
+        <v>-9.1113896075561726e-006</v>
       </c>
       <c r="AG20">
-        <v>-8.7689239253247917e-005</v>
+        <v>-8.7823961366210275e-005</v>
       </c>
       <c r="AH20">
-        <v>-3.8923708354400947e-005</v>
+        <v>-4.1752985355806609e-005</v>
       </c>
       <c r="AI20">
-        <v>0.00071586483129995181</v>
+        <v>0.00072279889790315133</v>
       </c>
       <c r="AJ20">
-        <v>0.00099631619131502645</v>
+        <v>0.0010032812529588058</v>
       </c>
       <c r="AK20">
-        <v>0.00043721242630778657</v>
+        <v>0.00050540442768694737</v>
       </c>
       <c r="AL20">
-        <v>-0.0034803783406338672</v>
+        <v>-0.0034862222953649259</v>
       </c>
     </row>
     <row r="21">
@@ -8469,115 +8469,115 @@
         <v>61</v>
       </c>
       <c r="B21" s="113">
-        <v>0.18422807934894206</v>
+        <v>0.18192833124818628</v>
       </c>
       <c r="C21">
-        <v>-4.9591308710746426e-005</v>
+        <v>-4.9980629689385994e-005</v>
       </c>
       <c r="D21">
-        <v>4.2991731641617986e-005</v>
+        <v>4.3202380057743087e-005</v>
       </c>
       <c r="E21">
-        <v>-3.7216991367534957e-007</v>
+        <v>-3.7417060888370339e-007</v>
       </c>
       <c r="F21">
-        <v>-8.1509598987286469e-005</v>
+        <v>-8.295507258406084e-005</v>
       </c>
       <c r="G21">
-        <v>-0.00018188013625273464</v>
+        <v>-0.00018315885554813263</v>
       </c>
       <c r="H21">
-        <v>9.5399644249249732e-005</v>
+        <v>9.6022349192697188e-005</v>
       </c>
       <c r="I21">
-        <v>6.2187938429037392e-005</v>
+        <v>6.043100965120432e-005</v>
       </c>
       <c r="J21">
-        <v>-4.8513008977520795e-005</v>
+        <v>-5.021440527871188e-005</v>
       </c>
       <c r="K21">
-        <v>-0.00011896613488462276</v>
+        <v>-0.00011999222804868473</v>
       </c>
       <c r="L21">
-        <v>-8.8316072749160821e-005</v>
+        <v>-8.6813063785103756e-005</v>
       </c>
       <c r="M21">
-        <v>-7.2154150656683039e-005</v>
+        <v>-7.0013929492082649e-005</v>
       </c>
       <c r="N21">
-        <v>-4.9110043948302458e-005</v>
+        <v>-4.7510673227908057e-005</v>
       </c>
       <c r="O21">
-        <v>8.0493806280849869e-005</v>
+        <v>8.0660431203442612e-005</v>
       </c>
       <c r="P21">
-        <v>1.267479724149314e-006</v>
+        <v>1.2232728494078606e-006</v>
       </c>
       <c r="Q21">
-        <v>3.7620430098976341e-006</v>
+        <v>3.7015030745122381e-006</v>
       </c>
       <c r="R21">
-        <v>-5.8900756535987145e-005</v>
+        <v>-5.7295345112959382e-005</v>
       </c>
       <c r="S21">
-        <v>3.44160149904022e-005</v>
+        <v>3.5299601814821991e-005</v>
       </c>
       <c r="T21">
-        <v>-0.00011733645250164716</v>
+        <v>-0.00011560387211441058</v>
       </c>
       <c r="U21">
-        <v>0.0020870943170429087</v>
+        <v>0.0020935666657551518</v>
       </c>
       <c r="V21">
-        <v>0.0031226371663294469</v>
+        <v>0.003127818193964781</v>
       </c>
       <c r="W21">
-        <v>0.0020623800336489924</v>
+        <v>0.0020658232570234043</v>
       </c>
       <c r="X21">
-        <v>0.0020639888588599208</v>
+        <v>0.0020670545909504158</v>
       </c>
       <c r="Y21">
-        <v>0.002060889998333129</v>
+        <v>0.0020660352210164759</v>
       </c>
       <c r="Z21">
-        <v>0.0020705671024829008</v>
+        <v>0.0020755920054939909</v>
       </c>
       <c r="AA21">
-        <v>0.0020475290202281661</v>
+        <v>0.0020517726424585389</v>
       </c>
       <c r="AB21">
-        <v>0.0020718271831167935</v>
+        <v>0.0020777852027579315</v>
       </c>
       <c r="AC21">
-        <v>0.0020862731403779762</v>
+        <v>0.0020919959410161731</v>
       </c>
       <c r="AD21">
-        <v>0.0020761026940223849</v>
+        <v>0.0020824157882239729</v>
       </c>
       <c r="AE21">
-        <v>0.0020930904194812828</v>
+        <v>0.0020995689332331648</v>
       </c>
       <c r="AF21">
-        <v>-6.442607260345589e-006</v>
+        <v>-6.5412148449336702e-006</v>
       </c>
       <c r="AG21">
-        <v>-9.3114263607707619e-005</v>
+        <v>-9.3040719214897087e-005</v>
       </c>
       <c r="AH21">
-        <v>-2.515438375788125e-005</v>
+        <v>-2.7215961954230881e-005</v>
       </c>
       <c r="AI21">
-        <v>0.00062056831042436693</v>
+        <v>0.00062630465113189628</v>
       </c>
       <c r="AJ21">
-        <v>0.0008714494058112577</v>
+        <v>0.00087749681937692521</v>
       </c>
       <c r="AK21">
-        <v>0.00038209653620029159</v>
+        <v>0.0004168063107550103</v>
       </c>
       <c r="AL21">
-        <v>-0.0033052808590818949</v>
+        <v>-0.0033109973661547016</v>
       </c>
     </row>
     <row r="22">
@@ -8585,115 +8585,115 @@
         <v>62</v>
       </c>
       <c r="B22" s="115">
-        <v>0.17611113396838282</v>
+        <v>0.17487354807125299</v>
       </c>
       <c r="C22">
-        <v>-6.2267434250050691e-005</v>
+        <v>-6.2602483746615852e-005</v>
       </c>
       <c r="D22">
-        <v>2.6073869286871373e-005</v>
+        <v>2.5909104870195168e-005</v>
       </c>
       <c r="E22">
-        <v>-2.3580908268989737e-007</v>
+        <v>-2.3501041342042465e-007</v>
       </c>
       <c r="F22">
-        <v>-6.6888872018463447e-005</v>
+        <v>-6.7848612160217487e-005</v>
       </c>
       <c r="G22">
-        <v>-0.00015823164391327434</v>
+        <v>-0.00015993530085241196</v>
       </c>
       <c r="H22">
-        <v>9.1153278991749583e-005</v>
+        <v>9.2158404481895915e-005</v>
       </c>
       <c r="I22">
-        <v>-2.031882791498317e-006</v>
+        <v>-2.797375905598011e-006</v>
       </c>
       <c r="J22">
-        <v>-2.0325985220728208e-005</v>
+        <v>-2.1437966321094992e-005</v>
       </c>
       <c r="K22">
-        <v>-5.5013635954640318e-005</v>
+        <v>-5.6698988704880328e-005</v>
       </c>
       <c r="L22">
-        <v>-4.6571471171513615e-005</v>
+        <v>-4.536775278098917e-005</v>
       </c>
       <c r="M22">
-        <v>-2.3870612708282385e-005</v>
+        <v>-2.1667358744415096e-005</v>
       </c>
       <c r="N22">
-        <v>1.0633765871446142e-005</v>
+        <v>1.2305872353615341e-005</v>
       </c>
       <c r="O22">
-        <v>6.7918691504911745e-005</v>
+        <v>6.8495742001418113e-005</v>
       </c>
       <c r="P22">
-        <v>5.2827120676362946e-007</v>
+        <v>4.7341485122719644e-007</v>
       </c>
       <c r="Q22">
-        <v>3.496302200014177e-006</v>
+        <v>3.4522138909796893e-006</v>
       </c>
       <c r="R22">
-        <v>-4.0318313042413784e-005</v>
+        <v>-3.9057336877795627e-005</v>
       </c>
       <c r="S22">
-        <v>3.8598906396723816e-005</v>
+        <v>3.9605215567342681e-005</v>
       </c>
       <c r="T22">
-        <v>-9.9510944604367152e-005</v>
+        <v>-9.8273371861923564e-005</v>
       </c>
       <c r="U22">
-        <v>0.002091877925856309</v>
+        <v>0.0020964399708307381</v>
       </c>
       <c r="V22">
-        <v>0.0020623800336489924</v>
+        <v>0.0020658232570234043</v>
       </c>
       <c r="W22">
-        <v>0.0033602491770216335</v>
+        <v>0.0033627905173597714</v>
       </c>
       <c r="X22">
-        <v>0.0020651752940866234</v>
+        <v>0.0020668604362945307</v>
       </c>
       <c r="Y22">
-        <v>0.0020601810634492375</v>
+        <v>0.0020639200551037869</v>
       </c>
       <c r="Z22">
-        <v>0.002064158606726174</v>
+        <v>0.0020678486842535034</v>
       </c>
       <c r="AA22">
-        <v>0.0020443522076683579</v>
+        <v>0.0020469187851532723</v>
       </c>
       <c r="AB22">
-        <v>0.0020609519816339309</v>
+        <v>0.0020654172142606326</v>
       </c>
       <c r="AC22">
-        <v>0.0020817351100469901</v>
+        <v>0.0020858060965314191</v>
       </c>
       <c r="AD22">
-        <v>0.002074479894959159</v>
+        <v>0.0020788759304035728</v>
       </c>
       <c r="AE22">
-        <v>0.0020922194962590466</v>
+        <v>0.0020973082291966382</v>
       </c>
       <c r="AF22">
-        <v>-1.2425473764993521e-005</v>
+        <v>-1.2452729580826351e-005</v>
       </c>
       <c r="AG22">
-        <v>2.7846839887154078e-005</v>
+        <v>2.7585995816681266e-005</v>
       </c>
       <c r="AH22">
-        <v>2.0192887892048112e-005</v>
+        <v>1.8702870754481931e-005</v>
       </c>
       <c r="AI22">
-        <v>0.00055243687131323793</v>
+        <v>0.00055677203337236843</v>
       </c>
       <c r="AJ22">
-        <v>0.00093110972511325151</v>
+        <v>0.00093582211518791021</v>
       </c>
       <c r="AK22">
-        <v>0.00041949400559103899</v>
+        <v>0.00037813280713927902</v>
       </c>
       <c r="AL22">
-        <v>-0.0026965335794873306</v>
+        <v>-0.0026897581478553686</v>
       </c>
     </row>
     <row r="23">
@@ -8701,115 +8701,115 @@
         <v>63</v>
       </c>
       <c r="B23" s="117">
-        <v>0.10866776402723567</v>
+        <v>0.10763850628016935</v>
       </c>
       <c r="C23">
-        <v>-5.826686717243177e-005</v>
+        <v>-5.8408117287658447e-005</v>
       </c>
       <c r="D23">
-        <v>2.1326741956019524e-005</v>
+        <v>2.1228324798706899e-005</v>
       </c>
       <c r="E23">
-        <v>-1.6672695676636109e-007</v>
+        <v>-1.6678487566103056e-007</v>
       </c>
       <c r="F23">
-        <v>-0.00010006611722477488</v>
+        <v>-0.00010109399779700163</v>
       </c>
       <c r="G23">
-        <v>-0.00018221139465057336</v>
+        <v>-0.00018376457093564021</v>
       </c>
       <c r="H23">
-        <v>8.9940267334252116e-005</v>
+        <v>9.0750299793510177e-005</v>
       </c>
       <c r="I23">
-        <v>4.0314357295996453e-005</v>
+        <v>4.0772776902932078e-005</v>
       </c>
       <c r="J23">
-        <v>-3.8860004471957463e-005</v>
+        <v>-4.1486655542825619e-005</v>
       </c>
       <c r="K23">
-        <v>-5.7781675802826699e-005</v>
+        <v>-5.8865349146027587e-005</v>
       </c>
       <c r="L23">
-        <v>-1.510709320142866e-005</v>
+        <v>-1.249148580986033e-005</v>
       </c>
       <c r="M23">
-        <v>-1.7739174661277426e-005</v>
+        <v>-1.5005553595656793e-005</v>
       </c>
       <c r="N23">
-        <v>3.8119284756727182e-005</v>
+        <v>4.0658308357769931e-005</v>
       </c>
       <c r="O23">
-        <v>3.8211467289232066e-005</v>
+        <v>3.7920105360446594e-005</v>
       </c>
       <c r="P23">
-        <v>-1.3361758790843563e-006</v>
+        <v>-1.3794930473454928e-006</v>
       </c>
       <c r="Q23">
-        <v>2.9406742007107683e-006</v>
+        <v>2.9097383727674577e-006</v>
       </c>
       <c r="R23">
-        <v>-2.7876233397252943e-005</v>
+        <v>-2.5827297826288664e-005</v>
       </c>
       <c r="S23">
-        <v>4.3090790189222665e-005</v>
+        <v>4.3938961459226008e-005</v>
       </c>
       <c r="T23">
-        <v>-3.837199490623242e-005</v>
+        <v>-3.7188242003786351e-005</v>
       </c>
       <c r="U23">
-        <v>0.002102578255041745</v>
+        <v>0.0021066723809085547</v>
       </c>
       <c r="V23">
-        <v>0.0020639888588599208</v>
+        <v>0.0020670545909504158</v>
       </c>
       <c r="W23">
-        <v>0.0020651752940866234</v>
+        <v>0.0020668604362945307</v>
       </c>
       <c r="X23">
-        <v>0.0032928411563011256</v>
+        <v>0.0032933279338765165</v>
       </c>
       <c r="Y23">
-        <v>0.002064444752521545</v>
+        <v>0.0020677166819120987</v>
       </c>
       <c r="Z23">
-        <v>0.0020678683260949454</v>
+        <v>0.0020712587759624799</v>
       </c>
       <c r="AA23">
-        <v>0.0020508140174251084</v>
+        <v>0.0020530097062713558</v>
       </c>
       <c r="AB23">
-        <v>0.0020698780177373886</v>
+        <v>0.0020742266701591966</v>
       </c>
       <c r="AC23">
-        <v>0.0020865334189532421</v>
+        <v>0.0020902163116772315</v>
       </c>
       <c r="AD23">
-        <v>0.0020794617109151929</v>
+        <v>0.0020835292071259889</v>
       </c>
       <c r="AE23">
-        <v>0.0020929681397010495</v>
+        <v>0.002097594095958269</v>
       </c>
       <c r="AF23">
-        <v>-1.3388608853577132e-005</v>
+        <v>-1.3410469193181691e-005</v>
       </c>
       <c r="AG23">
-        <v>3.6465521242944678e-005</v>
+        <v>3.6116526250481537e-005</v>
       </c>
       <c r="AH23">
-        <v>1.3368174736967462e-005</v>
+        <v>1.1292604487489974e-005</v>
       </c>
       <c r="AI23">
-        <v>0.00057554716155938049</v>
+        <v>0.00057969522001659996</v>
       </c>
       <c r="AJ23">
-        <v>0.00092405163779684567</v>
+        <v>0.00092835563251759902</v>
       </c>
       <c r="AK23">
-        <v>0.00043957354444606529</v>
+        <v>0.00038369993164404754</v>
       </c>
       <c r="AL23">
-        <v>-0.0025541327155281131</v>
+        <v>-0.002550070331434051</v>
       </c>
     </row>
     <row r="24">
@@ -8817,115 +8817,115 @@
         <v>64</v>
       </c>
       <c r="B24" s="119">
-        <v>0.1655092828949748</v>
+        <v>0.16304152301480423</v>
       </c>
       <c r="C24">
-        <v>-5.0174190819130785e-005</v>
+        <v>-5.042314594800197e-005</v>
       </c>
       <c r="D24">
-        <v>6.5248669655279534e-006</v>
+        <v>6.8829809831329886e-006</v>
       </c>
       <c r="E24">
-        <v>-3.7500265445943861e-008</v>
+        <v>-4.0623993365705821e-008</v>
       </c>
       <c r="F24">
-        <v>-0.0001263081914369294</v>
+        <v>-0.00012758147285488116</v>
       </c>
       <c r="G24">
-        <v>-0.00020486134641343659</v>
+        <v>-0.00020606458585733571</v>
       </c>
       <c r="H24">
-        <v>8.7445766701685281e-005</v>
+        <v>8.8126120935317102e-005</v>
       </c>
       <c r="I24">
-        <v>7.1114917507132495e-005</v>
+        <v>6.9254676939382734e-005</v>
       </c>
       <c r="J24">
-        <v>-8.2410979926316082e-005</v>
+        <v>-8.4047184660404877e-005</v>
       </c>
       <c r="K24">
-        <v>-5.3697833389746222e-005</v>
+        <v>-5.4663939063665954e-005</v>
       </c>
       <c r="L24">
-        <v>-4.9613902536066717e-005</v>
+        <v>-4.7960117308113088e-005</v>
       </c>
       <c r="M24">
-        <v>-1.4184649306315242e-005</v>
+        <v>-1.1828058482091426e-005</v>
       </c>
       <c r="N24">
-        <v>2.8785063358073592e-005</v>
+        <v>3.0766009301888466e-005</v>
       </c>
       <c r="O24">
-        <v>1.8447568700749465e-005</v>
+        <v>1.9168559081904975e-005</v>
       </c>
       <c r="P24">
-        <v>-2.8306574873551401e-007</v>
+        <v>-3.4264232788703728e-007</v>
       </c>
       <c r="Q24">
-        <v>2.5684994098722313e-006</v>
+        <v>2.5143723418842807e-006</v>
       </c>
       <c r="R24">
-        <v>-6.6530850359639558e-005</v>
+        <v>-6.4993340785407712e-005</v>
       </c>
       <c r="S24">
-        <v>4.3399096498467226e-005</v>
+        <v>4.4359774896589122e-005</v>
       </c>
       <c r="T24">
-        <v>-6.4207556363445227e-005</v>
+        <v>-6.3030542521512264e-005</v>
       </c>
       <c r="U24">
-        <v>0.0020836224031251386</v>
+        <v>0.0020902758621374968</v>
       </c>
       <c r="V24">
-        <v>0.002060889998333129</v>
+        <v>0.0020660352210164759</v>
       </c>
       <c r="W24">
-        <v>0.0020601810634492375</v>
+        <v>0.0020639200551037869</v>
       </c>
       <c r="X24">
-        <v>0.002064444752521545</v>
+        <v>0.0020677166819120987</v>
       </c>
       <c r="Y24">
-        <v>0.003336199165456152</v>
+        <v>0.0033415438141906288</v>
       </c>
       <c r="Z24">
-        <v>0.0020582579680998654</v>
+        <v>0.0020634144522886939</v>
       </c>
       <c r="AA24">
-        <v>0.0020370021011880302</v>
+        <v>0.002041446818227884</v>
       </c>
       <c r="AB24">
-        <v>0.002057670214965287</v>
+        <v>0.0020637448988096202</v>
       </c>
       <c r="AC24">
-        <v>0.0020755290388485173</v>
+        <v>0.002081420038662499</v>
       </c>
       <c r="AD24">
-        <v>0.0020669252306040166</v>
+        <v>0.0020734266146234899</v>
       </c>
       <c r="AE24">
-        <v>0.0020867658015134021</v>
+        <v>0.002093455208571092</v>
       </c>
       <c r="AF24">
-        <v>-1.1947387809798007e-005</v>
+        <v>-1.2034220114947982e-005</v>
       </c>
       <c r="AG24">
-        <v>-2.9473134279447794e-005</v>
+        <v>-2.9430259554203147e-005</v>
       </c>
       <c r="AH24">
-        <v>1.3409944193912515e-005</v>
+        <v>1.1291036672501796e-005</v>
       </c>
       <c r="AI24">
-        <v>0.00048965526110030574</v>
+        <v>0.00049570754863064608</v>
       </c>
       <c r="AJ24">
-        <v>0.0007483355149444337</v>
+        <v>0.00075484402302662635</v>
       </c>
       <c r="AK24">
-        <v>0.00036651710328811343</v>
+        <v>0.00040568614361482928</v>
       </c>
       <c r="AL24">
-        <v>-0.0021364165612331554</v>
+        <v>-0.0021473259189158191</v>
       </c>
     </row>
     <row r="25">
@@ -8933,115 +8933,115 @@
         <v>65</v>
       </c>
       <c r="B25" s="121">
-        <v>0.07754216994917193</v>
+        <v>0.07532842846845246</v>
       </c>
       <c r="C25">
-        <v>-4.2629870900569591e-005</v>
+        <v>-4.3082702626064534e-005</v>
       </c>
       <c r="D25">
-        <v>6.5657177947819889e-005</v>
+        <v>6.5535942142662743e-005</v>
       </c>
       <c r="E25">
-        <v>-5.6019454807650939e-007</v>
+        <v>-5.5983144051850427e-007</v>
       </c>
       <c r="F25">
-        <v>-7.3997063512828938e-005</v>
+        <v>-7.5031401256444013e-005</v>
       </c>
       <c r="G25">
-        <v>-0.00017474324192125716</v>
+        <v>-0.00017607238781062125</v>
       </c>
       <c r="H25">
-        <v>0.0001001418964368541</v>
+        <v>0.0001010545858191576</v>
       </c>
       <c r="I25">
-        <v>1.2249078888976065e-005</v>
+        <v>1.0881209227988579e-005</v>
       </c>
       <c r="J25">
-        <v>-2.2537636369674829e-005</v>
+        <v>-2.444286270466417e-005</v>
       </c>
       <c r="K25">
-        <v>-9.860095398986162e-005</v>
+        <v>-9.8923831817166906e-005</v>
       </c>
       <c r="L25">
-        <v>-0.00010023035834984067</v>
+        <v>-9.8252908133621098e-005</v>
       </c>
       <c r="M25">
-        <v>-8.2612701275149849e-005</v>
+        <v>-8.0085500054187758e-005</v>
       </c>
       <c r="N25">
-        <v>-9.0152015527852577e-005</v>
+        <v>-8.7941985322004344e-005</v>
       </c>
       <c r="O25">
-        <v>4.6568427712206451e-005</v>
+        <v>4.6999791038128381e-005</v>
       </c>
       <c r="P25">
-        <v>-9.6023156145441641e-007</v>
+        <v>-1.0098648268590349e-006</v>
       </c>
       <c r="Q25">
-        <v>2.4098941002141644e-006</v>
+        <v>2.3467233009478266e-006</v>
       </c>
       <c r="R25">
-        <v>-6.5134884432676134e-005</v>
+        <v>-6.3434906773530194e-005</v>
       </c>
       <c r="S25">
-        <v>3.6045999538909565e-005</v>
+        <v>3.6847810103707113e-005</v>
       </c>
       <c r="T25">
-        <v>-0.00011013977608649166</v>
+        <v>-0.00010900764366247546</v>
       </c>
       <c r="U25">
-        <v>0.0020894370026277027</v>
+        <v>0.0020958183074087653</v>
       </c>
       <c r="V25">
-        <v>0.0020705671024829008</v>
+        <v>0.0020755920054939909</v>
       </c>
       <c r="W25">
-        <v>0.002064158606726174</v>
+        <v>0.0020678486842535034</v>
       </c>
       <c r="X25">
-        <v>0.0020678683260949454</v>
+        <v>0.0020712587759624799</v>
       </c>
       <c r="Y25">
-        <v>0.0020582579680998654</v>
+        <v>0.0020634144522886939</v>
       </c>
       <c r="Z25">
-        <v>0.0030889156925130862</v>
+        <v>0.0030941263963704295</v>
       </c>
       <c r="AA25">
-        <v>0.0020644844975072438</v>
+        <v>0.0020689090970414711</v>
       </c>
       <c r="AB25">
-        <v>0.0020781405049368649</v>
+        <v>0.0020839130169449695</v>
       </c>
       <c r="AC25">
-        <v>0.0020915149333601809</v>
+        <v>0.0020972366461209199</v>
       </c>
       <c r="AD25">
-        <v>0.0020822894596726487</v>
+        <v>0.0020885501285572861</v>
       </c>
       <c r="AE25">
-        <v>0.0021010912340386268</v>
+        <v>0.0021075173235156177</v>
       </c>
       <c r="AF25">
-        <v>-8.8034259819557746e-006</v>
+        <v>-8.8108047248210055e-006</v>
       </c>
       <c r="AG25">
-        <v>-3.6316833699706211e-005</v>
+        <v>-3.6421879385295779e-005</v>
       </c>
       <c r="AH25">
-        <v>4.7658619422262347e-006</v>
+        <v>2.7538363387239549e-006</v>
       </c>
       <c r="AI25">
-        <v>0.00063080800262340665</v>
+        <v>0.00063641833513826494</v>
       </c>
       <c r="AJ25">
-        <v>0.0010216779667469654</v>
+        <v>0.001027757174410745</v>
       </c>
       <c r="AK25">
-        <v>0.00030072956921511592</v>
+        <v>0.00036462736975416833</v>
       </c>
       <c r="AL25">
-        <v>-0.0037594017186809957</v>
+        <v>-0.0037556356919631927</v>
       </c>
     </row>
     <row r="26">
@@ -9049,115 +9049,115 @@
         <v>66</v>
       </c>
       <c r="B26" s="123">
-        <v>0.072629222339300484</v>
+        <v>0.072034395567422457</v>
       </c>
       <c r="C26">
-        <v>-2.4561806571481832e-005</v>
+        <v>-2.5142560580283122e-005</v>
       </c>
       <c r="D26">
-        <v>4.2284153889774259e-005</v>
+        <v>4.2639364669928501e-005</v>
       </c>
       <c r="E26">
-        <v>-3.9623613642080207e-007</v>
+        <v>-3.992153775717283e-007</v>
       </c>
       <c r="F26">
-        <v>-4.6984366519952107e-005</v>
+        <v>-4.9325851238072333e-005</v>
       </c>
       <c r="G26">
-        <v>-0.0001537601650462794</v>
+        <v>-0.0001554995325619835</v>
       </c>
       <c r="H26">
-        <v>0.00010417043239365525</v>
+        <v>0.000104557831198107</v>
       </c>
       <c r="I26">
-        <v>-1.4777864761639789e-005</v>
+        <v>-1.6760029603749785e-005</v>
       </c>
       <c r="J26">
-        <v>-7.2646382838468821e-006</v>
+        <v>-8.923909431237222e-006</v>
       </c>
       <c r="K26">
-        <v>-6.026386910939715e-005</v>
+        <v>-6.1317867246222938e-005</v>
       </c>
       <c r="L26">
-        <v>-4.2191261575575886e-005</v>
+        <v>-4.0656052550373258e-005</v>
       </c>
       <c r="M26">
-        <v>-4.7674315698546397e-005</v>
+        <v>-4.5597508974621758e-005</v>
       </c>
       <c r="N26">
-        <v>-6.5709038139884755e-005</v>
+        <v>-6.3425491695266191e-005</v>
       </c>
       <c r="O26">
-        <v>2.7524613694881279e-005</v>
+        <v>2.8439756251447644e-005</v>
       </c>
       <c r="P26">
-        <v>-2.0599243549192285e-006</v>
+        <v>-2.1617005555535043e-006</v>
       </c>
       <c r="Q26">
-        <v>7.2670580250843814e-007</v>
+        <v>6.7963536811460842e-007</v>
       </c>
       <c r="R26">
-        <v>-4.4408562723469071e-005</v>
+        <v>-4.2839034886375013e-005</v>
       </c>
       <c r="S26">
-        <v>1.7921482915827864e-005</v>
+        <v>1.8586404540738522e-005</v>
       </c>
       <c r="T26">
-        <v>-3.6389777971275895e-005</v>
+        <v>-3.5431759040794025e-005</v>
       </c>
       <c r="U26">
-        <v>0.0020693967441865464</v>
+        <v>0.0020750595852434559</v>
       </c>
       <c r="V26">
-        <v>0.0020475290202281661</v>
+        <v>0.0020517726424585389</v>
       </c>
       <c r="W26">
-        <v>0.0020443522076683579</v>
+        <v>0.0020469187851532723</v>
       </c>
       <c r="X26">
-        <v>0.0020508140174251084</v>
+        <v>0.0020530097062713558</v>
       </c>
       <c r="Y26">
-        <v>0.0020370021011880302</v>
+        <v>0.002041446818227884</v>
       </c>
       <c r="Z26">
-        <v>0.0020644844975072438</v>
+        <v>0.0020689090970414711</v>
       </c>
       <c r="AA26">
-        <v>0.0028142485432344037</v>
+        <v>0.0028171210946466899</v>
       </c>
       <c r="AB26">
-        <v>0.0020657298839797797</v>
+        <v>0.0020707999628469375</v>
       </c>
       <c r="AC26">
-        <v>0.0020714286398387741</v>
+        <v>0.0020764549009668191</v>
       </c>
       <c r="AD26">
-        <v>0.0020665569678104288</v>
+        <v>0.0020717283018416984</v>
       </c>
       <c r="AE26">
-        <v>0.0020849172314799571</v>
+        <v>0.0020905292211753539</v>
       </c>
       <c r="AF26">
-        <v>-8.921247943055469e-006</v>
+        <v>-8.8811130033233178e-006</v>
       </c>
       <c r="AG26">
-        <v>-1.3482635775096053e-005</v>
+        <v>-1.3868474189457777e-005</v>
       </c>
       <c r="AH26">
-        <v>2.2214690516071861e-005</v>
+        <v>1.9265447203122806e-005</v>
       </c>
       <c r="AI26">
-        <v>0.00064467241346130913</v>
+        <v>0.00064977022344213354</v>
       </c>
       <c r="AJ26">
-        <v>0.00087276868640431349</v>
+        <v>0.00087819792942374364</v>
       </c>
       <c r="AK26">
-        <v>0.00043826327745392901</v>
+        <v>0.00048306336569502249</v>
       </c>
       <c r="AL26">
-        <v>-0.0028586104855541487</v>
+        <v>-0.0028680459730651984</v>
       </c>
     </row>
     <row r="27">
@@ -9165,115 +9165,115 @@
         <v>67</v>
       </c>
       <c r="B27" s="125">
-        <v>0.083302571177080245</v>
+        <v>0.080831274678797471</v>
       </c>
       <c r="C27">
-        <v>-2.7528087196425463e-005</v>
+        <v>-2.8019454047388755e-005</v>
       </c>
       <c r="D27">
-        <v>1.264920486046886e-005</v>
+        <v>1.2736551211482011e-005</v>
       </c>
       <c r="E27">
-        <v>-1.6106916197582968e-007</v>
+        <v>-1.6210919784383107e-007</v>
       </c>
       <c r="F27">
-        <v>-6.2434253876294952e-005</v>
+        <v>-6.3567293799264441e-005</v>
       </c>
       <c r="G27">
-        <v>-0.00011696518752404421</v>
+        <v>-0.00011836384065181665</v>
       </c>
       <c r="H27">
-        <v>0.00010841865699134592</v>
+        <v>0.00010942995137356306</v>
       </c>
       <c r="I27">
-        <v>5.7955561356669207e-005</v>
+        <v>5.5895091879126519e-005</v>
       </c>
       <c r="J27">
-        <v>-4.4187601372885736e-005</v>
+        <v>-4.6377116563901116e-005</v>
       </c>
       <c r="K27">
-        <v>-3.9508774239970044e-005</v>
+        <v>-4.055750456241256e-005</v>
       </c>
       <c r="L27">
-        <v>1.7171750966217883e-005</v>
+        <v>2.0040460459102736e-005</v>
       </c>
       <c r="M27">
-        <v>5.8199118585528376e-005</v>
+        <v>6.0942412835395454e-005</v>
       </c>
       <c r="N27">
-        <v>7.5695247923771329e-005</v>
+        <v>7.7510162386103623e-005</v>
       </c>
       <c r="O27">
-        <v>-6.1662800310140512e-006</v>
+        <v>-4.5204783373577239e-006</v>
       </c>
       <c r="P27">
-        <v>-1.2772291081765237e-006</v>
+        <v>-1.3025294112941431e-006</v>
       </c>
       <c r="Q27">
-        <v>6.128589158802805e-007</v>
+        <v>5.6149116629888317e-007</v>
       </c>
       <c r="R27">
-        <v>-6.4107242135798758e-005</v>
+        <v>-6.2496620788231143e-005</v>
       </c>
       <c r="S27">
-        <v>7.769849208689261e-005</v>
+        <v>7.8527011996696106e-005</v>
       </c>
       <c r="T27">
-        <v>-5.6836811984211174e-005</v>
+        <v>-5.5197557785431199e-005</v>
       </c>
       <c r="U27">
-        <v>0.0020876091508544841</v>
+        <v>0.002095174415683044</v>
       </c>
       <c r="V27">
-        <v>0.0020718271831167935</v>
+        <v>0.0020777852027579315</v>
       </c>
       <c r="W27">
-        <v>0.0020609519816339309</v>
+        <v>0.0020654172142606326</v>
       </c>
       <c r="X27">
-        <v>0.0020698780177373886</v>
+        <v>0.0020742266701591966</v>
       </c>
       <c r="Y27">
-        <v>0.002057670214965287</v>
+        <v>0.0020637448988096202</v>
       </c>
       <c r="Z27">
-        <v>0.0020781405049368649</v>
+        <v>0.0020839130169449695</v>
       </c>
       <c r="AA27">
-        <v>0.0020657298839797797</v>
+        <v>0.0020707999628469375</v>
       </c>
       <c r="AB27">
-        <v>0.0030998766894029858</v>
+        <v>0.0031064781299579643</v>
       </c>
       <c r="AC27">
-        <v>0.0020907685043308937</v>
+        <v>0.0020974134926408797</v>
       </c>
       <c r="AD27">
-        <v>0.0020843168729976092</v>
+        <v>0.0020915192115131412</v>
       </c>
       <c r="AE27">
-        <v>0.0021040562434955549</v>
+        <v>0.0021113645958403459</v>
       </c>
       <c r="AF27">
-        <v>-9.9598499125970817e-006</v>
+        <v>-1.0025383153013907e-005</v>
       </c>
       <c r="AG27">
-        <v>-2.5830837819339786e-006</v>
+        <v>-2.5867165887358003e-006</v>
       </c>
       <c r="AH27">
-        <v>-4.3628690754541087e-007</v>
+        <v>-2.6661650666187814e-006</v>
       </c>
       <c r="AI27">
-        <v>0.00068118565533865699</v>
+        <v>0.00068762524613509069</v>
       </c>
       <c r="AJ27">
-        <v>0.00096929839544497055</v>
+        <v>0.00097598438209600322</v>
       </c>
       <c r="AK27">
-        <v>0.00030965878251898254</v>
+        <v>0.00041312242488299384</v>
       </c>
       <c r="AL27">
-        <v>-0.0020859353157586824</v>
+        <v>-0.0020915791541587948</v>
       </c>
     </row>
     <row r="28">
@@ -9281,115 +9281,115 @@
         <v>68</v>
       </c>
       <c r="B28" s="127">
-        <v>0.15819019543261828</v>
+        <v>0.15549771104210355</v>
       </c>
       <c r="C28">
-        <v>-3.8584073993231703e-005</v>
+        <v>-3.8873262195926312e-005</v>
       </c>
       <c r="D28">
-        <v>2.6957194944391555e-005</v>
+        <v>2.7164932519162244e-005</v>
       </c>
       <c r="E28">
-        <v>-2.3525181102311034e-007</v>
+        <v>-2.3724628733144898e-007</v>
       </c>
       <c r="F28">
-        <v>-0.00010534650333036697</v>
+        <v>-0.00010685115880732464</v>
       </c>
       <c r="G28">
-        <v>-0.00018680862273720705</v>
+        <v>-0.00018844209870912096</v>
       </c>
       <c r="H28">
-        <v>8.9263433807360736e-005</v>
+        <v>9.0088088657474559e-005</v>
       </c>
       <c r="I28">
-        <v>1.0375518309037584e-005</v>
+        <v>8.3497468397965464e-006</v>
       </c>
       <c r="J28">
-        <v>-4.4753739520121162e-005</v>
+        <v>-4.6762092608255805e-005</v>
       </c>
       <c r="K28">
-        <v>-7.7634912757440413e-005</v>
+        <v>-7.8643550191122465e-005</v>
       </c>
       <c r="L28">
-        <v>-4.9602434788195617e-005</v>
+        <v>-4.8002937312104348e-005</v>
       </c>
       <c r="M28">
-        <v>-5.3292285921018446e-005</v>
+        <v>-5.0953442497791946e-005</v>
       </c>
       <c r="N28">
-        <v>-3.2810424652359805e-005</v>
+        <v>-3.1481235333647838e-005</v>
       </c>
       <c r="O28">
-        <v>-1.7576534025369548e-006</v>
+        <v>-1.1521190901402339e-006</v>
       </c>
       <c r="P28">
-        <v>-1.7200012153929567e-006</v>
+        <v>-1.7751102441287834e-006</v>
       </c>
       <c r="Q28">
-        <v>3.2550493293675512e-006</v>
+        <v>3.1936538727755874e-006</v>
       </c>
       <c r="R28">
-        <v>-6.7517939387905148e-005</v>
+        <v>-6.5810035346780863e-005</v>
       </c>
       <c r="S28">
-        <v>2.5439297223988492e-005</v>
+        <v>2.6205955447055749e-005</v>
       </c>
       <c r="T28">
-        <v>-9.5246400392910778e-005</v>
+        <v>-9.3847256416138388e-005</v>
       </c>
       <c r="U28">
-        <v>0.0021115995066239074</v>
+        <v>0.0021189496498780322</v>
       </c>
       <c r="V28">
-        <v>0.0020862731403779762</v>
+        <v>0.0020919959410161731</v>
       </c>
       <c r="W28">
-        <v>0.0020817351100469901</v>
+        <v>0.0020858060965314191</v>
       </c>
       <c r="X28">
-        <v>0.0020865334189532421</v>
+        <v>0.0020902163116772315</v>
       </c>
       <c r="Y28">
-        <v>0.0020755290388485173</v>
+        <v>0.002081420038662499</v>
       </c>
       <c r="Z28">
-        <v>0.0020915149333601809</v>
+        <v>0.0020972366461209199</v>
       </c>
       <c r="AA28">
-        <v>0.0020714286398387741</v>
+        <v>0.0020764549009668191</v>
       </c>
       <c r="AB28">
-        <v>0.0020907685043308937</v>
+        <v>0.0020974134926408797</v>
       </c>
       <c r="AC28">
-        <v>0.0034881703084892182</v>
+        <v>0.0034945328300634796</v>
       </c>
       <c r="AD28">
-        <v>0.0021031537177370056</v>
+        <v>0.002110354118226002</v>
       </c>
       <c r="AE28">
-        <v>0.0021277316350224252</v>
+        <v>0.0021350800594204305</v>
       </c>
       <c r="AF28">
-        <v>-7.3398769053672271e-006</v>
+        <v>-7.389180531178392e-006</v>
       </c>
       <c r="AG28">
-        <v>-2.3139307959507416e-005</v>
+        <v>-2.3369000240203029e-005</v>
       </c>
       <c r="AH28">
-        <v>-2.8839173461498938e-005</v>
+        <v>-3.107945322566884e-005</v>
       </c>
       <c r="AI28">
-        <v>0.00070692472901590238</v>
+        <v>0.00071313412638618551</v>
       </c>
       <c r="AJ28">
-        <v>0.0009754237245785159</v>
+        <v>0.00098179799015844587</v>
       </c>
       <c r="AK28">
-        <v>0.00038483822584461664</v>
+        <v>0.00044732175954199731</v>
       </c>
       <c r="AL28">
-        <v>-0.0026730236512599688</v>
+        <v>-0.002679644474326216</v>
       </c>
     </row>
     <row r="29">
@@ -9397,115 +9397,115 @@
         <v>69</v>
       </c>
       <c r="B29" s="129">
-        <v>0.13263894542935026</v>
+        <v>0.12986743611345791</v>
       </c>
       <c r="C29">
-        <v>-4.0237992835788979e-005</v>
+        <v>-4.0781699915135067e-005</v>
       </c>
       <c r="D29">
-        <v>2.2741333583514711e-005</v>
+        <v>2.2956164990747818e-005</v>
       </c>
       <c r="E29">
-        <v>-2.0962513312875841e-007</v>
+        <v>-2.1177052323927679e-007</v>
       </c>
       <c r="F29">
-        <v>-8.2780177273795975e-005</v>
+        <v>-8.4898031006578597e-005</v>
       </c>
       <c r="G29">
-        <v>-0.00014673836609690419</v>
+        <v>-0.00014890060259505923</v>
       </c>
       <c r="H29">
-        <v>0.00011945629031378408</v>
+        <v>0.00012003343515775517</v>
       </c>
       <c r="I29">
-        <v>-1.4658656117199059e-005</v>
+        <v>-1.7352770741063412e-005</v>
       </c>
       <c r="J29">
-        <v>-3.1358436202584897e-005</v>
+        <v>-3.3452044187214005e-005</v>
       </c>
       <c r="K29">
-        <v>-5.775452858847196e-005</v>
+        <v>-5.9062672938782089e-005</v>
       </c>
       <c r="L29">
-        <v>-4.6372473683291846e-005</v>
+        <v>-4.4900241118335212e-005</v>
       </c>
       <c r="M29">
-        <v>-2.2180289135376348e-005</v>
+        <v>-1.9910351460070618e-005</v>
       </c>
       <c r="N29">
-        <v>-2.0705570141084069e-005</v>
+        <v>-1.9936280294470705e-005</v>
       </c>
       <c r="O29">
-        <v>-3.3005065108149896e-005</v>
+        <v>-3.2139252947988007e-005</v>
       </c>
       <c r="P29">
-        <v>-1.2932730688513741e-006</v>
+        <v>-1.345773635430696e-006</v>
       </c>
       <c r="Q29">
-        <v>2.002944046406463e-006</v>
+        <v>1.9353818957403739e-006</v>
       </c>
       <c r="R29">
-        <v>-2.7822035924801375e-005</v>
+        <v>-2.5440354069383242e-005</v>
       </c>
       <c r="S29">
-        <v>1.6898383782980733e-005</v>
+        <v>1.7406167113051325e-005</v>
       </c>
       <c r="T29">
-        <v>-8.0487868817060468e-005</v>
+        <v>-7.8948896856809511e-005</v>
       </c>
       <c r="U29">
-        <v>0.0021127435328369198</v>
+        <v>0.0021208935932498889</v>
       </c>
       <c r="V29">
-        <v>0.0020761026940223849</v>
+        <v>0.0020824157882239729</v>
       </c>
       <c r="W29">
-        <v>0.002074479894959159</v>
+        <v>0.0020788759304035728</v>
       </c>
       <c r="X29">
-        <v>0.0020794617109151929</v>
+        <v>0.0020835292071259889</v>
       </c>
       <c r="Y29">
-        <v>0.0020669252306040166</v>
+        <v>0.0020734266146234899</v>
       </c>
       <c r="Z29">
-        <v>0.0020822894596726487</v>
+        <v>0.0020885501285572861</v>
       </c>
       <c r="AA29">
-        <v>0.0020665569678104288</v>
+        <v>0.0020717283018416984</v>
       </c>
       <c r="AB29">
-        <v>0.0020843168729976092</v>
+        <v>0.0020915192115131412</v>
       </c>
       <c r="AC29">
-        <v>0.0021031537177370056</v>
+        <v>0.002110354118226002</v>
       </c>
       <c r="AD29">
-        <v>0.0030434360420776951</v>
+        <v>0.0030515957085801878</v>
       </c>
       <c r="AE29">
-        <v>0.0021245643757831474</v>
+        <v>0.0021326760694652747</v>
       </c>
       <c r="AF29">
-        <v>-8.1204424843864526e-006</v>
+        <v>-8.2302198270154512e-006</v>
       </c>
       <c r="AG29">
-        <v>-3.2089220384655346e-005</v>
+        <v>-3.2103053319659385e-005</v>
       </c>
       <c r="AH29">
-        <v>-2.8912228021551799e-005</v>
+        <v>-3.1622619844012302e-005</v>
       </c>
       <c r="AI29">
-        <v>0.00070856667649343234</v>
+        <v>0.00071541621987640817</v>
       </c>
       <c r="AJ29">
-        <v>0.00097916908744330759</v>
+        <v>0.00098607227877851845</v>
       </c>
       <c r="AK29">
-        <v>0.00043848778429760521</v>
+        <v>0.0005213415758644446</v>
       </c>
       <c r="AL29">
-        <v>-0.0025001182521777396</v>
+        <v>-0.0025052900322560271</v>
       </c>
     </row>
     <row r="30">
@@ -9513,115 +9513,115 @@
         <v>70</v>
       </c>
       <c r="B30" s="131">
-        <v>0.10577777647769095</v>
+        <v>0.10265987361240904</v>
       </c>
       <c r="C30">
-        <v>-5.2713845064020817e-005</v>
+        <v>-5.3070412191997546e-005</v>
       </c>
       <c r="D30">
-        <v>9.9940663438703031e-005</v>
+        <v>0.00010006604332136668</v>
       </c>
       <c r="E30">
-        <v>-8.5127797982569075e-007</v>
+        <v>-8.5242632732147948e-007</v>
       </c>
       <c r="F30">
-        <v>-0.000107509415348735</v>
+        <v>-0.00010865126415228991</v>
       </c>
       <c r="G30">
-        <v>-0.00022483419386846182</v>
+        <v>-0.00022597583648494143</v>
       </c>
       <c r="H30">
-        <v>0.0001131692016542721</v>
+        <v>0.0001138566623554453</v>
       </c>
       <c r="I30">
-        <v>-1.6305131689403618e-006</v>
+        <v>-4.1950062328066119e-006</v>
       </c>
       <c r="J30">
-        <v>-0.00019373703807179683</v>
+        <v>-0.0001957494149204507</v>
       </c>
       <c r="K30">
-        <v>-7.7758099457827645e-005</v>
+        <v>-7.9195655479165957e-005</v>
       </c>
       <c r="L30">
-        <v>-4.9423767368642416e-005</v>
+        <v>-4.7765452124212161e-005</v>
       </c>
       <c r="M30">
-        <v>-3.6065863327354648e-005</v>
+        <v>-3.3746619638637789e-005</v>
       </c>
       <c r="N30">
-        <v>-2.4391223401627402e-005</v>
+        <v>-2.3056856903303988e-005</v>
       </c>
       <c r="O30">
-        <v>-5.1818521380137331e-005</v>
+        <v>-5.0382519611860774e-005</v>
       </c>
       <c r="P30">
-        <v>-2.6735682533017335e-006</v>
+        <v>-2.714266797101977e-006</v>
       </c>
       <c r="Q30">
-        <v>3.9631622441759688e-007</v>
+        <v>3.2972286052512984e-007</v>
       </c>
       <c r="R30">
-        <v>-5.0380687409740284e-006</v>
+        <v>-3.2351092831639852e-006</v>
       </c>
       <c r="S30">
-        <v>1.9111631464182095e-005</v>
+        <v>1.9730830909869114e-005</v>
       </c>
       <c r="T30">
-        <v>-0.00018168594190748452</v>
+        <v>-0.00018019357803006236</v>
       </c>
       <c r="U30">
-        <v>0.0021316509186119072</v>
+        <v>0.0021399683870519572</v>
       </c>
       <c r="V30">
-        <v>0.0020930904194812828</v>
+        <v>0.0020995689332331648</v>
       </c>
       <c r="W30">
-        <v>0.0020922194962590466</v>
+        <v>0.0020973082291966382</v>
       </c>
       <c r="X30">
-        <v>0.0020929681397010495</v>
+        <v>0.002097594095958269</v>
       </c>
       <c r="Y30">
-        <v>0.0020867658015134021</v>
+        <v>0.002093455208571092</v>
       </c>
       <c r="Z30">
-        <v>0.0021010912340386268</v>
+        <v>0.0021075173235156177</v>
       </c>
       <c r="AA30">
-        <v>0.0020849172314799571</v>
+        <v>0.0020905292211753539</v>
       </c>
       <c r="AB30">
-        <v>0.0021040562434955549</v>
+        <v>0.0021113645958403459</v>
       </c>
       <c r="AC30">
-        <v>0.0021277316350224252</v>
+        <v>0.0021350800594204305</v>
       </c>
       <c r="AD30">
-        <v>0.0021245643757831474</v>
+        <v>0.0021326760694652747</v>
       </c>
       <c r="AE30">
-        <v>0.0038506660460968603</v>
+        <v>0.0038586135267374517</v>
       </c>
       <c r="AF30">
-        <v>-5.9989683005288216e-006</v>
+        <v>-6.0751305988067581e-006</v>
       </c>
       <c r="AG30">
-        <v>-6.2898165741917471e-005</v>
+        <v>-6.2972271024655673e-005</v>
       </c>
       <c r="AH30">
-        <v>-3.4831549366826192e-005</v>
+        <v>-3.7182859016910031e-005</v>
       </c>
       <c r="AI30">
-        <v>0.00074337790998920013</v>
+        <v>0.00075022876637694967</v>
       </c>
       <c r="AJ30">
-        <v>0.00097257123809614771</v>
+        <v>0.00097973945971373223</v>
       </c>
       <c r="AK30">
-        <v>0.00040026560929266029</v>
+        <v>0.00048068790343383711</v>
       </c>
       <c r="AL30">
-        <v>-0.0046523772390602326</v>
+        <v>-0.0046583086714428569</v>
       </c>
     </row>
     <row r="31">
@@ -9629,115 +9629,115 @@
         <v>71</v>
       </c>
       <c r="B31" s="133">
-        <v>-0.0055728262741877891</v>
+        <v>-0.005392470922287701</v>
       </c>
       <c r="C31">
-        <v>4.3997728352519513e-006</v>
+        <v>4.4081203476355868e-006</v>
       </c>
       <c r="D31">
-        <v>9.4987469364925118e-006</v>
+        <v>9.582056843246531e-006</v>
       </c>
       <c r="E31">
-        <v>-9.4888899428429478e-008</v>
+        <v>-9.5530001529084797e-008</v>
       </c>
       <c r="F31">
-        <v>2.26961010598509e-006</v>
+        <v>2.1926453265303319e-006</v>
       </c>
       <c r="G31">
-        <v>1.0892052774323267e-005</v>
+        <v>1.0797784405801636e-005</v>
       </c>
       <c r="H31">
-        <v>2.1153358266019548e-005</v>
+        <v>2.1113641894424745e-005</v>
       </c>
       <c r="I31">
-        <v>7.4366907960093245e-006</v>
+        <v>7.4493111913573535e-006</v>
       </c>
       <c r="J31">
-        <v>5.8634893408772074e-006</v>
+        <v>5.8770159925179499e-006</v>
       </c>
       <c r="K31">
-        <v>-2.2349779833868188e-006</v>
+        <v>-2.2534624426036198e-006</v>
       </c>
       <c r="L31">
-        <v>-1.6254755521929196e-006</v>
+        <v>-1.6164222772267148e-006</v>
       </c>
       <c r="M31">
-        <v>-1.3809502020798206e-006</v>
+        <v>-1.42028363743978e-006</v>
       </c>
       <c r="N31">
-        <v>4.5535772324228527e-009</v>
+        <v>8.5718265796757686e-009</v>
       </c>
       <c r="O31">
-        <v>-2.7920312407014961e-006</v>
+        <v>-2.848590791806363e-006</v>
       </c>
       <c r="P31">
-        <v>1.4374136639538981e-007</v>
+        <v>1.3966777373314725e-007</v>
       </c>
       <c r="Q31">
-        <v>4.1684926637691798e-007</v>
+        <v>4.1701073012715971e-007</v>
       </c>
       <c r="R31">
-        <v>1.2761182121049299e-005</v>
+        <v>1.2773958360794778e-005</v>
       </c>
       <c r="S31">
-        <v>1.1638624454183509e-006</v>
+        <v>1.1211713232037788e-006</v>
       </c>
       <c r="T31">
-        <v>-2.61080459476704e-006</v>
+        <v>-2.6359361889454048e-006</v>
       </c>
       <c r="U31">
-        <v>-9.0230866150821363e-006</v>
+        <v>-9.1113896075561726e-006</v>
       </c>
       <c r="V31">
-        <v>-6.442607260345589e-006</v>
+        <v>-6.5412148449336702e-006</v>
       </c>
       <c r="W31">
-        <v>-1.2425473764993521e-005</v>
+        <v>-1.2452729580826351e-005</v>
       </c>
       <c r="X31">
-        <v>-1.3388608853577132e-005</v>
+        <v>-1.3410469193181691e-005</v>
       </c>
       <c r="Y31">
-        <v>-1.1947387809798007e-005</v>
+        <v>-1.2034220114947982e-005</v>
       </c>
       <c r="Z31">
-        <v>-8.8034259819557746e-006</v>
+        <v>-8.8108047248210055e-006</v>
       </c>
       <c r="AA31">
-        <v>-8.921247943055469e-006</v>
+        <v>-8.8811130033233178e-006</v>
       </c>
       <c r="AB31">
-        <v>-9.9598499125970817e-006</v>
+        <v>-1.0025383153013907e-005</v>
       </c>
       <c r="AC31">
-        <v>-7.3398769053672271e-006</v>
+        <v>-7.389180531178392e-006</v>
       </c>
       <c r="AD31">
-        <v>-8.1204424843864526e-006</v>
+        <v>-8.2302198270154512e-006</v>
       </c>
       <c r="AE31">
-        <v>-5.9989683005288216e-006</v>
+        <v>-6.0751305988067581e-006</v>
       </c>
       <c r="AF31">
-        <v>1.329880168306856e-005</v>
+        <v>1.3301336108584177e-005</v>
       </c>
       <c r="AG31">
-        <v>-5.6440783573828234e-005</v>
+        <v>-5.6442864620789149e-005</v>
       </c>
       <c r="AH31">
-        <v>-7.1305450878950938e-005</v>
+        <v>-7.1313589253499429e-005</v>
       </c>
       <c r="AI31">
-        <v>-1.9330123405071311e-005</v>
+        <v>-1.9410550481942858e-005</v>
       </c>
       <c r="AJ31">
-        <v>-2.3882033117804939e-005</v>
+        <v>-2.398137885473079e-005</v>
       </c>
       <c r="AK31">
-        <v>4.7935775239316516e-006</v>
+        <v>3.5729778321425671e-006</v>
       </c>
       <c r="AL31">
-        <v>-0.00046398389094083863</v>
+        <v>-0.00046635523764721002</v>
       </c>
     </row>
     <row r="32">
@@ -9745,115 +9745,115 @@
         <v>72</v>
       </c>
       <c r="B32" s="135">
-        <v>-0.0016471341093371361</v>
+        <v>-0.0025047256918448667</v>
       </c>
       <c r="C32">
-        <v>2.825831297490757e-005</v>
+        <v>2.80317234043927e-005</v>
       </c>
       <c r="D32">
-        <v>-2.3403354315185501e-005</v>
+        <v>-2.3431608989230924e-005</v>
       </c>
       <c r="E32">
-        <v>1.5527146780202242e-007</v>
+        <v>1.5571807342978988e-007</v>
       </c>
       <c r="F32">
-        <v>4.3649532064458574e-005</v>
+        <v>4.3873513722139039e-005</v>
       </c>
       <c r="G32">
-        <v>5.8382577604353925e-005</v>
+        <v>5.855993087358473e-005</v>
       </c>
       <c r="H32">
-        <v>6.5994015202632751e-005</v>
+        <v>6.5883162392173309e-005</v>
       </c>
       <c r="I32">
-        <v>-2.0668615887442024e-005</v>
+        <v>-2.0326980570782559e-005</v>
       </c>
       <c r="J32">
-        <v>-3.9672550754283334e-005</v>
+        <v>-3.9339478770001804e-005</v>
       </c>
       <c r="K32">
-        <v>-0.000166526442953639</v>
+        <v>-0.00016685463883088486</v>
       </c>
       <c r="L32">
-        <v>-0.00012914241574695824</v>
+        <v>-0.00012937079571624161</v>
       </c>
       <c r="M32">
-        <v>-0.00011971708488613497</v>
+        <v>-0.00011987060802612407</v>
       </c>
       <c r="N32">
-        <v>-0.00013260663443049819</v>
+        <v>-0.00013277373316869544</v>
       </c>
       <c r="O32">
-        <v>3.629048726057578e-005</v>
+        <v>3.6722687593711425e-005</v>
       </c>
       <c r="P32">
-        <v>2.1149954691117529e-006</v>
+        <v>2.1300944425176423e-006</v>
       </c>
       <c r="Q32">
-        <v>1.7450416840743005e-006</v>
+        <v>1.76075753321727e-006</v>
       </c>
       <c r="R32">
-        <v>-2.0564637155311837e-005</v>
+        <v>-2.0820177502445129e-005</v>
       </c>
       <c r="S32">
-        <v>6.8241317070275162e-006</v>
+        <v>6.9356755297149915e-006</v>
       </c>
       <c r="T32">
-        <v>1.40148763937476e-005</v>
+        <v>1.3748799963182637e-005</v>
       </c>
       <c r="U32">
-        <v>-8.7689239253247917e-005</v>
+        <v>-8.7823961366210275e-005</v>
       </c>
       <c r="V32">
-        <v>-9.3114263607707619e-005</v>
+        <v>-9.3040719214897087e-005</v>
       </c>
       <c r="W32">
-        <v>2.7846839887154078e-005</v>
+        <v>2.7585995816681266e-005</v>
       </c>
       <c r="X32">
-        <v>3.6465521242944678e-005</v>
+        <v>3.6116526250481537e-005</v>
       </c>
       <c r="Y32">
-        <v>-2.9473134279447794e-005</v>
+        <v>-2.9430259554203147e-005</v>
       </c>
       <c r="Z32">
-        <v>-3.6316833699706211e-005</v>
+        <v>-3.6421879385295779e-005</v>
       </c>
       <c r="AA32">
-        <v>-1.3482635775096053e-005</v>
+        <v>-1.3868474189457777e-005</v>
       </c>
       <c r="AB32">
-        <v>-2.5830837819339786e-006</v>
+        <v>-2.5867165887358003e-006</v>
       </c>
       <c r="AC32">
-        <v>-2.3139307959507416e-005</v>
+        <v>-2.3369000240203029e-005</v>
       </c>
       <c r="AD32">
-        <v>-3.2089220384655346e-005</v>
+        <v>-3.2103053319659385e-005</v>
       </c>
       <c r="AE32">
-        <v>-6.2898165741917471e-005</v>
+        <v>-6.2972271024655673e-005</v>
       </c>
       <c r="AF32">
-        <v>-5.6440783573828234e-005</v>
+        <v>-5.6442864620789149e-005</v>
       </c>
       <c r="AG32">
-        <v>0.0020745529509951029</v>
+        <v>0.0020739580758834582</v>
       </c>
       <c r="AH32">
-        <v>0.00045312627279921235</v>
+        <v>0.00045313853106371396</v>
       </c>
       <c r="AI32">
-        <v>2.9149863675856705e-005</v>
+        <v>2.9065069713482268e-005</v>
       </c>
       <c r="AJ32">
-        <v>6.2402692144663879e-006</v>
+        <v>6.2352058382121947e-006</v>
       </c>
       <c r="AK32">
-        <v>-7.0143007566737543e-006</v>
+        <v>-5.1949015729484853e-005</v>
       </c>
       <c r="AL32">
-        <v>0.0014766089137122241</v>
+        <v>0.0014756552486955951</v>
       </c>
     </row>
     <row r="33">
@@ -9861,115 +9861,115 @@
         <v>73</v>
       </c>
       <c r="B33" s="137">
-        <v>0.048471356770682678</v>
+        <v>0.048956121771478796</v>
       </c>
       <c r="C33">
-        <v>-1.6696286098243872e-005</v>
+        <v>-1.6797083993527142e-005</v>
       </c>
       <c r="D33">
-        <v>1.0742117965037749e-005</v>
+        <v>1.0495556920705367e-005</v>
       </c>
       <c r="E33">
-        <v>-7.8172404035512918e-008</v>
+        <v>-7.6115863414235584e-008</v>
       </c>
       <c r="F33">
-        <v>4.745500655885128e-005</v>
+        <v>4.7993985968779263e-005</v>
       </c>
       <c r="G33">
-        <v>-5.2216381271316628e-006</v>
+        <v>-5.0866145270530687e-006</v>
       </c>
       <c r="H33">
-        <v>1.2387980138129553e-005</v>
+        <v>1.2138919900348181e-005</v>
       </c>
       <c r="I33">
-        <v>-4.1948125660702634e-005</v>
+        <v>-4.0852301364071821e-005</v>
       </c>
       <c r="J33">
-        <v>-3.7024937143857595e-005</v>
+        <v>-3.7445754457609943e-005</v>
       </c>
       <c r="K33">
-        <v>-0.00013625504446151878</v>
+        <v>-0.0001367763667771299</v>
       </c>
       <c r="L33">
-        <v>-0.00012407580988533178</v>
+        <v>-0.00012512201768268775</v>
       </c>
       <c r="M33">
-        <v>-0.00011987175225658488</v>
+        <v>-0.00012082046165643907</v>
       </c>
       <c r="N33">
-        <v>-0.0001376952113692458</v>
+        <v>-0.00013823067708078151</v>
       </c>
       <c r="O33">
-        <v>5.9681510107050635e-005</v>
+        <v>5.9884059190793127e-005</v>
       </c>
       <c r="P33">
-        <v>9.070752444544634e-007</v>
+        <v>9.3222441562626164e-007</v>
       </c>
       <c r="Q33">
-        <v>8.7934981246885767e-007</v>
+        <v>9.1702834080550278e-007</v>
       </c>
       <c r="R33">
-        <v>-1.5312110465500915e-006</v>
+        <v>-2.0996843085187855e-006</v>
       </c>
       <c r="S33">
-        <v>-4.6817119002805801e-005</v>
+        <v>-4.6469561175763666e-005</v>
       </c>
       <c r="T33">
-        <v>1.3887436966015879e-005</v>
+        <v>1.3227164634994559e-005</v>
       </c>
       <c r="U33">
-        <v>-3.8923708354400947e-005</v>
+        <v>-4.1752985355806609e-005</v>
       </c>
       <c r="V33">
-        <v>-2.515438375788125e-005</v>
+        <v>-2.7215961954230881e-005</v>
       </c>
       <c r="W33">
-        <v>2.0192887892048112e-005</v>
+        <v>1.8702870754481931e-005</v>
       </c>
       <c r="X33">
-        <v>1.3368174736967462e-005</v>
+        <v>1.1292604487489974e-005</v>
       </c>
       <c r="Y33">
-        <v>1.3409944193912515e-005</v>
+        <v>1.1291036672501796e-005</v>
       </c>
       <c r="Z33">
-        <v>4.7658619422262347e-006</v>
+        <v>2.7538363387239549e-006</v>
       </c>
       <c r="AA33">
-        <v>2.2214690516071861e-005</v>
+        <v>1.9265447203122806e-005</v>
       </c>
       <c r="AB33">
-        <v>-4.3628690754541087e-007</v>
+        <v>-2.6661650666187814e-006</v>
       </c>
       <c r="AC33">
-        <v>-2.8839173461498938e-005</v>
+        <v>-3.107945322566884e-005</v>
       </c>
       <c r="AD33">
-        <v>-2.8912228021551799e-005</v>
+        <v>-3.1622619844012302e-005</v>
       </c>
       <c r="AE33">
-        <v>-3.4831549366826192e-005</v>
+        <v>-3.7182859016910031e-005</v>
       </c>
       <c r="AF33">
-        <v>-7.1305450878950938e-005</v>
+        <v>-7.1313589253499429e-005</v>
       </c>
       <c r="AG33">
-        <v>0.00045312627279921235</v>
+        <v>0.00045313853106371396</v>
       </c>
       <c r="AH33">
-        <v>0.0022444639578971014</v>
+        <v>0.0022420820591659099</v>
       </c>
       <c r="AI33">
-        <v>3.5441197832860975e-005</v>
+        <v>3.3535744249293714e-005</v>
       </c>
       <c r="AJ33">
-        <v>0.00020560898764605752</v>
+        <v>0.00020379531330519624</v>
       </c>
       <c r="AK33">
-        <v>-3.1704642194600849e-005</v>
+        <v>-0.00013860565454389432</v>
       </c>
       <c r="AL33">
-        <v>0.00064644780524882083</v>
+        <v>0.00065418705655371709</v>
       </c>
     </row>
     <row r="34">
@@ -9977,115 +9977,115 @@
         <v>74</v>
       </c>
       <c r="B34" s="139">
-        <v>-0.11197715774672683</v>
+        <v>-0.11436829973904347</v>
       </c>
       <c r="C34">
-        <v>-2.8283079227622628e-005</v>
+        <v>-2.8608954356871651e-005</v>
       </c>
       <c r="D34">
-        <v>-8.057292928381754e-006</v>
+        <v>-7.9362880805802782e-006</v>
       </c>
       <c r="E34">
-        <v>1.0182430891224358e-007</v>
+        <v>1.0087321904517026e-007</v>
       </c>
       <c r="F34">
-        <v>4.0027981105601913e-005</v>
+        <v>3.852625327185831e-005</v>
       </c>
       <c r="G34">
-        <v>-6.0909667544953514e-005</v>
+        <v>-6.2332865699330159e-005</v>
       </c>
       <c r="H34">
-        <v>-6.9332494336163224e-006</v>
+        <v>-6.3145695417952301e-006</v>
       </c>
       <c r="I34">
-        <v>-0.00018489816420867982</v>
+        <v>-0.0001868719591569441</v>
       </c>
       <c r="J34">
-        <v>3.9445661745304318e-005</v>
+        <v>3.8439506832055412e-005</v>
       </c>
       <c r="K34">
-        <v>0.00010896257343324272</v>
+        <v>0.00010879291063045139</v>
       </c>
       <c r="L34">
-        <v>0.00030177305051170872</v>
+        <v>0.00030247311081404288</v>
       </c>
       <c r="M34">
-        <v>0.00029247909836977609</v>
+        <v>0.00029348128661141077</v>
       </c>
       <c r="N34">
-        <v>0.00029389269658248833</v>
+        <v>0.00029411966285414507</v>
       </c>
       <c r="O34">
-        <v>0.00017946722395634739</v>
+        <v>0.00017977755866068824</v>
       </c>
       <c r="P34">
-        <v>-4.5588783468617617e-007</v>
+        <v>-4.8971313256314852e-007</v>
       </c>
       <c r="Q34">
-        <v>-9.894558717211301e-007</v>
+        <v>-1.0414154927419024e-006</v>
       </c>
       <c r="R34">
-        <v>1.6724647947093736e-005</v>
+        <v>1.7436231184573344e-005</v>
       </c>
       <c r="S34">
-        <v>-5.9382548501546993e-005</v>
+        <v>-5.8843734126049053e-005</v>
       </c>
       <c r="T34">
-        <v>9.2868482712168867e-005</v>
+        <v>9.3637202463065259e-005</v>
       </c>
       <c r="U34">
-        <v>0.00071586483129995181</v>
+        <v>0.00072279889790315133</v>
       </c>
       <c r="V34">
-        <v>0.00062056831042436693</v>
+        <v>0.00062630465113189628</v>
       </c>
       <c r="W34">
-        <v>0.00055243687131323793</v>
+        <v>0.00055677203337236843</v>
       </c>
       <c r="X34">
-        <v>0.00057554716155938049</v>
+        <v>0.00057969522001659996</v>
       </c>
       <c r="Y34">
-        <v>0.00048965526110030574</v>
+        <v>0.00049570754863064608</v>
       </c>
       <c r="Z34">
-        <v>0.00063080800262340665</v>
+        <v>0.00063641833513826494</v>
       </c>
       <c r="AA34">
-        <v>0.00064467241346130913</v>
+        <v>0.00064977022344213354</v>
       </c>
       <c r="AB34">
-        <v>0.00068118565533865699</v>
+        <v>0.00068762524613509069</v>
       </c>
       <c r="AC34">
-        <v>0.00070692472901590238</v>
+        <v>0.00071313412638618551</v>
       </c>
       <c r="AD34">
-        <v>0.00070856667649343234</v>
+        <v>0.00071541621987640817</v>
       </c>
       <c r="AE34">
-        <v>0.00074337790998920013</v>
+        <v>0.00075022876637694967</v>
       </c>
       <c r="AF34">
-        <v>-1.9330123405071311e-005</v>
+        <v>-1.9410550481942858e-005</v>
       </c>
       <c r="AG34">
-        <v>2.9149863675856705e-005</v>
+        <v>2.9065069713482268e-005</v>
       </c>
       <c r="AH34">
-        <v>3.5441197832860975e-005</v>
+        <v>3.3535744249293714e-005</v>
       </c>
       <c r="AI34">
-        <v>0.0030345752195614587</v>
+        <v>0.0030390502355083001</v>
       </c>
       <c r="AJ34">
-        <v>0.00043857342020057794</v>
+        <v>0.00044289315400655564</v>
       </c>
       <c r="AK34">
-        <v>0.00028400989984757324</v>
+        <v>0.00031885617725118997</v>
       </c>
       <c r="AL34">
-        <v>-0.00045952530072257067</v>
+        <v>-0.00046381228634174076</v>
       </c>
     </row>
     <row r="35">
@@ -10093,115 +10093,115 @@
         <v>75</v>
       </c>
       <c r="B35" s="141">
-        <v>-0.32301006690349693</v>
+        <v>-0.32552584756379255</v>
       </c>
       <c r="C35">
-        <v>-5.1206342478769679e-005</v>
+        <v>-5.1467791083552262e-005</v>
       </c>
       <c r="D35">
-        <v>-0.00011342191296093151</v>
+        <v>-0.00011341801768253654</v>
       </c>
       <c r="E35">
-        <v>9.0416399825733349e-007</v>
+        <v>9.0394600337078703e-007</v>
       </c>
       <c r="F35">
-        <v>0.00014135953502622298</v>
+        <v>0.00014028980676457248</v>
       </c>
       <c r="G35">
-        <v>0.00015064902639828304</v>
+        <v>0.00014941008529652499</v>
       </c>
       <c r="H35">
-        <v>5.7454150482989536e-005</v>
+        <v>5.8326591941274165e-005</v>
       </c>
       <c r="I35">
-        <v>-3.8897854302263456e-005</v>
+        <v>-4.0137772070962703e-005</v>
       </c>
       <c r="J35">
-        <v>-3.3230507639348504e-005</v>
+        <v>-3.4489947497507063e-005</v>
       </c>
       <c r="K35">
-        <v>-4.6855981270844688e-005</v>
+        <v>-4.7453801521580262e-005</v>
       </c>
       <c r="L35">
-        <v>-2.4526401316439257e-005</v>
+        <v>-2.3627662492500335e-005</v>
       </c>
       <c r="M35">
-        <v>3.3756692757188494e-005</v>
+        <v>3.4956935548667882e-005</v>
       </c>
       <c r="N35">
-        <v>0.00014647667481562296</v>
+        <v>0.00014694678852401834</v>
       </c>
       <c r="O35">
-        <v>4.5639660451942147e-006</v>
+        <v>4.8471868691038391e-006</v>
       </c>
       <c r="P35">
-        <v>-2.0082259928800612e-006</v>
+        <v>-2.0319329748109412e-006</v>
       </c>
       <c r="Q35">
-        <v>-1.1391537963898322e-006</v>
+        <v>-1.1884810149342194e-006</v>
       </c>
       <c r="R35">
-        <v>-9.3650434656049569e-005</v>
+        <v>-9.279611695516552e-005</v>
       </c>
       <c r="S35">
-        <v>6.1766429369361955e-005</v>
+        <v>6.237727405889792e-005</v>
       </c>
       <c r="T35">
-        <v>-1.1257623005125737e-005</v>
+        <v>-1.068163140729555e-005</v>
       </c>
       <c r="U35">
-        <v>0.00099631619131502645</v>
+        <v>0.0010032812529588058</v>
       </c>
       <c r="V35">
-        <v>0.0008714494058112577</v>
+        <v>0.00087749681937692521</v>
       </c>
       <c r="W35">
-        <v>0.00093110972511325151</v>
+        <v>0.00093582211518791021</v>
       </c>
       <c r="X35">
-        <v>0.00092405163779684567</v>
+        <v>0.00092835563251759902</v>
       </c>
       <c r="Y35">
-        <v>0.0007483355149444337</v>
+        <v>0.00075484402302662635</v>
       </c>
       <c r="Z35">
-        <v>0.0010216779667469654</v>
+        <v>0.001027757174410745</v>
       </c>
       <c r="AA35">
-        <v>0.00087276868640431349</v>
+        <v>0.00087819792942374364</v>
       </c>
       <c r="AB35">
-        <v>0.00096929839544497055</v>
+        <v>0.00097598438209600322</v>
       </c>
       <c r="AC35">
-        <v>0.0009754237245785159</v>
+        <v>0.00098179799015844587</v>
       </c>
       <c r="AD35">
-        <v>0.00097916908744330759</v>
+        <v>0.00098607227877851845</v>
       </c>
       <c r="AE35">
-        <v>0.00097257123809614771</v>
+        <v>0.00097973945971373223</v>
       </c>
       <c r="AF35">
-        <v>-2.3882033117804939e-005</v>
+        <v>-2.398137885473079e-005</v>
       </c>
       <c r="AG35">
-        <v>6.2402692144663879e-006</v>
+        <v>6.2352058382121947e-006</v>
       </c>
       <c r="AH35">
-        <v>0.00020560898764605752</v>
+        <v>0.00020379531330519624</v>
       </c>
       <c r="AI35">
-        <v>0.00043857342020057794</v>
+        <v>0.00044289315400655564</v>
       </c>
       <c r="AJ35">
-        <v>0.013240875094488033</v>
+        <v>0.013240767948932771</v>
       </c>
       <c r="AK35">
-        <v>0.00029713747989874937</v>
+        <v>0.00030273758732993466</v>
       </c>
       <c r="AL35">
-        <v>0.0029159439418498562</v>
+        <v>0.0029148651523656284</v>
       </c>
     </row>
     <row r="36">
@@ -10209,115 +10209,115 @@
         <v>76</v>
       </c>
       <c r="B36" s="143">
-        <v>-0.27144008953179688</v>
+        <v>-0.31428238869831449</v>
       </c>
       <c r="C36">
-        <v>-1.9136798726858858e-005</v>
+        <v>-3.9035868766022969e-005</v>
       </c>
       <c r="D36">
-        <v>1.3987053647662728e-005</v>
+        <v>3.5163098304277426e-005</v>
       </c>
       <c r="E36">
-        <v>-9.2118835686501744e-008</v>
+        <v>-2.6414144115373438e-007</v>
       </c>
       <c r="F36">
-        <v>0.00011625960718143543</v>
+        <v>-1.3335710271335162e-005</v>
       </c>
       <c r="G36">
-        <v>0.00016877164215886424</v>
+        <v>2.9324926140685565e-005</v>
       </c>
       <c r="H36">
-        <v>3.8548698070346059e-006</v>
+        <v>8.4700878838509994e-006</v>
       </c>
       <c r="I36">
-        <v>-0.00011664284849520088</v>
+        <v>-0.00016535255547567719</v>
       </c>
       <c r="J36">
-        <v>-0.00015034144203871142</v>
+        <v>-0.00011700011030614109</v>
       </c>
       <c r="K36">
-        <v>0.00011501634060341896</v>
+        <v>3.8584340426474047e-005</v>
       </c>
       <c r="L36">
-        <v>0.00011910151776988397</v>
+        <v>5.1935758466562258e-005</v>
       </c>
       <c r="M36">
-        <v>0.00014975296588664666</v>
+        <v>6.7486794861570319e-005</v>
       </c>
       <c r="N36">
-        <v>9.5208833662448265e-005</v>
+        <v>8.8557315503200998e-006</v>
       </c>
       <c r="O36">
-        <v>0.00019556529616013572</v>
+        <v>6.8655129968933713e-005</v>
       </c>
       <c r="P36">
-        <v>2.1183388434044346e-006</v>
+        <v>-2.3772438135726513e-006</v>
       </c>
       <c r="Q36">
-        <v>8.2258635342248427e-007</v>
+        <v>-1.316007239660337e-006</v>
       </c>
       <c r="R36">
-        <v>7.0774106531142479e-005</v>
+        <v>0.00011058907162805344</v>
       </c>
       <c r="S36">
-        <v>-6.8797838839408361e-005</v>
+        <v>-6.4909895676663667e-005</v>
       </c>
       <c r="T36">
-        <v>5.9300857922093262e-005</v>
+        <v>6.6450605024529841e-005</v>
       </c>
       <c r="U36">
-        <v>0.00043721242630778657</v>
+        <v>0.00050540442768694737</v>
       </c>
       <c r="V36">
-        <v>0.00038209653620029159</v>
+        <v>0.0004168063107550103</v>
       </c>
       <c r="W36">
-        <v>0.00041949400559103899</v>
+        <v>0.00037813280713927902</v>
       </c>
       <c r="X36">
-        <v>0.00043957354444606529</v>
+        <v>0.00038369993164404754</v>
       </c>
       <c r="Y36">
-        <v>0.00036651710328811343</v>
+        <v>0.00040568614361482928</v>
       </c>
       <c r="Z36">
-        <v>0.00030072956921511592</v>
+        <v>0.00036462736975416833</v>
       </c>
       <c r="AA36">
-        <v>0.00043826327745392901</v>
+        <v>0.00048306336569502249</v>
       </c>
       <c r="AB36">
-        <v>0.00030965878251898254</v>
+        <v>0.00041312242488299384</v>
       </c>
       <c r="AC36">
-        <v>0.00038483822584461664</v>
+        <v>0.00044732175954199731</v>
       </c>
       <c r="AD36">
-        <v>0.00043848778429760521</v>
+        <v>0.0005213415758644446</v>
       </c>
       <c r="AE36">
-        <v>0.00040026560929266029</v>
+        <v>0.00048068790343383711</v>
       </c>
       <c r="AF36">
-        <v>4.7935775239316516e-006</v>
+        <v>3.5729778321425671e-006</v>
       </c>
       <c r="AG36">
-        <v>-7.0143007566737543e-006</v>
+        <v>-5.1949015729484853e-005</v>
       </c>
       <c r="AH36">
-        <v>-3.1704642194600849e-005</v>
+        <v>-0.00013860565454389432</v>
       </c>
       <c r="AI36">
-        <v>0.00028400989984757324</v>
+        <v>0.00031885617725118997</v>
       </c>
       <c r="AJ36">
-        <v>0.00029713747989874937</v>
+        <v>0.00030273758732993466</v>
       </c>
       <c r="AK36">
-        <v>0.016065347428545665</v>
+        <v>0.010964435628625108</v>
       </c>
       <c r="AL36">
-        <v>-0.0014038067822532653</v>
+        <v>-0.0015483281996946437</v>
       </c>
     </row>
     <row r="37">
@@ -10325,115 +10325,115 @@
         <v>77</v>
       </c>
       <c r="B37" s="145">
-        <v>-21.88422650484754</v>
+        <v>-21.886319941826414</v>
       </c>
       <c r="C37">
-        <v>-0.0019417559221799605</v>
+        <v>-0.0019388168715905106</v>
       </c>
       <c r="D37">
-        <v>-0.040570056449759265</v>
+        <v>-0.040567455750415794</v>
       </c>
       <c r="E37">
-        <v>0.00033003390444120398</v>
+        <v>0.00033001634025847518</v>
       </c>
       <c r="F37">
-        <v>0.0020655870931514386</v>
+        <v>0.0020606261019060507</v>
       </c>
       <c r="G37">
-        <v>0.0029087277165818866</v>
+        <v>0.0028953746541147758</v>
       </c>
       <c r="H37">
-        <v>-0.0076260202491087335</v>
+        <v>-0.0076330832499604548</v>
       </c>
       <c r="I37">
-        <v>-0.0026415304948867423</v>
+        <v>-0.0026414587171512977</v>
       </c>
       <c r="J37">
-        <v>0.0044770649131338431</v>
+        <v>0.0044804252880234919</v>
       </c>
       <c r="K37">
-        <v>-0.00077408575993136684</v>
+        <v>-0.0008096289184060879</v>
       </c>
       <c r="L37">
-        <v>-0.00021970565402399354</v>
+        <v>-0.00024501891217756575</v>
       </c>
       <c r="M37">
-        <v>0.00067582778195102557</v>
+        <v>0.00065205509805747654</v>
       </c>
       <c r="N37">
-        <v>0.0010585732786154468</v>
+        <v>0.001024277844601771</v>
       </c>
       <c r="O37">
-        <v>-0.001124203656662306</v>
+        <v>-0.0011282370603845414</v>
       </c>
       <c r="P37">
-        <v>-0.00012819660185451955</v>
+        <v>-0.00012841902460906143</v>
       </c>
       <c r="Q37">
-        <v>-4.0559767138226413e-005</v>
+        <v>-4.0504988340076681e-005</v>
       </c>
       <c r="R37">
-        <v>-0.0005232816548235205</v>
+        <v>-0.00052119386060870895</v>
       </c>
       <c r="S37">
-        <v>0.00029625832523900547</v>
+        <v>0.00029847927832251145</v>
       </c>
       <c r="T37">
-        <v>0.0011382239793279675</v>
+        <v>0.0011417656754611624</v>
       </c>
       <c r="U37">
-        <v>-0.0034803783406338672</v>
+        <v>-0.0034862222953649259</v>
       </c>
       <c r="V37">
-        <v>-0.0033052808590818949</v>
+        <v>-0.0033109973661547016</v>
       </c>
       <c r="W37">
-        <v>-0.0026965335794873306</v>
+        <v>-0.0026897581478553686</v>
       </c>
       <c r="X37">
-        <v>-0.0025541327155281131</v>
+        <v>-0.002550070331434051</v>
       </c>
       <c r="Y37">
-        <v>-0.0021364165612331554</v>
+        <v>-0.0021473259189158191</v>
       </c>
       <c r="Z37">
-        <v>-0.0037594017186809957</v>
+        <v>-0.0037556356919631927</v>
       </c>
       <c r="AA37">
-        <v>-0.0028586104855541487</v>
+        <v>-0.0028680459730651984</v>
       </c>
       <c r="AB37">
-        <v>-0.0020859353157586824</v>
+        <v>-0.0020915791541587948</v>
       </c>
       <c r="AC37">
-        <v>-0.0026730236512599688</v>
+        <v>-0.002679644474326216</v>
       </c>
       <c r="AD37">
-        <v>-0.0025001182521777396</v>
+        <v>-0.0025052900322560271</v>
       </c>
       <c r="AE37">
-        <v>-0.0046523772390602326</v>
+        <v>-0.0046583086714428569</v>
       </c>
       <c r="AF37">
-        <v>-0.00046398389094083863</v>
+        <v>-0.00046635523764721002</v>
       </c>
       <c r="AG37">
-        <v>0.0014766089137122241</v>
+        <v>0.0014756552486955951</v>
       </c>
       <c r="AH37">
-        <v>0.00064644780524882083</v>
+        <v>0.00065418705655371709</v>
       </c>
       <c r="AI37">
-        <v>-0.00045952530072257067</v>
+        <v>-0.00046381228634174076</v>
       </c>
       <c r="AJ37">
-        <v>0.0029159439418498562</v>
+        <v>0.0029148651523656284</v>
       </c>
       <c r="AK37">
-        <v>-0.0014038067822532653</v>
+        <v>-0.0015483281996946437</v>
       </c>
       <c r="AL37">
-        <v>1.257261522065972</v>
+        <v>1.2572539288388074</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/Desktop/initial_populations/regression_estimates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BC14E5-3210-0B48-B355-8D5B6D66C459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8186070-4565-2749-8D6A-F314458B2E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="UK_R1a" sheetId="3" r:id="rId3"/>
-    <sheet name="UK_R1b" sheetId="4" r:id="rId4"/>
+    <sheet name="R1a" sheetId="3" r:id="rId3"/>
+    <sheet name="R1b" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
   <si>
     <t>Description:</t>
   </si>
@@ -155,9 +155,6 @@
   </si>
   <si>
     <t>Constant</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>R1a - Retirement single</t>
@@ -704,18 +701,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>0.22029683046666237</v>
       </c>
       <c r="E5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5">
         <v>1645.7124011500975</v>
@@ -723,13 +720,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>26159</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6">
         <v>-3457058.8340486912</v>
@@ -737,18 +734,18 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>0.21457656468585751</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11">
         <v>3311.6517762604585</v>
@@ -756,13 +753,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>60827</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F12">
         <v>-9011943.1780763194</v>
@@ -775,10 +772,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A1:AG32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -878,11 +875,8 @@
       <c r="AG1" t="s">
         <v>43</v>
       </c>
-      <c r="AH1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -983,7 +977,7 @@
         <v>6.2043114978482805E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1084,7 +1078,7 @@
         <v>-5.7705012434188546E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1185,7 +1179,7 @@
         <v>4.4805888014480837E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1286,7 +1280,7 @@
         <v>2.213837203694005E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1387,7 +1381,7 @@
         <v>-1.0445761682538867E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1488,7 +1482,7 @@
         <v>-3.1134931479971997E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1589,7 +1583,7 @@
         <v>-1.5726098690799206E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1690,7 +1684,7 @@
         <v>7.3091459209271986E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1791,7 +1785,7 @@
         <v>-4.8559390173042824E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1892,7 +1886,7 @@
         <v>-2.6759139423635836E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1993,7 +1987,7 @@
         <v>-4.3243244715416261E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2094,7 +2088,7 @@
         <v>-4.5943529534406183E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2195,7 +2189,7 @@
         <v>-4.6554219087351779E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2296,7 +2290,7 @@
         <v>3.338129410986334E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -4020,10 +4014,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AJ35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -4055,16 +4049,16 @@
         <v>20</v>
       </c>
       <c r="K1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L1" t="s">
         <v>21</v>
       </c>
       <c r="M1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N1" t="s">
         <v>51</v>
-      </c>
-      <c r="N1" t="s">
-        <v>52</v>
       </c>
       <c r="O1" t="s">
         <v>22</v>
@@ -4132,11 +4126,8 @@
       <c r="AJ1" t="s">
         <v>43</v>
       </c>
-      <c r="AK1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4246,7 +4237,7 @@
         <v>-2.7204892560691641E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4356,7 +4347,7 @@
         <v>-4.8088678300469062E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -4466,7 +4457,7 @@
         <v>3.8606296235684033E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4576,7 +4567,7 @@
         <v>1.9263754534478935E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -4686,7 +4677,7 @@
         <v>5.966364424646888E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4796,7 +4787,7 @@
         <v>-1.5710077137610456E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -4906,7 +4897,7 @@
         <v>-1.3596710315837336E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -5016,9 +5007,9 @@
         <v>-2.8645346773594734E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>0.53933856767342625</v>
@@ -5126,7 +5117,7 @@
         <v>-1.1585531045409082E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -5236,9 +5227,9 @@
         <v>-6.8207952601999546E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12">
         <v>0.5356682365726253</v>
@@ -5346,9 +5337,9 @@
         <v>1.0315479854308906E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B13">
         <v>-3.8811949863632213E-2</v>
@@ -5456,7 +5447,7 @@
         <v>-7.3817653992011871E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -5566,7 +5557,7 @@
         <v>-6.0556870308114503E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -5676,7 +5667,7 @@
         <v>-5.4009401585079896E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>

--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8186070-4565-2749-8D6A-F314458B2E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7001A211-65AC-DF43-A96F-F449CCA0119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="19540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="54">
   <si>
     <t>Description:</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Ydses_c5_Q5_L1</t>
+  </si>
+  <si>
+    <t>Dlltsd01_L1</t>
   </si>
   <si>
     <t>UKC</t>
@@ -701,68 +704,68 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B5">
-        <v>0.22029683046666237</v>
+        <v>0.2213905845571944</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F5">
-        <v>1645.7124011500975</v>
+        <v>1648.3842838862272</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6">
-        <v>26159</v>
+        <v>26156</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6">
-        <v>-3457058.8340486912</v>
+        <v>-3452261.0460356632</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11">
-        <v>0.21457656468585751</v>
+        <v>0.21485733363385973</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11">
-        <v>3311.6517762604585</v>
+        <v>3294.0849406273219</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12">
-        <v>60827</v>
+        <v>60833</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12">
-        <v>-9011943.1780763194</v>
+        <v>-9008031.6831588075</v>
       </c>
     </row>
   </sheetData>
@@ -772,10 +775,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AG32"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -875,3136 +878,3336 @@
       <c r="AG1" t="s">
         <v>43</v>
       </c>
+      <c r="AH1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0.11242431948012209</v>
+        <v>0.10954926867205772</v>
       </c>
       <c r="C2">
-        <v>1.6553030652294767E-3</v>
+        <v>1.6636339468067492E-3</v>
       </c>
       <c r="D2">
-        <v>6.6241313268033779E-6</v>
+        <v>-3.7221000597152388E-5</v>
       </c>
       <c r="E2">
-        <v>-2.857129247827846E-7</v>
+        <v>6.4772414891427306E-8</v>
       </c>
       <c r="F2">
-        <v>-1.9930638127097335E-4</v>
+        <v>-2.0562352849196942E-4</v>
       </c>
       <c r="G2">
-        <v>-1.7442976266016715E-4</v>
+        <v>-2.0822440536719312E-4</v>
       </c>
       <c r="H2">
-        <v>-6.5442521605166734E-7</v>
+        <v>3.8689516840200732E-6</v>
       </c>
       <c r="I2">
-        <v>-9.7290229096814231E-6</v>
+        <v>-7.5657553833130118E-6</v>
       </c>
       <c r="J2">
-        <v>5.9906626312385093E-4</v>
+        <v>5.982792048583852E-4</v>
       </c>
       <c r="K2">
-        <v>8.5404157343601291E-4</v>
+        <v>7.041998484249622E-4</v>
       </c>
       <c r="L2">
-        <v>8.5837091857702153E-4</v>
+        <v>9.0288484663960961E-4</v>
       </c>
       <c r="M2">
-        <v>1.2900300544420144E-3</v>
+        <v>1.3250295488772381E-3</v>
       </c>
       <c r="N2">
-        <v>1.2001911197017743E-3</v>
+        <v>1.2281547617617608E-3</v>
       </c>
       <c r="O2">
-        <v>8.2869379774168361E-4</v>
+        <v>8.4259762382982335E-4</v>
       </c>
       <c r="P2">
-        <v>-1.2233281710598847E-3</v>
+        <v>4.6022563817849928E-4</v>
       </c>
       <c r="Q2">
-        <v>-1.7886914694781693E-3</v>
+        <v>-1.1962979631865182E-3</v>
       </c>
       <c r="R2">
-        <v>-1.0335151182635934E-3</v>
+        <v>-1.7249994550706388E-3</v>
       </c>
       <c r="S2">
-        <v>-1.3260660839624072E-3</v>
+        <v>-1.0098658170196145E-3</v>
       </c>
       <c r="T2">
-        <v>-9.1612746393551878E-4</v>
+        <v>-1.2912129871671943E-3</v>
       </c>
       <c r="U2">
-        <v>-1.002835754993919E-3</v>
+        <v>-9.0383631110555786E-4</v>
       </c>
       <c r="V2">
-        <v>-1.106436525403166E-3</v>
+        <v>-9.847330591255081E-4</v>
       </c>
       <c r="W2">
-        <v>-1.1655726553340684E-3</v>
+        <v>-1.0924357778282711E-3</v>
       </c>
       <c r="X2">
-        <v>-1.1446484508254402E-3</v>
+        <v>-1.1501715642297061E-3</v>
       </c>
       <c r="Y2">
-        <v>-1.1648692273345507E-3</v>
+        <v>-1.1423072500666908E-3</v>
       </c>
       <c r="Z2">
-        <v>-6.6869505607167808E-4</v>
+        <v>-1.154843522886884E-3</v>
       </c>
       <c r="AA2">
-        <v>-1.1366951551944511E-5</v>
+        <v>-6.7325170719638016E-4</v>
       </c>
       <c r="AB2">
-        <v>2.5012365707570926E-4</v>
+        <v>-9.5909821632421963E-6</v>
       </c>
       <c r="AC2">
-        <v>2.6972907332088259E-4</v>
+        <v>2.3899944807097111E-4</v>
       </c>
       <c r="AD2">
-        <v>-1.8434475740953745E-4</v>
+        <v>2.7816574925235951E-4</v>
       </c>
       <c r="AE2">
-        <v>-4.4426992261511165E-3</v>
+        <v>-1.3356485573487605E-4</v>
       </c>
       <c r="AF2">
-        <v>-4.5553998471864194E-4</v>
+        <v>-4.2796241113990489E-3</v>
       </c>
       <c r="AG2">
-        <v>6.2043114978482805E-4</v>
+        <v>-4.6336786088605738E-4</v>
+      </c>
+      <c r="AH2">
+        <v>1.5716426711145401E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.50376165611927548</v>
+        <v>0.51601815435283793</v>
       </c>
       <c r="C3">
-        <v>6.6241313268033779E-6</v>
+        <v>-3.7221000597152388E-5</v>
       </c>
       <c r="D3">
-        <v>1.7918215786649934E-3</v>
+        <v>1.7759763502558908E-3</v>
       </c>
       <c r="E3">
-        <v>-1.3985134263062408E-5</v>
+        <v>-1.3849941871626024E-5</v>
       </c>
       <c r="F3">
-        <v>-1.1216728941729204E-4</v>
+        <v>-5.7897730298992617E-5</v>
       </c>
       <c r="G3">
-        <v>-2.5032437392740435E-5</v>
+        <v>-1.1735369832007679E-5</v>
       </c>
       <c r="H3">
-        <v>5.9218973532921366E-6</v>
+        <v>4.5510619755977132E-6</v>
       </c>
       <c r="I3">
-        <v>1.1973304482706709E-6</v>
+        <v>1.0982111255220623E-6</v>
       </c>
       <c r="J3">
-        <v>-1.4180150450474743E-4</v>
+        <v>-1.577968697157317E-4</v>
       </c>
       <c r="K3">
-        <v>1.3897141006309344E-3</v>
+        <v>1.2169642778855627E-3</v>
       </c>
       <c r="L3">
-        <v>7.9290253031658042E-4</v>
+        <v>6.4345649072568289E-4</v>
       </c>
       <c r="M3">
-        <v>1.3147163442918941E-3</v>
+        <v>1.0718837514020474E-3</v>
       </c>
       <c r="N3">
-        <v>1.3681747687588619E-3</v>
+        <v>1.1135467301564839E-3</v>
       </c>
       <c r="O3">
-        <v>1.382434796031895E-3</v>
+        <v>1.1566480569527304E-3</v>
       </c>
       <c r="P3">
-        <v>-2.5452365097821533E-4</v>
+        <v>-4.5181916970053748E-5</v>
       </c>
       <c r="Q3">
-        <v>-6.662161043312631E-4</v>
+        <v>-1.1816482201765927E-4</v>
       </c>
       <c r="R3">
-        <v>-3.4584808216091278E-4</v>
+        <v>-3.831810565506355E-4</v>
       </c>
       <c r="S3">
-        <v>-3.4009777578406647E-4</v>
+        <v>-1.9572465689284696E-4</v>
       </c>
       <c r="T3">
-        <v>-2.1232156514588985E-4</v>
+        <v>-1.9034775348235333E-4</v>
       </c>
       <c r="U3">
-        <v>-2.9349470368298519E-4</v>
+        <v>-4.9112849408235182E-5</v>
       </c>
       <c r="V3">
-        <v>-1.8292428886903384E-4</v>
+        <v>-1.4534294324750063E-4</v>
       </c>
       <c r="W3">
-        <v>-2.7936671993147172E-4</v>
+        <v>-3.3438882093485278E-5</v>
       </c>
       <c r="X3">
-        <v>-3.3984462553406786E-4</v>
+        <v>-1.1659868555197184E-4</v>
       </c>
       <c r="Y3">
-        <v>-2.8999699847368637E-4</v>
+        <v>-1.4601185880170481E-4</v>
       </c>
       <c r="Z3">
-        <v>-3.0815791782035085E-4</v>
+        <v>-1.2150128821220019E-4</v>
       </c>
       <c r="AA3">
-        <v>-2.7443141963271259E-5</v>
+        <v>-1.7457630591909135E-4</v>
       </c>
       <c r="AB3">
-        <v>1.1446273566451115E-4</v>
+        <v>-2.1414488845452814E-5</v>
       </c>
       <c r="AC3">
-        <v>1.4338622550074537E-4</v>
+        <v>7.3768484269390311E-5</v>
       </c>
       <c r="AD3">
-        <v>-2.5090533802485729E-4</v>
+        <v>8.3024242661412784E-5</v>
       </c>
       <c r="AE3">
-        <v>-2.1694328517966599E-3</v>
+        <v>-2.0324666875240829E-4</v>
       </c>
       <c r="AF3">
-        <v>-9.7901568037135622E-5</v>
+        <v>-1.4432699710086316E-3</v>
       </c>
       <c r="AG3">
-        <v>-5.7705012434188546E-2</v>
+        <v>-7.0481832906434203E-5</v>
+      </c>
+      <c r="AH3">
+        <v>-5.7208342731185038E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-3.500607216796907E-3</v>
+        <v>-3.597955859361499E-3</v>
       </c>
       <c r="C4">
-        <v>-2.857129247827846E-7</v>
+        <v>6.4772414891427306E-8</v>
       </c>
       <c r="D4">
-        <v>-1.3985134263062408E-5</v>
+        <v>-1.3849941871626024E-5</v>
       </c>
       <c r="E4">
-        <v>1.1044490535769686E-7</v>
+        <v>1.0929083071813395E-7</v>
       </c>
       <c r="F4">
-        <v>9.1606214129624829E-7</v>
+        <v>4.8881032980318965E-7</v>
       </c>
       <c r="G4">
-        <v>2.4175533542132206E-8</v>
+        <v>-7.5137548638683987E-8</v>
       </c>
       <c r="H4">
-        <v>-5.110592005761699E-8</v>
+        <v>-3.78504831691035E-8</v>
       </c>
       <c r="I4">
-        <v>-1.7152783230348018E-8</v>
+        <v>-1.5869206241652598E-8</v>
       </c>
       <c r="J4">
-        <v>-4.8034662956052653E-7</v>
+        <v>-3.4223423266198458E-7</v>
       </c>
       <c r="K4">
-        <v>-1.1804405128958183E-5</v>
+        <v>-1.0353993321016099E-5</v>
       </c>
       <c r="L4">
-        <v>-6.8921236093451863E-6</v>
+        <v>-5.5134203656734358E-6</v>
       </c>
       <c r="M4">
-        <v>-1.1383334336608538E-5</v>
+        <v>-9.2869777346749668E-6</v>
       </c>
       <c r="N4">
-        <v>-1.1670821307777296E-5</v>
+        <v>-9.4716332493015656E-6</v>
       </c>
       <c r="O4">
-        <v>-1.1702835394568779E-5</v>
+        <v>-9.7391856389795941E-6</v>
       </c>
       <c r="P4">
-        <v>2.4958791329438338E-6</v>
+        <v>5.4810385649985225E-7</v>
       </c>
       <c r="Q4">
-        <v>5.8082981427749498E-6</v>
+        <v>1.3755914342857348E-6</v>
       </c>
       <c r="R4">
-        <v>2.9752199325502578E-6</v>
+        <v>3.4887530264951679E-6</v>
       </c>
       <c r="S4">
-        <v>3.0537331985594691E-6</v>
+        <v>1.7434568931532076E-6</v>
       </c>
       <c r="T4">
-        <v>1.9175745964290195E-6</v>
+        <v>1.8233501463745406E-6</v>
       </c>
       <c r="U4">
-        <v>2.5995227511202705E-6</v>
+        <v>5.9983265515955574E-7</v>
       </c>
       <c r="V4">
-        <v>1.8568465652505218E-6</v>
+        <v>1.3867467653997647E-6</v>
       </c>
       <c r="W4">
-        <v>2.5272810334622331E-6</v>
+        <v>6.3584161861136032E-7</v>
       </c>
       <c r="X4">
-        <v>2.6895869347601806E-6</v>
+        <v>1.17026338321963E-6</v>
       </c>
       <c r="Y4">
-        <v>2.6129729643860691E-6</v>
+        <v>1.179180915106162E-6</v>
       </c>
       <c r="Z4">
-        <v>2.5171093490477235E-6</v>
+        <v>1.2318415760660261E-6</v>
       </c>
       <c r="AA4">
-        <v>1.7770612206448799E-7</v>
+        <v>1.4037523786891086E-6</v>
       </c>
       <c r="AB4">
-        <v>-9.7351215422054188E-7</v>
+        <v>1.3115388549533218E-7</v>
       </c>
       <c r="AC4">
-        <v>-1.313342239538703E-6</v>
+        <v>-6.4421253843731895E-7</v>
       </c>
       <c r="AD4">
-        <v>2.2733936873017087E-6</v>
+        <v>-8.4426249492158562E-7</v>
       </c>
       <c r="AE4">
-        <v>1.8440645990181262E-5</v>
+        <v>1.8824156444837629E-6</v>
       </c>
       <c r="AF4">
-        <v>6.5133108212459082E-7</v>
+        <v>1.2504475447712871E-5</v>
       </c>
       <c r="AG4">
-        <v>4.4805888014480837E-4</v>
+        <v>4.4850648512936622E-7</v>
+      </c>
+      <c r="AH4">
+        <v>4.4352568608887409E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-7.6098030091010085E-2</v>
+        <v>-7.1507216771985224E-2</v>
       </c>
       <c r="C5">
-        <v>-1.9930638127097335E-4</v>
+        <v>-2.0562352849196942E-4</v>
       </c>
       <c r="D5">
-        <v>-1.1216728941729204E-4</v>
+        <v>-5.7897730298992617E-5</v>
       </c>
       <c r="E5">
-        <v>9.1606214129624829E-7</v>
+        <v>4.8881032980318965E-7</v>
       </c>
       <c r="F5">
-        <v>2.3601965587915297E-3</v>
+        <v>2.3811437434428815E-3</v>
       </c>
       <c r="G5">
-        <v>1.6650936555297809E-3</v>
+        <v>1.7085055558805839E-3</v>
       </c>
       <c r="H5">
-        <v>-8.4667496548066198E-6</v>
+        <v>-1.3900231954001944E-5</v>
       </c>
       <c r="I5">
-        <v>-8.434701630915359E-6</v>
+        <v>-1.1162192775048216E-5</v>
       </c>
       <c r="J5">
-        <v>1.1596749038470514E-4</v>
+        <v>1.1272291384015177E-4</v>
       </c>
       <c r="K5">
-        <v>-6.8459474975087788E-4</v>
+        <v>-5.0189334682182625E-4</v>
       </c>
       <c r="L5">
-        <v>-8.4167026890158707E-4</v>
+        <v>-9.1475532328687444E-4</v>
       </c>
       <c r="M5">
-        <v>-8.1504901635518455E-4</v>
+        <v>-8.9185098652038233E-4</v>
       </c>
       <c r="N5">
-        <v>-7.3384821911865773E-4</v>
+        <v>-7.9710723232193689E-4</v>
       </c>
       <c r="O5">
-        <v>-1.9938872968201012E-4</v>
+        <v>-2.4862275678907801E-4</v>
       </c>
       <c r="P5">
-        <v>5.1887731768539627E-4</v>
+        <v>-5.9694186046919278E-4</v>
       </c>
       <c r="Q5">
-        <v>1.2699363874003789E-3</v>
+        <v>5.2160182075045307E-4</v>
       </c>
       <c r="R5">
-        <v>9.8503390927221412E-4</v>
+        <v>1.2372529205743592E-3</v>
       </c>
       <c r="S5">
-        <v>6.3139373180038337E-4</v>
+        <v>9.6536709390601379E-4</v>
       </c>
       <c r="T5">
-        <v>5.592323839378765E-4</v>
+        <v>6.1468788242573041E-4</v>
       </c>
       <c r="U5">
-        <v>6.3195200225049089E-4</v>
+        <v>5.3857973051496771E-4</v>
       </c>
       <c r="V5">
-        <v>9.3353938661150273E-4</v>
+        <v>6.3533371820659388E-4</v>
       </c>
       <c r="W5">
-        <v>8.169236732865656E-4</v>
+        <v>9.3796792388116087E-4</v>
       </c>
       <c r="X5">
-        <v>9.2585490335738698E-4</v>
+        <v>8.2964670507371888E-4</v>
       </c>
       <c r="Y5">
-        <v>6.7336019433498085E-4</v>
+        <v>9.1399263301876628E-4</v>
       </c>
       <c r="Z5">
-        <v>1.1387529075870806E-3</v>
+        <v>6.8644692588015776E-4</v>
       </c>
       <c r="AA5">
-        <v>1.7445225467772456E-5</v>
+        <v>1.1924040947890843E-3</v>
       </c>
       <c r="AB5">
-        <v>-8.4226157188011484E-5</v>
+        <v>1.3455199897537487E-5</v>
       </c>
       <c r="AC5">
-        <v>9.2782823284556868E-6</v>
+        <v>-7.0154215605294475E-5</v>
       </c>
       <c r="AD5">
-        <v>3.7007892389643438E-4</v>
+        <v>1.2208520768304879E-5</v>
       </c>
       <c r="AE5">
-        <v>3.7354317207578085E-3</v>
+        <v>3.220369553871658E-4</v>
       </c>
       <c r="AF5">
-        <v>3.4140853721482316E-4</v>
+        <v>3.6298414841735502E-3</v>
       </c>
       <c r="AG5">
-        <v>2.213837203694005E-3</v>
+        <v>3.6257130334769691E-4</v>
+      </c>
+      <c r="AH5">
+        <v>1.0284453137187339E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-0.12310261586150241</v>
+        <v>-0.11467903438673017</v>
       </c>
       <c r="C6">
-        <v>-1.7442976266016715E-4</v>
+        <v>-2.0822440536719312E-4</v>
       </c>
       <c r="D6">
-        <v>-2.5032437392740435E-5</v>
+        <v>-1.1735369832007679E-5</v>
       </c>
       <c r="E6">
-        <v>2.4175533542132206E-8</v>
+        <v>-7.5137548638683987E-8</v>
       </c>
       <c r="F6">
-        <v>1.6650936555297809E-3</v>
+        <v>1.7085055558805839E-3</v>
       </c>
       <c r="G6">
-        <v>3.158239846362361E-3</v>
+        <v>3.1937430985295315E-3</v>
       </c>
       <c r="H6">
-        <v>1.7675837763657296E-6</v>
+        <v>-6.7386713221845171E-7</v>
       </c>
       <c r="I6">
-        <v>-3.2141831066453425E-6</v>
+        <v>-4.237051459351654E-6</v>
       </c>
       <c r="J6">
-        <v>4.0552757646198067E-4</v>
+        <v>3.88135353909906E-4</v>
       </c>
       <c r="K6">
-        <v>4.8302449226533166E-4</v>
+        <v>4.219097022249616E-4</v>
       </c>
       <c r="L6">
-        <v>3.027597353444096E-4</v>
+        <v>1.9428022093635647E-4</v>
       </c>
       <c r="M6">
-        <v>8.8114849074720936E-4</v>
+        <v>7.0330448362312037E-4</v>
       </c>
       <c r="N6">
-        <v>1.1420640723983548E-3</v>
+        <v>9.5772644286733948E-4</v>
       </c>
       <c r="O6">
-        <v>1.5872714192021516E-3</v>
+        <v>1.4255193190902409E-3</v>
       </c>
       <c r="P6">
-        <v>-4.7335207487223229E-4</v>
+        <v>-2.3409187487754516E-4</v>
       </c>
       <c r="Q6">
-        <v>-5.5018871178856912E-4</v>
+        <v>-3.5261815585580435E-4</v>
       </c>
       <c r="R6">
-        <v>1.2464521832511411E-4</v>
+        <v>-3.6858311537051741E-4</v>
       </c>
       <c r="S6">
-        <v>-4.3163068994972275E-4</v>
+        <v>2.3344663094671198E-4</v>
       </c>
       <c r="T6">
-        <v>-2.1485989856697264E-4</v>
+        <v>-3.2922110499106129E-4</v>
       </c>
       <c r="U6">
-        <v>-2.5107716659964635E-4</v>
+        <v>-1.0398223168221114E-4</v>
       </c>
       <c r="V6">
-        <v>-1.8032816322024071E-4</v>
+        <v>-1.2764322120737629E-4</v>
       </c>
       <c r="W6">
-        <v>-2.8548992928781943E-4</v>
+        <v>-6.5424311590343712E-5</v>
       </c>
       <c r="X6">
-        <v>-4.7205054324509746E-4</v>
+        <v>-1.5177530750236888E-4</v>
       </c>
       <c r="Y6">
-        <v>-3.7494780298112824E-4</v>
+        <v>-3.7710233893113666E-4</v>
       </c>
       <c r="Z6">
-        <v>-9.2747198385329833E-4</v>
+        <v>-2.4304529010942249E-4</v>
       </c>
       <c r="AA6">
-        <v>5.3557519767366492E-6</v>
+        <v>-8.1107138794252686E-4</v>
       </c>
       <c r="AB6">
-        <v>2.4718836067931602E-4</v>
+        <v>6.513069069771912E-6</v>
       </c>
       <c r="AC6">
-        <v>5.5514469630770532E-4</v>
+        <v>2.2530026226605837E-4</v>
       </c>
       <c r="AD6">
-        <v>-2.8136892051779886E-4</v>
+        <v>5.4098960169393466E-4</v>
       </c>
       <c r="AE6">
-        <v>-4.8853759071950959E-4</v>
+        <v>-2.5592402160860513E-4</v>
       </c>
       <c r="AF6">
-        <v>4.0556765445366538E-4</v>
+        <v>1.6784197773048529E-5</v>
       </c>
       <c r="AG6">
-        <v>-1.0445761682538867E-3</v>
+        <v>4.270278188862661E-4</v>
+      </c>
+      <c r="AH6">
+        <v>-1.285783073726635E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7">
-        <v>-1.8285964556797767E-3</v>
+        <v>-3.7263926766791374E-3</v>
       </c>
       <c r="C7">
-        <v>-6.5442521605166734E-7</v>
+        <v>3.8689516840200732E-6</v>
       </c>
       <c r="D7">
-        <v>5.9218973532921366E-6</v>
+        <v>4.5510619755977132E-6</v>
       </c>
       <c r="E7">
-        <v>-5.110592005761699E-8</v>
+        <v>-3.78504831691035E-8</v>
       </c>
       <c r="F7">
-        <v>-8.4667496548066198E-6</v>
+        <v>-1.3900231954001944E-5</v>
       </c>
       <c r="G7">
-        <v>1.7675837763657296E-6</v>
+        <v>-6.7386713221845171E-7</v>
       </c>
       <c r="H7">
-        <v>3.0157360875166286E-6</v>
+        <v>3.6705347384126281E-6</v>
       </c>
       <c r="I7">
-        <v>1.96662802102237E-7</v>
+        <v>4.2345579782747338E-7</v>
       </c>
       <c r="J7">
-        <v>-1.2161923281238688E-7</v>
+        <v>-7.6100774806769206E-7</v>
       </c>
       <c r="K7">
-        <v>5.0464058521164216E-5</v>
+        <v>5.3773258391987618E-5</v>
       </c>
       <c r="L7">
-        <v>1.7808183340123969E-5</v>
+        <v>3.6867309317916059E-5</v>
       </c>
       <c r="M7">
-        <v>1.1130001754841752E-5</v>
+        <v>4.0927434184745079E-5</v>
       </c>
       <c r="N7">
-        <v>1.712493516734491E-5</v>
+        <v>4.8373808550933447E-5</v>
       </c>
       <c r="O7">
-        <v>3.6903238796955106E-6</v>
+        <v>3.0899879443307596E-5</v>
       </c>
       <c r="P7">
-        <v>-2.718762959967358E-5</v>
+        <v>5.6913455526318328E-5</v>
       </c>
       <c r="Q7">
-        <v>-4.672831012788117E-5</v>
+        <v>-4.456480910833868E-5</v>
       </c>
       <c r="R7">
-        <v>-1.8651755787865514E-5</v>
+        <v>-7.9106318668780936E-5</v>
       </c>
       <c r="S7">
-        <v>-2.7854091270386168E-5</v>
+        <v>-3.6095755063872984E-5</v>
       </c>
       <c r="T7">
-        <v>-2.1884429142721612E-5</v>
+        <v>-4.3486761779856396E-5</v>
       </c>
       <c r="U7">
-        <v>-2.7446273931177689E-5</v>
+        <v>-3.9288734670354209E-5</v>
       </c>
       <c r="V7">
-        <v>-2.1883421649596959E-5</v>
+        <v>-4.5478000587014568E-5</v>
       </c>
       <c r="W7">
-        <v>-3.1795184726540965E-5</v>
+        <v>-3.9519927201841414E-5</v>
       </c>
       <c r="X7">
-        <v>-2.9876435204284364E-5</v>
+        <v>-5.2663112499476064E-5</v>
       </c>
       <c r="Y7">
-        <v>-3.3225176670746779E-5</v>
+        <v>-5.3037754652481754E-5</v>
       </c>
       <c r="Z7">
-        <v>-4.3646174695807674E-5</v>
+        <v>-5.2587838813649416E-5</v>
       </c>
       <c r="AA7">
-        <v>1.1353574497580474E-7</v>
+        <v>-6.4884877886612767E-5</v>
       </c>
       <c r="AB7">
-        <v>5.3067780072667172E-6</v>
+        <v>-3.0175474393208867E-7</v>
       </c>
       <c r="AC7">
-        <v>4.7919920017070448E-6</v>
+        <v>8.2237333035854081E-6</v>
       </c>
       <c r="AD7">
-        <v>-1.3836965228521873E-5</v>
+        <v>1.2351937744690619E-5</v>
       </c>
       <c r="AE7">
-        <v>-1.2191014095483703E-4</v>
+        <v>-1.5065600838914652E-5</v>
       </c>
       <c r="AF7">
-        <v>-5.6979168551107842E-6</v>
+        <v>-2.0193319986267356E-4</v>
       </c>
       <c r="AG7">
-        <v>-3.1134931479971997E-4</v>
+        <v>-1.1366567289394905E-5</v>
+      </c>
+      <c r="AH7">
+        <v>-3.2331068767199795E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8">
-        <v>3.880282710716236E-4</v>
+        <v>-4.8618202773207232E-4</v>
       </c>
       <c r="C8">
-        <v>-9.7290229096814231E-6</v>
+        <v>-7.5657553833130118E-6</v>
       </c>
       <c r="D8">
-        <v>1.1973304482706709E-6</v>
+        <v>1.0982111255220623E-6</v>
       </c>
       <c r="E8">
-        <v>-1.7152783230348018E-8</v>
+        <v>-1.5869206241652598E-8</v>
       </c>
       <c r="F8">
-        <v>-8.434701630915359E-6</v>
+        <v>-1.1162192775048216E-5</v>
       </c>
       <c r="G8">
-        <v>-3.2141831066453425E-6</v>
+        <v>-4.237051459351654E-6</v>
       </c>
       <c r="H8">
-        <v>1.96662802102237E-7</v>
+        <v>4.2345579782747338E-7</v>
       </c>
       <c r="I8">
-        <v>3.1622864170640661E-6</v>
+        <v>3.2152322627037443E-6</v>
       </c>
       <c r="J8">
-        <v>-1.1427625015177862E-5</v>
+        <v>-1.1135364278935786E-5</v>
       </c>
       <c r="K8">
-        <v>-7.6739309084216702E-6</v>
+        <v>-1.549149465814774E-6</v>
       </c>
       <c r="L8">
-        <v>-2.8914860261969192E-6</v>
+        <v>8.7601248456730427E-6</v>
       </c>
       <c r="M8">
-        <v>-3.2275303898937602E-5</v>
+        <v>-1.6376100031404838E-5</v>
       </c>
       <c r="N8">
-        <v>-3.5271350365229147E-5</v>
+        <v>-1.8539937469083841E-5</v>
       </c>
       <c r="O8">
-        <v>-3.7922185349196298E-5</v>
+        <v>-2.3080870424543073E-5</v>
       </c>
       <c r="P8">
-        <v>-4.5331145470412643E-7</v>
+        <v>1.7411794912582793E-5</v>
       </c>
       <c r="Q8">
-        <v>9.4797271601292652E-6</v>
+        <v>-8.7508313021763976E-6</v>
       </c>
       <c r="R8">
-        <v>1.5956673036758725E-7</v>
+        <v>-7.6880857549925692E-6</v>
       </c>
       <c r="S8">
-        <v>-9.782801193795182E-6</v>
+        <v>-8.1507726445603464E-6</v>
       </c>
       <c r="T8">
-        <v>-4.0409964735373604E-6</v>
+        <v>-1.7970912302829817E-5</v>
       </c>
       <c r="U8">
-        <v>-7.5704114754820886E-6</v>
+        <v>-1.2598474277910297E-5</v>
       </c>
       <c r="V8">
-        <v>-6.1460110473547679E-6</v>
+        <v>-1.6524366834896165E-5</v>
       </c>
       <c r="W8">
-        <v>-6.748142536664272E-6</v>
+        <v>-1.4399214004307828E-5</v>
       </c>
       <c r="X8">
-        <v>-5.5755394995919596E-6</v>
+        <v>-1.7159754152147946E-5</v>
       </c>
       <c r="Y8">
-        <v>-6.2857391588469751E-6</v>
+        <v>-1.5629270179927227E-5</v>
       </c>
       <c r="Z8">
-        <v>-2.6445868137072126E-5</v>
+        <v>-1.5351652430080565E-5</v>
       </c>
       <c r="AA8">
-        <v>1.926202665160141E-6</v>
+        <v>-3.6326354668531215E-5</v>
       </c>
       <c r="AB8">
-        <v>-2.1251748286803252E-6</v>
+        <v>1.7226003919480057E-6</v>
       </c>
       <c r="AC8">
-        <v>-4.4795139987441703E-6</v>
+        <v>-6.7303034800909769E-7</v>
       </c>
       <c r="AD8">
-        <v>-1.3393998413329875E-5</v>
+        <v>-8.9726751490706511E-7</v>
       </c>
       <c r="AE8">
-        <v>5.9561762939144445E-5</v>
+        <v>-1.4615227430008252E-5</v>
       </c>
       <c r="AF8">
-        <v>-2.2340732903636963E-6</v>
+        <v>1.7071736895229962E-5</v>
       </c>
       <c r="AG8">
-        <v>-1.5726098690799206E-4</v>
+        <v>-2.537323481334834E-6</v>
+      </c>
+      <c r="AH8">
+        <v>-1.7234077610545748E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
       <c r="B9">
-        <v>0.76540195603404193</v>
+        <v>0.76317033407790569</v>
       </c>
       <c r="C9">
-        <v>5.9906626312385093E-4</v>
+        <v>5.982792048583852E-4</v>
       </c>
       <c r="D9">
-        <v>-1.4180150450474743E-4</v>
+        <v>-1.577968697157317E-4</v>
       </c>
       <c r="E9">
-        <v>-4.8034662956052653E-7</v>
+        <v>-3.4223423266198458E-7</v>
       </c>
       <c r="F9">
-        <v>1.1596749038470514E-4</v>
+        <v>1.1272291384015177E-4</v>
       </c>
       <c r="G9">
-        <v>4.0552757646198067E-4</v>
+        <v>3.88135353909906E-4</v>
       </c>
       <c r="H9">
-        <v>-1.2161923281238688E-7</v>
+        <v>-7.6100774806769206E-7</v>
       </c>
       <c r="I9">
-        <v>-1.1427625015177862E-5</v>
+        <v>-1.1135364278935786E-5</v>
       </c>
       <c r="J9">
-        <v>3.7586124468886196E-3</v>
+        <v>3.7379922552623667E-3</v>
       </c>
       <c r="K9">
-        <v>1.5785117467315493E-3</v>
+        <v>1.4763102363168357E-3</v>
       </c>
       <c r="L9">
-        <v>6.874547164757612E-4</v>
+        <v>5.1227277017757214E-4</v>
       </c>
       <c r="M9">
-        <v>1.4274956340256037E-3</v>
+        <v>1.2739867914771177E-3</v>
       </c>
       <c r="N9">
-        <v>1.4792926408807514E-3</v>
+        <v>1.3236039865338334E-3</v>
       </c>
       <c r="O9">
-        <v>1.5102726871854197E-3</v>
+        <v>1.3641492843854963E-3</v>
       </c>
       <c r="P9">
-        <v>-6.6538359264779572E-4</v>
+        <v>-4.2574892420049401E-5</v>
       </c>
       <c r="Q9">
-        <v>-1.1070492165856996E-3</v>
+        <v>-6.2487208335253175E-4</v>
       </c>
       <c r="R9">
-        <v>-1.0152303274702651E-4</v>
+        <v>-1.022824043948406E-3</v>
       </c>
       <c r="S9">
-        <v>-4.1836174668378502E-4</v>
+        <v>-6.2550295880437964E-5</v>
       </c>
       <c r="T9">
-        <v>-2.1189609882152176E-4</v>
+        <v>-3.7698572746154915E-4</v>
       </c>
       <c r="U9">
-        <v>-2.7638603269917669E-4</v>
+        <v>-1.9525169348198236E-4</v>
       </c>
       <c r="V9">
-        <v>-7.3931961400957626E-4</v>
+        <v>-2.3339764858111046E-4</v>
       </c>
       <c r="W9">
-        <v>-6.112365800291196E-4</v>
+        <v>-7.1547489369348273E-4</v>
       </c>
       <c r="X9">
-        <v>-2.7946955869048891E-4</v>
+        <v>-5.4547268011928725E-4</v>
       </c>
       <c r="Y9">
-        <v>-3.9028844305482278E-4</v>
+        <v>-2.6456056178748681E-4</v>
       </c>
       <c r="Z9">
-        <v>-2.5678979880757076E-4</v>
+        <v>-3.6362801984441036E-4</v>
       </c>
       <c r="AA9">
-        <v>5.5489645738426418E-5</v>
+        <v>-2.031664107929633E-4</v>
       </c>
       <c r="AB9">
-        <v>1.6227697476110629E-4</v>
+        <v>5.4182694337199123E-5</v>
       </c>
       <c r="AC9">
-        <v>5.6449348910767028E-4</v>
+        <v>1.579359286024689E-4</v>
       </c>
       <c r="AD9">
-        <v>-2.0185502486070976E-4</v>
+        <v>5.8132769883256948E-4</v>
       </c>
       <c r="AE9">
-        <v>-3.5112608088026798E-3</v>
+        <v>-1.8222289801069977E-4</v>
       </c>
       <c r="AF9">
-        <v>6.2126603546640811E-4</v>
+        <v>-3.3383567065673886E-3</v>
       </c>
       <c r="AG9">
-        <v>7.3091459209271986E-3</v>
+        <v>5.3409354832910231E-4</v>
+      </c>
+      <c r="AH9">
+        <v>7.9390310698239826E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10">
-        <v>0.43399706821766743</v>
+        <v>0.46706329757145792</v>
       </c>
       <c r="C10">
-        <v>8.5404157343601291E-4</v>
+        <v>7.041998484249622E-4</v>
       </c>
       <c r="D10">
-        <v>1.3897141006309344E-3</v>
+        <v>1.2169642778855627E-3</v>
       </c>
       <c r="E10">
-        <v>-1.1804405128958183E-5</v>
+        <v>-1.0353993321016099E-5</v>
       </c>
       <c r="F10">
-        <v>-6.8459474975087788E-4</v>
+        <v>-5.0189334682182625E-4</v>
       </c>
       <c r="G10">
-        <v>4.8302449226533166E-4</v>
+        <v>4.219097022249616E-4</v>
       </c>
       <c r="H10">
-        <v>5.0464058521164216E-5</v>
+        <v>5.3773258391987618E-5</v>
       </c>
       <c r="I10">
-        <v>-7.6739309084216702E-6</v>
+        <v>-1.549149465814774E-6</v>
       </c>
       <c r="J10">
-        <v>1.5785117467315493E-3</v>
+        <v>1.4763102363168357E-3</v>
       </c>
       <c r="K10">
-        <v>1.2167343443513307E-2</v>
+        <v>1.0774079599253868E-2</v>
       </c>
       <c r="L10">
-        <v>6.8837298547032855E-3</v>
+        <v>5.7604126401509283E-3</v>
       </c>
       <c r="M10">
-        <v>1.2178261914374829E-2</v>
+        <v>1.0863971123695727E-2</v>
       </c>
       <c r="N10">
-        <v>1.3015407752700672E-2</v>
+        <v>1.1601086686978415E-2</v>
       </c>
       <c r="O10">
-        <v>1.2444772222525595E-2</v>
+        <v>1.1114250693718464E-2</v>
       </c>
       <c r="P10">
-        <v>-4.0237574286098293E-3</v>
+        <v>8.9733520833347805E-4</v>
       </c>
       <c r="Q10">
-        <v>-8.6041245913911144E-3</v>
+        <v>-3.3889858531435859E-3</v>
       </c>
       <c r="R10">
-        <v>-3.676652672805987E-3</v>
+        <v>-7.2776146401295483E-3</v>
       </c>
       <c r="S10">
-        <v>-3.8296164986273504E-3</v>
+        <v>-2.961073702059917E-3</v>
       </c>
       <c r="T10">
-        <v>-3.063598227655992E-3</v>
+        <v>-3.1563411674357059E-3</v>
       </c>
       <c r="U10">
-        <v>-3.6205127910413637E-3</v>
+        <v>-2.3086834048780466E-3</v>
       </c>
       <c r="V10">
-        <v>-3.6843246532049078E-3</v>
+        <v>-2.9730178334474965E-3</v>
       </c>
       <c r="W10">
-        <v>-4.3446729745936011E-3</v>
+        <v>-2.9981899491668632E-3</v>
       </c>
       <c r="X10">
-        <v>-3.8526909312896589E-3</v>
+        <v>-3.5677001716953229E-3</v>
       </c>
       <c r="Y10">
-        <v>-4.1173233469504866E-3</v>
+        <v>-3.2642754439391256E-3</v>
       </c>
       <c r="Z10">
-        <v>-4.2159131747568166E-3</v>
+        <v>-3.3970837117349752E-3</v>
       </c>
       <c r="AA10">
-        <v>-1.9920285372653553E-4</v>
+        <v>-3.6756824102319348E-3</v>
       </c>
       <c r="AB10">
-        <v>1.6683539035454997E-3</v>
+        <v>-1.7550987748494356E-4</v>
       </c>
       <c r="AC10">
-        <v>1.799138155826099E-3</v>
+        <v>1.4977359110327788E-3</v>
       </c>
       <c r="AD10">
-        <v>-1.4308554159745378E-3</v>
+        <v>1.6003908164010459E-3</v>
       </c>
       <c r="AE10">
-        <v>-2.6400607554612016E-2</v>
+        <v>-1.0716389002940457E-3</v>
       </c>
       <c r="AF10">
-        <v>9.9664910247423944E-5</v>
+        <v>-2.3012891822242615E-2</v>
       </c>
       <c r="AG10">
-        <v>-4.8559390173042824E-2</v>
+        <v>1.5910213733708414E-4</v>
+      </c>
+      <c r="AH10">
+        <v>-4.3683841851853228E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
       <c r="B11">
-        <v>7.965766736111915E-2</v>
+        <v>2.8451394660730704E-2</v>
       </c>
       <c r="C11">
-        <v>8.5837091857702153E-4</v>
+        <v>9.0288484663960961E-4</v>
       </c>
       <c r="D11">
-        <v>7.9290253031658042E-4</v>
+        <v>6.4345649072568289E-4</v>
       </c>
       <c r="E11">
-        <v>-6.8921236093451863E-6</v>
+        <v>-5.5134203656734358E-6</v>
       </c>
       <c r="F11">
-        <v>-8.4167026890158707E-4</v>
+        <v>-9.1475532328687444E-4</v>
       </c>
       <c r="G11">
-        <v>3.027597353444096E-4</v>
+        <v>1.9428022093635647E-4</v>
       </c>
       <c r="H11">
-        <v>1.7808183340123969E-5</v>
+        <v>3.6867309317916059E-5</v>
       </c>
       <c r="I11">
-        <v>-2.8914860261969192E-6</v>
+        <v>8.7601248456730427E-6</v>
       </c>
       <c r="J11">
-        <v>6.874547164757612E-4</v>
+        <v>5.1227277017757214E-4</v>
       </c>
       <c r="K11">
-        <v>6.8837298547032855E-3</v>
+        <v>5.7604126401509283E-3</v>
       </c>
       <c r="L11">
-        <v>8.0440947029702739E-3</v>
+        <v>7.7633369025684167E-3</v>
       </c>
       <c r="M11">
-        <v>8.8895333967106676E-3</v>
+        <v>8.6592270527424357E-3</v>
       </c>
       <c r="N11">
-        <v>9.2681386468210537E-3</v>
+        <v>8.9662336051276412E-3</v>
       </c>
       <c r="O11">
-        <v>8.7015639616387069E-3</v>
+        <v>8.3492232508674945E-3</v>
       </c>
       <c r="P11">
-        <v>-3.8874425462541162E-3</v>
+        <v>2.2169767499534924E-3</v>
       </c>
       <c r="Q11">
-        <v>-7.2729400040075463E-3</v>
+        <v>-3.7922967977838109E-3</v>
       </c>
       <c r="R11">
-        <v>-3.6228186469875641E-3</v>
+        <v>-7.0347615237210739E-3</v>
       </c>
       <c r="S11">
-        <v>-3.8096707095451499E-3</v>
+        <v>-3.5325438495137579E-3</v>
       </c>
       <c r="T11">
-        <v>-3.3811344895484713E-3</v>
+        <v>-3.6861165655699725E-3</v>
       </c>
       <c r="U11">
-        <v>-3.714072700124897E-3</v>
+        <v>-3.1419904966237693E-3</v>
       </c>
       <c r="V11">
-        <v>-3.6722029169836377E-3</v>
+        <v>-3.7019928347610791E-3</v>
       </c>
       <c r="W11">
-        <v>-4.0308586632102888E-3</v>
+        <v>-3.5903177546743417E-3</v>
       </c>
       <c r="X11">
-        <v>-3.4065799477767107E-3</v>
+        <v>-3.9154658742369692E-3</v>
       </c>
       <c r="Y11">
-        <v>-3.5820955082193949E-3</v>
+        <v>-4.3349079283260894E-3</v>
       </c>
       <c r="Z11">
-        <v>-4.2304159945557576E-3</v>
+        <v>-3.537215179007651E-3</v>
       </c>
       <c r="AA11">
-        <v>-1.074595178927465E-4</v>
+        <v>-4.3500593473219159E-3</v>
       </c>
       <c r="AB11">
-        <v>1.0702474008021938E-3</v>
+        <v>-1.1146434163181851E-4</v>
       </c>
       <c r="AC11">
-        <v>9.4787777384084879E-4</v>
+        <v>1.0611165636366837E-3</v>
       </c>
       <c r="AD11">
-        <v>-1.1636883847742333E-3</v>
+        <v>1.0713022314313625E-3</v>
       </c>
       <c r="AE11">
-        <v>-1.9642108806765698E-2</v>
+        <v>-8.0609434730715313E-4</v>
       </c>
       <c r="AF11">
-        <v>-7.5206142269688395E-4</v>
+        <v>-1.8745656618896937E-2</v>
       </c>
       <c r="AG11">
-        <v>-2.6759139423635836E-2</v>
+        <v>-5.813230327526989E-4</v>
+      </c>
+      <c r="AH11">
+        <v>-2.395457321193321E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
       <c r="B12">
-        <v>-6.9712826847403389E-2</v>
+        <v>-0.12103968477857449</v>
       </c>
       <c r="C12">
-        <v>1.2900300544420144E-3</v>
+        <v>1.3250295488772381E-3</v>
       </c>
       <c r="D12">
-        <v>1.3147163442918941E-3</v>
+        <v>1.0718837514020474E-3</v>
       </c>
       <c r="E12">
-        <v>-1.1383334336608538E-5</v>
+        <v>-9.2869777346749668E-6</v>
       </c>
       <c r="F12">
-        <v>-8.1504901635518455E-4</v>
+        <v>-8.9185098652038233E-4</v>
       </c>
       <c r="G12">
-        <v>8.8114849074720936E-4</v>
+        <v>7.0330448362312037E-4</v>
       </c>
       <c r="H12">
-        <v>1.1130001754841752E-5</v>
+        <v>4.0927434184745079E-5</v>
       </c>
       <c r="I12">
-        <v>-3.2275303898937602E-5</v>
+        <v>-1.6376100031404838E-5</v>
       </c>
       <c r="J12">
-        <v>1.4274956340256037E-3</v>
+        <v>1.2739867914771177E-3</v>
       </c>
       <c r="K12">
-        <v>1.2178261914374829E-2</v>
+        <v>1.0863971123695727E-2</v>
       </c>
       <c r="L12">
-        <v>8.8895333967106676E-3</v>
+        <v>8.6592270527424357E-3</v>
       </c>
       <c r="M12">
-        <v>1.6555021323809819E-2</v>
+        <v>1.6404586479712567E-2</v>
       </c>
       <c r="N12">
-        <v>1.5560662479698336E-2</v>
+        <v>1.533773300248129E-2</v>
       </c>
       <c r="O12">
-        <v>1.4933224927463906E-2</v>
+        <v>1.4636778525933189E-2</v>
       </c>
       <c r="P12">
-        <v>-5.4555096844083485E-3</v>
+        <v>3.1593158007567541E-3</v>
       </c>
       <c r="Q12">
-        <v>-1.0717510936478797E-2</v>
+        <v>-5.3692812060422276E-3</v>
       </c>
       <c r="R12">
-        <v>-4.679329242420505E-3</v>
+        <v>-1.046661258676139E-2</v>
       </c>
       <c r="S12">
-        <v>-4.9328575378142468E-3</v>
+        <v>-4.5519473304118409E-3</v>
       </c>
       <c r="T12">
-        <v>-4.3080910418072504E-3</v>
+        <v>-4.7847108127675626E-3</v>
       </c>
       <c r="U12">
-        <v>-4.7303335049112428E-3</v>
+        <v>-4.059728804706811E-3</v>
       </c>
       <c r="V12">
-        <v>-4.9461157777943767E-3</v>
+        <v>-4.7238888628090437E-3</v>
       </c>
       <c r="W12">
-        <v>-5.3556919770340978E-3</v>
+        <v>-4.8753050863960829E-3</v>
       </c>
       <c r="X12">
-        <v>-5.0207216703439276E-3</v>
+        <v>-5.2996114354346606E-3</v>
       </c>
       <c r="Y12">
-        <v>-4.9834125599568495E-3</v>
+        <v>-5.5920306680627817E-3</v>
       </c>
       <c r="Z12">
-        <v>-5.3705006152882694E-3</v>
+        <v>-5.0219655595727664E-3</v>
       </c>
       <c r="AA12">
-        <v>-2.3107525649534392E-4</v>
+        <v>-5.5601789479914118E-3</v>
       </c>
       <c r="AB12">
-        <v>1.9794935184048101E-3</v>
+        <v>-2.2765543498336639E-4</v>
       </c>
       <c r="AC12">
-        <v>2.1657223908163837E-3</v>
+        <v>1.9520336994573763E-3</v>
       </c>
       <c r="AD12">
-        <v>-1.3567753895332504E-3</v>
+        <v>2.2657873002475894E-3</v>
       </c>
       <c r="AE12">
-        <v>-3.0417872461514606E-2</v>
+        <v>-9.4644610922082128E-4</v>
       </c>
       <c r="AF12">
-        <v>-6.9739569540872774E-4</v>
+        <v>-2.96100317643683E-2</v>
       </c>
       <c r="AG12">
-        <v>-4.3243244715416261E-2</v>
+        <v>-6.0770265234587546E-4</v>
+      </c>
+      <c r="AH12">
+        <v>-3.8385164177546907E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
       <c r="B13">
-        <v>-3.5858338581839025E-2</v>
+        <v>-8.6933401140201844E-2</v>
       </c>
       <c r="C13">
-        <v>1.2001911197017743E-3</v>
+        <v>1.2281547617617608E-3</v>
       </c>
       <c r="D13">
-        <v>1.3681747687588619E-3</v>
+        <v>1.1135467301564839E-3</v>
       </c>
       <c r="E13">
-        <v>-1.1670821307777296E-5</v>
+        <v>-9.4716332493015656E-6</v>
       </c>
       <c r="F13">
-        <v>-7.3384821911865773E-4</v>
+        <v>-7.9710723232193689E-4</v>
       </c>
       <c r="G13">
-        <v>1.1420640723983548E-3</v>
+        <v>9.5772644286733948E-4</v>
       </c>
       <c r="H13">
-        <v>1.712493516734491E-5</v>
+        <v>4.8373808550933447E-5</v>
       </c>
       <c r="I13">
-        <v>-3.5271350365229147E-5</v>
+        <v>-1.8539937469083841E-5</v>
       </c>
       <c r="J13">
-        <v>1.4792926408807514E-3</v>
+        <v>1.3236039865338334E-3</v>
       </c>
       <c r="K13">
-        <v>1.3015407752700672E-2</v>
+        <v>1.1601086686978415E-2</v>
       </c>
       <c r="L13">
-        <v>9.2681386468210537E-3</v>
+        <v>8.9662336051276412E-3</v>
       </c>
       <c r="M13">
-        <v>1.5560662479698336E-2</v>
+        <v>1.533773300248129E-2</v>
       </c>
       <c r="N13">
-        <v>1.7961279227949829E-2</v>
+        <v>1.7663312953374727E-2</v>
       </c>
       <c r="O13">
-        <v>1.5864864134963737E-2</v>
+        <v>1.5494420968188458E-2</v>
       </c>
       <c r="P13">
-        <v>-5.184852627421908E-3</v>
+        <v>3.305966189111539E-3</v>
       </c>
       <c r="Q13">
-        <v>-1.0993558988938249E-2</v>
+        <v>-5.057688838449992E-3</v>
       </c>
       <c r="R13">
-        <v>-4.6234670616553649E-3</v>
+        <v>-1.0673664857550927E-2</v>
       </c>
       <c r="S13">
-        <v>-4.9167415992928277E-3</v>
+        <v>-4.4475481501744848E-3</v>
       </c>
       <c r="T13">
-        <v>-4.2966160454700041E-3</v>
+        <v>-4.7299971134465895E-3</v>
       </c>
       <c r="U13">
-        <v>-4.5044900941965567E-3</v>
+        <v>-3.9881390170579331E-3</v>
       </c>
       <c r="V13">
-        <v>-4.6273659428022109E-3</v>
+        <v>-4.4574516045913668E-3</v>
       </c>
       <c r="W13">
-        <v>-5.3923067757059209E-3</v>
+        <v>-4.514258930512537E-3</v>
       </c>
       <c r="X13">
-        <v>-5.200732198768588E-3</v>
+        <v>-5.2913952164593894E-3</v>
       </c>
       <c r="Y13">
-        <v>-5.1296432830864021E-3</v>
+        <v>-5.7502873012921923E-3</v>
       </c>
       <c r="Z13">
-        <v>-5.2866858818126604E-3</v>
+        <v>-5.1083952405022014E-3</v>
       </c>
       <c r="AA13">
-        <v>-2.6744267304573493E-4</v>
+        <v>-5.4517739974620531E-3</v>
       </c>
       <c r="AB13">
-        <v>2.1883072746697345E-3</v>
+        <v>-2.618728405212223E-4</v>
       </c>
       <c r="AC13">
-        <v>2.2131246297581765E-3</v>
+        <v>2.1527184877529054E-3</v>
       </c>
       <c r="AD13">
-        <v>-1.3194456368283824E-3</v>
+        <v>2.3035551953170369E-3</v>
       </c>
       <c r="AE13">
-        <v>-3.2457778339151477E-2</v>
+        <v>-8.8548406727380433E-4</v>
       </c>
       <c r="AF13">
-        <v>-3.914461380713503E-4</v>
+        <v>-3.1494487695220195E-2</v>
       </c>
       <c r="AG13">
-        <v>-4.5943529534406183E-2</v>
+        <v>-3.2206269985366528E-4</v>
+      </c>
+      <c r="AH13">
+        <v>-4.0875373753253452E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14">
-        <v>0.11769271016307731</v>
+        <v>7.1806344092416957E-2</v>
       </c>
       <c r="C14">
-        <v>8.2869379774168361E-4</v>
+        <v>8.4259762382982335E-4</v>
       </c>
       <c r="D14">
-        <v>1.382434796031895E-3</v>
+        <v>1.1566480569527304E-3</v>
       </c>
       <c r="E14">
-        <v>-1.1702835394568779E-5</v>
+        <v>-9.7391856389795941E-6</v>
       </c>
       <c r="F14">
-        <v>-1.9938872968201012E-4</v>
+        <v>-2.4862275678907801E-4</v>
       </c>
       <c r="G14">
-        <v>1.5872714192021516E-3</v>
+        <v>1.4255193190902409E-3</v>
       </c>
       <c r="H14">
-        <v>3.6903238796955106E-6</v>
+        <v>3.0899879443307596E-5</v>
       </c>
       <c r="I14">
-        <v>-3.7922185349196298E-5</v>
+        <v>-2.3080870424543073E-5</v>
       </c>
       <c r="J14">
-        <v>1.5102726871854197E-3</v>
+        <v>1.3641492843854963E-3</v>
       </c>
       <c r="K14">
-        <v>1.2444772222525595E-2</v>
+        <v>1.1114250693718464E-2</v>
       </c>
       <c r="L14">
-        <v>8.7015639616387069E-3</v>
+        <v>8.3492232508674945E-3</v>
       </c>
       <c r="M14">
-        <v>1.4933224927463906E-2</v>
+        <v>1.4636778525933189E-2</v>
       </c>
       <c r="N14">
-        <v>1.5864864134963737E-2</v>
+        <v>1.5494420968188458E-2</v>
       </c>
       <c r="O14">
-        <v>1.7043281075086174E-2</v>
+        <v>1.6623732836505783E-2</v>
       </c>
       <c r="P14">
-        <v>-4.2919224462834374E-3</v>
+        <v>2.928144508149916E-3</v>
       </c>
       <c r="Q14">
-        <v>-9.4637937938716679E-3</v>
+        <v>-4.1264179213633071E-3</v>
       </c>
       <c r="R14">
-        <v>-3.8020202954637964E-3</v>
+        <v>-9.0995353536426557E-3</v>
       </c>
       <c r="S14">
-        <v>-3.7311523689233473E-3</v>
+        <v>-3.6051530573617619E-3</v>
       </c>
       <c r="T14">
-        <v>-3.5210314038118468E-3</v>
+        <v>-3.5220052793531699E-3</v>
       </c>
       <c r="U14">
-        <v>-3.9206065626019434E-3</v>
+        <v>-3.1908988432254853E-3</v>
       </c>
       <c r="V14">
-        <v>-3.9127517928091134E-3</v>
+        <v>-3.839149536404826E-3</v>
       </c>
       <c r="W14">
-        <v>-4.3384243174606086E-3</v>
+        <v>-3.7669760566994247E-3</v>
       </c>
       <c r="X14">
-        <v>-4.0628496490863883E-3</v>
+        <v>-4.1907259684440127E-3</v>
       </c>
       <c r="Y14">
-        <v>-4.1234114179733499E-3</v>
+        <v>-4.5787047585511024E-3</v>
       </c>
       <c r="Z14">
-        <v>-4.4392508360602814E-3</v>
+        <v>-4.0582972497101187E-3</v>
       </c>
       <c r="AA14">
-        <v>-2.673858631659508E-4</v>
+        <v>-4.5411369201331262E-3</v>
       </c>
       <c r="AB14">
-        <v>2.0603173676225642E-3</v>
+        <v>-2.6257544479177559E-4</v>
       </c>
       <c r="AC14">
-        <v>2.2106665824762166E-3</v>
+        <v>2.0250686858169697E-3</v>
       </c>
       <c r="AD14">
-        <v>-1.0440905161043512E-3</v>
+        <v>2.286023926794215E-3</v>
       </c>
       <c r="AE14">
-        <v>-2.9370391907755471E-2</v>
+        <v>-6.2362190477473038E-4</v>
       </c>
       <c r="AF14">
-        <v>-3.7512420324248784E-5</v>
+        <v>-2.8292654847919776E-2</v>
       </c>
       <c r="AG14">
-        <v>-4.6554219087351779E-2</v>
+        <v>5.7604530648233741E-5</v>
+      </c>
+      <c r="AH14">
+        <v>-4.2031837352031018E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
       <c r="B15">
-        <v>0.19340950339909446</v>
+        <v>-0.18762278415367012</v>
       </c>
       <c r="C15">
-        <v>-1.2233281710598847E-3</v>
+        <v>4.6022563817849928E-4</v>
       </c>
       <c r="D15">
-        <v>-2.5452365097821533E-4</v>
+        <v>-4.5181916970053748E-5</v>
       </c>
       <c r="E15">
-        <v>2.4958791329438338E-6</v>
+        <v>5.4810385649985225E-7</v>
       </c>
       <c r="F15">
-        <v>5.1887731768539627E-4</v>
+        <v>-5.9694186046919278E-4</v>
       </c>
       <c r="G15">
-        <v>-4.7335207487223229E-4</v>
+        <v>-2.3409187487754516E-4</v>
       </c>
       <c r="H15">
-        <v>-2.718762959967358E-5</v>
+        <v>5.6913455526318328E-5</v>
       </c>
       <c r="I15">
-        <v>-4.5331145470412643E-7</v>
+        <v>1.7411794912582793E-5</v>
       </c>
       <c r="J15">
-        <v>-6.6538359264779572E-4</v>
+        <v>-4.2574892420049401E-5</v>
       </c>
       <c r="K15">
-        <v>-4.0237574286098293E-3</v>
+        <v>8.9733520833347805E-4</v>
       </c>
       <c r="L15">
-        <v>-3.8874425462541162E-3</v>
+        <v>2.2169767499534924E-3</v>
       </c>
       <c r="M15">
-        <v>-5.4555096844083485E-3</v>
+        <v>3.1593158007567541E-3</v>
       </c>
       <c r="N15">
-        <v>-5.184852627421908E-3</v>
+        <v>3.305966189111539E-3</v>
       </c>
       <c r="O15">
-        <v>-4.2919224462834374E-3</v>
+        <v>2.928144508149916E-3</v>
       </c>
       <c r="P15">
-        <v>1.4776860521115619E-2</v>
+        <v>4.7118677910617949E-3</v>
       </c>
       <c r="Q15">
-        <v>1.1859096373737677E-2</v>
+        <v>-1.6359936810738662E-3</v>
       </c>
       <c r="R15">
-        <v>8.3496293791602404E-3</v>
+        <v>-3.2576237087906437E-3</v>
       </c>
       <c r="S15">
-        <v>8.7569853537532924E-3</v>
+        <v>-1.7255157161549018E-3</v>
       </c>
       <c r="T15">
-        <v>8.038594606426204E-3</v>
+        <v>-1.5830818545107274E-3</v>
       </c>
       <c r="U15">
-        <v>8.449647861603439E-3</v>
+        <v>-1.6338551722658154E-3</v>
       </c>
       <c r="V15">
-        <v>8.6079175015634224E-3</v>
+        <v>-1.7874723196066658E-3</v>
       </c>
       <c r="W15">
-        <v>8.9659041556467162E-3</v>
+        <v>-1.7384855818228101E-3</v>
       </c>
       <c r="X15">
-        <v>8.8312212180462705E-3</v>
+        <v>-2.0597582019736002E-3</v>
       </c>
       <c r="Y15">
-        <v>8.8913709929233121E-3</v>
+        <v>-2.3822228603555392E-3</v>
       </c>
       <c r="Z15">
-        <v>8.7845481905285405E-3</v>
+        <v>-1.9970491317217887E-3</v>
       </c>
       <c r="AA15">
-        <v>4.7919588673756659E-5</v>
+        <v>-1.9425962295622655E-3</v>
       </c>
       <c r="AB15">
-        <v>-8.9108422950021733E-4</v>
+        <v>-5.0213194636763644E-5</v>
       </c>
       <c r="AC15">
-        <v>-3.5370452681470366E-4</v>
+        <v>3.5799640924950122E-4</v>
       </c>
       <c r="AD15">
-        <v>3.1720525237311967E-3</v>
+        <v>7.6072760382328878E-4</v>
       </c>
       <c r="AE15">
-        <v>2.1677627377857715E-2</v>
+        <v>-1.6763241602153365E-4</v>
       </c>
       <c r="AF15">
-        <v>1.9638515595310161E-3</v>
+        <v>-8.1961209053173986E-3</v>
       </c>
       <c r="AG15">
-        <v>3.338129410986334E-3</v>
+        <v>-2.6916640561097389E-4</v>
+      </c>
+      <c r="AH15">
+        <v>-3.295598795347663E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
       <c r="B16">
-        <v>0.22455914010404779</v>
+        <v>0.19698774762245419</v>
       </c>
       <c r="C16">
-        <v>-1.7886914694781693E-3</v>
+        <v>-1.1962979631865182E-3</v>
       </c>
       <c r="D16">
-        <v>-6.662161043312631E-4</v>
+        <v>-1.1816482201765927E-4</v>
       </c>
       <c r="E16">
-        <v>5.8082981427749498E-6</v>
+        <v>1.3755914342857348E-6</v>
       </c>
       <c r="F16">
-        <v>1.2699363874003789E-3</v>
+        <v>5.2160182075045307E-4</v>
       </c>
       <c r="G16">
-        <v>-5.5018871178856912E-4</v>
+        <v>-3.5261815585580435E-4</v>
       </c>
       <c r="H16">
-        <v>-4.672831012788117E-5</v>
+        <v>-4.456480910833868E-5</v>
       </c>
       <c r="I16">
-        <v>9.4797271601292652E-6</v>
+        <v>-8.7508313021763976E-6</v>
       </c>
       <c r="J16">
-        <v>-1.1070492165856996E-3</v>
+        <v>-6.2487208335253175E-4</v>
       </c>
       <c r="K16">
-        <v>-8.6041245913911144E-3</v>
+        <v>-3.3889858531435859E-3</v>
       </c>
       <c r="L16">
-        <v>-7.2729400040075463E-3</v>
+        <v>-3.7922967977838109E-3</v>
       </c>
       <c r="M16">
-        <v>-1.0717510936478797E-2</v>
+        <v>-5.3692812060422276E-3</v>
       </c>
       <c r="N16">
-        <v>-1.0993558988938249E-2</v>
+        <v>-5.057688838449992E-3</v>
       </c>
       <c r="O16">
-        <v>-9.4637937938716679E-3</v>
+        <v>-4.1264179213633071E-3</v>
       </c>
       <c r="P16">
-        <v>1.1859096373737677E-2</v>
+        <v>-1.6359936810738662E-3</v>
       </c>
       <c r="Q16">
-        <v>2.0075300184704829E-2</v>
+        <v>1.4795926376961081E-2</v>
       </c>
       <c r="R16">
-        <v>1.1023533051510076E-2</v>
+        <v>1.1694605726966333E-2</v>
       </c>
       <c r="S16">
-        <v>1.1599622840432203E-2</v>
+        <v>8.2687981207548548E-3</v>
       </c>
       <c r="T16">
-        <v>1.0619588671516658E-2</v>
+        <v>8.6896355105272535E-3</v>
       </c>
       <c r="U16">
-        <v>1.1259232276866036E-2</v>
+        <v>7.9193739251977938E-3</v>
       </c>
       <c r="V16">
-        <v>1.1472395480892687E-2</v>
+        <v>8.4270570043335422E-3</v>
       </c>
       <c r="W16">
-        <v>1.2158826781762014E-2</v>
+        <v>8.5656369503609893E-3</v>
       </c>
       <c r="X16">
-        <v>1.2043049927135962E-2</v>
+        <v>8.9361848538632334E-3</v>
       </c>
       <c r="Y16">
-        <v>1.1897830493365527E-2</v>
+        <v>8.7353587247081983E-3</v>
       </c>
       <c r="Z16">
-        <v>1.1852900763123194E-2</v>
+        <v>8.9011675442085686E-3</v>
       </c>
       <c r="AA16">
-        <v>1.9170095709306533E-4</v>
+        <v>8.8881633414782009E-3</v>
       </c>
       <c r="AB16">
-        <v>-2.0489017586479991E-3</v>
+        <v>3.6811564240966325E-5</v>
       </c>
       <c r="AC16">
-        <v>-1.5835801456500001E-3</v>
+        <v>-8.4449452163280498E-4</v>
       </c>
       <c r="AD16">
-        <v>3.7641901911124776E-3</v>
+        <v>-3.3495061717894173E-4</v>
       </c>
       <c r="AE16">
-        <v>3.889245571963177E-2</v>
+        <v>2.998099777251512E-3</v>
       </c>
       <c r="AF16">
-        <v>2.0770292141523345E-3</v>
+        <v>2.1124708326911337E-2</v>
       </c>
       <c r="AG16">
-        <v>1.6429117687213685E-2</v>
+        <v>1.9852435422809279E-3</v>
+      </c>
+      <c r="AH16">
+        <v>5.7757262032454536E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17">
-        <v>0.10868540669643754</v>
+        <v>0.22805073885464278</v>
       </c>
       <c r="C17">
-        <v>-1.0335151182635934E-3</v>
+        <v>-1.7249994550706388E-3</v>
       </c>
       <c r="D17">
-        <v>-3.4584808216091278E-4</v>
+        <v>-3.831810565506355E-4</v>
       </c>
       <c r="E17">
-        <v>2.9752199325502578E-6</v>
+        <v>3.4887530264951679E-6</v>
       </c>
       <c r="F17">
-        <v>9.8503390927221412E-4</v>
+        <v>1.2372529205743592E-3</v>
       </c>
       <c r="G17">
-        <v>1.2464521832511411E-4</v>
+        <v>-3.6858311537051741E-4</v>
       </c>
       <c r="H17">
-        <v>-1.8651755787865514E-5</v>
+        <v>-7.9106318668780936E-5</v>
       </c>
       <c r="I17">
-        <v>1.5956673036758725E-7</v>
+        <v>-7.6880857549925692E-6</v>
       </c>
       <c r="J17">
-        <v>-1.0152303274702651E-4</v>
+        <v>-1.022824043948406E-3</v>
       </c>
       <c r="K17">
-        <v>-3.676652672805987E-3</v>
+        <v>-7.2776146401295483E-3</v>
       </c>
       <c r="L17">
-        <v>-3.6228186469875641E-3</v>
+        <v>-7.0347615237210739E-3</v>
       </c>
       <c r="M17">
-        <v>-4.679329242420505E-3</v>
+        <v>-1.046661258676139E-2</v>
       </c>
       <c r="N17">
-        <v>-4.6234670616553649E-3</v>
+        <v>-1.0673664857550927E-2</v>
       </c>
       <c r="O17">
-        <v>-3.8020202954637964E-3</v>
+        <v>-9.0995353536426557E-3</v>
       </c>
       <c r="P17">
-        <v>8.3496293791602404E-3</v>
+        <v>-3.2576237087906437E-3</v>
       </c>
       <c r="Q17">
-        <v>1.1023533051510076E-2</v>
+        <v>1.1694605726966333E-2</v>
       </c>
       <c r="R17">
-        <v>1.202078038001274E-2</v>
+        <v>1.9616462856900718E-2</v>
       </c>
       <c r="S17">
-        <v>8.2614981207509864E-3</v>
+        <v>1.0774585926933908E-2</v>
       </c>
       <c r="T17">
-        <v>7.646538112092976E-3</v>
+        <v>1.1380644365670715E-2</v>
       </c>
       <c r="U17">
-        <v>7.9793029745638244E-3</v>
+        <v>1.0304424601994863E-2</v>
       </c>
       <c r="V17">
-        <v>8.1492078914163543E-3</v>
+        <v>1.1121274118219929E-2</v>
       </c>
       <c r="W17">
-        <v>8.4659757639627426E-3</v>
+        <v>1.1302039385243519E-2</v>
       </c>
       <c r="X17">
-        <v>8.3391998345296453E-3</v>
+        <v>1.2003379509488852E-2</v>
       </c>
       <c r="Y17">
-        <v>8.3818503564281367E-3</v>
+        <v>1.1746470179013663E-2</v>
       </c>
       <c r="Z17">
-        <v>8.301971266248289E-3</v>
+        <v>1.1824137522899696E-2</v>
       </c>
       <c r="AA17">
-        <v>3.8762887797803933E-5</v>
+        <v>1.1978780344448478E-2</v>
       </c>
       <c r="AB17">
-        <v>-6.1942189544886153E-4</v>
+        <v>1.68478734443489E-4</v>
       </c>
       <c r="AC17">
-        <v>4.3792518407068104E-6</v>
+        <v>-1.9620267190770891E-3</v>
       </c>
       <c r="AD17">
-        <v>3.0414862896871427E-3</v>
+        <v>-1.5130642250818314E-3</v>
       </c>
       <c r="AE17">
-        <v>1.9511588873023136E-2</v>
+        <v>3.402725814964641E-3</v>
       </c>
       <c r="AF17">
-        <v>1.8221175893846067E-3</v>
+        <v>3.7511099710748383E-2</v>
       </c>
       <c r="AG17">
-        <v>6.1376912365996884E-3</v>
+        <v>2.1441458265871009E-3</v>
+      </c>
+      <c r="AH17">
+        <v>1.0569391465693316E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
       <c r="B18">
-        <v>0.17340089641793152</v>
+        <v>0.11152563747469367</v>
       </c>
       <c r="C18">
-        <v>-1.3260660839624072E-3</v>
+        <v>-1.0098658170196145E-3</v>
       </c>
       <c r="D18">
-        <v>-3.4009777578406647E-4</v>
+        <v>-1.9572465689284696E-4</v>
       </c>
       <c r="E18">
-        <v>3.0537331985594691E-6</v>
+        <v>1.7434568931532076E-6</v>
       </c>
       <c r="F18">
-        <v>6.3139373180038337E-4</v>
+        <v>9.6536709390601379E-4</v>
       </c>
       <c r="G18">
-        <v>-4.3163068994972275E-4</v>
+        <v>2.3344663094671198E-4</v>
       </c>
       <c r="H18">
-        <v>-2.7854091270386168E-5</v>
+        <v>-3.6095755063872984E-5</v>
       </c>
       <c r="I18">
-        <v>-9.782801193795182E-6</v>
+        <v>-8.1507726445603464E-6</v>
       </c>
       <c r="J18">
-        <v>-4.1836174668378502E-4</v>
+        <v>-6.2550295880437964E-5</v>
       </c>
       <c r="K18">
-        <v>-3.8296164986273504E-3</v>
+        <v>-2.961073702059917E-3</v>
       </c>
       <c r="L18">
-        <v>-3.8096707095451499E-3</v>
+        <v>-3.5325438495137579E-3</v>
       </c>
       <c r="M18">
-        <v>-4.9328575378142468E-3</v>
+        <v>-4.5519473304118409E-3</v>
       </c>
       <c r="N18">
-        <v>-4.9167415992928277E-3</v>
+        <v>-4.4475481501744848E-3</v>
       </c>
       <c r="O18">
-        <v>-3.7311523689233473E-3</v>
+        <v>-3.6051530573617619E-3</v>
       </c>
       <c r="P18">
-        <v>8.7569853537532924E-3</v>
+        <v>-1.7255157161549018E-3</v>
       </c>
       <c r="Q18">
-        <v>1.1599622840432203E-2</v>
+        <v>8.2687981207548548E-3</v>
       </c>
       <c r="R18">
-        <v>8.2614981207509864E-3</v>
+        <v>1.0774585926933908E-2</v>
       </c>
       <c r="S18">
-        <v>1.3083079240887628E-2</v>
+        <v>1.1881568104196241E-2</v>
       </c>
       <c r="T18">
-        <v>7.9865439479235023E-3</v>
+        <v>8.1553250436779794E-3</v>
       </c>
       <c r="U18">
-        <v>8.36722036905415E-3</v>
+        <v>7.501957610869167E-3</v>
       </c>
       <c r="V18">
-        <v>8.4962555306594863E-3</v>
+        <v>7.9164273085490719E-3</v>
       </c>
       <c r="W18">
-        <v>8.8797626294748223E-3</v>
+        <v>8.0735440514472755E-3</v>
       </c>
       <c r="X18">
-        <v>8.7961366283874371E-3</v>
+        <v>8.3979663932517313E-3</v>
       </c>
       <c r="Y18">
-        <v>8.8216177097435837E-3</v>
+        <v>8.1879396998947498E-3</v>
       </c>
       <c r="Z18">
-        <v>8.7780538513003784E-3</v>
+        <v>8.3577163916679041E-3</v>
       </c>
       <c r="AA18">
-        <v>6.022742599666453E-5</v>
+        <v>8.3673817095162792E-3</v>
       </c>
       <c r="AB18">
-        <v>-9.0885703377686488E-4</v>
+        <v>2.4418778485373288E-5</v>
       </c>
       <c r="AC18">
-        <v>-7.7941806223789803E-4</v>
+        <v>-5.6363391535268733E-4</v>
       </c>
       <c r="AD18">
-        <v>2.9166716340068921E-3</v>
+        <v>5.3193134213101127E-5</v>
       </c>
       <c r="AE18">
-        <v>2.0825724945639321E-2</v>
+        <v>2.8383210788795969E-3</v>
       </c>
       <c r="AF18">
-        <v>2.0553852271110993E-3</v>
+        <v>1.8700860631329752E-2</v>
       </c>
       <c r="AG18">
-        <v>6.4040874724277455E-3</v>
+        <v>1.8650394986656469E-3</v>
+      </c>
+      <c r="AH18">
+        <v>3.0383480951124957E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
       <c r="B19">
-        <v>5.5377272679262131E-2</v>
+        <v>0.17601143356572374</v>
       </c>
       <c r="C19">
-        <v>-9.1612746393551878E-4</v>
+        <v>-1.2912129871671943E-3</v>
       </c>
       <c r="D19">
-        <v>-2.1232156514588985E-4</v>
+        <v>-1.9034775348235333E-4</v>
       </c>
       <c r="E19">
-        <v>1.9175745964290195E-6</v>
+        <v>1.8233501463745406E-6</v>
       </c>
       <c r="F19">
-        <v>5.592323839378765E-4</v>
+        <v>6.1468788242573041E-4</v>
       </c>
       <c r="G19">
-        <v>-2.1485989856697264E-4</v>
+        <v>-3.2922110499106129E-4</v>
       </c>
       <c r="H19">
-        <v>-2.1884429142721612E-5</v>
+        <v>-4.3486761779856396E-5</v>
       </c>
       <c r="I19">
-        <v>-4.0409964735373604E-6</v>
+        <v>-1.7970912302829817E-5</v>
       </c>
       <c r="J19">
-        <v>-2.1189609882152176E-4</v>
+        <v>-3.7698572746154915E-4</v>
       </c>
       <c r="K19">
-        <v>-3.063598227655992E-3</v>
+        <v>-3.1563411674357059E-3</v>
       </c>
       <c r="L19">
-        <v>-3.3811344895484713E-3</v>
+        <v>-3.6861165655699725E-3</v>
       </c>
       <c r="M19">
-        <v>-4.3080910418072504E-3</v>
+        <v>-4.7847108127675626E-3</v>
       </c>
       <c r="N19">
-        <v>-4.2966160454700041E-3</v>
+        <v>-4.7299971134465895E-3</v>
       </c>
       <c r="O19">
-        <v>-3.5210314038118468E-3</v>
+        <v>-3.5220052793531699E-3</v>
       </c>
       <c r="P19">
-        <v>8.038594606426204E-3</v>
+        <v>-1.5830818545107274E-3</v>
       </c>
       <c r="Q19">
-        <v>1.0619588671516658E-2</v>
+        <v>8.6896355105272535E-3</v>
       </c>
       <c r="R19">
-        <v>7.646538112092976E-3</v>
+        <v>1.1380644365670715E-2</v>
       </c>
       <c r="S19">
-        <v>7.9865439479235023E-3</v>
+        <v>8.1553250436779794E-3</v>
       </c>
       <c r="T19">
-        <v>1.2049964060536371E-2</v>
+        <v>1.3004569773679191E-2</v>
       </c>
       <c r="U19">
-        <v>7.7439224351798525E-3</v>
+        <v>7.8526991065535727E-3</v>
       </c>
       <c r="V19">
-        <v>7.8791461227362934E-3</v>
+        <v>8.3145386251203997E-3</v>
       </c>
       <c r="W19">
-        <v>8.1984899575322789E-3</v>
+        <v>8.4253661993553865E-3</v>
       </c>
       <c r="X19">
-        <v>8.0690931114370083E-3</v>
+        <v>8.8185141425060724E-3</v>
       </c>
       <c r="Y19">
-        <v>8.0924982881819905E-3</v>
+        <v>8.6643359612591161E-3</v>
       </c>
       <c r="Z19">
-        <v>8.0000303359190894E-3</v>
+        <v>8.79542087200786E-3</v>
       </c>
       <c r="AA19">
-        <v>4.7347293135733453E-5</v>
+        <v>8.8512476215022763E-3</v>
       </c>
       <c r="AB19">
-        <v>-4.5628703044999159E-4</v>
+        <v>4.7296629706502493E-5</v>
       </c>
       <c r="AC19">
-        <v>-4.9872464845018361E-4</v>
+        <v>-8.4825251593716351E-4</v>
       </c>
       <c r="AD19">
-        <v>2.4124165522326317E-3</v>
+        <v>-7.499778912280204E-4</v>
       </c>
       <c r="AE19">
-        <v>1.8355011732366294E-2</v>
+        <v>2.7306670682286766E-3</v>
       </c>
       <c r="AF19">
-        <v>1.4284099483168799E-3</v>
+        <v>2.0116015181737626E-2</v>
       </c>
       <c r="AG19">
-        <v>2.2933291803295935E-3</v>
+        <v>2.0767754272771732E-3</v>
+      </c>
+      <c r="AH19">
+        <v>3.1677299623392927E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
       <c r="B20">
-        <v>0.19260583946726226</v>
+        <v>5.640807030642752E-2</v>
       </c>
       <c r="C20">
-        <v>-1.002835754993919E-3</v>
+        <v>-9.0383631110555786E-4</v>
       </c>
       <c r="D20">
-        <v>-2.9349470368298519E-4</v>
+        <v>-4.9112849408235182E-5</v>
       </c>
       <c r="E20">
-        <v>2.5995227511202705E-6</v>
+        <v>5.9983265515955574E-7</v>
       </c>
       <c r="F20">
-        <v>6.3195200225049089E-4</v>
+        <v>5.3857973051496771E-4</v>
       </c>
       <c r="G20">
-        <v>-2.5107716659964635E-4</v>
+        <v>-1.0398223168221114E-4</v>
       </c>
       <c r="H20">
-        <v>-2.7446273931177689E-5</v>
+        <v>-3.9288734670354209E-5</v>
       </c>
       <c r="I20">
-        <v>-7.5704114754820886E-6</v>
+        <v>-1.2598474277910297E-5</v>
       </c>
       <c r="J20">
-        <v>-2.7638603269917669E-4</v>
+        <v>-1.9525169348198236E-4</v>
       </c>
       <c r="K20">
-        <v>-3.6205127910413637E-3</v>
+        <v>-2.3086834048780466E-3</v>
       </c>
       <c r="L20">
-        <v>-3.714072700124897E-3</v>
+        <v>-3.1419904966237693E-3</v>
       </c>
       <c r="M20">
-        <v>-4.7303335049112428E-3</v>
+        <v>-4.059728804706811E-3</v>
       </c>
       <c r="N20">
-        <v>-4.5044900941965567E-3</v>
+        <v>-3.9881390170579331E-3</v>
       </c>
       <c r="O20">
-        <v>-3.9206065626019434E-3</v>
+        <v>-3.1908988432254853E-3</v>
       </c>
       <c r="P20">
-        <v>8.449647861603439E-3</v>
+        <v>-1.6338551722658154E-3</v>
       </c>
       <c r="Q20">
-        <v>1.1259232276866036E-2</v>
+        <v>7.9193739251977938E-3</v>
       </c>
       <c r="R20">
-        <v>7.9793029745638244E-3</v>
+        <v>1.0304424601994863E-2</v>
       </c>
       <c r="S20">
-        <v>8.36722036905415E-3</v>
+        <v>7.501957610869167E-3</v>
       </c>
       <c r="T20">
-        <v>7.7439224351798525E-3</v>
+        <v>7.8526991065535727E-3</v>
       </c>
       <c r="U20">
-        <v>1.151413364982309E-2</v>
+        <v>1.1871212027320083E-2</v>
       </c>
       <c r="V20">
-        <v>8.2468430151574623E-3</v>
+        <v>7.6458943084773013E-3</v>
       </c>
       <c r="W20">
-        <v>8.5590423331899368E-3</v>
+        <v>7.761572282628075E-3</v>
       </c>
       <c r="X20">
-        <v>8.4802216094199429E-3</v>
+        <v>8.0850015595935569E-3</v>
       </c>
       <c r="Y20">
-        <v>8.501518662253283E-3</v>
+        <v>7.9164536546233941E-3</v>
       </c>
       <c r="Z20">
-        <v>8.4802736448037451E-3</v>
+        <v>8.0263983820675049E-3</v>
       </c>
       <c r="AA20">
-        <v>6.203703919191385E-5</v>
+        <v>8.0286788057417624E-3</v>
       </c>
       <c r="AB20">
-        <v>-8.0607745343635453E-4</v>
+        <v>3.006751857983559E-5</v>
       </c>
       <c r="AC20">
-        <v>-2.9369524101501964E-4</v>
+        <v>-4.2458332584364078E-4</v>
       </c>
       <c r="AD20">
-        <v>2.7871885157924308E-3</v>
+        <v>-4.2540833475863092E-4</v>
       </c>
       <c r="AE20">
-        <v>2.0132366994540657E-2</v>
+        <v>2.2205062230388028E-3</v>
       </c>
       <c r="AF20">
-        <v>1.8028610640400352E-3</v>
+        <v>1.7374656907640351E-2</v>
       </c>
       <c r="AG20">
-        <v>4.957296887954047E-3</v>
+        <v>1.4660282419467409E-3</v>
+      </c>
+      <c r="AH20">
+        <v>-1.3047319719277049E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21">
-        <v>4.205946980044057E-2</v>
+        <v>0.19847671536447317</v>
       </c>
       <c r="C21">
-        <v>-1.106436525403166E-3</v>
+        <v>-9.847330591255081E-4</v>
       </c>
       <c r="D21">
-        <v>-1.8292428886903384E-4</v>
+        <v>-1.4534294324750063E-4</v>
       </c>
       <c r="E21">
-        <v>1.8568465652505218E-6</v>
+        <v>1.3867467653997647E-6</v>
       </c>
       <c r="F21">
-        <v>9.3353938661150273E-4</v>
+        <v>6.3533371820659388E-4</v>
       </c>
       <c r="G21">
-        <v>-1.8032816322024071E-4</v>
+        <v>-1.2764322120737629E-4</v>
       </c>
       <c r="H21">
-        <v>-2.1883421649596959E-5</v>
+        <v>-4.5478000587014568E-5</v>
       </c>
       <c r="I21">
-        <v>-6.1460110473547679E-6</v>
+        <v>-1.6524366834896165E-5</v>
       </c>
       <c r="J21">
-        <v>-7.3931961400957626E-4</v>
+        <v>-2.3339764858111046E-4</v>
       </c>
       <c r="K21">
-        <v>-3.6843246532049078E-3</v>
+        <v>-2.9730178334474965E-3</v>
       </c>
       <c r="L21">
-        <v>-3.6722029169836377E-3</v>
+        <v>-3.7019928347610791E-3</v>
       </c>
       <c r="M21">
-        <v>-4.9461157777943767E-3</v>
+        <v>-4.7238888628090437E-3</v>
       </c>
       <c r="N21">
-        <v>-4.6273659428022109E-3</v>
+        <v>-4.4574516045913668E-3</v>
       </c>
       <c r="O21">
-        <v>-3.9127517928091134E-3</v>
+        <v>-3.839149536404826E-3</v>
       </c>
       <c r="P21">
-        <v>8.6079175015634224E-3</v>
+        <v>-1.7874723196066658E-3</v>
       </c>
       <c r="Q21">
-        <v>1.1472395480892687E-2</v>
+        <v>8.4270570043335422E-3</v>
       </c>
       <c r="R21">
-        <v>8.1492078914163543E-3</v>
+        <v>1.1121274118219929E-2</v>
       </c>
       <c r="S21">
-        <v>8.4962555306594863E-3</v>
+        <v>7.9164273085490719E-3</v>
       </c>
       <c r="T21">
-        <v>7.8791461227362934E-3</v>
+        <v>8.3145386251203997E-3</v>
       </c>
       <c r="U21">
-        <v>8.2468430151574623E-3</v>
+        <v>7.6458943084773013E-3</v>
       </c>
       <c r="V21">
-        <v>1.0873262726504861E-2</v>
+        <v>1.1517597633306774E-2</v>
       </c>
       <c r="W21">
-        <v>8.7421471477505449E-3</v>
+        <v>8.2248316720800897E-3</v>
       </c>
       <c r="X21">
-        <v>8.6191367696619135E-3</v>
+        <v>8.5524533918958472E-3</v>
       </c>
       <c r="Y21">
-        <v>8.6452632750799695E-3</v>
+        <v>8.4348368264062206E-3</v>
       </c>
       <c r="Z21">
-        <v>8.7486139561991152E-3</v>
+        <v>8.5328592206396145E-3</v>
       </c>
       <c r="AA21">
-        <v>6.005370023625463E-5</v>
+        <v>8.6144486081287663E-3</v>
       </c>
       <c r="AB21">
-        <v>-8.5455480735939374E-4</v>
+        <v>5.0731627463186267E-5</v>
       </c>
       <c r="AC21">
-        <v>-7.1368420236440216E-4</v>
+        <v>-7.6202807355151133E-4</v>
       </c>
       <c r="AD21">
-        <v>3.0677911849076285E-3</v>
+        <v>-2.8056700462065869E-4</v>
       </c>
       <c r="AE21">
-        <v>2.0649891983928616E-2</v>
+        <v>2.6061038321676835E-3</v>
       </c>
       <c r="AF21">
-        <v>2.540564716296924E-3</v>
+        <v>1.9615161642248115E-2</v>
       </c>
       <c r="AG21">
-        <v>6.6584339631246131E-4</v>
+        <v>1.837498144022335E-3</v>
+      </c>
+      <c r="AH21">
+        <v>1.9580739813668622E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22">
-        <v>0.1166146028141402</v>
+        <v>4.9123934010158479E-2</v>
       </c>
       <c r="C22">
-        <v>-1.1655726553340684E-3</v>
+        <v>-1.0924357778282711E-3</v>
       </c>
       <c r="D22">
-        <v>-2.7936671993147172E-4</v>
+        <v>-3.3438882093485278E-5</v>
       </c>
       <c r="E22">
-        <v>2.5272810334622331E-6</v>
+        <v>6.3584161861136032E-7</v>
       </c>
       <c r="F22">
-        <v>8.169236732865656E-4</v>
+        <v>9.3796792388116087E-4</v>
       </c>
       <c r="G22">
-        <v>-2.8548992928781943E-4</v>
+        <v>-6.5424311590343712E-5</v>
       </c>
       <c r="H22">
-        <v>-3.1795184726540965E-5</v>
+        <v>-3.9519927201841414E-5</v>
       </c>
       <c r="I22">
-        <v>-6.748142536664272E-6</v>
+        <v>-1.4399214004307828E-5</v>
       </c>
       <c r="J22">
-        <v>-6.112365800291196E-4</v>
+        <v>-7.1547489369348273E-4</v>
       </c>
       <c r="K22">
-        <v>-4.3446729745936011E-3</v>
+        <v>-2.9981899491668632E-3</v>
       </c>
       <c r="L22">
-        <v>-4.0308586632102888E-3</v>
+        <v>-3.5903177546743417E-3</v>
       </c>
       <c r="M22">
-        <v>-5.3556919770340978E-3</v>
+        <v>-4.8753050863960829E-3</v>
       </c>
       <c r="N22">
-        <v>-5.3923067757059209E-3</v>
+        <v>-4.514258930512537E-3</v>
       </c>
       <c r="O22">
-        <v>-4.3384243174606086E-3</v>
+        <v>-3.7669760566994247E-3</v>
       </c>
       <c r="P22">
-        <v>8.9659041556467162E-3</v>
+        <v>-1.7384855818228101E-3</v>
       </c>
       <c r="Q22">
-        <v>1.2158826781762014E-2</v>
+        <v>8.5656369503609893E-3</v>
       </c>
       <c r="R22">
-        <v>8.4659757639627426E-3</v>
+        <v>1.1302039385243519E-2</v>
       </c>
       <c r="S22">
-        <v>8.8797626294748223E-3</v>
+        <v>8.0735440514472755E-3</v>
       </c>
       <c r="T22">
-        <v>8.1984899575322789E-3</v>
+        <v>8.4253661993553865E-3</v>
       </c>
       <c r="U22">
-        <v>8.5590423331899368E-3</v>
+        <v>7.761572282628075E-3</v>
       </c>
       <c r="V22">
-        <v>8.7421471477505449E-3</v>
+        <v>8.2248316720800897E-3</v>
       </c>
       <c r="W22">
-        <v>1.2375776669216174E-2</v>
+        <v>1.0837957222124984E-2</v>
       </c>
       <c r="X22">
-        <v>9.0334915906263788E-3</v>
+        <v>8.7126996077557094E-3</v>
       </c>
       <c r="Y22">
-        <v>9.0205636200634057E-3</v>
+        <v>8.5763905343282845E-3</v>
       </c>
       <c r="Z22">
-        <v>9.0711308878982481E-3</v>
+        <v>8.6586477196344928E-3</v>
       </c>
       <c r="AA22">
-        <v>5.3197356763222967E-5</v>
+        <v>8.8594582130853035E-3</v>
       </c>
       <c r="AB22">
-        <v>-9.6158808304679013E-4</v>
+        <v>4.9210360723202663E-5</v>
       </c>
       <c r="AC22">
-        <v>-6.7269403116919108E-4</v>
+        <v>-8.1856042452575902E-4</v>
       </c>
       <c r="AD22">
-        <v>3.2696541788754764E-3</v>
+        <v>-6.9952946293277583E-4</v>
       </c>
       <c r="AE22">
-        <v>2.2555573974949464E-2</v>
+        <v>2.8781878160798599E-3</v>
       </c>
       <c r="AF22">
-        <v>1.6520813459072966E-3</v>
+        <v>2.0051955780835969E-2</v>
       </c>
       <c r="AG22">
-        <v>4.9820809011349478E-3</v>
+        <v>2.5290166049351868E-3</v>
+      </c>
+      <c r="AH22">
+        <v>-2.485477448958915E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.22260548891356038</v>
+        <v>0.12590546949037715</v>
       </c>
       <c r="C23">
-        <v>-1.1446484508254402E-3</v>
+        <v>-1.1501715642297061E-3</v>
       </c>
       <c r="D23">
-        <v>-3.3984462553406786E-4</v>
+        <v>-1.1659868555197184E-4</v>
       </c>
       <c r="E23">
-        <v>2.6895869347601806E-6</v>
+        <v>1.17026338321963E-6</v>
       </c>
       <c r="F23">
-        <v>9.2585490335738698E-4</v>
+        <v>8.2964670507371888E-4</v>
       </c>
       <c r="G23">
-        <v>-4.7205054324509746E-4</v>
+        <v>-1.5177530750236888E-4</v>
       </c>
       <c r="H23">
-        <v>-2.9876435204284364E-5</v>
+        <v>-5.2663112499476064E-5</v>
       </c>
       <c r="I23">
-        <v>-5.5755394995919596E-6</v>
+        <v>-1.7159754152147946E-5</v>
       </c>
       <c r="J23">
-        <v>-2.7946955869048891E-4</v>
+        <v>-5.4547268011928725E-4</v>
       </c>
       <c r="K23">
-        <v>-3.8526909312896589E-3</v>
+        <v>-3.5677001716953229E-3</v>
       </c>
       <c r="L23">
-        <v>-3.4065799477767107E-3</v>
+        <v>-3.9154658742369692E-3</v>
       </c>
       <c r="M23">
-        <v>-5.0207216703439276E-3</v>
+        <v>-5.2996114354346606E-3</v>
       </c>
       <c r="N23">
-        <v>-5.200732198768588E-3</v>
+        <v>-5.2913952164593894E-3</v>
       </c>
       <c r="O23">
-        <v>-4.0628496490863883E-3</v>
+        <v>-4.1907259684440127E-3</v>
       </c>
       <c r="P23">
-        <v>8.8312212180462705E-3</v>
+        <v>-2.0597582019736002E-3</v>
       </c>
       <c r="Q23">
-        <v>1.2043049927135962E-2</v>
+        <v>8.9361848538632334E-3</v>
       </c>
       <c r="R23">
-        <v>8.3391998345296453E-3</v>
+        <v>1.2003379509488852E-2</v>
       </c>
       <c r="S23">
-        <v>8.7961366283874371E-3</v>
+        <v>8.3979663932517313E-3</v>
       </c>
       <c r="T23">
-        <v>8.0690931114370083E-3</v>
+        <v>8.8185141425060724E-3</v>
       </c>
       <c r="U23">
-        <v>8.4802216094199429E-3</v>
+        <v>8.0850015595935569E-3</v>
       </c>
       <c r="V23">
-        <v>8.6191367696619135E-3</v>
+        <v>8.5524533918958472E-3</v>
       </c>
       <c r="W23">
-        <v>9.0334915906263788E-3</v>
+        <v>8.7126996077557094E-3</v>
       </c>
       <c r="X23">
-        <v>1.4323412520735702E-2</v>
+        <v>1.2372946792771886E-2</v>
       </c>
       <c r="Y23">
-        <v>8.8862535074615018E-3</v>
+        <v>9.0084011071199996E-3</v>
       </c>
       <c r="Z23">
-        <v>8.9793589556667417E-3</v>
+        <v>9.0555249674078714E-3</v>
       </c>
       <c r="AA23">
-        <v>9.3096384138721677E-5</v>
+        <v>9.2263185487242265E-3</v>
       </c>
       <c r="AB23">
-        <v>-1.0874247517378473E-3</v>
+        <v>4.1211796409590384E-5</v>
       </c>
       <c r="AC23">
-        <v>-5.3582877207872769E-4</v>
+        <v>-9.0061752606208911E-4</v>
       </c>
       <c r="AD23">
-        <v>3.1640716488558845E-3</v>
+        <v>-6.5026301718389742E-4</v>
       </c>
       <c r="AE23">
-        <v>2.232790949620117E-2</v>
+        <v>3.0669698095329976E-3</v>
       </c>
       <c r="AF23">
-        <v>1.1943158965919793E-3</v>
+        <v>2.1982838294511781E-2</v>
       </c>
       <c r="AG23">
-        <v>6.806454199461149E-3</v>
+        <v>1.6846242617520801E-3</v>
+      </c>
+      <c r="AH23">
+        <v>1.7896458013391195E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24">
-        <v>0.13068232193359486</v>
+        <v>0.23183675841810009</v>
       </c>
       <c r="C24">
-        <v>-1.1648692273345507E-3</v>
+        <v>-1.1423072500666908E-3</v>
       </c>
       <c r="D24">
-        <v>-2.8999699847368637E-4</v>
+        <v>-1.4601185880170481E-4</v>
       </c>
       <c r="E24">
-        <v>2.6129729643860691E-6</v>
+        <v>1.179180915106162E-6</v>
       </c>
       <c r="F24">
-        <v>6.7336019433498085E-4</v>
+        <v>9.1399263301876628E-4</v>
       </c>
       <c r="G24">
-        <v>-3.7494780298112824E-4</v>
+        <v>-3.7710233893113666E-4</v>
       </c>
       <c r="H24">
-        <v>-3.3225176670746779E-5</v>
+        <v>-5.3037754652481754E-5</v>
       </c>
       <c r="I24">
-        <v>-6.2857391588469751E-6</v>
+        <v>-1.5629270179927227E-5</v>
       </c>
       <c r="J24">
-        <v>-3.9028844305482278E-4</v>
+        <v>-2.6456056178748681E-4</v>
       </c>
       <c r="K24">
-        <v>-4.1173233469504866E-3</v>
+        <v>-3.2642754439391256E-3</v>
       </c>
       <c r="L24">
-        <v>-3.5820955082193949E-3</v>
+        <v>-4.3349079283260894E-3</v>
       </c>
       <c r="M24">
-        <v>-4.9834125599568495E-3</v>
+        <v>-5.5920306680627817E-3</v>
       </c>
       <c r="N24">
-        <v>-5.1296432830864021E-3</v>
+        <v>-5.7502873012921923E-3</v>
       </c>
       <c r="O24">
-        <v>-4.1234114179733499E-3</v>
+        <v>-4.5787047585511024E-3</v>
       </c>
       <c r="P24">
-        <v>8.8913709929233121E-3</v>
+        <v>-2.3822228603555392E-3</v>
       </c>
       <c r="Q24">
-        <v>1.1897830493365527E-2</v>
+        <v>8.7353587247081983E-3</v>
       </c>
       <c r="R24">
-        <v>8.3818503564281367E-3</v>
+        <v>1.1746470179013663E-2</v>
       </c>
       <c r="S24">
-        <v>8.8216177097435837E-3</v>
+        <v>8.1879396998947498E-3</v>
       </c>
       <c r="T24">
-        <v>8.0924982881819905E-3</v>
+        <v>8.6643359612591161E-3</v>
       </c>
       <c r="U24">
-        <v>8.501518662253283E-3</v>
+        <v>7.9164536546233941E-3</v>
       </c>
       <c r="V24">
-        <v>8.6452632750799695E-3</v>
+        <v>8.4348368264062206E-3</v>
       </c>
       <c r="W24">
-        <v>9.0205636200634057E-3</v>
+        <v>8.5763905343282845E-3</v>
       </c>
       <c r="X24">
-        <v>8.8862535074615018E-3</v>
+        <v>9.0084011071199996E-3</v>
       </c>
       <c r="Y24">
-        <v>1.2299456228765512E-2</v>
+        <v>1.4214985793442629E-2</v>
       </c>
       <c r="Z24">
-        <v>8.8831891590137046E-3</v>
+        <v>8.8710532691758399E-3</v>
       </c>
       <c r="AA24">
-        <v>6.7902174205174376E-5</v>
+        <v>9.0410868650149748E-3</v>
       </c>
       <c r="AB24">
-        <v>-7.9308494796969352E-4</v>
+        <v>7.7167320084116277E-5</v>
       </c>
       <c r="AC24">
-        <v>-4.80970186501525E-4</v>
+        <v>-1.0458495211376623E-3</v>
       </c>
       <c r="AD24">
-        <v>3.1568639046200774E-3</v>
+        <v>-4.498201437935492E-4</v>
       </c>
       <c r="AE24">
-        <v>2.1698504024830874E-2</v>
+        <v>2.8608098858363038E-3</v>
       </c>
       <c r="AF24">
-        <v>1.9700524899285907E-3</v>
+        <v>2.1286060502171966E-2</v>
       </c>
       <c r="AG24">
-        <v>4.8448563740489115E-3</v>
+        <v>1.245278279531953E-3</v>
+      </c>
+      <c r="AH24">
+        <v>3.2282223474506197E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>36</v>
       </c>
       <c r="B25">
-        <v>7.9453675305928978E-2</v>
+        <v>0.14153708863180745</v>
       </c>
       <c r="C25">
-        <v>-6.6869505607167808E-4</v>
+        <v>-1.154843522886884E-3</v>
       </c>
       <c r="D25">
-        <v>-3.0815791782035085E-4</v>
+        <v>-1.2150128821220019E-4</v>
       </c>
       <c r="E25">
-        <v>2.5171093490477235E-6</v>
+        <v>1.2318415760660261E-6</v>
       </c>
       <c r="F25">
-        <v>1.1387529075870806E-3</v>
+        <v>6.8644692588015776E-4</v>
       </c>
       <c r="G25">
-        <v>-9.2747198385329833E-4</v>
+        <v>-2.4304529010942249E-4</v>
       </c>
       <c r="H25">
-        <v>-4.3646174695807674E-5</v>
+        <v>-5.2587838813649416E-5</v>
       </c>
       <c r="I25">
-        <v>-2.6445868137072126E-5</v>
+        <v>-1.5351652430080565E-5</v>
       </c>
       <c r="J25">
-        <v>-2.5678979880757076E-4</v>
+        <v>-3.6362801984441036E-4</v>
       </c>
       <c r="K25">
-        <v>-4.2159131747568166E-3</v>
+        <v>-3.3970837117349752E-3</v>
       </c>
       <c r="L25">
-        <v>-4.2304159945557576E-3</v>
+        <v>-3.537215179007651E-3</v>
       </c>
       <c r="M25">
-        <v>-5.3705006152882694E-3</v>
+        <v>-5.0219655595727664E-3</v>
       </c>
       <c r="N25">
-        <v>-5.2866858818126604E-3</v>
+        <v>-5.1083952405022014E-3</v>
       </c>
       <c r="O25">
-        <v>-4.4392508360602814E-3</v>
+        <v>-4.0582972497101187E-3</v>
       </c>
       <c r="P25">
-        <v>8.7845481905285405E-3</v>
+        <v>-1.9970491317217887E-3</v>
       </c>
       <c r="Q25">
-        <v>1.1852900763123194E-2</v>
+        <v>8.9011675442085686E-3</v>
       </c>
       <c r="R25">
-        <v>8.301971266248289E-3</v>
+        <v>1.1824137522899696E-2</v>
       </c>
       <c r="S25">
-        <v>8.7780538513003784E-3</v>
+        <v>8.3577163916679041E-3</v>
       </c>
       <c r="T25">
-        <v>8.0000303359190894E-3</v>
+        <v>8.79542087200786E-3</v>
       </c>
       <c r="U25">
-        <v>8.4802736448037451E-3</v>
+        <v>8.0263983820675049E-3</v>
       </c>
       <c r="V25">
-        <v>8.7486139561991152E-3</v>
+        <v>8.5328592206396145E-3</v>
       </c>
       <c r="W25">
-        <v>9.0711308878982481E-3</v>
+        <v>8.6586477196344928E-3</v>
       </c>
       <c r="X25">
-        <v>8.9793589556667417E-3</v>
+        <v>9.0555249674078714E-3</v>
       </c>
       <c r="Y25">
-        <v>8.8831891590137046E-3</v>
+        <v>8.8710532691758399E-3</v>
       </c>
       <c r="Z25">
-        <v>1.7505961061558616E-2</v>
+        <v>1.2378619408790389E-2</v>
       </c>
       <c r="AA25">
-        <v>1.278756700433994E-4</v>
+        <v>9.0575967819825666E-3</v>
       </c>
       <c r="AB25">
-        <v>-1.4009408751769602E-3</v>
+        <v>5.4777636529025663E-5</v>
       </c>
       <c r="AC25">
-        <v>-1.2243265788977236E-3</v>
+        <v>-7.3867379220454114E-4</v>
       </c>
       <c r="AD25">
-        <v>3.3988804018273899E-3</v>
+        <v>-4.2190834957272485E-4</v>
       </c>
       <c r="AE25">
-        <v>2.1580351466152864E-2</v>
+        <v>2.9690184143657595E-3</v>
       </c>
       <c r="AF25">
-        <v>1.8051719010219571E-3</v>
+        <v>2.134217449376339E-2</v>
       </c>
       <c r="AG25">
-        <v>6.7802449250441814E-3</v>
+        <v>2.0181842732747424E-3</v>
+      </c>
+      <c r="AH25">
+        <v>1.3199842918870403E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
       <c r="B26">
-        <v>-1.6079552016906182E-2</v>
+        <v>0.10074405829308571</v>
       </c>
       <c r="C26">
-        <v>-1.1366951551944511E-5</v>
+        <v>-6.7325170719638016E-4</v>
       </c>
       <c r="D26">
-        <v>-2.7443141963271259E-5</v>
+        <v>-1.7457630591909135E-4</v>
       </c>
       <c r="E26">
-        <v>1.7770612206448799E-7</v>
+        <v>1.4037523786891086E-6</v>
       </c>
       <c r="F26">
-        <v>1.7445225467772456E-5</v>
+        <v>1.1924040947890843E-3</v>
       </c>
       <c r="G26">
-        <v>5.3557519767366492E-6</v>
+        <v>-8.1107138794252686E-4</v>
       </c>
       <c r="H26">
-        <v>1.1353574497580474E-7</v>
+        <v>-6.4884877886612767E-5</v>
       </c>
       <c r="I26">
-        <v>1.926202665160141E-6</v>
+        <v>-3.6326354668531215E-5</v>
       </c>
       <c r="J26">
-        <v>5.5489645738426418E-5</v>
+        <v>-2.031664107929633E-4</v>
       </c>
       <c r="K26">
-        <v>-1.9920285372653553E-4</v>
+        <v>-3.6756824102319348E-3</v>
       </c>
       <c r="L26">
-        <v>-1.074595178927465E-4</v>
+        <v>-4.3500593473219159E-3</v>
       </c>
       <c r="M26">
-        <v>-2.3107525649534392E-4</v>
+        <v>-5.5601789479914118E-3</v>
       </c>
       <c r="N26">
-        <v>-2.6744267304573493E-4</v>
+        <v>-5.4517739974620531E-3</v>
       </c>
       <c r="O26">
-        <v>-2.673858631659508E-4</v>
+        <v>-4.5411369201331262E-3</v>
       </c>
       <c r="P26">
-        <v>4.7919588673756659E-5</v>
+        <v>-1.9425962295622655E-3</v>
       </c>
       <c r="Q26">
-        <v>1.9170095709306533E-4</v>
+        <v>8.8881633414782009E-3</v>
       </c>
       <c r="R26">
-        <v>3.8762887797803933E-5</v>
+        <v>1.1978780344448478E-2</v>
       </c>
       <c r="S26">
-        <v>6.022742599666453E-5</v>
+        <v>8.3673817095162792E-3</v>
       </c>
       <c r="T26">
-        <v>4.7347293135733453E-5</v>
+        <v>8.8512476215022763E-3</v>
       </c>
       <c r="U26">
-        <v>6.203703919191385E-5</v>
+        <v>8.0286788057417624E-3</v>
       </c>
       <c r="V26">
-        <v>6.005370023625463E-5</v>
+        <v>8.6144486081287663E-3</v>
       </c>
       <c r="W26">
-        <v>5.3197356763222967E-5</v>
+        <v>8.8594582130853035E-3</v>
       </c>
       <c r="X26">
-        <v>9.3096384138721677E-5</v>
+        <v>9.2263185487242265E-3</v>
       </c>
       <c r="Y26">
-        <v>6.7902174205174376E-5</v>
+        <v>9.0410868650149748E-3</v>
       </c>
       <c r="Z26">
-        <v>1.278756700433994E-4</v>
+        <v>9.0575967819825666E-3</v>
       </c>
       <c r="AA26">
-        <v>3.5897899893069091E-5</v>
+        <v>1.7877132639020618E-2</v>
       </c>
       <c r="AB26">
-        <v>-1.5268455410089303E-4</v>
+        <v>1.2192308526820235E-4</v>
       </c>
       <c r="AC26">
-        <v>-1.6990082234145769E-4</v>
+        <v>-1.3896215860871889E-3</v>
       </c>
       <c r="AD26">
-        <v>-3.234799862453023E-5</v>
+        <v>-1.2911172282988846E-3</v>
       </c>
       <c r="AE26">
-        <v>6.3436482062594469E-4</v>
+        <v>3.2388559399907559E-3</v>
       </c>
       <c r="AF26">
-        <v>-7.8249516064422406E-6</v>
+        <v>2.1749099718759123E-2</v>
       </c>
       <c r="AG26">
-        <v>4.7760863000565742E-4</v>
+        <v>1.8622190421784274E-3</v>
+      </c>
+      <c r="AH26">
+        <v>4.4440829780870265E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27">
-        <v>-0.10977757519051071</v>
+        <v>-1.6564979178240059E-2</v>
       </c>
       <c r="C27">
-        <v>2.5012365707570926E-4</v>
+        <v>-9.5909821632421963E-6</v>
       </c>
       <c r="D27">
-        <v>1.1446273566451115E-4</v>
+        <v>-2.1414488845452814E-5</v>
       </c>
       <c r="E27">
-        <v>-9.7351215422054188E-7</v>
+        <v>1.3115388549533218E-7</v>
       </c>
       <c r="F27">
-        <v>-8.4226157188011484E-5</v>
+        <v>1.3455199897537487E-5</v>
       </c>
       <c r="G27">
-        <v>2.4718836067931602E-4</v>
+        <v>6.513069069771912E-6</v>
       </c>
       <c r="H27">
-        <v>5.3067780072667172E-6</v>
+        <v>-3.0175474393208867E-7</v>
       </c>
       <c r="I27">
-        <v>-2.1251748286803252E-6</v>
+        <v>1.7226003919480057E-6</v>
       </c>
       <c r="J27">
-        <v>1.6227697476110629E-4</v>
+        <v>5.4182694337199123E-5</v>
       </c>
       <c r="K27">
-        <v>1.6683539035454997E-3</v>
+        <v>-1.7550987748494356E-4</v>
       </c>
       <c r="L27">
-        <v>1.0702474008021938E-3</v>
+        <v>-1.1146434163181851E-4</v>
       </c>
       <c r="M27">
-        <v>1.9794935184048101E-3</v>
+        <v>-2.2765543498336639E-4</v>
       </c>
       <c r="N27">
-        <v>2.1883072746697345E-3</v>
+        <v>-2.618728405212223E-4</v>
       </c>
       <c r="O27">
-        <v>2.0603173676225642E-3</v>
+        <v>-2.6257544479177559E-4</v>
       </c>
       <c r="P27">
-        <v>-8.9108422950021733E-4</v>
+        <v>-5.0213194636763644E-5</v>
       </c>
       <c r="Q27">
-        <v>-2.0489017586479991E-3</v>
+        <v>3.6811564240966325E-5</v>
       </c>
       <c r="R27">
-        <v>-6.1942189544886153E-4</v>
+        <v>1.68478734443489E-4</v>
       </c>
       <c r="S27">
-        <v>-9.0885703377686488E-4</v>
+        <v>2.4418778485373288E-5</v>
       </c>
       <c r="T27">
-        <v>-4.5628703044999159E-4</v>
+        <v>4.7296629706502493E-5</v>
       </c>
       <c r="U27">
-        <v>-8.0607745343635453E-4</v>
+        <v>3.006751857983559E-5</v>
       </c>
       <c r="V27">
-        <v>-8.5455480735939374E-4</v>
+        <v>5.0731627463186267E-5</v>
       </c>
       <c r="W27">
-        <v>-9.6158808304679013E-4</v>
+        <v>4.9210360723202663E-5</v>
       </c>
       <c r="X27">
-        <v>-1.0874247517378473E-3</v>
+        <v>4.1211796409590384E-5</v>
       </c>
       <c r="Y27">
-        <v>-7.9308494796969352E-4</v>
+        <v>7.7167320084116277E-5</v>
       </c>
       <c r="Z27">
-        <v>-1.4009408751769602E-3</v>
+        <v>5.4777636529025663E-5</v>
       </c>
       <c r="AA27">
-        <v>-1.5268455410089303E-4</v>
+        <v>1.2192308526820235E-4</v>
       </c>
       <c r="AB27">
-        <v>6.0340471246705654E-3</v>
+        <v>3.5411288729112589E-5</v>
       </c>
       <c r="AC27">
-        <v>1.2037347356442106E-3</v>
+        <v>-1.5116642171840759E-4</v>
       </c>
       <c r="AD27">
-        <v>-2.8871035763783565E-5</v>
+        <v>-1.6609493604615306E-4</v>
       </c>
       <c r="AE27">
-        <v>-5.7707452013542448E-3</v>
+        <v>-4.1347368790286662E-5</v>
       </c>
       <c r="AF27">
-        <v>-5.6134651978815637E-5</v>
+        <v>5.779015324047683E-4</v>
       </c>
       <c r="AG27">
-        <v>-2.5690194228501937E-3</v>
+        <v>-1.26251198857689E-5</v>
+      </c>
+      <c r="AH27">
+        <v>3.3458228060671326E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28">
-        <v>-3.6213275509334827E-2</v>
+        <v>-0.11081717176490555</v>
       </c>
       <c r="C28">
-        <v>2.6972907332088259E-4</v>
+        <v>2.3899944807097111E-4</v>
       </c>
       <c r="D28">
-        <v>1.4338622550074537E-4</v>
+        <v>7.3768484269390311E-5</v>
       </c>
       <c r="E28">
-        <v>-1.313342239538703E-6</v>
+        <v>-6.4421253843731895E-7</v>
       </c>
       <c r="F28">
-        <v>9.2782823284556868E-6</v>
+        <v>-7.0154215605294475E-5</v>
       </c>
       <c r="G28">
-        <v>5.5514469630770532E-4</v>
+        <v>2.2530026226605837E-4</v>
       </c>
       <c r="H28">
-        <v>4.7919920017070448E-6</v>
+        <v>8.2237333035854081E-6</v>
       </c>
       <c r="I28">
-        <v>-4.4795139987441703E-6</v>
+        <v>-6.7303034800909769E-7</v>
       </c>
       <c r="J28">
-        <v>5.6449348910767028E-4</v>
+        <v>1.579359286024689E-4</v>
       </c>
       <c r="K28">
-        <v>1.799138155826099E-3</v>
+        <v>1.4977359110327788E-3</v>
       </c>
       <c r="L28">
-        <v>9.4787777384084879E-4</v>
+        <v>1.0611165636366837E-3</v>
       </c>
       <c r="M28">
-        <v>2.1657223908163837E-3</v>
+        <v>1.9520336994573763E-3</v>
       </c>
       <c r="N28">
-        <v>2.2131246297581765E-3</v>
+        <v>2.1527184877529054E-3</v>
       </c>
       <c r="O28">
-        <v>2.2106665824762166E-3</v>
+        <v>2.0250686858169697E-3</v>
       </c>
       <c r="P28">
-        <v>-3.5370452681470366E-4</v>
+        <v>3.5799640924950122E-4</v>
       </c>
       <c r="Q28">
-        <v>-1.5835801456500001E-3</v>
+        <v>-8.4449452163280498E-4</v>
       </c>
       <c r="R28">
-        <v>4.3792518407068104E-6</v>
+        <v>-1.9620267190770891E-3</v>
       </c>
       <c r="S28">
-        <v>-7.7941806223789803E-4</v>
+        <v>-5.6363391535268733E-4</v>
       </c>
       <c r="T28">
-        <v>-4.9872464845018361E-4</v>
+        <v>-8.4825251593716351E-4</v>
       </c>
       <c r="U28">
-        <v>-2.9369524101501964E-4</v>
+        <v>-4.2458332584364078E-4</v>
       </c>
       <c r="V28">
-        <v>-7.1368420236440216E-4</v>
+        <v>-7.6202807355151133E-4</v>
       </c>
       <c r="W28">
-        <v>-6.7269403116919108E-4</v>
+        <v>-8.1856042452575902E-4</v>
       </c>
       <c r="X28">
-        <v>-5.3582877207872769E-4</v>
+        <v>-9.0061752606208911E-4</v>
       </c>
       <c r="Y28">
-        <v>-4.80970186501525E-4</v>
+        <v>-1.0458495211376623E-3</v>
       </c>
       <c r="Z28">
-        <v>-1.2243265788977236E-3</v>
+        <v>-7.3867379220454114E-4</v>
       </c>
       <c r="AA28">
-        <v>-1.6990082234145769E-4</v>
+        <v>-1.3896215860871889E-3</v>
       </c>
       <c r="AB28">
-        <v>1.2037347356442106E-3</v>
+        <v>-1.5116642171840759E-4</v>
       </c>
       <c r="AC28">
-        <v>5.8378555450972133E-3</v>
+        <v>6.0157979422917418E-3</v>
       </c>
       <c r="AD28">
-        <v>-9.8506094107649565E-5</v>
+        <v>1.2044679227264979E-3</v>
       </c>
       <c r="AE28">
-        <v>-5.231618497068373E-3</v>
+        <v>3.3225994220913613E-5</v>
       </c>
       <c r="AF28">
-        <v>1.6099336421514408E-4</v>
+        <v>-5.5800955046195269E-3</v>
       </c>
       <c r="AG28">
-        <v>-3.3431394050165552E-3</v>
+        <v>-4.9960251736090269E-5</v>
+      </c>
+      <c r="AH28">
+        <v>-1.5794481559328979E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
       <c r="B29">
-        <v>-0.14785159412509466</v>
+        <v>-3.2257370864543715E-2</v>
       </c>
       <c r="C29">
-        <v>-1.8434475740953745E-4</v>
+        <v>2.7816574925235951E-4</v>
       </c>
       <c r="D29">
-        <v>-2.5090533802485729E-4</v>
+        <v>8.3024242661412784E-5</v>
       </c>
       <c r="E29">
-        <v>2.2733936873017087E-6</v>
+        <v>-8.4426249492158562E-7</v>
       </c>
       <c r="F29">
-        <v>3.7007892389643438E-4</v>
+        <v>1.2208520768304879E-5</v>
       </c>
       <c r="G29">
-        <v>-2.8136892051779886E-4</v>
+        <v>5.4098960169393466E-4</v>
       </c>
       <c r="H29">
-        <v>-1.3836965228521873E-5</v>
+        <v>1.2351937744690619E-5</v>
       </c>
       <c r="I29">
-        <v>-1.3393998413329875E-5</v>
+        <v>-8.9726751490706511E-7</v>
       </c>
       <c r="J29">
-        <v>-2.0185502486070976E-4</v>
+        <v>5.8132769883256948E-4</v>
       </c>
       <c r="K29">
-        <v>-1.4308554159745378E-3</v>
+        <v>1.6003908164010459E-3</v>
       </c>
       <c r="L29">
-        <v>-1.1636883847742333E-3</v>
+        <v>1.0713022314313625E-3</v>
       </c>
       <c r="M29">
-        <v>-1.3567753895332504E-3</v>
+        <v>2.2657873002475894E-3</v>
       </c>
       <c r="N29">
-        <v>-1.3194456368283824E-3</v>
+        <v>2.3035551953170369E-3</v>
       </c>
       <c r="O29">
-        <v>-1.0440905161043512E-3</v>
+        <v>2.286023926794215E-3</v>
       </c>
       <c r="P29">
-        <v>3.1720525237311967E-3</v>
+        <v>7.6072760382328878E-4</v>
       </c>
       <c r="Q29">
-        <v>3.7641901911124776E-3</v>
+        <v>-3.3495061717894173E-4</v>
       </c>
       <c r="R29">
-        <v>3.0414862896871427E-3</v>
+        <v>-1.5130642250818314E-3</v>
       </c>
       <c r="S29">
-        <v>2.9166716340068921E-3</v>
+        <v>5.3193134213101127E-5</v>
       </c>
       <c r="T29">
-        <v>2.4124165522326317E-3</v>
+        <v>-7.499778912280204E-4</v>
       </c>
       <c r="U29">
-        <v>2.7871885157924308E-3</v>
+        <v>-4.2540833475863092E-4</v>
       </c>
       <c r="V29">
-        <v>3.0677911849076285E-3</v>
+        <v>-2.8056700462065869E-4</v>
       </c>
       <c r="W29">
-        <v>3.2696541788754764E-3</v>
+        <v>-6.9952946293277583E-4</v>
       </c>
       <c r="X29">
-        <v>3.1640716488558845E-3</v>
+        <v>-6.5026301718389742E-4</v>
       </c>
       <c r="Y29">
-        <v>3.1568639046200774E-3</v>
+        <v>-4.498201437935492E-4</v>
       </c>
       <c r="Z29">
-        <v>3.3988804018273899E-3</v>
+        <v>-4.2190834957272485E-4</v>
       </c>
       <c r="AA29">
-        <v>-3.234799862453023E-5</v>
+        <v>-1.2911172282988846E-3</v>
       </c>
       <c r="AB29">
-        <v>-2.8871035763783565E-5</v>
+        <v>-1.6609493604615306E-4</v>
       </c>
       <c r="AC29">
-        <v>-9.8506094107649565E-5</v>
+        <v>1.2044679227264979E-3</v>
       </c>
       <c r="AD29">
-        <v>9.4542403860965237E-3</v>
+        <v>5.8591553456817467E-3</v>
       </c>
       <c r="AE29">
-        <v>6.8034127392556862E-3</v>
+        <v>-3.5238623922876191E-5</v>
       </c>
       <c r="AF29">
-        <v>9.266308606391768E-4</v>
+        <v>-5.0473513390873193E-3</v>
       </c>
       <c r="AG29">
-        <v>6.7791014832399681E-3</v>
+        <v>1.3094536046546508E-4</v>
+      </c>
+      <c r="AH29">
+        <v>-2.1865436333162198E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>41</v>
       </c>
       <c r="B30">
-        <v>0.18006733205327938</v>
+        <v>-0.15851047262528631</v>
       </c>
       <c r="C30">
-        <v>-4.4426992261511165E-3</v>
+        <v>-1.3356485573487605E-4</v>
       </c>
       <c r="D30">
-        <v>-2.1694328517966599E-3</v>
+        <v>-2.0324666875240829E-4</v>
       </c>
       <c r="E30">
-        <v>1.8440645990181262E-5</v>
+        <v>1.8824156444837629E-6</v>
       </c>
       <c r="F30">
-        <v>3.7354317207578085E-3</v>
+        <v>3.220369553871658E-4</v>
       </c>
       <c r="G30">
-        <v>-4.8853759071950959E-4</v>
+        <v>-2.5592402160860513E-4</v>
       </c>
       <c r="H30">
-        <v>-1.2191014095483703E-4</v>
+        <v>-1.5065600838914652E-5</v>
       </c>
       <c r="I30">
-        <v>5.9561762939144445E-5</v>
+        <v>-1.4615227430008252E-5</v>
       </c>
       <c r="J30">
-        <v>-3.5112608088026798E-3</v>
+        <v>-1.8222289801069977E-4</v>
       </c>
       <c r="K30">
-        <v>-2.6400607554612016E-2</v>
+        <v>-1.0716389002940457E-3</v>
       </c>
       <c r="L30">
-        <v>-1.9642108806765698E-2</v>
+        <v>-8.0609434730715313E-4</v>
       </c>
       <c r="M30">
-        <v>-3.0417872461514606E-2</v>
+        <v>-9.4644610922082128E-4</v>
       </c>
       <c r="N30">
-        <v>-3.2457778339151477E-2</v>
+        <v>-8.8548406727380433E-4</v>
       </c>
       <c r="O30">
-        <v>-2.9370391907755471E-2</v>
+        <v>-6.2362190477473038E-4</v>
       </c>
       <c r="P30">
-        <v>2.1677627377857715E-2</v>
+        <v>-1.6763241602153365E-4</v>
       </c>
       <c r="Q30">
-        <v>3.889245571963177E-2</v>
+        <v>2.998099777251512E-3</v>
       </c>
       <c r="R30">
-        <v>1.9511588873023136E-2</v>
+        <v>3.402725814964641E-3</v>
       </c>
       <c r="S30">
-        <v>2.0825724945639321E-2</v>
+        <v>2.8383210788795969E-3</v>
       </c>
       <c r="T30">
-        <v>1.8355011732366294E-2</v>
+        <v>2.7306670682286766E-3</v>
       </c>
       <c r="U30">
-        <v>2.0132366994540657E-2</v>
+        <v>2.2205062230388028E-3</v>
       </c>
       <c r="V30">
-        <v>2.0649891983928616E-2</v>
+        <v>2.6061038321676835E-3</v>
       </c>
       <c r="W30">
-        <v>2.2555573974949464E-2</v>
+        <v>2.8781878160798599E-3</v>
       </c>
       <c r="X30">
-        <v>2.232790949620117E-2</v>
+        <v>3.0669698095329976E-3</v>
       </c>
       <c r="Y30">
-        <v>2.1698504024830874E-2</v>
+        <v>2.8608098858363038E-3</v>
       </c>
       <c r="Z30">
-        <v>2.1580351466152864E-2</v>
+        <v>2.9690184143657595E-3</v>
       </c>
       <c r="AA30">
-        <v>6.3436482062594469E-4</v>
+        <v>3.2388559399907559E-3</v>
       </c>
       <c r="AB30">
-        <v>-5.7707452013542448E-3</v>
+        <v>-4.1347368790286662E-5</v>
       </c>
       <c r="AC30">
-        <v>-5.231618497068373E-3</v>
+        <v>3.3225994220913613E-5</v>
       </c>
       <c r="AD30">
-        <v>6.8034127392556862E-3</v>
+        <v>-3.5238623922876191E-5</v>
       </c>
       <c r="AE30">
-        <v>0.10534301055162884</v>
+        <v>9.3885927450274558E-3</v>
       </c>
       <c r="AF30">
-        <v>2.9325990170691743E-3</v>
+        <v>5.8387706281173568E-3</v>
       </c>
       <c r="AG30">
-        <v>6.5516118031260229E-2</v>
+        <v>9.2455301499030397E-4</v>
+      </c>
+      <c r="AH30">
+        <v>5.3848191418780639E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
       <c r="B31">
-        <v>3.7116790135855629E-2</v>
+        <v>0.17462685783241594</v>
       </c>
       <c r="C31">
-        <v>-4.5553998471864194E-4</v>
+        <v>-4.2796241113990489E-3</v>
       </c>
       <c r="D31">
-        <v>-9.7901568037135622E-5</v>
+        <v>-1.4432699710086316E-3</v>
       </c>
       <c r="E31">
-        <v>6.5133108212459082E-7</v>
+        <v>1.2504475447712871E-5</v>
       </c>
       <c r="F31">
-        <v>3.4140853721482316E-4</v>
+        <v>3.6298414841735502E-3</v>
       </c>
       <c r="G31">
-        <v>4.0556765445366538E-4</v>
+        <v>1.6784197773048529E-5</v>
       </c>
       <c r="H31">
-        <v>-5.6979168551107842E-6</v>
+        <v>-2.0193319986267356E-4</v>
       </c>
       <c r="I31">
-        <v>-2.2340732903636963E-6</v>
+        <v>1.7071736895229962E-5</v>
       </c>
       <c r="J31">
-        <v>6.2126603546640811E-4</v>
+        <v>-3.3383567065673886E-3</v>
       </c>
       <c r="K31">
-        <v>9.9664910247423944E-5</v>
+        <v>-2.3012891822242615E-2</v>
       </c>
       <c r="L31">
-        <v>-7.5206142269688395E-4</v>
+        <v>-1.8745656618896937E-2</v>
       </c>
       <c r="M31">
-        <v>-6.9739569540872774E-4</v>
+        <v>-2.96100317643683E-2</v>
       </c>
       <c r="N31">
-        <v>-3.914461380713503E-4</v>
+        <v>-3.1494487695220195E-2</v>
       </c>
       <c r="O31">
-        <v>-3.7512420324248784E-5</v>
+        <v>-2.8292654847919776E-2</v>
       </c>
       <c r="P31">
-        <v>1.9638515595310161E-3</v>
+        <v>-8.1961209053173986E-3</v>
       </c>
       <c r="Q31">
-        <v>2.0770292141523345E-3</v>
+        <v>2.1124708326911337E-2</v>
       </c>
       <c r="R31">
-        <v>1.8221175893846067E-3</v>
+        <v>3.7511099710748383E-2</v>
       </c>
       <c r="S31">
-        <v>2.0553852271110993E-3</v>
+        <v>1.8700860631329752E-2</v>
       </c>
       <c r="T31">
-        <v>1.4284099483168799E-3</v>
+        <v>2.0116015181737626E-2</v>
       </c>
       <c r="U31">
-        <v>1.8028610640400352E-3</v>
+        <v>1.7374656907640351E-2</v>
       </c>
       <c r="V31">
-        <v>2.540564716296924E-3</v>
+        <v>1.9615161642248115E-2</v>
       </c>
       <c r="W31">
-        <v>1.6520813459072966E-3</v>
+        <v>2.0051955780835969E-2</v>
       </c>
       <c r="X31">
-        <v>1.1943158965919793E-3</v>
+        <v>2.1982838294511781E-2</v>
       </c>
       <c r="Y31">
-        <v>1.9700524899285907E-3</v>
+        <v>2.1286060502171966E-2</v>
       </c>
       <c r="Z31">
-        <v>1.8051719010219571E-3</v>
+        <v>2.134217449376339E-2</v>
       </c>
       <c r="AA31">
-        <v>-7.8249516064422406E-6</v>
+        <v>2.1749099718759123E-2</v>
       </c>
       <c r="AB31">
-        <v>-5.6134651978815637E-5</v>
+        <v>5.779015324047683E-4</v>
       </c>
       <c r="AC31">
-        <v>1.6099336421514408E-4</v>
+        <v>-5.5800955046195269E-3</v>
       </c>
       <c r="AD31">
-        <v>9.266308606391768E-4</v>
+        <v>-5.0473513390873193E-3</v>
       </c>
       <c r="AE31">
-        <v>2.9325990170691743E-3</v>
+        <v>5.8387706281173568E-3</v>
       </c>
       <c r="AF31">
-        <v>1.7847502204650485E-2</v>
+        <v>0.10180293514693942</v>
       </c>
       <c r="AG31">
-        <v>1.8100787066908852E-3</v>
+        <v>3.1338479652060934E-3</v>
+      </c>
+      <c r="AH31">
+        <v>5.017483122451083E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>43</v>
       </c>
       <c r="B32">
-        <v>-19.204902196132647</v>
+        <v>4.421343794281319E-2</v>
       </c>
       <c r="C32">
-        <v>6.2043114978482805E-4</v>
+        <v>-4.6336786088605738E-4</v>
       </c>
       <c r="D32">
-        <v>-5.7705012434188546E-2</v>
+        <v>-7.0481832906434203E-5</v>
       </c>
       <c r="E32">
-        <v>4.4805888014480837E-4</v>
+        <v>4.4850648512936622E-7</v>
       </c>
       <c r="F32">
-        <v>2.213837203694005E-3</v>
+        <v>3.6257130334769691E-4</v>
       </c>
       <c r="G32">
-        <v>-1.0445761682538867E-3</v>
+        <v>4.270278188862661E-4</v>
       </c>
       <c r="H32">
-        <v>-3.1134931479971997E-4</v>
+        <v>-1.1366567289394905E-5</v>
       </c>
       <c r="I32">
-        <v>-1.5726098690799206E-4</v>
+        <v>-2.537323481334834E-6</v>
       </c>
       <c r="J32">
-        <v>7.3091459209271986E-3</v>
+        <v>5.3409354832910231E-4</v>
       </c>
       <c r="K32">
-        <v>-4.8559390173042824E-2</v>
+        <v>1.5910213733708414E-4</v>
       </c>
       <c r="L32">
-        <v>-2.6759139423635836E-2</v>
+        <v>-5.813230327526989E-4</v>
       </c>
       <c r="M32">
-        <v>-4.3243244715416261E-2</v>
+        <v>-6.0770265234587546E-4</v>
       </c>
       <c r="N32">
-        <v>-4.5943529534406183E-2</v>
+        <v>-3.2206269985366528E-4</v>
       </c>
       <c r="O32">
-        <v>-4.6554219087351779E-2</v>
+        <v>5.7604530648233741E-5</v>
       </c>
       <c r="P32">
-        <v>3.338129410986334E-3</v>
+        <v>-2.6916640561097389E-4</v>
       </c>
       <c r="Q32">
-        <v>1.6429117687213685E-2</v>
+        <v>1.9852435422809279E-3</v>
       </c>
       <c r="R32">
-        <v>6.1376912365996884E-3</v>
+        <v>2.1441458265871009E-3</v>
       </c>
       <c r="S32">
-        <v>6.4040874724277455E-3</v>
+        <v>1.8650394986656469E-3</v>
       </c>
       <c r="T32">
-        <v>2.2933291803295935E-3</v>
+        <v>2.0767754272771732E-3</v>
       </c>
       <c r="U32">
-        <v>4.957296887954047E-3</v>
+        <v>1.4660282419467409E-3</v>
       </c>
       <c r="V32">
-        <v>6.6584339631246131E-4</v>
+        <v>1.837498144022335E-3</v>
       </c>
       <c r="W32">
-        <v>4.9820809011349478E-3</v>
+        <v>2.5290166049351868E-3</v>
       </c>
       <c r="X32">
-        <v>6.806454199461149E-3</v>
+        <v>1.6846242617520801E-3</v>
       </c>
       <c r="Y32">
-        <v>4.8448563740489115E-3</v>
+        <v>1.245278279531953E-3</v>
       </c>
       <c r="Z32">
-        <v>6.7802449250441814E-3</v>
+        <v>2.0181842732747424E-3</v>
       </c>
       <c r="AA32">
-        <v>4.7760863000565742E-4</v>
+        <v>1.8622190421784274E-3</v>
       </c>
       <c r="AB32">
-        <v>-2.5690194228501937E-3</v>
+        <v>-1.26251198857689E-5</v>
       </c>
       <c r="AC32">
-        <v>-3.3431394050165552E-3</v>
+        <v>-4.9960251736090269E-5</v>
       </c>
       <c r="AD32">
-        <v>6.7791014832399681E-3</v>
+        <v>1.3094536046546508E-4</v>
       </c>
       <c r="AE32">
-        <v>6.5516118031260229E-2</v>
+        <v>9.2455301499030397E-4</v>
       </c>
       <c r="AF32">
-        <v>1.8100787066908852E-3</v>
+        <v>3.1338479652060934E-3</v>
       </c>
       <c r="AG32">
-        <v>1.8919655278463927</v>
+        <v>1.7749339784970574E-2</v>
+      </c>
+      <c r="AH32">
+        <v>1.189347423167867E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>-19.396654019302577</v>
+      </c>
+      <c r="C33">
+        <v>1.5716426711145401E-3</v>
+      </c>
+      <c r="D33">
+        <v>-5.7208342731185038E-2</v>
+      </c>
+      <c r="E33">
+        <v>4.4352568608887409E-4</v>
+      </c>
+      <c r="F33">
+        <v>1.0284453137187339E-3</v>
+      </c>
+      <c r="G33">
+        <v>-1.285783073726635E-3</v>
+      </c>
+      <c r="H33">
+        <v>-3.2331068767199795E-4</v>
+      </c>
+      <c r="I33">
+        <v>-1.7234077610545748E-4</v>
+      </c>
+      <c r="J33">
+        <v>7.9390310698239826E-3</v>
+      </c>
+      <c r="K33">
+        <v>-4.3683841851853228E-2</v>
+      </c>
+      <c r="L33">
+        <v>-2.395457321193321E-2</v>
+      </c>
+      <c r="M33">
+        <v>-3.8385164177546907E-2</v>
+      </c>
+      <c r="N33">
+        <v>-4.0875373753253452E-2</v>
+      </c>
+      <c r="O33">
+        <v>-4.2031837352031018E-2</v>
+      </c>
+      <c r="P33">
+        <v>-3.295598795347663E-3</v>
+      </c>
+      <c r="Q33">
+        <v>5.7757262032454536E-4</v>
+      </c>
+      <c r="R33">
+        <v>1.0569391465693316E-2</v>
+      </c>
+      <c r="S33">
+        <v>3.0383480951124957E-3</v>
+      </c>
+      <c r="T33">
+        <v>3.1677299623392927E-3</v>
+      </c>
+      <c r="U33">
+        <v>-1.3047319719277049E-3</v>
+      </c>
+      <c r="V33">
+        <v>1.9580739813668622E-3</v>
+      </c>
+      <c r="W33">
+        <v>-2.485477448958915E-3</v>
+      </c>
+      <c r="X33">
+        <v>1.7896458013391195E-3</v>
+      </c>
+      <c r="Y33">
+        <v>3.2282223474506197E-3</v>
+      </c>
+      <c r="Z33">
+        <v>1.3199842918870403E-3</v>
+      </c>
+      <c r="AA33">
+        <v>4.4440829780870265E-3</v>
+      </c>
+      <c r="AB33">
+        <v>3.3458228060671326E-4</v>
+      </c>
+      <c r="AC33">
+        <v>-1.5794481559328979E-3</v>
+      </c>
+      <c r="AD33">
+        <v>-2.1865436333162198E-3</v>
+      </c>
+      <c r="AE33">
+        <v>5.3848191418780639E-3</v>
+      </c>
+      <c r="AF33">
+        <v>5.017483122451083E-2</v>
+      </c>
+      <c r="AG33">
+        <v>1.189347423167867E-3</v>
+      </c>
+      <c r="AH33">
+        <v>1.8812692290664841</v>
       </c>
     </row>
   </sheetData>
@@ -4014,10 +4217,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AJ35"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -4049,16 +4252,16 @@
         <v>20</v>
       </c>
       <c r="K1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L1" t="s">
         <v>21</v>
       </c>
       <c r="M1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O1" t="s">
         <v>22</v>
@@ -4126,3745 +4329,3963 @@
       <c r="AJ1" t="s">
         <v>43</v>
       </c>
+      <c r="AK1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2">
-        <v>-2.1097863769710734E-2</v>
+        <v>-1.9052838959593962E-2</v>
       </c>
       <c r="C2">
-        <v>5.7660152673472815E-4</v>
+        <v>5.7671938139858302E-4</v>
       </c>
       <c r="D2">
-        <v>9.4445436431476687E-5</v>
+        <v>9.5318050260102948E-5</v>
       </c>
       <c r="E2">
-        <v>-9.5158686699393316E-7</v>
+        <v>-9.574592782751447E-7</v>
       </c>
       <c r="F2">
-        <v>-3.8074557113165959E-6</v>
+        <v>-1.0125287202650485E-6</v>
       </c>
       <c r="G2">
-        <v>-5.2476430140872225E-5</v>
+        <v>-4.9706915823994821E-5</v>
       </c>
       <c r="H2">
-        <v>1.0522477708784961E-6</v>
+        <v>5.5423017313807548E-7</v>
       </c>
       <c r="I2">
-        <v>-1.5721346114236054E-6</v>
+        <v>-1.9126548327973104E-6</v>
       </c>
       <c r="J2">
-        <v>2.2437700208049373E-4</v>
+        <v>2.2606754347015756E-4</v>
       </c>
       <c r="K2">
-        <v>-2.5883515186912658E-5</v>
+        <v>-2.6200416479750711E-5</v>
       </c>
       <c r="L2">
-        <v>1.7346155067771894E-4</v>
+        <v>1.8436291178712874E-4</v>
       </c>
       <c r="M2">
-        <v>-4.7123762735964424E-5</v>
+        <v>-4.9935437549654063E-5</v>
       </c>
       <c r="N2">
-        <v>6.9941600291891797E-5</v>
+        <v>7.3599279448492624E-5</v>
       </c>
       <c r="O2">
-        <v>1.7349104636785913E-4</v>
+        <v>1.1893908353827507E-4</v>
       </c>
       <c r="P2">
-        <v>1.7179702049738594E-4</v>
+        <v>1.4135553900581472E-4</v>
       </c>
       <c r="Q2">
-        <v>1.1421760023383173E-4</v>
+        <v>8.2043532908925146E-5</v>
       </c>
       <c r="R2">
-        <v>9.9763474469805743E-5</v>
+        <v>7.1459089857877061E-5</v>
       </c>
       <c r="S2">
-        <v>-1.6671860581969492E-4</v>
+        <v>-5.1616644415208798E-5</v>
       </c>
       <c r="T2">
-        <v>-1.5348614172238013E-4</v>
+        <v>-1.5056202710243881E-4</v>
       </c>
       <c r="U2">
-        <v>-1.5021995363997715E-4</v>
+        <v>-1.4111586419066676E-4</v>
       </c>
       <c r="V2">
-        <v>-1.6195532910172876E-4</v>
+        <v>-1.3284621102419502E-4</v>
       </c>
       <c r="W2">
-        <v>-1.5374721266462254E-4</v>
+        <v>-1.502173557686047E-4</v>
       </c>
       <c r="X2">
-        <v>-9.3927476035234286E-5</v>
+        <v>-1.3982838380614354E-4</v>
       </c>
       <c r="Y2">
-        <v>-1.0860926609857651E-4</v>
+        <v>-7.8900990849105801E-5</v>
       </c>
       <c r="Z2">
-        <v>-1.3157293751504069E-4</v>
+        <v>-9.353278090634882E-5</v>
       </c>
       <c r="AA2">
-        <v>-1.2465759851939141E-4</v>
+        <v>-1.1465299372097413E-4</v>
       </c>
       <c r="AB2">
-        <v>-1.647042595937882E-4</v>
+        <v>-1.1066562368145969E-4</v>
       </c>
       <c r="AC2">
-        <v>-1.7614338374122079E-4</v>
+        <v>-1.4831856284484206E-4</v>
       </c>
       <c r="AD2">
-        <v>1.127971394364426E-5</v>
+        <v>-1.609703824956303E-4</v>
       </c>
       <c r="AE2">
-        <v>-3.2702739084470613E-5</v>
+        <v>1.0655861110370738E-5</v>
       </c>
       <c r="AF2">
-        <v>-3.4827233209817509E-5</v>
+        <v>-2.790350858174995E-5</v>
       </c>
       <c r="AG2">
-        <v>-1.4979199090367999E-4</v>
+        <v>-3.03932547317998E-5</v>
       </c>
       <c r="AH2">
-        <v>-1.1355022334917663E-4</v>
+        <v>-1.5622324587662883E-4</v>
       </c>
       <c r="AI2">
-        <v>-8.5299986398909301E-5</v>
+        <v>-1.0325310381750091E-4</v>
       </c>
       <c r="AJ2">
-        <v>-2.7204892560691641E-3</v>
+        <v>-8.5595679129652548E-5</v>
+      </c>
+      <c r="AK2">
+        <v>-2.6844751168727931E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.81418207784904528</v>
+        <v>0.81969428353471607</v>
       </c>
       <c r="C3">
-        <v>9.4445436431476687E-5</v>
+        <v>9.5318050260102948E-5</v>
       </c>
       <c r="D3">
-        <v>1.5601449589589195E-3</v>
+        <v>1.5673101170538689E-3</v>
       </c>
       <c r="E3">
-        <v>-1.258263394302317E-5</v>
+        <v>-1.2632569318597901E-5</v>
       </c>
       <c r="F3">
-        <v>-8.8813703861078883E-5</v>
+        <v>-9.1662069276550809E-5</v>
       </c>
       <c r="G3">
-        <v>-2.3351807922907149E-4</v>
+        <v>-2.4068025149229753E-4</v>
       </c>
       <c r="H3">
-        <v>2.7184659981376708E-6</v>
+        <v>1.3389838115938836E-6</v>
       </c>
       <c r="I3">
-        <v>1.554393545419037E-6</v>
+        <v>9.492716960845019E-7</v>
       </c>
       <c r="J3">
-        <v>1.3018552754448672E-4</v>
+        <v>1.2432899791148537E-4</v>
       </c>
       <c r="K3">
-        <v>4.3521903173615009E-4</v>
+        <v>4.5853917780486588E-4</v>
       </c>
       <c r="L3">
-        <v>1.3840011001892919E-4</v>
+        <v>1.4140755232654786E-4</v>
       </c>
       <c r="M3">
-        <v>-5.5305338397203772E-5</v>
+        <v>-5.8102323524528762E-5</v>
       </c>
       <c r="N3">
-        <v>4.8159266219989505E-5</v>
+        <v>4.7125845679071333E-5</v>
       </c>
       <c r="O3">
-        <v>1.0804671405246114E-4</v>
+        <v>-1.623718295914317E-5</v>
       </c>
       <c r="P3">
-        <v>7.4387507021934614E-5</v>
+        <v>-2.6719714216222323E-5</v>
       </c>
       <c r="Q3">
-        <v>-5.6845342394890674E-5</v>
+        <v>-1.6607347054710571E-4</v>
       </c>
       <c r="R3">
-        <v>-2.9695162008504207E-5</v>
+        <v>-1.3921603985933041E-4</v>
       </c>
       <c r="S3">
-        <v>-1.4688121829584816E-4</v>
+        <v>-1.4087696292298078E-4</v>
       </c>
       <c r="T3">
-        <v>-1.2886543055131219E-4</v>
+        <v>-1.481777840139295E-4</v>
       </c>
       <c r="U3">
-        <v>-1.266108480801123E-4</v>
+        <v>-1.324284447740201E-4</v>
       </c>
       <c r="V3">
-        <v>-3.4079446313014551E-4</v>
+        <v>-1.2842602683082668E-4</v>
       </c>
       <c r="W3">
-        <v>-1.8431976309869064E-4</v>
+        <v>-3.5086370415512991E-4</v>
       </c>
       <c r="X3">
-        <v>-2.1973304192768675E-4</v>
+        <v>-1.9171454975691615E-4</v>
       </c>
       <c r="Y3">
-        <v>-1.7277896348635857E-4</v>
+        <v>-2.21466355329724E-4</v>
       </c>
       <c r="Z3">
-        <v>-1.904258469413965E-4</v>
+        <v>-1.7471080436940248E-4</v>
       </c>
       <c r="AA3">
-        <v>-1.7868892089609872E-4</v>
+        <v>-1.8912723054915342E-4</v>
       </c>
       <c r="AB3">
-        <v>-1.8444489746613502E-4</v>
+        <v>-1.8131248668446648E-4</v>
       </c>
       <c r="AC3">
-        <v>-1.4459445441743907E-4</v>
+        <v>-1.8388804953683655E-4</v>
       </c>
       <c r="AD3">
-        <v>1.0995581087524207E-6</v>
+        <v>-1.5111368442356082E-4</v>
       </c>
       <c r="AE3">
-        <v>2.4850874306035428E-6</v>
+        <v>1.1871135048770881E-6</v>
       </c>
       <c r="AF3">
-        <v>8.4495061951665989E-5</v>
+        <v>2.3928309300673065E-6</v>
       </c>
       <c r="AG3">
-        <v>-6.2518010978919805E-4</v>
+        <v>8.3596636499339363E-5</v>
       </c>
       <c r="AH3">
-        <v>-2.0525873854236598E-4</v>
+        <v>-6.6209498048584031E-4</v>
       </c>
       <c r="AI3">
-        <v>-1.3825057456334257E-5</v>
+        <v>-2.0311080103175422E-4</v>
       </c>
       <c r="AJ3">
-        <v>-4.8088678300469062E-2</v>
+        <v>-3.0207635378866685E-5</v>
+      </c>
+      <c r="AK3">
+        <v>-4.8120650391440506E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-6.179331834334772E-3</v>
+        <v>-6.2251922166319858E-3</v>
       </c>
       <c r="C4">
-        <v>-9.5158686699393316E-7</v>
+        <v>-9.574592782751447E-7</v>
       </c>
       <c r="D4">
-        <v>-1.258263394302317E-5</v>
+        <v>-1.2632569318597901E-5</v>
       </c>
       <c r="E4">
-        <v>1.0234526844779318E-7</v>
+        <v>1.0268552986815166E-7</v>
       </c>
       <c r="F4">
-        <v>7.04059088466093E-7</v>
+        <v>7.2372655608077447E-7</v>
       </c>
       <c r="G4">
-        <v>1.7846919796071954E-6</v>
+        <v>1.835746389516882E-6</v>
       </c>
       <c r="H4">
-        <v>-2.2356133694358433E-8</v>
+        <v>-1.1397941042711271E-8</v>
       </c>
       <c r="I4">
-        <v>-1.6840124774400571E-8</v>
+        <v>-1.1895212507823611E-8</v>
       </c>
       <c r="J4">
-        <v>-1.7956616168644972E-6</v>
+        <v>-1.7500593829169562E-6</v>
       </c>
       <c r="K4">
-        <v>-3.6780447692297317E-6</v>
+        <v>-3.8701072939239475E-6</v>
       </c>
       <c r="L4">
-        <v>-1.1979020484123338E-6</v>
+        <v>-1.2266843969255167E-6</v>
       </c>
       <c r="M4">
-        <v>3.7205717380510119E-7</v>
+        <v>3.9580847772757063E-7</v>
       </c>
       <c r="N4">
-        <v>-6.2919863360889838E-7</v>
+        <v>-6.235630829777284E-7</v>
       </c>
       <c r="O4">
-        <v>-1.0267488268236927E-6</v>
+        <v>-3.02118308794278E-8</v>
       </c>
       <c r="P4">
-        <v>-8.4400853500799518E-7</v>
+        <v>-4.8414401384501578E-8</v>
       </c>
       <c r="Q4">
-        <v>2.1675169286545954E-7</v>
+        <v>1.0756139674487257E-6</v>
       </c>
       <c r="R4">
-        <v>3.6918070128258711E-8</v>
+        <v>8.9359546689148658E-7</v>
       </c>
       <c r="S4">
-        <v>1.2783184399834584E-6</v>
+        <v>1.117170375334771E-6</v>
       </c>
       <c r="T4">
-        <v>1.0740993058092052E-6</v>
+        <v>1.2663215036533011E-6</v>
       </c>
       <c r="U4">
-        <v>1.0642338172260537E-6</v>
+        <v>1.0856234133888444E-6</v>
       </c>
       <c r="V4">
-        <v>2.6170418917653986E-6</v>
+        <v>1.0583363867869853E-6</v>
       </c>
       <c r="W4">
-        <v>1.5681877424394833E-6</v>
+        <v>2.6780762834552373E-6</v>
       </c>
       <c r="X4">
-        <v>1.7200474949762988E-6</v>
+        <v>1.606436698605606E-6</v>
       </c>
       <c r="Y4">
-        <v>1.3757251940924324E-6</v>
+        <v>1.7147525672501801E-6</v>
       </c>
       <c r="Z4">
-        <v>1.5359367158542881E-6</v>
+        <v>1.3702840320293911E-6</v>
       </c>
       <c r="AA4">
-        <v>1.4684437568277995E-6</v>
+        <v>1.5041350888907754E-6</v>
       </c>
       <c r="AB4">
-        <v>1.5038103234080126E-6</v>
+        <v>1.4698149367860583E-6</v>
       </c>
       <c r="AC4">
-        <v>1.2043257375340976E-6</v>
+        <v>1.4784060070943878E-6</v>
       </c>
       <c r="AD4">
-        <v>-4.223057716067416E-8</v>
+        <v>1.236554652979849E-6</v>
       </c>
       <c r="AE4">
-        <v>4.5547216408820446E-8</v>
+        <v>-4.2238712472434346E-8</v>
       </c>
       <c r="AF4">
-        <v>-6.0188746302127329E-7</v>
+        <v>3.9630903982493406E-8</v>
       </c>
       <c r="AG4">
-        <v>4.6345040509475702E-6</v>
+        <v>-6.0013566440803967E-7</v>
       </c>
       <c r="AH4">
-        <v>1.7114048857310056E-6</v>
+        <v>4.9187769426147052E-6</v>
       </c>
       <c r="AI4">
-        <v>4.8524357592621297E-8</v>
+        <v>1.6857221606156715E-6</v>
       </c>
       <c r="AJ4">
-        <v>3.8606296235684033E-4</v>
+        <v>1.7207039169161878E-7</v>
+      </c>
+      <c r="AK4">
+        <v>3.8611593638665054E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-6.7141828092136369E-2</v>
+        <v>-6.7577506155236708E-2</v>
       </c>
       <c r="C5">
-        <v>-3.8074557113165959E-6</v>
+        <v>-1.0125287202650485E-6</v>
       </c>
       <c r="D5">
-        <v>-8.8813703861078883E-5</v>
+        <v>-9.1662069276550809E-5</v>
       </c>
       <c r="E5">
-        <v>7.04059088466093E-7</v>
+        <v>7.2372655608077447E-7</v>
       </c>
       <c r="F5">
-        <v>7.71640001077157E-4</v>
+        <v>7.7189469812069598E-4</v>
       </c>
       <c r="G5">
-        <v>6.0338509108765457E-4</v>
+        <v>6.0605709055740241E-4</v>
       </c>
       <c r="H5">
-        <v>1.9141189817709535E-6</v>
+        <v>2.2564648920458597E-6</v>
       </c>
       <c r="I5">
-        <v>-1.266768017101994E-6</v>
+        <v>-1.2062104801512601E-6</v>
       </c>
       <c r="J5">
-        <v>2.9119604119742241E-5</v>
+        <v>3.1450205459534042E-5</v>
       </c>
       <c r="K5">
-        <v>-3.696958500046361E-5</v>
+        <v>-5.0976557426500752E-5</v>
       </c>
       <c r="L5">
-        <v>1.7022206435712516E-5</v>
+        <v>2.7545320341562136E-5</v>
       </c>
       <c r="M5">
-        <v>9.0534653457400804E-5</v>
+        <v>9.5398055983771598E-5</v>
       </c>
       <c r="N5">
-        <v>3.8851368633268165E-6</v>
+        <v>9.218373616370752E-7</v>
       </c>
       <c r="O5">
-        <v>1.9887044408101184E-5</v>
+        <v>1.8334681464097369E-4</v>
       </c>
       <c r="P5">
-        <v>6.6687281837126764E-5</v>
+        <v>1.8337295037597475E-4</v>
       </c>
       <c r="Q5">
-        <v>1.9721802358567661E-4</v>
+        <v>3.1550117172656308E-4</v>
       </c>
       <c r="R5">
-        <v>3.1233631767167084E-4</v>
+        <v>4.3193762635629004E-4</v>
       </c>
       <c r="S5">
-        <v>6.0236184172522675E-5</v>
+        <v>4.7938368605416956E-5</v>
       </c>
       <c r="T5">
-        <v>9.5830998185315785E-5</v>
+        <v>6.2465577631625561E-5</v>
       </c>
       <c r="U5">
-        <v>9.597252574172386E-5</v>
+        <v>9.8668887315317384E-5</v>
       </c>
       <c r="V5">
-        <v>1.5283909496240143E-4</v>
+        <v>9.9921045536888097E-5</v>
       </c>
       <c r="W5">
-        <v>2.3956887689230742E-6</v>
+        <v>1.5622598332758295E-4</v>
       </c>
       <c r="X5">
-        <v>7.8955615727748768E-5</v>
+        <v>3.012660339628685E-6</v>
       </c>
       <c r="Y5">
-        <v>9.5241583454636864E-5</v>
+        <v>8.1774358178389001E-5</v>
       </c>
       <c r="Z5">
-        <v>1.1274510153335826E-4</v>
+        <v>1.0022814040613491E-4</v>
       </c>
       <c r="AA5">
-        <v>1.0456615111869883E-4</v>
+        <v>1.1294832131742948E-4</v>
       </c>
       <c r="AB5">
-        <v>1.0012700069703504E-4</v>
+        <v>1.0792754621088112E-4</v>
       </c>
       <c r="AC5">
-        <v>7.8094905223801097E-5</v>
+        <v>1.0440087796424771E-4</v>
       </c>
       <c r="AD5">
-        <v>-3.3933589015890168E-6</v>
+        <v>8.7995598908211355E-5</v>
       </c>
       <c r="AE5">
-        <v>6.6550596140620881E-5</v>
+        <v>-3.3718059539217433E-6</v>
       </c>
       <c r="AF5">
-        <v>3.2682807131647139E-5</v>
+        <v>7.0619400835429311E-5</v>
       </c>
       <c r="AG5">
-        <v>4.5310012459278965E-4</v>
+        <v>3.2194093384762973E-5</v>
       </c>
       <c r="AH5">
-        <v>2.7023268951671464E-4</v>
+        <v>4.6365365075414378E-4</v>
       </c>
       <c r="AI5">
-        <v>3.975032565901701E-5</v>
+        <v>2.6789813048165665E-4</v>
       </c>
       <c r="AJ5">
-        <v>1.9263754534478935E-3</v>
+        <v>4.4006391162126627E-5</v>
+      </c>
+      <c r="AK5">
+        <v>1.8769304441431326E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-0.19477807145426176</v>
+        <v>-0.19304301046667055</v>
       </c>
       <c r="C6">
-        <v>-5.2476430140872225E-5</v>
+        <v>-4.9706915823994821E-5</v>
       </c>
       <c r="D6">
-        <v>-2.3351807922907149E-4</v>
+        <v>-2.4068025149229753E-4</v>
       </c>
       <c r="E6">
-        <v>1.7846919796071954E-6</v>
+        <v>1.835746389516882E-6</v>
       </c>
       <c r="F6">
-        <v>6.0338509108765457E-4</v>
+        <v>6.0605709055740241E-4</v>
       </c>
       <c r="G6">
-        <v>1.3406267728695402E-3</v>
+        <v>1.349082656413429E-3</v>
       </c>
       <c r="H6">
-        <v>4.1115146258877637E-6</v>
+        <v>4.5637744242005594E-6</v>
       </c>
       <c r="I6">
-        <v>-2.9250542520933301E-7</v>
+        <v>-4.141398815185376E-7</v>
       </c>
       <c r="J6">
-        <v>3.9232672088386843E-5</v>
+        <v>4.596580591212049E-5</v>
       </c>
       <c r="K6">
-        <v>-5.9780350664670587E-5</v>
+        <v>-8.8185817540344216E-5</v>
       </c>
       <c r="L6">
-        <v>-8.0895295335826911E-5</v>
+        <v>-5.3122463979111591E-5</v>
       </c>
       <c r="M6">
-        <v>1.5285996320050295E-4</v>
+        <v>1.5938675155982541E-4</v>
       </c>
       <c r="N6">
-        <v>-3.4092458412065812E-6</v>
+        <v>-4.9198407767295914E-6</v>
       </c>
       <c r="O6">
-        <v>7.4573112165299759E-5</v>
+        <v>3.3070069703272756E-4</v>
       </c>
       <c r="P6">
-        <v>2.2800347010204443E-4</v>
+        <v>4.2172038568871365E-4</v>
       </c>
       <c r="Q6">
-        <v>5.0474300861618078E-4</v>
+        <v>7.0098746898073112E-4</v>
       </c>
       <c r="R6">
-        <v>6.2699526617207774E-4</v>
+        <v>8.2901195042744914E-4</v>
       </c>
       <c r="S6">
-        <v>5.5830596342553666E-5</v>
+        <v>5.3783212641841103E-5</v>
       </c>
       <c r="T6">
-        <v>1.1584869194010102E-4</v>
+        <v>7.4471734655046865E-5</v>
       </c>
       <c r="U6">
-        <v>8.0778707355858665E-5</v>
+        <v>1.3330182516804837E-4</v>
       </c>
       <c r="V6">
-        <v>2.9802725572670557E-4</v>
+        <v>1.0092798404837773E-4</v>
       </c>
       <c r="W6">
-        <v>1.9525428624003857E-5</v>
+        <v>3.1421301598471706E-4</v>
       </c>
       <c r="X6">
-        <v>9.4915320124848445E-5</v>
+        <v>3.4205872364993274E-5</v>
       </c>
       <c r="Y6">
-        <v>1.0792600736010953E-4</v>
+        <v>1.1354767851161617E-4</v>
       </c>
       <c r="Z6">
-        <v>1.7788146414214286E-4</v>
+        <v>1.3062016852951117E-4</v>
       </c>
       <c r="AA6">
-        <v>1.1164731108105066E-4</v>
+        <v>1.9221012261777667E-4</v>
       </c>
       <c r="AB6">
-        <v>1.5515989708899568E-4</v>
+        <v>1.3053671005980333E-4</v>
       </c>
       <c r="AC6">
-        <v>6.9543587995632146E-5</v>
+        <v>1.7824970065623871E-4</v>
       </c>
       <c r="AD6">
-        <v>1.1362807247179032E-5</v>
+        <v>9.8234134385062318E-5</v>
       </c>
       <c r="AE6">
-        <v>5.4142285441301141E-5</v>
+        <v>1.0832750904601662E-5</v>
       </c>
       <c r="AF6">
-        <v>-3.1983117986732934E-5</v>
+        <v>6.2050163587419534E-5</v>
       </c>
       <c r="AG6">
-        <v>9.2174590399475651E-4</v>
+        <v>-3.0025151282731721E-5</v>
       </c>
       <c r="AH6">
-        <v>3.1872475462040972E-4</v>
+        <v>9.3787914242145264E-4</v>
       </c>
       <c r="AI6">
-        <v>1.0550020164738351E-4</v>
+        <v>3.2333373684365876E-4</v>
       </c>
       <c r="AJ6">
-        <v>5.966364424646888E-3</v>
+        <v>1.1732894645242808E-4</v>
+      </c>
+      <c r="AK6">
+        <v>5.9743618877521375E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7">
-        <v>9.179349071412816E-4</v>
+        <v>-4.9789939979269797E-4</v>
       </c>
       <c r="C7">
-        <v>1.0522477708784961E-6</v>
+        <v>5.5423017313807548E-7</v>
       </c>
       <c r="D7">
-        <v>2.7184659981376708E-6</v>
+        <v>1.3389838115938836E-6</v>
       </c>
       <c r="E7">
-        <v>-2.2356133694358433E-8</v>
+        <v>-1.1397941042711271E-8</v>
       </c>
       <c r="F7">
-        <v>1.9141189817709535E-6</v>
+        <v>2.2564648920458597E-6</v>
       </c>
       <c r="G7">
-        <v>4.1115146258877637E-6</v>
+        <v>4.5637744242005594E-6</v>
       </c>
       <c r="H7">
-        <v>1.366943600576944E-6</v>
+        <v>1.5847761590639777E-6</v>
       </c>
       <c r="I7">
-        <v>-1.4102770493738354E-8</v>
+        <v>8.6783474027521943E-8</v>
       </c>
       <c r="J7">
-        <v>8.1188261700373261E-7</v>
+        <v>6.4832177928402255E-7</v>
       </c>
       <c r="K7">
-        <v>-6.1636445047820132E-6</v>
+        <v>-5.5954947612394952E-6</v>
       </c>
       <c r="L7">
-        <v>1.4368160504254122E-5</v>
+        <v>1.047707262291519E-5</v>
       </c>
       <c r="M7">
-        <v>-4.7598437233549348E-8</v>
+        <v>-3.4051743053824907E-8</v>
       </c>
       <c r="N7">
-        <v>8.4526913347212084E-7</v>
+        <v>1.0147341376593265E-6</v>
       </c>
       <c r="O7">
-        <v>-2.5147113312176582E-6</v>
+        <v>1.8440773928599409E-6</v>
       </c>
       <c r="P7">
-        <v>-1.2989264387660404E-6</v>
+        <v>3.7781763872483777E-6</v>
       </c>
       <c r="Q7">
-        <v>-2.6302003537715307E-6</v>
+        <v>3.4322112359841457E-6</v>
       </c>
       <c r="R7">
-        <v>-5.0225097027004704E-6</v>
+        <v>7.1163180188638244E-7</v>
       </c>
       <c r="S7">
-        <v>2.3588198672074565E-6</v>
+        <v>2.4227850722906905E-5</v>
       </c>
       <c r="T7">
-        <v>3.5001054865951571E-7</v>
+        <v>2.3229616815783743E-6</v>
       </c>
       <c r="U7">
-        <v>-3.9862920963298291E-7</v>
+        <v>1.1453476489031039E-6</v>
       </c>
       <c r="V7">
-        <v>1.703495506257018E-6</v>
+        <v>-2.6028835468126582E-7</v>
       </c>
       <c r="W7">
-        <v>-8.5142492864077261E-7</v>
+        <v>3.092717140203304E-6</v>
       </c>
       <c r="X7">
-        <v>-1.7605480533951435E-6</v>
+        <v>4.8017675775065705E-8</v>
       </c>
       <c r="Y7">
-        <v>-1.8290996556983381E-6</v>
+        <v>-1.4930872018712604E-6</v>
       </c>
       <c r="Z7">
-        <v>-5.9347365574343759E-7</v>
+        <v>-1.6752464451092201E-6</v>
       </c>
       <c r="AA7">
-        <v>-6.6268718913891386E-7</v>
+        <v>-8.5017929747139469E-7</v>
       </c>
       <c r="AB7">
-        <v>-5.8069306741687717E-7</v>
+        <v>-4.086838399922283E-7</v>
       </c>
       <c r="AC7">
-        <v>-1.1588830227949036E-6</v>
+        <v>-8.617180017449097E-7</v>
       </c>
       <c r="AD7">
-        <v>4.6884819359158843E-7</v>
+        <v>-1.681739772896383E-6</v>
       </c>
       <c r="AE7">
-        <v>-6.7401625497084514E-7</v>
+        <v>4.5961633301372582E-7</v>
       </c>
       <c r="AF7">
-        <v>-1.0928369990262868E-6</v>
+        <v>-1.9807745785110434E-7</v>
       </c>
       <c r="AG7">
-        <v>6.0083975362203737E-6</v>
+        <v>-7.4218462676764583E-7</v>
       </c>
       <c r="AH7">
-        <v>-2.2507651409347693E-6</v>
+        <v>1.1946016358840454E-5</v>
       </c>
       <c r="AI7">
-        <v>-4.446363690807167E-6</v>
+        <v>-2.3773646068840399E-6</v>
       </c>
       <c r="AJ7">
-        <v>-1.5710077137610456E-4</v>
+        <v>-1.7712939310388445E-6</v>
+      </c>
+      <c r="AK7">
+        <v>-1.363486099422297E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8">
-        <v>1.2067186317625013E-3</v>
+        <v>5.7966026206402669E-4</v>
       </c>
       <c r="C8">
-        <v>-1.5721346114236054E-6</v>
+        <v>-1.9126548327973104E-6</v>
       </c>
       <c r="D8">
-        <v>1.554393545419037E-6</v>
+        <v>9.492716960845019E-7</v>
       </c>
       <c r="E8">
-        <v>-1.6840124774400571E-8</v>
+        <v>-1.1895212507823611E-8</v>
       </c>
       <c r="F8">
-        <v>-1.266768017101994E-6</v>
+        <v>-1.2062104801512601E-6</v>
       </c>
       <c r="G8">
-        <v>-2.9250542520933301E-7</v>
+        <v>-4.141398815185376E-7</v>
       </c>
       <c r="H8">
-        <v>-1.4102770493738354E-8</v>
+        <v>8.6783474027521943E-8</v>
       </c>
       <c r="I8">
-        <v>1.8927993372343428E-6</v>
+        <v>1.9457293399632053E-6</v>
       </c>
       <c r="J8">
-        <v>5.8612024071847148E-7</v>
+        <v>3.1829345177485859E-7</v>
       </c>
       <c r="K8">
-        <v>-4.010610550763212E-6</v>
+        <v>-2.6099497343552858E-6</v>
       </c>
       <c r="L8">
-        <v>1.0902248441058385E-5</v>
+        <v>7.8459038006065026E-6</v>
       </c>
       <c r="M8">
-        <v>1.1888284800602007E-6</v>
+        <v>8.7665022545539856E-7</v>
       </c>
       <c r="N8">
-        <v>-1.9545516650572647E-6</v>
+        <v>-1.6826384379230505E-6</v>
       </c>
       <c r="O8">
-        <v>2.4503097419290602E-6</v>
+        <v>-5.3152547705610922E-6</v>
       </c>
       <c r="P8">
-        <v>-2.3793719653035117E-6</v>
+        <v>-7.2748881054494263E-6</v>
       </c>
       <c r="Q8">
-        <v>-2.4459121589099789E-6</v>
+        <v>-7.1258094243413821E-6</v>
       </c>
       <c r="R8">
-        <v>-5.406039898040916E-6</v>
+        <v>-1.0410241289253084E-5</v>
       </c>
       <c r="S8">
-        <v>-4.3557268296095345E-6</v>
+        <v>1.0389277140461733E-5</v>
       </c>
       <c r="T8">
-        <v>-1.3357047113760526E-6</v>
+        <v>-4.7990106867988911E-6</v>
       </c>
       <c r="U8">
-        <v>-2.2323289659488909E-6</v>
+        <v>-1.6941281760876918E-6</v>
       </c>
       <c r="V8">
-        <v>2.6131621558204792E-6</v>
+        <v>-2.7726538681246228E-6</v>
       </c>
       <c r="W8">
-        <v>-2.9241880685007898E-6</v>
+        <v>2.6991316569839996E-6</v>
       </c>
       <c r="X8">
-        <v>-5.3719504905100631E-6</v>
+        <v>-3.1289662888962232E-6</v>
       </c>
       <c r="Y8">
-        <v>-3.0018834323329441E-6</v>
+        <v>-5.8222573941848433E-6</v>
       </c>
       <c r="Z8">
-        <v>-4.6548603083457823E-6</v>
+        <v>-3.5262393750526842E-6</v>
       </c>
       <c r="AA8">
-        <v>-6.6409526917100305E-7</v>
+        <v>-5.1620181532873745E-6</v>
       </c>
       <c r="AB8">
-        <v>-2.499702730235091E-6</v>
+        <v>-1.2000576641078251E-6</v>
       </c>
       <c r="AC8">
-        <v>-4.0240387976389169E-6</v>
+        <v>-3.3450630693664571E-6</v>
       </c>
       <c r="AD8">
-        <v>8.4329243219766754E-7</v>
+        <v>-5.4723714933859168E-6</v>
       </c>
       <c r="AE8">
-        <v>-4.5890397871714276E-8</v>
+        <v>8.6635860411326022E-7</v>
       </c>
       <c r="AF8">
-        <v>-6.1225293075728576E-7</v>
+        <v>-6.0544934073119526E-8</v>
       </c>
       <c r="AG8">
-        <v>1.0999525334837217E-5</v>
+        <v>-5.5364655702988702E-7</v>
       </c>
       <c r="AH8">
-        <v>-2.9610503853712099E-6</v>
+        <v>1.3163100871880702E-5</v>
       </c>
       <c r="AI8">
-        <v>1.354345390042995E-6</v>
+        <v>-3.1333563733720139E-6</v>
       </c>
       <c r="AJ8">
-        <v>-1.3596710315837336E-4</v>
+        <v>2.2794908997929949E-6</v>
+      </c>
+      <c r="AK8">
+        <v>-1.2014489749146459E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
       <c r="B9">
-        <v>0.54502179339268131</v>
+        <v>0.54593960707814093</v>
       </c>
       <c r="C9">
-        <v>2.2437700208049373E-4</v>
+        <v>2.2606754347015756E-4</v>
       </c>
       <c r="D9">
-        <v>1.3018552754448672E-4</v>
+        <v>1.2432899791148537E-4</v>
       </c>
       <c r="E9">
-        <v>-1.7956616168644972E-6</v>
+        <v>-1.7500593829169562E-6</v>
       </c>
       <c r="F9">
-        <v>2.9119604119742241E-5</v>
+        <v>3.1450205459534042E-5</v>
       </c>
       <c r="G9">
-        <v>3.9232672088386843E-5</v>
+        <v>4.596580591212049E-5</v>
       </c>
       <c r="H9">
-        <v>8.1188261700373261E-7</v>
+        <v>6.4832177928402255E-7</v>
       </c>
       <c r="I9">
-        <v>5.8612024071847148E-7</v>
+        <v>3.1829345177485859E-7</v>
       </c>
       <c r="J9">
-        <v>1.5370549329779854E-3</v>
+        <v>1.537818287688899E-3</v>
       </c>
       <c r="K9">
-        <v>-5.4384791717255619E-4</v>
+        <v>-5.4323105698897802E-4</v>
       </c>
       <c r="L9">
-        <v>3.8541340187419487E-4</v>
+        <v>3.9869450526805309E-4</v>
       </c>
       <c r="M9">
-        <v>4.3859134329022787E-5</v>
+        <v>4.6598309352700035E-5</v>
       </c>
       <c r="N9">
-        <v>-9.6903543102085321E-5</v>
+        <v>-9.6536579943353959E-5</v>
       </c>
       <c r="O9">
-        <v>1.6724567353318E-4</v>
+        <v>2.4822187074786842E-4</v>
       </c>
       <c r="P9">
-        <v>2.7319531658585508E-4</v>
+        <v>3.3953297942277886E-4</v>
       </c>
       <c r="Q9">
-        <v>2.9595303695683088E-4</v>
+        <v>3.6497484954214334E-4</v>
       </c>
       <c r="R9">
-        <v>3.1373408289543891E-4</v>
+        <v>3.8724658507452908E-4</v>
       </c>
       <c r="S9">
-        <v>8.2361904878769767E-5</v>
+        <v>7.1415797844519258E-7</v>
       </c>
       <c r="T9">
-        <v>7.9056309048916758E-5</v>
+        <v>1.0143503141722308E-4</v>
       </c>
       <c r="U9">
-        <v>6.8408728318502675E-5</v>
+        <v>9.4236726205878889E-5</v>
       </c>
       <c r="V9">
-        <v>1.6833011569639312E-4</v>
+        <v>8.5579691037597819E-5</v>
       </c>
       <c r="W9">
-        <v>6.6715838838333065E-5</v>
+        <v>1.8536249974312094E-4</v>
       </c>
       <c r="X9">
-        <v>1.3614572635217226E-4</v>
+        <v>8.4839958406518392E-5</v>
       </c>
       <c r="Y9">
-        <v>8.2425218318142872E-5</v>
+        <v>1.5282463963091895E-4</v>
       </c>
       <c r="Z9">
-        <v>8.6507825143325293E-5</v>
+        <v>1.0123109445027596E-4</v>
       </c>
       <c r="AA9">
-        <v>9.0696321914166683E-5</v>
+        <v>1.043338556022083E-4</v>
       </c>
       <c r="AB9">
-        <v>1.0349654424098834E-4</v>
+        <v>1.0777022002765048E-4</v>
       </c>
       <c r="AC9">
-        <v>7.4101128021786125E-5</v>
+        <v>1.2287408525134128E-4</v>
       </c>
       <c r="AD9">
-        <v>3.5083785979385894E-5</v>
+        <v>9.491423626743138E-5</v>
       </c>
       <c r="AE9">
-        <v>-1.2861641145956582E-5</v>
+        <v>3.4442340028185004E-5</v>
       </c>
       <c r="AF9">
-        <v>-5.1712611672770034E-5</v>
+        <v>-6.3836646752876518E-6</v>
       </c>
       <c r="AG9">
-        <v>2.2579108128102025E-4</v>
+        <v>-4.731433493148294E-5</v>
       </c>
       <c r="AH9">
-        <v>1.0827650927691234E-5</v>
+        <v>2.3386879021880947E-4</v>
       </c>
       <c r="AI9">
-        <v>-9.1440888721767543E-7</v>
+        <v>1.9553274917460169E-5</v>
       </c>
       <c r="AJ9">
-        <v>-2.8645346773594734E-3</v>
+        <v>2.7691835204071637E-6</v>
+      </c>
+      <c r="AK9">
+        <v>-2.7392343950950627E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10">
-        <v>0.53933856767342625</v>
+        <v>0.53966078836915199</v>
       </c>
       <c r="C10">
-        <v>-2.5883515186912658E-5</v>
+        <v>-2.6200416479750711E-5</v>
       </c>
       <c r="D10">
-        <v>4.3521903173615009E-4</v>
+        <v>4.5853917780486588E-4</v>
       </c>
       <c r="E10">
-        <v>-3.6780447692297317E-6</v>
+        <v>-3.8701072939239475E-6</v>
       </c>
       <c r="F10">
-        <v>-3.696958500046361E-5</v>
+        <v>-5.0976557426500752E-5</v>
       </c>
       <c r="G10">
-        <v>-5.9780350664670587E-5</v>
+        <v>-8.8185817540344216E-5</v>
       </c>
       <c r="H10">
-        <v>-6.1636445047820132E-6</v>
+        <v>-5.5954947612394952E-6</v>
       </c>
       <c r="I10">
-        <v>-4.010610550763212E-6</v>
+        <v>-2.6099497343552858E-6</v>
       </c>
       <c r="J10">
-        <v>-5.4384791717255619E-4</v>
+        <v>-5.4323105698897802E-4</v>
       </c>
       <c r="K10">
-        <v>4.3431214293860989E-3</v>
+        <v>4.4288630388019303E-3</v>
       </c>
       <c r="L10">
-        <v>-1.3890007993192406E-3</v>
+        <v>-1.4425190334258734E-3</v>
       </c>
       <c r="M10">
-        <v>9.917496146197172E-5</v>
+        <v>9.1527031834853648E-5</v>
       </c>
       <c r="N10">
-        <v>5.9490209451641077E-6</v>
+        <v>7.3464897662169288E-6</v>
       </c>
       <c r="O10">
-        <v>-3.0663834451353107E-4</v>
+        <v>-6.2397604930264014E-4</v>
       </c>
       <c r="P10">
-        <v>-4.4962472412731706E-4</v>
+        <v>-7.0676914867222372E-4</v>
       </c>
       <c r="Q10">
-        <v>-5.1960355568191855E-4</v>
+        <v>-7.891575143505118E-4</v>
       </c>
       <c r="R10">
-        <v>-5.8141760891748098E-4</v>
+        <v>-8.6435099858807318E-4</v>
       </c>
       <c r="S10">
-        <v>7.7103587899369184E-5</v>
+        <v>6.4066955246437716E-6</v>
       </c>
       <c r="T10">
-        <v>-6.5919790478820642E-5</v>
+        <v>2.3486179167421864E-5</v>
       </c>
       <c r="U10">
-        <v>-3.3112399260010542E-5</v>
+        <v>-1.2178106605722962E-4</v>
       </c>
       <c r="V10">
-        <v>2.2582490595822804E-5</v>
+        <v>-9.2276065849091447E-5</v>
       </c>
       <c r="W10">
-        <v>-3.6047261115626505E-5</v>
+        <v>-2.9154488150160904E-5</v>
       </c>
       <c r="X10">
-        <v>2.0361368658764964E-5</v>
+        <v>-8.9938429641725319E-5</v>
       </c>
       <c r="Y10">
-        <v>2.148986686182925E-5</v>
+        <v>-3.0445186848698444E-5</v>
       </c>
       <c r="Z10">
-        <v>2.0503668398917652E-5</v>
+        <v>-3.6313395668926933E-5</v>
       </c>
       <c r="AA10">
-        <v>-1.8427814085231198E-6</v>
+        <v>-2.6394766076543244E-5</v>
       </c>
       <c r="AB10">
-        <v>1.805253008330468E-5</v>
+        <v>-5.6129326901471419E-5</v>
       </c>
       <c r="AC10">
-        <v>-1.6859999182384892E-4</v>
+        <v>-3.9809157249165103E-5</v>
       </c>
       <c r="AD10">
-        <v>2.0788056616144381E-6</v>
+        <v>-2.4101862783543551E-4</v>
       </c>
       <c r="AE10">
-        <v>2.7425430887820842E-5</v>
+        <v>5.1299779366311814E-6</v>
       </c>
       <c r="AF10">
-        <v>1.2727223665245642E-4</v>
+        <v>2.1554091317274073E-6</v>
       </c>
       <c r="AG10">
-        <v>1.3401368754289208E-4</v>
+        <v>1.2060495454712457E-4</v>
       </c>
       <c r="AH10">
-        <v>-9.7486362401097773E-5</v>
+        <v>1.0773482138722815E-4</v>
       </c>
       <c r="AI10">
-        <v>1.7391444803668073E-4</v>
+        <v>-1.3642704160463266E-4</v>
       </c>
       <c r="AJ10">
-        <v>-1.1585531045409082E-2</v>
+        <v>1.665610691439271E-4</v>
+      </c>
+      <c r="AK10">
+        <v>-1.2096474722976279E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11">
-        <v>0.54156889379557649</v>
+        <v>0.55849794881507531</v>
       </c>
       <c r="C11">
-        <v>1.7346155067771894E-4</v>
+        <v>1.8436291178712874E-4</v>
       </c>
       <c r="D11">
-        <v>1.3840011001892919E-4</v>
+        <v>1.4140755232654786E-4</v>
       </c>
       <c r="E11">
-        <v>-1.1979020484123338E-6</v>
+        <v>-1.2266843969255167E-6</v>
       </c>
       <c r="F11">
-        <v>1.7022206435712516E-5</v>
+        <v>2.7545320341562136E-5</v>
       </c>
       <c r="G11">
-        <v>-8.0895295335826911E-5</v>
+        <v>-5.3122463979111591E-5</v>
       </c>
       <c r="H11">
-        <v>1.4368160504254122E-5</v>
+        <v>1.047707262291519E-5</v>
       </c>
       <c r="I11">
-        <v>1.0902248441058385E-5</v>
+        <v>7.8459038006065026E-6</v>
       </c>
       <c r="J11">
-        <v>3.8541340187419487E-4</v>
+        <v>3.9869450526805309E-4</v>
       </c>
       <c r="K11">
-        <v>-1.3890007993192406E-3</v>
+        <v>-1.4425190334258734E-3</v>
       </c>
       <c r="L11">
-        <v>1.8913859555549297E-3</v>
+        <v>2.0012230546572226E-3</v>
       </c>
       <c r="M11">
-        <v>-3.1620485486537418E-5</v>
+        <v>-2.1820778645375584E-5</v>
       </c>
       <c r="N11">
-        <v>8.1310806291640624E-5</v>
+        <v>7.6940728052753317E-5</v>
       </c>
       <c r="O11">
-        <v>5.246557819793404E-4</v>
+        <v>9.1823379797202967E-4</v>
       </c>
       <c r="P11">
-        <v>1.0325378832722908E-3</v>
+        <v>1.341409273277399E-3</v>
       </c>
       <c r="Q11">
-        <v>1.1233547844473654E-3</v>
+        <v>1.4281851826411806E-3</v>
       </c>
       <c r="R11">
-        <v>1.1871256135702626E-3</v>
+        <v>1.5139346696045168E-3</v>
       </c>
       <c r="S11">
-        <v>-2.0656058174984811E-4</v>
+        <v>-3.2619189929830784E-4</v>
       </c>
       <c r="T11">
-        <v>-1.2914510941831533E-5</v>
+        <v>-1.2785247699368752E-4</v>
       </c>
       <c r="U11">
-        <v>-6.53506952899615E-5</v>
+        <v>5.7549412386469646E-5</v>
       </c>
       <c r="V11">
-        <v>-9.1236113159791181E-5</v>
+        <v>1.670138549767072E-5</v>
       </c>
       <c r="W11">
-        <v>-7.1075564574340708E-5</v>
+        <v>-3.1393311505431912E-5</v>
       </c>
       <c r="X11">
-        <v>-1.2883630584387563E-4</v>
+        <v>-2.7629103894325803E-6</v>
       </c>
       <c r="Y11">
-        <v>-1.4135757918639583E-4</v>
+        <v>-5.3338477968464283E-5</v>
       </c>
       <c r="Z11">
-        <v>-1.0570516638756669E-4</v>
+        <v>-6.0902678793040271E-5</v>
       </c>
       <c r="AA11">
-        <v>-6.7450027553259302E-5</v>
+        <v>-2.6459056302386742E-5</v>
       </c>
       <c r="AB11">
-        <v>-1.526014273797306E-4</v>
+        <v>8.3289354075553879E-6</v>
       </c>
       <c r="AC11">
-        <v>-5.8743600567605185E-5</v>
+        <v>-6.0247860903062198E-5</v>
       </c>
       <c r="AD11">
-        <v>1.110414137248984E-5</v>
+        <v>4.7693767975935143E-5</v>
       </c>
       <c r="AE11">
-        <v>-4.3693960598504254E-5</v>
+        <v>7.9365520947956075E-6</v>
       </c>
       <c r="AF11">
-        <v>-5.9181699399147919E-5</v>
+        <v>-1.9814880131643941E-5</v>
       </c>
       <c r="AG11">
-        <v>-2.6014591300140997E-4</v>
+        <v>-4.6723274659226982E-5</v>
       </c>
       <c r="AH11">
-        <v>-9.0065154026749972E-5</v>
+        <v>-2.872320429850991E-4</v>
       </c>
       <c r="AI11">
-        <v>-2.920123339211773E-4</v>
+        <v>-4.6958022544065295E-5</v>
       </c>
       <c r="AJ11">
-        <v>-6.8207952601999546E-3</v>
+        <v>-3.1737142395660251E-4</v>
+      </c>
+      <c r="AK11">
+        <v>-6.9006113307261748E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12">
-        <v>0.5356682365726253</v>
+        <v>0.53695442962402862</v>
       </c>
       <c r="C12">
-        <v>-4.7123762735964424E-5</v>
+        <v>-4.9935437549654063E-5</v>
       </c>
       <c r="D12">
-        <v>-5.5305338397203772E-5</v>
+        <v>-5.8102323524528762E-5</v>
       </c>
       <c r="E12">
-        <v>3.7205717380510119E-7</v>
+        <v>3.9580847772757063E-7</v>
       </c>
       <c r="F12">
-        <v>9.0534653457400804E-5</v>
+        <v>9.5398055983771598E-5</v>
       </c>
       <c r="G12">
-        <v>1.5285996320050295E-4</v>
+        <v>1.5938675155982541E-4</v>
       </c>
       <c r="H12">
-        <v>-4.7598437233549348E-8</v>
+        <v>-3.4051743053824907E-8</v>
       </c>
       <c r="I12">
-        <v>1.1888284800602007E-6</v>
+        <v>8.7665022545539856E-7</v>
       </c>
       <c r="J12">
-        <v>4.3859134329022787E-5</v>
+        <v>4.6598309352700035E-5</v>
       </c>
       <c r="K12">
-        <v>9.917496146197172E-5</v>
+        <v>9.1527031834853648E-5</v>
       </c>
       <c r="L12">
-        <v>-3.1620485486537418E-5</v>
+        <v>-2.1820778645375584E-5</v>
       </c>
       <c r="M12">
-        <v>7.3743924970332757E-4</v>
+        <v>7.3356435997316502E-4</v>
       </c>
       <c r="N12">
-        <v>-2.8393964067966457E-4</v>
+        <v>-2.7842480654734978E-4</v>
       </c>
       <c r="O12">
-        <v>2.1263975800500385E-4</v>
+        <v>1.8377394127904796E-4</v>
       </c>
       <c r="P12">
-        <v>2.978478005995211E-4</v>
+        <v>2.9251401488315321E-4</v>
       </c>
       <c r="Q12">
-        <v>4.9304324365008142E-4</v>
+        <v>4.885553180158798E-4</v>
       </c>
       <c r="R12">
-        <v>5.2116261020920612E-4</v>
+        <v>5.2128057228869793E-4</v>
       </c>
       <c r="S12">
-        <v>2.2469540052322907E-5</v>
+        <v>-8.1384547839668763E-6</v>
       </c>
       <c r="T12">
-        <v>4.014841525412584E-5</v>
+        <v>5.3324086425137032E-5</v>
       </c>
       <c r="U12">
-        <v>2.6590709781554848E-5</v>
+        <v>6.2360433835689506E-5</v>
       </c>
       <c r="V12">
-        <v>2.21613825126355E-4</v>
+        <v>5.4083384724044144E-5</v>
       </c>
       <c r="W12">
-        <v>-5.4220208865518637E-7</v>
+        <v>2.4671662517094546E-4</v>
       </c>
       <c r="X12">
-        <v>5.3474595343543774E-5</v>
+        <v>2.3435223645025684E-5</v>
       </c>
       <c r="Y12">
-        <v>2.4204398410527579E-5</v>
+        <v>7.7711380781966778E-5</v>
       </c>
       <c r="Z12">
-        <v>3.8995259556857807E-5</v>
+        <v>5.0106478525074367E-5</v>
       </c>
       <c r="AA12">
-        <v>4.5872317584711429E-5</v>
+        <v>6.5871605897387418E-5</v>
       </c>
       <c r="AB12">
-        <v>2.8815558138892811E-5</v>
+        <v>7.1224902489720266E-5</v>
       </c>
       <c r="AC12">
-        <v>-1.1332842866951384E-5</v>
+        <v>5.4705081980232741E-5</v>
       </c>
       <c r="AD12">
-        <v>4.3275536290433945E-6</v>
+        <v>1.5304337996143445E-5</v>
       </c>
       <c r="AE12">
-        <v>-6.0151603273059079E-5</v>
+        <v>3.62994500967456E-6</v>
       </c>
       <c r="AF12">
-        <v>-8.5291550336128008E-5</v>
+        <v>-5.5042079319060915E-5</v>
       </c>
       <c r="AG12">
-        <v>4.7861534335817658E-4</v>
+        <v>-7.9372285403567639E-5</v>
       </c>
       <c r="AH12">
-        <v>1.1519724639620055E-4</v>
+        <v>4.8615278624124919E-4</v>
       </c>
       <c r="AI12">
-        <v>3.8252509052642987E-4</v>
+        <v>1.3273266088431731E-4</v>
       </c>
       <c r="AJ12">
-        <v>1.0315479854308906E-3</v>
+        <v>3.9275790311003476E-4</v>
+      </c>
+      <c r="AK12">
+        <v>1.1153355799062741E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13">
-        <v>-3.8811949863632213E-2</v>
+        <v>-3.9935957360109207E-2</v>
       </c>
       <c r="C13">
-        <v>6.9941600291891797E-5</v>
+        <v>7.3599279448492624E-5</v>
       </c>
       <c r="D13">
-        <v>4.8159266219989505E-5</v>
+        <v>4.7125845679071333E-5</v>
       </c>
       <c r="E13">
-        <v>-6.2919863360889838E-7</v>
+        <v>-6.235630829777284E-7</v>
       </c>
       <c r="F13">
-        <v>3.8851368633268165E-6</v>
+        <v>9.218373616370752E-7</v>
       </c>
       <c r="G13">
-        <v>-3.4092458412065812E-6</v>
+        <v>-4.9198407767295914E-6</v>
       </c>
       <c r="H13">
-        <v>8.4526913347212084E-7</v>
+        <v>1.0147341376593265E-6</v>
       </c>
       <c r="I13">
-        <v>-1.9545516650572647E-6</v>
+        <v>-1.6826384379230505E-6</v>
       </c>
       <c r="J13">
-        <v>-9.6903543102085321E-5</v>
+        <v>-9.6536579943353959E-5</v>
       </c>
       <c r="K13">
-        <v>5.9490209451641077E-6</v>
+        <v>7.3464897662169288E-6</v>
       </c>
       <c r="L13">
-        <v>8.1310806291640624E-5</v>
+        <v>7.6940728052753317E-5</v>
       </c>
       <c r="M13">
-        <v>-2.8393964067966457E-4</v>
+        <v>-2.7842480654734978E-4</v>
       </c>
       <c r="N13">
-        <v>9.3082587355671723E-4</v>
+        <v>9.2466685937944921E-4</v>
       </c>
       <c r="O13">
-        <v>-2.0734584829474833E-4</v>
+        <v>-9.8142748711984023E-5</v>
       </c>
       <c r="P13">
-        <v>-1.6075124146088226E-4</v>
+        <v>-9.2455343445059415E-5</v>
       </c>
       <c r="Q13">
-        <v>-1.2739222808071517E-4</v>
+        <v>-5.7125712789763688E-5</v>
       </c>
       <c r="R13">
-        <v>-9.8099344641510843E-5</v>
+        <v>-2.9565632003537218E-5</v>
       </c>
       <c r="S13">
-        <v>2.3125903491909996E-5</v>
+        <v>3.5358756637799835E-5</v>
       </c>
       <c r="T13">
-        <v>-6.6327059365275368E-6</v>
+        <v>2.8966191470785983E-6</v>
       </c>
       <c r="U13">
-        <v>3.5962075315635394E-5</v>
+        <v>-2.0134821537692022E-5</v>
       </c>
       <c r="V13">
-        <v>-1.6523935308007683E-5</v>
+        <v>1.9185532280462003E-5</v>
       </c>
       <c r="W13">
-        <v>-2.0768536322806155E-5</v>
+        <v>-2.9936562894084858E-5</v>
       </c>
       <c r="X13">
-        <v>1.6780228941833412E-6</v>
+        <v>-3.597132230272906E-5</v>
       </c>
       <c r="Y13">
-        <v>1.6358507218846292E-5</v>
+        <v>-1.2794118211391752E-5</v>
       </c>
       <c r="Z13">
-        <v>-3.2943889189098884E-5</v>
+        <v>1.1857200517539766E-6</v>
       </c>
       <c r="AA13">
-        <v>-2.6690059767881837E-5</v>
+        <v>-5.1074586637544836E-5</v>
       </c>
       <c r="AB13">
-        <v>2.2221448934820352E-5</v>
+        <v>-4.2406182428843557E-5</v>
       </c>
       <c r="AC13">
-        <v>6.8231468848627841E-5</v>
+        <v>7.0699603840609969E-6</v>
       </c>
       <c r="AD13">
-        <v>9.5240313151064144E-6</v>
+        <v>5.3099876972129817E-5</v>
       </c>
       <c r="AE13">
-        <v>-4.8272027592214132E-6</v>
+        <v>9.9894871184291119E-6</v>
       </c>
       <c r="AF13">
-        <v>1.410395194126141E-5</v>
+        <v>-6.4879262942067981E-6</v>
       </c>
       <c r="AG13">
-        <v>-1.3326387390700175E-4</v>
+        <v>1.0022965829816121E-5</v>
       </c>
       <c r="AH13">
-        <v>-6.7074755479444359E-5</v>
+        <v>-1.3215083105059337E-4</v>
       </c>
       <c r="AI13">
-        <v>-5.3229641321534684E-5</v>
+        <v>-7.3468817721465338E-5</v>
       </c>
       <c r="AJ13">
-        <v>-7.3817653992011871E-4</v>
+        <v>-6.0784182484479872E-5</v>
+      </c>
+      <c r="AK13">
+        <v>-7.829378479813513E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14">
-        <v>0.12328341852920965</v>
+        <v>6.6709481605570747E-2</v>
       </c>
       <c r="C14">
-        <v>1.7349104636785913E-4</v>
+        <v>1.1893908353827507E-4</v>
       </c>
       <c r="D14">
-        <v>1.0804671405246114E-4</v>
+        <v>-1.623718295914317E-5</v>
       </c>
       <c r="E14">
-        <v>-1.0267488268236927E-6</v>
+        <v>-3.02118308794278E-8</v>
       </c>
       <c r="F14">
-        <v>1.9887044408101184E-5</v>
+        <v>1.8334681464097369E-4</v>
       </c>
       <c r="G14">
-        <v>7.4573112165299759E-5</v>
+        <v>3.3070069703272756E-4</v>
       </c>
       <c r="H14">
-        <v>-2.5147113312176582E-6</v>
+        <v>1.8440773928599409E-6</v>
       </c>
       <c r="I14">
-        <v>2.4503097419290602E-6</v>
+        <v>-5.3152547705610922E-6</v>
       </c>
       <c r="J14">
-        <v>1.6724567353318E-4</v>
+        <v>2.4822187074786842E-4</v>
       </c>
       <c r="K14">
-        <v>-3.0663834451353107E-4</v>
+        <v>-6.2397604930264014E-4</v>
       </c>
       <c r="L14">
-        <v>5.246557819793404E-4</v>
+        <v>9.1823379797202967E-4</v>
       </c>
       <c r="M14">
-        <v>2.1263975800500385E-4</v>
+        <v>1.8377394127904796E-4</v>
       </c>
       <c r="N14">
-        <v>-2.0734584829474833E-4</v>
+        <v>-9.8142748711984023E-5</v>
       </c>
       <c r="O14">
-        <v>4.2218648354767525E-3</v>
+        <v>4.9156899290860832E-3</v>
       </c>
       <c r="P14">
-        <v>3.0568791135916679E-3</v>
+        <v>4.0677838580871466E-3</v>
       </c>
       <c r="Q14">
-        <v>3.1319677052564516E-3</v>
+        <v>4.2429681795243908E-3</v>
       </c>
       <c r="R14">
-        <v>3.1433011124164284E-3</v>
+        <v>4.3588349891868486E-3</v>
       </c>
       <c r="S14">
-        <v>-3.0638659811790011E-4</v>
+        <v>2.7416275742890198E-4</v>
       </c>
       <c r="T14">
-        <v>-1.9567610730566076E-4</v>
+        <v>4.5425941400981139E-4</v>
       </c>
       <c r="U14">
-        <v>-2.1008734202103527E-4</v>
+        <v>5.3887264531805499E-4</v>
       </c>
       <c r="V14">
-        <v>-2.4625184040852214E-4</v>
+        <v>5.4516246997962734E-4</v>
       </c>
       <c r="W14">
-        <v>-2.9127495433161005E-4</v>
+        <v>5.0929763837080394E-4</v>
       </c>
       <c r="X14">
-        <v>-2.4473496054505076E-4</v>
+        <v>4.4677085589189499E-4</v>
       </c>
       <c r="Y14">
-        <v>-4.0016429235927476E-4</v>
+        <v>4.678657406572181E-4</v>
       </c>
       <c r="Z14">
-        <v>-2.779011665331229E-4</v>
+        <v>3.4560393461230453E-4</v>
       </c>
       <c r="AA14">
-        <v>-2.5520173982600172E-4</v>
+        <v>4.3892556046235096E-4</v>
       </c>
       <c r="AB14">
-        <v>-2.4305149684916293E-4</v>
+        <v>4.7369731707011748E-4</v>
       </c>
       <c r="AC14">
-        <v>-1.394356059149335E-4</v>
+        <v>5.0881804907443036E-4</v>
       </c>
       <c r="AD14">
-        <v>1.3366301245292824E-5</v>
+        <v>6.3552267416706843E-4</v>
       </c>
       <c r="AE14">
-        <v>-3.1317109501761742E-4</v>
+        <v>-1.2807847623821434E-5</v>
       </c>
       <c r="AF14">
-        <v>-1.9050449404362825E-4</v>
+        <v>-9.7762280146985596E-5</v>
       </c>
       <c r="AG14">
-        <v>3.3214239948988877E-4</v>
+        <v>8.9681582280645884E-7</v>
       </c>
       <c r="AH14">
-        <v>-1.7844598179609945E-4</v>
+        <v>8.6332339376490918E-4</v>
       </c>
       <c r="AI14">
-        <v>-9.2837715544830221E-6</v>
+        <v>2.1318150158074938E-4</v>
       </c>
       <c r="AJ14">
-        <v>-6.0556870308114503E-3</v>
+        <v>2.0634659070800003E-4</v>
+      </c>
+      <c r="AK14">
+        <v>-3.6092604757943696E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0.21941483583499521</v>
+        <v>0.16535373803170331</v>
       </c>
       <c r="C15">
-        <v>1.7179702049738594E-4</v>
+        <v>1.4135553900581472E-4</v>
       </c>
       <c r="D15">
-        <v>7.4387507021934614E-5</v>
+        <v>-2.6719714216222323E-5</v>
       </c>
       <c r="E15">
-        <v>-8.4400853500799518E-7</v>
+        <v>-4.8414401384501578E-8</v>
       </c>
       <c r="F15">
-        <v>6.6687281837126764E-5</v>
+        <v>1.8337295037597475E-4</v>
       </c>
       <c r="G15">
-        <v>2.2800347010204443E-4</v>
+        <v>4.2172038568871365E-4</v>
       </c>
       <c r="H15">
-        <v>-1.2989264387660404E-6</v>
+        <v>3.7781763872483777E-6</v>
       </c>
       <c r="I15">
-        <v>-2.3793719653035117E-6</v>
+        <v>-7.2748881054494263E-6</v>
       </c>
       <c r="J15">
-        <v>2.7319531658585508E-4</v>
+        <v>3.3953297942277886E-4</v>
       </c>
       <c r="K15">
-        <v>-4.4962472412731706E-4</v>
+        <v>-7.0676914867222372E-4</v>
       </c>
       <c r="L15">
-        <v>1.0325378832722908E-3</v>
+        <v>1.341409273277399E-3</v>
       </c>
       <c r="M15">
-        <v>2.978478005995211E-4</v>
+        <v>2.9251401488315321E-4</v>
       </c>
       <c r="N15">
-        <v>-1.6075124146088226E-4</v>
+        <v>-9.2455343445059415E-5</v>
       </c>
       <c r="O15">
-        <v>3.0568791135916679E-3</v>
+        <v>4.0677838580871466E-3</v>
       </c>
       <c r="P15">
-        <v>4.2108854579471899E-3</v>
+        <v>5.3085653518315816E-3</v>
       </c>
       <c r="Q15">
-        <v>3.7255493623848043E-3</v>
+        <v>4.9037283154031094E-3</v>
       </c>
       <c r="R15">
-        <v>3.7755010345921426E-3</v>
+        <v>5.0261839858275793E-3</v>
       </c>
       <c r="S15">
-        <v>-2.7258706811351605E-4</v>
+        <v>4.2468722072888816E-4</v>
       </c>
       <c r="T15">
-        <v>-1.1520178970014869E-4</v>
+        <v>2.6344845288188076E-4</v>
       </c>
       <c r="U15">
-        <v>-1.470378071739744E-4</v>
+        <v>4.1424741579953171E-4</v>
       </c>
       <c r="V15">
-        <v>-3.0514038848139481E-5</v>
+        <v>3.9611479968327005E-4</v>
       </c>
       <c r="W15">
-        <v>-2.4276590035820795E-4</v>
+        <v>5.1735410444571394E-4</v>
       </c>
       <c r="X15">
-        <v>-1.5405488217267328E-4</v>
+        <v>2.8800816193008888E-4</v>
       </c>
       <c r="Y15">
-        <v>-2.8261753375442324E-4</v>
+        <v>3.5404783483078926E-4</v>
       </c>
       <c r="Z15">
-        <v>-1.2534493678949352E-4</v>
+        <v>2.5737123016834657E-4</v>
       </c>
       <c r="AA15">
-        <v>-1.348706046294364E-4</v>
+        <v>3.7735599968097104E-4</v>
       </c>
       <c r="AB15">
-        <v>-1.4211090915036955E-4</v>
+        <v>3.8539126972713268E-4</v>
       </c>
       <c r="AC15">
-        <v>-3.4721559293059492E-6</v>
+        <v>3.9466224684815308E-4</v>
       </c>
       <c r="AD15">
-        <v>1.5022519824091113E-5</v>
+        <v>5.6294639400246383E-4</v>
       </c>
       <c r="AE15">
-        <v>-3.045385356129099E-4</v>
+        <v>-3.3358311870261429E-6</v>
       </c>
       <c r="AF15">
-        <v>-2.1843155481892826E-4</v>
+        <v>-1.366271549274088E-4</v>
       </c>
       <c r="AG15">
-        <v>7.6799750243809967E-4</v>
+        <v>-8.3912234266735085E-5</v>
       </c>
       <c r="AH15">
-        <v>-1.0795353988602785E-4</v>
+        <v>1.210952013005955E-3</v>
       </c>
       <c r="AI15">
-        <v>1.5402379436889264E-4</v>
+        <v>1.671948722658358E-4</v>
       </c>
       <c r="AJ15">
-        <v>-5.4009401585079896E-3</v>
+        <v>3.2293461944150198E-4</v>
+      </c>
+      <c r="AK15">
+        <v>-3.7608584647295974E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0.25542190814661131</v>
+        <v>0.20265575733264535</v>
       </c>
       <c r="C16">
-        <v>1.1421760023383173E-4</v>
+        <v>8.2043532908925146E-5</v>
       </c>
       <c r="D16">
-        <v>-5.6845342394890674E-5</v>
+        <v>-1.6607347054710571E-4</v>
       </c>
       <c r="E16">
-        <v>2.1675169286545954E-7</v>
+        <v>1.0756139674487257E-6</v>
       </c>
       <c r="F16">
-        <v>1.9721802358567661E-4</v>
+        <v>3.1550117172656308E-4</v>
       </c>
       <c r="G16">
-        <v>5.0474300861618078E-4</v>
+        <v>7.0098746898073112E-4</v>
       </c>
       <c r="H16">
-        <v>-2.6302003537715307E-6</v>
+        <v>3.4322112359841457E-6</v>
       </c>
       <c r="I16">
-        <v>-2.4459121589099789E-6</v>
+        <v>-7.1258094243413821E-6</v>
       </c>
       <c r="J16">
-        <v>2.9595303695683088E-4</v>
+        <v>3.6497484954214334E-4</v>
       </c>
       <c r="K16">
-        <v>-5.1960355568191855E-4</v>
+        <v>-7.891575143505118E-4</v>
       </c>
       <c r="L16">
-        <v>1.1233547844473654E-3</v>
+        <v>1.4281851826411806E-3</v>
       </c>
       <c r="M16">
-        <v>4.9304324365008142E-4</v>
+        <v>4.885553180158798E-4</v>
       </c>
       <c r="N16">
-        <v>-1.2739222808071517E-4</v>
+        <v>-5.7125712789763688E-5</v>
       </c>
       <c r="O16">
-        <v>3.1319677052564516E-3</v>
+        <v>4.2429681795243908E-3</v>
       </c>
       <c r="P16">
-        <v>3.7255493623848043E-3</v>
+        <v>4.9037283154031094E-3</v>
       </c>
       <c r="Q16">
-        <v>4.5204980908480777E-3</v>
+        <v>5.7843740002046619E-3</v>
       </c>
       <c r="R16">
-        <v>4.1714432028223721E-3</v>
+        <v>5.5084890520473067E-3</v>
       </c>
       <c r="S16">
-        <v>-7.7152194454076575E-5</v>
+        <v>5.3063009618429581E-4</v>
       </c>
       <c r="T16">
-        <v>1.389431010289854E-4</v>
+        <v>4.7028472541138836E-4</v>
       </c>
       <c r="U16">
-        <v>9.7995996973948302E-5</v>
+        <v>6.7633500551217429E-4</v>
       </c>
       <c r="V16">
-        <v>3.9015399566231005E-4</v>
+        <v>6.4779434250588817E-4</v>
       </c>
       <c r="W16">
-        <v>5.6599587270442188E-5</v>
+        <v>9.5046289104455542E-4</v>
       </c>
       <c r="X16">
-        <v>9.5060662162425261E-5</v>
+        <v>5.9656680418134801E-4</v>
       </c>
       <c r="Y16">
-        <v>-7.3358354011554376E-5</v>
+        <v>6.1238461550212203E-4</v>
       </c>
       <c r="Z16">
-        <v>1.2070455831876699E-4</v>
+        <v>4.7357048850340091E-4</v>
       </c>
       <c r="AA16">
-        <v>1.3673858727443391E-4</v>
+        <v>6.2852340696331458E-4</v>
       </c>
       <c r="AB16">
-        <v>1.2068254732219038E-4</v>
+        <v>6.6662198554022327E-4</v>
       </c>
       <c r="AC16">
-        <v>2.8691857311444234E-4</v>
+        <v>6.6687806717807981E-4</v>
       </c>
       <c r="AD16">
-        <v>1.4594272762942539E-5</v>
+        <v>8.6476466028424662E-4</v>
       </c>
       <c r="AE16">
-        <v>-2.8399492062849735E-4</v>
+        <v>-4.0327157283170044E-6</v>
       </c>
       <c r="AF16">
-        <v>-2.1331045252778112E-4</v>
+        <v>-1.152901468668294E-4</v>
       </c>
       <c r="AG16">
-        <v>1.6219072450019865E-3</v>
+        <v>-7.7369112444771387E-5</v>
       </c>
       <c r="AH16">
-        <v>1.4358507471572352E-4</v>
+        <v>2.0960225345401907E-3</v>
       </c>
       <c r="AI16">
-        <v>1.7705970971344402E-4</v>
+        <v>4.0748601460296281E-4</v>
       </c>
       <c r="AJ16">
-        <v>-2.0786250874296266E-3</v>
+        <v>3.5848104095381858E-4</v>
+      </c>
+      <c r="AK16">
+        <v>-3.3468602507928484E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0.43057380574011778</v>
+        <v>0.37511250992989437</v>
       </c>
       <c r="C17">
-        <v>9.9763474469805743E-5</v>
+        <v>7.1459089857877061E-5</v>
       </c>
       <c r="D17">
-        <v>-2.9695162008504207E-5</v>
+        <v>-1.3921603985933041E-4</v>
       </c>
       <c r="E17">
-        <v>3.6918070128258711E-8</v>
+        <v>8.9359546689148658E-7</v>
       </c>
       <c r="F17">
-        <v>3.1233631767167084E-4</v>
+        <v>4.3193762635629004E-4</v>
       </c>
       <c r="G17">
-        <v>6.2699526617207774E-4</v>
+        <v>8.2901195042744914E-4</v>
       </c>
       <c r="H17">
-        <v>-5.0225097027004704E-6</v>
+        <v>7.1163180188638244E-7</v>
       </c>
       <c r="I17">
-        <v>-5.406039898040916E-6</v>
+        <v>-1.0410241289253084E-5</v>
       </c>
       <c r="J17">
-        <v>3.1373408289543891E-4</v>
+        <v>3.8724658507452908E-4</v>
       </c>
       <c r="K17">
-        <v>-5.8141760891748098E-4</v>
+        <v>-8.6435099858807318E-4</v>
       </c>
       <c r="L17">
-        <v>1.1871256135702626E-3</v>
+        <v>1.5139346696045168E-3</v>
       </c>
       <c r="M17">
-        <v>5.2116261020920612E-4</v>
+        <v>5.2128057228869793E-4</v>
       </c>
       <c r="N17">
-        <v>-9.8099344641510843E-5</v>
+        <v>-2.9565632003537218E-5</v>
       </c>
       <c r="O17">
-        <v>3.1433011124164284E-3</v>
+        <v>4.3588349891868486E-3</v>
       </c>
       <c r="P17">
-        <v>3.7755010345921426E-3</v>
+        <v>5.0261839858275793E-3</v>
       </c>
       <c r="Q17">
-        <v>4.1714432028223721E-3</v>
+        <v>5.5084890520473067E-3</v>
       </c>
       <c r="R17">
-        <v>4.6418134547416392E-3</v>
+        <v>6.0542186305666511E-3</v>
       </c>
       <c r="S17">
-        <v>3.9107419689196187E-5</v>
+        <v>4.9263305894964836E-4</v>
       </c>
       <c r="T17">
-        <v>2.5183174512763201E-4</v>
+        <v>5.8903559766386839E-4</v>
       </c>
       <c r="U17">
-        <v>2.2317780188114804E-4</v>
+        <v>7.9431328506174943E-4</v>
       </c>
       <c r="V17">
-        <v>3.4997174829232668E-4</v>
+        <v>7.7887310748811478E-4</v>
       </c>
       <c r="W17">
-        <v>1.6239503990817883E-4</v>
+        <v>9.1384286830919472E-4</v>
       </c>
       <c r="X17">
-        <v>1.5797289784869962E-4</v>
+        <v>7.0823785451135319E-4</v>
       </c>
       <c r="Y17">
-        <v>-4.2177464930226709E-5</v>
+        <v>6.7896312213133509E-4</v>
       </c>
       <c r="Z17">
-        <v>1.8665381039746241E-4</v>
+        <v>5.1351880990341205E-4</v>
       </c>
       <c r="AA17">
-        <v>2.1313795217272474E-4</v>
+        <v>6.9878651390394247E-4</v>
       </c>
       <c r="AB17">
-        <v>2.3548834513761798E-4</v>
+        <v>7.4925589215152789E-4</v>
       </c>
       <c r="AC17">
-        <v>3.8502130206073248E-4</v>
+        <v>7.8666457975058333E-4</v>
       </c>
       <c r="AD17">
-        <v>8.5850256576550099E-6</v>
+        <v>9.7180379293169885E-4</v>
       </c>
       <c r="AE17">
-        <v>-2.1703180233486892E-4</v>
+        <v>-1.0336742084194987E-5</v>
       </c>
       <c r="AF17">
-        <v>-1.936095120110815E-4</v>
+        <v>-4.3262053502564324E-5</v>
       </c>
       <c r="AG17">
-        <v>1.1596193884992039E-3</v>
+        <v>-5.6985776334853185E-5</v>
       </c>
       <c r="AH17">
-        <v>2.4423396534955328E-4</v>
+        <v>1.6252484531499587E-3</v>
       </c>
       <c r="AI17">
-        <v>3.3118551018452246E-4</v>
+        <v>5.3471701326602075E-4</v>
       </c>
       <c r="AJ17">
-        <v>-2.9939802552018408E-3</v>
+        <v>5.0847586407035909E-4</v>
+      </c>
+      <c r="AK17">
+        <v>-1.2729034716397261E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>26</v>
       </c>
       <c r="B18">
-        <v>0.21059747726097172</v>
+        <v>-0.15485311713647984</v>
       </c>
       <c r="C18">
-        <v>-1.6671860581969492E-4</v>
+        <v>-5.1616644415208798E-5</v>
       </c>
       <c r="D18">
-        <v>-1.4688121829584816E-4</v>
+        <v>-1.4087696292298078E-4</v>
       </c>
       <c r="E18">
-        <v>1.2783184399834584E-6</v>
+        <v>1.117170375334771E-6</v>
       </c>
       <c r="F18">
-        <v>6.0236184172522675E-5</v>
+        <v>4.7938368605416956E-5</v>
       </c>
       <c r="G18">
-        <v>5.5830596342553666E-5</v>
+        <v>5.3783212641841103E-5</v>
       </c>
       <c r="H18">
-        <v>2.3588198672074565E-6</v>
+        <v>2.4227850722906905E-5</v>
       </c>
       <c r="I18">
-        <v>-4.3557268296095345E-6</v>
+        <v>1.0389277140461733E-5</v>
       </c>
       <c r="J18">
-        <v>8.2361904878769767E-5</v>
+        <v>7.1415797844519258E-7</v>
       </c>
       <c r="K18">
-        <v>7.7103587899369184E-5</v>
+        <v>6.4066955246437716E-6</v>
       </c>
       <c r="L18">
-        <v>-2.0656058174984811E-4</v>
+        <v>-3.2619189929830784E-4</v>
       </c>
       <c r="M18">
-        <v>2.2469540052322907E-5</v>
+        <v>-8.1384547839668763E-6</v>
       </c>
       <c r="N18">
-        <v>2.3125903491909996E-5</v>
+        <v>3.5358756637799835E-5</v>
       </c>
       <c r="O18">
-        <v>-3.0638659811790011E-4</v>
+        <v>2.7416275742890198E-4</v>
       </c>
       <c r="P18">
-        <v>-2.7258706811351605E-4</v>
+        <v>4.2468722072888816E-4</v>
       </c>
       <c r="Q18">
-        <v>-7.7152194454076575E-5</v>
+        <v>5.3063009618429581E-4</v>
       </c>
       <c r="R18">
-        <v>3.9107419689196187E-5</v>
+        <v>4.9263305894964836E-4</v>
       </c>
       <c r="S18">
-        <v>5.6442867839185326E-3</v>
+        <v>2.6103512740418525E-3</v>
       </c>
       <c r="T18">
-        <v>2.8224108030806749E-3</v>
+        <v>2.125786497340844E-5</v>
       </c>
       <c r="U18">
-        <v>2.8211232922102964E-3</v>
+        <v>1.1195111871092282E-4</v>
       </c>
       <c r="V18">
-        <v>3.0187701378542164E-3</v>
+        <v>3.2664359254440173E-5</v>
       </c>
       <c r="W18">
-        <v>2.8220749523599053E-3</v>
+        <v>1.7456445650821111E-4</v>
       </c>
       <c r="X18">
-        <v>2.8070951913604981E-3</v>
+        <v>1.1175392799283847E-4</v>
       </c>
       <c r="Y18">
-        <v>2.8035773847667079E-3</v>
+        <v>4.6711134390362724E-5</v>
       </c>
       <c r="Z18">
-        <v>2.8492083462291445E-3</v>
+        <v>3.9976788809224263E-5</v>
       </c>
       <c r="AA18">
-        <v>2.857354682087007E-3</v>
+        <v>-2.1041955767897406E-6</v>
       </c>
       <c r="AB18">
-        <v>2.8771550642812845E-3</v>
+        <v>5.0725580636866874E-5</v>
       </c>
       <c r="AC18">
-        <v>2.9031032178762554E-3</v>
+        <v>-1.4272463930039745E-5</v>
       </c>
       <c r="AD18">
-        <v>-2.4676939088522987E-5</v>
+        <v>-5.2833794686084042E-5</v>
       </c>
       <c r="AE18">
-        <v>1.0407073645614466E-5</v>
+        <v>-1.3659313498668281E-6</v>
       </c>
       <c r="AF18">
-        <v>1.7963388023711365E-4</v>
+        <v>4.9756773546746016E-5</v>
       </c>
       <c r="AG18">
-        <v>1.6216548888864115E-3</v>
+        <v>4.3797475804492398E-5</v>
       </c>
       <c r="AH18">
-        <v>1.3938610653002098E-3</v>
+        <v>6.4085984605168392E-4</v>
       </c>
       <c r="AI18">
-        <v>5.4059553605153438E-5</v>
+        <v>1.9406978048294395E-5</v>
       </c>
       <c r="AJ18">
-        <v>1.9499250104715177E-3</v>
+        <v>2.6581924329379661E-4</v>
+      </c>
+      <c r="AK18">
+        <v>2.0655648568618156E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>27</v>
       </c>
       <c r="B19">
-        <v>9.7825410162857979E-2</v>
+        <v>0.21117728006773107</v>
       </c>
       <c r="C19">
-        <v>-1.5348614172238013E-4</v>
+        <v>-1.5056202710243881E-4</v>
       </c>
       <c r="D19">
-        <v>-1.2886543055131219E-4</v>
+        <v>-1.481777840139295E-4</v>
       </c>
       <c r="E19">
-        <v>1.0740993058092052E-6</v>
+        <v>1.2663215036533011E-6</v>
       </c>
       <c r="F19">
-        <v>9.5830998185315785E-5</v>
+        <v>6.2465577631625561E-5</v>
       </c>
       <c r="G19">
-        <v>1.1584869194010102E-4</v>
+        <v>7.4471734655046865E-5</v>
       </c>
       <c r="H19">
-        <v>3.5001054865951571E-7</v>
+        <v>2.3229616815783743E-6</v>
       </c>
       <c r="I19">
-        <v>-1.3357047113760526E-6</v>
+        <v>-4.7990106867988911E-6</v>
       </c>
       <c r="J19">
-        <v>7.9056309048916758E-5</v>
+        <v>1.0143503141722308E-4</v>
       </c>
       <c r="K19">
-        <v>-6.5919790478820642E-5</v>
+        <v>2.3486179167421864E-5</v>
       </c>
       <c r="L19">
-        <v>-1.2914510941831533E-5</v>
+        <v>-1.2785247699368752E-4</v>
       </c>
       <c r="M19">
-        <v>4.014841525412584E-5</v>
+        <v>5.3324086425137032E-5</v>
       </c>
       <c r="N19">
-        <v>-6.6327059365275368E-6</v>
+        <v>2.8966191470785983E-6</v>
       </c>
       <c r="O19">
-        <v>-1.9567610730566076E-4</v>
+        <v>4.5425941400981139E-4</v>
       </c>
       <c r="P19">
-        <v>-1.1520178970014869E-4</v>
+        <v>2.6344845288188076E-4</v>
       </c>
       <c r="Q19">
-        <v>1.389431010289854E-4</v>
+        <v>4.7028472541138836E-4</v>
       </c>
       <c r="R19">
-        <v>2.5183174512763201E-4</v>
+        <v>5.8903559766386839E-4</v>
       </c>
       <c r="S19">
-        <v>2.8224108030806749E-3</v>
+        <v>2.125786497340844E-5</v>
       </c>
       <c r="T19">
-        <v>3.894513303947955E-3</v>
+        <v>5.6371984815811772E-3</v>
       </c>
       <c r="U19">
-        <v>2.7407868149442825E-3</v>
+        <v>2.8317936564392771E-3</v>
       </c>
       <c r="V19">
-        <v>2.9164084011784712E-3</v>
+        <v>2.8280462880954441E-3</v>
       </c>
       <c r="W19">
-        <v>2.7412509677542315E-3</v>
+        <v>3.0289833406881989E-3</v>
       </c>
       <c r="X19">
-        <v>2.7322353634798291E-3</v>
+        <v>2.8251425947621728E-3</v>
       </c>
       <c r="Y19">
-        <v>2.7338776718379867E-3</v>
+        <v>2.813880954614714E-3</v>
       </c>
       <c r="Z19">
-        <v>2.7794414449557039E-3</v>
+        <v>2.8125130654111661E-3</v>
       </c>
       <c r="AA19">
-        <v>2.7742431474260254E-3</v>
+        <v>2.846025136125304E-3</v>
       </c>
       <c r="AB19">
-        <v>2.7806989327984859E-3</v>
+        <v>2.8629717029838185E-3</v>
       </c>
       <c r="AC19">
-        <v>2.8077222503266226E-3</v>
+        <v>2.8914073089686253E-3</v>
       </c>
       <c r="AD19">
-        <v>-2.1336319976813763E-5</v>
+        <v>2.9419299605024018E-3</v>
       </c>
       <c r="AE19">
-        <v>3.028883529880848E-5</v>
+        <v>-2.4588219424363284E-5</v>
       </c>
       <c r="AF19">
-        <v>7.8062316686907816E-6</v>
+        <v>1.981876578103722E-5</v>
       </c>
       <c r="AG19">
-        <v>1.4414482305536796E-3</v>
+        <v>1.806562385231628E-4</v>
       </c>
       <c r="AH19">
-        <v>1.2622250946694358E-3</v>
+        <v>1.6412509049184532E-3</v>
       </c>
       <c r="AI19">
-        <v>-1.4862027242271343E-4</v>
+        <v>1.3851247432372464E-3</v>
       </c>
       <c r="AJ19">
-        <v>1.3512628544703181E-3</v>
+        <v>4.121615422709486E-5</v>
+      </c>
+      <c r="AK19">
+        <v>1.5078356791364874E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0.1378162677367703</v>
+        <v>0.10027658631026473</v>
       </c>
       <c r="C20">
-        <v>-1.5021995363997715E-4</v>
+        <v>-1.4111586419066676E-4</v>
       </c>
       <c r="D20">
-        <v>-1.266108480801123E-4</v>
+        <v>-1.324284447740201E-4</v>
       </c>
       <c r="E20">
-        <v>1.0642338172260537E-6</v>
+        <v>1.0856234133888444E-6</v>
       </c>
       <c r="F20">
-        <v>9.597252574172386E-5</v>
+        <v>9.8668887315317384E-5</v>
       </c>
       <c r="G20">
-        <v>8.0778707355858665E-5</v>
+        <v>1.3330182516804837E-4</v>
       </c>
       <c r="H20">
-        <v>-3.9862920963298291E-7</v>
+        <v>1.1453476489031039E-6</v>
       </c>
       <c r="I20">
-        <v>-2.2323289659488909E-6</v>
+        <v>-1.6941281760876918E-6</v>
       </c>
       <c r="J20">
-        <v>6.8408728318502675E-5</v>
+        <v>9.4236726205878889E-5</v>
       </c>
       <c r="K20">
-        <v>-3.3112399260010542E-5</v>
+        <v>-1.2178106605722962E-4</v>
       </c>
       <c r="L20">
-        <v>-6.53506952899615E-5</v>
+        <v>5.7549412386469646E-5</v>
       </c>
       <c r="M20">
-        <v>2.6590709781554848E-5</v>
+        <v>6.2360433835689506E-5</v>
       </c>
       <c r="N20">
-        <v>3.5962075315635394E-5</v>
+        <v>-2.0134821537692022E-5</v>
       </c>
       <c r="O20">
-        <v>-2.1008734202103527E-4</v>
+        <v>5.3887264531805499E-4</v>
       </c>
       <c r="P20">
-        <v>-1.470378071739744E-4</v>
+        <v>4.1424741579953171E-4</v>
       </c>
       <c r="Q20">
-        <v>9.7995996973948302E-5</v>
+        <v>6.7633500551217429E-4</v>
       </c>
       <c r="R20">
-        <v>2.2317780188114804E-4</v>
+        <v>7.9431328506174943E-4</v>
       </c>
       <c r="S20">
-        <v>2.8211232922102964E-3</v>
+        <v>1.1195111871092282E-4</v>
       </c>
       <c r="T20">
-        <v>2.7407868149442825E-3</v>
+        <v>2.8317936564392771E-3</v>
       </c>
       <c r="U20">
-        <v>4.2051618101911726E-3</v>
+        <v>3.9155493171841218E-3</v>
       </c>
       <c r="V20">
-        <v>2.8842345932157776E-3</v>
+        <v>2.7577741791902123E-3</v>
       </c>
       <c r="W20">
-        <v>2.747637499496954E-3</v>
+        <v>2.9300220457328056E-3</v>
       </c>
       <c r="X20">
-        <v>2.7294349336426716E-3</v>
+        <v>2.7541349607621223E-3</v>
       </c>
       <c r="Y20">
-        <v>2.7267480872654533E-3</v>
+        <v>2.7473386179332356E-3</v>
       </c>
       <c r="Z20">
-        <v>2.7704629251877472E-3</v>
+        <v>2.7534992231461166E-3</v>
       </c>
       <c r="AA20">
-        <v>2.7653570435845604E-3</v>
+        <v>2.7859573954441023E-3</v>
       </c>
       <c r="AB20">
-        <v>2.7772810581020231E-3</v>
+        <v>2.7886145144306951E-3</v>
       </c>
       <c r="AC20">
-        <v>2.8107077665393489E-3</v>
+        <v>2.8022847674327176E-3</v>
       </c>
       <c r="AD20">
-        <v>-1.5307802830029257E-5</v>
+        <v>2.8549314782281244E-3</v>
       </c>
       <c r="AE20">
-        <v>8.605820344800834E-5</v>
+        <v>-2.1867524591059841E-5</v>
       </c>
       <c r="AF20">
-        <v>-2.2314478866818245E-5</v>
+        <v>4.7089582603104536E-5</v>
       </c>
       <c r="AG20">
-        <v>1.2581305121438706E-3</v>
+        <v>1.1639780296327716E-5</v>
       </c>
       <c r="AH20">
-        <v>1.3185912335190782E-3</v>
+        <v>1.4586428930581043E-3</v>
       </c>
       <c r="AI20">
-        <v>-7.6255679635014344E-5</v>
+        <v>1.2510546866361131E-3</v>
       </c>
       <c r="AJ20">
-        <v>1.2752876262266408E-3</v>
+        <v>-1.5743724308450743E-4</v>
+      </c>
+      <c r="AK20">
+        <v>9.2560924361584709E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="B21">
-        <v>7.9906491017220832E-2</v>
+        <v>0.13808717153851505</v>
       </c>
       <c r="C21">
-        <v>-1.6195532910172876E-4</v>
+        <v>-1.3284621102419502E-4</v>
       </c>
       <c r="D21">
-        <v>-3.4079446313014551E-4</v>
+        <v>-1.2842602683082668E-4</v>
       </c>
       <c r="E21">
-        <v>2.6170418917653986E-6</v>
+        <v>1.0583363867869853E-6</v>
       </c>
       <c r="F21">
-        <v>1.5283909496240143E-4</v>
+        <v>9.9921045536888097E-5</v>
       </c>
       <c r="G21">
-        <v>2.9802725572670557E-4</v>
+        <v>1.0092798404837773E-4</v>
       </c>
       <c r="H21">
-        <v>1.703495506257018E-6</v>
+        <v>-2.6028835468126582E-7</v>
       </c>
       <c r="I21">
-        <v>2.6131621558204792E-6</v>
+        <v>-2.7726538681246228E-6</v>
       </c>
       <c r="J21">
-        <v>1.6833011569639312E-4</v>
+        <v>8.5579691037597819E-5</v>
       </c>
       <c r="K21">
-        <v>2.2582490595822804E-5</v>
+        <v>-9.2276065849091447E-5</v>
       </c>
       <c r="L21">
-        <v>-9.1236113159791181E-5</v>
+        <v>1.670138549767072E-5</v>
       </c>
       <c r="M21">
-        <v>2.21613825126355E-4</v>
+        <v>5.4083384724044144E-5</v>
       </c>
       <c r="N21">
-        <v>-1.6523935308007683E-5</v>
+        <v>1.9185532280462003E-5</v>
       </c>
       <c r="O21">
-        <v>-2.4625184040852214E-4</v>
+        <v>5.4516246997962734E-4</v>
       </c>
       <c r="P21">
-        <v>-3.0514038848139481E-5</v>
+        <v>3.9611479968327005E-4</v>
       </c>
       <c r="Q21">
-        <v>3.9015399566231005E-4</v>
+        <v>6.4779434250588817E-4</v>
       </c>
       <c r="R21">
-        <v>3.4997174829232668E-4</v>
+        <v>7.7887310748811478E-4</v>
       </c>
       <c r="S21">
-        <v>3.0187701378542164E-3</v>
+        <v>3.2664359254440173E-5</v>
       </c>
       <c r="T21">
-        <v>2.9164084011784712E-3</v>
+        <v>2.8280462880954441E-3</v>
       </c>
       <c r="U21">
-        <v>2.8842345932157776E-3</v>
+        <v>2.7577741791902123E-3</v>
       </c>
       <c r="V21">
-        <v>4.8706726995557731E-3</v>
+        <v>4.221283631687116E-3</v>
       </c>
       <c r="W21">
-        <v>2.8853448235494684E-3</v>
+        <v>2.9014830377893644E-3</v>
       </c>
       <c r="X21">
-        <v>2.9220027727354984E-3</v>
+        <v>2.7586715814798138E-3</v>
       </c>
       <c r="Y21">
-        <v>2.9297823637036498E-3</v>
+        <v>2.7434528286471626E-3</v>
       </c>
       <c r="Z21">
-        <v>2.9998439868249255E-3</v>
+        <v>2.7433013281783266E-3</v>
       </c>
       <c r="AA21">
-        <v>2.9671792457865039E-3</v>
+        <v>2.7747657040364283E-3</v>
       </c>
       <c r="AB21">
-        <v>2.9848745436834327E-3</v>
+        <v>2.7789325555003896E-3</v>
       </c>
       <c r="AC21">
-        <v>3.0089750218469666E-3</v>
+        <v>2.7989518739522114E-3</v>
       </c>
       <c r="AD21">
-        <v>3.170680546752861E-6</v>
+        <v>2.8570117779306626E-3</v>
       </c>
       <c r="AE21">
-        <v>-5.0746963250893726E-5</v>
+        <v>-1.5631923637349899E-5</v>
       </c>
       <c r="AF21">
-        <v>-1.2093750229926273E-4</v>
+        <v>9.9420780422664081E-5</v>
       </c>
       <c r="AG21">
-        <v>3.1675296498545865E-3</v>
+        <v>-2.2369923079074416E-5</v>
       </c>
       <c r="AH21">
-        <v>1.4024615115860225E-3</v>
+        <v>1.2818731015259506E-3</v>
       </c>
       <c r="AI21">
-        <v>-6.5097562287870389E-5</v>
+        <v>1.312234074011494E-3</v>
       </c>
       <c r="AJ21">
-        <v>7.3263712788868606E-3</v>
+        <v>-8.4276562516360387E-5</v>
+      </c>
+      <c r="AK21">
+        <v>8.3210776151225116E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>30</v>
       </c>
       <c r="B22">
-        <v>9.5665513940925581E-2</v>
+        <v>8.3239673868843816E-2</v>
       </c>
       <c r="C22">
-        <v>-1.5374721266462254E-4</v>
+        <v>-1.502173557686047E-4</v>
       </c>
       <c r="D22">
-        <v>-1.8431976309869064E-4</v>
+        <v>-3.5086370415512991E-4</v>
       </c>
       <c r="E22">
-        <v>1.5681877424394833E-6</v>
+        <v>2.6780762834552373E-6</v>
       </c>
       <c r="F22">
-        <v>2.3956887689230742E-6</v>
+        <v>1.5622598332758295E-4</v>
       </c>
       <c r="G22">
-        <v>1.9525428624003857E-5</v>
+        <v>3.1421301598471706E-4</v>
       </c>
       <c r="H22">
-        <v>-8.5142492864077261E-7</v>
+        <v>3.092717140203304E-6</v>
       </c>
       <c r="I22">
-        <v>-2.9241880685007898E-6</v>
+        <v>2.6991316569839996E-6</v>
       </c>
       <c r="J22">
-        <v>6.6715838838333065E-5</v>
+        <v>1.8536249974312094E-4</v>
       </c>
       <c r="K22">
-        <v>-3.6047261115626505E-5</v>
+        <v>-2.9154488150160904E-5</v>
       </c>
       <c r="L22">
-        <v>-7.1075564574340708E-5</v>
+        <v>-3.1393311505431912E-5</v>
       </c>
       <c r="M22">
-        <v>-5.4220208865518637E-7</v>
+        <v>2.4671662517094546E-4</v>
       </c>
       <c r="N22">
-        <v>-2.0768536322806155E-5</v>
+        <v>-2.9936562894084858E-5</v>
       </c>
       <c r="O22">
-        <v>-2.9127495433161005E-4</v>
+        <v>5.0929763837080394E-4</v>
       </c>
       <c r="P22">
-        <v>-2.4276590035820795E-4</v>
+        <v>5.1735410444571394E-4</v>
       </c>
       <c r="Q22">
-        <v>5.6599587270442188E-5</v>
+        <v>9.5046289104455542E-4</v>
       </c>
       <c r="R22">
-        <v>1.6239503990817883E-4</v>
+        <v>9.1384286830919472E-4</v>
       </c>
       <c r="S22">
-        <v>2.8220749523599053E-3</v>
+        <v>1.7456445650821111E-4</v>
       </c>
       <c r="T22">
-        <v>2.7412509677542315E-3</v>
+        <v>3.0289833406881989E-3</v>
       </c>
       <c r="U22">
-        <v>2.747637499496954E-3</v>
+        <v>2.9300220457328056E-3</v>
       </c>
       <c r="V22">
-        <v>2.8853448235494684E-3</v>
+        <v>2.9014830377893644E-3</v>
       </c>
       <c r="W22">
-        <v>4.3560006220541214E-3</v>
+        <v>4.891211163251339E-3</v>
       </c>
       <c r="X22">
-        <v>2.7288257793324443E-3</v>
+        <v>2.8978594555717479E-3</v>
       </c>
       <c r="Y22">
-        <v>2.7239778478736357E-3</v>
+        <v>2.9369398302331227E-3</v>
       </c>
       <c r="Z22">
-        <v>2.7647598042917854E-3</v>
+        <v>2.9477334355863072E-3</v>
       </c>
       <c r="AA22">
-        <v>2.7710032542407632E-3</v>
+        <v>3.0064056373992911E-3</v>
       </c>
       <c r="AB22">
-        <v>2.7722039859502368E-3</v>
+        <v>2.9812422227236679E-3</v>
       </c>
       <c r="AC22">
-        <v>2.8021294653456643E-3</v>
+        <v>3.0055928177607494E-3</v>
       </c>
       <c r="AD22">
-        <v>-2.6425382525216891E-5</v>
+        <v>3.0568279746538201E-3</v>
       </c>
       <c r="AE22">
-        <v>1.2219990822727163E-4</v>
+        <v>2.9821535887171089E-6</v>
       </c>
       <c r="AF22">
-        <v>1.5094269393716602E-4</v>
+        <v>-3.4699631699067798E-5</v>
       </c>
       <c r="AG22">
-        <v>1.2052191172634559E-3</v>
+        <v>-1.1923536252575763E-4</v>
       </c>
       <c r="AH22">
-        <v>1.0886711697358593E-3</v>
+        <v>3.2083286898510746E-3</v>
       </c>
       <c r="AI22">
-        <v>-1.8583418055729279E-4</v>
+        <v>1.393858786937349E-3</v>
       </c>
       <c r="AJ22">
-        <v>3.2943547642091358E-3</v>
+        <v>-6.4618926396795847E-5</v>
+      </c>
+      <c r="AK22">
+        <v>7.0299381565938771E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
       <c r="B23">
-        <v>4.8690232491963754E-2</v>
+        <v>9.5548094625685601E-2</v>
       </c>
       <c r="C23">
-        <v>-9.3927476035234286E-5</v>
+        <v>-1.3982838380614354E-4</v>
       </c>
       <c r="D23">
-        <v>-2.1973304192768675E-4</v>
+        <v>-1.9171454975691615E-4</v>
       </c>
       <c r="E23">
-        <v>1.7200474949762988E-6</v>
+        <v>1.606436698605606E-6</v>
       </c>
       <c r="F23">
-        <v>7.8955615727748768E-5</v>
+        <v>3.012660339628685E-6</v>
       </c>
       <c r="G23">
-        <v>9.4915320124848445E-5</v>
+        <v>3.4205872364993274E-5</v>
       </c>
       <c r="H23">
-        <v>-1.7605480533951435E-6</v>
+        <v>4.8017675775065705E-8</v>
       </c>
       <c r="I23">
-        <v>-5.3719504905100631E-6</v>
+        <v>-3.1289662888962232E-6</v>
       </c>
       <c r="J23">
-        <v>1.3614572635217226E-4</v>
+        <v>8.4839958406518392E-5</v>
       </c>
       <c r="K23">
-        <v>2.0361368658764964E-5</v>
+        <v>-8.9938429641725319E-5</v>
       </c>
       <c r="L23">
-        <v>-1.2883630584387563E-4</v>
+        <v>-2.7629103894325803E-6</v>
       </c>
       <c r="M23">
-        <v>5.3474595343543774E-5</v>
+        <v>2.3435223645025684E-5</v>
       </c>
       <c r="N23">
-        <v>1.6780228941833412E-6</v>
+        <v>-3.597132230272906E-5</v>
       </c>
       <c r="O23">
-        <v>-2.4473496054505076E-4</v>
+        <v>4.4677085589189499E-4</v>
       </c>
       <c r="P23">
-        <v>-1.5405488217267328E-4</v>
+        <v>2.8800816193008888E-4</v>
       </c>
       <c r="Q23">
-        <v>9.5060662162425261E-5</v>
+        <v>5.9656680418134801E-4</v>
       </c>
       <c r="R23">
-        <v>1.5797289784869962E-4</v>
+        <v>7.0823785451135319E-4</v>
       </c>
       <c r="S23">
-        <v>2.8070951913604981E-3</v>
+        <v>1.1175392799283847E-4</v>
       </c>
       <c r="T23">
-        <v>2.7322353634798291E-3</v>
+        <v>2.8251425947621728E-3</v>
       </c>
       <c r="U23">
-        <v>2.7294349336426716E-3</v>
+        <v>2.7541349607621223E-3</v>
       </c>
       <c r="V23">
-        <v>2.9220027727354984E-3</v>
+        <v>2.7586715814798138E-3</v>
       </c>
       <c r="W23">
-        <v>2.7288257793324443E-3</v>
+        <v>2.8978594555717479E-3</v>
       </c>
       <c r="X23">
-        <v>3.9087369632180326E-3</v>
+        <v>4.368655466395626E-3</v>
       </c>
       <c r="Y23">
-        <v>2.7396155337880736E-3</v>
+        <v>2.7388657196559672E-3</v>
       </c>
       <c r="Z23">
-        <v>2.7814757821504679E-3</v>
+        <v>2.7362206784021146E-3</v>
       </c>
       <c r="AA23">
-        <v>2.7680760587253809E-3</v>
+        <v>2.7648943525472379E-3</v>
       </c>
       <c r="AB23">
-        <v>2.7737019599909079E-3</v>
+        <v>2.781093112469451E-3</v>
       </c>
       <c r="AC23">
-        <v>2.808666231796412E-3</v>
+        <v>2.7880368855622796E-3</v>
       </c>
       <c r="AD23">
-        <v>-1.3373266889330632E-5</v>
+        <v>2.8430523114158423E-3</v>
       </c>
       <c r="AE23">
-        <v>3.3090932180006224E-5</v>
+        <v>-2.674417115406803E-5</v>
       </c>
       <c r="AF23">
-        <v>-7.8692211453392934E-6</v>
+        <v>1.3502734843439296E-4</v>
       </c>
       <c r="AG23">
-        <v>1.4783579493801613E-3</v>
+        <v>1.5294533671644166E-4</v>
       </c>
       <c r="AH23">
-        <v>1.310138643980044E-3</v>
+        <v>1.2278448892159518E-3</v>
       </c>
       <c r="AI23">
-        <v>-1.3355213415643536E-4</v>
+        <v>1.0759731157713611E-3</v>
       </c>
       <c r="AJ23">
-        <v>4.6841423914621965E-3</v>
+        <v>-1.9262681582776591E-4</v>
+      </c>
+      <c r="AK23">
+        <v>2.9882895462922023E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>32</v>
       </c>
       <c r="B24">
-        <v>2.076349395029568E-2</v>
+        <v>4.9793407901525422E-2</v>
       </c>
       <c r="C24">
-        <v>-1.0860926609857651E-4</v>
+        <v>-7.8900990849105801E-5</v>
       </c>
       <c r="D24">
-        <v>-1.7277896348635857E-4</v>
+        <v>-2.21466355329724E-4</v>
       </c>
       <c r="E24">
-        <v>1.3757251940924324E-6</v>
+        <v>1.7147525672501801E-6</v>
       </c>
       <c r="F24">
-        <v>9.5241583454636864E-5</v>
+        <v>8.1774358178389001E-5</v>
       </c>
       <c r="G24">
-        <v>1.0792600736010953E-4</v>
+        <v>1.1354767851161617E-4</v>
       </c>
       <c r="H24">
-        <v>-1.8290996556983381E-6</v>
+        <v>-1.4930872018712604E-6</v>
       </c>
       <c r="I24">
-        <v>-3.0018834323329441E-6</v>
+        <v>-5.8222573941848433E-6</v>
       </c>
       <c r="J24">
-        <v>8.2425218318142872E-5</v>
+        <v>1.5282463963091895E-4</v>
       </c>
       <c r="K24">
-        <v>2.148986686182925E-5</v>
+        <v>-3.0445186848698444E-5</v>
       </c>
       <c r="L24">
-        <v>-1.4135757918639583E-4</v>
+        <v>-5.3338477968464283E-5</v>
       </c>
       <c r="M24">
-        <v>2.4204398410527579E-5</v>
+        <v>7.7711380781966778E-5</v>
       </c>
       <c r="N24">
-        <v>1.6358507218846292E-5</v>
+        <v>-1.2794118211391752E-5</v>
       </c>
       <c r="O24">
-        <v>-4.0016429235927476E-4</v>
+        <v>4.678657406572181E-4</v>
       </c>
       <c r="P24">
-        <v>-2.8261753375442324E-4</v>
+        <v>3.5404783483078926E-4</v>
       </c>
       <c r="Q24">
-        <v>-7.3358354011554376E-5</v>
+        <v>6.1238461550212203E-4</v>
       </c>
       <c r="R24">
-        <v>-4.2177464930226709E-5</v>
+        <v>6.7896312213133509E-4</v>
       </c>
       <c r="S24">
-        <v>2.8035773847667079E-3</v>
+        <v>4.6711134390362724E-5</v>
       </c>
       <c r="T24">
-        <v>2.7338776718379867E-3</v>
+        <v>2.813880954614714E-3</v>
       </c>
       <c r="U24">
-        <v>2.7267480872654533E-3</v>
+        <v>2.7473386179332356E-3</v>
       </c>
       <c r="V24">
-        <v>2.9297823637036498E-3</v>
+        <v>2.7434528286471626E-3</v>
       </c>
       <c r="W24">
-        <v>2.7239778478736357E-3</v>
+        <v>2.9369398302331227E-3</v>
       </c>
       <c r="X24">
-        <v>2.7396155337880736E-3</v>
+        <v>2.7388657196559672E-3</v>
       </c>
       <c r="Y24">
-        <v>3.6194185902898766E-3</v>
+        <v>3.9212417729994524E-3</v>
       </c>
       <c r="Z24">
-        <v>2.7857923714427794E-3</v>
+        <v>2.755443537245098E-3</v>
       </c>
       <c r="AA24">
-        <v>2.769664092834228E-3</v>
+        <v>2.7857176050128515E-3</v>
       </c>
       <c r="AB24">
-        <v>2.7736709309198705E-3</v>
+        <v>2.7807591050313385E-3</v>
       </c>
       <c r="AC24">
-        <v>2.7918490173763017E-3</v>
+        <v>2.7941165549943072E-3</v>
       </c>
       <c r="AD24">
-        <v>-1.5392107487407678E-5</v>
+        <v>2.8525259231793024E-3</v>
       </c>
       <c r="AE24">
-        <v>2.2930923981968979E-5</v>
+        <v>-1.3788855900143983E-5</v>
       </c>
       <c r="AF24">
-        <v>-1.0890367733368413E-5</v>
+        <v>4.6667512741768524E-5</v>
       </c>
       <c r="AG24">
-        <v>1.5354267337454126E-3</v>
+        <v>-5.115806391101335E-6</v>
       </c>
       <c r="AH24">
-        <v>1.2035974654582909E-3</v>
+        <v>1.4975389422720922E-3</v>
       </c>
       <c r="AI24">
-        <v>-1.3546184266651339E-4</v>
+        <v>1.3020200421445811E-3</v>
       </c>
       <c r="AJ24">
-        <v>3.214056136152204E-3</v>
+        <v>-1.4283005487500587E-4</v>
+      </c>
+      <c r="AK24">
+        <v>4.261426102712941E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25">
-        <v>2.9326148186443832E-2</v>
+        <v>2.1808001995440168E-2</v>
       </c>
       <c r="C25">
-        <v>-1.3157293751504069E-4</v>
+        <v>-9.353278090634882E-5</v>
       </c>
       <c r="D25">
-        <v>-1.904258469413965E-4</v>
+        <v>-1.7471080436940248E-4</v>
       </c>
       <c r="E25">
-        <v>1.5359367158542881E-6</v>
+        <v>1.3702840320293911E-6</v>
       </c>
       <c r="F25">
-        <v>1.1274510153335826E-4</v>
+        <v>1.0022814040613491E-4</v>
       </c>
       <c r="G25">
-        <v>1.7788146414214286E-4</v>
+        <v>1.3062016852951117E-4</v>
       </c>
       <c r="H25">
-        <v>-5.9347365574343759E-7</v>
+        <v>-1.6752464451092201E-6</v>
       </c>
       <c r="I25">
-        <v>-4.6548603083457823E-6</v>
+        <v>-3.5262393750526842E-6</v>
       </c>
       <c r="J25">
-        <v>8.6507825143325293E-5</v>
+        <v>1.0123109445027596E-4</v>
       </c>
       <c r="K25">
-        <v>2.0503668398917652E-5</v>
+        <v>-3.6313395668926933E-5</v>
       </c>
       <c r="L25">
-        <v>-1.0570516638756669E-4</v>
+        <v>-6.0902678793040271E-5</v>
       </c>
       <c r="M25">
-        <v>3.8995259556857807E-5</v>
+        <v>5.0106478525074367E-5</v>
       </c>
       <c r="N25">
-        <v>-3.2943889189098884E-5</v>
+        <v>1.1857200517539766E-6</v>
       </c>
       <c r="O25">
-        <v>-2.779011665331229E-4</v>
+        <v>3.4560393461230453E-4</v>
       </c>
       <c r="P25">
-        <v>-1.2534493678949352E-4</v>
+        <v>2.5737123016834657E-4</v>
       </c>
       <c r="Q25">
-        <v>1.2070455831876699E-4</v>
+        <v>4.7357048850340091E-4</v>
       </c>
       <c r="R25">
-        <v>1.8665381039746241E-4</v>
+        <v>5.1351880990341205E-4</v>
       </c>
       <c r="S25">
-        <v>2.8492083462291445E-3</v>
+        <v>3.9976788809224263E-5</v>
       </c>
       <c r="T25">
-        <v>2.7794414449557039E-3</v>
+        <v>2.8125130654111661E-3</v>
       </c>
       <c r="U25">
-        <v>2.7704629251877472E-3</v>
+        <v>2.7534992231461166E-3</v>
       </c>
       <c r="V25">
-        <v>2.9998439868249255E-3</v>
+        <v>2.7433013281783266E-3</v>
       </c>
       <c r="W25">
-        <v>2.7647598042917854E-3</v>
+        <v>2.9477334355863072E-3</v>
       </c>
       <c r="X25">
-        <v>2.7814757821504679E-3</v>
+        <v>2.7362206784021146E-3</v>
       </c>
       <c r="Y25">
-        <v>2.7857923714427794E-3</v>
+        <v>2.755443537245098E-3</v>
       </c>
       <c r="Z25">
-        <v>3.9525448107029385E-3</v>
+        <v>3.6366504282107381E-3</v>
       </c>
       <c r="AA25">
-        <v>2.8130941815627548E-3</v>
+        <v>2.7929208269317852E-3</v>
       </c>
       <c r="AB25">
-        <v>2.8236345801520811E-3</v>
+        <v>2.785290199358928E-3</v>
       </c>
       <c r="AC25">
-        <v>2.8495280996619597E-3</v>
+        <v>2.7980841409786664E-3</v>
       </c>
       <c r="AD25">
-        <v>-1.8555289581524749E-5</v>
+        <v>2.8416782937837459E-3</v>
       </c>
       <c r="AE25">
-        <v>7.0174491056883683E-5</v>
+        <v>-1.5958071844769363E-5</v>
       </c>
       <c r="AF25">
-        <v>1.4595272571904668E-5</v>
+        <v>3.771894953198259E-5</v>
       </c>
       <c r="AG25">
-        <v>1.6977332527709152E-3</v>
+        <v>-7.4038107101304128E-6</v>
       </c>
       <c r="AH25">
-        <v>1.3689053142016496E-3</v>
+        <v>1.5559368776512669E-3</v>
       </c>
       <c r="AI25">
-        <v>-9.6757156243544763E-5</v>
+        <v>1.1992774560520233E-3</v>
       </c>
       <c r="AJ25">
-        <v>3.52401830288139E-3</v>
+        <v>-1.4575172547589689E-4</v>
+      </c>
+      <c r="AK25">
+        <v>2.7782441668772438E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>34</v>
       </c>
       <c r="B26">
-        <v>8.6274646307265779E-2</v>
+        <v>3.1158857395230118E-2</v>
       </c>
       <c r="C26">
-        <v>-1.2465759851939141E-4</v>
+        <v>-1.1465299372097413E-4</v>
       </c>
       <c r="D26">
-        <v>-1.7868892089609872E-4</v>
+        <v>-1.8912723054915342E-4</v>
       </c>
       <c r="E26">
-        <v>1.4684437568277995E-6</v>
+        <v>1.5041350888907754E-6</v>
       </c>
       <c r="F26">
-        <v>1.0456615111869883E-4</v>
+        <v>1.1294832131742948E-4</v>
       </c>
       <c r="G26">
-        <v>1.1164731108105066E-4</v>
+        <v>1.9221012261777667E-4</v>
       </c>
       <c r="H26">
-        <v>-6.6268718913891386E-7</v>
+        <v>-8.5017929747139469E-7</v>
       </c>
       <c r="I26">
-        <v>-6.6409526917100305E-7</v>
+        <v>-5.1620181532873745E-6</v>
       </c>
       <c r="J26">
-        <v>9.0696321914166683E-5</v>
+        <v>1.043338556022083E-4</v>
       </c>
       <c r="K26">
-        <v>-1.8427814085231198E-6</v>
+        <v>-2.6394766076543244E-5</v>
       </c>
       <c r="L26">
-        <v>-6.7450027553259302E-5</v>
+        <v>-2.6459056302386742E-5</v>
       </c>
       <c r="M26">
-        <v>4.5872317584711429E-5</v>
+        <v>6.5871605897387418E-5</v>
       </c>
       <c r="N26">
-        <v>-2.6690059767881837E-5</v>
+        <v>-5.1074586637544836E-5</v>
       </c>
       <c r="O26">
-        <v>-2.5520173982600172E-4</v>
+        <v>4.3892556046235096E-4</v>
       </c>
       <c r="P26">
-        <v>-1.348706046294364E-4</v>
+        <v>3.7735599968097104E-4</v>
       </c>
       <c r="Q26">
-        <v>1.3673858727443391E-4</v>
+        <v>6.2852340696331458E-4</v>
       </c>
       <c r="R26">
-        <v>2.1313795217272474E-4</v>
+        <v>6.9878651390394247E-4</v>
       </c>
       <c r="S26">
-        <v>2.857354682087007E-3</v>
+        <v>-2.1041955767897406E-6</v>
       </c>
       <c r="T26">
-        <v>2.7742431474260254E-3</v>
+        <v>2.846025136125304E-3</v>
       </c>
       <c r="U26">
-        <v>2.7653570435845604E-3</v>
+        <v>2.7859573954441023E-3</v>
       </c>
       <c r="V26">
-        <v>2.9671792457865039E-3</v>
+        <v>2.7747657040364283E-3</v>
       </c>
       <c r="W26">
-        <v>2.7710032542407632E-3</v>
+        <v>3.0064056373992911E-3</v>
       </c>
       <c r="X26">
-        <v>2.7680760587253809E-3</v>
+        <v>2.7648943525472379E-3</v>
       </c>
       <c r="Y26">
-        <v>2.769664092834228E-3</v>
+        <v>2.7857176050128515E-3</v>
       </c>
       <c r="Z26">
-        <v>2.8130941815627548E-3</v>
+        <v>2.7929208269317852E-3</v>
       </c>
       <c r="AA26">
-        <v>4.382255952619183E-3</v>
+        <v>3.9482010350014324E-3</v>
       </c>
       <c r="AB26">
-        <v>2.8186643241363985E-3</v>
+        <v>2.816808475703926E-3</v>
       </c>
       <c r="AC26">
-        <v>2.8454961411827212E-3</v>
+        <v>2.8359012085754191E-3</v>
       </c>
       <c r="AD26">
-        <v>-1.7521223286053855E-5</v>
+        <v>2.8848816565021826E-3</v>
       </c>
       <c r="AE26">
-        <v>3.8599663038757728E-5</v>
+        <v>-1.8601810035982552E-5</v>
       </c>
       <c r="AF26">
-        <v>-2.6629893078840148E-5</v>
+        <v>8.2464297104937171E-5</v>
       </c>
       <c r="AG26">
-        <v>1.6104000254114998E-3</v>
+        <v>1.7390098762402602E-5</v>
       </c>
       <c r="AH26">
-        <v>1.3414664036750473E-3</v>
+        <v>1.7083354203336785E-3</v>
       </c>
       <c r="AI26">
-        <v>-7.7514857546593025E-6</v>
+        <v>1.3576144451007115E-3</v>
       </c>
       <c r="AJ26">
-        <v>2.8462900837226855E-3</v>
+        <v>-1.1012311935863675E-4</v>
+      </c>
+      <c r="AK26">
+        <v>3.0569586077554742E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="B27">
-        <v>5.0595241881566395E-2</v>
+        <v>8.8159124607529352E-2</v>
       </c>
       <c r="C27">
-        <v>-1.647042595937882E-4</v>
+        <v>-1.1066562368145969E-4</v>
       </c>
       <c r="D27">
-        <v>-1.8444489746613502E-4</v>
+        <v>-1.8131248668446648E-4</v>
       </c>
       <c r="E27">
-        <v>1.5038103234080126E-6</v>
+        <v>1.4698149367860583E-6</v>
       </c>
       <c r="F27">
-        <v>1.0012700069703504E-4</v>
+        <v>1.0792754621088112E-4</v>
       </c>
       <c r="G27">
-        <v>1.5515989708899568E-4</v>
+        <v>1.3053671005980333E-4</v>
       </c>
       <c r="H27">
-        <v>-5.8069306741687717E-7</v>
+        <v>-4.086838399922283E-7</v>
       </c>
       <c r="I27">
-        <v>-2.499702730235091E-6</v>
+        <v>-1.2000576641078251E-6</v>
       </c>
       <c r="J27">
-        <v>1.0349654424098834E-4</v>
+        <v>1.0777022002765048E-4</v>
       </c>
       <c r="K27">
-        <v>1.805253008330468E-5</v>
+        <v>-5.6129326901471419E-5</v>
       </c>
       <c r="L27">
-        <v>-1.526014273797306E-4</v>
+        <v>8.3289354075553879E-6</v>
       </c>
       <c r="M27">
-        <v>2.8815558138892811E-5</v>
+        <v>7.1224902489720266E-5</v>
       </c>
       <c r="N27">
-        <v>2.2221448934820352E-5</v>
+        <v>-4.2406182428843557E-5</v>
       </c>
       <c r="O27">
-        <v>-2.4305149684916293E-4</v>
+        <v>4.7369731707011748E-4</v>
       </c>
       <c r="P27">
-        <v>-1.4211090915036955E-4</v>
+        <v>3.8539126972713268E-4</v>
       </c>
       <c r="Q27">
-        <v>1.2068254732219038E-4</v>
+        <v>6.6662198554022327E-4</v>
       </c>
       <c r="R27">
-        <v>2.3548834513761798E-4</v>
+        <v>7.4925589215152789E-4</v>
       </c>
       <c r="S27">
-        <v>2.8771550642812845E-3</v>
+        <v>5.0725580636866874E-5</v>
       </c>
       <c r="T27">
-        <v>2.7806989327984859E-3</v>
+        <v>2.8629717029838185E-3</v>
       </c>
       <c r="U27">
-        <v>2.7772810581020231E-3</v>
+        <v>2.7886145144306951E-3</v>
       </c>
       <c r="V27">
-        <v>2.9848745436834327E-3</v>
+        <v>2.7789325555003896E-3</v>
       </c>
       <c r="W27">
-        <v>2.7722039859502368E-3</v>
+        <v>2.9812422227236679E-3</v>
       </c>
       <c r="X27">
-        <v>2.7737019599909079E-3</v>
+        <v>2.781093112469451E-3</v>
       </c>
       <c r="Y27">
-        <v>2.7736709309198705E-3</v>
+        <v>2.7807591050313385E-3</v>
       </c>
       <c r="Z27">
-        <v>2.8236345801520811E-3</v>
+        <v>2.785290199358928E-3</v>
       </c>
       <c r="AA27">
-        <v>2.8186643241363985E-3</v>
+        <v>2.816808475703926E-3</v>
       </c>
       <c r="AB27">
-        <v>4.0632530752244753E-3</v>
+        <v>4.3962613010409875E-3</v>
       </c>
       <c r="AC27">
-        <v>2.860010324281606E-3</v>
+        <v>2.8387347726823091E-3</v>
       </c>
       <c r="AD27">
-        <v>-2.2037915800916823E-5</v>
+        <v>2.8900102883720651E-3</v>
       </c>
       <c r="AE27">
-        <v>1.7813519547170089E-4</v>
+        <v>-1.7999803686327587E-5</v>
       </c>
       <c r="AF27">
-        <v>3.6784707442144218E-5</v>
+        <v>5.2839678723094105E-5</v>
       </c>
       <c r="AG27">
-        <v>1.6507959948011408E-3</v>
+        <v>-2.258727941452577E-5</v>
       </c>
       <c r="AH27">
-        <v>1.3776218208620952E-3</v>
+        <v>1.6285340317362929E-3</v>
       </c>
       <c r="AI27">
-        <v>-2.7020533446921722E-5</v>
+        <v>1.3367675731569286E-3</v>
       </c>
       <c r="AJ27">
-        <v>3.2164395718050874E-3</v>
+        <v>-2.1879756912024172E-5</v>
+      </c>
+      <c r="AK27">
+        <v>2.4457954293697526E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="B28">
-        <v>6.1533279976177156E-2</v>
+        <v>5.3906552786215034E-2</v>
       </c>
       <c r="C28">
-        <v>-1.7614338374122079E-4</v>
+        <v>-1.4831856284484206E-4</v>
       </c>
       <c r="D28">
-        <v>-1.4459445441743907E-4</v>
+        <v>-1.8388804953683655E-4</v>
       </c>
       <c r="E28">
-        <v>1.2043257375340976E-6</v>
+        <v>1.4784060070943878E-6</v>
       </c>
       <c r="F28">
-        <v>7.8094905223801097E-5</v>
+        <v>1.0440087796424771E-4</v>
       </c>
       <c r="G28">
-        <v>6.9543587995632146E-5</v>
+        <v>1.7824970065623871E-4</v>
       </c>
       <c r="H28">
-        <v>-1.1588830227949036E-6</v>
+        <v>-8.617180017449097E-7</v>
       </c>
       <c r="I28">
-        <v>-4.0240387976389169E-6</v>
+        <v>-3.3450630693664571E-6</v>
       </c>
       <c r="J28">
-        <v>7.4101128021786125E-5</v>
+        <v>1.2287408525134128E-4</v>
       </c>
       <c r="K28">
-        <v>-1.6859999182384892E-4</v>
+        <v>-3.9809157249165103E-5</v>
       </c>
       <c r="L28">
-        <v>-5.8743600567605185E-5</v>
+        <v>-6.0247860903062198E-5</v>
       </c>
       <c r="M28">
-        <v>-1.1332842866951384E-5</v>
+        <v>5.4705081980232741E-5</v>
       </c>
       <c r="N28">
-        <v>6.8231468848627841E-5</v>
+        <v>7.0699603840609969E-6</v>
       </c>
       <c r="O28">
-        <v>-1.394356059149335E-4</v>
+        <v>5.0881804907443036E-4</v>
       </c>
       <c r="P28">
-        <v>-3.4721559293059492E-6</v>
+        <v>3.9466224684815308E-4</v>
       </c>
       <c r="Q28">
-        <v>2.8691857311444234E-4</v>
+        <v>6.6687806717807981E-4</v>
       </c>
       <c r="R28">
-        <v>3.8502130206073248E-4</v>
+        <v>7.8666457975058333E-4</v>
       </c>
       <c r="S28">
-        <v>2.9031032178762554E-3</v>
+        <v>-1.4272463930039745E-5</v>
       </c>
       <c r="T28">
-        <v>2.8077222503266226E-3</v>
+        <v>2.8914073089686253E-3</v>
       </c>
       <c r="U28">
-        <v>2.8107077665393489E-3</v>
+        <v>2.8022847674327176E-3</v>
       </c>
       <c r="V28">
-        <v>3.0089750218469666E-3</v>
+        <v>2.7989518739522114E-3</v>
       </c>
       <c r="W28">
-        <v>2.8021294653456643E-3</v>
+        <v>3.0055928177607494E-3</v>
       </c>
       <c r="X28">
-        <v>2.808666231796412E-3</v>
+        <v>2.7880368855622796E-3</v>
       </c>
       <c r="Y28">
-        <v>2.7918490173763017E-3</v>
+        <v>2.7941165549943072E-3</v>
       </c>
       <c r="Z28">
-        <v>2.8495280996619597E-3</v>
+        <v>2.7980841409786664E-3</v>
       </c>
       <c r="AA28">
-        <v>2.8454961411827212E-3</v>
+        <v>2.8359012085754191E-3</v>
       </c>
       <c r="AB28">
-        <v>2.860010324281606E-3</v>
+        <v>2.8387347726823091E-3</v>
       </c>
       <c r="AC28">
-        <v>5.1821504910681609E-3</v>
+        <v>4.0932705986364134E-3</v>
       </c>
       <c r="AD28">
-        <v>-2.25835898440605E-5</v>
+        <v>2.9158802769515477E-3</v>
       </c>
       <c r="AE28">
-        <v>-1.0549514499793433E-5</v>
+        <v>-2.2531550582725277E-5</v>
       </c>
       <c r="AF28">
-        <v>4.9532903105212832E-5</v>
+        <v>1.9491106165183376E-4</v>
       </c>
       <c r="AG28">
-        <v>1.7470845864942909E-3</v>
+        <v>3.8813424469368003E-5</v>
       </c>
       <c r="AH28">
-        <v>1.3725062449071387E-3</v>
+        <v>1.6676095041176864E-3</v>
       </c>
       <c r="AI28">
-        <v>-3.3220045154663466E-5</v>
+        <v>1.3731086731114403E-3</v>
       </c>
       <c r="AJ28">
-        <v>1.907514205292231E-3</v>
+        <v>-4.0563016184415269E-5</v>
+      </c>
+      <c r="AK28">
+        <v>2.7388379504331289E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="B29">
-        <v>-1.9509928835825259E-3</v>
+        <v>6.128731425600694E-2</v>
       </c>
       <c r="C29">
-        <v>1.127971394364426E-5</v>
+        <v>-1.609703824956303E-4</v>
       </c>
       <c r="D29">
-        <v>1.0995581087524207E-6</v>
+        <v>-1.5111368442356082E-4</v>
       </c>
       <c r="E29">
-        <v>-4.223057716067416E-8</v>
+        <v>1.236554652979849E-6</v>
       </c>
       <c r="F29">
-        <v>-3.3933589015890168E-6</v>
+        <v>8.7995598908211355E-5</v>
       </c>
       <c r="G29">
-        <v>1.1362807247179032E-5</v>
+        <v>9.8234134385062318E-5</v>
       </c>
       <c r="H29">
-        <v>4.6884819359158843E-7</v>
+        <v>-1.681739772896383E-6</v>
       </c>
       <c r="I29">
-        <v>8.4329243219766754E-7</v>
+        <v>-5.4723714933859168E-6</v>
       </c>
       <c r="J29">
-        <v>3.5083785979385894E-5</v>
+        <v>9.491423626743138E-5</v>
       </c>
       <c r="K29">
-        <v>2.0788056616144381E-6</v>
+        <v>-2.4101862783543551E-4</v>
       </c>
       <c r="L29">
-        <v>1.110414137248984E-5</v>
+        <v>4.7693767975935143E-5</v>
       </c>
       <c r="M29">
-        <v>4.3275536290433945E-6</v>
+        <v>1.5304337996143445E-5</v>
       </c>
       <c r="N29">
-        <v>9.5240313151064144E-6</v>
+        <v>5.3099876972129817E-5</v>
       </c>
       <c r="O29">
-        <v>1.3366301245292824E-5</v>
+        <v>6.3552267416706843E-4</v>
       </c>
       <c r="P29">
-        <v>1.5022519824091113E-5</v>
+        <v>5.6294639400246383E-4</v>
       </c>
       <c r="Q29">
-        <v>1.4594272762942539E-5</v>
+        <v>8.6476466028424662E-4</v>
       </c>
       <c r="R29">
-        <v>8.5850256576550099E-6</v>
+        <v>9.7180379293169885E-4</v>
       </c>
       <c r="S29">
-        <v>-2.4676939088522987E-5</v>
+        <v>-5.2833794686084042E-5</v>
       </c>
       <c r="T29">
-        <v>-2.1336319976813763E-5</v>
+        <v>2.9419299605024018E-3</v>
       </c>
       <c r="U29">
-        <v>-1.5307802830029257E-5</v>
+        <v>2.8549314782281244E-3</v>
       </c>
       <c r="V29">
-        <v>3.170680546752861E-6</v>
+        <v>2.8570117779306626E-3</v>
       </c>
       <c r="W29">
-        <v>-2.6425382525216891E-5</v>
+        <v>3.0568279746538201E-3</v>
       </c>
       <c r="X29">
-        <v>-1.3373266889330632E-5</v>
+        <v>2.8430523114158423E-3</v>
       </c>
       <c r="Y29">
-        <v>-1.5392107487407678E-5</v>
+        <v>2.8525259231793024E-3</v>
       </c>
       <c r="Z29">
-        <v>-1.8555289581524749E-5</v>
+        <v>2.8416782937837459E-3</v>
       </c>
       <c r="AA29">
-        <v>-1.7521223286053855E-5</v>
+        <v>2.8848816565021826E-3</v>
       </c>
       <c r="AB29">
-        <v>-2.2037915800916823E-5</v>
+        <v>2.8900102883720651E-3</v>
       </c>
       <c r="AC29">
-        <v>-2.25835898440605E-5</v>
+        <v>2.9158802769515477E-3</v>
       </c>
       <c r="AD29">
-        <v>1.3063179144930468E-5</v>
+        <v>5.2386147417131041E-3</v>
       </c>
       <c r="AE29">
-        <v>-4.7711054204131869E-5</v>
+        <v>-2.4093123203820682E-5</v>
       </c>
       <c r="AF29">
-        <v>-6.1336166288894123E-5</v>
+        <v>1.3160905223136537E-5</v>
       </c>
       <c r="AG29">
-        <v>5.1105787629442874E-5</v>
+        <v>5.72951624399199E-5</v>
       </c>
       <c r="AH29">
-        <v>-3.8153939962756663E-5</v>
+        <v>1.778605172571706E-3</v>
       </c>
       <c r="AI29">
-        <v>2.5555954341961236E-5</v>
+        <v>1.3851330460748065E-3</v>
       </c>
       <c r="AJ29">
-        <v>-2.0353368657968817E-4</v>
+        <v>-4.0545412071304988E-5</v>
+      </c>
+      <c r="AK29">
+        <v>1.6462334489793337E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-5.6723354608294974E-2</v>
+        <v>-1.8928483153270554E-3</v>
       </c>
       <c r="C30">
-        <v>-3.2702739084470613E-5</v>
+        <v>1.0655861110370738E-5</v>
       </c>
       <c r="D30">
-        <v>2.4850874306035428E-6</v>
+        <v>1.1871135048770881E-6</v>
       </c>
       <c r="E30">
-        <v>4.5547216408820446E-8</v>
+        <v>-4.2238712472434346E-8</v>
       </c>
       <c r="F30">
-        <v>6.6550596140620881E-5</v>
+        <v>-3.3718059539217433E-6</v>
       </c>
       <c r="G30">
-        <v>5.4142285441301141E-5</v>
+        <v>1.0832750904601662E-5</v>
       </c>
       <c r="H30">
-        <v>-6.7401625497084514E-7</v>
+        <v>4.5961633301372582E-7</v>
       </c>
       <c r="I30">
-        <v>-4.5890397871714276E-8</v>
+        <v>8.6635860411326022E-7</v>
       </c>
       <c r="J30">
-        <v>-1.2861641145956582E-5</v>
+        <v>3.4442340028185004E-5</v>
       </c>
       <c r="K30">
-        <v>2.7425430887820842E-5</v>
+        <v>5.1299779366311814E-6</v>
       </c>
       <c r="L30">
-        <v>-4.3693960598504254E-5</v>
+        <v>7.9365520947956075E-6</v>
       </c>
       <c r="M30">
-        <v>-6.0151603273059079E-5</v>
+        <v>3.62994500967456E-6</v>
       </c>
       <c r="N30">
-        <v>-4.8272027592214132E-6</v>
+        <v>9.9894871184291119E-6</v>
       </c>
       <c r="O30">
-        <v>-3.1317109501761742E-4</v>
+        <v>-1.2807847623821434E-5</v>
       </c>
       <c r="P30">
-        <v>-3.045385356129099E-4</v>
+        <v>-3.3358311870261429E-6</v>
       </c>
       <c r="Q30">
-        <v>-2.8399492062849735E-4</v>
+        <v>-4.0327157283170044E-6</v>
       </c>
       <c r="R30">
-        <v>-2.1703180233486892E-4</v>
+        <v>-1.0336742084194987E-5</v>
       </c>
       <c r="S30">
-        <v>1.0407073645614466E-5</v>
+        <v>-1.3659313498668281E-6</v>
       </c>
       <c r="T30">
-        <v>3.028883529880848E-5</v>
+        <v>-2.4588219424363284E-5</v>
       </c>
       <c r="U30">
-        <v>8.605820344800834E-5</v>
+        <v>-2.1867524591059841E-5</v>
       </c>
       <c r="V30">
-        <v>-5.0746963250893726E-5</v>
+        <v>-1.5631923637349899E-5</v>
       </c>
       <c r="W30">
-        <v>1.2219990822727163E-4</v>
+        <v>2.9821535887171089E-6</v>
       </c>
       <c r="X30">
-        <v>3.3090932180006224E-5</v>
+        <v>-2.674417115406803E-5</v>
       </c>
       <c r="Y30">
-        <v>2.2930923981968979E-5</v>
+        <v>-1.3788855900143983E-5</v>
       </c>
       <c r="Z30">
-        <v>7.0174491056883683E-5</v>
+        <v>-1.5958071844769363E-5</v>
       </c>
       <c r="AA30">
-        <v>3.8599663038757728E-5</v>
+        <v>-1.8601810035982552E-5</v>
       </c>
       <c r="AB30">
-        <v>1.7813519547170089E-4</v>
+        <v>-1.7999803686327587E-5</v>
       </c>
       <c r="AC30">
-        <v>-1.0549514499793433E-5</v>
+        <v>-2.2531550582725277E-5</v>
       </c>
       <c r="AD30">
-        <v>-4.7711054204131869E-5</v>
+        <v>-2.4093123203820682E-5</v>
       </c>
       <c r="AE30">
-        <v>2.1424087843943066E-3</v>
+        <v>1.3077601145817113E-5</v>
       </c>
       <c r="AF30">
-        <v>3.6432354254915811E-4</v>
+        <v>-4.8116225927232134E-5</v>
       </c>
       <c r="AG30">
-        <v>-2.3620497622273056E-4</v>
+        <v>-6.1335081816123464E-5</v>
       </c>
       <c r="AH30">
-        <v>6.916766917412686E-5</v>
+        <v>5.1580046343860611E-5</v>
       </c>
       <c r="AI30">
-        <v>-1.4581156730317574E-4</v>
+        <v>-3.7790753466806365E-5</v>
       </c>
       <c r="AJ30">
-        <v>5.7032719689132511E-4</v>
+        <v>2.6090013485434248E-5</v>
+      </c>
+      <c r="AK30">
+        <v>-1.895744988866107E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>39</v>
       </c>
       <c r="B31">
-        <v>5.0786587924448991E-2</v>
+        <v>-5.8224731730995072E-2</v>
       </c>
       <c r="C31">
-        <v>-3.4827233209817509E-5</v>
+        <v>-2.790350858174995E-5</v>
       </c>
       <c r="D31">
-        <v>8.4495061951665989E-5</v>
+        <v>2.3928309300673065E-6</v>
       </c>
       <c r="E31">
-        <v>-6.0188746302127329E-7</v>
+        <v>3.9630903982493406E-8</v>
       </c>
       <c r="F31">
-        <v>3.2682807131647139E-5</v>
+        <v>7.0619400835429311E-5</v>
       </c>
       <c r="G31">
-        <v>-3.1983117986732934E-5</v>
+        <v>6.2050163587419534E-5</v>
       </c>
       <c r="H31">
-        <v>-1.0928369990262868E-6</v>
+        <v>-1.9807745785110434E-7</v>
       </c>
       <c r="I31">
-        <v>-6.1225293075728576E-7</v>
+        <v>-6.0544934073119526E-8</v>
       </c>
       <c r="J31">
-        <v>-5.1712611672770034E-5</v>
+        <v>-6.3836646752876518E-6</v>
       </c>
       <c r="K31">
-        <v>1.2727223665245642E-4</v>
+        <v>2.1554091317274073E-6</v>
       </c>
       <c r="L31">
-        <v>-5.9181699399147919E-5</v>
+        <v>-1.9814880131643941E-5</v>
       </c>
       <c r="M31">
-        <v>-8.5291550336128008E-5</v>
+        <v>-5.5042079319060915E-5</v>
       </c>
       <c r="N31">
-        <v>1.410395194126141E-5</v>
+        <v>-6.4879262942067981E-6</v>
       </c>
       <c r="O31">
-        <v>-1.9050449404362825E-4</v>
+        <v>-9.7762280146985596E-5</v>
       </c>
       <c r="P31">
-        <v>-2.1843155481892826E-4</v>
+        <v>-1.366271549274088E-4</v>
       </c>
       <c r="Q31">
-        <v>-2.1331045252778112E-4</v>
+        <v>-1.152901468668294E-4</v>
       </c>
       <c r="R31">
-        <v>-1.936095120110815E-4</v>
+        <v>-4.3262053502564324E-5</v>
       </c>
       <c r="S31">
-        <v>1.7963388023711365E-4</v>
+        <v>4.9756773546746016E-5</v>
       </c>
       <c r="T31">
-        <v>7.8062316686907816E-6</v>
+        <v>1.981876578103722E-5</v>
       </c>
       <c r="U31">
-        <v>-2.2314478866818245E-5</v>
+        <v>4.7089582603104536E-5</v>
       </c>
       <c r="V31">
-        <v>-1.2093750229926273E-4</v>
+        <v>9.9420780422664081E-5</v>
       </c>
       <c r="W31">
-        <v>1.5094269393716602E-4</v>
+        <v>-3.4699631699067798E-5</v>
       </c>
       <c r="X31">
-        <v>-7.8692211453392934E-6</v>
+        <v>1.3502734843439296E-4</v>
       </c>
       <c r="Y31">
-        <v>-1.0890367733368413E-5</v>
+        <v>4.6667512741768524E-5</v>
       </c>
       <c r="Z31">
-        <v>1.4595272571904668E-5</v>
+        <v>3.771894953198259E-5</v>
       </c>
       <c r="AA31">
-        <v>-2.6629893078840148E-5</v>
+        <v>8.2464297104937171E-5</v>
       </c>
       <c r="AB31">
-        <v>3.6784707442144218E-5</v>
+        <v>5.2839678723094105E-5</v>
       </c>
       <c r="AC31">
-        <v>4.9532903105212832E-5</v>
+        <v>1.9491106165183376E-4</v>
       </c>
       <c r="AD31">
-        <v>-6.1336166288894123E-5</v>
+        <v>1.3160905223136537E-5</v>
       </c>
       <c r="AE31">
-        <v>3.6432354254915811E-4</v>
+        <v>-4.8116225927232134E-5</v>
       </c>
       <c r="AF31">
-        <v>2.3446774174641478E-3</v>
+        <v>2.1466995036416052E-3</v>
       </c>
       <c r="AG31">
-        <v>-2.5333325936281823E-4</v>
+        <v>3.671864522928486E-4</v>
       </c>
       <c r="AH31">
-        <v>9.606344884506774E-5</v>
+        <v>-2.2482620839237976E-4</v>
       </c>
       <c r="AI31">
-        <v>-2.9174943652320804E-4</v>
+        <v>7.1241192622241119E-5</v>
       </c>
       <c r="AJ31">
-        <v>-1.7062363640408598E-3</v>
+        <v>-1.4033139077025943E-4</v>
+      </c>
+      <c r="AK31">
+        <v>3.8380024766797527E-4</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
       <c r="B32">
-        <v>-0.11837935792366518</v>
+        <v>5.0127734988602658E-2</v>
       </c>
       <c r="C32">
-        <v>-1.4979199090367999E-4</v>
+        <v>-3.03932547317998E-5</v>
       </c>
       <c r="D32">
-        <v>-6.2518010978919805E-4</v>
+        <v>8.3596636499339363E-5</v>
       </c>
       <c r="E32">
-        <v>4.6345040509475702E-6</v>
+        <v>-6.0013566440803967E-7</v>
       </c>
       <c r="F32">
-        <v>4.5310012459278965E-4</v>
+        <v>3.2194093384762973E-5</v>
       </c>
       <c r="G32">
-        <v>9.2174590399475651E-4</v>
+        <v>-3.0025151282731721E-5</v>
       </c>
       <c r="H32">
-        <v>6.0083975362203737E-6</v>
+        <v>-7.4218462676764583E-7</v>
       </c>
       <c r="I32">
-        <v>1.0999525334837217E-5</v>
+        <v>-5.5364655702988702E-7</v>
       </c>
       <c r="J32">
-        <v>2.2579108128102025E-4</v>
+        <v>-4.731433493148294E-5</v>
       </c>
       <c r="K32">
-        <v>1.3401368754289208E-4</v>
+        <v>1.2060495454712457E-4</v>
       </c>
       <c r="L32">
-        <v>-2.6014591300140997E-4</v>
+        <v>-4.6723274659226982E-5</v>
       </c>
       <c r="M32">
-        <v>4.7861534335817658E-4</v>
+        <v>-7.9372285403567639E-5</v>
       </c>
       <c r="N32">
-        <v>-1.3326387390700175E-4</v>
+        <v>1.0022965829816121E-5</v>
       </c>
       <c r="O32">
-        <v>3.3214239948988877E-4</v>
+        <v>8.9681582280645884E-7</v>
       </c>
       <c r="P32">
-        <v>7.6799750243809967E-4</v>
+        <v>-8.3912234266735085E-5</v>
       </c>
       <c r="Q32">
-        <v>1.6219072450019865E-3</v>
+        <v>-7.7369112444771387E-5</v>
       </c>
       <c r="R32">
-        <v>1.1596193884992039E-3</v>
+        <v>-5.6985776334853185E-5</v>
       </c>
       <c r="S32">
-        <v>1.6216548888864115E-3</v>
+        <v>4.3797475804492398E-5</v>
       </c>
       <c r="T32">
-        <v>1.4414482305536796E-3</v>
+        <v>1.806562385231628E-4</v>
       </c>
       <c r="U32">
-        <v>1.2581305121438706E-3</v>
+        <v>1.1639780296327716E-5</v>
       </c>
       <c r="V32">
-        <v>3.1675296498545865E-3</v>
+        <v>-2.2369923079074416E-5</v>
       </c>
       <c r="W32">
-        <v>1.2052191172634559E-3</v>
+        <v>-1.1923536252575763E-4</v>
       </c>
       <c r="X32">
-        <v>1.4783579493801613E-3</v>
+        <v>1.5294533671644166E-4</v>
       </c>
       <c r="Y32">
-        <v>1.5354267337454126E-3</v>
+        <v>-5.115806391101335E-6</v>
       </c>
       <c r="Z32">
-        <v>1.6977332527709152E-3</v>
+        <v>-7.4038107101304128E-6</v>
       </c>
       <c r="AA32">
-        <v>1.6104000254114998E-3</v>
+        <v>1.7390098762402602E-5</v>
       </c>
       <c r="AB32">
-        <v>1.6507959948011408E-3</v>
+        <v>-2.258727941452577E-5</v>
       </c>
       <c r="AC32">
-        <v>1.7470845864942909E-3</v>
+        <v>3.8813424469368003E-5</v>
       </c>
       <c r="AD32">
-        <v>5.1105787629442874E-5</v>
+        <v>5.72951624399199E-5</v>
       </c>
       <c r="AE32">
-        <v>-2.3620497622273056E-4</v>
+        <v>-6.1335081816123464E-5</v>
       </c>
       <c r="AF32">
-        <v>-2.5333325936281823E-4</v>
+        <v>3.671864522928486E-4</v>
       </c>
       <c r="AG32">
-        <v>9.2582400312846581E-3</v>
+        <v>2.348908076431368E-3</v>
       </c>
       <c r="AH32">
-        <v>9.64628147264894E-4</v>
+        <v>-2.5151894365529502E-4</v>
       </c>
       <c r="AI32">
-        <v>2.2685327494546533E-4</v>
+        <v>8.4846268631227147E-5</v>
       </c>
       <c r="AJ32">
-        <v>1.5733455285279183E-2</v>
+        <v>-2.9505486877774018E-4</v>
+      </c>
+      <c r="AK32">
+        <v>-1.8259115028702497E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-0.46181451065208373</v>
+        <v>-0.12886479127195932</v>
       </c>
       <c r="C33">
-        <v>-1.1355022334917663E-4</v>
+        <v>-1.5622324587662883E-4</v>
       </c>
       <c r="D33">
-        <v>-2.0525873854236598E-4</v>
+        <v>-6.6209498048584031E-4</v>
       </c>
       <c r="E33">
-        <v>1.7114048857310056E-6</v>
+        <v>4.9187769426147052E-6</v>
       </c>
       <c r="F33">
-        <v>2.7023268951671464E-4</v>
+        <v>4.6365365075414378E-4</v>
       </c>
       <c r="G33">
-        <v>3.1872475462040972E-4</v>
+        <v>9.3787914242145264E-4</v>
       </c>
       <c r="H33">
-        <v>-2.2507651409347693E-6</v>
+        <v>1.1946016358840454E-5</v>
       </c>
       <c r="I33">
-        <v>-2.9610503853712099E-6</v>
+        <v>1.3163100871880702E-5</v>
       </c>
       <c r="J33">
-        <v>1.0827650927691234E-5</v>
+        <v>2.3386879021880947E-4</v>
       </c>
       <c r="K33">
-        <v>-9.7486362401097773E-5</v>
+        <v>1.0773482138722815E-4</v>
       </c>
       <c r="L33">
-        <v>-9.0065154026749972E-5</v>
+        <v>-2.872320429850991E-4</v>
       </c>
       <c r="M33">
-        <v>1.1519724639620055E-4</v>
+        <v>4.8615278624124919E-4</v>
       </c>
       <c r="N33">
-        <v>-6.7074755479444359E-5</v>
+        <v>-1.3215083105059337E-4</v>
       </c>
       <c r="O33">
-        <v>-1.7844598179609945E-4</v>
+        <v>8.6332339376490918E-4</v>
       </c>
       <c r="P33">
-        <v>-1.0795353988602785E-4</v>
+        <v>1.210952013005955E-3</v>
       </c>
       <c r="Q33">
-        <v>1.4358507471572352E-4</v>
+        <v>2.0960225345401907E-3</v>
       </c>
       <c r="R33">
-        <v>2.4423396534955328E-4</v>
+        <v>1.6252484531499587E-3</v>
       </c>
       <c r="S33">
-        <v>1.3938610653002098E-3</v>
+        <v>6.4085984605168392E-4</v>
       </c>
       <c r="T33">
-        <v>1.2622250946694358E-3</v>
+        <v>1.6412509049184532E-3</v>
       </c>
       <c r="U33">
-        <v>1.3185912335190782E-3</v>
+        <v>1.4586428930581043E-3</v>
       </c>
       <c r="V33">
-        <v>1.4024615115860225E-3</v>
+        <v>1.2818731015259506E-3</v>
       </c>
       <c r="W33">
-        <v>1.0886711697358593E-3</v>
+        <v>3.2083286898510746E-3</v>
       </c>
       <c r="X33">
-        <v>1.310138643980044E-3</v>
+        <v>1.2278448892159518E-3</v>
       </c>
       <c r="Y33">
-        <v>1.2035974654582909E-3</v>
+        <v>1.4975389422720922E-3</v>
       </c>
       <c r="Z33">
-        <v>1.3689053142016496E-3</v>
+        <v>1.5559368776512669E-3</v>
       </c>
       <c r="AA33">
-        <v>1.3414664036750473E-3</v>
+        <v>1.7083354203336785E-3</v>
       </c>
       <c r="AB33">
-        <v>1.3776218208620952E-3</v>
+        <v>1.6285340317362929E-3</v>
       </c>
       <c r="AC33">
-        <v>1.3725062449071387E-3</v>
+        <v>1.6676095041176864E-3</v>
       </c>
       <c r="AD33">
-        <v>-3.8153939962756663E-5</v>
+        <v>1.778605172571706E-3</v>
       </c>
       <c r="AE33">
-        <v>6.916766917412686E-5</v>
+        <v>5.1580046343860611E-5</v>
       </c>
       <c r="AF33">
-        <v>9.606344884506774E-5</v>
+        <v>-2.2482620839237976E-4</v>
       </c>
       <c r="AG33">
-        <v>9.64628147264894E-4</v>
+        <v>-2.5151894365529502E-4</v>
       </c>
       <c r="AH33">
-        <v>1.438100822177556E-2</v>
+        <v>9.4505935856479938E-3</v>
       </c>
       <c r="AI33">
-        <v>1.5088577618481538E-4</v>
+        <v>9.6094481364437522E-4</v>
       </c>
       <c r="AJ33">
-        <v>5.3665706979937576E-3</v>
+        <v>2.7720415619392788E-4</v>
+      </c>
+      <c r="AK33">
+        <v>1.5990240438679228E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-6.9441423785691889E-2</v>
+        <v>-0.45898917060836303</v>
       </c>
       <c r="C34">
-        <v>-8.5299986398909301E-5</v>
+        <v>-1.0325310381750091E-4</v>
       </c>
       <c r="D34">
-        <v>-1.3825057456334257E-5</v>
+        <v>-2.0311080103175422E-4</v>
       </c>
       <c r="E34">
-        <v>4.8524357592621297E-8</v>
+        <v>1.6857221606156715E-6</v>
       </c>
       <c r="F34">
-        <v>3.975032565901701E-5</v>
+        <v>2.6789813048165665E-4</v>
       </c>
       <c r="G34">
-        <v>1.0550020164738351E-4</v>
+        <v>3.2333373684365876E-4</v>
       </c>
       <c r="H34">
-        <v>-4.446363690807167E-6</v>
+        <v>-2.3773646068840399E-6</v>
       </c>
       <c r="I34">
-        <v>1.354345390042995E-6</v>
+        <v>-3.1333563733720139E-6</v>
       </c>
       <c r="J34">
-        <v>-9.1440888721767543E-7</v>
+        <v>1.9553274917460169E-5</v>
       </c>
       <c r="K34">
-        <v>1.7391444803668073E-4</v>
+        <v>-1.3642704160463266E-4</v>
       </c>
       <c r="L34">
-        <v>-2.920123339211773E-4</v>
+        <v>-4.6958022544065295E-5</v>
       </c>
       <c r="M34">
-        <v>3.8252509052642987E-4</v>
+        <v>1.3273266088431731E-4</v>
       </c>
       <c r="N34">
-        <v>-5.3229641321534684E-5</v>
+        <v>-7.3468817721465338E-5</v>
       </c>
       <c r="O34">
-        <v>-9.2837715544830221E-6</v>
+        <v>2.1318150158074938E-4</v>
       </c>
       <c r="P34">
-        <v>1.5402379436889264E-4</v>
+        <v>1.671948722658358E-4</v>
       </c>
       <c r="Q34">
-        <v>1.7705970971344402E-4</v>
+        <v>4.0748601460296281E-4</v>
       </c>
       <c r="R34">
-        <v>3.3118551018452246E-4</v>
+        <v>5.3471701326602075E-4</v>
       </c>
       <c r="S34">
-        <v>5.4059553605153438E-5</v>
+        <v>1.9406978048294395E-5</v>
       </c>
       <c r="T34">
-        <v>-1.4862027242271343E-4</v>
+        <v>1.3851247432372464E-3</v>
       </c>
       <c r="U34">
-        <v>-7.6255679635014344E-5</v>
+        <v>1.2510546866361131E-3</v>
       </c>
       <c r="V34">
-        <v>-6.5097562287870389E-5</v>
+        <v>1.312234074011494E-3</v>
       </c>
       <c r="W34">
-        <v>-1.8583418055729279E-4</v>
+        <v>1.393858786937349E-3</v>
       </c>
       <c r="X34">
-        <v>-1.3355213415643536E-4</v>
+        <v>1.0759731157713611E-3</v>
       </c>
       <c r="Y34">
-        <v>-1.3546184266651339E-4</v>
+        <v>1.3020200421445811E-3</v>
       </c>
       <c r="Z34">
-        <v>-9.6757156243544763E-5</v>
+        <v>1.1992774560520233E-3</v>
       </c>
       <c r="AA34">
-        <v>-7.7514857546593025E-6</v>
+        <v>1.3576144451007115E-3</v>
       </c>
       <c r="AB34">
-        <v>-2.7020533446921722E-5</v>
+        <v>1.3367675731569286E-3</v>
       </c>
       <c r="AC34">
-        <v>-3.3220045154663466E-5</v>
+        <v>1.3731086731114403E-3</v>
       </c>
       <c r="AD34">
-        <v>2.5555954341961236E-5</v>
+        <v>1.3851330460748065E-3</v>
       </c>
       <c r="AE34">
-        <v>-1.4581156730317574E-4</v>
+        <v>-3.7790753466806365E-5</v>
       </c>
       <c r="AF34">
-        <v>-2.9174943652320804E-4</v>
+        <v>7.1241192622241119E-5</v>
       </c>
       <c r="AG34">
-        <v>2.2685327494546533E-4</v>
+        <v>8.4846268631227147E-5</v>
       </c>
       <c r="AH34">
-        <v>1.5088577618481538E-4</v>
+        <v>9.6094481364437522E-4</v>
       </c>
       <c r="AI34">
-        <v>1.618972213682595E-2</v>
+        <v>1.4178606251474615E-2</v>
       </c>
       <c r="AJ34">
-        <v>-2.1777702188036129E-5</v>
+        <v>1.4299919586889908E-4</v>
+      </c>
+      <c r="AK34">
+        <v>5.0498872970179305E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-28.730717649552549</v>
+        <v>-8.0502213117706292E-2</v>
       </c>
       <c r="C35">
-        <v>-2.7204892560691641E-3</v>
+        <v>-8.5595679129652548E-5</v>
       </c>
       <c r="D35">
-        <v>-4.8088678300469062E-2</v>
+        <v>-3.0207635378866685E-5</v>
       </c>
       <c r="E35">
-        <v>3.8606296235684033E-4</v>
+        <v>1.7207039169161878E-7</v>
       </c>
       <c r="F35">
-        <v>1.9263754534478935E-3</v>
+        <v>4.4006391162126627E-5</v>
       </c>
       <c r="G35">
-        <v>5.966364424646888E-3</v>
+        <v>1.1732894645242808E-4</v>
       </c>
       <c r="H35">
-        <v>-1.5710077137610456E-4</v>
+        <v>-1.7712939310388445E-6</v>
       </c>
       <c r="I35">
-        <v>-1.3596710315837336E-4</v>
+        <v>2.2794908997929949E-6</v>
       </c>
       <c r="J35">
-        <v>-2.8645346773594734E-3</v>
+        <v>2.7691835204071637E-6</v>
       </c>
       <c r="K35">
-        <v>-1.1585531045409082E-2</v>
+        <v>1.665610691439271E-4</v>
       </c>
       <c r="L35">
-        <v>-6.8207952601999546E-3</v>
+        <v>-3.1737142395660251E-4</v>
       </c>
       <c r="M35">
-        <v>1.0315479854308906E-3</v>
+        <v>3.9275790311003476E-4</v>
       </c>
       <c r="N35">
-        <v>-7.3817653992011871E-4</v>
+        <v>-6.0784182484479872E-5</v>
       </c>
       <c r="O35">
-        <v>-6.0556870308114503E-3</v>
+        <v>2.0634659070800003E-4</v>
       </c>
       <c r="P35">
-        <v>-5.4009401585079896E-3</v>
+        <v>3.2293461944150198E-4</v>
       </c>
       <c r="Q35">
-        <v>-2.0786250874296266E-3</v>
+        <v>3.5848104095381858E-4</v>
       </c>
       <c r="R35">
-        <v>-2.9939802552018408E-3</v>
+        <v>5.0847586407035909E-4</v>
       </c>
       <c r="S35">
-        <v>1.9499250104715177E-3</v>
+        <v>2.6581924329379661E-4</v>
       </c>
       <c r="T35">
-        <v>1.3512628544703181E-3</v>
+        <v>4.121615422709486E-5</v>
       </c>
       <c r="U35">
-        <v>1.2752876262266408E-3</v>
+        <v>-1.5743724308450743E-4</v>
       </c>
       <c r="V35">
-        <v>7.3263712788868606E-3</v>
+        <v>-8.4276562516360387E-5</v>
       </c>
       <c r="W35">
-        <v>3.2943547642091358E-3</v>
+        <v>-6.4618926396795847E-5</v>
       </c>
       <c r="X35">
-        <v>4.6841423914621965E-3</v>
+        <v>-1.9262681582776591E-4</v>
       </c>
       <c r="Y35">
-        <v>3.214056136152204E-3</v>
+        <v>-1.4283005487500587E-4</v>
       </c>
       <c r="Z35">
-        <v>3.52401830288139E-3</v>
+        <v>-1.4575172547589689E-4</v>
       </c>
       <c r="AA35">
-        <v>2.8462900837226855E-3</v>
+        <v>-1.1012311935863675E-4</v>
       </c>
       <c r="AB35">
-        <v>3.2164395718050874E-3</v>
+        <v>-2.1879756912024172E-5</v>
       </c>
       <c r="AC35">
-        <v>1.907514205292231E-3</v>
+        <v>-4.0563016184415269E-5</v>
       </c>
       <c r="AD35">
-        <v>-2.0353368657968817E-4</v>
+        <v>-4.0545412071304988E-5</v>
       </c>
       <c r="AE35">
-        <v>5.7032719689132511E-4</v>
+        <v>2.6090013485434248E-5</v>
       </c>
       <c r="AF35">
-        <v>-1.7062363640408598E-3</v>
+        <v>-1.4033139077025943E-4</v>
       </c>
       <c r="AG35">
-        <v>1.5733455285279183E-2</v>
+        <v>-2.9505486877774018E-4</v>
       </c>
       <c r="AH35">
-        <v>5.3665706979937576E-3</v>
+        <v>2.7720415619392788E-4</v>
       </c>
       <c r="AI35">
-        <v>-2.1777702188036129E-5</v>
+        <v>1.4299919586889908E-4</v>
       </c>
       <c r="AJ35">
-        <v>1.5063362222807584</v>
+        <v>1.6385642209018777E-2</v>
+      </c>
+      <c r="AK35">
+        <v>1.4189189852683803E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36">
+        <v>-28.737462399995636</v>
+      </c>
+      <c r="C36">
+        <v>-2.6844751168727931E-3</v>
+      </c>
+      <c r="D36">
+        <v>-4.8120650391440506E-2</v>
+      </c>
+      <c r="E36">
+        <v>3.8611593638665054E-4</v>
+      </c>
+      <c r="F36">
+        <v>1.8769304441431326E-3</v>
+      </c>
+      <c r="G36">
+        <v>5.9743618877521375E-3</v>
+      </c>
+      <c r="H36">
+        <v>-1.363486099422297E-4</v>
+      </c>
+      <c r="I36">
+        <v>-1.2014489749146459E-4</v>
+      </c>
+      <c r="J36">
+        <v>-2.7392343950950627E-3</v>
+      </c>
+      <c r="K36">
+        <v>-1.2096474722976279E-2</v>
+      </c>
+      <c r="L36">
+        <v>-6.9006113307261748E-3</v>
+      </c>
+      <c r="M36">
+        <v>1.1153355799062741E-3</v>
+      </c>
+      <c r="N36">
+        <v>-7.829378479813513E-4</v>
+      </c>
+      <c r="O36">
+        <v>-3.6092604757943696E-3</v>
+      </c>
+      <c r="P36">
+        <v>-3.7608584647295974E-3</v>
+      </c>
+      <c r="Q36">
+        <v>-3.3468602507928484E-4</v>
+      </c>
+      <c r="R36">
+        <v>-1.2729034716397261E-3</v>
+      </c>
+      <c r="S36">
+        <v>2.0655648568618156E-3</v>
+      </c>
+      <c r="T36">
+        <v>1.5078356791364874E-3</v>
+      </c>
+      <c r="U36">
+        <v>9.2560924361584709E-4</v>
+      </c>
+      <c r="V36">
+        <v>8.3210776151225116E-4</v>
+      </c>
+      <c r="W36">
+        <v>7.0299381565938771E-3</v>
+      </c>
+      <c r="X36">
+        <v>2.9882895462922023E-3</v>
+      </c>
+      <c r="Y36">
+        <v>4.261426102712941E-3</v>
+      </c>
+      <c r="Z36">
+        <v>2.7782441668772438E-3</v>
+      </c>
+      <c r="AA36">
+        <v>3.0569586077554742E-3</v>
+      </c>
+      <c r="AB36">
+        <v>2.4457954293697526E-3</v>
+      </c>
+      <c r="AC36">
+        <v>2.7388379504331289E-3</v>
+      </c>
+      <c r="AD36">
+        <v>1.6462334489793337E-3</v>
+      </c>
+      <c r="AE36">
+        <v>-1.895744988866107E-4</v>
+      </c>
+      <c r="AF36">
+        <v>3.8380024766797527E-4</v>
+      </c>
+      <c r="AG36">
+        <v>-1.8259115028702497E-3</v>
+      </c>
+      <c r="AH36">
+        <v>1.5990240438679228E-2</v>
+      </c>
+      <c r="AI36">
+        <v>5.0498872970179305E-3</v>
+      </c>
+      <c r="AJ36">
+        <v>1.4189189852683803E-4</v>
+      </c>
+      <c r="AK36">
+        <v>1.5045886239093011</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_retirement.xlsx
+++ b/input/reg_retirement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7001A211-65AC-DF43-A96F-F449CCA0119F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF510F6-F31E-8847-B6DB-3B53342C67CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="19540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <t>Model parameters governing projection of retirement</t>
   </si>
   <si>
-    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova</t>
+    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova, Aleksandra Kolndrekaj</t>
   </si>
   <si>
     <t>Last edit: 26 jan 2026 DP</t>
@@ -73,10 +73,10 @@
     <t>Dag_sq</t>
   </si>
   <si>
-    <t>Deh_c3_Medium</t>
+    <t>Deh_c4_Medium_L1</t>
   </si>
   <si>
-    <t>Deh_c3_Low</t>
+    <t>Deh_c4_Low_L1</t>
   </si>
   <si>
     <t>Dhe_pcs_L1</t>
@@ -178,7 +178,7 @@
     <t>Reached_Retirement_Age_Les</t>
   </si>
   <si>
-    <t>Lessp_c3_NotEmployed</t>
+    <t>Lessp_c3_NotEmployed_L1</t>
   </si>
   <si>
     <t>Reached_Retirement_Age_Sp</t>
@@ -712,13 +712,13 @@
         <v>46</v>
       </c>
       <c r="B5">
-        <v>0.2213905845571944</v>
+        <v>0.2214079046691978</v>
       </c>
       <c r="E5" t="s">
         <v>48</v>
       </c>
       <c r="F5">
-        <v>1648.3842838862272</v>
+        <v>1648.7774590403296</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -732,7 +732,7 @@
         <v>49</v>
       </c>
       <c r="F6">
-        <v>-3452261.0460356632</v>
+        <v>-3452184.2507300889</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -745,13 +745,13 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>0.21485733363385973</v>
+        <v>0.1978403284372392</v>
       </c>
       <c r="E11" t="s">
         <v>48</v>
       </c>
       <c r="F11">
-        <v>3294.0849406273219</v>
+        <v>3018.2253661222517</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -759,13 +759,13 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>60833</v>
+        <v>60524</v>
       </c>
       <c r="E12" t="s">
         <v>49</v>
       </c>
       <c r="F12">
-        <v>-9008031.6831588075</v>
+        <v>-9161806.9902482908</v>
       </c>
     </row>
   </sheetData>
@@ -887,103 +887,103 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0.10954926867205772</v>
+        <v>0.10959560091831981</v>
       </c>
       <c r="C2">
-        <v>1.6636339468067492E-3</v>
+        <v>1.6638283433812807E-3</v>
       </c>
       <c r="D2">
-        <v>-3.7221000597152388E-5</v>
+        <v>-3.7255469194964248E-5</v>
       </c>
       <c r="E2">
-        <v>6.4772414891427306E-8</v>
+        <v>6.4960058014465595E-8</v>
       </c>
       <c r="F2">
-        <v>-2.0562352849196942E-4</v>
+        <v>-2.0748578451535772E-4</v>
       </c>
       <c r="G2">
-        <v>-2.0822440536719312E-4</v>
+        <v>-2.0779793968747878E-4</v>
       </c>
       <c r="H2">
-        <v>3.8689516840200732E-6</v>
+        <v>3.8749924739925942E-6</v>
       </c>
       <c r="I2">
-        <v>-7.5657553833130118E-6</v>
+        <v>-7.5620935218659037E-6</v>
       </c>
       <c r="J2">
-        <v>5.982792048583852E-4</v>
+        <v>5.9827565431061426E-4</v>
       </c>
       <c r="K2">
-        <v>7.041998484249622E-4</v>
+        <v>7.0475624649908152E-4</v>
       </c>
       <c r="L2">
-        <v>9.0288484663960961E-4</v>
+        <v>9.036371025626733E-4</v>
       </c>
       <c r="M2">
-        <v>1.3250295488772381E-3</v>
+        <v>1.3260898149406886E-3</v>
       </c>
       <c r="N2">
-        <v>1.2281547617617608E-3</v>
+        <v>1.2297555743673375E-3</v>
       </c>
       <c r="O2">
-        <v>8.4259762382982335E-4</v>
+        <v>8.4364565570690768E-4</v>
       </c>
       <c r="P2">
-        <v>4.6022563817849928E-4</v>
+        <v>4.6043735733614305E-4</v>
       </c>
       <c r="Q2">
-        <v>-1.1962979631865182E-3</v>
+        <v>-1.196216929928484E-3</v>
       </c>
       <c r="R2">
-        <v>-1.7249994550706388E-3</v>
+        <v>-1.7258255830639125E-3</v>
       </c>
       <c r="S2">
-        <v>-1.0098658170196145E-3</v>
+        <v>-1.0103609567496765E-3</v>
       </c>
       <c r="T2">
-        <v>-1.2912129871671943E-3</v>
+        <v>-1.2915105682933757E-3</v>
       </c>
       <c r="U2">
-        <v>-9.0383631110555786E-4</v>
+        <v>-9.0393757910196566E-4</v>
       </c>
       <c r="V2">
-        <v>-9.847330591255081E-4</v>
+        <v>-9.8464210532238231E-4</v>
       </c>
       <c r="W2">
-        <v>-1.0924357778282711E-3</v>
+        <v>-1.092665221925344E-3</v>
       </c>
       <c r="X2">
-        <v>-1.1501715642297061E-3</v>
+        <v>-1.1504169706080141E-3</v>
       </c>
       <c r="Y2">
-        <v>-1.1423072500666908E-3</v>
+        <v>-1.1425412024495055E-3</v>
       </c>
       <c r="Z2">
-        <v>-1.154843522886884E-3</v>
+        <v>-1.1551409165193485E-3</v>
       </c>
       <c r="AA2">
-        <v>-6.7325170719638016E-4</v>
+        <v>-6.7439608985179946E-4</v>
       </c>
       <c r="AB2">
-        <v>-9.5909821632421963E-6</v>
+        <v>-9.628894713794179E-6</v>
       </c>
       <c r="AC2">
-        <v>2.3899944807097111E-4</v>
+        <v>2.3954457091663771E-4</v>
       </c>
       <c r="AD2">
-        <v>2.7816574925235951E-4</v>
+        <v>2.784072028534537E-4</v>
       </c>
       <c r="AE2">
-        <v>-1.3356485573487605E-4</v>
+        <v>-1.339873225772027E-4</v>
       </c>
       <c r="AF2">
-        <v>-4.2796241113990489E-3</v>
+        <v>-4.2823018633447729E-3</v>
       </c>
       <c r="AG2">
-        <v>-4.6336786088605738E-4</v>
+        <v>-4.6276051007821545E-4</v>
       </c>
       <c r="AH2">
-        <v>1.5716426711145401E-3</v>
+        <v>1.5731496333588261E-3</v>
       </c>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.2">
@@ -991,103 +991,103 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.51601815435283793</v>
+        <v>0.51597619795326488</v>
       </c>
       <c r="C3">
-        <v>-3.7221000597152388E-5</v>
+        <v>-3.7255469194964248E-5</v>
       </c>
       <c r="D3">
-        <v>1.7759763502558908E-3</v>
+        <v>1.7761990181611024E-3</v>
       </c>
       <c r="E3">
-        <v>-1.3849941871626024E-5</v>
+        <v>-1.3851846165605547E-5</v>
       </c>
       <c r="F3">
-        <v>-5.7897730298992617E-5</v>
+        <v>-5.8304428329575275E-5</v>
       </c>
       <c r="G3">
-        <v>-1.1735369832007679E-5</v>
+        <v>-7.9036280403558818E-6</v>
       </c>
       <c r="H3">
-        <v>4.5510619755977132E-6</v>
+        <v>4.5540317193094003E-6</v>
       </c>
       <c r="I3">
-        <v>1.0982111255220623E-6</v>
+        <v>1.0982051059420998E-6</v>
       </c>
       <c r="J3">
-        <v>-1.577968697157317E-4</v>
+        <v>-1.5769945476213146E-4</v>
       </c>
       <c r="K3">
-        <v>1.2169642778855627E-3</v>
+        <v>1.2174800680164466E-3</v>
       </c>
       <c r="L3">
-        <v>6.4345649072568289E-4</v>
+        <v>6.4447635752569454E-4</v>
       </c>
       <c r="M3">
-        <v>1.0718837514020474E-3</v>
+        <v>1.0734930272445209E-3</v>
       </c>
       <c r="N3">
-        <v>1.1135467301564839E-3</v>
+        <v>1.1155599124189064E-3</v>
       </c>
       <c r="O3">
-        <v>1.1566480569527304E-3</v>
+        <v>1.1588175219010288E-3</v>
       </c>
       <c r="P3">
-        <v>-4.5181916970053748E-5</v>
+        <v>-4.5202919264623886E-5</v>
       </c>
       <c r="Q3">
-        <v>-1.1816482201765927E-4</v>
+        <v>-1.1881298267574225E-4</v>
       </c>
       <c r="R3">
-        <v>-3.831810565506355E-4</v>
+        <v>-3.8407163789677679E-4</v>
       </c>
       <c r="S3">
-        <v>-1.9572465689284696E-4</v>
+        <v>-1.961903132857018E-4</v>
       </c>
       <c r="T3">
-        <v>-1.9034775348235333E-4</v>
+        <v>-1.9123357446303169E-4</v>
       </c>
       <c r="U3">
-        <v>-4.9112849408235182E-5</v>
+        <v>-4.9529005060874876E-5</v>
       </c>
       <c r="V3">
-        <v>-1.4534294324750063E-4</v>
+        <v>-1.4570018202381824E-4</v>
       </c>
       <c r="W3">
-        <v>-3.3438882093485278E-5</v>
+        <v>-3.3723970293532413E-5</v>
       </c>
       <c r="X3">
-        <v>-1.1659868555197184E-4</v>
+        <v>-1.1711153731298191E-4</v>
       </c>
       <c r="Y3">
-        <v>-1.4601185880170481E-4</v>
+        <v>-1.4678745714986896E-4</v>
       </c>
       <c r="Z3">
-        <v>-1.2150128821220019E-4</v>
+        <v>-1.2197468142541995E-4</v>
       </c>
       <c r="AA3">
-        <v>-1.7457630591909135E-4</v>
+        <v>-1.7609711060475458E-4</v>
       </c>
       <c r="AB3">
-        <v>-2.1414488845452814E-5</v>
+        <v>-2.1390749815840965E-5</v>
       </c>
       <c r="AC3">
-        <v>7.3768484269390311E-5</v>
+        <v>7.4194082303892517E-5</v>
       </c>
       <c r="AD3">
-        <v>8.3024242661412784E-5</v>
+        <v>8.3442471515975114E-5</v>
       </c>
       <c r="AE3">
-        <v>-2.0324666875240829E-4</v>
+        <v>-2.0408464249808619E-4</v>
       </c>
       <c r="AF3">
-        <v>-1.4432699710086316E-3</v>
+        <v>-1.4449645075072515E-3</v>
       </c>
       <c r="AG3">
-        <v>-7.0481832906434203E-5</v>
+        <v>-7.0119841844526812E-5</v>
       </c>
       <c r="AH3">
-        <v>-5.7208342731185038E-2</v>
+        <v>-5.7217288359011374E-2</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.2">
@@ -1095,103 +1095,103 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-3.597955859361499E-3</v>
+        <v>-3.5976238660590386E-3</v>
       </c>
       <c r="C4">
-        <v>6.4772414891427306E-8</v>
+        <v>6.4960058014465595E-8</v>
       </c>
       <c r="D4">
-        <v>-1.3849941871626024E-5</v>
+        <v>-1.3851846165605547E-5</v>
       </c>
       <c r="E4">
-        <v>1.0929083071813395E-7</v>
+        <v>1.0930664765760666E-7</v>
       </c>
       <c r="F4">
-        <v>4.8881032980318965E-7</v>
+        <v>4.9026210171945522E-7</v>
       </c>
       <c r="G4">
-        <v>-7.5137548638683987E-8</v>
+        <v>-1.0400711998548437E-7</v>
       </c>
       <c r="H4">
-        <v>-3.78504831691035E-8</v>
+        <v>-3.7863436297426322E-8</v>
       </c>
       <c r="I4">
-        <v>-1.5869206241652598E-8</v>
+        <v>-1.5851467523072862E-8</v>
       </c>
       <c r="J4">
-        <v>-3.4223423266198458E-7</v>
+        <v>-3.4293769468607665E-7</v>
       </c>
       <c r="K4">
-        <v>-1.0353993321016099E-5</v>
+        <v>-1.0356887249016113E-5</v>
       </c>
       <c r="L4">
-        <v>-5.5134203656734358E-6</v>
+        <v>-5.5201291750194914E-6</v>
       </c>
       <c r="M4">
-        <v>-9.2869777346749668E-6</v>
+        <v>-9.2976535166623513E-6</v>
       </c>
       <c r="N4">
-        <v>-9.4716332493015656E-6</v>
+        <v>-9.4852677225039372E-6</v>
       </c>
       <c r="O4">
-        <v>-9.7391856389795941E-6</v>
+        <v>-9.7543981756407355E-6</v>
       </c>
       <c r="P4">
-        <v>5.4810385649985225E-7</v>
+        <v>5.4847301099274215E-7</v>
       </c>
       <c r="Q4">
-        <v>1.3755914342857348E-6</v>
+        <v>1.3795291867283745E-6</v>
       </c>
       <c r="R4">
-        <v>3.4887530264951679E-6</v>
+        <v>3.4939884152742446E-6</v>
       </c>
       <c r="S4">
-        <v>1.7434568931532076E-6</v>
+        <v>1.7462071489906215E-6</v>
       </c>
       <c r="T4">
-        <v>1.8233501463745406E-6</v>
+        <v>1.8298776638330612E-6</v>
       </c>
       <c r="U4">
-        <v>5.9983265515955574E-7</v>
+        <v>6.0273072696005259E-7</v>
       </c>
       <c r="V4">
-        <v>1.3867467653997647E-6</v>
+        <v>1.3888533162993016E-6</v>
       </c>
       <c r="W4">
-        <v>6.3584161861136032E-7</v>
+        <v>6.369646465037202E-7</v>
       </c>
       <c r="X4">
-        <v>1.17026338321963E-6</v>
+        <v>1.1732989288444975E-6</v>
       </c>
       <c r="Y4">
-        <v>1.179180915106162E-6</v>
+        <v>1.1852007102621138E-6</v>
       </c>
       <c r="Z4">
-        <v>1.2318415760660261E-6</v>
+        <v>1.2344633904560207E-6</v>
       </c>
       <c r="AA4">
-        <v>1.4037523786891086E-6</v>
+        <v>1.4130297614056556E-6</v>
       </c>
       <c r="AB4">
-        <v>1.3115388549533218E-7</v>
+        <v>1.3092676285549076E-7</v>
       </c>
       <c r="AC4">
-        <v>-6.4421253843731895E-7</v>
+        <v>-6.4725658894420647E-7</v>
       </c>
       <c r="AD4">
-        <v>-8.4426249492158562E-7</v>
+        <v>-8.46917291042696E-7</v>
       </c>
       <c r="AE4">
-        <v>1.8824156444837629E-6</v>
+        <v>1.8885013698764351E-6</v>
       </c>
       <c r="AF4">
-        <v>1.2504475447712871E-5</v>
+        <v>1.2513783935876304E-5</v>
       </c>
       <c r="AG4">
-        <v>4.4850648512936622E-7</v>
+        <v>4.4717655558178067E-7</v>
       </c>
       <c r="AH4">
-        <v>4.4352568608887409E-4</v>
+        <v>4.4360144502349994E-4</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.2">
@@ -1199,103 +1199,103 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-7.1507216771985224E-2</v>
+        <v>-7.2645141552528783E-2</v>
       </c>
       <c r="C5">
-        <v>-2.0562352849196942E-4</v>
+        <v>-2.0748578451535772E-4</v>
       </c>
       <c r="D5">
-        <v>-5.7897730298992617E-5</v>
+        <v>-5.8304428329575275E-5</v>
       </c>
       <c r="E5">
-        <v>4.8881032980318965E-7</v>
+        <v>4.9026210171945522E-7</v>
       </c>
       <c r="F5">
-        <v>2.3811437434428815E-3</v>
+        <v>2.3865073330420162E-3</v>
       </c>
       <c r="G5">
-        <v>1.7085055558805839E-3</v>
+        <v>1.7100585547271234E-3</v>
       </c>
       <c r="H5">
-        <v>-1.3900231954001944E-5</v>
+        <v>-1.3874103618579035E-5</v>
       </c>
       <c r="I5">
-        <v>-1.1162192775048216E-5</v>
+        <v>-1.117082903292491E-5</v>
       </c>
       <c r="J5">
-        <v>1.1272291384015177E-4</v>
+        <v>1.1418403061337607E-4</v>
       </c>
       <c r="K5">
-        <v>-5.0189334682182625E-4</v>
+        <v>-4.9904861517102326E-4</v>
       </c>
       <c r="L5">
-        <v>-9.1475532328687444E-4</v>
+        <v>-9.1591495283498831E-4</v>
       </c>
       <c r="M5">
-        <v>-8.9185098652038233E-4</v>
+        <v>-8.9192590848376045E-4</v>
       </c>
       <c r="N5">
-        <v>-7.9710723232193689E-4</v>
+        <v>-8.0045938912392308E-4</v>
       </c>
       <c r="O5">
-        <v>-2.4862275678907801E-4</v>
+        <v>-2.469983590830992E-4</v>
       </c>
       <c r="P5">
-        <v>-5.9694186046919278E-4</v>
+        <v>-5.9902793620118116E-4</v>
       </c>
       <c r="Q5">
-        <v>5.2160182075045307E-4</v>
+        <v>5.1944245634604727E-4</v>
       </c>
       <c r="R5">
-        <v>1.2372529205743592E-3</v>
+        <v>1.238100589835426E-3</v>
       </c>
       <c r="S5">
-        <v>9.6536709390601379E-4</v>
+        <v>9.6693023960063573E-4</v>
       </c>
       <c r="T5">
-        <v>6.1468788242573041E-4</v>
+        <v>6.1768553182833569E-4</v>
       </c>
       <c r="U5">
-        <v>5.3857973051496771E-4</v>
+        <v>5.373693806418234E-4</v>
       </c>
       <c r="V5">
-        <v>6.3533371820659388E-4</v>
+        <v>6.3231930927641275E-4</v>
       </c>
       <c r="W5">
-        <v>9.3796792388116087E-4</v>
+        <v>9.360301261169086E-4</v>
       </c>
       <c r="X5">
-        <v>8.2964670507371888E-4</v>
+        <v>8.2958681279894381E-4</v>
       </c>
       <c r="Y5">
-        <v>9.1399263301876628E-4</v>
+        <v>9.1792796731814119E-4</v>
       </c>
       <c r="Z5">
-        <v>6.8644692588015776E-4</v>
+        <v>6.8704818128752405E-4</v>
       </c>
       <c r="AA5">
-        <v>1.1924040947890843E-3</v>
+        <v>1.1935343535236424E-3</v>
       </c>
       <c r="AB5">
-        <v>1.3455199897537487E-5</v>
+        <v>1.3681131692889375E-5</v>
       </c>
       <c r="AC5">
-        <v>-7.0154215605294475E-5</v>
+        <v>-7.477171489832235E-5</v>
       </c>
       <c r="AD5">
-        <v>1.2208520768304879E-5</v>
+        <v>1.228943983439131E-5</v>
       </c>
       <c r="AE5">
-        <v>3.220369553871658E-4</v>
+        <v>3.2282307109531591E-4</v>
       </c>
       <c r="AF5">
-        <v>3.6298414841735502E-3</v>
+        <v>3.6356188324013251E-3</v>
       </c>
       <c r="AG5">
-        <v>3.6257130334769691E-4</v>
+        <v>3.6482834998838754E-4</v>
       </c>
       <c r="AH5">
-        <v>1.0284453137187339E-3</v>
+        <v>1.0412056092644426E-3</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.2">
@@ -1303,103 +1303,103 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-0.11467903438673017</v>
+        <v>-0.11633779590899834</v>
       </c>
       <c r="C6">
-        <v>-2.0822440536719312E-4</v>
+        <v>-2.0779793968747878E-4</v>
       </c>
       <c r="D6">
-        <v>-1.1735369832007679E-5</v>
+        <v>-7.9036280403558818E-6</v>
       </c>
       <c r="E6">
-        <v>-7.5137548638683987E-8</v>
+        <v>-1.0400711998548437E-7</v>
       </c>
       <c r="F6">
-        <v>1.7085055558805839E-3</v>
+        <v>1.7100585547271234E-3</v>
       </c>
       <c r="G6">
-        <v>3.1937430985295315E-3</v>
+        <v>3.1865651731540602E-3</v>
       </c>
       <c r="H6">
-        <v>-6.7386713221845171E-7</v>
+        <v>-6.2401031185589133E-7</v>
       </c>
       <c r="I6">
-        <v>-4.237051459351654E-6</v>
+        <v>-4.3308130614073355E-6</v>
       </c>
       <c r="J6">
-        <v>3.88135353909906E-4</v>
+        <v>3.9078341527845259E-4</v>
       </c>
       <c r="K6">
-        <v>4.219097022249616E-4</v>
+        <v>4.2677714760033835E-4</v>
       </c>
       <c r="L6">
-        <v>1.9428022093635647E-4</v>
+        <v>1.9805583881503299E-4</v>
       </c>
       <c r="M6">
-        <v>7.0330448362312037E-4</v>
+        <v>7.0931115276663724E-4</v>
       </c>
       <c r="N6">
-        <v>9.5772644286733948E-4</v>
+        <v>9.5993725590227865E-4</v>
       </c>
       <c r="O6">
-        <v>1.4255193190902409E-3</v>
+        <v>1.4307525747664029E-3</v>
       </c>
       <c r="P6">
-        <v>-2.3409187487754516E-4</v>
+        <v>-2.2942689898118227E-4</v>
       </c>
       <c r="Q6">
-        <v>-3.5261815585580435E-4</v>
+        <v>-3.5209478615387622E-4</v>
       </c>
       <c r="R6">
-        <v>-3.6858311537051741E-4</v>
+        <v>-3.6887401135022495E-4</v>
       </c>
       <c r="S6">
-        <v>2.3344663094671198E-4</v>
+        <v>2.3201973583002666E-4</v>
       </c>
       <c r="T6">
-        <v>-3.2922110499106129E-4</v>
+        <v>-3.3424661907031992E-4</v>
       </c>
       <c r="U6">
-        <v>-1.0398223168221114E-4</v>
+        <v>-1.0707033493597665E-4</v>
       </c>
       <c r="V6">
-        <v>-1.2764322120737629E-4</v>
+        <v>-1.313032641487757E-4</v>
       </c>
       <c r="W6">
-        <v>-6.5424311590343712E-5</v>
+        <v>-6.6732746928455837E-5</v>
       </c>
       <c r="X6">
-        <v>-1.5177530750236888E-4</v>
+        <v>-1.5389007778650061E-4</v>
       </c>
       <c r="Y6">
-        <v>-3.7710233893113666E-4</v>
+        <v>-3.8920613272410808E-4</v>
       </c>
       <c r="Z6">
-        <v>-2.4304529010942249E-4</v>
+        <v>-2.4212543880392347E-4</v>
       </c>
       <c r="AA6">
-        <v>-8.1107138794252686E-4</v>
+        <v>-8.0578056156833098E-4</v>
       </c>
       <c r="AB6">
-        <v>6.513069069771912E-6</v>
+        <v>6.8143731573285296E-6</v>
       </c>
       <c r="AC6">
-        <v>2.2530026226605837E-4</v>
+        <v>2.2518313282466392E-4</v>
       </c>
       <c r="AD6">
-        <v>5.4098960169393466E-4</v>
+        <v>5.4007716534134318E-4</v>
       </c>
       <c r="AE6">
-        <v>-2.5592402160860513E-4</v>
+        <v>-2.5804718849088205E-4</v>
       </c>
       <c r="AF6">
-        <v>1.6784197773048529E-5</v>
+        <v>6.019385197265914E-6</v>
       </c>
       <c r="AG6">
-        <v>4.270278188862661E-4</v>
+        <v>4.1359957179699989E-4</v>
       </c>
       <c r="AH6">
-        <v>-1.285783073726635E-3</v>
+        <v>-1.4204445317214421E-3</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.2">
@@ -1407,103 +1407,103 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>-3.7263926766791374E-3</v>
+        <v>-3.7303151061770221E-3</v>
       </c>
       <c r="C7">
-        <v>3.8689516840200732E-6</v>
+        <v>3.8749924739925942E-6</v>
       </c>
       <c r="D7">
-        <v>4.5510619755977132E-6</v>
+        <v>4.5540317193094003E-6</v>
       </c>
       <c r="E7">
-        <v>-3.78504831691035E-8</v>
+        <v>-3.7863436297426322E-8</v>
       </c>
       <c r="F7">
-        <v>-1.3900231954001944E-5</v>
+        <v>-1.3874103618579035E-5</v>
       </c>
       <c r="G7">
-        <v>-6.7386713221845171E-7</v>
+        <v>-6.2401031185589133E-7</v>
       </c>
       <c r="H7">
-        <v>3.6705347384126281E-6</v>
+        <v>3.6705254214032258E-6</v>
       </c>
       <c r="I7">
-        <v>4.2345579782747338E-7</v>
+        <v>4.2271688336731026E-7</v>
       </c>
       <c r="J7">
-        <v>-7.6100774806769206E-7</v>
+        <v>-7.5932866323189473E-7</v>
       </c>
       <c r="K7">
-        <v>5.3773258391987618E-5</v>
+        <v>5.3765625357840162E-5</v>
       </c>
       <c r="L7">
-        <v>3.6867309317916059E-5</v>
+        <v>3.6865844221213248E-5</v>
       </c>
       <c r="M7">
-        <v>4.0927434184745079E-5</v>
+        <v>4.0927763753897213E-5</v>
       </c>
       <c r="N7">
-        <v>4.8373808550933447E-5</v>
+        <v>4.8395541452294797E-5</v>
       </c>
       <c r="O7">
-        <v>3.0899879443307596E-5</v>
+        <v>3.0922968614743385E-5</v>
       </c>
       <c r="P7">
-        <v>5.6913455526318328E-5</v>
+        <v>5.693689756194374E-5</v>
       </c>
       <c r="Q7">
-        <v>-4.456480910833868E-5</v>
+        <v>-4.4531243722130745E-5</v>
       </c>
       <c r="R7">
-        <v>-7.9106318668780936E-5</v>
+        <v>-7.9094778995130377E-5</v>
       </c>
       <c r="S7">
-        <v>-3.6095755063872984E-5</v>
+        <v>-3.6067708511942507E-5</v>
       </c>
       <c r="T7">
-        <v>-4.3486761779856396E-5</v>
+        <v>-4.3503363720806586E-5</v>
       </c>
       <c r="U7">
-        <v>-3.9288734670354209E-5</v>
+        <v>-3.9270380720104336E-5</v>
       </c>
       <c r="V7">
-        <v>-4.5478000587014568E-5</v>
+        <v>-4.5443583192592165E-5</v>
       </c>
       <c r="W7">
-        <v>-3.9519927201841414E-5</v>
+        <v>-3.9485421556802641E-5</v>
       </c>
       <c r="X7">
-        <v>-5.2663112499476064E-5</v>
+        <v>-5.2642390306993338E-5</v>
       </c>
       <c r="Y7">
-        <v>-5.3037754652481754E-5</v>
+        <v>-5.3065848629901358E-5</v>
       </c>
       <c r="Z7">
-        <v>-5.2587838813649416E-5</v>
+        <v>-5.2565808822866209E-5</v>
       </c>
       <c r="AA7">
-        <v>-6.4884877886612767E-5</v>
+        <v>-6.4860692325813756E-5</v>
       </c>
       <c r="AB7">
-        <v>-3.0175474393208867E-7</v>
+        <v>-3.0101125077156411E-7</v>
       </c>
       <c r="AC7">
-        <v>8.2237333035854081E-6</v>
+        <v>8.2442642542627565E-6</v>
       </c>
       <c r="AD7">
-        <v>1.2351937744690619E-5</v>
+        <v>1.2367202380624871E-5</v>
       </c>
       <c r="AE7">
-        <v>-1.5065600838914652E-5</v>
+        <v>-1.507802647904497E-5</v>
       </c>
       <c r="AF7">
-        <v>-2.0193319986267356E-4</v>
+        <v>-2.0189317452700404E-4</v>
       </c>
       <c r="AG7">
-        <v>-1.1366567289394905E-5</v>
+        <v>-1.1410297390924243E-5</v>
       </c>
       <c r="AH7">
-        <v>-3.2331068767199795E-4</v>
+        <v>-3.2349648031645777E-4</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.2">
@@ -1511,103 +1511,103 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>-4.8618202773207232E-4</v>
+        <v>-4.8303395460764934E-4</v>
       </c>
       <c r="C8">
-        <v>-7.5657553833130118E-6</v>
+        <v>-7.5620935218659037E-6</v>
       </c>
       <c r="D8">
-        <v>1.0982111255220623E-6</v>
+        <v>1.0982051059420998E-6</v>
       </c>
       <c r="E8">
-        <v>-1.5869206241652598E-8</v>
+        <v>-1.5851467523072862E-8</v>
       </c>
       <c r="F8">
-        <v>-1.1162192775048216E-5</v>
+        <v>-1.117082903292491E-5</v>
       </c>
       <c r="G8">
-        <v>-4.237051459351654E-6</v>
+        <v>-4.3308130614073355E-6</v>
       </c>
       <c r="H8">
-        <v>4.2345579782747338E-7</v>
+        <v>4.2271688336731026E-7</v>
       </c>
       <c r="I8">
-        <v>3.2152322627037443E-6</v>
+        <v>3.2145993754362767E-6</v>
       </c>
       <c r="J8">
-        <v>-1.1135364278935786E-5</v>
+        <v>-1.1156017633006518E-5</v>
       </c>
       <c r="K8">
-        <v>-1.549149465814774E-6</v>
+        <v>-1.6079775695276464E-6</v>
       </c>
       <c r="L8">
-        <v>8.7601248456730427E-6</v>
+        <v>8.6994982534420646E-6</v>
       </c>
       <c r="M8">
-        <v>-1.6376100031404838E-5</v>
+        <v>-1.6465480932469426E-5</v>
       </c>
       <c r="N8">
-        <v>-1.8539937469083841E-5</v>
+        <v>-1.8624955950558258E-5</v>
       </c>
       <c r="O8">
-        <v>-2.3080870424543073E-5</v>
+        <v>-2.3172873892009769E-5</v>
       </c>
       <c r="P8">
-        <v>1.7411794912582793E-5</v>
+        <v>1.7399437326567918E-5</v>
       </c>
       <c r="Q8">
-        <v>-8.7508313021763976E-6</v>
+        <v>-8.671437795624052E-6</v>
       </c>
       <c r="R8">
-        <v>-7.6880857549925692E-6</v>
+        <v>-7.5835420391289388E-6</v>
       </c>
       <c r="S8">
-        <v>-8.1507726445603464E-6</v>
+        <v>-8.0894635348666014E-6</v>
       </c>
       <c r="T8">
-        <v>-1.7970912302829817E-5</v>
+        <v>-1.7910593406075603E-5</v>
       </c>
       <c r="U8">
-        <v>-1.2598474277910297E-5</v>
+        <v>-1.2539374583407339E-5</v>
       </c>
       <c r="V8">
-        <v>-1.6524366834896165E-5</v>
+        <v>-1.6454346157781423E-5</v>
       </c>
       <c r="W8">
-        <v>-1.4399214004307828E-5</v>
+        <v>-1.4318271615701428E-5</v>
       </c>
       <c r="X8">
-        <v>-1.7159754152147946E-5</v>
+        <v>-1.7081177313098294E-5</v>
       </c>
       <c r="Y8">
-        <v>-1.5629270179927227E-5</v>
+        <v>-1.5556397394592071E-5</v>
       </c>
       <c r="Z8">
-        <v>-1.5351652430080565E-5</v>
+        <v>-1.5282545453612541E-5</v>
       </c>
       <c r="AA8">
-        <v>-3.6326354668531215E-5</v>
+        <v>-3.6197719127975341E-5</v>
       </c>
       <c r="AB8">
-        <v>1.7226003919480057E-6</v>
+        <v>1.7230136200941106E-6</v>
       </c>
       <c r="AC8">
-        <v>-6.7303034800909769E-7</v>
+        <v>-6.8339890418574537E-7</v>
       </c>
       <c r="AD8">
-        <v>-8.9726751490706511E-7</v>
+        <v>-9.2613604091743387E-7</v>
       </c>
       <c r="AE8">
-        <v>-1.4615227430008252E-5</v>
+        <v>-1.4588301351949894E-5</v>
       </c>
       <c r="AF8">
-        <v>1.7071736895229962E-5</v>
+        <v>1.7284044444611842E-5</v>
       </c>
       <c r="AG8">
-        <v>-2.537323481334834E-6</v>
+        <v>-2.5535628020466579E-6</v>
       </c>
       <c r="AH8">
-        <v>-1.7234077610545748E-4</v>
+        <v>-1.7230645427570465E-4</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.2">
@@ -1615,103 +1615,103 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>0.76317033407790569</v>
+        <v>0.76317454478752422</v>
       </c>
       <c r="C9">
-        <v>5.982792048583852E-4</v>
+        <v>5.9827565431061426E-4</v>
       </c>
       <c r="D9">
-        <v>-1.577968697157317E-4</v>
+        <v>-1.5769945476213146E-4</v>
       </c>
       <c r="E9">
-        <v>-3.4223423266198458E-7</v>
+        <v>-3.4293769468607665E-7</v>
       </c>
       <c r="F9">
-        <v>1.1272291384015177E-4</v>
+        <v>1.1418403061337607E-4</v>
       </c>
       <c r="G9">
-        <v>3.88135353909906E-4</v>
+        <v>3.9078341527845259E-4</v>
       </c>
       <c r="H9">
-        <v>-7.6100774806769206E-7</v>
+        <v>-7.5932866323189473E-7</v>
       </c>
       <c r="I9">
-        <v>-1.1135364278935786E-5</v>
+        <v>-1.1156017633006518E-5</v>
       </c>
       <c r="J9">
-        <v>3.7379922552623667E-3</v>
+        <v>3.7382377812147597E-3</v>
       </c>
       <c r="K9">
-        <v>1.4763102363168357E-3</v>
+        <v>1.4753568988152554E-3</v>
       </c>
       <c r="L9">
-        <v>5.1227277017757214E-4</v>
+        <v>5.1164730060006963E-4</v>
       </c>
       <c r="M9">
-        <v>1.2739867914771177E-3</v>
+        <v>1.2729122240458662E-3</v>
       </c>
       <c r="N9">
-        <v>1.3236039865338334E-3</v>
+        <v>1.3225698258609378E-3</v>
       </c>
       <c r="O9">
-        <v>1.3641492843854963E-3</v>
+        <v>1.3638170881669007E-3</v>
       </c>
       <c r="P9">
-        <v>-4.2574892420049401E-5</v>
+        <v>-4.300420491561846E-5</v>
       </c>
       <c r="Q9">
-        <v>-6.2487208335253175E-4</v>
+        <v>-6.2433237836262943E-4</v>
       </c>
       <c r="R9">
-        <v>-1.022824043948406E-3</v>
+        <v>-1.022023229298008E-3</v>
       </c>
       <c r="S9">
-        <v>-6.2550295880437964E-5</v>
+        <v>-6.1942319330094212E-5</v>
       </c>
       <c r="T9">
-        <v>-3.7698572746154915E-4</v>
+        <v>-3.773027874134742E-4</v>
       </c>
       <c r="U9">
-        <v>-1.9525169348198236E-4</v>
+        <v>-1.9562495085715705E-4</v>
       </c>
       <c r="V9">
-        <v>-2.3339764858111046E-4</v>
+        <v>-2.3314059319947192E-4</v>
       </c>
       <c r="W9">
-        <v>-7.1547489369348273E-4</v>
+        <v>-7.1488028150213344E-4</v>
       </c>
       <c r="X9">
-        <v>-5.4547268011928725E-4</v>
+        <v>-5.4502263269484534E-4</v>
       </c>
       <c r="Y9">
-        <v>-2.6456056178748681E-4</v>
+        <v>-2.6529179922785834E-4</v>
       </c>
       <c r="Z9">
-        <v>-3.6362801984441036E-4</v>
+        <v>-3.6292247941270561E-4</v>
       </c>
       <c r="AA9">
-        <v>-2.031664107929633E-4</v>
+        <v>-2.0214024603167069E-4</v>
       </c>
       <c r="AB9">
-        <v>5.4182694337199123E-5</v>
+        <v>5.4283043635743912E-5</v>
       </c>
       <c r="AC9">
-        <v>1.579359286024689E-4</v>
+        <v>1.5773557233882303E-4</v>
       </c>
       <c r="AD9">
-        <v>5.8132769883256948E-4</v>
+        <v>5.8116835579826061E-4</v>
       </c>
       <c r="AE9">
-        <v>-1.8222289801069977E-4</v>
+        <v>-1.8270190902896534E-4</v>
       </c>
       <c r="AF9">
-        <v>-3.3383567065673886E-3</v>
+        <v>-3.3352720278828352E-3</v>
       </c>
       <c r="AG9">
-        <v>5.3409354832910231E-4</v>
+        <v>5.3317149618431405E-4</v>
       </c>
       <c r="AH9">
-        <v>7.9390310698239826E-3</v>
+        <v>7.9336691023474334E-3</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.2">
@@ -1719,103 +1719,103 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>0.46706329757145792</v>
+        <v>0.46704352983466363</v>
       </c>
       <c r="C10">
-        <v>7.041998484249622E-4</v>
+        <v>7.0475624649908152E-4</v>
       </c>
       <c r="D10">
-        <v>1.2169642778855627E-3</v>
+        <v>1.2174800680164466E-3</v>
       </c>
       <c r="E10">
-        <v>-1.0353993321016099E-5</v>
+        <v>-1.0356887249016113E-5</v>
       </c>
       <c r="F10">
-        <v>-5.0189334682182625E-4</v>
+        <v>-4.9904861517102326E-4</v>
       </c>
       <c r="G10">
-        <v>4.219097022249616E-4</v>
+        <v>4.2677714760033835E-4</v>
       </c>
       <c r="H10">
-        <v>5.3773258391987618E-5</v>
+        <v>5.3765625357840162E-5</v>
       </c>
       <c r="I10">
-        <v>-1.549149465814774E-6</v>
+        <v>-1.6079775695276464E-6</v>
       </c>
       <c r="J10">
-        <v>1.4763102363168357E-3</v>
+        <v>1.4753568988152554E-3</v>
       </c>
       <c r="K10">
-        <v>1.0774079599253868E-2</v>
+        <v>1.0771996760356513E-2</v>
       </c>
       <c r="L10">
-        <v>5.7604126401509283E-3</v>
+        <v>5.759954566019073E-3</v>
       </c>
       <c r="M10">
-        <v>1.0863971123695727E-2</v>
+        <v>1.0861205746355136E-2</v>
       </c>
       <c r="N10">
-        <v>1.1601086686978415E-2</v>
+        <v>1.1600062812356794E-2</v>
       </c>
       <c r="O10">
-        <v>1.1114250693718464E-2</v>
+        <v>1.1113820979844743E-2</v>
       </c>
       <c r="P10">
-        <v>8.9733520833347805E-4</v>
+        <v>8.9696904951721418E-4</v>
       </c>
       <c r="Q10">
-        <v>-3.3889858531435859E-3</v>
+        <v>-3.387640257984971E-3</v>
       </c>
       <c r="R10">
-        <v>-7.2776146401295483E-3</v>
+        <v>-7.277255876424929E-3</v>
       </c>
       <c r="S10">
-        <v>-2.961073702059917E-3</v>
+        <v>-2.9602118685094735E-3</v>
       </c>
       <c r="T10">
-        <v>-3.1563411674357059E-3</v>
+        <v>-3.1579580672437112E-3</v>
       </c>
       <c r="U10">
-        <v>-2.3086834048780466E-3</v>
+        <v>-2.3090191549817451E-3</v>
       </c>
       <c r="V10">
-        <v>-2.9730178334474965E-3</v>
+        <v>-2.9718768074558349E-3</v>
       </c>
       <c r="W10">
-        <v>-2.9981899491668632E-3</v>
+        <v>-2.9964422876942436E-3</v>
       </c>
       <c r="X10">
-        <v>-3.5677001716953229E-3</v>
+        <v>-3.5669820404849849E-3</v>
       </c>
       <c r="Y10">
-        <v>-3.2642754439391256E-3</v>
+        <v>-3.2659079395376805E-3</v>
       </c>
       <c r="Z10">
-        <v>-3.3970837117349752E-3</v>
+        <v>-3.3959438589497345E-3</v>
       </c>
       <c r="AA10">
-        <v>-3.6756824102319348E-3</v>
+        <v>-3.6745430814306874E-3</v>
       </c>
       <c r="AB10">
-        <v>-1.7550987748494356E-4</v>
+        <v>-1.7534877365664404E-4</v>
       </c>
       <c r="AC10">
-        <v>1.4977359110327788E-3</v>
+        <v>1.498606757074715E-3</v>
       </c>
       <c r="AD10">
-        <v>1.6003908164010459E-3</v>
+        <v>1.6004798899475862E-3</v>
       </c>
       <c r="AE10">
-        <v>-1.0716389002940457E-3</v>
+        <v>-1.0735279842179913E-3</v>
       </c>
       <c r="AF10">
-        <v>-2.3012891822242615E-2</v>
+        <v>-2.3007373902769634E-2</v>
       </c>
       <c r="AG10">
-        <v>1.5910213733708414E-4</v>
+        <v>1.5714877147954146E-4</v>
       </c>
       <c r="AH10">
-        <v>-4.3683841851853228E-2</v>
+        <v>-4.3706826687121766E-2</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.2">
@@ -1823,103 +1823,103 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>2.8451394660730704E-2</v>
+        <v>2.8323464631268867E-2</v>
       </c>
       <c r="C11">
-        <v>9.0288484663960961E-4</v>
+        <v>9.036371025626733E-4</v>
       </c>
       <c r="D11">
-        <v>6.4345649072568289E-4</v>
+        <v>6.4447635752569454E-4</v>
       </c>
       <c r="E11">
-        <v>-5.5134203656734358E-6</v>
+        <v>-5.5201291750194914E-6</v>
       </c>
       <c r="F11">
-        <v>-9.1475532328687444E-4</v>
+        <v>-9.1591495283498831E-4</v>
       </c>
       <c r="G11">
-        <v>1.9428022093635647E-4</v>
+        <v>1.9805583881503299E-4</v>
       </c>
       <c r="H11">
-        <v>3.6867309317916059E-5</v>
+        <v>3.6865844221213248E-5</v>
       </c>
       <c r="I11">
-        <v>8.7601248456730427E-6</v>
+        <v>8.6994982534420646E-6</v>
       </c>
       <c r="J11">
-        <v>5.1227277017757214E-4</v>
+        <v>5.1164730060006963E-4</v>
       </c>
       <c r="K11">
-        <v>5.7604126401509283E-3</v>
+        <v>5.759954566019073E-3</v>
       </c>
       <c r="L11">
-        <v>7.7633369025684167E-3</v>
+        <v>7.7649693929451391E-3</v>
       </c>
       <c r="M11">
-        <v>8.6592270527424357E-3</v>
+        <v>8.6600627856620246E-3</v>
       </c>
       <c r="N11">
-        <v>8.9662336051276412E-3</v>
+        <v>8.9689435716693924E-3</v>
       </c>
       <c r="O11">
-        <v>8.3492232508674945E-3</v>
+        <v>8.3515497918105162E-3</v>
       </c>
       <c r="P11">
-        <v>2.2169767499534924E-3</v>
+        <v>2.2181609683460043E-3</v>
       </c>
       <c r="Q11">
-        <v>-3.7922967977838109E-3</v>
+        <v>-3.7901294281876977E-3</v>
       </c>
       <c r="R11">
-        <v>-7.0347615237210739E-3</v>
+        <v>-7.0350822214457591E-3</v>
       </c>
       <c r="S11">
-        <v>-3.5325438495137579E-3</v>
+        <v>-3.5320773097815327E-3</v>
       </c>
       <c r="T11">
-        <v>-3.6861165655699725E-3</v>
+        <v>-3.6886945138835253E-3</v>
       </c>
       <c r="U11">
-        <v>-3.1419904966237693E-3</v>
+        <v>-3.1420362437829009E-3</v>
       </c>
       <c r="V11">
-        <v>-3.7019928347610791E-3</v>
+        <v>-3.7006312744867365E-3</v>
       </c>
       <c r="W11">
-        <v>-3.5903177546743417E-3</v>
+        <v>-3.5884353277335643E-3</v>
       </c>
       <c r="X11">
-        <v>-3.9154658742369692E-3</v>
+        <v>-3.9149208084051281E-3</v>
       </c>
       <c r="Y11">
-        <v>-4.3349079283260894E-3</v>
+        <v>-4.3387438802221477E-3</v>
       </c>
       <c r="Z11">
-        <v>-3.537215179007651E-3</v>
+        <v>-3.5359702014658052E-3</v>
       </c>
       <c r="AA11">
-        <v>-4.3500593473219159E-3</v>
+        <v>-4.3494662285958642E-3</v>
       </c>
       <c r="AB11">
-        <v>-1.1146434163181851E-4</v>
+        <v>-1.1137329201647784E-4</v>
       </c>
       <c r="AC11">
-        <v>1.0611165636366837E-3</v>
+        <v>1.0631027921588743E-3</v>
       </c>
       <c r="AD11">
-        <v>1.0713022314313625E-3</v>
+        <v>1.0715308746698604E-3</v>
       </c>
       <c r="AE11">
-        <v>-8.0609434730715313E-4</v>
+        <v>-8.0762270224728878E-4</v>
       </c>
       <c r="AF11">
-        <v>-1.8745656618896937E-2</v>
+        <v>-1.8745668644477419E-2</v>
       </c>
       <c r="AG11">
-        <v>-5.813230327526989E-4</v>
+        <v>-5.8436862514844238E-4</v>
       </c>
       <c r="AH11">
-        <v>-2.395457321193321E-2</v>
+        <v>-2.399423154617724E-2</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.2">
@@ -1927,103 +1927,103 @@
         <v>23</v>
       </c>
       <c r="B12">
-        <v>-0.12103968477857449</v>
+        <v>-0.12115823599768669</v>
       </c>
       <c r="C12">
-        <v>1.3250295488772381E-3</v>
+        <v>1.3260898149406886E-3</v>
       </c>
       <c r="D12">
-        <v>1.0718837514020474E-3</v>
+        <v>1.0734930272445209E-3</v>
       </c>
       <c r="E12">
-        <v>-9.2869777346749668E-6</v>
+        <v>-9.2976535166623513E-6</v>
       </c>
       <c r="F12">
-        <v>-8.9185098652038233E-4</v>
+        <v>-8.9192590848376045E-4</v>
       </c>
       <c r="G12">
-        <v>7.0330448362312037E-4</v>
+        <v>7.0931115276663724E-4</v>
       </c>
       <c r="H12">
-        <v>4.0927434184745079E-5</v>
+        <v>4.0927763753897213E-5</v>
       </c>
       <c r="I12">
-        <v>-1.6376100031404838E-5</v>
+        <v>-1.6465480932469426E-5</v>
       </c>
       <c r="J12">
-        <v>1.2739867914771177E-3</v>
+        <v>1.2729122240458662E-3</v>
       </c>
       <c r="K12">
-        <v>1.0863971123695727E-2</v>
+        <v>1.0861205746355136E-2</v>
       </c>
       <c r="L12">
-        <v>8.6592270527424357E-3</v>
+        <v>8.6600627856620246E-3</v>
       </c>
       <c r="M12">
-        <v>1.6404586479712567E-2</v>
+        <v>1.6403306502944692E-2</v>
       </c>
       <c r="N12">
-        <v>1.533773300248129E-2</v>
+        <v>1.5338371884165279E-2</v>
       </c>
       <c r="O12">
-        <v>1.4636778525933189E-2</v>
+        <v>1.463750148775679E-2</v>
       </c>
       <c r="P12">
-        <v>3.1593158007567541E-3</v>
+        <v>3.1602954210189654E-3</v>
       </c>
       <c r="Q12">
-        <v>-5.3692812060422276E-3</v>
+        <v>-5.3667499881119921E-3</v>
       </c>
       <c r="R12">
-        <v>-1.046661258676139E-2</v>
+        <v>-1.0466056223736843E-2</v>
       </c>
       <c r="S12">
-        <v>-4.5519473304118409E-3</v>
+        <v>-4.5515410322003892E-3</v>
       </c>
       <c r="T12">
-        <v>-4.7847108127675626E-3</v>
+        <v>-4.7886714483998116E-3</v>
       </c>
       <c r="U12">
-        <v>-4.059728804706811E-3</v>
+        <v>-4.060707637841136E-3</v>
       </c>
       <c r="V12">
-        <v>-4.7238888628090437E-3</v>
+        <v>-4.72269334923975E-3</v>
       </c>
       <c r="W12">
-        <v>-4.8753050863960829E-3</v>
+        <v>-4.8726554079112959E-3</v>
       </c>
       <c r="X12">
-        <v>-5.2996114354346606E-3</v>
+        <v>-5.2988742444510795E-3</v>
       </c>
       <c r="Y12">
-        <v>-5.5920306680627817E-3</v>
+        <v>-5.5974723656057939E-3</v>
       </c>
       <c r="Z12">
-        <v>-5.0219655595727664E-3</v>
+        <v>-5.0202967614037808E-3</v>
       </c>
       <c r="AA12">
-        <v>-5.5601789479914118E-3</v>
+        <v>-5.5579350291298105E-3</v>
       </c>
       <c r="AB12">
-        <v>-2.2765543498336639E-4</v>
+        <v>-2.2742670042666337E-4</v>
       </c>
       <c r="AC12">
-        <v>1.9520336994573763E-3</v>
+        <v>1.954105185215872E-3</v>
       </c>
       <c r="AD12">
-        <v>2.2657873002475894E-3</v>
+        <v>2.2653443312605176E-3</v>
       </c>
       <c r="AE12">
-        <v>-9.4644610922082128E-4</v>
+        <v>-9.4949965991187116E-4</v>
       </c>
       <c r="AF12">
-        <v>-2.96100317643683E-2</v>
+        <v>-2.9606475169022872E-2</v>
       </c>
       <c r="AG12">
-        <v>-6.0770265234587546E-4</v>
+        <v>-6.1287725232649526E-4</v>
       </c>
       <c r="AH12">
-        <v>-3.8385164177546907E-2</v>
+        <v>-3.8446727236973351E-2</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.2">
@@ -2031,103 +2031,103 @@
         <v>24</v>
       </c>
       <c r="B13">
-        <v>-8.6933401140201844E-2</v>
+        <v>-8.7079904789529275E-2</v>
       </c>
       <c r="C13">
-        <v>1.2281547617617608E-3</v>
+        <v>1.2297555743673375E-3</v>
       </c>
       <c r="D13">
-        <v>1.1135467301564839E-3</v>
+        <v>1.1155599124189064E-3</v>
       </c>
       <c r="E13">
-        <v>-9.4716332493015656E-6</v>
+        <v>-9.4852677225039372E-6</v>
       </c>
       <c r="F13">
-        <v>-7.9710723232193689E-4</v>
+        <v>-8.0045938912392308E-4</v>
       </c>
       <c r="G13">
-        <v>9.5772644286733948E-4</v>
+        <v>9.5993725590227865E-4</v>
       </c>
       <c r="H13">
-        <v>4.8373808550933447E-5</v>
+        <v>4.8395541452294797E-5</v>
       </c>
       <c r="I13">
-        <v>-1.8539937469083841E-5</v>
+        <v>-1.8624955950558258E-5</v>
       </c>
       <c r="J13">
-        <v>1.3236039865338334E-3</v>
+        <v>1.3225698258609378E-3</v>
       </c>
       <c r="K13">
-        <v>1.1601086686978415E-2</v>
+        <v>1.1600062812356794E-2</v>
       </c>
       <c r="L13">
-        <v>8.9662336051276412E-3</v>
+        <v>8.9689435716693924E-3</v>
       </c>
       <c r="M13">
-        <v>1.533773300248129E-2</v>
+        <v>1.5338371884165279E-2</v>
       </c>
       <c r="N13">
-        <v>1.7663312953374727E-2</v>
+        <v>1.766611065040528E-2</v>
       </c>
       <c r="O13">
-        <v>1.5494420968188458E-2</v>
+        <v>1.5496257233729863E-2</v>
       </c>
       <c r="P13">
-        <v>3.305966189111539E-3</v>
+        <v>3.308322695153668E-3</v>
       </c>
       <c r="Q13">
-        <v>-5.057688838449992E-3</v>
+        <v>-5.0557760084747952E-3</v>
       </c>
       <c r="R13">
-        <v>-1.0673664857550927E-2</v>
+        <v>-1.067569271665841E-2</v>
       </c>
       <c r="S13">
-        <v>-4.4475481501744848E-3</v>
+        <v>-4.4485142538378316E-3</v>
       </c>
       <c r="T13">
-        <v>-4.7299971134465895E-3</v>
+        <v>-4.7351567209534739E-3</v>
       </c>
       <c r="U13">
-        <v>-3.9881390170579331E-3</v>
+        <v>-3.9901288368114672E-3</v>
       </c>
       <c r="V13">
-        <v>-4.4574516045913668E-3</v>
+        <v>-4.456928383969834E-3</v>
       </c>
       <c r="W13">
-        <v>-4.514258930512537E-3</v>
+        <v>-4.5130875324806384E-3</v>
       </c>
       <c r="X13">
-        <v>-5.2913952164593894E-3</v>
+        <v>-5.2922277022345284E-3</v>
       </c>
       <c r="Y13">
-        <v>-5.7502873012921923E-3</v>
+        <v>-5.7578052898101259E-3</v>
       </c>
       <c r="Z13">
-        <v>-5.1083952405022014E-3</v>
+        <v>-5.1078596395233693E-3</v>
       </c>
       <c r="AA13">
-        <v>-5.4517739974620531E-3</v>
+        <v>-5.45166380314638E-3</v>
       </c>
       <c r="AB13">
-        <v>-2.618728405212223E-4</v>
+        <v>-2.6167500397874166E-4</v>
       </c>
       <c r="AC13">
-        <v>2.1527184877529054E-3</v>
+        <v>2.1555406747238762E-3</v>
       </c>
       <c r="AD13">
-        <v>2.3035551953170369E-3</v>
+        <v>2.3034957109029234E-3</v>
       </c>
       <c r="AE13">
-        <v>-8.8548406727380433E-4</v>
+        <v>-8.8901885234130701E-4</v>
       </c>
       <c r="AF13">
-        <v>-3.1494487695220195E-2</v>
+        <v>-3.1498027778669134E-2</v>
       </c>
       <c r="AG13">
-        <v>-3.2206269985366528E-4</v>
+        <v>-3.2832996745600781E-4</v>
       </c>
       <c r="AH13">
-        <v>-4.0875373753253452E-2</v>
+        <v>-4.0949789722922236E-2</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.2">
@@ -2135,103 +2135,103 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>7.1806344092416957E-2</v>
+        <v>7.1220826620635044E-2</v>
       </c>
       <c r="C14">
-        <v>8.4259762382982335E-4</v>
+        <v>8.4364565570690768E-4</v>
       </c>
       <c r="D14">
-        <v>1.1566480569527304E-3</v>
+        <v>1.1588175219010288E-3</v>
       </c>
       <c r="E14">
-        <v>-9.7391856389795941E-6</v>
+        <v>-9.7543981756407355E-6</v>
       </c>
       <c r="F14">
-        <v>-2.4862275678907801E-4</v>
+        <v>-2.469983590830992E-4</v>
       </c>
       <c r="G14">
-        <v>1.4255193190902409E-3</v>
+        <v>1.4307525747664029E-3</v>
       </c>
       <c r="H14">
-        <v>3.0899879443307596E-5</v>
+        <v>3.0922968614743385E-5</v>
       </c>
       <c r="I14">
-        <v>-2.3080870424543073E-5</v>
+        <v>-2.3172873892009769E-5</v>
       </c>
       <c r="J14">
-        <v>1.3641492843854963E-3</v>
+        <v>1.3638170881669007E-3</v>
       </c>
       <c r="K14">
-        <v>1.1114250693718464E-2</v>
+        <v>1.1113820979844743E-2</v>
       </c>
       <c r="L14">
-        <v>8.3492232508674945E-3</v>
+        <v>8.3515497918105162E-3</v>
       </c>
       <c r="M14">
-        <v>1.4636778525933189E-2</v>
+        <v>1.463750148775679E-2</v>
       </c>
       <c r="N14">
-        <v>1.5494420968188458E-2</v>
+        <v>1.5496257233729863E-2</v>
       </c>
       <c r="O14">
-        <v>1.6623732836505783E-2</v>
+        <v>1.6626828819804942E-2</v>
       </c>
       <c r="P14">
-        <v>2.928144508149916E-3</v>
+        <v>2.9299649876195428E-3</v>
       </c>
       <c r="Q14">
-        <v>-4.1264179213633071E-3</v>
+        <v>-4.1252685350479518E-3</v>
       </c>
       <c r="R14">
-        <v>-9.0995353536426557E-3</v>
+        <v>-9.1009724097033569E-3</v>
       </c>
       <c r="S14">
-        <v>-3.6051530573617619E-3</v>
+        <v>-3.60563682645573E-3</v>
       </c>
       <c r="T14">
-        <v>-3.5220052793531699E-3</v>
+        <v>-3.5274021099097382E-3</v>
       </c>
       <c r="U14">
-        <v>-3.1908988432254853E-3</v>
+        <v>-3.1934336106942572E-3</v>
       </c>
       <c r="V14">
-        <v>-3.839149536404826E-3</v>
+        <v>-3.8399124833235721E-3</v>
       </c>
       <c r="W14">
-        <v>-3.7669760566994247E-3</v>
+        <v>-3.7662552467134071E-3</v>
       </c>
       <c r="X14">
-        <v>-4.1907259684440127E-3</v>
+        <v>-4.191793783629846E-3</v>
       </c>
       <c r="Y14">
-        <v>-4.5787047585511024E-3</v>
+        <v>-4.5867497792626321E-3</v>
       </c>
       <c r="Z14">
-        <v>-4.0582972497101187E-3</v>
+        <v>-4.0577771243731787E-3</v>
       </c>
       <c r="AA14">
-        <v>-4.5411369201331262E-3</v>
+        <v>-4.5402407203856748E-3</v>
       </c>
       <c r="AB14">
-        <v>-2.6257544479177559E-4</v>
+        <v>-2.6228891861156708E-4</v>
       </c>
       <c r="AC14">
-        <v>2.0250686858169697E-3</v>
+        <v>2.0266471336778885E-3</v>
       </c>
       <c r="AD14">
-        <v>2.286023926794215E-3</v>
+        <v>2.2858713793871624E-3</v>
       </c>
       <c r="AE14">
-        <v>-6.2362190477473038E-4</v>
+        <v>-6.2732342892909618E-4</v>
       </c>
       <c r="AF14">
-        <v>-2.8292654847919776E-2</v>
+        <v>-2.8293856792582735E-2</v>
       </c>
       <c r="AG14">
-        <v>5.7604530648233741E-5</v>
+        <v>5.0667593865012187E-5</v>
       </c>
       <c r="AH14">
-        <v>-4.2031837352031018E-2</v>
+        <v>-4.211426232650059E-2</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.2">
@@ -2239,103 +2239,103 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>-0.18762278415367012</v>
+        <v>-0.18756434027933527</v>
       </c>
       <c r="C15">
-        <v>4.6022563817849928E-4</v>
+        <v>4.6043735733614305E-4</v>
       </c>
       <c r="D15">
-        <v>-4.5181916970053748E-5</v>
+        <v>-4.5202919264623886E-5</v>
       </c>
       <c r="E15">
-        <v>5.4810385649985225E-7</v>
+        <v>5.4847301099274215E-7</v>
       </c>
       <c r="F15">
-        <v>-5.9694186046919278E-4</v>
+        <v>-5.9902793620118116E-4</v>
       </c>
       <c r="G15">
-        <v>-2.3409187487754516E-4</v>
+        <v>-2.2942689898118227E-4</v>
       </c>
       <c r="H15">
-        <v>5.6913455526318328E-5</v>
+        <v>5.693689756194374E-5</v>
       </c>
       <c r="I15">
-        <v>1.7411794912582793E-5</v>
+        <v>1.7399437326567918E-5</v>
       </c>
       <c r="J15">
-        <v>-4.2574892420049401E-5</v>
+        <v>-4.300420491561846E-5</v>
       </c>
       <c r="K15">
-        <v>8.9733520833347805E-4</v>
+        <v>8.9696904951721418E-4</v>
       </c>
       <c r="L15">
-        <v>2.2169767499534924E-3</v>
+        <v>2.2181609683460043E-3</v>
       </c>
       <c r="M15">
-        <v>3.1593158007567541E-3</v>
+        <v>3.1602954210189654E-3</v>
       </c>
       <c r="N15">
-        <v>3.305966189111539E-3</v>
+        <v>3.308322695153668E-3</v>
       </c>
       <c r="O15">
-        <v>2.928144508149916E-3</v>
+        <v>2.9299649876195428E-3</v>
       </c>
       <c r="P15">
-        <v>4.7118677910617949E-3</v>
+        <v>4.7125588519599162E-3</v>
       </c>
       <c r="Q15">
-        <v>-1.6359936810738662E-3</v>
+        <v>-1.6356576584672551E-3</v>
       </c>
       <c r="R15">
-        <v>-3.2576237087906437E-3</v>
+        <v>-3.2590409741617993E-3</v>
       </c>
       <c r="S15">
-        <v>-1.7255157161549018E-3</v>
+        <v>-1.7256702404432702E-3</v>
       </c>
       <c r="T15">
-        <v>-1.5830818545107274E-3</v>
+        <v>-1.5844195861659557E-3</v>
       </c>
       <c r="U15">
-        <v>-1.6338551722658154E-3</v>
+        <v>-1.634071124029429E-3</v>
       </c>
       <c r="V15">
-        <v>-1.7874723196066658E-3</v>
+        <v>-1.7870489072831621E-3</v>
       </c>
       <c r="W15">
-        <v>-1.7384855818228101E-3</v>
+        <v>-1.7381688308318001E-3</v>
       </c>
       <c r="X15">
-        <v>-2.0597582019736002E-3</v>
+        <v>-2.0598215695307193E-3</v>
       </c>
       <c r="Y15">
-        <v>-2.3822228603555392E-3</v>
+        <v>-2.383615553507485E-3</v>
       </c>
       <c r="Z15">
-        <v>-1.9970491317217887E-3</v>
+        <v>-1.9971686324481881E-3</v>
       </c>
       <c r="AA15">
-        <v>-1.9425962295622655E-3</v>
+        <v>-1.944550840342482E-3</v>
       </c>
       <c r="AB15">
-        <v>-5.0213194636763644E-5</v>
+        <v>-5.0186138360469156E-5</v>
       </c>
       <c r="AC15">
-        <v>3.5799640924950122E-4</v>
+        <v>3.5895833978418206E-4</v>
       </c>
       <c r="AD15">
-        <v>7.6072760382328878E-4</v>
+        <v>7.6160373622462165E-4</v>
       </c>
       <c r="AE15">
-        <v>-1.6763241602153365E-4</v>
+        <v>-1.689489210115868E-4</v>
       </c>
       <c r="AF15">
-        <v>-8.1961209053173986E-3</v>
+        <v>-8.1973675600612375E-3</v>
       </c>
       <c r="AG15">
-        <v>-2.6916640561097389E-4</v>
+        <v>-2.6907846389361131E-4</v>
       </c>
       <c r="AH15">
-        <v>-3.295598795347663E-3</v>
+        <v>-3.2982370648724935E-3</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.2">
@@ -2343,103 +2343,103 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>0.19698774762245419</v>
+        <v>0.1972160890146713</v>
       </c>
       <c r="C16">
-        <v>-1.1962979631865182E-3</v>
+        <v>-1.196216929928484E-3</v>
       </c>
       <c r="D16">
-        <v>-1.1816482201765927E-4</v>
+        <v>-1.1881298267574225E-4</v>
       </c>
       <c r="E16">
-        <v>1.3755914342857348E-6</v>
+        <v>1.3795291867283745E-6</v>
       </c>
       <c r="F16">
-        <v>5.2160182075045307E-4</v>
+        <v>5.1944245634604727E-4</v>
       </c>
       <c r="G16">
-        <v>-3.5261815585580435E-4</v>
+        <v>-3.5209478615387622E-4</v>
       </c>
       <c r="H16">
-        <v>-4.456480910833868E-5</v>
+        <v>-4.4531243722130745E-5</v>
       </c>
       <c r="I16">
-        <v>-8.7508313021763976E-6</v>
+        <v>-8.671437795624052E-6</v>
       </c>
       <c r="J16">
-        <v>-6.2487208335253175E-4</v>
+        <v>-6.2433237836262943E-4</v>
       </c>
       <c r="K16">
-        <v>-3.3889858531435859E-3</v>
+        <v>-3.387640257984971E-3</v>
       </c>
       <c r="L16">
-        <v>-3.7922967977838109E-3</v>
+        <v>-3.7901294281876977E-3</v>
       </c>
       <c r="M16">
-        <v>-5.3692812060422276E-3</v>
+        <v>-5.3667499881119921E-3</v>
       </c>
       <c r="N16">
-        <v>-5.057688838449992E-3</v>
+        <v>-5.0557760084747952E-3</v>
       </c>
       <c r="O16">
-        <v>-4.1264179213633071E-3</v>
+        <v>-4.1252685350479518E-3</v>
       </c>
       <c r="P16">
-        <v>-1.6359936810738662E-3</v>
+        <v>-1.6356576584672551E-3</v>
       </c>
       <c r="Q16">
-        <v>1.4795926376961081E-2</v>
+        <v>1.4793390382287865E-2</v>
       </c>
       <c r="R16">
-        <v>1.1694605726966333E-2</v>
+        <v>1.1691651834132229E-2</v>
       </c>
       <c r="S16">
-        <v>8.2687981207548548E-3</v>
+        <v>8.2666312957366886E-3</v>
       </c>
       <c r="T16">
-        <v>8.6896355105272535E-3</v>
+        <v>8.6891425744784201E-3</v>
       </c>
       <c r="U16">
-        <v>7.9193739251977938E-3</v>
+        <v>7.9179840465210278E-3</v>
       </c>
       <c r="V16">
-        <v>8.4270570043335422E-3</v>
+        <v>8.4248000447742603E-3</v>
       </c>
       <c r="W16">
-        <v>8.5656369503609893E-3</v>
+        <v>8.562510115342651E-3</v>
       </c>
       <c r="X16">
-        <v>8.9361848538632334E-3</v>
+        <v>8.9337028638596435E-3</v>
       </c>
       <c r="Y16">
-        <v>8.7353587247081983E-3</v>
+        <v>8.7358896447039536E-3</v>
       </c>
       <c r="Z16">
-        <v>8.9011675442085686E-3</v>
+        <v>8.8982290035191924E-3</v>
       </c>
       <c r="AA16">
-        <v>8.8881633414782009E-3</v>
+        <v>8.8835944046558382E-3</v>
       </c>
       <c r="AB16">
-        <v>3.6811564240966325E-5</v>
+        <v>3.6747372441739727E-5</v>
       </c>
       <c r="AC16">
-        <v>-8.4449452163280498E-4</v>
+        <v>-8.4500898862072994E-4</v>
       </c>
       <c r="AD16">
-        <v>-3.3495061717894173E-4</v>
+        <v>-3.3429316284523149E-4</v>
       </c>
       <c r="AE16">
-        <v>2.998099777251512E-3</v>
+        <v>2.9982241138869358E-3</v>
       </c>
       <c r="AF16">
-        <v>2.1124708326911337E-2</v>
+        <v>2.1116428289733126E-2</v>
       </c>
       <c r="AG16">
-        <v>1.9852435422809279E-3</v>
+        <v>1.9866684123103248E-3</v>
       </c>
       <c r="AH16">
-        <v>5.7757262032454536E-4</v>
+        <v>6.0016569687947226E-4</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.2">
@@ -2447,103 +2447,103 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>0.22805073885464278</v>
+        <v>0.22833001212752729</v>
       </c>
       <c r="C17">
-        <v>-1.7249994550706388E-3</v>
+        <v>-1.7258255830639125E-3</v>
       </c>
       <c r="D17">
-        <v>-3.831810565506355E-4</v>
+        <v>-3.8407163789677679E-4</v>
       </c>
       <c r="E17">
-        <v>3.4887530264951679E-6</v>
+        <v>3.4939884152742446E-6</v>
       </c>
       <c r="F17">
-        <v>1.2372529205743592E-3</v>
+        <v>1.238100589835426E-3</v>
       </c>
       <c r="G17">
-        <v>-3.6858311537051741E-4</v>
+        <v>-3.6887401135022495E-4</v>
       </c>
       <c r="H17">
-        <v>-7.9106318668780936E-5</v>
+        <v>-7.9094778995130377E-5</v>
       </c>
       <c r="I17">
-        <v>-7.6880857549925692E-6</v>
+        <v>-7.5835420391289388E-6</v>
       </c>
       <c r="J17">
-        <v>-1.022824043948406E-3</v>
+        <v>-1.022023229298008E-3</v>
       </c>
       <c r="K17">
-        <v>-7.2776146401295483E-3</v>
+        <v>-7.277255876424929E-3</v>
       </c>
       <c r="L17">
-        <v>-7.0347615237210739E-3</v>
+        <v>-7.0350822214457591E-3</v>
       </c>
       <c r="M17">
-        <v>-1.046661258676139E-2</v>
+        <v>-1.0466056223736843E-2</v>
       </c>
       <c r="N17">
-        <v>-1.0673664857550927E-2</v>
+        <v>-1.067569271665841E-2</v>
       </c>
       <c r="O17">
-        <v>-9.0995353536426557E-3</v>
+        <v>-9.1009724097033569E-3</v>
       </c>
       <c r="P17">
-        <v>-3.2576237087906437E-3</v>
+        <v>-3.2590409741617993E-3</v>
       </c>
       <c r="Q17">
-        <v>1.1694605726966333E-2</v>
+        <v>1.1691651834132229E-2</v>
       </c>
       <c r="R17">
-        <v>1.9616462856900718E-2</v>
+        <v>1.961654262427473E-2</v>
       </c>
       <c r="S17">
-        <v>1.0774585926933908E-2</v>
+        <v>1.0773487610471557E-2</v>
       </c>
       <c r="T17">
-        <v>1.1380644365670715E-2</v>
+        <v>1.138294730508866E-2</v>
       </c>
       <c r="U17">
-        <v>1.0304424601994863E-2</v>
+        <v>1.0303752597260088E-2</v>
       </c>
       <c r="V17">
-        <v>1.1121274118219929E-2</v>
+        <v>1.1119182293353413E-2</v>
       </c>
       <c r="W17">
-        <v>1.1302039385243519E-2</v>
+        <v>1.1299561958143862E-2</v>
       </c>
       <c r="X17">
-        <v>1.2003379509488852E-2</v>
+        <v>1.2002286844667746E-2</v>
       </c>
       <c r="Y17">
-        <v>1.1746470179013663E-2</v>
+        <v>1.1751092103508614E-2</v>
       </c>
       <c r="Z17">
-        <v>1.1824137522899696E-2</v>
+        <v>1.1822122750104944E-2</v>
       </c>
       <c r="AA17">
-        <v>1.1978780344448478E-2</v>
+        <v>1.1977287286877903E-2</v>
       </c>
       <c r="AB17">
-        <v>1.68478734443489E-4</v>
+        <v>1.6836237704619095E-4</v>
       </c>
       <c r="AC17">
-        <v>-1.9620267190770891E-3</v>
+        <v>-1.9640815652146402E-3</v>
       </c>
       <c r="AD17">
-        <v>-1.5130642250818314E-3</v>
+        <v>-1.5134214970794688E-3</v>
       </c>
       <c r="AE17">
-        <v>3.402725814964641E-3</v>
+        <v>3.405023089859341E-3</v>
       </c>
       <c r="AF17">
-        <v>3.7511099710748383E-2</v>
+        <v>3.7508458036117999E-2</v>
       </c>
       <c r="AG17">
-        <v>2.1441458265871009E-3</v>
+        <v>2.147296759212429E-3</v>
       </c>
       <c r="AH17">
-        <v>1.0569391465693316E-2</v>
+        <v>1.0604036528223162E-2</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.2">
@@ -2551,103 +2551,103 @@
         <v>29</v>
       </c>
       <c r="B18">
-        <v>0.11152563747469367</v>
+        <v>0.11162602498242925</v>
       </c>
       <c r="C18">
-        <v>-1.0098658170196145E-3</v>
+        <v>-1.0103609567496765E-3</v>
       </c>
       <c r="D18">
-        <v>-1.9572465689284696E-4</v>
+        <v>-1.961903132857018E-4</v>
       </c>
       <c r="E18">
-        <v>1.7434568931532076E-6</v>
+        <v>1.7462071489906215E-6</v>
       </c>
       <c r="F18">
-        <v>9.6536709390601379E-4</v>
+        <v>9.6693023960063573E-4</v>
       </c>
       <c r="G18">
-        <v>2.3344663094671198E-4</v>
+        <v>2.3201973583002666E-4</v>
       </c>
       <c r="H18">
-        <v>-3.6095755063872984E-5</v>
+        <v>-3.6067708511942507E-5</v>
       </c>
       <c r="I18">
-        <v>-8.1507726445603464E-6</v>
+        <v>-8.0894635348666014E-6</v>
       </c>
       <c r="J18">
-        <v>-6.2550295880437964E-5</v>
+        <v>-6.1942319330094212E-5</v>
       </c>
       <c r="K18">
-        <v>-2.961073702059917E-3</v>
+        <v>-2.9602118685094735E-3</v>
       </c>
       <c r="L18">
-        <v>-3.5325438495137579E-3</v>
+        <v>-3.5320773097815327E-3</v>
       </c>
       <c r="M18">
-        <v>-4.5519473304118409E-3</v>
+        <v>-4.5515410322003892E-3</v>
       </c>
       <c r="N18">
-        <v>-4.4475481501744848E-3</v>
+        <v>-4.4485142538378316E-3</v>
       </c>
       <c r="O18">
-        <v>-3.6051530573617619E-3</v>
+        <v>-3.60563682645573E-3</v>
       </c>
       <c r="P18">
-        <v>-1.7255157161549018E-3</v>
+        <v>-1.7256702404432702E-3</v>
       </c>
       <c r="Q18">
-        <v>8.2687981207548548E-3</v>
+        <v>8.2666312957366886E-3</v>
       </c>
       <c r="R18">
-        <v>1.0774585926933908E-2</v>
+        <v>1.0773487610471557E-2</v>
       </c>
       <c r="S18">
-        <v>1.1881568104196241E-2</v>
+        <v>1.1881829349989315E-2</v>
       </c>
       <c r="T18">
-        <v>8.1553250436779794E-3</v>
+        <v>8.1557649193127919E-3</v>
       </c>
       <c r="U18">
-        <v>7.501957610869167E-3</v>
+        <v>7.5010239929748177E-3</v>
       </c>
       <c r="V18">
-        <v>7.9164273085490719E-3</v>
+        <v>7.9145719147056728E-3</v>
       </c>
       <c r="W18">
-        <v>8.0735440514472755E-3</v>
+        <v>8.0713614225765944E-3</v>
       </c>
       <c r="X18">
-        <v>8.3979663932517313E-3</v>
+        <v>8.3965678338579278E-3</v>
       </c>
       <c r="Y18">
-        <v>8.1879396998947498E-3</v>
+        <v>8.1891557097414254E-3</v>
       </c>
       <c r="Z18">
-        <v>8.3577163916679041E-3</v>
+        <v>8.3560186482364018E-3</v>
       </c>
       <c r="AA18">
-        <v>8.3673817095162792E-3</v>
+        <v>8.3658241327099828E-3</v>
       </c>
       <c r="AB18">
-        <v>2.4418778485373288E-5</v>
+        <v>2.4414908693136308E-5</v>
       </c>
       <c r="AC18">
-        <v>-5.6363391535268733E-4</v>
+        <v>-5.6464077884375592E-4</v>
       </c>
       <c r="AD18">
-        <v>5.3193134213101127E-5</v>
+        <v>5.3495166847195106E-5</v>
       </c>
       <c r="AE18">
-        <v>2.8383210788795969E-3</v>
+        <v>2.8390896711018715E-3</v>
       </c>
       <c r="AF18">
-        <v>1.8700860631329752E-2</v>
+        <v>1.8697158431966884E-2</v>
       </c>
       <c r="AG18">
-        <v>1.8650394986656469E-3</v>
+        <v>1.8649874657630486E-3</v>
       </c>
       <c r="AH18">
-        <v>3.0383480951124957E-3</v>
+        <v>3.0538972236596757E-3</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.2">
@@ -2655,103 +2655,103 @@
         <v>30</v>
       </c>
       <c r="B19">
-        <v>0.17601143356572374</v>
+        <v>0.17631905783596219</v>
       </c>
       <c r="C19">
-        <v>-1.2912129871671943E-3</v>
+        <v>-1.2915105682933757E-3</v>
       </c>
       <c r="D19">
-        <v>-1.9034775348235333E-4</v>
+        <v>-1.9123357446303169E-4</v>
       </c>
       <c r="E19">
-        <v>1.8233501463745406E-6</v>
+        <v>1.8298776638330612E-6</v>
       </c>
       <c r="F19">
-        <v>6.1468788242573041E-4</v>
+        <v>6.1768553182833569E-4</v>
       </c>
       <c r="G19">
-        <v>-3.2922110499106129E-4</v>
+        <v>-3.3424661907031992E-4</v>
       </c>
       <c r="H19">
-        <v>-4.3486761779856396E-5</v>
+        <v>-4.3503363720806586E-5</v>
       </c>
       <c r="I19">
-        <v>-1.7970912302829817E-5</v>
+        <v>-1.7910593406075603E-5</v>
       </c>
       <c r="J19">
-        <v>-3.7698572746154915E-4</v>
+        <v>-3.773027874134742E-4</v>
       </c>
       <c r="K19">
-        <v>-3.1563411674357059E-3</v>
+        <v>-3.1579580672437112E-3</v>
       </c>
       <c r="L19">
-        <v>-3.6861165655699725E-3</v>
+        <v>-3.6886945138835253E-3</v>
       </c>
       <c r="M19">
-        <v>-4.7847108127675626E-3</v>
+        <v>-4.7886714483998116E-3</v>
       </c>
       <c r="N19">
-        <v>-4.7299971134465895E-3</v>
+        <v>-4.7351567209534739E-3</v>
       </c>
       <c r="O19">
-        <v>-3.5220052793531699E-3</v>
+        <v>-3.5274021099097382E-3</v>
       </c>
       <c r="P19">
-        <v>-1.5830818545107274E-3</v>
+        <v>-1.5844195861659557E-3</v>
       </c>
       <c r="Q19">
-        <v>8.6896355105272535E-3</v>
+        <v>8.6891425744784201E-3</v>
       </c>
       <c r="R19">
-        <v>1.1380644365670715E-2</v>
+        <v>1.138294730508866E-2</v>
       </c>
       <c r="S19">
-        <v>8.1553250436779794E-3</v>
+        <v>8.1557649193127919E-3</v>
       </c>
       <c r="T19">
-        <v>1.3004569773679191E-2</v>
+        <v>1.3007513141047087E-2</v>
       </c>
       <c r="U19">
-        <v>7.8526991065535727E-3</v>
+        <v>7.8534714303743862E-3</v>
       </c>
       <c r="V19">
-        <v>8.3145386251203997E-3</v>
+        <v>8.314620717638348E-3</v>
       </c>
       <c r="W19">
-        <v>8.4253661993553865E-3</v>
+        <v>8.4252782640377253E-3</v>
       </c>
       <c r="X19">
-        <v>8.8185141425060724E-3</v>
+        <v>8.8191368590615667E-3</v>
       </c>
       <c r="Y19">
-        <v>8.6643359612591161E-3</v>
+        <v>8.6692478263784879E-3</v>
       </c>
       <c r="Z19">
-        <v>8.79542087200786E-3</v>
+        <v>8.7953736692883838E-3</v>
       </c>
       <c r="AA19">
-        <v>8.8512476215022763E-3</v>
+        <v>8.8533024646464779E-3</v>
       </c>
       <c r="AB19">
-        <v>4.7296629706502493E-5</v>
+        <v>4.720002404799673E-5</v>
       </c>
       <c r="AC19">
-        <v>-8.4825251593716351E-4</v>
+        <v>-8.4976814960533104E-4</v>
       </c>
       <c r="AD19">
-        <v>-7.499778912280204E-4</v>
+        <v>-7.5101265776521481E-4</v>
       </c>
       <c r="AE19">
-        <v>2.7306670682286766E-3</v>
+        <v>2.7329186041669964E-3</v>
       </c>
       <c r="AF19">
-        <v>2.0116015181737626E-2</v>
+        <v>2.0120242648692589E-2</v>
       </c>
       <c r="AG19">
-        <v>2.0767754272771732E-3</v>
+        <v>2.077851596064178E-3</v>
       </c>
       <c r="AH19">
-        <v>3.1677299623392927E-3</v>
+        <v>3.201520537964327E-3</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.2">
@@ -2759,103 +2759,103 @@
         <v>31</v>
       </c>
       <c r="B20">
-        <v>5.640807030642752E-2</v>
+        <v>5.6708860357168309E-2</v>
       </c>
       <c r="C20">
-        <v>-9.0383631110555786E-4</v>
+        <v>-9.0393757910196566E-4</v>
       </c>
       <c r="D20">
-        <v>-4.9112849408235182E-5</v>
+        <v>-4.9529005060874876E-5</v>
       </c>
       <c r="E20">
-        <v>5.9983265515955574E-7</v>
+        <v>6.0273072696005259E-7</v>
       </c>
       <c r="F20">
-        <v>5.3857973051496771E-4</v>
+        <v>5.373693806418234E-4</v>
       </c>
       <c r="G20">
-        <v>-1.0398223168221114E-4</v>
+        <v>-1.0707033493597665E-4</v>
       </c>
       <c r="H20">
-        <v>-3.9288734670354209E-5</v>
+        <v>-3.9270380720104336E-5</v>
       </c>
       <c r="I20">
-        <v>-1.2598474277910297E-5</v>
+        <v>-1.2539374583407339E-5</v>
       </c>
       <c r="J20">
-        <v>-1.9525169348198236E-4</v>
+        <v>-1.9562495085715705E-4</v>
       </c>
       <c r="K20">
-        <v>-2.3086834048780466E-3</v>
+        <v>-2.3090191549817451E-3</v>
       </c>
       <c r="L20">
-        <v>-3.1419904966237693E-3</v>
+        <v>-3.1420362437829009E-3</v>
       </c>
       <c r="M20">
-        <v>-4.059728804706811E-3</v>
+        <v>-4.060707637841136E-3</v>
       </c>
       <c r="N20">
-        <v>-3.9881390170579331E-3</v>
+        <v>-3.9901288368114672E-3</v>
       </c>
       <c r="O20">
-        <v>-3.1908988432254853E-3</v>
+        <v>-3.1934336106942572E-3</v>
       </c>
       <c r="P20">
-        <v>-1.6338551722658154E-3</v>
+        <v>-1.634071124029429E-3</v>
       </c>
       <c r="Q20">
-        <v>7.9193739251977938E-3</v>
+        <v>7.9179840465210278E-3</v>
       </c>
       <c r="R20">
-        <v>1.0304424601994863E-2</v>
+        <v>1.0303752597260088E-2</v>
       </c>
       <c r="S20">
-        <v>7.501957610869167E-3</v>
+        <v>7.5010239929748177E-3</v>
       </c>
       <c r="T20">
-        <v>7.8526991065535727E-3</v>
+        <v>7.8534714303743862E-3</v>
       </c>
       <c r="U20">
-        <v>1.1871212027320083E-2</v>
+        <v>1.187164258827773E-2</v>
       </c>
       <c r="V20">
-        <v>7.6458943084773013E-3</v>
+        <v>7.6449745507117675E-3</v>
       </c>
       <c r="W20">
-        <v>7.761572282628075E-3</v>
+        <v>7.7600519601884986E-3</v>
       </c>
       <c r="X20">
-        <v>8.0850015595935569E-3</v>
+        <v>8.0841028220991883E-3</v>
       </c>
       <c r="Y20">
-        <v>7.9164536546233941E-3</v>
+        <v>7.9183223739861322E-3</v>
       </c>
       <c r="Z20">
-        <v>8.0263983820675049E-3</v>
+        <v>8.0251178931460103E-3</v>
       </c>
       <c r="AA20">
-        <v>8.0286788057417624E-3</v>
+        <v>8.0271426648541588E-3</v>
       </c>
       <c r="AB20">
-        <v>3.006751857983559E-5</v>
+        <v>3.0025305331633605E-5</v>
       </c>
       <c r="AC20">
-        <v>-4.2458332584364078E-4</v>
+        <v>-4.2539664753046564E-4</v>
       </c>
       <c r="AD20">
-        <v>-4.2540833475863092E-4</v>
+        <v>-4.257466288548192E-4</v>
       </c>
       <c r="AE20">
-        <v>2.2205062230388028E-3</v>
+        <v>2.2210409241572924E-3</v>
       </c>
       <c r="AF20">
-        <v>1.7374656907640351E-2</v>
+        <v>1.737252148841336E-2</v>
       </c>
       <c r="AG20">
-        <v>1.4660282419467409E-3</v>
+        <v>1.4663781921407087E-3</v>
       </c>
       <c r="AH20">
-        <v>-1.3047319719277049E-3</v>
+        <v>-1.2886820069850542E-3</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.2">
@@ -2863,103 +2863,103 @@
         <v>32</v>
       </c>
       <c r="B21">
-        <v>0.19847671536447317</v>
+        <v>0.19872457268059227</v>
       </c>
       <c r="C21">
-        <v>-9.847330591255081E-4</v>
+        <v>-9.8464210532238231E-4</v>
       </c>
       <c r="D21">
-        <v>-1.4534294324750063E-4</v>
+        <v>-1.4570018202381824E-4</v>
       </c>
       <c r="E21">
-        <v>1.3867467653997647E-6</v>
+        <v>1.3888533162993016E-6</v>
       </c>
       <c r="F21">
-        <v>6.3533371820659388E-4</v>
+        <v>6.3231930927641275E-4</v>
       </c>
       <c r="G21">
-        <v>-1.2764322120737629E-4</v>
+        <v>-1.313032641487757E-4</v>
       </c>
       <c r="H21">
-        <v>-4.5478000587014568E-5</v>
+        <v>-4.5443583192592165E-5</v>
       </c>
       <c r="I21">
-        <v>-1.6524366834896165E-5</v>
+        <v>-1.6454346157781423E-5</v>
       </c>
       <c r="J21">
-        <v>-2.3339764858111046E-4</v>
+        <v>-2.3314059319947192E-4</v>
       </c>
       <c r="K21">
-        <v>-2.9730178334474965E-3</v>
+        <v>-2.9718768074558349E-3</v>
       </c>
       <c r="L21">
-        <v>-3.7019928347610791E-3</v>
+        <v>-3.7006312744867365E-3</v>
       </c>
       <c r="M21">
-        <v>-4.7238888628090437E-3</v>
+        <v>-4.72269334923975E-3</v>
       </c>
       <c r="N21">
-        <v>-4.4574516045913668E-3</v>
+        <v>-4.456928383969834E-3</v>
       </c>
       <c r="O21">
-        <v>-3.839149536404826E-3</v>
+        <v>-3.8399124833235721E-3</v>
       </c>
       <c r="P21">
-        <v>-1.7874723196066658E-3</v>
+        <v>-1.7870489072831621E-3</v>
       </c>
       <c r="Q21">
-        <v>8.4270570043335422E-3</v>
+        <v>8.4248000447742603E-3</v>
       </c>
       <c r="R21">
-        <v>1.1121274118219929E-2</v>
+        <v>1.1119182293353413E-2</v>
       </c>
       <c r="S21">
-        <v>7.9164273085490719E-3</v>
+        <v>7.9145719147056728E-3</v>
       </c>
       <c r="T21">
-        <v>8.3145386251203997E-3</v>
+        <v>8.314620717638348E-3</v>
       </c>
       <c r="U21">
-        <v>7.6458943084773013E-3</v>
+        <v>7.6449745507117675E-3</v>
       </c>
       <c r="V21">
-        <v>1.1517597633306774E-2</v>
+        <v>1.1516000275429063E-2</v>
       </c>
       <c r="W21">
-        <v>8.2248316720800897E-3</v>
+        <v>8.2222223192792987E-3</v>
       </c>
       <c r="X21">
-        <v>8.5524533918958472E-3</v>
+        <v>8.5504673829122184E-3</v>
       </c>
       <c r="Y21">
-        <v>8.4348368264062206E-3</v>
+        <v>8.4357663191102546E-3</v>
       </c>
       <c r="Z21">
-        <v>8.5328592206396145E-3</v>
+        <v>8.5306657617593151E-3</v>
       </c>
       <c r="AA21">
-        <v>8.6144486081287663E-3</v>
+        <v>8.6115652360437452E-3</v>
       </c>
       <c r="AB21">
-        <v>5.0731627463186267E-5</v>
+        <v>5.0645945429676374E-5</v>
       </c>
       <c r="AC21">
-        <v>-7.6202807355151133E-4</v>
+        <v>-7.6217902219994716E-4</v>
       </c>
       <c r="AD21">
-        <v>-2.8056700462065869E-4</v>
+        <v>-2.8032830554853725E-4</v>
       </c>
       <c r="AE21">
-        <v>2.6061038321676835E-3</v>
+        <v>2.6064570770870281E-3</v>
       </c>
       <c r="AF21">
-        <v>1.9615161642248115E-2</v>
+        <v>1.9607967700461894E-2</v>
       </c>
       <c r="AG21">
-        <v>1.837498144022335E-3</v>
+        <v>1.8380051837685587E-3</v>
       </c>
       <c r="AH21">
-        <v>1.9580739813668622E-3</v>
+        <v>1.9726245344748334E-3</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.2">
@@ -2967,103 +2967,103 @@
         <v>33</v>
       </c>
       <c r="B22">
-        <v>4.9123934010158479E-2</v>
+        <v>4.9285939661335848E-2</v>
       </c>
       <c r="C22">
-        <v>-1.0924357778282711E-3</v>
+        <v>-1.092665221925344E-3</v>
       </c>
       <c r="D22">
-        <v>-3.3438882093485278E-5</v>
+        <v>-3.3723970293532413E-5</v>
       </c>
       <c r="E22">
-        <v>6.3584161861136032E-7</v>
+        <v>6.369646465037202E-7</v>
       </c>
       <c r="F22">
-        <v>9.3796792388116087E-4</v>
+        <v>9.360301261169086E-4</v>
       </c>
       <c r="G22">
-        <v>-6.5424311590343712E-5</v>
+        <v>-6.6732746928455837E-5</v>
       </c>
       <c r="H22">
-        <v>-3.9519927201841414E-5</v>
+        <v>-3.9485421556802641E-5</v>
       </c>
       <c r="I22">
-        <v>-1.4399214004307828E-5</v>
+        <v>-1.4318271615701428E-5</v>
       </c>
       <c r="J22">
-        <v>-7.1547489369348273E-4</v>
+        <v>-7.1488028150213344E-4</v>
       </c>
       <c r="K22">
-        <v>-2.9981899491668632E-3</v>
+        <v>-2.9964422876942436E-3</v>
       </c>
       <c r="L22">
-        <v>-3.5903177546743417E-3</v>
+        <v>-3.5884353277335643E-3</v>
       </c>
       <c r="M22">
-        <v>-4.8753050863960829E-3</v>
+        <v>-4.8726554079112959E-3</v>
       </c>
       <c r="N22">
-        <v>-4.514258930512537E-3</v>
+        <v>-4.5130875324806384E-3</v>
       </c>
       <c r="O22">
-        <v>-3.7669760566994247E-3</v>
+        <v>-3.7662552467134071E-3</v>
       </c>
       <c r="P22">
-        <v>-1.7384855818228101E-3</v>
+        <v>-1.7381688308318001E-3</v>
       </c>
       <c r="Q22">
-        <v>8.5656369503609893E-3</v>
+        <v>8.562510115342651E-3</v>
       </c>
       <c r="R22">
-        <v>1.1302039385243519E-2</v>
+        <v>1.1299561958143862E-2</v>
       </c>
       <c r="S22">
-        <v>8.0735440514472755E-3</v>
+        <v>8.0713614225765944E-3</v>
       </c>
       <c r="T22">
-        <v>8.4253661993553865E-3</v>
+        <v>8.4252782640377253E-3</v>
       </c>
       <c r="U22">
-        <v>7.761572282628075E-3</v>
+        <v>7.7600519601884986E-3</v>
       </c>
       <c r="V22">
-        <v>8.2248316720800897E-3</v>
+        <v>8.2222223192792987E-3</v>
       </c>
       <c r="W22">
-        <v>1.0837957222124984E-2</v>
+        <v>1.0834707896987917E-2</v>
       </c>
       <c r="X22">
-        <v>8.7126996077557094E-3</v>
+        <v>8.7102108557624517E-3</v>
       </c>
       <c r="Y22">
-        <v>8.5763905343282845E-3</v>
+        <v>8.5772022294622226E-3</v>
       </c>
       <c r="Z22">
-        <v>8.6586477196344928E-3</v>
+        <v>8.6558594006053285E-3</v>
       </c>
       <c r="AA22">
-        <v>8.8594582130853035E-3</v>
+        <v>8.8557066084896247E-3</v>
       </c>
       <c r="AB22">
-        <v>4.9210360723202663E-5</v>
+        <v>4.9126554128396845E-5</v>
       </c>
       <c r="AC22">
-        <v>-8.1856042452575902E-4</v>
+        <v>-8.1944948530748938E-4</v>
       </c>
       <c r="AD22">
-        <v>-6.9952946293277583E-4</v>
+        <v>-6.992416436402576E-4</v>
       </c>
       <c r="AE22">
-        <v>2.8781878160798599E-3</v>
+        <v>2.878689923552208E-3</v>
       </c>
       <c r="AF22">
-        <v>2.0051955780835969E-2</v>
+        <v>2.0043221146248701E-2</v>
       </c>
       <c r="AG22">
-        <v>2.5290166049351868E-3</v>
+        <v>2.5298232466520569E-3</v>
       </c>
       <c r="AH22">
-        <v>-2.485477448958915E-3</v>
+        <v>-2.4735388982470158E-3</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.2">
@@ -3071,103 +3071,103 @@
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.12590546949037715</v>
+        <v>0.12601884945813385</v>
       </c>
       <c r="C23">
-        <v>-1.1501715642297061E-3</v>
+        <v>-1.1504169706080141E-3</v>
       </c>
       <c r="D23">
-        <v>-1.1659868555197184E-4</v>
+        <v>-1.1711153731298191E-4</v>
       </c>
       <c r="E23">
-        <v>1.17026338321963E-6</v>
+        <v>1.1732989288444975E-6</v>
       </c>
       <c r="F23">
-        <v>8.2964670507371888E-4</v>
+        <v>8.2958681279894381E-4</v>
       </c>
       <c r="G23">
-        <v>-1.5177530750236888E-4</v>
+        <v>-1.5389007778650061E-4</v>
       </c>
       <c r="H23">
-        <v>-5.2663112499476064E-5</v>
+        <v>-5.2642390306993338E-5</v>
       </c>
       <c r="I23">
-        <v>-1.7159754152147946E-5</v>
+        <v>-1.7081177313098294E-5</v>
       </c>
       <c r="J23">
-        <v>-5.4547268011928725E-4</v>
+        <v>-5.4502263269484534E-4</v>
       </c>
       <c r="K23">
-        <v>-3.5677001716953229E-3</v>
+        <v>-3.5669820404849849E-3</v>
       </c>
       <c r="L23">
-        <v>-3.9154658742369692E-3</v>
+        <v>-3.9149208084051281E-3</v>
       </c>
       <c r="M23">
-        <v>-5.2996114354346606E-3</v>
+        <v>-5.2988742444510795E-3</v>
       </c>
       <c r="N23">
-        <v>-5.2913952164593894E-3</v>
+        <v>-5.2922277022345284E-3</v>
       </c>
       <c r="O23">
-        <v>-4.1907259684440127E-3</v>
+        <v>-4.191793783629846E-3</v>
       </c>
       <c r="P23">
-        <v>-2.0597582019736002E-3</v>
+        <v>-2.0598215695307193E-3</v>
       </c>
       <c r="Q23">
-        <v>8.9361848538632334E-3</v>
+        <v>8.9337028638596435E-3</v>
       </c>
       <c r="R23">
-        <v>1.2003379509488852E-2</v>
+        <v>1.2002286844667746E-2</v>
       </c>
       <c r="S23">
-        <v>8.3979663932517313E-3</v>
+        <v>8.3965678338579278E-3</v>
       </c>
       <c r="T23">
-        <v>8.8185141425060724E-3</v>
+        <v>8.8191368590615667E-3</v>
       </c>
       <c r="U23">
-        <v>8.0850015595935569E-3</v>
+        <v>8.0841028220991883E-3</v>
       </c>
       <c r="V23">
-        <v>8.5524533918958472E-3</v>
+        <v>8.5504673829122184E-3</v>
       </c>
       <c r="W23">
-        <v>8.7126996077557094E-3</v>
+        <v>8.7102108557624517E-3</v>
       </c>
       <c r="X23">
-        <v>1.2372946792771886E-2</v>
+        <v>1.2371458841776387E-2</v>
       </c>
       <c r="Y23">
-        <v>9.0084011071199996E-3</v>
+        <v>9.0101774250320107E-3</v>
       </c>
       <c r="Z23">
-        <v>9.0555249674078714E-3</v>
+        <v>9.053476896509146E-3</v>
       </c>
       <c r="AA23">
-        <v>9.2263185487242265E-3</v>
+        <v>9.2241842545567609E-3</v>
       </c>
       <c r="AB23">
-        <v>4.1211796409590384E-5</v>
+        <v>4.1127135986024485E-5</v>
       </c>
       <c r="AC23">
-        <v>-9.0061752606208911E-4</v>
+        <v>-9.0173761738946041E-4</v>
       </c>
       <c r="AD23">
-        <v>-6.5026301718389742E-4</v>
+        <v>-6.5005051067750126E-4</v>
       </c>
       <c r="AE23">
-        <v>3.0669698095329976E-3</v>
+        <v>3.0680068158984637E-3</v>
       </c>
       <c r="AF23">
-        <v>2.1982838294511781E-2</v>
+        <v>2.1978182824095298E-2</v>
       </c>
       <c r="AG23">
-        <v>1.6846242617520801E-3</v>
+        <v>1.6853219912899666E-3</v>
       </c>
       <c r="AH23">
-        <v>1.7896458013391195E-3</v>
+        <v>1.8093912072256781E-3</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.2">
@@ -3175,103 +3175,103 @@
         <v>35</v>
       </c>
       <c r="B24">
-        <v>0.23183675841810009</v>
+        <v>0.23228307820056088</v>
       </c>
       <c r="C24">
-        <v>-1.1423072500666908E-3</v>
+        <v>-1.1425412024495055E-3</v>
       </c>
       <c r="D24">
-        <v>-1.4601185880170481E-4</v>
+        <v>-1.4678745714986896E-4</v>
       </c>
       <c r="E24">
-        <v>1.179180915106162E-6</v>
+        <v>1.1852007102621138E-6</v>
       </c>
       <c r="F24">
-        <v>9.1399263301876628E-4</v>
+        <v>9.1792796731814119E-4</v>
       </c>
       <c r="G24">
-        <v>-3.7710233893113666E-4</v>
+        <v>-3.8920613272410808E-4</v>
       </c>
       <c r="H24">
-        <v>-5.3037754652481754E-5</v>
+        <v>-5.3065848629901358E-5</v>
       </c>
       <c r="I24">
-        <v>-1.5629270179927227E-5</v>
+        <v>-1.5556397394592071E-5</v>
       </c>
       <c r="J24">
-        <v>-2.6456056178748681E-4</v>
+        <v>-2.6529179922785834E-4</v>
       </c>
       <c r="K24">
-        <v>-3.2642754439391256E-3</v>
+        <v>-3.2659079395376805E-3</v>
       </c>
       <c r="L24">
-        <v>-4.3349079283260894E-3</v>
+        <v>-4.3387438802221477E-3</v>
       </c>
       <c r="M24">
-        <v>-5.5920306680627817E-3</v>
+        <v>-5.5974723656057939E-3</v>
       </c>
       <c r="N24">
-        <v>-5.7502873012921923E-3</v>
+        <v>-5.7578052898101259E-3</v>
       </c>
       <c r="O24">
-        <v>-4.5787047585511024E-3</v>
+        <v>-4.5867497792626321E-3</v>
       </c>
       <c r="P24">
-        <v>-2.3822228603555392E-3</v>
+        <v>-2.383615553507485E-3</v>
       </c>
       <c r="Q24">
-        <v>8.7353587247081983E-3</v>
+        <v>8.7358896447039536E-3</v>
       </c>
       <c r="R24">
-        <v>1.1746470179013663E-2</v>
+        <v>1.1751092103508614E-2</v>
       </c>
       <c r="S24">
-        <v>8.1879396998947498E-3</v>
+        <v>8.1891557097414254E-3</v>
       </c>
       <c r="T24">
-        <v>8.6643359612591161E-3</v>
+        <v>8.6692478263784879E-3</v>
       </c>
       <c r="U24">
-        <v>7.9164536546233941E-3</v>
+        <v>7.9183223739861322E-3</v>
       </c>
       <c r="V24">
-        <v>8.4348368264062206E-3</v>
+        <v>8.4357663191102546E-3</v>
       </c>
       <c r="W24">
-        <v>8.5763905343282845E-3</v>
+        <v>8.5772022294622226E-3</v>
       </c>
       <c r="X24">
-        <v>9.0084011071199996E-3</v>
+        <v>9.0101774250320107E-3</v>
       </c>
       <c r="Y24">
-        <v>1.4214985793442629E-2</v>
+        <v>1.4222096971985721E-2</v>
       </c>
       <c r="Z24">
-        <v>8.8710532691758399E-3</v>
+        <v>8.8720194061185365E-3</v>
       </c>
       <c r="AA24">
-        <v>9.0410868650149748E-3</v>
+        <v>9.0465279740827905E-3</v>
       </c>
       <c r="AB24">
-        <v>7.7167320084116277E-5</v>
+        <v>7.697264343848524E-5</v>
       </c>
       <c r="AC24">
-        <v>-1.0458495211376623E-3</v>
+        <v>-1.0481416071512067E-3</v>
       </c>
       <c r="AD24">
-        <v>-4.498201437935492E-4</v>
+        <v>-4.5165999984702297E-4</v>
       </c>
       <c r="AE24">
-        <v>2.8608098858363038E-3</v>
+        <v>2.8654995355700541E-3</v>
       </c>
       <c r="AF24">
-        <v>2.1286060502171966E-2</v>
+        <v>2.129243625540049E-2</v>
       </c>
       <c r="AG24">
-        <v>1.245278279531953E-3</v>
+        <v>1.2470376430770884E-3</v>
       </c>
       <c r="AH24">
-        <v>3.2282223474506197E-3</v>
+        <v>3.261092848030684E-3</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.2">
@@ -3279,103 +3279,103 @@
         <v>36</v>
       </c>
       <c r="B25">
-        <v>0.14153708863180745</v>
+        <v>0.14164453460504328</v>
       </c>
       <c r="C25">
-        <v>-1.154843522886884E-3</v>
+        <v>-1.1551409165193485E-3</v>
       </c>
       <c r="D25">
-        <v>-1.2150128821220019E-4</v>
+        <v>-1.2197468142541995E-4</v>
       </c>
       <c r="E25">
-        <v>1.2318415760660261E-6</v>
+        <v>1.2344633904560207E-6</v>
       </c>
       <c r="F25">
-        <v>6.8644692588015776E-4</v>
+        <v>6.8704818128752405E-4</v>
       </c>
       <c r="G25">
-        <v>-2.4304529010942249E-4</v>
+        <v>-2.4212543880392347E-4</v>
       </c>
       <c r="H25">
-        <v>-5.2587838813649416E-5</v>
+        <v>-5.2565808822866209E-5</v>
       </c>
       <c r="I25">
-        <v>-1.5351652430080565E-5</v>
+        <v>-1.5282545453612541E-5</v>
       </c>
       <c r="J25">
-        <v>-3.6362801984441036E-4</v>
+        <v>-3.6292247941270561E-4</v>
       </c>
       <c r="K25">
-        <v>-3.3970837117349752E-3</v>
+        <v>-3.3959438589497345E-3</v>
       </c>
       <c r="L25">
-        <v>-3.537215179007651E-3</v>
+        <v>-3.5359702014658052E-3</v>
       </c>
       <c r="M25">
-        <v>-5.0219655595727664E-3</v>
+        <v>-5.0202967614037808E-3</v>
       </c>
       <c r="N25">
-        <v>-5.1083952405022014E-3</v>
+        <v>-5.1078596395233693E-3</v>
       </c>
       <c r="O25">
-        <v>-4.0582972497101187E-3</v>
+        <v>-4.0577771243731787E-3</v>
       </c>
       <c r="P25">
-        <v>-1.9970491317217887E-3</v>
+        <v>-1.9971686324481881E-3</v>
       </c>
       <c r="Q25">
-        <v>8.9011675442085686E-3</v>
+        <v>8.8982290035191924E-3</v>
       </c>
       <c r="R25">
-        <v>1.1824137522899696E-2</v>
+        <v>1.1822122750104944E-2</v>
       </c>
       <c r="S25">
-        <v>8.3577163916679041E-3</v>
+        <v>8.3560186482364018E-3</v>
       </c>
       <c r="T25">
-        <v>8.79542087200786E-3</v>
+        <v>8.7953736692883838E-3</v>
       </c>
       <c r="U25">
-        <v>8.0263983820675049E-3</v>
+        <v>8.0251178931460103E-3</v>
       </c>
       <c r="V25">
-        <v>8.5328592206396145E-3</v>
+        <v>8.5306657617593151E-3</v>
       </c>
       <c r="W25">
-        <v>8.6586477196344928E-3</v>
+        <v>8.6558594006053285E-3</v>
       </c>
       <c r="X25">
-        <v>9.0555249674078714E-3</v>
+        <v>9.053476896509146E-3</v>
       </c>
       <c r="Y25">
-        <v>8.8710532691758399E-3</v>
+        <v>8.8720194061185365E-3</v>
       </c>
       <c r="Z25">
-        <v>1.2378619408790389E-2</v>
+        <v>1.2375937336901377E-2</v>
       </c>
       <c r="AA25">
-        <v>9.0575967819825666E-3</v>
+        <v>9.0542492456744828E-3</v>
       </c>
       <c r="AB25">
-        <v>5.4777636529025663E-5</v>
+        <v>5.4699367631997828E-5</v>
       </c>
       <c r="AC25">
-        <v>-7.3867379220454114E-4</v>
+        <v>-7.3942298937775246E-4</v>
       </c>
       <c r="AD25">
-        <v>-4.2190834957272485E-4</v>
+        <v>-4.2131569590603962E-4</v>
       </c>
       <c r="AE25">
-        <v>2.9690184143657595E-3</v>
+        <v>2.9696004758221302E-3</v>
       </c>
       <c r="AF25">
-        <v>2.134217449376339E-2</v>
+        <v>2.1336248715089261E-2</v>
       </c>
       <c r="AG25">
-        <v>2.0181842732747424E-3</v>
+        <v>2.0194372491672821E-3</v>
       </c>
       <c r="AH25">
-        <v>1.3199842918870403E-3</v>
+        <v>1.3372451266587398E-3</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.2">
@@ -3383,103 +3383,103 @@
         <v>37</v>
       </c>
       <c r="B26">
-        <v>0.10074405829308571</v>
+        <v>0.10094353664292048</v>
       </c>
       <c r="C26">
-        <v>-6.7325170719638016E-4</v>
+        <v>-6.7439608985179946E-4</v>
       </c>
       <c r="D26">
-        <v>-1.7457630591909135E-4</v>
+        <v>-1.7609711060475458E-4</v>
       </c>
       <c r="E26">
-        <v>1.4037523786891086E-6</v>
+        <v>1.4130297614056556E-6</v>
       </c>
       <c r="F26">
-        <v>1.1924040947890843E-3</v>
+        <v>1.1935343535236424E-3</v>
       </c>
       <c r="G26">
-        <v>-8.1107138794252686E-4</v>
+        <v>-8.0578056156833098E-4</v>
       </c>
       <c r="H26">
-        <v>-6.4884877886612767E-5</v>
+        <v>-6.4860692325813756E-5</v>
       </c>
       <c r="I26">
-        <v>-3.6326354668531215E-5</v>
+        <v>-3.6197719127975341E-5</v>
       </c>
       <c r="J26">
-        <v>-2.031664107929633E-4</v>
+        <v>-2.0214024603167069E-4</v>
       </c>
       <c r="K26">
-        <v>-3.6756824102319348E-3</v>
+        <v>-3.6745430814306874E-3</v>
       </c>
       <c r="L26">
-        <v>-4.3500593473219159E-3</v>
+        <v>-4.3494662285958642E-3</v>
       </c>
       <c r="M26">
-        <v>-5.5601789479914118E-3</v>
+        <v>-5.5579350291298105E-3</v>
       </c>
       <c r="N26">
-        <v>-5.4517739974620531E-3</v>
+        <v>-5.45166380314638E-3</v>
       </c>
       <c r="O26">
-        <v>-4.5411369201331262E-3</v>
+        <v>-4.5402407203856748E-3</v>
       </c>
       <c r="P26">
-        <v>-1.9425962295622655E-3</v>
+        <v>-1.944550840342482E-3</v>
       </c>
       <c r="Q26">
-        <v>8.8881633414782009E-3</v>
+        <v>8.8835944046558382E-3</v>
       </c>
       <c r="R26">
-        <v>1.1978780344448478E-2</v>
+        <v>1.1977287286877903E-2</v>
       </c>
       <c r="S26">
-        <v>8.3673817095162792E-3</v>
+        <v>8.3658241327099828E-3</v>
       </c>
       <c r="T26">
-        <v>8.8512476215022763E-3</v>
+        <v>8.8533024646464779E-3</v>
       </c>
       <c r="U26">
-        <v>8.0286788057417624E-3</v>
+        <v>8.0271426648541588E-3</v>
       </c>
       <c r="V26">
-        <v>8.6144486081287663E-3</v>
+        <v>8.6115652360437452E-3</v>
       </c>
       <c r="W26">
-        <v>8.8594582130853035E-3</v>
+        <v>8.8557066084896247E-3</v>
       </c>
       <c r="X26">
-        <v>9.2263185487242265E-3</v>
+        <v>9.2241842545567609E-3</v>
       </c>
       <c r="Y26">
-        <v>9.0410868650149748E-3</v>
+        <v>9.0465279740827905E-3</v>
       </c>
       <c r="Z26">
-        <v>9.0575967819825666E-3</v>
+        <v>9.0542492456744828E-3</v>
       </c>
       <c r="AA26">
-        <v>1.7877132639020618E-2</v>
+        <v>1.787227672453625E-2</v>
       </c>
       <c r="AB26">
-        <v>1.2192308526820235E-4</v>
+        <v>1.2181983698899591E-4</v>
       </c>
       <c r="AC26">
-        <v>-1.3896215860871889E-3</v>
+        <v>-1.3919225072686605E-3</v>
       </c>
       <c r="AD26">
-        <v>-1.2911172282988846E-3</v>
+        <v>-1.2906609452671232E-3</v>
       </c>
       <c r="AE26">
-        <v>3.2388559399907559E-3</v>
+        <v>3.2404226215289318E-3</v>
       </c>
       <c r="AF26">
-        <v>2.1749099718759123E-2</v>
+        <v>2.1744379868262498E-2</v>
       </c>
       <c r="AG26">
-        <v>1.8622190421784274E-3</v>
+        <v>1.8684438977426992E-3</v>
       </c>
       <c r="AH26">
-        <v>4.4440829780870265E-3</v>
+        <v>4.4983961650464921E-3</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.2">
@@ -3487,103 +3487,103 @@
         <v>38</v>
       </c>
       <c r="B27">
-        <v>-1.6564979178240059E-2</v>
+        <v>-1.6586486618150691E-2</v>
       </c>
       <c r="C27">
-        <v>-9.5909821632421963E-6</v>
+        <v>-9.628894713794179E-6</v>
       </c>
       <c r="D27">
-        <v>-2.1414488845452814E-5</v>
+        <v>-2.1390749815840965E-5</v>
       </c>
       <c r="E27">
-        <v>1.3115388549533218E-7</v>
+        <v>1.3092676285549076E-7</v>
       </c>
       <c r="F27">
-        <v>1.3455199897537487E-5</v>
+        <v>1.3681131692889375E-5</v>
       </c>
       <c r="G27">
-        <v>6.513069069771912E-6</v>
+        <v>6.8143731573285296E-6</v>
       </c>
       <c r="H27">
-        <v>-3.0175474393208867E-7</v>
+        <v>-3.0101125077156411E-7</v>
       </c>
       <c r="I27">
-        <v>1.7226003919480057E-6</v>
+        <v>1.7230136200941106E-6</v>
       </c>
       <c r="J27">
-        <v>5.4182694337199123E-5</v>
+        <v>5.4283043635743912E-5</v>
       </c>
       <c r="K27">
-        <v>-1.7550987748494356E-4</v>
+        <v>-1.7534877365664404E-4</v>
       </c>
       <c r="L27">
-        <v>-1.1146434163181851E-4</v>
+        <v>-1.1137329201647784E-4</v>
       </c>
       <c r="M27">
-        <v>-2.2765543498336639E-4</v>
+        <v>-2.2742670042666337E-4</v>
       </c>
       <c r="N27">
-        <v>-2.618728405212223E-4</v>
+        <v>-2.6167500397874166E-4</v>
       </c>
       <c r="O27">
-        <v>-2.6257544479177559E-4</v>
+        <v>-2.6228891861156708E-4</v>
       </c>
       <c r="P27">
-        <v>-5.0213194636763644E-5</v>
+        <v>-5.0186138360469156E-5</v>
       </c>
       <c r="Q27">
-        <v>3.6811564240966325E-5</v>
+        <v>3.6747372441739727E-5</v>
       </c>
       <c r="R27">
-        <v>1.68478734443489E-4</v>
+        <v>1.6836237704619095E-4</v>
       </c>
       <c r="S27">
-        <v>2.4418778485373288E-5</v>
+        <v>2.4414908693136308E-5</v>
       </c>
       <c r="T27">
-        <v>4.7296629706502493E-5</v>
+        <v>4.720002404799673E-5</v>
       </c>
       <c r="U27">
-        <v>3.006751857983559E-5</v>
+        <v>3.0025305331633605E-5</v>
       </c>
       <c r="V27">
-        <v>5.0731627463186267E-5</v>
+        <v>5.0645945429676374E-5</v>
       </c>
       <c r="W27">
-        <v>4.9210360723202663E-5</v>
+        <v>4.9126554128396845E-5</v>
       </c>
       <c r="X27">
-        <v>4.1211796409590384E-5</v>
+        <v>4.1127135986024485E-5</v>
       </c>
       <c r="Y27">
-        <v>7.7167320084116277E-5</v>
+        <v>7.697264343848524E-5</v>
       </c>
       <c r="Z27">
-        <v>5.4777636529025663E-5</v>
+        <v>5.4699367631997828E-5</v>
       </c>
       <c r="AA27">
-        <v>1.2192308526820235E-4</v>
+        <v>1.2181983698899591E-4</v>
       </c>
       <c r="AB27">
-        <v>3.5411288729112589E-5</v>
+        <v>3.5413155600992927E-5</v>
       </c>
       <c r="AC27">
-        <v>-1.5116642171840759E-4</v>
+        <v>-1.5116575934752069E-4</v>
       </c>
       <c r="AD27">
-        <v>-1.6609493604615306E-4</v>
+        <v>-1.6604616621470903E-4</v>
       </c>
       <c r="AE27">
-        <v>-4.1347368790286662E-5</v>
+        <v>-4.133556795215011E-5</v>
       </c>
       <c r="AF27">
-        <v>5.779015324047683E-4</v>
+        <v>5.7756974913565043E-4</v>
       </c>
       <c r="AG27">
-        <v>-1.26251198857689E-5</v>
+        <v>-1.2674169938520864E-5</v>
       </c>
       <c r="AH27">
-        <v>3.3458228060671326E-4</v>
+        <v>3.33551737656329E-4</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.2">
@@ -3591,103 +3591,103 @@
         <v>39</v>
       </c>
       <c r="B28">
-        <v>-0.11081717176490555</v>
+        <v>-0.11077232633982934</v>
       </c>
       <c r="C28">
-        <v>2.3899944807097111E-4</v>
+        <v>2.3954457091663771E-4</v>
       </c>
       <c r="D28">
-        <v>7.3768484269390311E-5</v>
+        <v>7.4194082303892517E-5</v>
       </c>
       <c r="E28">
-        <v>-6.4421253843731895E-7</v>
+        <v>-6.4725658894420647E-7</v>
       </c>
       <c r="F28">
-        <v>-7.0154215605294475E-5</v>
+        <v>-7.477171489832235E-5</v>
       </c>
       <c r="G28">
-        <v>2.2530026226605837E-4</v>
+        <v>2.2518313282466392E-4</v>
       </c>
       <c r="H28">
-        <v>8.2237333035854081E-6</v>
+        <v>8.2442642542627565E-6</v>
       </c>
       <c r="I28">
-        <v>-6.7303034800909769E-7</v>
+        <v>-6.8339890418574537E-7</v>
       </c>
       <c r="J28">
-        <v>1.579359286024689E-4</v>
+        <v>1.5773557233882303E-4</v>
       </c>
       <c r="K28">
-        <v>1.4977359110327788E-3</v>
+        <v>1.498606757074715E-3</v>
       </c>
       <c r="L28">
-        <v>1.0611165636366837E-3</v>
+        <v>1.0631027921588743E-3</v>
       </c>
       <c r="M28">
-        <v>1.9520336994573763E-3</v>
+        <v>1.954105185215872E-3</v>
       </c>
       <c r="N28">
-        <v>2.1527184877529054E-3</v>
+        <v>2.1555406747238762E-3</v>
       </c>
       <c r="O28">
-        <v>2.0250686858169697E-3</v>
+        <v>2.0266471336778885E-3</v>
       </c>
       <c r="P28">
-        <v>3.5799640924950122E-4</v>
+        <v>3.5895833978418206E-4</v>
       </c>
       <c r="Q28">
-        <v>-8.4449452163280498E-4</v>
+        <v>-8.4500898862072994E-4</v>
       </c>
       <c r="R28">
-        <v>-1.9620267190770891E-3</v>
+        <v>-1.9640815652146402E-3</v>
       </c>
       <c r="S28">
-        <v>-5.6363391535268733E-4</v>
+        <v>-5.6464077884375592E-4</v>
       </c>
       <c r="T28">
-        <v>-8.4825251593716351E-4</v>
+        <v>-8.4976814960533104E-4</v>
       </c>
       <c r="U28">
-        <v>-4.2458332584364078E-4</v>
+        <v>-4.2539664753046564E-4</v>
       </c>
       <c r="V28">
-        <v>-7.6202807355151133E-4</v>
+        <v>-7.6217902219994716E-4</v>
       </c>
       <c r="W28">
-        <v>-8.1856042452575902E-4</v>
+        <v>-8.1944948530748938E-4</v>
       </c>
       <c r="X28">
-        <v>-9.0061752606208911E-4</v>
+        <v>-9.0173761738946041E-4</v>
       </c>
       <c r="Y28">
-        <v>-1.0458495211376623E-3</v>
+        <v>-1.0481416071512067E-3</v>
       </c>
       <c r="Z28">
-        <v>-7.3867379220454114E-4</v>
+        <v>-7.3942298937775246E-4</v>
       </c>
       <c r="AA28">
-        <v>-1.3896215860871889E-3</v>
+        <v>-1.3919225072686605E-3</v>
       </c>
       <c r="AB28">
-        <v>-1.5116642171840759E-4</v>
+        <v>-1.5116575934752069E-4</v>
       </c>
       <c r="AC28">
-        <v>6.0157979422917418E-3</v>
+        <v>6.0166793530984832E-3</v>
       </c>
       <c r="AD28">
-        <v>1.2044679227264979E-3</v>
+        <v>1.2050662988662563E-3</v>
       </c>
       <c r="AE28">
-        <v>3.3225994220913613E-5</v>
+        <v>3.1738157942205443E-5</v>
       </c>
       <c r="AF28">
-        <v>-5.5800955046195269E-3</v>
+        <v>-5.5853341491376128E-3</v>
       </c>
       <c r="AG28">
-        <v>-4.9960251736090269E-5</v>
+        <v>-5.0736237843033575E-5</v>
       </c>
       <c r="AH28">
-        <v>-1.5794481559328979E-3</v>
+        <v>-1.5937974640766342E-3</v>
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.2">
@@ -3695,103 +3695,103 @@
         <v>40</v>
       </c>
       <c r="B29">
-        <v>-3.2257370864543715E-2</v>
+        <v>-3.2256345154647467E-2</v>
       </c>
       <c r="C29">
-        <v>2.7816574925235951E-4</v>
+        <v>2.784072028534537E-4</v>
       </c>
       <c r="D29">
-        <v>8.3024242661412784E-5</v>
+        <v>8.3442471515975114E-5</v>
       </c>
       <c r="E29">
-        <v>-8.4426249492158562E-7</v>
+        <v>-8.46917291042696E-7</v>
       </c>
       <c r="F29">
-        <v>1.2208520768304879E-5</v>
+        <v>1.228943983439131E-5</v>
       </c>
       <c r="G29">
-        <v>5.4098960169393466E-4</v>
+        <v>5.4007716534134318E-4</v>
       </c>
       <c r="H29">
-        <v>1.2351937744690619E-5</v>
+        <v>1.2367202380624871E-5</v>
       </c>
       <c r="I29">
-        <v>-8.9726751490706511E-7</v>
+        <v>-9.2613604091743387E-7</v>
       </c>
       <c r="J29">
-        <v>5.8132769883256948E-4</v>
+        <v>5.8116835579826061E-4</v>
       </c>
       <c r="K29">
-        <v>1.6003908164010459E-3</v>
+        <v>1.6004798899475862E-3</v>
       </c>
       <c r="L29">
-        <v>1.0713022314313625E-3</v>
+        <v>1.0715308746698604E-3</v>
       </c>
       <c r="M29">
-        <v>2.2657873002475894E-3</v>
+        <v>2.2653443312605176E-3</v>
       </c>
       <c r="N29">
-        <v>2.3035551953170369E-3</v>
+        <v>2.3034957109029234E-3</v>
       </c>
       <c r="O29">
-        <v>2.286023926794215E-3</v>
+        <v>2.2858713793871624E-3</v>
       </c>
       <c r="P29">
-        <v>7.6072760382328878E-4</v>
+        <v>7.6160373622462165E-4</v>
       </c>
       <c r="Q29">
-        <v>-3.3495061717894173E-4</v>
+        <v>-3.3429316284523149E-4</v>
       </c>
       <c r="R29">
-        <v>-1.5130642250818314E-3</v>
+        <v>-1.5134214970794688E-3</v>
       </c>
       <c r="S29">
-        <v>5.3193134213101127E-5</v>
+        <v>5.3495166847195106E-5</v>
       </c>
       <c r="T29">
-        <v>-7.499778912280204E-4</v>
+        <v>-7.5101265776521481E-4</v>
       </c>
       <c r="U29">
-        <v>-4.2540833475863092E-4</v>
+        <v>-4.257466288548192E-4</v>
       </c>
       <c r="V29">
-        <v>-2.8056700462065869E-4</v>
+        <v>-2.8032830554853725E-4</v>
       </c>
       <c r="W29">
-        <v>-6.9952946293277583E-4</v>
+        <v>-6.992416436402576E-4</v>
       </c>
       <c r="X29">
-        <v>-6.5026301718389742E-4</v>
+        <v>-6.5005051067750126E-4</v>
       </c>
       <c r="Y29">
-        <v>-4.498201437935492E-4</v>
+        <v>-4.5165999984702297E-4</v>
       </c>
       <c r="Z29">
-        <v>-4.2190834957272485E-4</v>
+        <v>-4.2131569590603962E-4</v>
       </c>
       <c r="AA29">
-        <v>-1.2911172282988846E-3</v>
+        <v>-1.2906609452671232E-3</v>
       </c>
       <c r="AB29">
-        <v>-1.6609493604615306E-4</v>
+        <v>-1.6604616621470903E-4</v>
       </c>
       <c r="AC29">
-        <v>1.2044679227264979E-3</v>
+        <v>1.2050662988662563E-3</v>
       </c>
       <c r="AD29">
-        <v>5.8591553456817467E-3</v>
+        <v>5.8600503641921247E-3</v>
       </c>
       <c r="AE29">
-        <v>-3.5238623922876191E-5</v>
+        <v>-3.6201900178088999E-5</v>
       </c>
       <c r="AF29">
-        <v>-5.0473513390873193E-3</v>
+        <v>-5.0472440386575418E-3</v>
       </c>
       <c r="AG29">
-        <v>1.3094536046546508E-4</v>
+        <v>1.2862588378309577E-4</v>
       </c>
       <c r="AH29">
-        <v>-2.1865436333162198E-3</v>
+        <v>-2.2029497683937775E-3</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.2">
@@ -3799,103 +3799,103 @@
         <v>41</v>
       </c>
       <c r="B30">
-        <v>-0.15851047262528631</v>
+        <v>-0.15831443361017025</v>
       </c>
       <c r="C30">
-        <v>-1.3356485573487605E-4</v>
+        <v>-1.339873225772027E-4</v>
       </c>
       <c r="D30">
-        <v>-2.0324666875240829E-4</v>
+        <v>-2.0408464249808619E-4</v>
       </c>
       <c r="E30">
-        <v>1.8824156444837629E-6</v>
+        <v>1.8885013698764351E-6</v>
       </c>
       <c r="F30">
-        <v>3.220369553871658E-4</v>
+        <v>3.2282307109531591E-4</v>
       </c>
       <c r="G30">
-        <v>-2.5592402160860513E-4</v>
+        <v>-2.5804718849088205E-4</v>
       </c>
       <c r="H30">
-        <v>-1.5065600838914652E-5</v>
+        <v>-1.507802647904497E-5</v>
       </c>
       <c r="I30">
-        <v>-1.4615227430008252E-5</v>
+        <v>-1.4588301351949894E-5</v>
       </c>
       <c r="J30">
-        <v>-1.8222289801069977E-4</v>
+        <v>-1.8270190902896534E-4</v>
       </c>
       <c r="K30">
-        <v>-1.0716389002940457E-3</v>
+        <v>-1.0735279842179913E-3</v>
       </c>
       <c r="L30">
-        <v>-8.0609434730715313E-4</v>
+        <v>-8.0762270224728878E-4</v>
       </c>
       <c r="M30">
-        <v>-9.4644610922082128E-4</v>
+        <v>-9.4949965991187116E-4</v>
       </c>
       <c r="N30">
-        <v>-8.8548406727380433E-4</v>
+        <v>-8.8901885234130701E-4</v>
       </c>
       <c r="O30">
-        <v>-6.2362190477473038E-4</v>
+        <v>-6.2732342892909618E-4</v>
       </c>
       <c r="P30">
-        <v>-1.6763241602153365E-4</v>
+        <v>-1.689489210115868E-4</v>
       </c>
       <c r="Q30">
-        <v>2.998099777251512E-3</v>
+        <v>2.9982241138869358E-3</v>
       </c>
       <c r="R30">
-        <v>3.402725814964641E-3</v>
+        <v>3.405023089859341E-3</v>
       </c>
       <c r="S30">
-        <v>2.8383210788795969E-3</v>
+        <v>2.8390896711018715E-3</v>
       </c>
       <c r="T30">
-        <v>2.7306670682286766E-3</v>
+        <v>2.7329186041669964E-3</v>
       </c>
       <c r="U30">
-        <v>2.2205062230388028E-3</v>
+        <v>2.2210409241572924E-3</v>
       </c>
       <c r="V30">
-        <v>2.6061038321676835E-3</v>
+        <v>2.6064570770870281E-3</v>
       </c>
       <c r="W30">
-        <v>2.8781878160798599E-3</v>
+        <v>2.878689923552208E-3</v>
       </c>
       <c r="X30">
-        <v>3.0669698095329976E-3</v>
+        <v>3.0680068158984637E-3</v>
       </c>
       <c r="Y30">
-        <v>2.8608098858363038E-3</v>
+        <v>2.8654995355700541E-3</v>
       </c>
       <c r="Z30">
-        <v>2.9690184143657595E-3</v>
+        <v>2.9696004758221302E-3</v>
       </c>
       <c r="AA30">
-        <v>3.2388559399907559E-3</v>
+        <v>3.2404226215289318E-3</v>
       </c>
       <c r="AB30">
-        <v>-4.1347368790286662E-5</v>
+        <v>-4.133556795215011E-5</v>
       </c>
       <c r="AC30">
-        <v>3.3225994220913613E-5</v>
+        <v>3.1738157942205443E-5</v>
       </c>
       <c r="AD30">
-        <v>-3.5238623922876191E-5</v>
+        <v>-3.6201900178088999E-5</v>
       </c>
       <c r="AE30">
-        <v>9.3885927450274558E-3</v>
+        <v>9.3895014151525406E-3</v>
       </c>
       <c r="AF30">
-        <v>5.8387706281173568E-3</v>
+        <v>5.8450344502074397E-3</v>
       </c>
       <c r="AG30">
-        <v>9.2455301499030397E-4</v>
+        <v>9.2674768614337249E-4</v>
       </c>
       <c r="AH30">
-        <v>5.3848191418780639E-3</v>
+        <v>5.4157104226828547E-3</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.2">
@@ -3903,103 +3903,103 @@
         <v>42</v>
       </c>
       <c r="B31">
-        <v>0.17462685783241594</v>
+        <v>0.17457035933422538</v>
       </c>
       <c r="C31">
-        <v>-4.2796241113990489E-3</v>
+        <v>-4.2823018633447729E-3</v>
       </c>
       <c r="D31">
-        <v>-1.4432699710086316E-3</v>
+        <v>-1.4449645075072515E-3</v>
       </c>
       <c r="E31">
-        <v>1.2504475447712871E-5</v>
+        <v>1.2513783935876304E-5</v>
       </c>
       <c r="F31">
-        <v>3.6298414841735502E-3</v>
+        <v>3.6356188324013251E-3</v>
       </c>
       <c r="G31">
-        <v>1.6784197773048529E-5</v>
+        <v>6.019385197265914E-6</v>
       </c>
       <c r="H31">
-        <v>-2.0193319986267356E-4</v>
+        <v>-2.0189317452700404E-4</v>
       </c>
       <c r="I31">
-        <v>1.7071736895229962E-5</v>
+        <v>1.7284044444611842E-5</v>
       </c>
       <c r="J31">
-        <v>-3.3383567065673886E-3</v>
+        <v>-3.3352720278828352E-3</v>
       </c>
       <c r="K31">
-        <v>-2.3012891822242615E-2</v>
+        <v>-2.3007373902769634E-2</v>
       </c>
       <c r="L31">
-        <v>-1.8745656618896937E-2</v>
+        <v>-1.8745668644477419E-2</v>
       </c>
       <c r="M31">
-        <v>-2.96100317643683E-2</v>
+        <v>-2.9606475169022872E-2</v>
       </c>
       <c r="N31">
-        <v>-3.1494487695220195E-2</v>
+        <v>-3.1498027778669134E-2</v>
       </c>
       <c r="O31">
-        <v>-2.8292654847919776E-2</v>
+        <v>-2.8293856792582735E-2</v>
       </c>
       <c r="P31">
-        <v>-8.1961209053173986E-3</v>
+        <v>-8.1973675600612375E-3</v>
       </c>
       <c r="Q31">
-        <v>2.1124708326911337E-2</v>
+        <v>2.1116428289733126E-2</v>
       </c>
       <c r="R31">
-        <v>3.7511099710748383E-2</v>
+        <v>3.7508458036117999E-2</v>
       </c>
       <c r="S31">
-        <v>1.8700860631329752E-2</v>
+        <v>1.8697158431966884E-2</v>
       </c>
       <c r="T31">
-        <v>2.0116015181737626E-2</v>
+        <v>2.0120242648692589E-2</v>
       </c>
       <c r="U31">
-        <v>1.7374656907640351E-2</v>
+        <v>1.737252148841336E-2</v>
       </c>
       <c r="V31">
-        <v>1.9615161642248115E-2</v>
+        <v>1.9607967700461894E-2</v>
       </c>
       <c r="W31">
-        <v>2.0051955780835969E-2</v>
+        <v>2.0043221146248701E-2</v>
       </c>
       <c r="X31">
-        <v>2.1982838294511781E-2</v>
+        <v>2.1978182824095298E-2</v>
       </c>
       <c r="Y31">
-        <v>2.1286060502171966E-2</v>
+        <v>2.129243625540049E-2</v>
       </c>
       <c r="Z31">
-        <v>2.134217449376339E-2</v>
+        <v>2.1336248715089261E-2</v>
       </c>
       <c r="AA31">
-        <v>2.1749099718759123E-2</v>
+        <v>2.1744379868262498E-2</v>
       </c>
       <c r="AB31">
-        <v>5.779015324047683E-4</v>
+        <v>5.7756974913565043E-4</v>
       </c>
       <c r="AC31">
-        <v>-5.5800955046195269E-3</v>
+        <v>-5.5853341491376128E-3</v>
       </c>
       <c r="AD31">
-        <v>-5.0473513390873193E-3</v>
+        <v>-5.0472440386575418E-3</v>
       </c>
       <c r="AE31">
-        <v>5.8387706281173568E-3</v>
+        <v>5.8450344502074397E-3</v>
       </c>
       <c r="AF31">
-        <v>0.10180293514693942</v>
+        <v>0.1017921222849138</v>
       </c>
       <c r="AG31">
-        <v>3.1338479652060934E-3</v>
+        <v>3.1387378186158023E-3</v>
       </c>
       <c r="AH31">
-        <v>5.017483122451083E-2</v>
+        <v>5.0244381923311023E-2</v>
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.2">
@@ -4007,103 +4007,103 @@
         <v>43</v>
       </c>
       <c r="B32">
-        <v>4.421343794281319E-2</v>
+        <v>4.4392163110681129E-2</v>
       </c>
       <c r="C32">
-        <v>-4.6336786088605738E-4</v>
+        <v>-4.6276051007821545E-4</v>
       </c>
       <c r="D32">
-        <v>-7.0481832906434203E-5</v>
+        <v>-7.0119841844526812E-5</v>
       </c>
       <c r="E32">
-        <v>4.4850648512936622E-7</v>
+        <v>4.4717655558178067E-7</v>
       </c>
       <c r="F32">
-        <v>3.6257130334769691E-4</v>
+        <v>3.6482834998838754E-4</v>
       </c>
       <c r="G32">
-        <v>4.270278188862661E-4</v>
+        <v>4.1359957179699989E-4</v>
       </c>
       <c r="H32">
-        <v>-1.1366567289394905E-5</v>
+        <v>-1.1410297390924243E-5</v>
       </c>
       <c r="I32">
-        <v>-2.537323481334834E-6</v>
+        <v>-2.5535628020466579E-6</v>
       </c>
       <c r="J32">
-        <v>5.3409354832910231E-4</v>
+        <v>5.3317149618431405E-4</v>
       </c>
       <c r="K32">
-        <v>1.5910213733708414E-4</v>
+        <v>1.5714877147954146E-4</v>
       </c>
       <c r="L32">
-        <v>-5.813230327526989E-4</v>
+        <v>-5.8436862514844238E-4</v>
       </c>
       <c r="M32">
-        <v>-6.0770265234587546E-4</v>
+        <v>-6.1287725232649526E-4</v>
       </c>
       <c r="N32">
-        <v>-3.2206269985366528E-4</v>
+        <v>-3.2832996745600781E-4</v>
       </c>
       <c r="O32">
-        <v>5.7604530648233741E-5</v>
+        <v>5.0667593865012187E-5</v>
       </c>
       <c r="P32">
-        <v>-2.6916640561097389E-4</v>
+        <v>-2.6907846389361131E-4</v>
       </c>
       <c r="Q32">
-        <v>1.9852435422809279E-3</v>
+        <v>1.9866684123103248E-3</v>
       </c>
       <c r="R32">
-        <v>2.1441458265871009E-3</v>
+        <v>2.147296759212429E-3</v>
       </c>
       <c r="S32">
-        <v>1.8650394986656469E-3</v>
+        <v>1.8649874657630486E-3</v>
       </c>
       <c r="T32">
-        <v>2.0767754272771732E-3</v>
+        <v>2.077851596064178E-3</v>
       </c>
       <c r="U32">
-        <v>1.4660282419467409E-3</v>
+        <v>1.4663781921407087E-3</v>
       </c>
       <c r="V32">
-        <v>1.837498144022335E-3</v>
+        <v>1.8380051837685587E-3</v>
       </c>
       <c r="W32">
-        <v>2.5290166049351868E-3</v>
+        <v>2.5298232466520569E-3</v>
       </c>
       <c r="X32">
-        <v>1.6846242617520801E-3</v>
+        <v>1.6853219912899666E-3</v>
       </c>
       <c r="Y32">
-        <v>1.245278279531953E-3</v>
+        <v>1.2470376430770884E-3</v>
       </c>
       <c r="Z32">
-        <v>2.0181842732747424E-3</v>
+        <v>2.0194372491672821E-3</v>
       </c>
       <c r="AA32">
-        <v>1.8622190421784274E-3</v>
+        <v>1.8684438977426992E-3</v>
       </c>
       <c r="AB32">
-        <v>-1.26251198857689E-5</v>
+        <v>-1.2674169938520864E-5</v>
       </c>
       <c r="AC32">
-        <v>-4.9960251736090269E-5</v>
+        <v>-5.0736237843033575E-5</v>
       </c>
       <c r="AD32">
-        <v>1.3094536046546508E-4</v>
+        <v>1.2862588378309577E-4</v>
       </c>
       <c r="AE32">
-        <v>9.2455301499030397E-4</v>
+        <v>9.2674768614337249E-4</v>
       </c>
       <c r="AF32">
-        <v>3.1338479652060934E-3</v>
+        <v>3.1387378186158023E-3</v>
       </c>
       <c r="AG32">
-        <v>1.7749339784970574E-2</v>
+        <v>1.7744379516989192E-2</v>
       </c>
       <c r="AH32">
-        <v>1.189347423167867E-3</v>
+        <v>1.1820810716502974E-3</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.2">
@@ -4111,103 +4111,103 @@
         <v>44</v>
       </c>
       <c r="B33">
-        <v>-19.396654019302577</v>
+        <v>-19.393854727987783</v>
       </c>
       <c r="C33">
-        <v>1.5716426711145401E-3</v>
+        <v>1.5731496333588261E-3</v>
       </c>
       <c r="D33">
-        <v>-5.7208342731185038E-2</v>
+        <v>-5.7217288359011374E-2</v>
       </c>
       <c r="E33">
-        <v>4.4352568608887409E-4</v>
+        <v>4.4360144502349994E-4</v>
       </c>
       <c r="F33">
-        <v>1.0284453137187339E-3</v>
+        <v>1.0412056092644426E-3</v>
       </c>
       <c r="G33">
-        <v>-1.285783073726635E-3</v>
+        <v>-1.4204445317214421E-3</v>
       </c>
       <c r="H33">
-        <v>-3.2331068767199795E-4</v>
+        <v>-3.2349648031645777E-4</v>
       </c>
       <c r="I33">
-        <v>-1.7234077610545748E-4</v>
+        <v>-1.7230645427570465E-4</v>
       </c>
       <c r="J33">
-        <v>7.9390310698239826E-3</v>
+        <v>7.9336691023474334E-3</v>
       </c>
       <c r="K33">
-        <v>-4.3683841851853228E-2</v>
+        <v>-4.3706826687121766E-2</v>
       </c>
       <c r="L33">
-        <v>-2.395457321193321E-2</v>
+        <v>-2.399423154617724E-2</v>
       </c>
       <c r="M33">
-        <v>-3.8385164177546907E-2</v>
+        <v>-3.8446727236973351E-2</v>
       </c>
       <c r="N33">
-        <v>-4.0875373753253452E-2</v>
+        <v>-4.0949789722922236E-2</v>
       </c>
       <c r="O33">
-        <v>-4.2031837352031018E-2</v>
+        <v>-4.211426232650059E-2</v>
       </c>
       <c r="P33">
-        <v>-3.295598795347663E-3</v>
+        <v>-3.2982370648724935E-3</v>
       </c>
       <c r="Q33">
-        <v>5.7757262032454536E-4</v>
+        <v>6.0016569687947226E-4</v>
       </c>
       <c r="R33">
-        <v>1.0569391465693316E-2</v>
+        <v>1.0604036528223162E-2</v>
       </c>
       <c r="S33">
-        <v>3.0383480951124957E-3</v>
+        <v>3.0538972236596757E-3</v>
       </c>
       <c r="T33">
-        <v>3.1677299623392927E-3</v>
+        <v>3.201520537964327E-3</v>
       </c>
       <c r="U33">
-        <v>-1.3047319719277049E-3</v>
+        <v>-1.2886820069850542E-3</v>
       </c>
       <c r="V33">
-        <v>1.9580739813668622E-3</v>
+        <v>1.9726245344748334E-3</v>
       </c>
       <c r="W33">
-        <v>-2.485477448958915E-3</v>
+        <v>-2.4735388982470158E-3</v>
       </c>
       <c r="X33">
-        <v>1.7896458013391195E-3</v>
+        <v>1.8093912072256781E-3</v>
       </c>
       <c r="Y33">
-        <v>3.2282223474506197E-3</v>
+        <v>3.261092848030684E-3</v>
       </c>
       <c r="Z33">
-        <v>1.3199842918870403E-3</v>
+        <v>1.3372451266587398E-3</v>
       </c>
       <c r="AA33">
-        <v>4.4440829780870265E-3</v>
+        <v>4.4983961650464921E-3</v>
       </c>
       <c r="AB33">
-        <v>3.3458228060671326E-4</v>
+        <v>3.33551737656329E-4</v>
       </c>
       <c r="AC33">
-        <v>-1.5794481559328979E-3</v>
+        <v>-1.5937974640766342E-3</v>
       </c>
       <c r="AD33">
-        <v>-2.1865436333162198E-3</v>
+        <v>-2.2029497683937775E-3</v>
       </c>
       <c r="AE33">
-        <v>5.3848191418780639E-3</v>
+        <v>5.4157104226828547E-3</v>
       </c>
       <c r="AF33">
-        <v>5.017483122451083E-2</v>
+        <v>5.0244381923311023E-2</v>
       </c>
       <c r="AG33">
-        <v>1.189347423167867E-3</v>
+        <v>1.1820810716502974E-3</v>
       </c>
       <c r="AH33">
-        <v>1.8812692290664841</v>
+        <v>1.881630880084092</v>
       </c>
     </row>
   </sheetData>
@@ -4338,112 +4338,112 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>-1.9052838959593962E-2</v>
+        <v>-2.170370792628366E-2</v>
       </c>
       <c r="C2">
-        <v>5.7671938139858302E-4</v>
+        <v>5.6872025132308809E-4</v>
       </c>
       <c r="D2">
-        <v>9.5318050260102948E-5</v>
+        <v>9.9719693751555415E-5</v>
       </c>
       <c r="E2">
-        <v>-9.574592782751447E-7</v>
+        <v>-9.8278168695078219E-7</v>
       </c>
       <c r="F2">
-        <v>-1.0125287202650485E-6</v>
+        <v>4.9557540527966665E-6</v>
       </c>
       <c r="G2">
-        <v>-4.9706915823994821E-5</v>
+        <v>-5.4759937683968702E-5</v>
       </c>
       <c r="H2">
-        <v>5.5423017313807548E-7</v>
+        <v>6.0739386919657008E-7</v>
       </c>
       <c r="I2">
-        <v>-1.9126548327973104E-6</v>
+        <v>-2.2088561417499869E-6</v>
       </c>
       <c r="J2">
-        <v>2.2606754347015756E-4</v>
+        <v>2.2529176596763293E-4</v>
       </c>
       <c r="K2">
-        <v>-2.6200416479750711E-5</v>
+        <v>-2.0548441723671957E-5</v>
       </c>
       <c r="L2">
-        <v>1.8436291178712874E-4</v>
+        <v>1.7601299452373021E-4</v>
       </c>
       <c r="M2">
-        <v>-4.9935437549654063E-5</v>
+        <v>-4.4172814031230657E-5</v>
       </c>
       <c r="N2">
-        <v>7.3599279448492624E-5</v>
+        <v>6.8788711189425242E-5</v>
       </c>
       <c r="O2">
-        <v>1.1893908353827507E-4</v>
+        <v>1.0442048261291538E-4</v>
       </c>
       <c r="P2">
-        <v>1.4135553900581472E-4</v>
+        <v>1.1669191381123278E-4</v>
       </c>
       <c r="Q2">
-        <v>8.2043532908925146E-5</v>
+        <v>6.531060290314826E-5</v>
       </c>
       <c r="R2">
-        <v>7.1459089857877061E-5</v>
+        <v>5.8531001542073881E-5</v>
       </c>
       <c r="S2">
-        <v>-5.1616644415208798E-5</v>
+        <v>-4.739628191338259E-5</v>
       </c>
       <c r="T2">
-        <v>-1.5056202710243881E-4</v>
+        <v>-1.307915989941787E-4</v>
       </c>
       <c r="U2">
-        <v>-1.4111586419066676E-4</v>
+        <v>-1.2322888170924464E-4</v>
       </c>
       <c r="V2">
-        <v>-1.3284621102419502E-4</v>
+        <v>-1.1467332293602214E-4</v>
       </c>
       <c r="W2">
-        <v>-1.502173557686047E-4</v>
+        <v>-1.3230289687276659E-4</v>
       </c>
       <c r="X2">
-        <v>-1.3982838380614354E-4</v>
+        <v>-1.2693357248660248E-4</v>
       </c>
       <c r="Y2">
-        <v>-7.8900990849105801E-5</v>
+        <v>-6.584471121018592E-5</v>
       </c>
       <c r="Z2">
-        <v>-9.353278090634882E-5</v>
+        <v>-8.1713753196895013E-5</v>
       </c>
       <c r="AA2">
-        <v>-1.1465299372097413E-4</v>
+        <v>-9.4010203455339439E-5</v>
       </c>
       <c r="AB2">
-        <v>-1.1066562368145969E-4</v>
+        <v>-9.6382845607393352E-5</v>
       </c>
       <c r="AC2">
-        <v>-1.4831856284484206E-4</v>
+        <v>-1.2588986616100871E-4</v>
       </c>
       <c r="AD2">
-        <v>-1.609703824956303E-4</v>
+        <v>-1.3739928202127533E-4</v>
       </c>
       <c r="AE2">
-        <v>1.0655861110370738E-5</v>
+        <v>1.0008730318499459E-5</v>
       </c>
       <c r="AF2">
-        <v>-2.790350858174995E-5</v>
+        <v>-2.0644422778944423E-5</v>
       </c>
       <c r="AG2">
-        <v>-3.03932547317998E-5</v>
+        <v>-2.8730728865376366E-5</v>
       </c>
       <c r="AH2">
-        <v>-1.5622324587662883E-4</v>
+        <v>-1.394900418480279E-4</v>
       </c>
       <c r="AI2">
-        <v>-1.0325310381750091E-4</v>
+        <v>-9.7158083913428906E-5</v>
       </c>
       <c r="AJ2">
-        <v>-8.5595679129652548E-5</v>
+        <v>-9.8535376230442055E-5</v>
       </c>
       <c r="AK2">
-        <v>-2.6844751168727931E-3</v>
+        <v>-2.8395360787424476E-3</v>
       </c>
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.2">
@@ -4451,112 +4451,112 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.81969428353471607</v>
+        <v>0.82897557879182626</v>
       </c>
       <c r="C3">
-        <v>9.5318050260102948E-5</v>
+        <v>9.9719693751555415E-5</v>
       </c>
       <c r="D3">
-        <v>1.5673101170538689E-3</v>
+        <v>1.5638196030990075E-3</v>
       </c>
       <c r="E3">
-        <v>-1.2632569318597901E-5</v>
+        <v>-1.2621742237629265E-5</v>
       </c>
       <c r="F3">
-        <v>-9.1662069276550809E-5</v>
+        <v>-9.7324294422685212E-5</v>
       </c>
       <c r="G3">
-        <v>-2.4068025149229753E-4</v>
+        <v>-2.6176299722823967E-4</v>
       </c>
       <c r="H3">
-        <v>1.3389838115938836E-6</v>
+        <v>1.1491706640339968E-6</v>
       </c>
       <c r="I3">
-        <v>9.492716960845019E-7</v>
+        <v>4.4777492796705537E-7</v>
       </c>
       <c r="J3">
-        <v>1.2432899791148537E-4</v>
+        <v>1.4859619361107712E-4</v>
       </c>
       <c r="K3">
-        <v>4.5853917780486588E-4</v>
+        <v>4.5884048072610331E-4</v>
       </c>
       <c r="L3">
-        <v>1.4140755232654786E-4</v>
+        <v>1.5144512068155253E-4</v>
       </c>
       <c r="M3">
-        <v>-5.8102323524528762E-5</v>
+        <v>1.9855584685798955E-5</v>
       </c>
       <c r="N3">
-        <v>4.7125845679071333E-5</v>
+        <v>1.7673660204770686E-5</v>
       </c>
       <c r="O3">
-        <v>-1.623718295914317E-5</v>
+        <v>3.7620956363122737E-6</v>
       </c>
       <c r="P3">
-        <v>-2.6719714216222323E-5</v>
+        <v>8.254009989114644E-6</v>
       </c>
       <c r="Q3">
-        <v>-1.6607347054710571E-4</v>
+        <v>-1.3434767886447846E-4</v>
       </c>
       <c r="R3">
-        <v>-1.3921603985933041E-4</v>
+        <v>-8.3187136322901076E-5</v>
       </c>
       <c r="S3">
-        <v>-1.4087696292298078E-4</v>
+        <v>-1.5064655017354642E-4</v>
       </c>
       <c r="T3">
-        <v>-1.481777840139295E-4</v>
+        <v>-1.4673392213709197E-4</v>
       </c>
       <c r="U3">
-        <v>-1.324284447740201E-4</v>
+        <v>-1.3503864256285067E-4</v>
       </c>
       <c r="V3">
-        <v>-1.2842602683082668E-4</v>
+        <v>-1.33622255640925E-4</v>
       </c>
       <c r="W3">
-        <v>-3.5086370415512991E-4</v>
+        <v>-3.9991525273359949E-4</v>
       </c>
       <c r="X3">
-        <v>-1.9171454975691615E-4</v>
+        <v>-1.8777134995880476E-4</v>
       </c>
       <c r="Y3">
-        <v>-2.21466355329724E-4</v>
+        <v>-2.2403050864703081E-4</v>
       </c>
       <c r="Z3">
-        <v>-1.7471080436940248E-4</v>
+        <v>-1.8486715644576435E-4</v>
       </c>
       <c r="AA3">
-        <v>-1.8912723054915342E-4</v>
+        <v>-1.9992115601267027E-4</v>
       </c>
       <c r="AB3">
-        <v>-1.8131248668446648E-4</v>
+        <v>-1.8623613112133189E-4</v>
       </c>
       <c r="AC3">
-        <v>-1.8388804953683655E-4</v>
+        <v>-1.9608417332638711E-4</v>
       </c>
       <c r="AD3">
-        <v>-1.5111368442356082E-4</v>
+        <v>-1.6168602529209597E-4</v>
       </c>
       <c r="AE3">
-        <v>1.1871135048770881E-6</v>
+        <v>1.5246196051043465E-7</v>
       </c>
       <c r="AF3">
-        <v>2.3928309300673065E-6</v>
+        <v>2.0716468091265018E-5</v>
       </c>
       <c r="AG3">
-        <v>8.3596636499339363E-5</v>
+        <v>8.0875074290668453E-5</v>
       </c>
       <c r="AH3">
-        <v>-6.6209498048584031E-4</v>
+        <v>-8.0981932894618955E-4</v>
       </c>
       <c r="AI3">
-        <v>-2.0311080103175422E-4</v>
+        <v>-2.5595938273887536E-4</v>
       </c>
       <c r="AJ3">
-        <v>-3.0207635378866685E-5</v>
+        <v>-5.2786647929986552E-5</v>
       </c>
       <c r="AK3">
-        <v>-4.8120650391440506E-2</v>
+        <v>-4.7956508298531195E-2</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.2">
@@ -4564,112 +4564,112 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-6.2251922166319858E-3</v>
+        <v>-6.2835293628200929E-3</v>
       </c>
       <c r="C4">
-        <v>-9.574592782751447E-7</v>
+        <v>-9.8278168695078219E-7</v>
       </c>
       <c r="D4">
-        <v>-1.2632569318597901E-5</v>
+        <v>-1.2621742237629265E-5</v>
       </c>
       <c r="E4">
-        <v>1.0268552986815166E-7</v>
+        <v>1.0271256683775973E-7</v>
       </c>
       <c r="F4">
-        <v>7.2372655608077447E-7</v>
+        <v>7.6173882556785212E-7</v>
       </c>
       <c r="G4">
-        <v>1.835746389516882E-6</v>
+        <v>1.9993447099193602E-6</v>
       </c>
       <c r="H4">
-        <v>-1.1397941042711271E-8</v>
+        <v>-1.0127805696835031E-8</v>
       </c>
       <c r="I4">
-        <v>-1.1895212507823611E-8</v>
+        <v>-7.7230956275637158E-9</v>
       </c>
       <c r="J4">
-        <v>-1.7500593829169562E-6</v>
+        <v>-1.9267937644833574E-6</v>
       </c>
       <c r="K4">
-        <v>-3.8701072939239475E-6</v>
+        <v>-3.8736981227546687E-6</v>
       </c>
       <c r="L4">
-        <v>-1.2266843969255167E-6</v>
+        <v>-1.2850566672853449E-6</v>
       </c>
       <c r="M4">
-        <v>3.9580847772757063E-7</v>
+        <v>-1.6651304885271815E-7</v>
       </c>
       <c r="N4">
-        <v>-6.235630829777284E-7</v>
+        <v>-4.0579552966791997E-7</v>
       </c>
       <c r="O4">
-        <v>-3.02118308794278E-8</v>
+        <v>-1.6643903211136359E-7</v>
       </c>
       <c r="P4">
-        <v>-4.8414401384501578E-8</v>
+        <v>-2.7879447496040137E-7</v>
       </c>
       <c r="Q4">
-        <v>1.0756139674487257E-6</v>
+        <v>8.6120746106998797E-7</v>
       </c>
       <c r="R4">
-        <v>8.9359546689148658E-7</v>
+        <v>5.0051621512941114E-7</v>
       </c>
       <c r="S4">
-        <v>1.117170375334771E-6</v>
+        <v>1.1811655201364232E-6</v>
       </c>
       <c r="T4">
-        <v>1.2663215036533011E-6</v>
+        <v>1.2572979350558902E-6</v>
       </c>
       <c r="U4">
-        <v>1.0856234133888444E-6</v>
+        <v>1.1121106758511595E-6</v>
       </c>
       <c r="V4">
-        <v>1.0583363867869853E-6</v>
+        <v>1.0988824933326913E-6</v>
       </c>
       <c r="W4">
-        <v>2.6780762834552373E-6</v>
+        <v>3.0525896865609038E-6</v>
       </c>
       <c r="X4">
-        <v>1.606436698605606E-6</v>
+        <v>1.5725416605516214E-6</v>
       </c>
       <c r="Y4">
-        <v>1.7147525672501801E-6</v>
+        <v>1.7413372828775804E-6</v>
       </c>
       <c r="Z4">
-        <v>1.3702840320293911E-6</v>
+        <v>1.4564276571855917E-6</v>
       </c>
       <c r="AA4">
-        <v>1.5041350888907754E-6</v>
+        <v>1.5883295104024019E-6</v>
       </c>
       <c r="AB4">
-        <v>1.4698149367860583E-6</v>
+        <v>1.511761188948183E-6</v>
       </c>
       <c r="AC4">
-        <v>1.4784060070943878E-6</v>
+        <v>1.5654625753571717E-6</v>
       </c>
       <c r="AD4">
-        <v>1.236554652979849E-6</v>
+        <v>1.3195225956968114E-6</v>
       </c>
       <c r="AE4">
-        <v>-4.2238712472434346E-8</v>
+        <v>-3.3326178073087985E-8</v>
       </c>
       <c r="AF4">
-        <v>3.9630903982493406E-8</v>
+        <v>-1.0870632736586497E-7</v>
       </c>
       <c r="AG4">
-        <v>-6.0013566440803967E-7</v>
+        <v>-5.8952704006295982E-7</v>
       </c>
       <c r="AH4">
-        <v>4.9187769426147052E-6</v>
+        <v>6.0325555803057186E-6</v>
       </c>
       <c r="AI4">
-        <v>1.6857221606156715E-6</v>
+        <v>2.0888653269183805E-6</v>
       </c>
       <c r="AJ4">
-        <v>1.7207039169161878E-7</v>
+        <v>3.2332482230684571E-7</v>
       </c>
       <c r="AK4">
-        <v>3.8611593638665054E-4</v>
+        <v>3.8533737148229959E-4</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.2">
@@ -4677,112 +4677,112 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-6.7577506155236708E-2</v>
+        <v>-8.429448431286192E-2</v>
       </c>
       <c r="C5">
-        <v>-1.0125287202650485E-6</v>
+        <v>4.9557540527966665E-6</v>
       </c>
       <c r="D5">
-        <v>-9.1662069276550809E-5</v>
+        <v>-9.7324294422685212E-5</v>
       </c>
       <c r="E5">
-        <v>7.2372655608077447E-7</v>
+        <v>7.6173882556785212E-7</v>
       </c>
       <c r="F5">
-        <v>7.7189469812069598E-4</v>
+        <v>7.5010134738004517E-4</v>
       </c>
       <c r="G5">
-        <v>6.0605709055740241E-4</v>
+        <v>5.7945848013616318E-4</v>
       </c>
       <c r="H5">
-        <v>2.2564648920458597E-6</v>
+        <v>2.6084053073063944E-6</v>
       </c>
       <c r="I5">
-        <v>-1.2062104801512601E-6</v>
+        <v>-9.1779242203756693E-7</v>
       </c>
       <c r="J5">
-        <v>3.1450205459534042E-5</v>
+        <v>3.3025224200890583E-5</v>
       </c>
       <c r="K5">
-        <v>-5.0976557426500752E-5</v>
+        <v>-5.544450800709143E-5</v>
       </c>
       <c r="L5">
-        <v>2.7545320341562136E-5</v>
+        <v>3.6253060516695869E-5</v>
       </c>
       <c r="M5">
-        <v>9.5398055983771598E-5</v>
+        <v>5.8609632661560172E-5</v>
       </c>
       <c r="N5">
-        <v>9.218373616370752E-7</v>
+        <v>1.8051453636668337E-5</v>
       </c>
       <c r="O5">
-        <v>1.8334681464097369E-4</v>
+        <v>1.6734040092520328E-4</v>
       </c>
       <c r="P5">
-        <v>1.8337295037597475E-4</v>
+        <v>1.7292786894208947E-4</v>
       </c>
       <c r="Q5">
-        <v>3.1550117172656308E-4</v>
+        <v>2.9701332218438166E-4</v>
       </c>
       <c r="R5">
-        <v>4.3193762635629004E-4</v>
+        <v>3.9747841356160352E-4</v>
       </c>
       <c r="S5">
-        <v>4.7938368605416956E-5</v>
+        <v>5.3077359012407903E-5</v>
       </c>
       <c r="T5">
-        <v>6.2465577631625561E-5</v>
+        <v>4.9406147657960018E-5</v>
       </c>
       <c r="U5">
-        <v>9.8668887315317384E-5</v>
+        <v>9.8897195012665845E-5</v>
       </c>
       <c r="V5">
-        <v>9.9921045536888097E-5</v>
+        <v>1.0298652859396768E-4</v>
       </c>
       <c r="W5">
-        <v>1.5622598332758295E-4</v>
+        <v>1.5432534442884455E-4</v>
       </c>
       <c r="X5">
-        <v>3.012660339628685E-6</v>
+        <v>5.2131969652930397E-8</v>
       </c>
       <c r="Y5">
-        <v>8.1774358178389001E-5</v>
+        <v>7.6514091080250594E-5</v>
       </c>
       <c r="Z5">
-        <v>1.0022814040613491E-4</v>
+        <v>1.0141401370349309E-4</v>
       </c>
       <c r="AA5">
-        <v>1.1294832131742948E-4</v>
+        <v>1.0687766741390532E-4</v>
       </c>
       <c r="AB5">
-        <v>1.0792754621088112E-4</v>
+        <v>1.1421101200235397E-4</v>
       </c>
       <c r="AC5">
-        <v>1.0440087796424771E-4</v>
+        <v>8.772871460425649E-5</v>
       </c>
       <c r="AD5">
-        <v>8.7995598908211355E-5</v>
+        <v>9.0027008713736666E-5</v>
       </c>
       <c r="AE5">
-        <v>-3.3718059539217433E-6</v>
+        <v>-2.3413431322887977E-6</v>
       </c>
       <c r="AF5">
-        <v>7.0619400835429311E-5</v>
+        <v>6.3472178592082195E-5</v>
       </c>
       <c r="AG5">
-        <v>3.2194093384762973E-5</v>
+        <v>2.3842657832721293E-5</v>
       </c>
       <c r="AH5">
-        <v>4.6365365075414378E-4</v>
+        <v>4.6702938611525196E-4</v>
       </c>
       <c r="AI5">
-        <v>2.6789813048165665E-4</v>
+        <v>2.5363623535887541E-4</v>
       </c>
       <c r="AJ5">
-        <v>4.4006391162126627E-5</v>
+        <v>-7.7695612340520609E-5</v>
       </c>
       <c r="AK5">
-        <v>1.8769304441431326E-3</v>
+        <v>2.08987457373785E-3</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.2">
@@ -4790,112 +4790,112 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-0.19304301046667055</v>
+        <v>-0.21276182872414173</v>
       </c>
       <c r="C6">
-        <v>-4.9706915823994821E-5</v>
+        <v>-5.4759937683968702E-5</v>
       </c>
       <c r="D6">
-        <v>-2.4068025149229753E-4</v>
+        <v>-2.6176299722823967E-4</v>
       </c>
       <c r="E6">
-        <v>1.835746389516882E-6</v>
+        <v>1.9993447099193602E-6</v>
       </c>
       <c r="F6">
-        <v>6.0605709055740241E-4</v>
+        <v>5.7945848013616318E-4</v>
       </c>
       <c r="G6">
-        <v>1.349082656413429E-3</v>
+        <v>1.3192224703439024E-3</v>
       </c>
       <c r="H6">
-        <v>4.5637744242005594E-6</v>
+        <v>5.1851836373419749E-6</v>
       </c>
       <c r="I6">
-        <v>-4.141398815185376E-7</v>
+        <v>4.5608674640032191E-7</v>
       </c>
       <c r="J6">
-        <v>4.596580591212049E-5</v>
+        <v>4.3033807523263406E-5</v>
       </c>
       <c r="K6">
-        <v>-8.8185817540344216E-5</v>
+        <v>-9.8055375851610328E-5</v>
       </c>
       <c r="L6">
-        <v>-5.3122463979111591E-5</v>
+        <v>-5.8063069406458523E-5</v>
       </c>
       <c r="M6">
-        <v>1.5938675155982541E-4</v>
+        <v>6.1084580255740348E-5</v>
       </c>
       <c r="N6">
-        <v>-4.9198407767295914E-6</v>
+        <v>3.0854455091388612E-5</v>
       </c>
       <c r="O6">
-        <v>3.3070069703272756E-4</v>
+        <v>3.0604033415907231E-4</v>
       </c>
       <c r="P6">
-        <v>4.2172038568871365E-4</v>
+        <v>3.8391521113138405E-4</v>
       </c>
       <c r="Q6">
-        <v>7.0098746898073112E-4</v>
+        <v>6.5285844395733886E-4</v>
       </c>
       <c r="R6">
-        <v>8.2901195042744914E-4</v>
+        <v>7.4337403460923387E-4</v>
       </c>
       <c r="S6">
-        <v>5.3783212641841103E-5</v>
+        <v>6.8581633730294491E-5</v>
       </c>
       <c r="T6">
-        <v>7.4471734655046865E-5</v>
+        <v>7.419182245523698E-5</v>
       </c>
       <c r="U6">
-        <v>1.3330182516804837E-4</v>
+        <v>1.5320258455627867E-4</v>
       </c>
       <c r="V6">
-        <v>1.0092798404837773E-4</v>
+        <v>1.1291709717118443E-4</v>
       </c>
       <c r="W6">
-        <v>3.1421301598471706E-4</v>
+        <v>3.6280075365191608E-4</v>
       </c>
       <c r="X6">
-        <v>3.4205872364993274E-5</v>
+        <v>5.0122813733793881E-5</v>
       </c>
       <c r="Y6">
-        <v>1.1354767851161617E-4</v>
+        <v>1.2023187573095173E-4</v>
       </c>
       <c r="Z6">
-        <v>1.3062016852951117E-4</v>
+        <v>1.471058196338124E-4</v>
       </c>
       <c r="AA6">
-        <v>1.9221012261777667E-4</v>
+        <v>2.0430125309287705E-4</v>
       </c>
       <c r="AB6">
-        <v>1.3053671005980333E-4</v>
+        <v>1.4717987433800959E-4</v>
       </c>
       <c r="AC6">
-        <v>1.7824970065623871E-4</v>
+        <v>1.8175104947745351E-4</v>
       </c>
       <c r="AD6">
-        <v>9.8234134385062318E-5</v>
+        <v>1.1650644190839058E-4</v>
       </c>
       <c r="AE6">
-        <v>1.0832750904601662E-5</v>
+        <v>1.3837225192972278E-5</v>
       </c>
       <c r="AF6">
-        <v>6.2050163587419534E-5</v>
+        <v>5.0237718827327008E-5</v>
       </c>
       <c r="AG6">
-        <v>-3.0025151282731721E-5</v>
+        <v>-4.1980072964322587E-5</v>
       </c>
       <c r="AH6">
-        <v>9.3787914242145264E-4</v>
+        <v>1.0449098498480887E-3</v>
       </c>
       <c r="AI6">
-        <v>3.2333373684365876E-4</v>
+        <v>3.1137272475631743E-4</v>
       </c>
       <c r="AJ6">
-        <v>1.1732894645242808E-4</v>
+        <v>1.0392523740486003E-5</v>
       </c>
       <c r="AK6">
-        <v>5.9743618877521375E-3</v>
+        <v>6.6349645717235072E-3</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.2">
@@ -4903,112 +4903,112 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>-4.9789939979269797E-4</v>
+        <v>-5.885254224327773E-5</v>
       </c>
       <c r="C7">
-        <v>5.5423017313807548E-7</v>
+        <v>6.0739386919657008E-7</v>
       </c>
       <c r="D7">
-        <v>1.3389838115938836E-6</v>
+        <v>1.1491706640339968E-6</v>
       </c>
       <c r="E7">
-        <v>-1.1397941042711271E-8</v>
+        <v>-1.0127805696835031E-8</v>
       </c>
       <c r="F7">
-        <v>2.2564648920458597E-6</v>
+        <v>2.6084053073063944E-6</v>
       </c>
       <c r="G7">
-        <v>4.5637744242005594E-6</v>
+        <v>5.1851836373419749E-6</v>
       </c>
       <c r="H7">
-        <v>1.5847761590639777E-6</v>
+        <v>1.5803013160979967E-6</v>
       </c>
       <c r="I7">
-        <v>8.6783474027521943E-8</v>
+        <v>1.1604823944446868E-7</v>
       </c>
       <c r="J7">
-        <v>6.4832177928402255E-7</v>
+        <v>9.4702839248742349E-7</v>
       </c>
       <c r="K7">
-        <v>-5.5954947612394952E-6</v>
+        <v>-4.401199011040834E-6</v>
       </c>
       <c r="L7">
-        <v>1.047707262291519E-5</v>
+        <v>9.6510771116259272E-6</v>
       </c>
       <c r="M7">
-        <v>-3.4051743053824907E-8</v>
+        <v>-1.0844940908296771E-6</v>
       </c>
       <c r="N7">
-        <v>1.0147341376593265E-6</v>
+        <v>1.0988362813333218E-6</v>
       </c>
       <c r="O7">
-        <v>1.8440773928599409E-6</v>
+        <v>2.6483242758050461E-6</v>
       </c>
       <c r="P7">
-        <v>3.7781763872483777E-6</v>
+        <v>4.0169411752427592E-6</v>
       </c>
       <c r="Q7">
-        <v>3.4322112359841457E-6</v>
+        <v>4.1782816503778517E-6</v>
       </c>
       <c r="R7">
-        <v>7.1163180188638244E-7</v>
+        <v>7.7470878303642301E-7</v>
       </c>
       <c r="S7">
-        <v>2.4227850722906905E-5</v>
+        <v>2.4367621533231145E-5</v>
       </c>
       <c r="T7">
-        <v>2.3229616815783743E-6</v>
+        <v>3.2773328765490004E-6</v>
       </c>
       <c r="U7">
-        <v>1.1453476489031039E-6</v>
+        <v>2.096056659420389E-6</v>
       </c>
       <c r="V7">
-        <v>-2.6028835468126582E-7</v>
+        <v>7.8949081730263541E-7</v>
       </c>
       <c r="W7">
-        <v>3.092717140203304E-6</v>
+        <v>5.5584871126726433E-6</v>
       </c>
       <c r="X7">
-        <v>4.8017675775065705E-8</v>
+        <v>1.1374161826246783E-6</v>
       </c>
       <c r="Y7">
-        <v>-1.4930872018712604E-6</v>
+        <v>-6.1397120649970573E-7</v>
       </c>
       <c r="Z7">
-        <v>-1.6752464451092201E-6</v>
+        <v>-1.0349763290918906E-6</v>
       </c>
       <c r="AA7">
-        <v>-8.5017929747139469E-7</v>
+        <v>-1.0236924644404231E-7</v>
       </c>
       <c r="AB7">
-        <v>-4.086838399922283E-7</v>
+        <v>5.1057908645391265E-7</v>
       </c>
       <c r="AC7">
-        <v>-8.617180017449097E-7</v>
+        <v>-3.9255432288917745E-7</v>
       </c>
       <c r="AD7">
-        <v>-1.681739772896383E-6</v>
+        <v>-7.1783446234100954E-7</v>
       </c>
       <c r="AE7">
-        <v>4.5961633301372582E-7</v>
+        <v>5.728321888608592E-7</v>
       </c>
       <c r="AF7">
-        <v>-1.9807745785110434E-7</v>
+        <v>-8.3443453407580788E-7</v>
       </c>
       <c r="AG7">
-        <v>-7.4218462676764583E-7</v>
+        <v>-1.4145760398459902E-6</v>
       </c>
       <c r="AH7">
-        <v>1.1946016358840454E-5</v>
+        <v>1.6830492548681271E-5</v>
       </c>
       <c r="AI7">
-        <v>-2.3773646068840399E-6</v>
+        <v>-1.9566637039408524E-6</v>
       </c>
       <c r="AJ7">
-        <v>-1.7712939310388445E-6</v>
+        <v>-2.782999312935937E-6</v>
       </c>
       <c r="AK7">
-        <v>-1.363486099422297E-4</v>
+        <v>-1.3384058999697974E-4</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.2">
@@ -5016,112 +5016,112 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>5.7966026206402669E-4</v>
+        <v>9.0473247864441024E-4</v>
       </c>
       <c r="C8">
-        <v>-1.9126548327973104E-6</v>
+        <v>-2.2088561417499869E-6</v>
       </c>
       <c r="D8">
-        <v>9.492716960845019E-7</v>
+        <v>4.4777492796705537E-7</v>
       </c>
       <c r="E8">
-        <v>-1.1895212507823611E-8</v>
+        <v>-7.7230956275637158E-9</v>
       </c>
       <c r="F8">
-        <v>-1.2062104801512601E-6</v>
+        <v>-9.1779242203756693E-7</v>
       </c>
       <c r="G8">
-        <v>-4.141398815185376E-7</v>
+        <v>4.5608674640032191E-7</v>
       </c>
       <c r="H8">
-        <v>8.6783474027521943E-8</v>
+        <v>1.1604823944446868E-7</v>
       </c>
       <c r="I8">
-        <v>1.9457293399632053E-6</v>
+        <v>1.9046645949031428E-6</v>
       </c>
       <c r="J8">
-        <v>3.1829345177485859E-7</v>
+        <v>2.1498814411932517E-8</v>
       </c>
       <c r="K8">
-        <v>-2.6099497343552858E-6</v>
+        <v>-1.6197059921707615E-6</v>
       </c>
       <c r="L8">
-        <v>7.8459038006065026E-6</v>
+        <v>6.4242146333737011E-6</v>
       </c>
       <c r="M8">
-        <v>8.7665022545539856E-7</v>
+        <v>-9.3196005555395635E-7</v>
       </c>
       <c r="N8">
-        <v>-1.6826384379230505E-6</v>
+        <v>-9.4692979887358084E-7</v>
       </c>
       <c r="O8">
-        <v>-5.3152547705610922E-6</v>
+        <v>-6.0141970657503151E-6</v>
       </c>
       <c r="P8">
-        <v>-7.2748881054494263E-6</v>
+        <v>-8.0043657425833342E-6</v>
       </c>
       <c r="Q8">
-        <v>-7.1258094243413821E-6</v>
+        <v>-7.2889804471182601E-6</v>
       </c>
       <c r="R8">
-        <v>-1.0410241289253084E-5</v>
+        <v>-1.1216758935520883E-5</v>
       </c>
       <c r="S8">
-        <v>1.0389277140461733E-5</v>
+        <v>1.0972283498756754E-5</v>
       </c>
       <c r="T8">
-        <v>-4.7990106867988911E-6</v>
+        <v>-3.2819300250063119E-6</v>
       </c>
       <c r="U8">
-        <v>-1.6941281760876918E-6</v>
+        <v>-1.316123531435961E-6</v>
       </c>
       <c r="V8">
-        <v>-2.7726538681246228E-6</v>
+        <v>-2.8456998599393605E-6</v>
       </c>
       <c r="W8">
-        <v>2.6991316569839996E-6</v>
+        <v>5.3255959304321382E-6</v>
       </c>
       <c r="X8">
-        <v>-3.1289662888962232E-6</v>
+        <v>-2.563157997585605E-6</v>
       </c>
       <c r="Y8">
-        <v>-5.8222573941848433E-6</v>
+        <v>-4.863353051129751E-6</v>
       </c>
       <c r="Z8">
-        <v>-3.5262393750526842E-6</v>
+        <v>-3.2468884823768591E-6</v>
       </c>
       <c r="AA8">
-        <v>-5.1620181532873745E-6</v>
+        <v>-4.1296004189726656E-6</v>
       </c>
       <c r="AB8">
-        <v>-1.2000576641078251E-6</v>
+        <v>-5.0497791333825928E-7</v>
       </c>
       <c r="AC8">
-        <v>-3.3450630693664571E-6</v>
+        <v>-2.8368143759664543E-6</v>
       </c>
       <c r="AD8">
-        <v>-5.4723714933859168E-6</v>
+        <v>-4.6318538766678758E-6</v>
       </c>
       <c r="AE8">
-        <v>8.6635860411326022E-7</v>
+        <v>9.1031253138933639E-7</v>
       </c>
       <c r="AF8">
-        <v>-6.0544934073119526E-8</v>
+        <v>-4.9583490595744228E-7</v>
       </c>
       <c r="AG8">
-        <v>-5.5364655702988702E-7</v>
+        <v>-6.4525897580194404E-7</v>
       </c>
       <c r="AH8">
-        <v>1.3163100871880702E-5</v>
+        <v>1.9816179429924181E-5</v>
       </c>
       <c r="AI8">
-        <v>-3.1333563733720139E-6</v>
+        <v>-2.9665120197590821E-6</v>
       </c>
       <c r="AJ8">
-        <v>2.2794908997929949E-6</v>
+        <v>5.0698884553582014E-6</v>
       </c>
       <c r="AK8">
-        <v>-1.2014489749146459E-4</v>
+        <v>-1.0477500967522881E-4</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.2">
@@ -5129,112 +5129,112 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>0.54593960707814093</v>
+        <v>0.52964423736097543</v>
       </c>
       <c r="C9">
-        <v>2.2606754347015756E-4</v>
+        <v>2.2529176596763293E-4</v>
       </c>
       <c r="D9">
-        <v>1.2432899791148537E-4</v>
+        <v>1.4859619361107712E-4</v>
       </c>
       <c r="E9">
-        <v>-1.7500593829169562E-6</v>
+        <v>-1.9267937644833574E-6</v>
       </c>
       <c r="F9">
-        <v>3.1450205459534042E-5</v>
+        <v>3.3025224200890583E-5</v>
       </c>
       <c r="G9">
-        <v>4.596580591212049E-5</v>
+        <v>4.3033807523263406E-5</v>
       </c>
       <c r="H9">
-        <v>6.4832177928402255E-7</v>
+        <v>9.4702839248742349E-7</v>
       </c>
       <c r="I9">
-        <v>3.1829345177485859E-7</v>
+        <v>2.1498814411932517E-8</v>
       </c>
       <c r="J9">
-        <v>1.537818287688899E-3</v>
+        <v>1.5135194743828759E-3</v>
       </c>
       <c r="K9">
-        <v>-5.4323105698897802E-4</v>
+        <v>-5.2329794726636673E-4</v>
       </c>
       <c r="L9">
-        <v>3.9869450526805309E-4</v>
+        <v>3.7446055078474042E-4</v>
       </c>
       <c r="M9">
-        <v>4.6598309352700035E-5</v>
+        <v>-4.064791976689003E-7</v>
       </c>
       <c r="N9">
-        <v>-9.6536579943353959E-5</v>
+        <v>-7.9334672414404386E-5</v>
       </c>
       <c r="O9">
-        <v>2.4822187074786842E-4</v>
+        <v>2.2505160337565053E-4</v>
       </c>
       <c r="P9">
-        <v>3.3953297942277886E-4</v>
+        <v>2.8285138698867828E-4</v>
       </c>
       <c r="Q9">
-        <v>3.6497484954214334E-4</v>
+        <v>3.1534273351962062E-4</v>
       </c>
       <c r="R9">
-        <v>3.8724658507452908E-4</v>
+        <v>3.257269616151306E-4</v>
       </c>
       <c r="S9">
-        <v>7.1415797844519258E-7</v>
+        <v>1.2904793069568266E-5</v>
       </c>
       <c r="T9">
-        <v>1.0143503141722308E-4</v>
+        <v>6.4579980432223193E-5</v>
       </c>
       <c r="U9">
-        <v>9.4236726205878889E-5</v>
+        <v>6.1143824624214122E-5</v>
       </c>
       <c r="V9">
-        <v>8.5579691037597819E-5</v>
+        <v>6.2896592744648722E-5</v>
       </c>
       <c r="W9">
-        <v>1.8536249974312094E-4</v>
+        <v>1.5711326662011066E-4</v>
       </c>
       <c r="X9">
-        <v>8.4839958406518392E-5</v>
+        <v>5.7109178617172659E-5</v>
       </c>
       <c r="Y9">
-        <v>1.5282463963091895E-4</v>
+        <v>1.1693178648300353E-4</v>
       </c>
       <c r="Z9">
-        <v>1.0123109445027596E-4</v>
+        <v>7.4444882629161064E-5</v>
       </c>
       <c r="AA9">
-        <v>1.043338556022083E-4</v>
+        <v>7.9162375088037045E-5</v>
       </c>
       <c r="AB9">
-        <v>1.0777022002765048E-4</v>
+        <v>7.1998910980921108E-5</v>
       </c>
       <c r="AC9">
-        <v>1.2287408525134128E-4</v>
+        <v>1.0322587521874272E-4</v>
       </c>
       <c r="AD9">
-        <v>9.491423626743138E-5</v>
+        <v>7.0064325990980411E-5</v>
       </c>
       <c r="AE9">
-        <v>3.4442340028185004E-5</v>
+        <v>3.2891121345850883E-5</v>
       </c>
       <c r="AF9">
-        <v>-6.3836646752876518E-6</v>
+        <v>-8.1066462823112706E-7</v>
       </c>
       <c r="AG9">
-        <v>-4.731433493148294E-5</v>
+        <v>-2.9945070001293809E-5</v>
       </c>
       <c r="AH9">
-        <v>2.3386879021880947E-4</v>
+        <v>2.2806202404377935E-4</v>
       </c>
       <c r="AI9">
-        <v>1.9553274917460169E-5</v>
+        <v>1.635334306059077E-5</v>
       </c>
       <c r="AJ9">
-        <v>2.7691835204071637E-6</v>
+        <v>-4.2648525998761422E-5</v>
       </c>
       <c r="AK9">
-        <v>-2.7392343950950627E-3</v>
+        <v>-3.4251587740652257E-3</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.2">
@@ -5242,112 +5242,112 @@
         <v>50</v>
       </c>
       <c r="B10">
-        <v>0.53966078836915199</v>
+        <v>0.52780127587879733</v>
       </c>
       <c r="C10">
-        <v>-2.6200416479750711E-5</v>
+        <v>-2.0548441723671957E-5</v>
       </c>
       <c r="D10">
-        <v>4.5853917780486588E-4</v>
+        <v>4.5884048072610331E-4</v>
       </c>
       <c r="E10">
-        <v>-3.8701072939239475E-6</v>
+        <v>-3.8736981227546687E-6</v>
       </c>
       <c r="F10">
-        <v>-5.0976557426500752E-5</v>
+        <v>-5.544450800709143E-5</v>
       </c>
       <c r="G10">
-        <v>-8.8185817540344216E-5</v>
+        <v>-9.8055375851610328E-5</v>
       </c>
       <c r="H10">
-        <v>-5.5954947612394952E-6</v>
+        <v>-4.401199011040834E-6</v>
       </c>
       <c r="I10">
-        <v>-2.6099497343552858E-6</v>
+        <v>-1.6197059921707615E-6</v>
       </c>
       <c r="J10">
-        <v>-5.4323105698897802E-4</v>
+        <v>-5.2329794726636673E-4</v>
       </c>
       <c r="K10">
-        <v>4.4288630388019303E-3</v>
+        <v>4.3863966129429281E-3</v>
       </c>
       <c r="L10">
-        <v>-1.4425190334258734E-3</v>
+        <v>-1.3647484750340391E-3</v>
       </c>
       <c r="M10">
-        <v>9.1527031834853648E-5</v>
+        <v>1.8177811566238555E-5</v>
       </c>
       <c r="N10">
-        <v>7.3464897662169288E-6</v>
+        <v>3.1525749202471513E-5</v>
       </c>
       <c r="O10">
-        <v>-6.2397604930264014E-4</v>
+        <v>-6.1744957377851337E-4</v>
       </c>
       <c r="P10">
-        <v>-7.0676914867222372E-4</v>
+        <v>-6.7504527774846137E-4</v>
       </c>
       <c r="Q10">
-        <v>-7.891575143505118E-4</v>
+        <v>-7.6243995611447162E-4</v>
       </c>
       <c r="R10">
-        <v>-8.6435099858807318E-4</v>
+        <v>-8.4823204946391298E-4</v>
       </c>
       <c r="S10">
-        <v>6.4066955246437716E-6</v>
+        <v>-5.8172439978917447E-6</v>
       </c>
       <c r="T10">
-        <v>2.3486179167421864E-5</v>
+        <v>1.7977673046019708E-5</v>
       </c>
       <c r="U10">
-        <v>-1.2178106605722962E-4</v>
+        <v>-1.3162396842780495E-4</v>
       </c>
       <c r="V10">
-        <v>-9.2276065849091447E-5</v>
+        <v>-1.0652099111587311E-4</v>
       </c>
       <c r="W10">
-        <v>-2.9154488150160904E-5</v>
+        <v>-3.5193131140875706E-5</v>
       </c>
       <c r="X10">
-        <v>-8.9938429641725319E-5</v>
+        <v>-9.7087932971795347E-5</v>
       </c>
       <c r="Y10">
-        <v>-3.0445186848698444E-5</v>
+        <v>-5.2714122348815687E-5</v>
       </c>
       <c r="Z10">
-        <v>-3.6313395668926933E-5</v>
+        <v>-5.8122854693033223E-5</v>
       </c>
       <c r="AA10">
-        <v>-2.6394766076543244E-5</v>
+        <v>-5.2996055533708307E-5</v>
       </c>
       <c r="AB10">
-        <v>-5.6129326901471419E-5</v>
+        <v>-5.3181423414917078E-5</v>
       </c>
       <c r="AC10">
-        <v>-3.9809157249165103E-5</v>
+        <v>-4.5213304343750399E-5</v>
       </c>
       <c r="AD10">
-        <v>-2.4101862783543551E-4</v>
+        <v>-2.3479083116685791E-4</v>
       </c>
       <c r="AE10">
-        <v>5.1299779366311814E-6</v>
+        <v>9.3425388733360017E-6</v>
       </c>
       <c r="AF10">
-        <v>2.1554091317274073E-6</v>
+        <v>-1.1688850206849734E-5</v>
       </c>
       <c r="AG10">
-        <v>1.2060495454712457E-4</v>
+        <v>8.8535083284796532E-5</v>
       </c>
       <c r="AH10">
-        <v>1.0773482138722815E-4</v>
+        <v>1.6249536345622206E-4</v>
       </c>
       <c r="AI10">
-        <v>-1.3642704160463266E-4</v>
+        <v>-1.6294053114226936E-4</v>
       </c>
       <c r="AJ10">
-        <v>1.665610691439271E-4</v>
+        <v>1.8707908949439859E-4</v>
       </c>
       <c r="AK10">
-        <v>-1.2096474722976279E-2</v>
+        <v>-1.226844840346631E-2</v>
       </c>
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
@@ -5355,112 +5355,112 @@
         <v>21</v>
       </c>
       <c r="B11">
-        <v>0.55849794881507531</v>
+        <v>0.54200111045623378</v>
       </c>
       <c r="C11">
-        <v>1.8436291178712874E-4</v>
+        <v>1.7601299452373021E-4</v>
       </c>
       <c r="D11">
-        <v>1.4140755232654786E-4</v>
+        <v>1.5144512068155253E-4</v>
       </c>
       <c r="E11">
-        <v>-1.2266843969255167E-6</v>
+        <v>-1.2850566672853449E-6</v>
       </c>
       <c r="F11">
-        <v>2.7545320341562136E-5</v>
+        <v>3.6253060516695869E-5</v>
       </c>
       <c r="G11">
-        <v>-5.3122463979111591E-5</v>
+        <v>-5.8063069406458523E-5</v>
       </c>
       <c r="H11">
-        <v>1.047707262291519E-5</v>
+        <v>9.6510771116259272E-6</v>
       </c>
       <c r="I11">
-        <v>7.8459038006065026E-6</v>
+        <v>6.4242146333737011E-6</v>
       </c>
       <c r="J11">
-        <v>3.9869450526805309E-4</v>
+        <v>3.7446055078474042E-4</v>
       </c>
       <c r="K11">
-        <v>-1.4425190334258734E-3</v>
+        <v>-1.3647484750340391E-3</v>
       </c>
       <c r="L11">
-        <v>2.0012230546572226E-3</v>
+        <v>1.9103786494794261E-3</v>
       </c>
       <c r="M11">
-        <v>-2.1820778645375584E-5</v>
+        <v>3.7926381450024049E-5</v>
       </c>
       <c r="N11">
-        <v>7.6940728052753317E-5</v>
+        <v>5.2395366692802847E-5</v>
       </c>
       <c r="O11">
-        <v>9.1823379797202967E-4</v>
+        <v>8.9444189545884482E-4</v>
       </c>
       <c r="P11">
-        <v>1.341409273277399E-3</v>
+        <v>1.2731793704679713E-3</v>
       </c>
       <c r="Q11">
-        <v>1.4281851826411806E-3</v>
+        <v>1.3695061629795369E-3</v>
       </c>
       <c r="R11">
-        <v>1.5139346696045168E-3</v>
+        <v>1.4669588230674688E-3</v>
       </c>
       <c r="S11">
-        <v>-3.2619189929830784E-4</v>
+        <v>-3.310994008482011E-4</v>
       </c>
       <c r="T11">
-        <v>-1.2785247699368752E-4</v>
+        <v>-1.3153368416030792E-4</v>
       </c>
       <c r="U11">
-        <v>5.7549412386469646E-5</v>
+        <v>4.8562894898203108E-5</v>
       </c>
       <c r="V11">
-        <v>1.670138549767072E-5</v>
+        <v>1.4442268127854915E-5</v>
       </c>
       <c r="W11">
-        <v>-3.1393311505431912E-5</v>
+        <v>-7.38157581338533E-5</v>
       </c>
       <c r="X11">
-        <v>-2.7629103894325803E-6</v>
+        <v>8.4281490520818694E-6</v>
       </c>
       <c r="Y11">
-        <v>-5.3338477968464283E-5</v>
+        <v>-5.0058156338636441E-5</v>
       </c>
       <c r="Z11">
-        <v>-6.0902678793040271E-5</v>
+        <v>-6.7123660475483862E-5</v>
       </c>
       <c r="AA11">
-        <v>-2.6459056302386742E-5</v>
+        <v>-2.1949874487003918E-5</v>
       </c>
       <c r="AB11">
-        <v>8.3289354075553879E-6</v>
+        <v>-1.0838422014373093E-5</v>
       </c>
       <c r="AC11">
-        <v>-6.0247860903062198E-5</v>
+        <v>-7.0924759601178385E-5</v>
       </c>
       <c r="AD11">
-        <v>4.7693767975935143E-5</v>
+        <v>2.3345825883063463E-5</v>
       </c>
       <c r="AE11">
-        <v>7.9365520947956075E-6</v>
+        <v>2.8974331368229267E-6</v>
       </c>
       <c r="AF11">
-        <v>-1.9814880131643941E-5</v>
+        <v>1.0495903727462236E-5</v>
       </c>
       <c r="AG11">
-        <v>-4.6723274659226982E-5</v>
+        <v>-2.0504214208845071E-5</v>
       </c>
       <c r="AH11">
-        <v>-2.872320429850991E-4</v>
+        <v>-4.6550791893365442E-4</v>
       </c>
       <c r="AI11">
-        <v>-4.6958022544065295E-5</v>
+        <v>-5.0744145823698739E-5</v>
       </c>
       <c r="AJ11">
-        <v>-3.1737142395660251E-4</v>
+        <v>-4.156203906077161E-4</v>
       </c>
       <c r="AK11">
-        <v>-6.9006113307261748E-3</v>
+        <v>-7.0400499304077904E-3</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.2">
@@ -5468,112 +5468,112 @@
         <v>51</v>
       </c>
       <c r="B12">
-        <v>0.53695442962402862</v>
+        <v>0.28582669636145841</v>
       </c>
       <c r="C12">
-        <v>-4.9935437549654063E-5</v>
+        <v>-4.4172814031230657E-5</v>
       </c>
       <c r="D12">
-        <v>-5.8102323524528762E-5</v>
+        <v>1.9855584685798955E-5</v>
       </c>
       <c r="E12">
-        <v>3.9580847772757063E-7</v>
+        <v>-1.6651304885271815E-7</v>
       </c>
       <c r="F12">
-        <v>9.5398055983771598E-5</v>
+        <v>5.8609632661560172E-5</v>
       </c>
       <c r="G12">
-        <v>1.5938675155982541E-4</v>
+        <v>6.1084580255740348E-5</v>
       </c>
       <c r="H12">
-        <v>-3.4051743053824907E-8</v>
+        <v>-1.0844940908296771E-6</v>
       </c>
       <c r="I12">
-        <v>8.7665022545539856E-7</v>
+        <v>-9.3196005555395635E-7</v>
       </c>
       <c r="J12">
-        <v>4.6598309352700035E-5</v>
+        <v>-4.064791976689003E-7</v>
       </c>
       <c r="K12">
-        <v>9.1527031834853648E-5</v>
+        <v>1.8177811566238555E-5</v>
       </c>
       <c r="L12">
-        <v>-2.1820778645375584E-5</v>
+        <v>3.7926381450024049E-5</v>
       </c>
       <c r="M12">
-        <v>7.3356435997316502E-4</v>
+        <v>7.0575034847344107E-4</v>
       </c>
       <c r="N12">
-        <v>-2.7842480654734978E-4</v>
+        <v>-2.5600311457498213E-4</v>
       </c>
       <c r="O12">
-        <v>1.8377394127904796E-4</v>
+        <v>1.9936139001228568E-4</v>
       </c>
       <c r="P12">
-        <v>2.9251401488315321E-4</v>
+        <v>2.9698617199282483E-4</v>
       </c>
       <c r="Q12">
-        <v>4.885553180158798E-4</v>
+        <v>4.3530971939770139E-4</v>
       </c>
       <c r="R12">
-        <v>5.2128057228869793E-4</v>
+        <v>5.1710527467294229E-4</v>
       </c>
       <c r="S12">
-        <v>-8.1384547839668763E-6</v>
+        <v>-3.0672255857299981E-5</v>
       </c>
       <c r="T12">
-        <v>5.3324086425137032E-5</v>
+        <v>-5.7889281380473054E-5</v>
       </c>
       <c r="U12">
-        <v>6.2360433835689506E-5</v>
+        <v>-3.2395423382957983E-5</v>
       </c>
       <c r="V12">
-        <v>5.4083384724044144E-5</v>
+        <v>-4.0842975025620002E-5</v>
       </c>
       <c r="W12">
-        <v>2.4671662517094546E-4</v>
+        <v>-9.2673938335579401E-5</v>
       </c>
       <c r="X12">
-        <v>2.3435223645025684E-5</v>
+        <v>-3.0407095223224524E-5</v>
       </c>
       <c r="Y12">
-        <v>7.7711380781966778E-5</v>
+        <v>-2.9919729361354023E-5</v>
       </c>
       <c r="Z12">
-        <v>5.0106478525074367E-5</v>
+        <v>-5.2587430502741464E-5</v>
       </c>
       <c r="AA12">
-        <v>6.5871605897387418E-5</v>
+        <v>-2.7410074746720759E-5</v>
       </c>
       <c r="AB12">
-        <v>7.1224902489720266E-5</v>
+        <v>-5.0006482550280559E-5</v>
       </c>
       <c r="AC12">
-        <v>5.4705081980232741E-5</v>
+        <v>-5.5048856433448172E-5</v>
       </c>
       <c r="AD12">
-        <v>1.5304337996143445E-5</v>
+        <v>-9.3872856654440579E-5</v>
       </c>
       <c r="AE12">
-        <v>3.62994500967456E-6</v>
+        <v>-7.9532753529085547E-6</v>
       </c>
       <c r="AF12">
-        <v>-5.5042079319060915E-5</v>
+        <v>3.8729997029774159E-5</v>
       </c>
       <c r="AG12">
-        <v>-7.9372285403567639E-5</v>
+        <v>-2.5384919889256347E-5</v>
       </c>
       <c r="AH12">
-        <v>4.8615278624124919E-4</v>
+        <v>-3.2319979013348721E-4</v>
       </c>
       <c r="AI12">
-        <v>1.3273266088431731E-4</v>
+        <v>3.6669712060458473E-5</v>
       </c>
       <c r="AJ12">
-        <v>3.9275790311003476E-4</v>
+        <v>-1.0743728745995259E-4</v>
       </c>
       <c r="AK12">
-        <v>1.1153355799062741E-3</v>
+        <v>-9.4784755049151536E-4</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.2">
@@ -5581,112 +5581,112 @@
         <v>52</v>
       </c>
       <c r="B13">
-        <v>-3.9935957360109207E-2</v>
+        <v>6.5171810468876948E-2</v>
       </c>
       <c r="C13">
-        <v>7.3599279448492624E-5</v>
+        <v>6.8788711189425242E-5</v>
       </c>
       <c r="D13">
-        <v>4.7125845679071333E-5</v>
+        <v>1.7673660204770686E-5</v>
       </c>
       <c r="E13">
-        <v>-6.235630829777284E-7</v>
+        <v>-4.0579552966791997E-7</v>
       </c>
       <c r="F13">
-        <v>9.218373616370752E-7</v>
+        <v>1.8051453636668337E-5</v>
       </c>
       <c r="G13">
-        <v>-4.9198407767295914E-6</v>
+        <v>3.0854455091388612E-5</v>
       </c>
       <c r="H13">
-        <v>1.0147341376593265E-6</v>
+        <v>1.0988362813333218E-6</v>
       </c>
       <c r="I13">
-        <v>-1.6826384379230505E-6</v>
+        <v>-9.4692979887358084E-7</v>
       </c>
       <c r="J13">
-        <v>-9.6536579943353959E-5</v>
+        <v>-7.9334672414404386E-5</v>
       </c>
       <c r="K13">
-        <v>7.3464897662169288E-6</v>
+        <v>3.1525749202471513E-5</v>
       </c>
       <c r="L13">
-        <v>7.6940728052753317E-5</v>
+        <v>5.2395366692802847E-5</v>
       </c>
       <c r="M13">
-        <v>-2.7842480654734978E-4</v>
+        <v>-2.5600311457498213E-4</v>
       </c>
       <c r="N13">
-        <v>9.2466685937944921E-4</v>
+        <v>8.9843319040199129E-4</v>
       </c>
       <c r="O13">
-        <v>-9.8142748711984023E-5</v>
+        <v>-8.7949819377236533E-5</v>
       </c>
       <c r="P13">
-        <v>-9.2455343445059415E-5</v>
+        <v>-7.6497095317426989E-5</v>
       </c>
       <c r="Q13">
-        <v>-5.7125712789763688E-5</v>
+        <v>-1.9012598474125204E-5</v>
       </c>
       <c r="R13">
-        <v>-2.9565632003537218E-5</v>
+        <v>-1.1588468072637187E-5</v>
       </c>
       <c r="S13">
-        <v>3.5358756637799835E-5</v>
+        <v>3.9282837961941271E-5</v>
       </c>
       <c r="T13">
-        <v>2.8966191470785983E-6</v>
+        <v>4.8731856495153973E-5</v>
       </c>
       <c r="U13">
-        <v>-2.0134821537692022E-5</v>
+        <v>1.9047936101847617E-5</v>
       </c>
       <c r="V13">
-        <v>1.9185532280462003E-5</v>
+        <v>6.4286492957583242E-5</v>
       </c>
       <c r="W13">
-        <v>-2.9936562894084858E-5</v>
+        <v>1.129425613282534E-4</v>
       </c>
       <c r="X13">
-        <v>-3.597132230272906E-5</v>
+        <v>3.8939141903934757E-6</v>
       </c>
       <c r="Y13">
-        <v>-1.2794118211391752E-5</v>
+        <v>3.854494564043739E-5</v>
       </c>
       <c r="Z13">
-        <v>1.1857200517539766E-6</v>
+        <v>5.1951596354073685E-5</v>
       </c>
       <c r="AA13">
-        <v>-5.1074586637544836E-5</v>
+        <v>-1.0104534219602213E-6</v>
       </c>
       <c r="AB13">
-        <v>-4.2406182428843557E-5</v>
+        <v>1.365323600859495E-5</v>
       </c>
       <c r="AC13">
-        <v>7.0699603840609969E-6</v>
+        <v>5.7969846389339827E-5</v>
       </c>
       <c r="AD13">
-        <v>5.3099876972129817E-5</v>
+        <v>9.7416967805587614E-5</v>
       </c>
       <c r="AE13">
-        <v>9.9894871184291119E-6</v>
+        <v>1.3311953359105044E-5</v>
       </c>
       <c r="AF13">
-        <v>-6.4879262942067981E-6</v>
+        <v>-3.6862007149667896E-5</v>
       </c>
       <c r="AG13">
-        <v>1.0022965829816121E-5</v>
+        <v>3.0437820501347844E-6</v>
       </c>
       <c r="AH13">
-        <v>-1.3215083105059337E-4</v>
+        <v>1.710820018068597E-4</v>
       </c>
       <c r="AI13">
-        <v>-7.3468817721465338E-5</v>
+        <v>-3.0838051703088146E-5</v>
       </c>
       <c r="AJ13">
-        <v>-6.0784182484479872E-5</v>
+        <v>1.6674119423135589E-4</v>
       </c>
       <c r="AK13">
-        <v>-7.829378479813513E-4</v>
+        <v>-1.8773406464490461E-5</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.2">
@@ -5694,112 +5694,112 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>6.6709481605570747E-2</v>
+        <v>4.4114543472539066E-3</v>
       </c>
       <c r="C14">
-        <v>1.1893908353827507E-4</v>
+        <v>1.0442048261291538E-4</v>
       </c>
       <c r="D14">
-        <v>-1.623718295914317E-5</v>
+        <v>3.7620956363122737E-6</v>
       </c>
       <c r="E14">
-        <v>-3.02118308794278E-8</v>
+        <v>-1.6643903211136359E-7</v>
       </c>
       <c r="F14">
-        <v>1.8334681464097369E-4</v>
+        <v>1.6734040092520328E-4</v>
       </c>
       <c r="G14">
-        <v>3.3070069703272756E-4</v>
+        <v>3.0604033415907231E-4</v>
       </c>
       <c r="H14">
-        <v>1.8440773928599409E-6</v>
+        <v>2.6483242758050461E-6</v>
       </c>
       <c r="I14">
-        <v>-5.3152547705610922E-6</v>
+        <v>-6.0141970657503151E-6</v>
       </c>
       <c r="J14">
-        <v>2.4822187074786842E-4</v>
+        <v>2.2505160337565053E-4</v>
       </c>
       <c r="K14">
-        <v>-6.2397604930264014E-4</v>
+        <v>-6.1744957377851337E-4</v>
       </c>
       <c r="L14">
-        <v>9.1823379797202967E-4</v>
+        <v>8.9444189545884482E-4</v>
       </c>
       <c r="M14">
-        <v>1.8377394127904796E-4</v>
+        <v>1.9936139001228568E-4</v>
       </c>
       <c r="N14">
-        <v>-9.8142748711984023E-5</v>
+        <v>-8.7949819377236533E-5</v>
       </c>
       <c r="O14">
-        <v>4.9156899290860832E-3</v>
+        <v>4.9096484904991482E-3</v>
       </c>
       <c r="P14">
-        <v>4.0677838580871466E-3</v>
+        <v>4.051813809653455E-3</v>
       </c>
       <c r="Q14">
-        <v>4.2429681795243908E-3</v>
+        <v>4.2290520863409869E-3</v>
       </c>
       <c r="R14">
-        <v>4.3588349891868486E-3</v>
+        <v>4.346849345930992E-3</v>
       </c>
       <c r="S14">
-        <v>2.7416275742890198E-4</v>
+        <v>2.6517982177591792E-4</v>
       </c>
       <c r="T14">
-        <v>4.5425941400981139E-4</v>
+        <v>4.5313175819080643E-4</v>
       </c>
       <c r="U14">
-        <v>5.3887264531805499E-4</v>
+        <v>5.2394424869642124E-4</v>
       </c>
       <c r="V14">
-        <v>5.4516246997962734E-4</v>
+        <v>5.1972797084243291E-4</v>
       </c>
       <c r="W14">
-        <v>5.0929763837080394E-4</v>
+        <v>4.4218941116260565E-4</v>
       </c>
       <c r="X14">
-        <v>4.4677085589189499E-4</v>
+        <v>4.2602564168626653E-4</v>
       </c>
       <c r="Y14">
-        <v>4.678657406572181E-4</v>
+        <v>4.3860285173461184E-4</v>
       </c>
       <c r="Z14">
-        <v>3.4560393461230453E-4</v>
+        <v>3.3739997694502396E-4</v>
       </c>
       <c r="AA14">
-        <v>4.3892556046235096E-4</v>
+        <v>4.3023946775139123E-4</v>
       </c>
       <c r="AB14">
-        <v>4.7369731707011748E-4</v>
+        <v>4.4896253075790509E-4</v>
       </c>
       <c r="AC14">
-        <v>5.0881804907443036E-4</v>
+        <v>4.8311215650485568E-4</v>
       </c>
       <c r="AD14">
-        <v>6.3552267416706843E-4</v>
+        <v>6.2002306705657723E-4</v>
       </c>
       <c r="AE14">
-        <v>-1.2807847623821434E-5</v>
+        <v>-1.5945101422037229E-5</v>
       </c>
       <c r="AF14">
-        <v>-9.7762280146985596E-5</v>
+        <v>-6.0761903032912712E-5</v>
       </c>
       <c r="AG14">
-        <v>8.9681582280645884E-7</v>
+        <v>1.8420808879070878E-5</v>
       </c>
       <c r="AH14">
-        <v>8.6332339376490918E-4</v>
+        <v>7.0807347997160026E-4</v>
       </c>
       <c r="AI14">
-        <v>2.1318150158074938E-4</v>
+        <v>1.9915938184299209E-4</v>
       </c>
       <c r="AJ14">
-        <v>2.0634659070800003E-4</v>
+        <v>4.9546297821529729E-5</v>
       </c>
       <c r="AK14">
-        <v>-3.6092604757943696E-3</v>
+        <v>-4.2026570635990742E-3</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.2">
@@ -5807,112 +5807,112 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>0.16535373803170331</v>
+        <v>7.3332048726932914E-2</v>
       </c>
       <c r="C15">
-        <v>1.4135553900581472E-4</v>
+        <v>1.1669191381123278E-4</v>
       </c>
       <c r="D15">
-        <v>-2.6719714216222323E-5</v>
+        <v>8.254009989114644E-6</v>
       </c>
       <c r="E15">
-        <v>-4.8414401384501578E-8</v>
+        <v>-2.7879447496040137E-7</v>
       </c>
       <c r="F15">
-        <v>1.8337295037597475E-4</v>
+        <v>1.7292786894208947E-4</v>
       </c>
       <c r="G15">
-        <v>4.2172038568871365E-4</v>
+        <v>3.8391521113138405E-4</v>
       </c>
       <c r="H15">
-        <v>3.7781763872483777E-6</v>
+        <v>4.0169411752427592E-6</v>
       </c>
       <c r="I15">
-        <v>-7.2748881054494263E-6</v>
+        <v>-8.0043657425833342E-6</v>
       </c>
       <c r="J15">
-        <v>3.3953297942277886E-4</v>
+        <v>2.8285138698867828E-4</v>
       </c>
       <c r="K15">
-        <v>-7.0676914867222372E-4</v>
+        <v>-6.7504527774846137E-4</v>
       </c>
       <c r="L15">
-        <v>1.341409273277399E-3</v>
+        <v>1.2731793704679713E-3</v>
       </c>
       <c r="M15">
-        <v>2.9251401488315321E-4</v>
+        <v>2.9698617199282483E-4</v>
       </c>
       <c r="N15">
-        <v>-9.2455343445059415E-5</v>
+        <v>-7.6497095317426989E-5</v>
       </c>
       <c r="O15">
-        <v>4.0677838580871466E-3</v>
+        <v>4.051813809653455E-3</v>
       </c>
       <c r="P15">
-        <v>5.3085653518315816E-3</v>
+        <v>5.1999955991633012E-3</v>
       </c>
       <c r="Q15">
-        <v>4.9037283154031094E-3</v>
+        <v>4.8091101045284988E-3</v>
       </c>
       <c r="R15">
-        <v>5.0261839858275793E-3</v>
+        <v>4.936723919089986E-3</v>
       </c>
       <c r="S15">
-        <v>4.2468722072888816E-4</v>
+        <v>3.6995814203498071E-4</v>
       </c>
       <c r="T15">
-        <v>2.6344845288188076E-4</v>
+        <v>2.2866551560719157E-4</v>
       </c>
       <c r="U15">
-        <v>4.1424741579953171E-4</v>
+        <v>3.9288922873829827E-4</v>
       </c>
       <c r="V15">
-        <v>3.9611479968327005E-4</v>
+        <v>3.6297932416843454E-4</v>
       </c>
       <c r="W15">
-        <v>5.1735410444571394E-4</v>
+        <v>4.0108667435848522E-4</v>
       </c>
       <c r="X15">
-        <v>2.8800816193008888E-4</v>
+        <v>2.8743493977203475E-4</v>
       </c>
       <c r="Y15">
-        <v>3.5404783483078926E-4</v>
+        <v>3.1826120750875868E-4</v>
       </c>
       <c r="Z15">
-        <v>2.5737123016834657E-4</v>
+        <v>2.3592661773069279E-4</v>
       </c>
       <c r="AA15">
-        <v>3.7735599968097104E-4</v>
+        <v>3.616053711458548E-4</v>
       </c>
       <c r="AB15">
-        <v>3.8539126972713268E-4</v>
+        <v>3.5020088728453551E-4</v>
       </c>
       <c r="AC15">
-        <v>3.9466224684815308E-4</v>
+        <v>3.5895540101782853E-4</v>
       </c>
       <c r="AD15">
-        <v>5.6294639400246383E-4</v>
+        <v>5.2991526319304304E-4</v>
       </c>
       <c r="AE15">
-        <v>-3.3358311870261429E-6</v>
+        <v>-8.7419108588623375E-6</v>
       </c>
       <c r="AF15">
-        <v>-1.366271549274088E-4</v>
+        <v>-7.668415310707903E-5</v>
       </c>
       <c r="AG15">
-        <v>-8.3912234266735085E-5</v>
+        <v>-5.2937924844451346E-5</v>
       </c>
       <c r="AH15">
-        <v>1.210952013005955E-3</v>
+        <v>9.0745782597323292E-4</v>
       </c>
       <c r="AI15">
-        <v>1.671948722658358E-4</v>
+        <v>1.3643123462541784E-4</v>
       </c>
       <c r="AJ15">
-        <v>3.2293461944150198E-4</v>
+        <v>1.0742878139482852E-4</v>
       </c>
       <c r="AK15">
-        <v>-3.7608584647295974E-3</v>
+        <v>-4.7277375057128441E-3</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.2">
@@ -5920,112 +5920,112 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>0.20265575733264535</v>
+        <v>9.2690371447546202E-2</v>
       </c>
       <c r="C16">
-        <v>8.2043532908925146E-5</v>
+        <v>6.531060290314826E-5</v>
       </c>
       <c r="D16">
-        <v>-1.6607347054710571E-4</v>
+        <v>-1.3434767886447846E-4</v>
       </c>
       <c r="E16">
-        <v>1.0756139674487257E-6</v>
+        <v>8.6120746106998797E-7</v>
       </c>
       <c r="F16">
-        <v>3.1550117172656308E-4</v>
+        <v>2.9701332218438166E-4</v>
       </c>
       <c r="G16">
-        <v>7.0098746898073112E-4</v>
+        <v>6.5285844395733886E-4</v>
       </c>
       <c r="H16">
-        <v>3.4322112359841457E-6</v>
+        <v>4.1782816503778517E-6</v>
       </c>
       <c r="I16">
-        <v>-7.1258094243413821E-6</v>
+        <v>-7.2889804471182601E-6</v>
       </c>
       <c r="J16">
-        <v>3.6497484954214334E-4</v>
+        <v>3.1534273351962062E-4</v>
       </c>
       <c r="K16">
-        <v>-7.891575143505118E-4</v>
+        <v>-7.6243995611447162E-4</v>
       </c>
       <c r="L16">
-        <v>1.4281851826411806E-3</v>
+        <v>1.3695061629795369E-3</v>
       </c>
       <c r="M16">
-        <v>4.885553180158798E-4</v>
+        <v>4.3530971939770139E-4</v>
       </c>
       <c r="N16">
-        <v>-5.7125712789763688E-5</v>
+        <v>-1.9012598474125204E-5</v>
       </c>
       <c r="O16">
-        <v>4.2429681795243908E-3</v>
+        <v>4.2290520863409869E-3</v>
       </c>
       <c r="P16">
-        <v>4.9037283154031094E-3</v>
+        <v>4.8091101045284988E-3</v>
       </c>
       <c r="Q16">
-        <v>5.7843740002046619E-3</v>
+        <v>5.6748606730368505E-3</v>
       </c>
       <c r="R16">
-        <v>5.5084890520473067E-3</v>
+        <v>5.397783949678563E-3</v>
       </c>
       <c r="S16">
-        <v>5.3063009618429581E-4</v>
+        <v>4.843293721102258E-4</v>
       </c>
       <c r="T16">
-        <v>4.7028472541138836E-4</v>
+        <v>4.3926901192413957E-4</v>
       </c>
       <c r="U16">
-        <v>6.7633500551217429E-4</v>
+        <v>6.5171889835163594E-4</v>
       </c>
       <c r="V16">
-        <v>6.4779434250588817E-4</v>
+        <v>6.1013654416429463E-4</v>
       </c>
       <c r="W16">
-        <v>9.5046289104455542E-4</v>
+        <v>8.5759954421396351E-4</v>
       </c>
       <c r="X16">
-        <v>5.9656680418134801E-4</v>
+        <v>5.9923552875350977E-4</v>
       </c>
       <c r="Y16">
-        <v>6.1238461550212203E-4</v>
+        <v>5.7635655715212769E-4</v>
       </c>
       <c r="Z16">
-        <v>4.7357048850340091E-4</v>
+        <v>4.6202937145138514E-4</v>
       </c>
       <c r="AA16">
-        <v>6.2852340696331458E-4</v>
+        <v>6.1653112208986428E-4</v>
       </c>
       <c r="AB16">
-        <v>6.6662198554022327E-4</v>
+        <v>6.2660810575814255E-4</v>
       </c>
       <c r="AC16">
-        <v>6.6687806717807981E-4</v>
+        <v>6.3503010871683412E-4</v>
       </c>
       <c r="AD16">
-        <v>8.6476466028424662E-4</v>
+        <v>8.3047054677832903E-4</v>
       </c>
       <c r="AE16">
-        <v>-4.0327157283170044E-6</v>
+        <v>-7.9180035156913063E-6</v>
       </c>
       <c r="AF16">
-        <v>-1.152901468668294E-4</v>
+        <v>-5.038796619940319E-5</v>
       </c>
       <c r="AG16">
-        <v>-7.7369112444771387E-5</v>
+        <v>-3.7028976092199918E-5</v>
       </c>
       <c r="AH16">
-        <v>2.0960225345401907E-3</v>
+        <v>1.8389634217473457E-3</v>
       </c>
       <c r="AI16">
-        <v>4.0748601460296281E-4</v>
+        <v>3.6133029357266486E-4</v>
       </c>
       <c r="AJ16">
-        <v>3.5848104095381858E-4</v>
+        <v>5.1583026682494766E-5</v>
       </c>
       <c r="AK16">
-        <v>-3.3468602507928484E-4</v>
+        <v>-1.2017918212612402E-3</v>
       </c>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.2">
@@ -6033,112 +6033,112 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>0.37511250992989437</v>
+        <v>0.24572493076980759</v>
       </c>
       <c r="C17">
-        <v>7.1459089857877061E-5</v>
+        <v>5.8531001542073881E-5</v>
       </c>
       <c r="D17">
-        <v>-1.3921603985933041E-4</v>
+        <v>-8.3187136322901076E-5</v>
       </c>
       <c r="E17">
-        <v>8.9359546689148658E-7</v>
+        <v>5.0051621512941114E-7</v>
       </c>
       <c r="F17">
-        <v>4.3193762635629004E-4</v>
+        <v>3.9747841356160352E-4</v>
       </c>
       <c r="G17">
-        <v>8.2901195042744914E-4</v>
+        <v>7.4337403460923387E-4</v>
       </c>
       <c r="H17">
-        <v>7.1163180188638244E-7</v>
+        <v>7.7470878303642301E-7</v>
       </c>
       <c r="I17">
-        <v>-1.0410241289253084E-5</v>
+        <v>-1.1216758935520883E-5</v>
       </c>
       <c r="J17">
-        <v>3.8724658507452908E-4</v>
+        <v>3.257269616151306E-4</v>
       </c>
       <c r="K17">
-        <v>-8.6435099858807318E-4</v>
+        <v>-8.4823204946391298E-4</v>
       </c>
       <c r="L17">
-        <v>1.5139346696045168E-3</v>
+        <v>1.4669588230674688E-3</v>
       </c>
       <c r="M17">
-        <v>5.2128057228869793E-4</v>
+        <v>5.1710527467294229E-4</v>
       </c>
       <c r="N17">
-        <v>-2.9565632003537218E-5</v>
+        <v>-1.1588468072637187E-5</v>
       </c>
       <c r="O17">
-        <v>4.3588349891868486E-3</v>
+        <v>4.346849345930992E-3</v>
       </c>
       <c r="P17">
-        <v>5.0261839858275793E-3</v>
+        <v>4.936723919089986E-3</v>
       </c>
       <c r="Q17">
-        <v>5.5084890520473067E-3</v>
+        <v>5.397783949678563E-3</v>
       </c>
       <c r="R17">
-        <v>6.0542186305666511E-3</v>
+        <v>5.94452854580854E-3</v>
       </c>
       <c r="S17">
-        <v>4.9263305894964836E-4</v>
+        <v>4.3085715879434387E-4</v>
       </c>
       <c r="T17">
-        <v>5.8903559766386839E-4</v>
+        <v>5.304179396251477E-4</v>
       </c>
       <c r="U17">
-        <v>7.9431328506174943E-4</v>
+        <v>7.3941247443417104E-4</v>
       </c>
       <c r="V17">
-        <v>7.7887310748811478E-4</v>
+        <v>7.1923218730674627E-4</v>
       </c>
       <c r="W17">
-        <v>9.1384286830919472E-4</v>
+        <v>7.2139221561440432E-4</v>
       </c>
       <c r="X17">
-        <v>7.0823785451135319E-4</v>
+        <v>6.852077528651866E-4</v>
       </c>
       <c r="Y17">
-        <v>6.7896312213133509E-4</v>
+        <v>6.0920070493409727E-4</v>
       </c>
       <c r="Z17">
-        <v>5.1351880990341205E-4</v>
+        <v>4.7061164934405651E-4</v>
       </c>
       <c r="AA17">
-        <v>6.9878651390394247E-4</v>
+        <v>6.564208731300895E-4</v>
       </c>
       <c r="AB17">
-        <v>7.4925589215152789E-4</v>
+        <v>6.7601479428946011E-4</v>
       </c>
       <c r="AC17">
-        <v>7.8666457975058333E-4</v>
+        <v>7.0786014715517546E-4</v>
       </c>
       <c r="AD17">
-        <v>9.7180379293169885E-4</v>
+        <v>8.9567495960767669E-4</v>
       </c>
       <c r="AE17">
-        <v>-1.0336742084194987E-5</v>
+        <v>-1.7348121850435921E-5</v>
       </c>
       <c r="AF17">
-        <v>-4.3262053502564324E-5</v>
+        <v>3.205705732235904E-5</v>
       </c>
       <c r="AG17">
-        <v>-5.6985776334853185E-5</v>
+        <v>-2.917581279860711E-6</v>
       </c>
       <c r="AH17">
-        <v>1.6252484531499587E-3</v>
+        <v>1.1268594425125921E-3</v>
       </c>
       <c r="AI17">
-        <v>5.3471701326602075E-4</v>
+        <v>4.7176136977543489E-4</v>
       </c>
       <c r="AJ17">
-        <v>5.0847586407035909E-4</v>
+        <v>1.7918969946929949E-4</v>
       </c>
       <c r="AK17">
-        <v>-1.2729034716397261E-3</v>
+        <v>-2.7931737949935323E-3</v>
       </c>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.2">
@@ -6146,112 +6146,112 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>-0.15485311713647984</v>
+        <v>-0.12663499102890524</v>
       </c>
       <c r="C18">
-        <v>-5.1616644415208798E-5</v>
+        <v>-4.739628191338259E-5</v>
       </c>
       <c r="D18">
-        <v>-1.4087696292298078E-4</v>
+        <v>-1.5064655017354642E-4</v>
       </c>
       <c r="E18">
-        <v>1.117170375334771E-6</v>
+        <v>1.1811655201364232E-6</v>
       </c>
       <c r="F18">
-        <v>4.7938368605416956E-5</v>
+        <v>5.3077359012407903E-5</v>
       </c>
       <c r="G18">
-        <v>5.3783212641841103E-5</v>
+        <v>6.8581633730294491E-5</v>
       </c>
       <c r="H18">
-        <v>2.4227850722906905E-5</v>
+        <v>2.4367621533231145E-5</v>
       </c>
       <c r="I18">
-        <v>1.0389277140461733E-5</v>
+        <v>1.0972283498756754E-5</v>
       </c>
       <c r="J18">
-        <v>7.1415797844519258E-7</v>
+        <v>1.2904793069568266E-5</v>
       </c>
       <c r="K18">
-        <v>6.4066955246437716E-6</v>
+        <v>-5.8172439978917447E-6</v>
       </c>
       <c r="L18">
-        <v>-3.2619189929830784E-4</v>
+        <v>-3.310994008482011E-4</v>
       </c>
       <c r="M18">
-        <v>-8.1384547839668763E-6</v>
+        <v>-3.0672255857299981E-5</v>
       </c>
       <c r="N18">
-        <v>3.5358756637799835E-5</v>
+        <v>3.9282837961941271E-5</v>
       </c>
       <c r="O18">
-        <v>2.7416275742890198E-4</v>
+        <v>2.6517982177591792E-4</v>
       </c>
       <c r="P18">
-        <v>4.2468722072888816E-4</v>
+        <v>3.6995814203498071E-4</v>
       </c>
       <c r="Q18">
-        <v>5.3063009618429581E-4</v>
+        <v>4.843293721102258E-4</v>
       </c>
       <c r="R18">
-        <v>4.9263305894964836E-4</v>
+        <v>4.3085715879434387E-4</v>
       </c>
       <c r="S18">
-        <v>2.6103512740418525E-3</v>
+        <v>2.5497437937447211E-3</v>
       </c>
       <c r="T18">
-        <v>2.125786497340844E-5</v>
+        <v>5.4326536763121467E-5</v>
       </c>
       <c r="U18">
-        <v>1.1195111871092282E-4</v>
+        <v>1.1753627286205712E-4</v>
       </c>
       <c r="V18">
-        <v>3.2664359254440173E-5</v>
+        <v>3.5928558674161361E-5</v>
       </c>
       <c r="W18">
-        <v>1.7456445650821111E-4</v>
+        <v>2.3890859828158351E-4</v>
       </c>
       <c r="X18">
-        <v>1.1175392799283847E-4</v>
+        <v>1.1775992654773095E-4</v>
       </c>
       <c r="Y18">
-        <v>4.6711134390362724E-5</v>
+        <v>5.6299877271471827E-5</v>
       </c>
       <c r="Z18">
-        <v>3.9976788809224263E-5</v>
+        <v>5.7333638767174966E-5</v>
       </c>
       <c r="AA18">
-        <v>-2.1041955767897406E-6</v>
+        <v>1.2108088385298687E-5</v>
       </c>
       <c r="AB18">
-        <v>5.0725580636866874E-5</v>
+        <v>6.0993607536711765E-5</v>
       </c>
       <c r="AC18">
-        <v>-1.4272463930039745E-5</v>
+        <v>-5.2895951805966577E-6</v>
       </c>
       <c r="AD18">
-        <v>-5.2833794686084042E-5</v>
+        <v>-3.2155969603644193E-5</v>
       </c>
       <c r="AE18">
-        <v>-1.3659313498668281E-6</v>
+        <v>2.8770135869575069E-6</v>
       </c>
       <c r="AF18">
-        <v>4.9756773546746016E-5</v>
+        <v>3.1491794593027281E-5</v>
       </c>
       <c r="AG18">
-        <v>4.3797475804492398E-5</v>
+        <v>3.3365200170013794E-5</v>
       </c>
       <c r="AH18">
-        <v>6.4085984605168392E-4</v>
+        <v>7.592819735681239E-4</v>
       </c>
       <c r="AI18">
-        <v>1.9406978048294395E-5</v>
+        <v>3.4497568413986864E-5</v>
       </c>
       <c r="AJ18">
-        <v>2.6581924329379661E-4</v>
+        <v>3.4584755429030418E-4</v>
       </c>
       <c r="AK18">
-        <v>2.0655648568618156E-3</v>
+        <v>2.3502628636551375E-3</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.2">
@@ -6259,112 +6259,112 @@
         <v>27</v>
       </c>
       <c r="B19">
-        <v>0.21117728006773107</v>
+        <v>0.22746814910164787</v>
       </c>
       <c r="C19">
-        <v>-1.5056202710243881E-4</v>
+        <v>-1.307915989941787E-4</v>
       </c>
       <c r="D19">
-        <v>-1.481777840139295E-4</v>
+        <v>-1.4673392213709197E-4</v>
       </c>
       <c r="E19">
-        <v>1.2663215036533011E-6</v>
+        <v>1.2572979350558902E-6</v>
       </c>
       <c r="F19">
-        <v>6.2465577631625561E-5</v>
+        <v>4.9406147657960018E-5</v>
       </c>
       <c r="G19">
-        <v>7.4471734655046865E-5</v>
+        <v>7.419182245523698E-5</v>
       </c>
       <c r="H19">
-        <v>2.3229616815783743E-6</v>
+        <v>3.2773328765490004E-6</v>
       </c>
       <c r="I19">
-        <v>-4.7990106867988911E-6</v>
+        <v>-3.2819300250063119E-6</v>
       </c>
       <c r="J19">
-        <v>1.0143503141722308E-4</v>
+        <v>6.4579980432223193E-5</v>
       </c>
       <c r="K19">
-        <v>2.3486179167421864E-5</v>
+        <v>1.7977673046019708E-5</v>
       </c>
       <c r="L19">
-        <v>-1.2785247699368752E-4</v>
+        <v>-1.3153368416030792E-4</v>
       </c>
       <c r="M19">
-        <v>5.3324086425137032E-5</v>
+        <v>-5.7889281380473054E-5</v>
       </c>
       <c r="N19">
-        <v>2.8966191470785983E-6</v>
+        <v>4.8731856495153973E-5</v>
       </c>
       <c r="O19">
-        <v>4.5425941400981139E-4</v>
+        <v>4.5313175819080643E-4</v>
       </c>
       <c r="P19">
-        <v>2.6344845288188076E-4</v>
+        <v>2.2866551560719157E-4</v>
       </c>
       <c r="Q19">
-        <v>4.7028472541138836E-4</v>
+        <v>4.3926901192413957E-4</v>
       </c>
       <c r="R19">
-        <v>5.8903559766386839E-4</v>
+        <v>5.304179396251477E-4</v>
       </c>
       <c r="S19">
-        <v>2.125786497340844E-5</v>
+        <v>5.4326536763121467E-5</v>
       </c>
       <c r="T19">
-        <v>5.6371984815811772E-3</v>
+        <v>5.4734008102580584E-3</v>
       </c>
       <c r="U19">
-        <v>2.8317936564392771E-3</v>
+        <v>2.7747322040088734E-3</v>
       </c>
       <c r="V19">
-        <v>2.8280462880954441E-3</v>
+        <v>2.7697660961865135E-3</v>
       </c>
       <c r="W19">
-        <v>3.0289833406881989E-3</v>
+        <v>3.0206883255023105E-3</v>
       </c>
       <c r="X19">
-        <v>2.8251425947621728E-3</v>
+        <v>2.7633851244418103E-3</v>
       </c>
       <c r="Y19">
-        <v>2.813880954614714E-3</v>
+        <v>2.7514142592845008E-3</v>
       </c>
       <c r="Z19">
-        <v>2.8125130654111661E-3</v>
+        <v>2.7564092617406218E-3</v>
       </c>
       <c r="AA19">
-        <v>2.846025136125304E-3</v>
+        <v>2.7848044772073102E-3</v>
       </c>
       <c r="AB19">
-        <v>2.8629717029838185E-3</v>
+        <v>2.8047961638477188E-3</v>
       </c>
       <c r="AC19">
-        <v>2.8914073089686253E-3</v>
+        <v>2.8309743396028935E-3</v>
       </c>
       <c r="AD19">
-        <v>2.9419299605024018E-3</v>
+        <v>2.8836386585876501E-3</v>
       </c>
       <c r="AE19">
-        <v>-2.4588219424363284E-5</v>
+        <v>-2.245084751036842E-5</v>
       </c>
       <c r="AF19">
-        <v>1.981876578103722E-5</v>
+        <v>1.2064556184856687E-5</v>
       </c>
       <c r="AG19">
-        <v>1.806562385231628E-4</v>
+        <v>1.5435793053792966E-4</v>
       </c>
       <c r="AH19">
-        <v>1.6412509049184532E-3</v>
+        <v>1.7783642705371419E-3</v>
       </c>
       <c r="AI19">
-        <v>1.3851247432372464E-3</v>
+        <v>1.3513621495204438E-3</v>
       </c>
       <c r="AJ19">
-        <v>4.121615422709486E-5</v>
+        <v>-2.5668139031183052E-4</v>
       </c>
       <c r="AK19">
-        <v>1.5078356791364874E-3</v>
+        <v>1.4383697523435704E-3</v>
       </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.2">
@@ -6372,112 +6372,112 @@
         <v>28</v>
       </c>
       <c r="B20">
-        <v>0.10027658631026473</v>
+        <v>0.11993273276117496</v>
       </c>
       <c r="C20">
-        <v>-1.4111586419066676E-4</v>
+        <v>-1.2322888170924464E-4</v>
       </c>
       <c r="D20">
-        <v>-1.324284447740201E-4</v>
+        <v>-1.3503864256285067E-4</v>
       </c>
       <c r="E20">
-        <v>1.0856234133888444E-6</v>
+        <v>1.1121106758511595E-6</v>
       </c>
       <c r="F20">
-        <v>9.8668887315317384E-5</v>
+        <v>9.8897195012665845E-5</v>
       </c>
       <c r="G20">
-        <v>1.3330182516804837E-4</v>
+        <v>1.5320258455627867E-4</v>
       </c>
       <c r="H20">
-        <v>1.1453476489031039E-6</v>
+        <v>2.096056659420389E-6</v>
       </c>
       <c r="I20">
-        <v>-1.6941281760876918E-6</v>
+        <v>-1.316123531435961E-6</v>
       </c>
       <c r="J20">
-        <v>9.4236726205878889E-5</v>
+        <v>6.1143824624214122E-5</v>
       </c>
       <c r="K20">
-        <v>-1.2178106605722962E-4</v>
+        <v>-1.3162396842780495E-4</v>
       </c>
       <c r="L20">
-        <v>5.7549412386469646E-5</v>
+        <v>4.8562894898203108E-5</v>
       </c>
       <c r="M20">
-        <v>6.2360433835689506E-5</v>
+        <v>-3.2395423382957983E-5</v>
       </c>
       <c r="N20">
-        <v>-2.0134821537692022E-5</v>
+        <v>1.9047936101847617E-5</v>
       </c>
       <c r="O20">
-        <v>5.3887264531805499E-4</v>
+        <v>5.2394424869642124E-4</v>
       </c>
       <c r="P20">
-        <v>4.1424741579953171E-4</v>
+        <v>3.9288922873829827E-4</v>
       </c>
       <c r="Q20">
-        <v>6.7633500551217429E-4</v>
+        <v>6.5171889835163594E-4</v>
       </c>
       <c r="R20">
-        <v>7.9431328506174943E-4</v>
+        <v>7.3941247443417104E-4</v>
       </c>
       <c r="S20">
-        <v>1.1195111871092282E-4</v>
+        <v>1.1753627286205712E-4</v>
       </c>
       <c r="T20">
-        <v>2.8317936564392771E-3</v>
+        <v>2.7747322040088734E-3</v>
       </c>
       <c r="U20">
-        <v>3.9155493171841218E-3</v>
+        <v>3.8441836643879866E-3</v>
       </c>
       <c r="V20">
-        <v>2.7577741791902123E-3</v>
+        <v>2.7050468359217689E-3</v>
       </c>
       <c r="W20">
-        <v>2.9300220457328056E-3</v>
+        <v>2.9361540936474252E-3</v>
       </c>
       <c r="X20">
-        <v>2.7541349607621223E-3</v>
+        <v>2.6959377809277736E-3</v>
       </c>
       <c r="Y20">
-        <v>2.7473386179332356E-3</v>
+        <v>2.6929349710437902E-3</v>
       </c>
       <c r="Z20">
-        <v>2.7534992231461166E-3</v>
+        <v>2.7050534292394346E-3</v>
       </c>
       <c r="AA20">
-        <v>2.7859573954441023E-3</v>
+        <v>2.7328032640307831E-3</v>
       </c>
       <c r="AB20">
-        <v>2.7886145144306951E-3</v>
+        <v>2.7371516872061403E-3</v>
       </c>
       <c r="AC20">
-        <v>2.8022847674327176E-3</v>
+        <v>2.7514902527995362E-3</v>
       </c>
       <c r="AD20">
-        <v>2.8549314782281244E-3</v>
+        <v>2.8053500145827589E-3</v>
       </c>
       <c r="AE20">
-        <v>-2.1867524591059841E-5</v>
+        <v>-1.9003680997826727E-5</v>
       </c>
       <c r="AF20">
-        <v>4.7089582603104536E-5</v>
+        <v>3.400064713707441E-5</v>
       </c>
       <c r="AG20">
-        <v>1.1639780296327716E-5</v>
+        <v>-3.2090818919509325E-6</v>
       </c>
       <c r="AH20">
-        <v>1.4586428930581043E-3</v>
+        <v>1.619070318045113E-3</v>
       </c>
       <c r="AI20">
-        <v>1.2510546866361131E-3</v>
+        <v>1.228152676058014E-3</v>
       </c>
       <c r="AJ20">
-        <v>-1.5743724308450743E-4</v>
+        <v>-4.3845365037426594E-4</v>
       </c>
       <c r="AK20">
-        <v>9.2560924361584709E-4</v>
+        <v>9.900843193810082E-4</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.2">
@@ -6485,112 +6485,112 @@
         <v>29</v>
       </c>
       <c r="B21">
-        <v>0.13808717153851505</v>
+        <v>0.15112312717125864</v>
       </c>
       <c r="C21">
-        <v>-1.3284621102419502E-4</v>
+        <v>-1.1467332293602214E-4</v>
       </c>
       <c r="D21">
-        <v>-1.2842602683082668E-4</v>
+        <v>-1.33622255640925E-4</v>
       </c>
       <c r="E21">
-        <v>1.0583363867869853E-6</v>
+        <v>1.0988824933326913E-6</v>
       </c>
       <c r="F21">
-        <v>9.9921045536888097E-5</v>
+        <v>1.0298652859396768E-4</v>
       </c>
       <c r="G21">
-        <v>1.0092798404837773E-4</v>
+        <v>1.1291709717118443E-4</v>
       </c>
       <c r="H21">
-        <v>-2.6028835468126582E-7</v>
+        <v>7.8949081730263541E-7</v>
       </c>
       <c r="I21">
-        <v>-2.7726538681246228E-6</v>
+        <v>-2.8456998599393605E-6</v>
       </c>
       <c r="J21">
-        <v>8.5579691037597819E-5</v>
+        <v>6.2896592744648722E-5</v>
       </c>
       <c r="K21">
-        <v>-9.2276065849091447E-5</v>
+        <v>-1.0652099111587311E-4</v>
       </c>
       <c r="L21">
-        <v>1.670138549767072E-5</v>
+        <v>1.4442268127854915E-5</v>
       </c>
       <c r="M21">
-        <v>5.4083384724044144E-5</v>
+        <v>-4.0842975025620002E-5</v>
       </c>
       <c r="N21">
-        <v>1.9185532280462003E-5</v>
+        <v>6.4286492957583242E-5</v>
       </c>
       <c r="O21">
-        <v>5.4516246997962734E-4</v>
+        <v>5.1972797084243291E-4</v>
       </c>
       <c r="P21">
-        <v>3.9611479968327005E-4</v>
+        <v>3.6297932416843454E-4</v>
       </c>
       <c r="Q21">
-        <v>6.4779434250588817E-4</v>
+        <v>6.1013654416429463E-4</v>
       </c>
       <c r="R21">
-        <v>7.7887310748811478E-4</v>
+        <v>7.1923218730674627E-4</v>
       </c>
       <c r="S21">
-        <v>3.2664359254440173E-5</v>
+        <v>3.5928558674161361E-5</v>
       </c>
       <c r="T21">
-        <v>2.8280462880954441E-3</v>
+        <v>2.7697660961865135E-3</v>
       </c>
       <c r="U21">
-        <v>2.7577741791902123E-3</v>
+        <v>2.7050468359217689E-3</v>
       </c>
       <c r="V21">
-        <v>4.221283631687116E-3</v>
+        <v>4.1478326648667907E-3</v>
       </c>
       <c r="W21">
-        <v>2.9014830377893644E-3</v>
+        <v>2.8925676978253001E-3</v>
       </c>
       <c r="X21">
-        <v>2.7586715814798138E-3</v>
+        <v>2.699972492598741E-3</v>
       </c>
       <c r="Y21">
-        <v>2.7434528286471626E-3</v>
+        <v>2.6873365732685726E-3</v>
       </c>
       <c r="Z21">
-        <v>2.7433013281783266E-3</v>
+        <v>2.6938083113208894E-3</v>
       </c>
       <c r="AA21">
-        <v>2.7747657040364283E-3</v>
+        <v>2.7199572925010462E-3</v>
       </c>
       <c r="AB21">
-        <v>2.7789325555003896E-3</v>
+        <v>2.7249929667691806E-3</v>
       </c>
       <c r="AC21">
-        <v>2.7989518739522114E-3</v>
+        <v>2.7462350162442925E-3</v>
       </c>
       <c r="AD21">
-        <v>2.8570117779306626E-3</v>
+        <v>2.805700375583526E-3</v>
       </c>
       <c r="AE21">
-        <v>-1.5631923637349899E-5</v>
+        <v>-1.429618660964561E-5</v>
       </c>
       <c r="AF21">
-        <v>9.9420780422664081E-5</v>
+        <v>9.4577350601097456E-5</v>
       </c>
       <c r="AG21">
-        <v>-2.2369923079074416E-5</v>
+        <v>-1.0319328790364666E-5</v>
       </c>
       <c r="AH21">
-        <v>1.2818731015259506E-3</v>
+        <v>1.4090593624099792E-3</v>
       </c>
       <c r="AI21">
-        <v>1.312234074011494E-3</v>
+        <v>1.2848864285724567E-3</v>
       </c>
       <c r="AJ21">
-        <v>-8.4276562516360387E-5</v>
+        <v>-4.1656625359183541E-4</v>
       </c>
       <c r="AK21">
-        <v>8.3210776151225116E-4</v>
+        <v>1.0481234167936272E-3</v>
       </c>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.2">
@@ -6598,112 +6598,112 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>8.3239673868843816E-2</v>
+        <v>9.5738110028160031E-2</v>
       </c>
       <c r="C22">
-        <v>-1.502173557686047E-4</v>
+        <v>-1.3230289687276659E-4</v>
       </c>
       <c r="D22">
-        <v>-3.5086370415512991E-4</v>
+        <v>-3.9991525273359949E-4</v>
       </c>
       <c r="E22">
-        <v>2.6780762834552373E-6</v>
+        <v>3.0525896865609038E-6</v>
       </c>
       <c r="F22">
-        <v>1.5622598332758295E-4</v>
+        <v>1.5432534442884455E-4</v>
       </c>
       <c r="G22">
-        <v>3.1421301598471706E-4</v>
+        <v>3.6280075365191608E-4</v>
       </c>
       <c r="H22">
-        <v>3.092717140203304E-6</v>
+        <v>5.5584871126726433E-6</v>
       </c>
       <c r="I22">
-        <v>2.6991316569839996E-6</v>
+        <v>5.3255959304321382E-6</v>
       </c>
       <c r="J22">
-        <v>1.8536249974312094E-4</v>
+        <v>1.5711326662011066E-4</v>
       </c>
       <c r="K22">
-        <v>-2.9154488150160904E-5</v>
+        <v>-3.5193131140875706E-5</v>
       </c>
       <c r="L22">
-        <v>-3.1393311505431912E-5</v>
+        <v>-7.38157581338533E-5</v>
       </c>
       <c r="M22">
-        <v>2.4671662517094546E-4</v>
+        <v>-9.2673938335579401E-5</v>
       </c>
       <c r="N22">
-        <v>-2.9936562894084858E-5</v>
+        <v>1.129425613282534E-4</v>
       </c>
       <c r="O22">
-        <v>5.0929763837080394E-4</v>
+        <v>4.4218941116260565E-4</v>
       </c>
       <c r="P22">
-        <v>5.1735410444571394E-4</v>
+        <v>4.0108667435848522E-4</v>
       </c>
       <c r="Q22">
-        <v>9.5046289104455542E-4</v>
+        <v>8.5759954421396351E-4</v>
       </c>
       <c r="R22">
-        <v>9.1384286830919472E-4</v>
+        <v>7.2139221561440432E-4</v>
       </c>
       <c r="S22">
-        <v>1.7456445650821111E-4</v>
+        <v>2.3890859828158351E-4</v>
       </c>
       <c r="T22">
-        <v>3.0289833406881989E-3</v>
+        <v>3.0206883255023105E-3</v>
       </c>
       <c r="U22">
-        <v>2.9300220457328056E-3</v>
+        <v>2.9361540936474252E-3</v>
       </c>
       <c r="V22">
-        <v>2.9014830377893644E-3</v>
+        <v>2.8925676978253001E-3</v>
       </c>
       <c r="W22">
-        <v>4.891211163251339E-3</v>
+        <v>5.0373727985443765E-3</v>
       </c>
       <c r="X22">
-        <v>2.8978594555717479E-3</v>
+        <v>2.8816720076971511E-3</v>
       </c>
       <c r="Y22">
-        <v>2.9369398302331227E-3</v>
+        <v>2.9244600194964694E-3</v>
       </c>
       <c r="Z22">
-        <v>2.9477334355863072E-3</v>
+        <v>2.9495913404561191E-3</v>
       </c>
       <c r="AA22">
-        <v>3.0064056373992911E-3</v>
+        <v>3.0068009543869991E-3</v>
       </c>
       <c r="AB22">
-        <v>2.9812422227236679E-3</v>
+        <v>2.9863282608865926E-3</v>
       </c>
       <c r="AC22">
-        <v>3.0055928177607494E-3</v>
+        <v>3.0187540877594007E-3</v>
       </c>
       <c r="AD22">
-        <v>3.0568279746538201E-3</v>
+        <v>3.0756419236610765E-3</v>
       </c>
       <c r="AE22">
-        <v>2.9821535887171089E-6</v>
+        <v>1.1713933768479478E-5</v>
       </c>
       <c r="AF22">
-        <v>-3.4699631699067798E-5</v>
+        <v>-5.3244011822030422E-5</v>
       </c>
       <c r="AG22">
-        <v>-1.1923536252575763E-4</v>
+        <v>-1.6072293212113047E-4</v>
       </c>
       <c r="AH22">
-        <v>3.2083286898510746E-3</v>
+        <v>3.8037232856959501E-3</v>
       </c>
       <c r="AI22">
-        <v>1.393858786937349E-3</v>
+        <v>1.3599764444285098E-3</v>
       </c>
       <c r="AJ22">
-        <v>-6.4618926396795847E-5</v>
+        <v>-3.7280377926815489E-4</v>
       </c>
       <c r="AK22">
-        <v>7.0299381565938771E-3</v>
+        <v>8.46019379524297E-3</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.2">
@@ -6711,112 +6711,112 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>9.5548094625685601E-2</v>
+        <v>0.10018390753502265</v>
       </c>
       <c r="C23">
-        <v>-1.3982838380614354E-4</v>
+        <v>-1.2693357248660248E-4</v>
       </c>
       <c r="D23">
-        <v>-1.9171454975691615E-4</v>
+        <v>-1.8777134995880476E-4</v>
       </c>
       <c r="E23">
-        <v>1.606436698605606E-6</v>
+        <v>1.5725416605516214E-6</v>
       </c>
       <c r="F23">
-        <v>3.012660339628685E-6</v>
+        <v>5.2131969652930397E-8</v>
       </c>
       <c r="G23">
-        <v>3.4205872364993274E-5</v>
+        <v>5.0122813733793881E-5</v>
       </c>
       <c r="H23">
-        <v>4.8017675775065705E-8</v>
+        <v>1.1374161826246783E-6</v>
       </c>
       <c r="I23">
-        <v>-3.1289662888962232E-6</v>
+        <v>-2.563157997585605E-6</v>
       </c>
       <c r="J23">
-        <v>8.4839958406518392E-5</v>
+        <v>5.7109178617172659E-5</v>
       </c>
       <c r="K23">
-        <v>-8.9938429641725319E-5</v>
+        <v>-9.7087932971795347E-5</v>
       </c>
       <c r="L23">
-        <v>-2.7629103894325803E-6</v>
+        <v>8.4281490520818694E-6</v>
       </c>
       <c r="M23">
-        <v>2.3435223645025684E-5</v>
+        <v>-3.0407095223224524E-5</v>
       </c>
       <c r="N23">
-        <v>-3.597132230272906E-5</v>
+        <v>3.8939141903934757E-6</v>
       </c>
       <c r="O23">
-        <v>4.4677085589189499E-4</v>
+        <v>4.2602564168626653E-4</v>
       </c>
       <c r="P23">
-        <v>2.8800816193008888E-4</v>
+        <v>2.8743493977203475E-4</v>
       </c>
       <c r="Q23">
-        <v>5.9656680418134801E-4</v>
+        <v>5.9923552875350977E-4</v>
       </c>
       <c r="R23">
-        <v>7.0823785451135319E-4</v>
+        <v>6.852077528651866E-4</v>
       </c>
       <c r="S23">
-        <v>1.1175392799283847E-4</v>
+        <v>1.1775992654773095E-4</v>
       </c>
       <c r="T23">
-        <v>2.8251425947621728E-3</v>
+        <v>2.7633851244418103E-3</v>
       </c>
       <c r="U23">
-        <v>2.7541349607621223E-3</v>
+        <v>2.6959377809277736E-3</v>
       </c>
       <c r="V23">
-        <v>2.7586715814798138E-3</v>
+        <v>2.699972492598741E-3</v>
       </c>
       <c r="W23">
-        <v>2.8978594555717479E-3</v>
+        <v>2.8816720076971511E-3</v>
       </c>
       <c r="X23">
-        <v>4.368655466395626E-3</v>
+        <v>4.2674650525665872E-3</v>
       </c>
       <c r="Y23">
-        <v>2.7388657196559672E-3</v>
+        <v>2.6782853696535316E-3</v>
       </c>
       <c r="Z23">
-        <v>2.7362206784021146E-3</v>
+        <v>2.6811331344558107E-3</v>
       </c>
       <c r="AA23">
-        <v>2.7648943525472379E-3</v>
+        <v>2.7059115848437855E-3</v>
       </c>
       <c r="AB23">
-        <v>2.781093112469451E-3</v>
+        <v>2.7215959571901152E-3</v>
       </c>
       <c r="AC23">
-        <v>2.7880368855622796E-3</v>
+        <v>2.7289999346365155E-3</v>
       </c>
       <c r="AD23">
-        <v>2.8430523114158423E-3</v>
+        <v>2.7836145533383437E-3</v>
       </c>
       <c r="AE23">
-        <v>-2.674417115406803E-5</v>
+        <v>-2.5516630864483928E-5</v>
       </c>
       <c r="AF23">
-        <v>1.3502734843439296E-4</v>
+        <v>1.5623610031467993E-4</v>
       </c>
       <c r="AG23">
-        <v>1.5294533671644166E-4</v>
+        <v>1.2613247924652334E-4</v>
       </c>
       <c r="AH23">
-        <v>1.2278448892159518E-3</v>
+        <v>1.3477736410026748E-3</v>
       </c>
       <c r="AI23">
-        <v>1.0759731157713611E-3</v>
+        <v>1.044295903928415E-3</v>
       </c>
       <c r="AJ23">
-        <v>-1.9262681582776591E-4</v>
+        <v>-4.9887313714724662E-4</v>
       </c>
       <c r="AK23">
-        <v>2.9882895462922023E-3</v>
+        <v>2.8523411712167378E-3</v>
       </c>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.2">
@@ -6824,112 +6824,112 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>4.9793407901525422E-2</v>
+        <v>5.103386311151694E-2</v>
       </c>
       <c r="C24">
-        <v>-7.8900990849105801E-5</v>
+        <v>-6.584471121018592E-5</v>
       </c>
       <c r="D24">
-        <v>-2.21466355329724E-4</v>
+        <v>-2.2403050864703081E-4</v>
       </c>
       <c r="E24">
-        <v>1.7147525672501801E-6</v>
+        <v>1.7413372828775804E-6</v>
       </c>
       <c r="F24">
-        <v>8.1774358178389001E-5</v>
+        <v>7.6514091080250594E-5</v>
       </c>
       <c r="G24">
-        <v>1.1354767851161617E-4</v>
+        <v>1.2023187573095173E-4</v>
       </c>
       <c r="H24">
-        <v>-1.4930872018712604E-6</v>
+        <v>-6.1397120649970573E-7</v>
       </c>
       <c r="I24">
-        <v>-5.8222573941848433E-6</v>
+        <v>-4.863353051129751E-6</v>
       </c>
       <c r="J24">
-        <v>1.5282463963091895E-4</v>
+        <v>1.1693178648300353E-4</v>
       </c>
       <c r="K24">
-        <v>-3.0445186848698444E-5</v>
+        <v>-5.2714122348815687E-5</v>
       </c>
       <c r="L24">
-        <v>-5.3338477968464283E-5</v>
+        <v>-5.0058156338636441E-5</v>
       </c>
       <c r="M24">
-        <v>7.7711380781966778E-5</v>
+        <v>-2.9919729361354023E-5</v>
       </c>
       <c r="N24">
-        <v>-1.2794118211391752E-5</v>
+        <v>3.854494564043739E-5</v>
       </c>
       <c r="O24">
-        <v>4.678657406572181E-4</v>
+        <v>4.3860285173461184E-4</v>
       </c>
       <c r="P24">
-        <v>3.5404783483078926E-4</v>
+        <v>3.1826120750875868E-4</v>
       </c>
       <c r="Q24">
-        <v>6.1238461550212203E-4</v>
+        <v>5.7635655715212769E-4</v>
       </c>
       <c r="R24">
-        <v>6.7896312213133509E-4</v>
+        <v>6.0920070493409727E-4</v>
       </c>
       <c r="S24">
-        <v>4.6711134390362724E-5</v>
+        <v>5.6299877271471827E-5</v>
       </c>
       <c r="T24">
-        <v>2.813880954614714E-3</v>
+        <v>2.7514142592845008E-3</v>
       </c>
       <c r="U24">
-        <v>2.7473386179332356E-3</v>
+        <v>2.6929349710437902E-3</v>
       </c>
       <c r="V24">
-        <v>2.7434528286471626E-3</v>
+        <v>2.6873365732685726E-3</v>
       </c>
       <c r="W24">
-        <v>2.9369398302331227E-3</v>
+        <v>2.9244600194964694E-3</v>
       </c>
       <c r="X24">
-        <v>2.7388657196559672E-3</v>
+        <v>2.6782853696535316E-3</v>
       </c>
       <c r="Y24">
-        <v>3.9212417729994524E-3</v>
+        <v>3.8414642289045352E-3</v>
       </c>
       <c r="Z24">
-        <v>2.755443537245098E-3</v>
+        <v>2.7013963216352532E-3</v>
       </c>
       <c r="AA24">
-        <v>2.7857176050128515E-3</v>
+        <v>2.727148591122215E-3</v>
       </c>
       <c r="AB24">
-        <v>2.7807591050313385E-3</v>
+        <v>2.7238152395789193E-3</v>
       </c>
       <c r="AC24">
-        <v>2.7941165549943072E-3</v>
+        <v>2.7394105067973622E-3</v>
       </c>
       <c r="AD24">
-        <v>2.8525259231793024E-3</v>
+        <v>2.7972833304172181E-3</v>
       </c>
       <c r="AE24">
-        <v>-1.3788855900143983E-5</v>
+        <v>-1.3158010222385043E-5</v>
       </c>
       <c r="AF24">
-        <v>4.6667512741768524E-5</v>
+        <v>4.5546531140810411E-5</v>
       </c>
       <c r="AG24">
-        <v>-5.115806391101335E-6</v>
+        <v>-8.9432622037777454E-6</v>
       </c>
       <c r="AH24">
-        <v>1.4975389422720922E-3</v>
+        <v>1.613880737985031E-3</v>
       </c>
       <c r="AI24">
-        <v>1.3020200421445811E-3</v>
+        <v>1.3138863511488834E-3</v>
       </c>
       <c r="AJ24">
-        <v>-1.4283005487500587E-4</v>
+        <v>-4.4783339022323547E-4</v>
       </c>
       <c r="AK24">
-        <v>4.261426102712941E-3</v>
+        <v>4.3625085018779812E-3</v>
       </c>
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.2">
@@ -6937,112 +6937,112 @@
         <v>33</v>
       </c>
       <c r="B25">
-        <v>2.1808001995440168E-2</v>
+        <v>2.9786345885821294E-2</v>
       </c>
       <c r="C25">
-        <v>-9.353278090634882E-5</v>
+        <v>-8.1713753196895013E-5</v>
       </c>
       <c r="D25">
-        <v>-1.7471080436940248E-4</v>
+        <v>-1.8486715644576435E-4</v>
       </c>
       <c r="E25">
-        <v>1.3702840320293911E-6</v>
+        <v>1.4564276571855917E-6</v>
       </c>
       <c r="F25">
-        <v>1.0022814040613491E-4</v>
+        <v>1.0141401370349309E-4</v>
       </c>
       <c r="G25">
-        <v>1.3062016852951117E-4</v>
+        <v>1.471058196338124E-4</v>
       </c>
       <c r="H25">
-        <v>-1.6752464451092201E-6</v>
+        <v>-1.0349763290918906E-6</v>
       </c>
       <c r="I25">
-        <v>-3.5262393750526842E-6</v>
+        <v>-3.2468884823768591E-6</v>
       </c>
       <c r="J25">
-        <v>1.0123109445027596E-4</v>
+        <v>7.4444882629161064E-5</v>
       </c>
       <c r="K25">
-        <v>-3.6313395668926933E-5</v>
+        <v>-5.8122854693033223E-5</v>
       </c>
       <c r="L25">
-        <v>-6.0902678793040271E-5</v>
+        <v>-6.7123660475483862E-5</v>
       </c>
       <c r="M25">
-        <v>5.0106478525074367E-5</v>
+        <v>-5.2587430502741464E-5</v>
       </c>
       <c r="N25">
-        <v>1.1857200517539766E-6</v>
+        <v>5.1951596354073685E-5</v>
       </c>
       <c r="O25">
-        <v>3.4560393461230453E-4</v>
+        <v>3.3739997694502396E-4</v>
       </c>
       <c r="P25">
-        <v>2.5737123016834657E-4</v>
+        <v>2.3592661773069279E-4</v>
       </c>
       <c r="Q25">
-        <v>4.7357048850340091E-4</v>
+        <v>4.6202937145138514E-4</v>
       </c>
       <c r="R25">
-        <v>5.1351880990341205E-4</v>
+        <v>4.7061164934405651E-4</v>
       </c>
       <c r="S25">
-        <v>3.9976788809224263E-5</v>
+        <v>5.7333638767174966E-5</v>
       </c>
       <c r="T25">
-        <v>2.8125130654111661E-3</v>
+        <v>2.7564092617406218E-3</v>
       </c>
       <c r="U25">
-        <v>2.7534992231461166E-3</v>
+        <v>2.7050534292394346E-3</v>
       </c>
       <c r="V25">
-        <v>2.7433013281783266E-3</v>
+        <v>2.6938083113208894E-3</v>
       </c>
       <c r="W25">
-        <v>2.9477334355863072E-3</v>
+        <v>2.9495913404561191E-3</v>
       </c>
       <c r="X25">
-        <v>2.7362206784021146E-3</v>
+        <v>2.6811331344558107E-3</v>
       </c>
       <c r="Y25">
-        <v>2.755443537245098E-3</v>
+        <v>2.7013963216352532E-3</v>
       </c>
       <c r="Z25">
-        <v>3.6366504282107381E-3</v>
+        <v>3.5690411366131563E-3</v>
       </c>
       <c r="AA25">
-        <v>2.7929208269317852E-3</v>
+        <v>2.7412329994251205E-3</v>
       </c>
       <c r="AB25">
-        <v>2.785290199358928E-3</v>
+        <v>2.7345891497149652E-3</v>
       </c>
       <c r="AC25">
-        <v>2.7980841409786664E-3</v>
+        <v>2.7511952589872146E-3</v>
       </c>
       <c r="AD25">
-        <v>2.8416782937837459E-3</v>
+        <v>2.7964598044259853E-3</v>
       </c>
       <c r="AE25">
-        <v>-1.5958071844769363E-5</v>
+        <v>-1.4621723294185783E-5</v>
       </c>
       <c r="AF25">
-        <v>3.771894953198259E-5</v>
+        <v>4.2372538600183435E-5</v>
       </c>
       <c r="AG25">
-        <v>-7.4038107101304128E-6</v>
+        <v>-1.3139504685883278E-5</v>
       </c>
       <c r="AH25">
-        <v>1.5559368776512669E-3</v>
+        <v>1.7009958081512925E-3</v>
       </c>
       <c r="AI25">
-        <v>1.1992774560520233E-3</v>
+        <v>1.1822031526856412E-3</v>
       </c>
       <c r="AJ25">
-        <v>-1.4575172547589689E-4</v>
+        <v>-4.3706048332005452E-4</v>
       </c>
       <c r="AK25">
-        <v>2.7782441668772438E-3</v>
+        <v>3.1131612200366605E-3</v>
       </c>
     </row>
     <row r="26" spans="1:37" x14ac:dyDescent="0.2">
@@ -7050,112 +7050,112 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>3.1158857395230118E-2</v>
+        <v>3.4639111448961493E-2</v>
       </c>
       <c r="C26">
-        <v>-1.1465299372097413E-4</v>
+        <v>-9.4010203455339439E-5</v>
       </c>
       <c r="D26">
-        <v>-1.8912723054915342E-4</v>
+        <v>-1.9992115601267027E-4</v>
       </c>
       <c r="E26">
-        <v>1.5041350888907754E-6</v>
+        <v>1.5883295104024019E-6</v>
       </c>
       <c r="F26">
-        <v>1.1294832131742948E-4</v>
+        <v>1.0687766741390532E-4</v>
       </c>
       <c r="G26">
-        <v>1.9221012261777667E-4</v>
+        <v>2.0430125309287705E-4</v>
       </c>
       <c r="H26">
-        <v>-8.5017929747139469E-7</v>
+        <v>-1.0236924644404231E-7</v>
       </c>
       <c r="I26">
-        <v>-5.1620181532873745E-6</v>
+        <v>-4.1296004189726656E-6</v>
       </c>
       <c r="J26">
-        <v>1.043338556022083E-4</v>
+        <v>7.9162375088037045E-5</v>
       </c>
       <c r="K26">
-        <v>-2.6394766076543244E-5</v>
+        <v>-5.2996055533708307E-5</v>
       </c>
       <c r="L26">
-        <v>-2.6459056302386742E-5</v>
+        <v>-2.1949874487003918E-5</v>
       </c>
       <c r="M26">
-        <v>6.5871605897387418E-5</v>
+        <v>-2.7410074746720759E-5</v>
       </c>
       <c r="N26">
-        <v>-5.1074586637544836E-5</v>
+        <v>-1.0104534219602213E-6</v>
       </c>
       <c r="O26">
-        <v>4.3892556046235096E-4</v>
+        <v>4.3023946775139123E-4</v>
       </c>
       <c r="P26">
-        <v>3.7735599968097104E-4</v>
+        <v>3.616053711458548E-4</v>
       </c>
       <c r="Q26">
-        <v>6.2852340696331458E-4</v>
+        <v>6.1653112208986428E-4</v>
       </c>
       <c r="R26">
-        <v>6.9878651390394247E-4</v>
+        <v>6.564208731300895E-4</v>
       </c>
       <c r="S26">
-        <v>-2.1041955767897406E-6</v>
+        <v>1.2108088385298687E-5</v>
       </c>
       <c r="T26">
-        <v>2.846025136125304E-3</v>
+        <v>2.7848044772073102E-3</v>
       </c>
       <c r="U26">
-        <v>2.7859573954441023E-3</v>
+        <v>2.7328032640307831E-3</v>
       </c>
       <c r="V26">
-        <v>2.7747657040364283E-3</v>
+        <v>2.7199572925010462E-3</v>
       </c>
       <c r="W26">
-        <v>3.0064056373992911E-3</v>
+        <v>3.0068009543869991E-3</v>
       </c>
       <c r="X26">
-        <v>2.7648943525472379E-3</v>
+        <v>2.7059115848437855E-3</v>
       </c>
       <c r="Y26">
-        <v>2.7857176050128515E-3</v>
+        <v>2.727148591122215E-3</v>
       </c>
       <c r="Z26">
-        <v>2.7929208269317852E-3</v>
+        <v>2.7412329994251205E-3</v>
       </c>
       <c r="AA26">
-        <v>3.9482010350014324E-3</v>
+        <v>3.8574735589652449E-3</v>
       </c>
       <c r="AB26">
-        <v>2.816808475703926E-3</v>
+        <v>2.762035801446198E-3</v>
       </c>
       <c r="AC26">
-        <v>2.8359012085754191E-3</v>
+        <v>2.7824796079092525E-3</v>
       </c>
       <c r="AD26">
-        <v>2.8848816565021826E-3</v>
+        <v>2.8315678807272317E-3</v>
       </c>
       <c r="AE26">
-        <v>-1.8601810035982552E-5</v>
+        <v>-1.6288210963045282E-5</v>
       </c>
       <c r="AF26">
-        <v>8.2464297104937171E-5</v>
+        <v>8.0403432130701308E-5</v>
       </c>
       <c r="AG26">
-        <v>1.7390098762402602E-5</v>
+        <v>3.0424153855295168E-6</v>
       </c>
       <c r="AH26">
-        <v>1.7083354203336785E-3</v>
+        <v>1.8586007823908103E-3</v>
       </c>
       <c r="AI26">
-        <v>1.3576144451007115E-3</v>
+        <v>1.3298250878426118E-3</v>
       </c>
       <c r="AJ26">
-        <v>-1.1012311935863675E-4</v>
+        <v>-4.2154322502118498E-4</v>
       </c>
       <c r="AK26">
-        <v>3.0569586077554742E-3</v>
+        <v>3.3779722801262606E-3</v>
       </c>
     </row>
     <row r="27" spans="1:37" x14ac:dyDescent="0.2">
@@ -7163,112 +7163,112 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>8.8159124607529352E-2</v>
+        <v>0.10889306181614702</v>
       </c>
       <c r="C27">
-        <v>-1.1066562368145969E-4</v>
+        <v>-9.6382845607393352E-5</v>
       </c>
       <c r="D27">
-        <v>-1.8131248668446648E-4</v>
+        <v>-1.8623613112133189E-4</v>
       </c>
       <c r="E27">
-        <v>1.4698149367860583E-6</v>
+        <v>1.511761188948183E-6</v>
       </c>
       <c r="F27">
-        <v>1.0792754621088112E-4</v>
+        <v>1.1421101200235397E-4</v>
       </c>
       <c r="G27">
-        <v>1.3053671005980333E-4</v>
+        <v>1.4717987433800959E-4</v>
       </c>
       <c r="H27">
-        <v>-4.086838399922283E-7</v>
+        <v>5.1057908645391265E-7</v>
       </c>
       <c r="I27">
-        <v>-1.2000576641078251E-6</v>
+        <v>-5.0497791333825928E-7</v>
       </c>
       <c r="J27">
-        <v>1.0777022002765048E-4</v>
+        <v>7.1998910980921108E-5</v>
       </c>
       <c r="K27">
-        <v>-5.6129326901471419E-5</v>
+        <v>-5.3181423414917078E-5</v>
       </c>
       <c r="L27">
-        <v>8.3289354075553879E-6</v>
+        <v>-1.0838422014373093E-5</v>
       </c>
       <c r="M27">
-        <v>7.1224902489720266E-5</v>
+        <v>-5.0006482550280559E-5</v>
       </c>
       <c r="N27">
-        <v>-4.2406182428843557E-5</v>
+        <v>1.365323600859495E-5</v>
       </c>
       <c r="O27">
-        <v>4.7369731707011748E-4</v>
+        <v>4.4896253075790509E-4</v>
       </c>
       <c r="P27">
-        <v>3.8539126972713268E-4</v>
+        <v>3.5020088728453551E-4</v>
       </c>
       <c r="Q27">
-        <v>6.6662198554022327E-4</v>
+        <v>6.2660810575814255E-4</v>
       </c>
       <c r="R27">
-        <v>7.4925589215152789E-4</v>
+        <v>6.7601479428946011E-4</v>
       </c>
       <c r="S27">
-        <v>5.0725580636866874E-5</v>
+        <v>6.0993607536711765E-5</v>
       </c>
       <c r="T27">
-        <v>2.8629717029838185E-3</v>
+        <v>2.8047961638477188E-3</v>
       </c>
       <c r="U27">
-        <v>2.7886145144306951E-3</v>
+        <v>2.7371516872061403E-3</v>
       </c>
       <c r="V27">
-        <v>2.7789325555003896E-3</v>
+        <v>2.7249929667691806E-3</v>
       </c>
       <c r="W27">
-        <v>2.9812422227236679E-3</v>
+        <v>2.9863282608865926E-3</v>
       </c>
       <c r="X27">
-        <v>2.781093112469451E-3</v>
+        <v>2.7215959571901152E-3</v>
       </c>
       <c r="Y27">
-        <v>2.7807591050313385E-3</v>
+        <v>2.7238152395789193E-3</v>
       </c>
       <c r="Z27">
-        <v>2.785290199358928E-3</v>
+        <v>2.7345891497149652E-3</v>
       </c>
       <c r="AA27">
-        <v>2.816808475703926E-3</v>
+        <v>2.762035801446198E-3</v>
       </c>
       <c r="AB27">
-        <v>4.3962613010409875E-3</v>
+        <v>4.3366442718877005E-3</v>
       </c>
       <c r="AC27">
-        <v>2.8387347726823091E-3</v>
+        <v>2.7878999533756171E-3</v>
       </c>
       <c r="AD27">
-        <v>2.8900102883720651E-3</v>
+        <v>2.8406215367596929E-3</v>
       </c>
       <c r="AE27">
-        <v>-1.7999803686327587E-5</v>
+        <v>-1.4906827471086249E-5</v>
       </c>
       <c r="AF27">
-        <v>5.2839678723094105E-5</v>
+        <v>3.6918951485569155E-5</v>
       </c>
       <c r="AG27">
-        <v>-2.258727941452577E-5</v>
+        <v>-3.998532955152068E-5</v>
       </c>
       <c r="AH27">
-        <v>1.6285340317362929E-3</v>
+        <v>1.7933361855781045E-3</v>
       </c>
       <c r="AI27">
-        <v>1.3367675731569286E-3</v>
+        <v>1.3135055966825282E-3</v>
       </c>
       <c r="AJ27">
-        <v>-2.1879756912024172E-5</v>
+        <v>-3.0686520046077154E-4</v>
       </c>
       <c r="AK27">
-        <v>2.4457954293697526E-3</v>
+        <v>2.6001290062031843E-3</v>
       </c>
     </row>
     <row r="28" spans="1:37" x14ac:dyDescent="0.2">
@@ -7276,112 +7276,112 @@
         <v>36</v>
       </c>
       <c r="B28">
-        <v>5.3906552786215034E-2</v>
+        <v>7.459638680723038E-2</v>
       </c>
       <c r="C28">
-        <v>-1.4831856284484206E-4</v>
+        <v>-1.2588986616100871E-4</v>
       </c>
       <c r="D28">
-        <v>-1.8388804953683655E-4</v>
+        <v>-1.9608417332638711E-4</v>
       </c>
       <c r="E28">
-        <v>1.4784060070943878E-6</v>
+        <v>1.5654625753571717E-6</v>
       </c>
       <c r="F28">
-        <v>1.0440087796424771E-4</v>
+        <v>8.772871460425649E-5</v>
       </c>
       <c r="G28">
-        <v>1.7824970065623871E-4</v>
+        <v>1.8175104947745351E-4</v>
       </c>
       <c r="H28">
-        <v>-8.617180017449097E-7</v>
+        <v>-3.9255432288917745E-7</v>
       </c>
       <c r="I28">
-        <v>-3.3450630693664571E-6</v>
+        <v>-2.8368143759664543E-6</v>
       </c>
       <c r="J28">
-        <v>1.2287408525134128E-4</v>
+        <v>1.0322587521874272E-4</v>
       </c>
       <c r="K28">
-        <v>-3.9809157249165103E-5</v>
+        <v>-4.5213304343750399E-5</v>
       </c>
       <c r="L28">
-        <v>-6.0247860903062198E-5</v>
+        <v>-7.0924759601178385E-5</v>
       </c>
       <c r="M28">
-        <v>5.4705081980232741E-5</v>
+        <v>-5.5048856433448172E-5</v>
       </c>
       <c r="N28">
-        <v>7.0699603840609969E-6</v>
+        <v>5.7969846389339827E-5</v>
       </c>
       <c r="O28">
-        <v>5.0881804907443036E-4</v>
+        <v>4.8311215650485568E-4</v>
       </c>
       <c r="P28">
-        <v>3.9466224684815308E-4</v>
+        <v>3.5895540101782853E-4</v>
       </c>
       <c r="Q28">
-        <v>6.6687806717807981E-4</v>
+        <v>6.3503010871683412E-4</v>
       </c>
       <c r="R28">
-        <v>7.8666457975058333E-4</v>
+        <v>7.0786014715517546E-4</v>
       </c>
       <c r="S28">
-        <v>-1.4272463930039745E-5</v>
+        <v>-5.2895951805966577E-6</v>
       </c>
       <c r="T28">
-        <v>2.8914073089686253E-3</v>
+        <v>2.8309743396028935E-3</v>
       </c>
       <c r="U28">
-        <v>2.8022847674327176E-3</v>
+        <v>2.7514902527995362E-3</v>
       </c>
       <c r="V28">
-        <v>2.7989518739522114E-3</v>
+        <v>2.7462350162442925E-3</v>
       </c>
       <c r="W28">
-        <v>3.0055928177607494E-3</v>
+        <v>3.0187540877594007E-3</v>
       </c>
       <c r="X28">
-        <v>2.7880368855622796E-3</v>
+        <v>2.7289999346365155E-3</v>
       </c>
       <c r="Y28">
-        <v>2.7941165549943072E-3</v>
+        <v>2.7394105067973622E-3</v>
       </c>
       <c r="Z28">
-        <v>2.7980841409786664E-3</v>
+        <v>2.7511952589872146E-3</v>
       </c>
       <c r="AA28">
-        <v>2.8359012085754191E-3</v>
+        <v>2.7824796079092525E-3</v>
       </c>
       <c r="AB28">
-        <v>2.8387347726823091E-3</v>
+        <v>2.7878999533756171E-3</v>
       </c>
       <c r="AC28">
-        <v>4.0932705986364134E-3</v>
+        <v>4.0088967982356482E-3</v>
       </c>
       <c r="AD28">
-        <v>2.9158802769515477E-3</v>
+        <v>2.8666106064310715E-3</v>
       </c>
       <c r="AE28">
-        <v>-2.2531550582725277E-5</v>
+        <v>-2.0111429432628032E-5</v>
       </c>
       <c r="AF28">
-        <v>1.9491106165183376E-4</v>
+        <v>1.5703377568652109E-4</v>
       </c>
       <c r="AG28">
-        <v>3.8813424469368003E-5</v>
+        <v>5.8434103244289857E-5</v>
       </c>
       <c r="AH28">
-        <v>1.6676095041176864E-3</v>
+        <v>1.8474941709717477E-3</v>
       </c>
       <c r="AI28">
-        <v>1.3731086731114403E-3</v>
+        <v>1.3456260899932205E-3</v>
       </c>
       <c r="AJ28">
-        <v>-4.0563016184415269E-5</v>
+        <v>-3.0873729277021607E-4</v>
       </c>
       <c r="AK28">
-        <v>2.7388379504331289E-3</v>
+        <v>3.2066914787324966E-3</v>
       </c>
     </row>
     <row r="29" spans="1:37" x14ac:dyDescent="0.2">
@@ -7389,112 +7389,112 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>6.128731425600694E-2</v>
+        <v>8.8612756263639472E-2</v>
       </c>
       <c r="C29">
-        <v>-1.609703824956303E-4</v>
+        <v>-1.3739928202127533E-4</v>
       </c>
       <c r="D29">
-        <v>-1.5111368442356082E-4</v>
+        <v>-1.6168602529209597E-4</v>
       </c>
       <c r="E29">
-        <v>1.236554652979849E-6</v>
+        <v>1.3195225956968114E-6</v>
       </c>
       <c r="F29">
-        <v>8.7995598908211355E-5</v>
+        <v>9.0027008713736666E-5</v>
       </c>
       <c r="G29">
-        <v>9.8234134385062318E-5</v>
+        <v>1.1650644190839058E-4</v>
       </c>
       <c r="H29">
-        <v>-1.681739772896383E-6</v>
+        <v>-7.1783446234100954E-7</v>
       </c>
       <c r="I29">
-        <v>-5.4723714933859168E-6</v>
+        <v>-4.6318538766678758E-6</v>
       </c>
       <c r="J29">
-        <v>9.491423626743138E-5</v>
+        <v>7.0064325990980411E-5</v>
       </c>
       <c r="K29">
-        <v>-2.4101862783543551E-4</v>
+        <v>-2.3479083116685791E-4</v>
       </c>
       <c r="L29">
-        <v>4.7693767975935143E-5</v>
+        <v>2.3345825883063463E-5</v>
       </c>
       <c r="M29">
-        <v>1.5304337996143445E-5</v>
+        <v>-9.3872856654440579E-5</v>
       </c>
       <c r="N29">
-        <v>5.3099876972129817E-5</v>
+        <v>9.7416967805587614E-5</v>
       </c>
       <c r="O29">
-        <v>6.3552267416706843E-4</v>
+        <v>6.2002306705657723E-4</v>
       </c>
       <c r="P29">
-        <v>5.6294639400246383E-4</v>
+        <v>5.2991526319304304E-4</v>
       </c>
       <c r="Q29">
-        <v>8.6476466028424662E-4</v>
+        <v>8.3047054677832903E-4</v>
       </c>
       <c r="R29">
-        <v>9.7180379293169885E-4</v>
+        <v>8.9567495960767669E-4</v>
       </c>
       <c r="S29">
-        <v>-5.2833794686084042E-5</v>
+        <v>-3.2155969603644193E-5</v>
       </c>
       <c r="T29">
-        <v>2.9419299605024018E-3</v>
+        <v>2.8836386585876501E-3</v>
       </c>
       <c r="U29">
-        <v>2.8549314782281244E-3</v>
+        <v>2.8053500145827589E-3</v>
       </c>
       <c r="V29">
-        <v>2.8570117779306626E-3</v>
+        <v>2.805700375583526E-3</v>
       </c>
       <c r="W29">
-        <v>3.0568279746538201E-3</v>
+        <v>3.0756419236610765E-3</v>
       </c>
       <c r="X29">
-        <v>2.8430523114158423E-3</v>
+        <v>2.7836145533383437E-3</v>
       </c>
       <c r="Y29">
-        <v>2.8525259231793024E-3</v>
+        <v>2.7972833304172181E-3</v>
       </c>
       <c r="Z29">
-        <v>2.8416782937837459E-3</v>
+        <v>2.7964598044259853E-3</v>
       </c>
       <c r="AA29">
-        <v>2.8848816565021826E-3</v>
+        <v>2.8315678807272317E-3</v>
       </c>
       <c r="AB29">
-        <v>2.8900102883720651E-3</v>
+        <v>2.8406215367596929E-3</v>
       </c>
       <c r="AC29">
-        <v>2.9158802769515477E-3</v>
+        <v>2.8666106064310715E-3</v>
       </c>
       <c r="AD29">
-        <v>5.2386147417131041E-3</v>
+        <v>5.0644964740382045E-3</v>
       </c>
       <c r="AE29">
-        <v>-2.4093123203820682E-5</v>
+        <v>-2.112686108084534E-5</v>
       </c>
       <c r="AF29">
-        <v>1.3160905223136537E-5</v>
+        <v>8.8019531097173562E-6</v>
       </c>
       <c r="AG29">
-        <v>5.72951624399199E-5</v>
+        <v>3.245364624230401E-5</v>
       </c>
       <c r="AH29">
-        <v>1.778605172571706E-3</v>
+        <v>1.9820978936956938E-3</v>
       </c>
       <c r="AI29">
-        <v>1.3851330460748065E-3</v>
+        <v>1.3658961135486565E-3</v>
       </c>
       <c r="AJ29">
-        <v>-4.0545412071304988E-5</v>
+        <v>-3.1591231395698563E-4</v>
       </c>
       <c r="AK29">
-        <v>1.6462334489793337E-3</v>
+        <v>1.9665829481506263E-3</v>
       </c>
     </row>
     <row r="30" spans="1:37" x14ac:dyDescent="0.2">
@@ -7502,112 +7502,112 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>-1.8928483153270554E-3</v>
+        <v>-1.3085518649888521E-3</v>
       </c>
       <c r="C30">
-        <v>1.0655861110370738E-5</v>
+        <v>1.0008730318499459E-5</v>
       </c>
       <c r="D30">
-        <v>1.1871135048770881E-6</v>
+        <v>1.5246196051043465E-7</v>
       </c>
       <c r="E30">
-        <v>-4.2238712472434346E-8</v>
+        <v>-3.3326178073087985E-8</v>
       </c>
       <c r="F30">
-        <v>-3.3718059539217433E-6</v>
+        <v>-2.3413431322887977E-6</v>
       </c>
       <c r="G30">
-        <v>1.0832750904601662E-5</v>
+        <v>1.3837225192972278E-5</v>
       </c>
       <c r="H30">
-        <v>4.5961633301372582E-7</v>
+        <v>5.728321888608592E-7</v>
       </c>
       <c r="I30">
-        <v>8.6635860411326022E-7</v>
+        <v>9.1031253138933639E-7</v>
       </c>
       <c r="J30">
-        <v>3.4442340028185004E-5</v>
+        <v>3.2891121345850883E-5</v>
       </c>
       <c r="K30">
-        <v>5.1299779366311814E-6</v>
+        <v>9.3425388733360017E-6</v>
       </c>
       <c r="L30">
-        <v>7.9365520947956075E-6</v>
+        <v>2.8974331368229267E-6</v>
       </c>
       <c r="M30">
-        <v>3.62994500967456E-6</v>
+        <v>-7.9532753529085547E-6</v>
       </c>
       <c r="N30">
-        <v>9.9894871184291119E-6</v>
+        <v>1.3311953359105044E-5</v>
       </c>
       <c r="O30">
-        <v>-1.2807847623821434E-5</v>
+        <v>-1.5945101422037229E-5</v>
       </c>
       <c r="P30">
-        <v>-3.3358311870261429E-6</v>
+        <v>-8.7419108588623375E-6</v>
       </c>
       <c r="Q30">
-        <v>-4.0327157283170044E-6</v>
+        <v>-7.9180035156913063E-6</v>
       </c>
       <c r="R30">
-        <v>-1.0336742084194987E-5</v>
+        <v>-1.7348121850435921E-5</v>
       </c>
       <c r="S30">
-        <v>-1.3659313498668281E-6</v>
+        <v>2.8770135869575069E-6</v>
       </c>
       <c r="T30">
-        <v>-2.4588219424363284E-5</v>
+        <v>-2.245084751036842E-5</v>
       </c>
       <c r="U30">
-        <v>-2.1867524591059841E-5</v>
+        <v>-1.9003680997826727E-5</v>
       </c>
       <c r="V30">
-        <v>-1.5631923637349899E-5</v>
+        <v>-1.429618660964561E-5</v>
       </c>
       <c r="W30">
-        <v>2.9821535887171089E-6</v>
+        <v>1.1713933768479478E-5</v>
       </c>
       <c r="X30">
-        <v>-2.674417115406803E-5</v>
+        <v>-2.5516630864483928E-5</v>
       </c>
       <c r="Y30">
-        <v>-1.3788855900143983E-5</v>
+        <v>-1.3158010222385043E-5</v>
       </c>
       <c r="Z30">
-        <v>-1.5958071844769363E-5</v>
+        <v>-1.4621723294185783E-5</v>
       </c>
       <c r="AA30">
-        <v>-1.8601810035982552E-5</v>
+        <v>-1.6288210963045282E-5</v>
       </c>
       <c r="AB30">
-        <v>-1.7999803686327587E-5</v>
+        <v>-1.4906827471086249E-5</v>
       </c>
       <c r="AC30">
-        <v>-2.2531550582725277E-5</v>
+        <v>-2.0111429432628032E-5</v>
       </c>
       <c r="AD30">
-        <v>-2.4093123203820682E-5</v>
+        <v>-2.112686108084534E-5</v>
       </c>
       <c r="AE30">
-        <v>1.3077601145817113E-5</v>
+        <v>1.311602407583777E-5</v>
       </c>
       <c r="AF30">
-        <v>-4.8116225927232134E-5</v>
+        <v>-4.8564913572071201E-5</v>
       </c>
       <c r="AG30">
-        <v>-6.1335081816123464E-5</v>
+        <v>-6.1161297120438949E-5</v>
       </c>
       <c r="AH30">
-        <v>5.1580046343860611E-5</v>
+        <v>7.5510699204536487E-5</v>
       </c>
       <c r="AI30">
-        <v>-3.7790753466806365E-5</v>
+        <v>-3.8646068379103522E-5</v>
       </c>
       <c r="AJ30">
-        <v>2.6090013485434248E-5</v>
+        <v>4.2266621170038561E-5</v>
       </c>
       <c r="AK30">
-        <v>-1.895744988866107E-4</v>
+        <v>-1.6144761437702311E-4</v>
       </c>
     </row>
     <row r="31" spans="1:37" x14ac:dyDescent="0.2">
@@ -7615,112 +7615,112 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>-5.8224731730995072E-2</v>
+        <v>-5.1774882868026582E-2</v>
       </c>
       <c r="C31">
-        <v>-2.790350858174995E-5</v>
+        <v>-2.0644422778944423E-5</v>
       </c>
       <c r="D31">
-        <v>2.3928309300673065E-6</v>
+        <v>2.0716468091265018E-5</v>
       </c>
       <c r="E31">
-        <v>3.9630903982493406E-8</v>
+        <v>-1.0870632736586497E-7</v>
       </c>
       <c r="F31">
-        <v>7.0619400835429311E-5</v>
+        <v>6.3472178592082195E-5</v>
       </c>
       <c r="G31">
-        <v>6.2050163587419534E-5</v>
+        <v>5.0237718827327008E-5</v>
       </c>
       <c r="H31">
-        <v>-1.9807745785110434E-7</v>
+        <v>-8.3443453407580788E-7</v>
       </c>
       <c r="I31">
-        <v>-6.0544934073119526E-8</v>
+        <v>-4.9583490595744228E-7</v>
       </c>
       <c r="J31">
-        <v>-6.3836646752876518E-6</v>
+        <v>-8.1066462823112706E-7</v>
       </c>
       <c r="K31">
-        <v>2.1554091317274073E-6</v>
+        <v>-1.1688850206849734E-5</v>
       </c>
       <c r="L31">
-        <v>-1.9814880131643941E-5</v>
+        <v>1.0495903727462236E-5</v>
       </c>
       <c r="M31">
-        <v>-5.5042079319060915E-5</v>
+        <v>3.8729997029774159E-5</v>
       </c>
       <c r="N31">
-        <v>-6.4879262942067981E-6</v>
+        <v>-3.6862007149667896E-5</v>
       </c>
       <c r="O31">
-        <v>-9.7762280146985596E-5</v>
+        <v>-6.0761903032912712E-5</v>
       </c>
       <c r="P31">
-        <v>-1.366271549274088E-4</v>
+        <v>-7.668415310707903E-5</v>
       </c>
       <c r="Q31">
-        <v>-1.152901468668294E-4</v>
+        <v>-5.038796619940319E-5</v>
       </c>
       <c r="R31">
-        <v>-4.3262053502564324E-5</v>
+        <v>3.205705732235904E-5</v>
       </c>
       <c r="S31">
-        <v>4.9756773546746016E-5</v>
+        <v>3.1491794593027281E-5</v>
       </c>
       <c r="T31">
-        <v>1.981876578103722E-5</v>
+        <v>1.2064556184856687E-5</v>
       </c>
       <c r="U31">
-        <v>4.7089582603104536E-5</v>
+        <v>3.400064713707441E-5</v>
       </c>
       <c r="V31">
-        <v>9.9420780422664081E-5</v>
+        <v>9.4577350601097456E-5</v>
       </c>
       <c r="W31">
-        <v>-3.4699631699067798E-5</v>
+        <v>-5.3244011822030422E-5</v>
       </c>
       <c r="X31">
-        <v>1.3502734843439296E-4</v>
+        <v>1.5623610031467993E-4</v>
       </c>
       <c r="Y31">
-        <v>4.6667512741768524E-5</v>
+        <v>4.5546531140810411E-5</v>
       </c>
       <c r="Z31">
-        <v>3.771894953198259E-5</v>
+        <v>4.2372538600183435E-5</v>
       </c>
       <c r="AA31">
-        <v>8.2464297104937171E-5</v>
+        <v>8.0403432130701308E-5</v>
       </c>
       <c r="AB31">
-        <v>5.2839678723094105E-5</v>
+        <v>3.6918951485569155E-5</v>
       </c>
       <c r="AC31">
-        <v>1.9491106165183376E-4</v>
+        <v>1.5703377568652109E-4</v>
       </c>
       <c r="AD31">
-        <v>1.3160905223136537E-5</v>
+        <v>8.8019531097173562E-6</v>
       </c>
       <c r="AE31">
-        <v>-4.8116225927232134E-5</v>
+        <v>-4.8564913572071201E-5</v>
       </c>
       <c r="AF31">
-        <v>2.1466995036416052E-3</v>
+        <v>2.0778216676470384E-3</v>
       </c>
       <c r="AG31">
-        <v>3.671864522928486E-4</v>
+        <v>3.6531770436262848E-4</v>
       </c>
       <c r="AH31">
-        <v>-2.2482620839237976E-4</v>
+        <v>-3.0088333559501244E-4</v>
       </c>
       <c r="AI31">
-        <v>7.1241192622241119E-5</v>
+        <v>8.5617278214747129E-5</v>
       </c>
       <c r="AJ31">
-        <v>-1.4033139077025943E-4</v>
+        <v>-2.0823833189785636E-4</v>
       </c>
       <c r="AK31">
-        <v>3.8380024766797527E-4</v>
+        <v>-2.0974946694206212E-4</v>
       </c>
     </row>
     <row r="32" spans="1:37" x14ac:dyDescent="0.2">
@@ -7728,112 +7728,112 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>5.0127734988602658E-2</v>
+        <v>4.844311464078177E-2</v>
       </c>
       <c r="C32">
-        <v>-3.03932547317998E-5</v>
+        <v>-2.8730728865376366E-5</v>
       </c>
       <c r="D32">
-        <v>8.3596636499339363E-5</v>
+        <v>8.0875074290668453E-5</v>
       </c>
       <c r="E32">
-        <v>-6.0013566440803967E-7</v>
+        <v>-5.8952704006295982E-7</v>
       </c>
       <c r="F32">
-        <v>3.2194093384762973E-5</v>
+        <v>2.3842657832721293E-5</v>
       </c>
       <c r="G32">
-        <v>-3.0025151282731721E-5</v>
+        <v>-4.1980072964322587E-5</v>
       </c>
       <c r="H32">
-        <v>-7.4218462676764583E-7</v>
+        <v>-1.4145760398459902E-6</v>
       </c>
       <c r="I32">
-        <v>-5.5364655702988702E-7</v>
+        <v>-6.4525897580194404E-7</v>
       </c>
       <c r="J32">
-        <v>-4.731433493148294E-5</v>
+        <v>-2.9945070001293809E-5</v>
       </c>
       <c r="K32">
-        <v>1.2060495454712457E-4</v>
+        <v>8.8535083284796532E-5</v>
       </c>
       <c r="L32">
-        <v>-4.6723274659226982E-5</v>
+        <v>-2.0504214208845071E-5</v>
       </c>
       <c r="M32">
-        <v>-7.9372285403567639E-5</v>
+        <v>-2.5384919889256347E-5</v>
       </c>
       <c r="N32">
-        <v>1.0022965829816121E-5</v>
+        <v>3.0437820501347844E-6</v>
       </c>
       <c r="O32">
-        <v>8.9681582280645884E-7</v>
+        <v>1.8420808879070878E-5</v>
       </c>
       <c r="P32">
-        <v>-8.3912234266735085E-5</v>
+        <v>-5.2937924844451346E-5</v>
       </c>
       <c r="Q32">
-        <v>-7.7369112444771387E-5</v>
+        <v>-3.7028976092199918E-5</v>
       </c>
       <c r="R32">
-        <v>-5.6985776334853185E-5</v>
+        <v>-2.917581279860711E-6</v>
       </c>
       <c r="S32">
-        <v>4.3797475804492398E-5</v>
+        <v>3.3365200170013794E-5</v>
       </c>
       <c r="T32">
-        <v>1.806562385231628E-4</v>
+        <v>1.5435793053792966E-4</v>
       </c>
       <c r="U32">
-        <v>1.1639780296327716E-5</v>
+        <v>-3.2090818919509325E-6</v>
       </c>
       <c r="V32">
-        <v>-2.2369923079074416E-5</v>
+        <v>-1.0319328790364666E-5</v>
       </c>
       <c r="W32">
-        <v>-1.1923536252575763E-4</v>
+        <v>-1.6072293212113047E-4</v>
       </c>
       <c r="X32">
-        <v>1.5294533671644166E-4</v>
+        <v>1.2613247924652334E-4</v>
       </c>
       <c r="Y32">
-        <v>-5.115806391101335E-6</v>
+        <v>-8.9432622037777454E-6</v>
       </c>
       <c r="Z32">
-        <v>-7.4038107101304128E-6</v>
+        <v>-1.3139504685883278E-5</v>
       </c>
       <c r="AA32">
-        <v>1.7390098762402602E-5</v>
+        <v>3.0424153855295168E-6</v>
       </c>
       <c r="AB32">
-        <v>-2.258727941452577E-5</v>
+        <v>-3.998532955152068E-5</v>
       </c>
       <c r="AC32">
-        <v>3.8813424469368003E-5</v>
+        <v>5.8434103244289857E-5</v>
       </c>
       <c r="AD32">
-        <v>5.72951624399199E-5</v>
+        <v>3.245364624230401E-5</v>
       </c>
       <c r="AE32">
-        <v>-6.1335081816123464E-5</v>
+        <v>-6.1161297120438949E-5</v>
       </c>
       <c r="AF32">
-        <v>3.671864522928486E-4</v>
+        <v>3.6531770436262848E-4</v>
       </c>
       <c r="AG32">
-        <v>2.348908076431368E-3</v>
+        <v>2.3018400849301734E-3</v>
       </c>
       <c r="AH32">
-        <v>-2.5151894365529502E-4</v>
+        <v>-3.4879645197312739E-4</v>
       </c>
       <c r="AI32">
-        <v>8.4846268631227147E-5</v>
+        <v>1.0450988440113081E-4</v>
       </c>
       <c r="AJ32">
-        <v>-2.9505486877774018E-4</v>
+        <v>-3.8493646470813233E-4</v>
       </c>
       <c r="AK32">
-        <v>-1.8259115028702497E-3</v>
+        <v>-1.7220976501903401E-3</v>
       </c>
     </row>
     <row r="33" spans="1:37" x14ac:dyDescent="0.2">
@@ -7841,112 +7841,112 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>-0.12886479127195932</v>
+        <v>-0.10596499063722963</v>
       </c>
       <c r="C33">
-        <v>-1.5622324587662883E-4</v>
+        <v>-1.394900418480279E-4</v>
       </c>
       <c r="D33">
-        <v>-6.6209498048584031E-4</v>
+        <v>-8.0981932894618955E-4</v>
       </c>
       <c r="E33">
-        <v>4.9187769426147052E-6</v>
+        <v>6.0325555803057186E-6</v>
       </c>
       <c r="F33">
-        <v>4.6365365075414378E-4</v>
+        <v>4.6702938611525196E-4</v>
       </c>
       <c r="G33">
-        <v>9.3787914242145264E-4</v>
+        <v>1.0449098498480887E-3</v>
       </c>
       <c r="H33">
-        <v>1.1946016358840454E-5</v>
+        <v>1.6830492548681271E-5</v>
       </c>
       <c r="I33">
-        <v>1.3163100871880702E-5</v>
+        <v>1.9816179429924181E-5</v>
       </c>
       <c r="J33">
-        <v>2.3386879021880947E-4</v>
+        <v>2.2806202404377935E-4</v>
       </c>
       <c r="K33">
-        <v>1.0773482138722815E-4</v>
+        <v>1.6249536345622206E-4</v>
       </c>
       <c r="L33">
-        <v>-2.872320429850991E-4</v>
+        <v>-4.6550791893365442E-4</v>
       </c>
       <c r="M33">
-        <v>4.8615278624124919E-4</v>
+        <v>-3.2319979013348721E-4</v>
       </c>
       <c r="N33">
-        <v>-1.3215083105059337E-4</v>
+        <v>1.710820018068597E-4</v>
       </c>
       <c r="O33">
-        <v>8.6332339376490918E-4</v>
+        <v>7.0807347997160026E-4</v>
       </c>
       <c r="P33">
-        <v>1.210952013005955E-3</v>
+        <v>9.0745782597323292E-4</v>
       </c>
       <c r="Q33">
-        <v>2.0960225345401907E-3</v>
+        <v>1.8389634217473457E-3</v>
       </c>
       <c r="R33">
-        <v>1.6252484531499587E-3</v>
+        <v>1.1268594425125921E-3</v>
       </c>
       <c r="S33">
-        <v>6.4085984605168392E-4</v>
+        <v>7.592819735681239E-4</v>
       </c>
       <c r="T33">
-        <v>1.6412509049184532E-3</v>
+        <v>1.7783642705371419E-3</v>
       </c>
       <c r="U33">
-        <v>1.4586428930581043E-3</v>
+        <v>1.619070318045113E-3</v>
       </c>
       <c r="V33">
-        <v>1.2818731015259506E-3</v>
+        <v>1.4090593624099792E-3</v>
       </c>
       <c r="W33">
-        <v>3.2083286898510746E-3</v>
+        <v>3.8037232856959501E-3</v>
       </c>
       <c r="X33">
-        <v>1.2278448892159518E-3</v>
+        <v>1.3477736410026748E-3</v>
       </c>
       <c r="Y33">
-        <v>1.4975389422720922E-3</v>
+        <v>1.613880737985031E-3</v>
       </c>
       <c r="Z33">
-        <v>1.5559368776512669E-3</v>
+        <v>1.7009958081512925E-3</v>
       </c>
       <c r="AA33">
-        <v>1.7083354203336785E-3</v>
+        <v>1.8586007823908103E-3</v>
       </c>
       <c r="AB33">
-        <v>1.6285340317362929E-3</v>
+        <v>1.7933361855781045E-3</v>
       </c>
       <c r="AC33">
-        <v>1.6676095041176864E-3</v>
+        <v>1.8474941709717477E-3</v>
       </c>
       <c r="AD33">
-        <v>1.778605172571706E-3</v>
+        <v>1.9820978936956938E-3</v>
       </c>
       <c r="AE33">
-        <v>5.1580046343860611E-5</v>
+        <v>7.5510699204536487E-5</v>
       </c>
       <c r="AF33">
-        <v>-2.2482620839237976E-4</v>
+        <v>-3.0088333559501244E-4</v>
       </c>
       <c r="AG33">
-        <v>-2.5151894365529502E-4</v>
+        <v>-3.4879645197312739E-4</v>
       </c>
       <c r="AH33">
-        <v>9.4505935856479938E-3</v>
+        <v>1.0913943582153826E-2</v>
       </c>
       <c r="AI33">
-        <v>9.6094481364437522E-4</v>
+        <v>9.4899547979719829E-4</v>
       </c>
       <c r="AJ33">
-        <v>2.7720415619392788E-4</v>
+        <v>1.629376651450142E-4</v>
       </c>
       <c r="AK33">
-        <v>1.5990240438679228E-2</v>
+        <v>2.0311612994149207E-2</v>
       </c>
     </row>
     <row r="34" spans="1:37" x14ac:dyDescent="0.2">
@@ -7954,112 +7954,112 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>-0.45898917060836303</v>
+        <v>-0.4903350377751115</v>
       </c>
       <c r="C34">
-        <v>-1.0325310381750091E-4</v>
+        <v>-9.7158083913428906E-5</v>
       </c>
       <c r="D34">
-        <v>-2.0311080103175422E-4</v>
+        <v>-2.5595938273887536E-4</v>
       </c>
       <c r="E34">
-        <v>1.6857221606156715E-6</v>
+        <v>2.0888653269183805E-6</v>
       </c>
       <c r="F34">
-        <v>2.6789813048165665E-4</v>
+        <v>2.5363623535887541E-4</v>
       </c>
       <c r="G34">
-        <v>3.2333373684365876E-4</v>
+        <v>3.1137272475631743E-4</v>
       </c>
       <c r="H34">
-        <v>-2.3773646068840399E-6</v>
+        <v>-1.9566637039408524E-6</v>
       </c>
       <c r="I34">
-        <v>-3.1333563733720139E-6</v>
+        <v>-2.9665120197590821E-6</v>
       </c>
       <c r="J34">
-        <v>1.9553274917460169E-5</v>
+        <v>1.635334306059077E-5</v>
       </c>
       <c r="K34">
-        <v>-1.3642704160463266E-4</v>
+        <v>-1.6294053114226936E-4</v>
       </c>
       <c r="L34">
-        <v>-4.6958022544065295E-5</v>
+        <v>-5.0744145823698739E-5</v>
       </c>
       <c r="M34">
-        <v>1.3273266088431731E-4</v>
+        <v>3.6669712060458473E-5</v>
       </c>
       <c r="N34">
-        <v>-7.3468817721465338E-5</v>
+        <v>-3.0838051703088146E-5</v>
       </c>
       <c r="O34">
-        <v>2.1318150158074938E-4</v>
+        <v>1.9915938184299209E-4</v>
       </c>
       <c r="P34">
-        <v>1.671948722658358E-4</v>
+        <v>1.3643123462541784E-4</v>
       </c>
       <c r="Q34">
-        <v>4.0748601460296281E-4</v>
+        <v>3.6133029357266486E-4</v>
       </c>
       <c r="R34">
-        <v>5.3471701326602075E-4</v>
+        <v>4.7176136977543489E-4</v>
       </c>
       <c r="S34">
-        <v>1.9406978048294395E-5</v>
+        <v>3.4497568413986864E-5</v>
       </c>
       <c r="T34">
-        <v>1.3851247432372464E-3</v>
+        <v>1.3513621495204438E-3</v>
       </c>
       <c r="U34">
-        <v>1.2510546866361131E-3</v>
+        <v>1.228152676058014E-3</v>
       </c>
       <c r="V34">
-        <v>1.312234074011494E-3</v>
+        <v>1.2848864285724567E-3</v>
       </c>
       <c r="W34">
-        <v>1.393858786937349E-3</v>
+        <v>1.3599764444285098E-3</v>
       </c>
       <c r="X34">
-        <v>1.0759731157713611E-3</v>
+        <v>1.044295903928415E-3</v>
       </c>
       <c r="Y34">
-        <v>1.3020200421445811E-3</v>
+        <v>1.3138863511488834E-3</v>
       </c>
       <c r="Z34">
-        <v>1.1992774560520233E-3</v>
+        <v>1.1822031526856412E-3</v>
       </c>
       <c r="AA34">
-        <v>1.3576144451007115E-3</v>
+        <v>1.3298250878426118E-3</v>
       </c>
       <c r="AB34">
-        <v>1.3367675731569286E-3</v>
+        <v>1.3135055966825282E-3</v>
       </c>
       <c r="AC34">
-        <v>1.3731086731114403E-3</v>
+        <v>1.3456260899932205E-3</v>
       </c>
       <c r="AD34">
-        <v>1.3851330460748065E-3</v>
+        <v>1.3658961135486565E-3</v>
       </c>
       <c r="AE34">
-        <v>-3.7790753466806365E-5</v>
+        <v>-3.8646068379103522E-5</v>
       </c>
       <c r="AF34">
-        <v>7.1241192622241119E-5</v>
+        <v>8.5617278214747129E-5</v>
       </c>
       <c r="AG34">
-        <v>8.4846268631227147E-5</v>
+        <v>1.0450988440113081E-4</v>
       </c>
       <c r="AH34">
-        <v>9.6094481364437522E-4</v>
+        <v>9.4899547979719829E-4</v>
       </c>
       <c r="AI34">
-        <v>1.4178606251474615E-2</v>
+        <v>1.4368017890557932E-2</v>
       </c>
       <c r="AJ34">
-        <v>1.4299919586889908E-4</v>
+        <v>-4.7396630188442322E-5</v>
       </c>
       <c r="AK34">
-        <v>5.0498872970179305E-3</v>
+        <v>6.8670972802151002E-3</v>
       </c>
     </row>
     <row r="35" spans="1:37" x14ac:dyDescent="0.2">
@@ -8067,112 +8067,112 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-8.0502213117706292E-2</v>
+        <v>-7.9962680918647791E-2</v>
       </c>
       <c r="C35">
-        <v>-8.5595679129652548E-5</v>
+        <v>-9.8535376230442055E-5</v>
       </c>
       <c r="D35">
-        <v>-3.0207635378866685E-5</v>
+        <v>-5.2786647929986552E-5</v>
       </c>
       <c r="E35">
-        <v>1.7207039169161878E-7</v>
+        <v>3.2332482230684571E-7</v>
       </c>
       <c r="F35">
-        <v>4.4006391162126627E-5</v>
+        <v>-7.7695612340520609E-5</v>
       </c>
       <c r="G35">
-        <v>1.1732894645242808E-4</v>
+        <v>1.0392523740486003E-5</v>
       </c>
       <c r="H35">
-        <v>-1.7712939310388445E-6</v>
+        <v>-2.782999312935937E-6</v>
       </c>
       <c r="I35">
-        <v>2.2794908997929949E-6</v>
+        <v>5.0698884553582014E-6</v>
       </c>
       <c r="J35">
-        <v>2.7691835204071637E-6</v>
+        <v>-4.2648525998761422E-5</v>
       </c>
       <c r="K35">
-        <v>1.665610691439271E-4</v>
+        <v>1.8707908949439859E-4</v>
       </c>
       <c r="L35">
-        <v>-3.1737142395660251E-4</v>
+        <v>-4.156203906077161E-4</v>
       </c>
       <c r="M35">
-        <v>3.9275790311003476E-4</v>
+        <v>-1.0743728745995259E-4</v>
       </c>
       <c r="N35">
-        <v>-6.0784182484479872E-5</v>
+        <v>1.6674119423135589E-4</v>
       </c>
       <c r="O35">
-        <v>2.0634659070800003E-4</v>
+        <v>4.9546297821529729E-5</v>
       </c>
       <c r="P35">
-        <v>3.2293461944150198E-4</v>
+        <v>1.0742878139482852E-4</v>
       </c>
       <c r="Q35">
-        <v>3.5848104095381858E-4</v>
+        <v>5.1583026682494766E-5</v>
       </c>
       <c r="R35">
-        <v>5.0847586407035909E-4</v>
+        <v>1.7918969946929949E-4</v>
       </c>
       <c r="S35">
-        <v>2.6581924329379661E-4</v>
+        <v>3.4584755429030418E-4</v>
       </c>
       <c r="T35">
-        <v>4.121615422709486E-5</v>
+        <v>-2.5668139031183052E-4</v>
       </c>
       <c r="U35">
-        <v>-1.5743724308450743E-4</v>
+        <v>-4.3845365037426594E-4</v>
       </c>
       <c r="V35">
-        <v>-8.4276562516360387E-5</v>
+        <v>-4.1656625359183541E-4</v>
       </c>
       <c r="W35">
-        <v>-6.4618926396795847E-5</v>
+        <v>-3.7280377926815489E-4</v>
       </c>
       <c r="X35">
-        <v>-1.9262681582776591E-4</v>
+        <v>-4.9887313714724662E-4</v>
       </c>
       <c r="Y35">
-        <v>-1.4283005487500587E-4</v>
+        <v>-4.4783339022323547E-4</v>
       </c>
       <c r="Z35">
-        <v>-1.4575172547589689E-4</v>
+        <v>-4.3706048332005452E-4</v>
       </c>
       <c r="AA35">
-        <v>-1.1012311935863675E-4</v>
+        <v>-4.2154322502118498E-4</v>
       </c>
       <c r="AB35">
-        <v>-2.1879756912024172E-5</v>
+        <v>-3.0686520046077154E-4</v>
       </c>
       <c r="AC35">
-        <v>-4.0563016184415269E-5</v>
+        <v>-3.0873729277021607E-4</v>
       </c>
       <c r="AD35">
-        <v>-4.0545412071304988E-5</v>
+        <v>-3.1591231395698563E-4</v>
       </c>
       <c r="AE35">
-        <v>2.6090013485434248E-5</v>
+        <v>4.2266621170038561E-5</v>
       </c>
       <c r="AF35">
-        <v>-1.4033139077025943E-4</v>
+        <v>-2.0823833189785636E-4</v>
       </c>
       <c r="AG35">
-        <v>-2.9505486877774018E-4</v>
+        <v>-3.8493646470813233E-4</v>
       </c>
       <c r="AH35">
-        <v>2.7720415619392788E-4</v>
+        <v>1.629376651450142E-4</v>
       </c>
       <c r="AI35">
-        <v>1.4299919586889908E-4</v>
+        <v>-4.7396630188442322E-5</v>
       </c>
       <c r="AJ35">
-        <v>1.6385642209018777E-2</v>
+        <v>1.9688889697587145E-2</v>
       </c>
       <c r="AK35">
-        <v>1.4189189852683803E-4</v>
+        <v>1.4309590135917535E-3</v>
       </c>
     </row>
     <row r="36" spans="1:37" x14ac:dyDescent="0.2">
@@ -8180,112 +8180,112 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-28.737462399995636</v>
+        <v>-28.909087044526036</v>
       </c>
       <c r="C36">
-        <v>-2.6844751168727931E-3</v>
+        <v>-2.8395360787424476E-3</v>
       </c>
       <c r="D36">
-        <v>-4.8120650391440506E-2</v>
+        <v>-4.7956508298531195E-2</v>
       </c>
       <c r="E36">
-        <v>3.8611593638665054E-4</v>
+        <v>3.8533737148229959E-4</v>
       </c>
       <c r="F36">
-        <v>1.8769304441431326E-3</v>
+        <v>2.08987457373785E-3</v>
       </c>
       <c r="G36">
-        <v>5.9743618877521375E-3</v>
+        <v>6.6349645717235072E-3</v>
       </c>
       <c r="H36">
-        <v>-1.363486099422297E-4</v>
+        <v>-1.3384058999697974E-4</v>
       </c>
       <c r="I36">
-        <v>-1.2014489749146459E-4</v>
+        <v>-1.0477500967522881E-4</v>
       </c>
       <c r="J36">
-        <v>-2.7392343950950627E-3</v>
+        <v>-3.4251587740652257E-3</v>
       </c>
       <c r="K36">
-        <v>-1.2096474722976279E-2</v>
+        <v>-1.226844840346631E-2</v>
       </c>
       <c r="L36">
-        <v>-6.9006113307261748E-3</v>
+        <v>-7.0400499304077904E-3</v>
       </c>
       <c r="M36">
-        <v>1.1153355799062741E-3</v>
+        <v>-9.4784755049151536E-4</v>
       </c>
       <c r="N36">
-        <v>-7.829378479813513E-4</v>
+        <v>-1.8773406464490461E-5</v>
       </c>
       <c r="O36">
-        <v>-3.6092604757943696E-3</v>
+        <v>-4.2026570635990742E-3</v>
       </c>
       <c r="P36">
-        <v>-3.7608584647295974E-3</v>
+        <v>-4.7277375057128441E-3</v>
       </c>
       <c r="Q36">
-        <v>-3.3468602507928484E-4</v>
+        <v>-1.2017918212612402E-3</v>
       </c>
       <c r="R36">
-        <v>-1.2729034716397261E-3</v>
+        <v>-2.7931737949935323E-3</v>
       </c>
       <c r="S36">
-        <v>2.0655648568618156E-3</v>
+        <v>2.3502628636551375E-3</v>
       </c>
       <c r="T36">
-        <v>1.5078356791364874E-3</v>
+        <v>1.4383697523435704E-3</v>
       </c>
       <c r="U36">
-        <v>9.2560924361584709E-4</v>
+        <v>9.900843193810082E-4</v>
       </c>
       <c r="V36">
-        <v>8.3210776151225116E-4</v>
+        <v>1.0481234167936272E-3</v>
       </c>
       <c r="W36">
-        <v>7.0299381565938771E-3</v>
+        <v>8.46019379524297E-3</v>
       </c>
       <c r="X36">
-        <v>2.9882895462922023E-3</v>
+        <v>2.8523411712167378E-3</v>
       </c>
       <c r="Y36">
-        <v>4.261426102712941E-3</v>
+        <v>4.3625085018779812E-3</v>
       </c>
       <c r="Z36">
-        <v>2.7782441668772438E-3</v>
+        <v>3.1131612200366605E-3</v>
       </c>
       <c r="AA36">
-        <v>3.0569586077554742E-3</v>
+        <v>3.3779722801262606E-3</v>
       </c>
       <c r="AB36">
-        <v>2.4457954293697526E-3</v>
+        <v>2.6001290062031843E-3</v>
       </c>
       <c r="AC36">
-        <v>2.7388379504331289E-3</v>
+        <v>3.2066914787324966E-3</v>
       </c>
       <c r="AD36">
-        <v>1.6462334489793337E-3</v>
+        <v>1.9665829481506263E-3</v>
       </c>
       <c r="AE36">
-        <v>-1.895744988866107E-4</v>
+        <v>-1.6144761437702311E-4</v>
       </c>
       <c r="AF36">
-        <v>3.8380024766797527E-4</v>
+        <v>-2.0974946694206212E-4</v>
       </c>
       <c r="AG36">
-        <v>-1.8259115028702497E-3</v>
+        <v>-1.7220976501903401E-3</v>
       </c>
       <c r="AH36">
-        <v>1.5990240438679228E-2</v>
+        <v>2.0311612994149207E-2</v>
       </c>
       <c r="AI36">
-        <v>5.0498872970179305E-3</v>
+        <v>6.8670972802151002E-3</v>
       </c>
       <c r="AJ36">
-        <v>1.4189189852683803E-4</v>
+        <v>1.4309590135917535E-3</v>
       </c>
       <c r="AK36">
-        <v>1.5045886239093011</v>
+        <v>1.4976088259489551</v>
       </c>
     </row>
   </sheetData>
